--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1A87419-2772-4A45-B7AD-E28D14A3919C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE407FCC-A0AB-4842-959D-94F6C2AD0C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2557" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2580" uniqueCount="755">
   <si>
     <t>Deployment date</t>
   </si>
@@ -1606,12 +1606,6 @@
     <t>22u3742</t>
   </si>
   <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>tx (warranty below 56k)</t>
-  </si>
-  <si>
     <t>20230908</t>
   </si>
   <si>
@@ -2176,24 +2170,6 @@
     <t>GL1-GL2-GL3-GL7</t>
   </si>
   <si>
-    <t>7k</t>
-  </si>
-  <si>
-    <t>3.3</t>
-  </si>
-  <si>
-    <t>3.32</t>
-  </si>
-  <si>
-    <t>3.33</t>
-  </si>
-  <si>
-    <t>1.5k</t>
-  </si>
-  <si>
-    <t>As of Aug 2024</t>
-  </si>
-  <si>
     <t>GLI2024_SEA019_132</t>
   </si>
   <si>
@@ -2206,9 +2182,6 @@
     <t>3.6.2-r gps module</t>
   </si>
   <si>
-    <t>2k</t>
-  </si>
-  <si>
     <t>AZMP fall 2024, HL2 sampling on recovery</t>
   </si>
   <si>
@@ -2314,9 +2287,6 @@
     <t>Firmware upgrade to read sensors in lab. GPCTD swap at sea. Back and forth on Emerald basin. Rough recovery</t>
   </si>
   <si>
-    <t>Another firmware updrade with many changes like showing humidity inside glider if X3 board, and many more things.</t>
-  </si>
-  <si>
     <t>2.24.2</t>
   </si>
   <si>
@@ -2324,6 +2294,30 @@
   </si>
   <si>
     <t>3.8.2-r humidity</t>
+  </si>
+  <si>
+    <t>Sigma-T/</t>
+  </si>
+  <si>
+    <t>HL2 day after deployment, 4.2km appart</t>
+  </si>
+  <si>
+    <t>206711</t>
+  </si>
+  <si>
+    <t>Another firmware updrade with many changes like showing humidity inside glider with X3 board, and many more little things. GPCTD possibly clogged</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA022_104</t>
+  </si>
+  <si>
+    <t>20240916</t>
+  </si>
+  <si>
+    <t>duet T.ODO</t>
+  </si>
+  <si>
+    <t>feb 2025</t>
   </si>
 </sst>
 </file>
@@ -2334,7 +2328,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2408,6 +2402,13 @@
     <font>
       <sz val="11"/>
       <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2648,7 +2649,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3012,6 +3013,12 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3341,7 +3348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CW90"/>
+  <dimension ref="A1:CW95"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.1796875" customWidth="1"/>
@@ -3661,7 +3668,7 @@
         <v>222</v>
       </c>
       <c r="BL2" s="70" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="BM2" s="32" t="s">
         <v>41</v>
@@ -3673,10 +3680,10 @@
         <v>193</v>
       </c>
       <c r="BP2" s="75" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="BQ2" s="75" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="BR2" s="76" t="s">
         <v>12</v>
@@ -3705,7 +3712,7 @@
         <v>14</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I3" s="13">
         <v>29.2</v>
@@ -3878,7 +3885,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I4" s="2">
         <v>29.2</v>
@@ -4024,10 +4031,10 @@
         <v>198</v>
       </c>
       <c r="BQ4" s="18" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="BR4" s="21" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="5" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
@@ -4053,7 +4060,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="36" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="I5" s="3">
         <v>29.2</v>
@@ -4228,7 +4235,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="36" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="I6" s="3">
         <v>29.2</v>
@@ -4375,7 +4382,7 @@
         <v>197</v>
       </c>
       <c r="BQ6" s="37" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="BR6" s="43" t="s">
         <v>220</v>
@@ -4404,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="I7" s="3">
         <v>29.2</v>
@@ -4552,7 +4559,7 @@
         <v>197</v>
       </c>
       <c r="BQ7" s="37" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="BR7" s="43" t="s">
         <v>217</v>
@@ -4581,7 +4588,7 @@
         <v>15</v>
       </c>
       <c r="H8" s="36" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="I8" s="3">
         <v>29.2</v>
@@ -4727,7 +4734,7 @@
         <v>197</v>
       </c>
       <c r="BQ8" s="37" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="BR8" s="43" t="s">
         <v>218</v>
@@ -4756,7 +4763,7 @@
         <v>15</v>
       </c>
       <c r="H9" s="36" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="I9" s="3">
         <v>29.3</v>
@@ -4902,7 +4909,7 @@
         <v>197</v>
       </c>
       <c r="BQ9" s="37" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="BR9" s="43" t="s">
         <v>49</v>
@@ -4931,7 +4938,7 @@
         <v>15</v>
       </c>
       <c r="H10" s="36" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="I10" s="3">
         <v>29.2</v>
@@ -5077,7 +5084,7 @@
         <v>201</v>
       </c>
       <c r="BQ10" s="37" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="BR10" s="51" t="s">
         <v>219</v>
@@ -5106,7 +5113,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="36" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>62</v>
@@ -5252,7 +5259,7 @@
         <v>197</v>
       </c>
       <c r="BQ11" s="37" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="BR11" s="51" t="s">
         <v>106</v>
@@ -5281,7 +5288,7 @@
         <v>15</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>62</v>
@@ -5431,7 +5438,7 @@
         <v>197</v>
       </c>
       <c r="BQ12" s="37" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="BR12" s="51" t="s">
         <v>107</v>
@@ -5460,7 +5467,7 @@
         <v>129</v>
       </c>
       <c r="H13" s="36" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="I13" s="3">
         <v>29.2</v>
@@ -5608,7 +5615,7 @@
         <v>199</v>
       </c>
       <c r="BQ13" s="148" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="BR13" s="52" t="s">
         <v>242</v>
@@ -5637,7 +5644,7 @@
         <v>15</v>
       </c>
       <c r="H14" s="36" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="I14" s="3">
         <v>29.1</v>
@@ -5783,7 +5790,7 @@
         <v>197</v>
       </c>
       <c r="BQ14" s="37" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="BR14" s="43" t="s">
         <v>91</v>
@@ -5812,7 +5819,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="I15" s="3">
         <v>29.2</v>
@@ -5962,7 +5969,7 @@
         <v>197</v>
       </c>
       <c r="BQ15" s="147" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="BR15" s="43" t="s">
         <v>221</v>
@@ -5991,7 +5998,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="36" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="I16" s="3">
         <v>29.2</v>
@@ -6139,7 +6146,7 @@
         <v>197</v>
       </c>
       <c r="BQ16" s="37" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="BR16" s="43" t="s">
         <v>223</v>
@@ -6168,7 +6175,7 @@
         <v>15</v>
       </c>
       <c r="H17" s="36" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="I17" s="3">
         <v>29.2</v>
@@ -6315,7 +6322,7 @@
         <v>197</v>
       </c>
       <c r="BQ17" s="37" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="BR17" s="43" t="s">
         <v>125</v>
@@ -6344,7 +6351,7 @@
         <v>15</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="I18" s="2">
         <v>29.2</v>
@@ -6491,7 +6498,7 @@
         <v>197</v>
       </c>
       <c r="BQ18" s="18" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="BR18" s="21" t="s">
         <v>128</v>
@@ -6520,7 +6527,7 @@
         <v>14</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="I19" s="2">
         <v>29.1</v>
@@ -6661,7 +6668,7 @@
         <v>197</v>
       </c>
       <c r="BQ19" s="18" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="BR19" s="21" t="s">
         <v>133</v>
@@ -6690,7 +6697,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="I20" s="2">
         <v>29.3</v>
@@ -6837,7 +6844,7 @@
         <v>197</v>
       </c>
       <c r="BQ20" s="146" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="BR20" s="21" t="s">
         <v>224</v>
@@ -6866,7 +6873,7 @@
         <v>15</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="I21" s="2">
         <v>29.2</v>
@@ -7014,7 +7021,7 @@
         <v>197</v>
       </c>
       <c r="BQ21" s="18" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="BR21" s="21" t="s">
         <v>167</v>
@@ -7043,7 +7050,7 @@
         <v>15</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="I22" s="2">
         <v>29.2</v>
@@ -7191,7 +7198,7 @@
         <v>197</v>
       </c>
       <c r="BQ22" s="18" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="BR22" s="21" t="s">
         <v>154</v>
@@ -7220,7 +7227,7 @@
         <v>15</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="I23" s="2">
         <v>29.2</v>
@@ -7368,7 +7375,7 @@
         <v>202</v>
       </c>
       <c r="BQ23" s="146" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="BR23" s="21" t="s">
         <v>173</v>
@@ -7397,7 +7404,7 @@
         <v>129</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="I24" s="55">
         <v>29</v>
@@ -7543,7 +7550,7 @@
         <v>209</v>
       </c>
       <c r="BQ24" s="145" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="BR24" s="50" t="s">
         <v>243</v>
@@ -7572,7 +7579,7 @@
         <v>15</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="I25" s="2">
         <v>29.2</v>
@@ -7717,10 +7724,10 @@
         <v>200</v>
       </c>
       <c r="BQ25" s="146" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="BR25" s="21" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="26" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
@@ -7746,7 +7753,7 @@
         <v>15</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="I26" s="2">
         <v>29.2</v>
@@ -7895,7 +7902,7 @@
         <v>200</v>
       </c>
       <c r="BQ26" s="18" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="BR26" s="21" t="s">
         <v>179</v>
@@ -7924,7 +7931,7 @@
         <v>129</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="I27" s="2">
         <v>29.2</v>
@@ -8069,7 +8076,7 @@
         <v>208</v>
       </c>
       <c r="BQ27" s="145" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="BR27" s="50" t="s">
         <v>244</v>
@@ -8098,7 +8105,7 @@
         <v>15</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="I28" s="2">
         <v>29.2</v>
@@ -8246,7 +8253,7 @@
         <v>197</v>
       </c>
       <c r="BQ28" s="18" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="BR28" s="21" t="s">
         <v>191</v>
@@ -8275,7 +8282,7 @@
         <v>211</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="I29" s="2">
         <v>29.2</v>
@@ -8435,7 +8442,7 @@
         <v>15</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="I30" s="2">
         <v>29.1</v>
@@ -8583,7 +8590,7 @@
         <v>197</v>
       </c>
       <c r="BQ30" s="18" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="BR30" s="21" t="s">
         <v>196</v>
@@ -8612,7 +8619,7 @@
         <v>15</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="I31" s="2">
         <v>29.2</v>
@@ -8759,7 +8766,7 @@
         <v>197</v>
       </c>
       <c r="BQ31" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR31" s="21" t="s">
         <v>227</v>
@@ -8788,7 +8795,7 @@
         <v>15</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I32" s="2">
         <v>29</v>
@@ -9117,7 +9124,7 @@
         <v>15</v>
       </c>
       <c r="H35" s="36" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I35" s="3">
         <v>29.1</v>
@@ -9265,7 +9272,7 @@
         <v>262</v>
       </c>
       <c r="BQ35" s="37" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="BR35" s="43" t="s">
         <v>263</v>
@@ -9294,7 +9301,7 @@
         <v>15</v>
       </c>
       <c r="H36" s="36" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="I36" s="3">
         <v>29.3</v>
@@ -9443,7 +9450,7 @@
         <v>197</v>
       </c>
       <c r="BQ36" s="37" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR36" s="43" t="s">
         <v>255</v>
@@ -9472,7 +9479,7 @@
         <v>211</v>
       </c>
       <c r="H37" s="36" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="I37" s="3">
         <v>29.2</v>
@@ -9609,7 +9616,7 @@
         <v>197</v>
       </c>
       <c r="BQ37" s="37" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="BR37" s="43" t="s">
         <v>271</v>
@@ -9638,7 +9645,7 @@
         <v>129</v>
       </c>
       <c r="H38" s="36" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I38" s="3">
         <v>28.5</v>
@@ -9815,7 +9822,7 @@
         <v>129</v>
       </c>
       <c r="H39" s="36" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="I39" s="3">
         <v>29.1</v>
@@ -9992,7 +9999,7 @@
         <v>129</v>
       </c>
       <c r="H40" s="36" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="I40" s="3">
         <v>29.1</v>
@@ -10142,7 +10149,7 @@
         <v>208</v>
       </c>
       <c r="BQ40" s="37" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="BR40" s="43" t="s">
         <v>288</v>
@@ -10171,7 +10178,7 @@
         <v>15</v>
       </c>
       <c r="H41" s="36" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="I41" s="3">
         <v>29.1</v>
@@ -10328,7 +10335,7 @@
         <v>197</v>
       </c>
       <c r="BQ41" s="37" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="BR41" s="43" t="s">
         <v>295</v>
@@ -10357,7 +10364,7 @@
         <v>15</v>
       </c>
       <c r="H42" s="36" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="I42" s="3">
         <v>29.2</v>
@@ -10504,7 +10511,7 @@
         <v>197</v>
       </c>
       <c r="BQ42" s="147" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="BR42" s="43" t="s">
         <v>297</v>
@@ -10533,7 +10540,7 @@
         <v>15</v>
       </c>
       <c r="H43" s="36" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="I43" s="3">
         <v>29.1</v>
@@ -10678,7 +10685,7 @@
         <v>354</v>
       </c>
       <c r="BQ43" s="37" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR43" s="43" t="s">
         <v>349</v>
@@ -10707,7 +10714,7 @@
         <v>15</v>
       </c>
       <c r="H44" s="36" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="I44" s="3">
         <v>29.1</v>
@@ -10856,10 +10863,10 @@
         <v>358</v>
       </c>
       <c r="BQ44" s="37" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR44" s="43" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="45" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
@@ -10885,7 +10892,7 @@
         <v>15</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="I45" s="2">
         <v>29.1</v>
@@ -11032,7 +11039,7 @@
         <v>197</v>
       </c>
       <c r="BQ45" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR45" s="21" t="s">
         <v>369</v>
@@ -11061,7 +11068,7 @@
         <v>15</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="I46" s="2">
         <v>29.1</v>
@@ -11209,7 +11216,7 @@
         <v>376</v>
       </c>
       <c r="BQ46" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="BR46" s="21" t="s">
         <v>377</v>
@@ -11238,7 +11245,7 @@
         <v>15</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="I47" s="2">
         <v>29</v>
@@ -11385,7 +11392,7 @@
         <v>197</v>
       </c>
       <c r="BQ47" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR47" s="21" t="s">
         <v>383</v>
@@ -11414,7 +11421,7 @@
         <v>211</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="I48" s="2">
         <v>29.2</v>
@@ -11561,7 +11568,7 @@
         <v>197</v>
       </c>
       <c r="BQ48" s="18" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="BR48" s="21" t="s">
         <v>400</v>
@@ -11587,10 +11594,10 @@
         <v>4800994</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="I49" s="2">
         <v>28.9</v>
@@ -11775,7 +11782,7 @@
         <v>15</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="I50" s="2">
         <v>29.1</v>
@@ -11922,7 +11929,7 @@
         <v>354</v>
       </c>
       <c r="BQ50" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR50" s="21" t="s">
         <v>398</v>
@@ -11951,7 +11958,7 @@
         <v>211</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="I51" s="2">
         <v>29.2</v>
@@ -12098,7 +12105,7 @@
         <v>354</v>
       </c>
       <c r="BQ51" s="18" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="BR51" s="21" t="s">
         <v>399</v>
@@ -12127,7 +12134,7 @@
         <v>129</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="I52" s="2">
         <v>28.8</v>
@@ -12312,7 +12319,7 @@
         <v>129</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="I53" s="2">
         <v>28.9</v>
@@ -12469,7 +12476,7 @@
         <v>208</v>
       </c>
       <c r="BQ53" s="18" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="BR53" s="21" t="s">
         <v>417</v>
@@ -12498,7 +12505,7 @@
         <v>15</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="I54" s="2">
         <v>29.1</v>
@@ -12647,7 +12654,7 @@
         <v>197</v>
       </c>
       <c r="BQ54" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR54" s="21" t="s">
         <v>409</v>
@@ -12676,7 +12683,7 @@
         <v>211</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="I55" s="2">
         <v>29.2</v>
@@ -12825,7 +12832,7 @@
         <v>197</v>
       </c>
       <c r="BQ55" s="18" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="BR55" s="21" t="s">
         <v>419</v>
@@ -12854,7 +12861,7 @@
         <v>129</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="I56" s="2">
         <v>28.9</v>
@@ -13016,7 +13023,7 @@
         <v>424</v>
       </c>
       <c r="BQ56" s="18" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="BR56" s="21" t="s">
         <v>426</v>
@@ -13045,7 +13052,7 @@
         <v>15</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="I57" s="2">
         <v>29.1</v>
@@ -13193,7 +13200,7 @@
         <v>197</v>
       </c>
       <c r="BQ57" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR57" s="21" t="s">
         <v>427</v>
@@ -13369,7 +13376,7 @@
         <v>354</v>
       </c>
       <c r="BQ58" s="18" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="BR58" s="21" t="s">
         <v>509</v>
@@ -13398,7 +13405,7 @@
         <v>15</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="I59" s="2">
         <v>29.1</v>
@@ -13557,7 +13564,7 @@
         <v>202</v>
       </c>
       <c r="BQ59" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR59" s="21" t="s">
         <v>396</v>
@@ -13586,7 +13593,7 @@
         <v>15</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="I60" s="3">
         <v>29.1</v>
@@ -13733,7 +13740,7 @@
         <v>197</v>
       </c>
       <c r="BQ60" s="37" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR60" s="43" t="s">
         <v>442</v>
@@ -13762,7 +13769,7 @@
         <v>15</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="I61" s="3">
         <v>29</v>
@@ -13909,10 +13916,10 @@
         <v>197</v>
       </c>
       <c r="BQ61" s="37" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="BR61" s="43" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="62" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
@@ -13938,7 +13945,7 @@
         <v>129</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="I62" s="48">
         <v>29.1</v>
@@ -14095,10 +14102,10 @@
         <v>208</v>
       </c>
       <c r="BQ62" s="37" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="BR62" s="43" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="63" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
@@ -14124,7 +14131,7 @@
         <v>15</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="I63" s="3">
         <v>29.2</v>
@@ -14280,7 +14287,7 @@
       </c>
       <c r="BQ63" s="37"/>
       <c r="BR63" s="43" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="64" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
@@ -14306,7 +14313,7 @@
         <v>15</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="I64" s="3">
         <v>29.2</v>
@@ -14453,7 +14460,7 @@
         <v>202</v>
       </c>
       <c r="BQ64" s="37" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="BR64" s="43" t="s">
         <v>510</v>
@@ -14482,7 +14489,7 @@
         <v>15</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="I65" s="2">
         <v>29.2</v>
@@ -14641,7 +14648,7 @@
       </c>
       <c r="BQ65" s="18"/>
       <c r="BR65" s="21" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="66" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.35">
@@ -14667,7 +14674,7 @@
         <v>15</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="I66" s="2">
         <v>29.2</v>
@@ -14817,10 +14824,10 @@
         <v>197</v>
       </c>
       <c r="BQ66" s="18" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="BR66" s="21" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="67" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.35">
@@ -14846,7 +14853,7 @@
         <v>15</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="I67" s="2">
         <v>29.2</v>
@@ -14996,7 +15003,7 @@
         <v>503</v>
       </c>
       <c r="BQ67" s="18" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="BR67" s="21" t="s">
         <v>505</v>
@@ -15025,7 +15032,7 @@
         <v>129</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="I68" s="2">
         <v>29.2</v>
@@ -15185,10 +15192,10 @@
         <v>513</v>
       </c>
       <c r="BQ68" s="18" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="BR68" s="21" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="69" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.35">
@@ -15196,10 +15203,10 @@
         <v>5</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D69" s="14" t="s">
         <v>13</v>
@@ -15214,7 +15221,7 @@
         <v>15</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="I69" s="2">
         <v>29.1</v>
@@ -15352,7 +15359,7 @@
       </c>
       <c r="BL69" s="22"/>
       <c r="BM69" s="97" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="BN69" s="2" t="s">
         <v>206</v>
@@ -15365,7 +15372,7 @@
       </c>
       <c r="BQ69" s="18"/>
       <c r="BR69" s="21" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="70" spans="1:101" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -15391,7 +15398,7 @@
         <v>15</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="I70" s="2">
         <v>29.1</v>
@@ -15421,7 +15428,7 @@
         <v>-61.4</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="S70" s="2">
         <v>20</v>
@@ -15514,7 +15521,7 @@
         <v>451</v>
       </c>
       <c r="BB70" s="22" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="BC70" s="22" t="s">
         <v>420</v>
@@ -15550,7 +15557,7 @@
       </c>
       <c r="BQ70" s="18"/>
       <c r="BR70" s="21" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="71" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -15576,7 +15583,7 @@
         <v>15</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="I71" s="2">
         <v>29.1</v>
@@ -15606,7 +15613,7 @@
         <v>-61.44</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="S71" s="2">
         <v>23</v>
@@ -15655,7 +15662,7 @@
         <v>20240131</v>
       </c>
       <c r="AJ71" s="18" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AK71" s="18" t="s">
         <v>464</v>
@@ -15699,7 +15706,7 @@
         <v>451</v>
       </c>
       <c r="BB71" s="22" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="BC71" s="22" t="s">
         <v>420</v>
@@ -15735,7 +15742,7 @@
       </c>
       <c r="BQ71" s="18"/>
       <c r="BR71" s="21" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="BS71" s="88"/>
       <c r="BT71" s="88"/>
@@ -15792,7 +15799,7 @@
         <v>15</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="I72" s="2">
         <v>29.1</v>
@@ -15822,7 +15829,7 @@
         <v>-61.43</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="S72" s="2">
         <v>26</v>
@@ -15868,7 +15875,7 @@
         <v>20240306</v>
       </c>
       <c r="AJ72" s="18" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AK72" s="18" t="s">
         <v>464</v>
@@ -15880,7 +15887,7 @@
         <v>81</v>
       </c>
       <c r="AN72" s="22" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="AO72" s="22" t="s">
         <v>212</v>
@@ -15892,7 +15899,7 @@
         <v>83</v>
       </c>
       <c r="AR72" s="22" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AS72" s="22"/>
       <c r="AT72" s="22"/>
@@ -15941,10 +15948,10 @@
         <v>197</v>
       </c>
       <c r="BQ72" s="18" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="BR72" s="21" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="BS72" s="88"/>
       <c r="BT72" s="88"/>
@@ -16001,7 +16008,7 @@
         <v>15</v>
       </c>
       <c r="H73" s="37" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="I73" s="3">
         <v>29.1</v>
@@ -16031,7 +16038,7 @@
         <v>-61.42</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="S73" s="3">
         <v>20</v>
@@ -16078,7 +16085,7 @@
         <v>20240322</v>
       </c>
       <c r="AJ73" s="37" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AK73" s="37" t="s">
         <v>464</v>
@@ -16090,7 +16097,7 @@
         <v>76</v>
       </c>
       <c r="AN73" s="38" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AO73" s="38" t="s">
         <v>212</v>
@@ -16102,7 +16109,7 @@
         <v>78</v>
       </c>
       <c r="AR73" s="38" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AS73" s="38"/>
       <c r="AT73" s="38"/>
@@ -16141,10 +16148,10 @@
       </c>
       <c r="BL73" s="38"/>
       <c r="BM73" s="3" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="BN73" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="BO73" s="3" t="s">
         <v>205</v>
@@ -16154,7 +16161,7 @@
       </c>
       <c r="BQ73" s="37"/>
       <c r="BR73" s="43" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="74" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -16180,7 +16187,7 @@
         <v>15</v>
       </c>
       <c r="H74" s="37" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="I74" s="3">
         <v>29.2</v>
@@ -16257,7 +16264,7 @@
         <v>20240322</v>
       </c>
       <c r="AJ74" s="37" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AK74" s="37" t="s">
         <v>464</v>
@@ -16269,7 +16276,7 @@
         <v>76</v>
       </c>
       <c r="AN74" s="38" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AO74" s="38" t="s">
         <v>212</v>
@@ -16281,7 +16288,7 @@
         <v>78</v>
       </c>
       <c r="AR74" s="38" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AS74" s="38"/>
       <c r="AT74" s="38"/>
@@ -16321,7 +16328,7 @@
       <c r="BL74" s="38"/>
       <c r="BM74" s="3"/>
       <c r="BN74" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="BO74" s="3" t="s">
         <v>205</v>
@@ -16331,7 +16338,7 @@
       </c>
       <c r="BQ74" s="37"/>
       <c r="BR74" s="43" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="75" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -16357,7 +16364,7 @@
         <v>129</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I75" s="3">
         <v>29.1</v>
@@ -16387,7 +16394,7 @@
         <v>-51.84</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="S75" s="3">
         <v>11</v>
@@ -16436,7 +16443,7 @@
         <v>20240403</v>
       </c>
       <c r="AJ75" s="37" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AK75" s="37" t="s">
         <v>464</v>
@@ -16498,7 +16505,7 @@
         <v>95</v>
       </c>
       <c r="BJ75" s="38" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="BK75" s="38"/>
       <c r="BL75" s="38"/>
@@ -16510,11 +16517,11 @@
         <v>205</v>
       </c>
       <c r="BP75" s="37" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="BQ75" s="37"/>
       <c r="BR75" s="43" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="76" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -16540,7 +16547,7 @@
         <v>15</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="I76" s="3">
         <v>29.1</v>
@@ -16617,7 +16624,7 @@
         <v>20240322</v>
       </c>
       <c r="AJ76" s="37" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AK76" s="37" t="s">
         <v>464</v>
@@ -16629,7 +16636,7 @@
         <v>76</v>
       </c>
       <c r="AN76" s="38" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AO76" s="38" t="s">
         <v>212</v>
@@ -16641,7 +16648,7 @@
         <v>78</v>
       </c>
       <c r="AR76" s="38" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AS76" s="38"/>
       <c r="AT76" s="38"/>
@@ -16673,7 +16680,7 @@
         <v>117</v>
       </c>
       <c r="BJ76" s="38" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="BK76" s="92" t="s">
         <v>137</v>
@@ -16681,7 +16688,7 @@
       <c r="BL76" s="38"/>
       <c r="BM76" s="3"/>
       <c r="BN76" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="BO76" s="3" t="s">
         <v>205</v>
@@ -16715,7 +16722,7 @@
         <v>15</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="I77" s="3">
         <v>29.2</v>
@@ -16745,7 +16752,7 @@
         <v>-61.46</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="S77" s="3">
         <v>25</v>
@@ -16792,7 +16799,7 @@
         <v>20240821</v>
       </c>
       <c r="AJ77" s="37" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AK77" s="37" t="s">
         <v>464</v>
@@ -16804,7 +16811,7 @@
         <v>76</v>
       </c>
       <c r="AN77" s="38" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AO77" s="38" t="s">
         <v>212</v>
@@ -16816,7 +16823,7 @@
         <v>78</v>
       </c>
       <c r="AR77" s="38" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AS77" s="38"/>
       <c r="AT77" s="38"/>
@@ -16858,19 +16865,19 @@
       </c>
       <c r="BM77" s="3"/>
       <c r="BN77" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="BO77" s="3" t="s">
         <v>205</v>
       </c>
       <c r="BP77" s="37" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="BQ77" s="37" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="BR77" s="43" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
     </row>
     <row r="78" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -16896,7 +16903,7 @@
         <v>15</v>
       </c>
       <c r="H78" s="37" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="I78" s="3">
         <v>29.1</v>
@@ -16926,7 +16933,7 @@
         <v>-61.41</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="S78" s="3">
         <v>20</v>
@@ -16973,7 +16980,7 @@
         <v>20240822</v>
       </c>
       <c r="AJ78" s="37" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AK78" s="37" t="s">
         <v>464</v>
@@ -16985,7 +16992,7 @@
         <v>69</v>
       </c>
       <c r="AN78" s="46" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AO78" s="38" t="s">
         <v>212</v>
@@ -16997,7 +17004,7 @@
         <v>71</v>
       </c>
       <c r="AR78" s="46" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="AS78" s="38"/>
       <c r="AT78" s="38"/>
@@ -17029,7 +17036,7 @@
         <v>117</v>
       </c>
       <c r="BJ78" s="38" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="BK78" s="92" t="s">
         <v>137</v>
@@ -17038,10 +17045,10 @@
         <v>1272212</v>
       </c>
       <c r="BM78" s="3" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="BN78" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="BO78" s="3" t="s">
         <v>205</v>
@@ -17051,7 +17058,7 @@
       </c>
       <c r="BQ78" s="37"/>
       <c r="BR78" s="43" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
     </row>
     <row r="79" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -17077,7 +17084,7 @@
         <v>15</v>
       </c>
       <c r="H79" s="37" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="I79" s="3">
         <v>29.1</v>
@@ -17107,7 +17114,7 @@
         <v>-61.44</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="S79" s="3">
         <v>26</v>
@@ -17154,10 +17161,10 @@
         <v>20241015</v>
       </c>
       <c r="AJ79" s="37" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="AK79" s="37" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="AL79" s="35">
         <v>33</v>
@@ -17166,7 +17173,7 @@
         <v>69</v>
       </c>
       <c r="AN79" s="46" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AO79" s="38" t="s">
         <v>212</v>
@@ -17178,7 +17185,7 @@
         <v>71</v>
       </c>
       <c r="AR79" s="46" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="AS79" s="38"/>
       <c r="AT79" s="38"/>
@@ -17210,19 +17217,19 @@
         <v>95</v>
       </c>
       <c r="BJ79" s="38" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="BK79" s="92" t="s">
         <v>138</v>
       </c>
       <c r="BL79" s="38" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="BM79" s="3" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="BN79" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="BO79" s="3" t="s">
         <v>205</v>
@@ -17232,12 +17239,16 @@
       </c>
       <c r="BQ79" s="37"/>
       <c r="BR79" s="43" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
     </row>
     <row r="80" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="137"/>
-      <c r="B80" s="35"/>
+      <c r="A80" s="137">
+        <v>8</v>
+      </c>
+      <c r="B80" s="35">
+        <v>20250211</v>
+      </c>
       <c r="C80" s="35"/>
       <c r="D80" s="35" t="s">
         <v>13</v>
@@ -17252,13 +17263,21 @@
         <v>15</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>755</v>
-      </c>
-      <c r="I80" s="3"/>
+        <v>745</v>
+      </c>
+      <c r="I80" s="3">
+        <v>29.1</v>
+      </c>
       <c r="J80" s="3"/>
-      <c r="K80" s="35"/>
-      <c r="L80" s="35"/>
-      <c r="M80" s="138"/>
+      <c r="K80" s="35">
+        <v>44.488300000000002</v>
+      </c>
+      <c r="L80" s="35">
+        <v>-63.358699999999999</v>
+      </c>
+      <c r="M80" s="138">
+        <v>0.68819444444444444</v>
+      </c>
       <c r="N80" s="37"/>
       <c r="O80" s="37"/>
       <c r="P80" s="37"/>
@@ -17296,10 +17315,10 @@
         <v>20250131</v>
       </c>
       <c r="AJ80" s="37" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="AK80" s="37" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="AL80" s="35">
         <v>33</v>
@@ -17308,7 +17327,7 @@
         <v>69</v>
       </c>
       <c r="AN80" s="46" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AO80" s="38" t="s">
         <v>212</v>
@@ -17320,7 +17339,7 @@
         <v>71</v>
       </c>
       <c r="AR80" s="46" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="AS80" s="38"/>
       <c r="AT80" s="38"/>
@@ -17354,34 +17373,50 @@
       <c r="BJ80" s="38" t="s">
         <v>516</v>
       </c>
-      <c r="BK80" s="133" t="s">
+      <c r="BK80" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="BL80" s="133" t="s">
-        <v>714</v>
-      </c>
-      <c r="BM80" s="3"/>
+      <c r="BL80" s="38" t="s">
+        <v>706</v>
+      </c>
+      <c r="BM80" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="BN80" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="BO80" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP80" s="37"/>
+      <c r="BP80" s="37" t="s">
+        <v>747</v>
+      </c>
       <c r="BQ80" s="37"/>
       <c r="BR80" s="43" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="81" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="137"/>
+      <c r="A81" s="137">
+        <v>9</v>
+      </c>
       <c r="B81" s="35"/>
       <c r="C81" s="35"/>
-      <c r="D81" s="35"/>
-      <c r="E81" s="35"/>
-      <c r="F81" s="35"/>
-      <c r="G81" s="35"/>
-      <c r="H81" s="37"/>
+      <c r="D81" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E81" s="35">
+        <v>104</v>
+      </c>
+      <c r="F81" s="35">
+        <v>4800993</v>
+      </c>
+      <c r="G81" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" s="37" t="s">
+        <v>751</v>
+      </c>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
       <c r="K81" s="35"/>
@@ -17391,65 +17426,123 @@
       <c r="O81" s="37"/>
       <c r="P81" s="37"/>
       <c r="Q81" s="37"/>
-      <c r="R81" s="3"/>
+      <c r="R81" s="3" t="s">
+        <v>472</v>
+      </c>
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
       <c r="U81" s="3"/>
       <c r="V81" s="3"/>
-      <c r="W81" s="37"/>
-      <c r="X81" s="37"/>
-      <c r="Y81" s="37"/>
-      <c r="Z81" s="37"/>
+      <c r="W81" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="X81" s="37">
+        <v>1</v>
+      </c>
+      <c r="Y81" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z81" s="37" t="s">
+        <v>183</v>
+      </c>
       <c r="AA81" s="37"/>
       <c r="AB81" s="37"/>
-      <c r="AC81" s="37"/>
+      <c r="AC81" s="37" t="s">
+        <v>462</v>
+      </c>
       <c r="AD81" s="37"/>
       <c r="AE81" s="3"/>
       <c r="AF81" s="3"/>
       <c r="AG81" s="3"/>
-      <c r="AH81" s="3"/>
-      <c r="AI81" s="37"/>
-      <c r="AJ81" s="37"/>
-      <c r="AK81" s="37"/>
-      <c r="AL81" s="35"/>
-      <c r="AM81" s="34"/>
-      <c r="AN81" s="38"/>
-      <c r="AO81" s="38"/>
-      <c r="AP81" s="34"/>
-      <c r="AQ81" s="34"/>
-      <c r="AR81" s="38"/>
+      <c r="AH81" s="3">
+        <v>1024.9000000000001</v>
+      </c>
+      <c r="AI81" s="37">
+        <v>20250218</v>
+      </c>
+      <c r="AJ81" s="37" t="s">
+        <v>746</v>
+      </c>
+      <c r="AK81" s="37" t="s">
+        <v>744</v>
+      </c>
+      <c r="AL81" s="35">
+        <v>30</v>
+      </c>
+      <c r="AM81" s="144" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN81" s="46" t="s">
+        <v>678</v>
+      </c>
+      <c r="AO81" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="AP81" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="AQ81" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR81" s="46" t="s">
+        <v>681</v>
+      </c>
       <c r="AS81" s="38"/>
       <c r="AT81" s="38"/>
       <c r="AU81" s="38"/>
-      <c r="AV81" s="41"/>
-      <c r="AW81" s="39"/>
-      <c r="AX81" s="38"/>
+      <c r="AV81" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW81" s="39">
+        <v>42723</v>
+      </c>
+      <c r="AX81" s="38" t="s">
+        <v>461</v>
+      </c>
       <c r="AY81" s="38"/>
       <c r="AZ81" s="38"/>
-      <c r="BA81" s="38"/>
-      <c r="BB81" s="38"/>
-      <c r="BC81" s="38"/>
+      <c r="BA81" s="38" t="s">
+        <v>451</v>
+      </c>
+      <c r="BB81" s="38" t="s">
+        <v>752</v>
+      </c>
+      <c r="BC81" s="38" t="s">
+        <v>420</v>
+      </c>
       <c r="BD81" s="38"/>
       <c r="BE81" s="38"/>
       <c r="BF81" s="38"/>
-      <c r="BG81" s="34"/>
-      <c r="BH81" s="139"/>
-      <c r="BI81" s="38"/>
+      <c r="BG81" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="BH81" s="96" t="s">
+        <v>171</v>
+      </c>
+      <c r="BI81" s="38" t="s">
+        <v>95</v>
+      </c>
       <c r="BJ81" s="38" t="s">
-        <v>712</v>
+        <v>588</v>
       </c>
       <c r="BK81" s="38" t="s">
-        <v>517</v>
-      </c>
-      <c r="BL81" s="38"/>
-      <c r="BM81" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="BN81" s="120"/>
-      <c r="BO81" s="35"/>
+        <v>749</v>
+      </c>
+      <c r="BL81" s="3">
+        <v>1540746</v>
+      </c>
+      <c r="BM81" s="3"/>
+      <c r="BN81" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="BO81" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="BP81" s="37"/>
       <c r="BQ81" s="37"/>
-      <c r="BR81" s="43"/>
+      <c r="BR81" s="43" t="s">
+        <v>753</v>
+      </c>
     </row>
     <row r="82" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="137"/>
@@ -17464,7 +17557,7 @@
       <c r="J82" s="3"/>
       <c r="K82" s="35"/>
       <c r="L82" s="35"/>
-      <c r="M82" s="3"/>
+      <c r="M82" s="138"/>
       <c r="N82" s="37"/>
       <c r="O82" s="37"/>
       <c r="P82" s="37"/>
@@ -17490,17 +17583,17 @@
       <c r="AJ82" s="37"/>
       <c r="AK82" s="37"/>
       <c r="AL82" s="35"/>
-      <c r="AM82" s="34"/>
-      <c r="AN82" s="38"/>
+      <c r="AM82" s="144"/>
+      <c r="AN82" s="46"/>
       <c r="AO82" s="38"/>
-      <c r="AP82" s="34"/>
-      <c r="AQ82" s="34"/>
-      <c r="AR82" s="38"/>
+      <c r="AP82" s="41"/>
+      <c r="AQ82" s="41"/>
+      <c r="AR82" s="46"/>
       <c r="AS82" s="38"/>
       <c r="AT82" s="38"/>
       <c r="AU82" s="38"/>
-      <c r="AV82" s="34"/>
-      <c r="AW82" s="38"/>
+      <c r="AV82" s="41"/>
+      <c r="AW82" s="39"/>
       <c r="AX82" s="38"/>
       <c r="AY82" s="38"/>
       <c r="AZ82" s="38"/>
@@ -17512,363 +17605,382 @@
       <c r="BF82" s="38"/>
       <c r="BG82" s="34"/>
       <c r="BH82" s="139"/>
-      <c r="BI82" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="BJ82" s="133" t="s">
-        <v>287</v>
-      </c>
-      <c r="BK82" s="38"/>
-      <c r="BL82" s="38"/>
+      <c r="BI82" s="38"/>
+      <c r="BJ82" s="38"/>
+      <c r="BK82" s="133"/>
+      <c r="BL82" s="133"/>
       <c r="BM82" s="3"/>
-      <c r="BN82" s="120"/>
-      <c r="BO82" s="35"/>
+      <c r="BN82" s="151"/>
+      <c r="BO82" s="3"/>
       <c r="BP82" s="37"/>
       <c r="BQ82" s="37"/>
       <c r="BR82" s="43"/>
     </row>
-    <row r="83" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="116"/>
-      <c r="C83" s="116"/>
-      <c r="D83" s="116"/>
-      <c r="E83" s="116"/>
-      <c r="F83" s="116"/>
-      <c r="G83" s="116"/>
-      <c r="H83" s="77"/>
-      <c r="K83" s="116"/>
-      <c r="L83" s="116"/>
-      <c r="N83" s="77"/>
-      <c r="O83" s="77"/>
-      <c r="P83" s="77"/>
-      <c r="Q83" s="77"/>
-      <c r="W83" s="77"/>
-      <c r="X83" s="77"/>
-      <c r="Y83" s="77"/>
-      <c r="Z83" s="77"/>
-      <c r="AA83" s="77"/>
-      <c r="AB83" s="77"/>
-      <c r="AC83" s="77"/>
-      <c r="AD83" s="77"/>
-      <c r="AI83" s="77"/>
-      <c r="AJ83" s="77"/>
-      <c r="AK83" s="77"/>
-      <c r="AL83" s="116"/>
-      <c r="AM83" s="140" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN83" s="141" t="s">
-        <v>691</v>
-      </c>
-      <c r="AO83" s="142"/>
-      <c r="AP83" s="143"/>
-      <c r="AQ83" s="140" t="s">
-        <v>681</v>
-      </c>
-      <c r="AR83" s="141" t="s">
-        <v>690</v>
-      </c>
-      <c r="AS83" s="78"/>
-      <c r="AT83" s="78"/>
-      <c r="AU83" s="78"/>
-      <c r="AV83" s="117"/>
-      <c r="AW83" s="78"/>
-      <c r="AX83" s="78"/>
-      <c r="AY83" s="78"/>
-      <c r="AZ83" s="78"/>
-      <c r="BA83" s="78"/>
-      <c r="BB83" s="78"/>
-      <c r="BC83" s="78"/>
-      <c r="BD83" s="78"/>
-      <c r="BE83" s="78"/>
-      <c r="BF83" s="78"/>
-      <c r="BG83" s="117"/>
-      <c r="BH83" s="118"/>
-      <c r="BI83" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="BJ83" s="38" t="s">
-        <v>590</v>
-      </c>
-      <c r="BK83" s="38" t="s">
-        <v>709</v>
-      </c>
-      <c r="BL83" s="38"/>
-      <c r="BM83" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="BN83" s="121"/>
-      <c r="BO83" s="45"/>
-      <c r="BP83" s="77"/>
-      <c r="BQ83" s="77"/>
-      <c r="BR83" s="119"/>
+    <row r="83" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="137"/>
+      <c r="B83" s="35"/>
+      <c r="C83" s="35"/>
+      <c r="D83" s="35"/>
+      <c r="E83" s="35"/>
+      <c r="F83" s="35"/>
+      <c r="G83" s="35"/>
+      <c r="H83" s="37"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="35"/>
+      <c r="L83" s="35"/>
+      <c r="M83" s="138"/>
+      <c r="N83" s="37"/>
+      <c r="O83" s="37"/>
+      <c r="P83" s="37"/>
+      <c r="Q83" s="37"/>
+      <c r="R83" s="3"/>
+      <c r="S83" s="3"/>
+      <c r="T83" s="3"/>
+      <c r="U83" s="3"/>
+      <c r="V83" s="3"/>
+      <c r="W83" s="37"/>
+      <c r="X83" s="37"/>
+      <c r="Y83" s="37"/>
+      <c r="Z83" s="37"/>
+      <c r="AA83" s="37"/>
+      <c r="AB83" s="37"/>
+      <c r="AC83" s="37"/>
+      <c r="AD83" s="37"/>
+      <c r="AE83" s="3"/>
+      <c r="AF83" s="3"/>
+      <c r="AG83" s="3"/>
+      <c r="AH83" s="3"/>
+      <c r="AI83" s="37"/>
+      <c r="AJ83" s="37"/>
+      <c r="AK83" s="37"/>
+      <c r="AL83" s="35"/>
+      <c r="AM83" s="144"/>
+      <c r="AN83" s="46"/>
+      <c r="AO83" s="38"/>
+      <c r="AP83" s="41"/>
+      <c r="AQ83" s="41"/>
+      <c r="AR83" s="46"/>
+      <c r="AS83" s="38"/>
+      <c r="AT83" s="38"/>
+      <c r="AU83" s="38"/>
+      <c r="AV83" s="41"/>
+      <c r="AW83" s="39"/>
+      <c r="AX83" s="38"/>
+      <c r="AY83" s="38"/>
+      <c r="AZ83" s="38"/>
+      <c r="BA83" s="38"/>
+      <c r="BB83" s="38"/>
+      <c r="BC83" s="38"/>
+      <c r="BD83" s="38"/>
+      <c r="BE83" s="38"/>
+      <c r="BF83" s="38"/>
+      <c r="BG83" s="34"/>
+      <c r="BH83" s="139"/>
+      <c r="BI83" s="38"/>
+      <c r="BJ83" s="38"/>
+      <c r="BK83" s="133"/>
+      <c r="BL83" s="133"/>
+      <c r="BM83" s="3"/>
+      <c r="BN83" s="151"/>
+      <c r="BO83" s="3"/>
+      <c r="BP83" s="37"/>
+      <c r="BQ83" s="37"/>
+      <c r="BR83" s="43"/>
     </row>
-    <row r="84" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="116"/>
-      <c r="C84" s="116"/>
-      <c r="D84" s="116"/>
-      <c r="E84" s="116"/>
-      <c r="F84" s="116"/>
-      <c r="G84" s="116"/>
-      <c r="H84" s="77"/>
-      <c r="K84" s="116"/>
-      <c r="L84" s="116"/>
-      <c r="N84" s="77"/>
-      <c r="O84" s="77"/>
-      <c r="P84" s="77"/>
-      <c r="Q84" s="77"/>
-      <c r="W84" s="77"/>
-      <c r="X84" s="77"/>
-      <c r="Y84" s="77"/>
-      <c r="Z84" s="77"/>
-      <c r="AA84" s="77"/>
-      <c r="AB84" s="77"/>
-      <c r="AC84" s="77"/>
-      <c r="AD84" s="77"/>
-      <c r="AI84" s="77"/>
-      <c r="AJ84" s="77"/>
-      <c r="AK84" s="77"/>
-      <c r="AL84" s="116"/>
-      <c r="AM84" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN84" s="26" t="s">
-        <v>680</v>
-      </c>
-      <c r="AO84" s="78"/>
-      <c r="AP84" s="117"/>
-      <c r="AQ84" s="27" t="s">
-        <v>682</v>
-      </c>
-      <c r="AR84" s="26" t="s">
-        <v>683</v>
-      </c>
-      <c r="AS84" s="78"/>
-      <c r="AT84" s="78"/>
-      <c r="AU84" s="78"/>
-      <c r="AV84" s="117"/>
-      <c r="AW84" s="78"/>
-      <c r="AX84" s="78"/>
-      <c r="AY84" s="78"/>
-      <c r="AZ84" s="78"/>
-      <c r="BA84" s="78"/>
-      <c r="BB84" s="78"/>
-      <c r="BC84" s="78"/>
-      <c r="BD84" s="78"/>
-      <c r="BE84" s="78"/>
-      <c r="BF84" s="78"/>
-      <c r="BG84" s="117"/>
-      <c r="BH84" s="118"/>
-      <c r="BI84" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="BJ84" s="150" t="s">
-        <v>591</v>
-      </c>
-      <c r="BK84" s="38" t="s">
-        <v>710</v>
-      </c>
-      <c r="BL84" s="38"/>
-      <c r="BM84" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="BN84" s="120"/>
-      <c r="BO84" s="35"/>
-      <c r="BP84" s="77"/>
-      <c r="BQ84" s="77"/>
-      <c r="BR84" s="119"/>
+    <row r="84" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="137"/>
+      <c r="B84" s="35"/>
+      <c r="C84" s="35"/>
+      <c r="D84" s="35"/>
+      <c r="E84" s="35"/>
+      <c r="F84" s="35"/>
+      <c r="G84" s="35"/>
+      <c r="H84" s="37"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="35"/>
+      <c r="L84" s="35"/>
+      <c r="M84" s="138"/>
+      <c r="N84" s="37"/>
+      <c r="O84" s="37"/>
+      <c r="P84" s="37"/>
+      <c r="Q84" s="37"/>
+      <c r="R84" s="3"/>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="37"/>
+      <c r="X84" s="37"/>
+      <c r="Y84" s="37"/>
+      <c r="Z84" s="37"/>
+      <c r="AA84" s="37"/>
+      <c r="AB84" s="37"/>
+      <c r="AC84" s="37"/>
+      <c r="AD84" s="37"/>
+      <c r="AE84" s="3"/>
+      <c r="AF84" s="3"/>
+      <c r="AG84" s="3"/>
+      <c r="AH84" s="3"/>
+      <c r="AI84" s="37"/>
+      <c r="AJ84" s="37"/>
+      <c r="AK84" s="37"/>
+      <c r="AL84" s="35"/>
+      <c r="AM84" s="144"/>
+      <c r="AN84" s="46"/>
+      <c r="AO84" s="38"/>
+      <c r="AP84" s="41"/>
+      <c r="AQ84" s="41"/>
+      <c r="AR84" s="46"/>
+      <c r="AS84" s="38"/>
+      <c r="AT84" s="38"/>
+      <c r="AU84" s="38"/>
+      <c r="AV84" s="41"/>
+      <c r="AW84" s="39"/>
+      <c r="AX84" s="38"/>
+      <c r="AY84" s="38"/>
+      <c r="AZ84" s="38"/>
+      <c r="BA84" s="38"/>
+      <c r="BB84" s="38"/>
+      <c r="BC84" s="38"/>
+      <c r="BD84" s="38"/>
+      <c r="BE84" s="38"/>
+      <c r="BF84" s="38"/>
+      <c r="BG84" s="34"/>
+      <c r="BH84" s="139"/>
+      <c r="BI84" s="38"/>
+      <c r="BJ84" s="38"/>
+      <c r="BK84" s="133"/>
+      <c r="BL84" s="133"/>
+      <c r="BM84" s="3"/>
+      <c r="BN84" s="151"/>
+      <c r="BO84" s="3"/>
+      <c r="BP84" s="37"/>
+      <c r="BQ84" s="37"/>
+      <c r="BR84" s="43"/>
     </row>
-    <row r="85" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="116"/>
-      <c r="C85" s="116"/>
-      <c r="D85" s="116"/>
-      <c r="E85" s="116"/>
-      <c r="F85" s="116"/>
-      <c r="G85" s="116"/>
-      <c r="H85" s="77"/>
-      <c r="K85" s="116"/>
-      <c r="L85" s="116"/>
-      <c r="N85" s="77"/>
-      <c r="O85" s="77"/>
-      <c r="P85" s="77"/>
-      <c r="Q85" s="77"/>
-      <c r="W85" s="77"/>
-      <c r="X85" s="77"/>
-      <c r="Y85" s="77"/>
-      <c r="Z85" s="77"/>
-      <c r="AA85" s="77"/>
-      <c r="AB85" s="77"/>
-      <c r="AC85" s="77"/>
-      <c r="AD85" s="77"/>
-      <c r="AI85" s="77"/>
-      <c r="AJ85" s="77"/>
-      <c r="AK85" s="77"/>
-      <c r="AL85" s="116"/>
-      <c r="AM85" s="117"/>
-      <c r="AN85" s="78"/>
-      <c r="AO85" s="78"/>
-      <c r="AP85" s="117"/>
-      <c r="AQ85" s="117"/>
-      <c r="AR85" s="78"/>
-      <c r="AS85" s="78"/>
-      <c r="AT85" s="78"/>
-      <c r="AU85" s="78"/>
-      <c r="AV85" s="117"/>
-      <c r="AW85" s="78"/>
-      <c r="AX85" s="78"/>
-      <c r="AY85" s="78"/>
-      <c r="AZ85" s="78"/>
-      <c r="BA85" s="78"/>
-      <c r="BB85" s="78"/>
-      <c r="BC85" s="78"/>
-      <c r="BD85" s="78"/>
-      <c r="BE85" s="78"/>
-      <c r="BF85" s="78"/>
-      <c r="BG85" s="117"/>
-      <c r="BH85" s="118"/>
-      <c r="BI85" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="BJ85" s="133" t="s">
-        <v>453</v>
-      </c>
+    <row r="85" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="137"/>
+      <c r="B85" s="35"/>
+      <c r="C85" s="35"/>
+      <c r="D85" s="35"/>
+      <c r="E85" s="35"/>
+      <c r="F85" s="35"/>
+      <c r="G85" s="35"/>
+      <c r="H85" s="37"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="35"/>
+      <c r="L85" s="35"/>
+      <c r="M85" s="138"/>
+      <c r="N85" s="37"/>
+      <c r="O85" s="37"/>
+      <c r="P85" s="37"/>
+      <c r="Q85" s="37"/>
+      <c r="R85" s="3"/>
+      <c r="S85" s="3"/>
+      <c r="T85" s="3"/>
+      <c r="U85" s="3"/>
+      <c r="V85" s="3"/>
+      <c r="W85" s="37"/>
+      <c r="X85" s="37"/>
+      <c r="Y85" s="37"/>
+      <c r="Z85" s="37"/>
+      <c r="AA85" s="37"/>
+      <c r="AB85" s="37"/>
+      <c r="AC85" s="37"/>
+      <c r="AD85" s="37"/>
+      <c r="AE85" s="3"/>
+      <c r="AF85" s="3"/>
+      <c r="AG85" s="3"/>
+      <c r="AH85" s="3"/>
+      <c r="AI85" s="37"/>
+      <c r="AJ85" s="37"/>
+      <c r="AK85" s="37"/>
+      <c r="AL85" s="35"/>
+      <c r="AM85" s="144"/>
+      <c r="AN85" s="46"/>
+      <c r="AO85" s="38"/>
+      <c r="AP85" s="41"/>
+      <c r="AQ85" s="41"/>
+      <c r="AR85" s="46"/>
+      <c r="AS85" s="38"/>
+      <c r="AT85" s="38"/>
+      <c r="AU85" s="38"/>
+      <c r="AV85" s="41"/>
+      <c r="AW85" s="39"/>
+      <c r="AX85" s="38"/>
+      <c r="AY85" s="38"/>
+      <c r="AZ85" s="38"/>
+      <c r="BA85" s="38"/>
+      <c r="BB85" s="38"/>
+      <c r="BC85" s="38"/>
+      <c r="BD85" s="38"/>
+      <c r="BE85" s="38"/>
+      <c r="BF85" s="38"/>
+      <c r="BG85" s="34"/>
+      <c r="BH85" s="139"/>
+      <c r="BI85" s="38"/>
+      <c r="BJ85" s="38"/>
       <c r="BK85" s="133"/>
       <c r="BL85" s="133"/>
-      <c r="BM85" s="134"/>
-      <c r="BN85" s="135"/>
-      <c r="BO85" s="29"/>
-      <c r="BP85" s="77"/>
-      <c r="BQ85" s="77"/>
-      <c r="BR85" s="119"/>
+      <c r="BM85" s="3"/>
+      <c r="BN85" s="151"/>
+      <c r="BO85" s="3"/>
+      <c r="BP85" s="37"/>
+      <c r="BQ85" s="37"/>
+      <c r="BR85" s="43"/>
     </row>
-    <row r="86" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="116"/>
-      <c r="C86" s="116"/>
-      <c r="D86" s="116"/>
-      <c r="E86" s="116"/>
-      <c r="F86" s="116"/>
-      <c r="G86" s="116"/>
-      <c r="H86" s="77"/>
-      <c r="K86" s="116"/>
-      <c r="L86" s="116"/>
-      <c r="N86" s="77"/>
-      <c r="O86" s="77"/>
-      <c r="P86" s="77"/>
-      <c r="Q86" s="77"/>
-      <c r="W86" s="77"/>
-      <c r="X86" s="77"/>
-      <c r="Y86" s="77"/>
-      <c r="Z86" s="77"/>
-      <c r="AA86" s="77"/>
-      <c r="AB86" s="77"/>
-      <c r="AC86" s="77"/>
-      <c r="AD86" s="77"/>
-      <c r="AI86" s="77"/>
-      <c r="AJ86" s="77"/>
-      <c r="AK86" s="77"/>
-      <c r="AL86" s="116"/>
-      <c r="AM86" s="117"/>
-      <c r="AN86" s="78"/>
-      <c r="AO86" s="78"/>
-      <c r="AP86" s="117"/>
-      <c r="AQ86" s="117"/>
-      <c r="AR86" s="78"/>
-      <c r="AS86" s="78"/>
-      <c r="AT86" s="78"/>
-      <c r="AU86" s="78"/>
-      <c r="AV86" s="117"/>
-      <c r="AW86" s="78"/>
-      <c r="AX86" s="78"/>
-      <c r="AY86" s="78"/>
-      <c r="AZ86" s="78"/>
-      <c r="BA86" s="78"/>
-      <c r="BB86" s="78"/>
-      <c r="BC86" s="78"/>
-      <c r="BD86" s="78"/>
-      <c r="BE86" s="78"/>
-      <c r="BF86" s="78"/>
-      <c r="BG86" s="117"/>
-      <c r="BH86" s="118"/>
-      <c r="BI86" s="38" t="s">
-        <v>515</v>
-      </c>
+    <row r="86" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="137"/>
+      <c r="B86" s="35"/>
+      <c r="C86" s="35"/>
+      <c r="D86" s="35"/>
+      <c r="E86" s="35"/>
+      <c r="F86" s="35"/>
+      <c r="G86" s="35"/>
+      <c r="H86" s="37"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="35"/>
+      <c r="L86" s="35"/>
+      <c r="M86" s="138"/>
+      <c r="N86" s="37"/>
+      <c r="O86" s="37"/>
+      <c r="P86" s="37"/>
+      <c r="Q86" s="37"/>
+      <c r="R86" s="3"/>
+      <c r="S86" s="3"/>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="37"/>
+      <c r="X86" s="37"/>
+      <c r="Y86" s="37"/>
+      <c r="Z86" s="37"/>
+      <c r="AA86" s="37"/>
+      <c r="AB86" s="37"/>
+      <c r="AC86" s="37"/>
+      <c r="AD86" s="37"/>
+      <c r="AE86" s="3"/>
+      <c r="AF86" s="3"/>
+      <c r="AG86" s="3"/>
+      <c r="AH86" s="3"/>
+      <c r="AI86" s="37"/>
+      <c r="AJ86" s="37"/>
+      <c r="AK86" s="37"/>
+      <c r="AL86" s="35"/>
+      <c r="AM86" s="34"/>
+      <c r="AN86" s="38"/>
+      <c r="AO86" s="38"/>
+      <c r="AP86" s="34"/>
+      <c r="AQ86" s="34"/>
+      <c r="AR86" s="38"/>
+      <c r="AS86" s="38"/>
+      <c r="AT86" s="38"/>
+      <c r="AU86" s="38"/>
+      <c r="AV86" s="41"/>
+      <c r="AW86" s="39"/>
+      <c r="AX86" s="38"/>
+      <c r="AY86" s="38"/>
+      <c r="AZ86" s="38"/>
+      <c r="BA86" s="38"/>
+      <c r="BB86" s="38"/>
+      <c r="BC86" s="38"/>
+      <c r="BD86" s="38"/>
+      <c r="BE86" s="38"/>
+      <c r="BF86" s="38"/>
+      <c r="BG86" s="34"/>
+      <c r="BH86" s="139"/>
+      <c r="BI86" s="38"/>
       <c r="BJ86" s="38" t="s">
-        <v>516</v>
-      </c>
-      <c r="BK86" s="38" t="s">
-        <v>708</v>
-      </c>
+        <v>754</v>
+      </c>
+      <c r="BK86" s="38"/>
       <c r="BL86" s="38"/>
-      <c r="BM86" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="BN86" s="29"/>
-      <c r="BO86" s="93"/>
-      <c r="BP86" s="77"/>
-      <c r="BQ86" s="77"/>
-      <c r="BR86" s="119"/>
+      <c r="BM86" s="3"/>
+      <c r="BN86" s="120"/>
+      <c r="BO86" s="35"/>
+      <c r="BP86" s="37"/>
+      <c r="BQ86" s="37"/>
+      <c r="BR86" s="43"/>
     </row>
-    <row r="87" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="116"/>
-      <c r="C87" s="116"/>
-      <c r="D87" s="116"/>
-      <c r="E87" s="116"/>
-      <c r="F87" s="116"/>
-      <c r="G87" s="116"/>
-      <c r="H87" s="77"/>
-      <c r="K87" s="116"/>
-      <c r="L87" s="116"/>
-      <c r="N87" s="77"/>
-      <c r="O87" s="77"/>
-      <c r="P87" s="77"/>
-      <c r="Q87" s="77"/>
-      <c r="W87" s="77"/>
-      <c r="X87" s="77"/>
-      <c r="Y87" s="77"/>
-      <c r="Z87" s="77"/>
-      <c r="AA87" s="77"/>
-      <c r="AB87" s="77"/>
-      <c r="AC87" s="77"/>
-      <c r="AD87" s="77"/>
-      <c r="AI87" s="77"/>
-      <c r="AJ87" s="77"/>
-      <c r="AK87" s="77"/>
-      <c r="AL87" s="116"/>
-      <c r="AM87" s="117"/>
-      <c r="AN87" s="78"/>
-      <c r="AO87" s="78"/>
-      <c r="AP87" s="117"/>
-      <c r="AQ87" s="117"/>
-      <c r="AR87" s="78"/>
-      <c r="AS87" s="78"/>
-      <c r="AT87" s="78"/>
-      <c r="AU87" s="78"/>
-      <c r="AV87" s="117"/>
-      <c r="AW87" s="78"/>
-      <c r="AX87" s="78"/>
-      <c r="AY87" s="78"/>
-      <c r="AZ87" s="78"/>
-      <c r="BA87" s="78"/>
-      <c r="BB87" s="78"/>
-      <c r="BC87" s="78"/>
-      <c r="BD87" s="78"/>
-      <c r="BE87" s="78"/>
-      <c r="BF87" s="78"/>
-      <c r="BG87" s="117"/>
-      <c r="BH87" s="118"/>
+    <row r="87" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="137"/>
+      <c r="B87" s="35"/>
+      <c r="C87" s="35"/>
+      <c r="D87" s="35"/>
+      <c r="E87" s="35"/>
+      <c r="F87" s="35"/>
+      <c r="G87" s="35"/>
+      <c r="H87" s="37"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="35"/>
+      <c r="L87" s="35"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="37"/>
+      <c r="O87" s="37"/>
+      <c r="P87" s="37"/>
+      <c r="Q87" s="37"/>
+      <c r="R87" s="3"/>
+      <c r="S87" s="3"/>
+      <c r="T87" s="3"/>
+      <c r="U87" s="3"/>
+      <c r="V87" s="3"/>
+      <c r="W87" s="37"/>
+      <c r="X87" s="37"/>
+      <c r="Y87" s="37"/>
+      <c r="Z87" s="37"/>
+      <c r="AA87" s="37"/>
+      <c r="AB87" s="37"/>
+      <c r="AC87" s="37"/>
+      <c r="AD87" s="37"/>
+      <c r="AE87" s="3"/>
+      <c r="AF87" s="3"/>
+      <c r="AG87" s="3"/>
+      <c r="AH87" s="3"/>
+      <c r="AI87" s="37"/>
+      <c r="AJ87" s="37"/>
+      <c r="AK87" s="37"/>
+      <c r="AL87" s="35"/>
+      <c r="AM87" s="34"/>
+      <c r="AN87" s="38"/>
+      <c r="AO87" s="38"/>
+      <c r="AP87" s="34"/>
+      <c r="AQ87" s="34"/>
+      <c r="AR87" s="38"/>
+      <c r="AS87" s="38"/>
+      <c r="AT87" s="38"/>
+      <c r="AU87" s="38"/>
+      <c r="AV87" s="34"/>
+      <c r="AW87" s="38"/>
+      <c r="AX87" s="38"/>
+      <c r="AY87" s="38"/>
+      <c r="AZ87" s="38"/>
+      <c r="BA87" s="38"/>
+      <c r="BB87" s="38"/>
+      <c r="BC87" s="38"/>
+      <c r="BD87" s="38"/>
+      <c r="BE87" s="38"/>
+      <c r="BF87" s="38"/>
+      <c r="BG87" s="34"/>
+      <c r="BH87" s="139"/>
       <c r="BI87" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="BJ87" s="38" t="s">
-        <v>118</v>
+        <v>98</v>
+      </c>
+      <c r="BJ87" s="133" t="s">
+        <v>287</v>
       </c>
       <c r="BK87" s="38"/>
       <c r="BL87" s="38"/>
       <c r="BM87" s="3"/>
-      <c r="BN87" s="29"/>
-      <c r="BO87" s="29"/>
-      <c r="BP87" s="77"/>
-      <c r="BQ87" s="77"/>
-      <c r="BR87" s="119"/>
+      <c r="BN87" s="120"/>
+      <c r="BO87" s="35"/>
+      <c r="BP87" s="37"/>
+      <c r="BQ87" s="37"/>
+      <c r="BR87" s="43"/>
     </row>
     <row r="88" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="116"/>
@@ -17896,12 +18008,20 @@
       <c r="AJ88" s="77"/>
       <c r="AK88" s="77"/>
       <c r="AL88" s="116"/>
-      <c r="AM88" s="117"/>
-      <c r="AN88" s="78"/>
-      <c r="AO88" s="78"/>
-      <c r="AP88" s="117"/>
-      <c r="AQ88" s="117"/>
-      <c r="AR88" s="78"/>
+      <c r="AM88" s="140" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN88" s="141" t="s">
+        <v>689</v>
+      </c>
+      <c r="AO88" s="142"/>
+      <c r="AP88" s="143"/>
+      <c r="AQ88" s="140" t="s">
+        <v>679</v>
+      </c>
+      <c r="AR88" s="141" t="s">
+        <v>688</v>
+      </c>
       <c r="AS88" s="78"/>
       <c r="AT88" s="78"/>
       <c r="AU88" s="78"/>
@@ -17918,13 +18038,17 @@
       <c r="BF88" s="78"/>
       <c r="BG88" s="117"/>
       <c r="BH88" s="118"/>
-      <c r="BI88" s="46"/>
-      <c r="BJ88" s="46"/>
-      <c r="BK88" s="46"/>
-      <c r="BL88" s="46"/>
-      <c r="BM88" s="48"/>
-      <c r="BN88" s="29"/>
-      <c r="BO88" s="29"/>
+      <c r="BI88" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="BJ88" s="150" t="s">
+        <v>588</v>
+      </c>
+      <c r="BK88" s="38"/>
+      <c r="BL88" s="38"/>
+      <c r="BM88" s="3"/>
+      <c r="BN88" s="121"/>
+      <c r="BO88" s="45"/>
       <c r="BP88" s="77"/>
       <c r="BQ88" s="77"/>
       <c r="BR88" s="119"/>
@@ -17955,12 +18079,20 @@
       <c r="AJ89" s="77"/>
       <c r="AK89" s="77"/>
       <c r="AL89" s="116"/>
-      <c r="AM89" s="117"/>
-      <c r="AN89" s="78"/>
+      <c r="AM89" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN89" s="26" t="s">
+        <v>678</v>
+      </c>
       <c r="AO89" s="78"/>
       <c r="AP89" s="117"/>
-      <c r="AQ89" s="117"/>
-      <c r="AR89" s="78"/>
+      <c r="AQ89" s="27" t="s">
+        <v>680</v>
+      </c>
+      <c r="AR89" s="26" t="s">
+        <v>681</v>
+      </c>
       <c r="AS89" s="78"/>
       <c r="AT89" s="78"/>
       <c r="AU89" s="78"/>
@@ -17977,12 +18109,17 @@
       <c r="BF89" s="78"/>
       <c r="BG89" s="117"/>
       <c r="BH89" s="118"/>
-      <c r="BI89" s="78"/>
-      <c r="BJ89" s="78"/>
-      <c r="BK89" s="78"/>
-      <c r="BL89" s="78"/>
-      <c r="BN89" s="116"/>
-      <c r="BO89" s="116"/>
+      <c r="BI89" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ89" s="150" t="s">
+        <v>589</v>
+      </c>
+      <c r="BK89" s="38"/>
+      <c r="BL89" s="38"/>
+      <c r="BM89" s="3"/>
+      <c r="BN89" s="120"/>
+      <c r="BO89" s="35"/>
       <c r="BP89" s="77"/>
       <c r="BQ89" s="77"/>
       <c r="BR89" s="119"/>
@@ -18035,15 +18172,321 @@
       <c r="BF90" s="78"/>
       <c r="BG90" s="117"/>
       <c r="BH90" s="118"/>
-      <c r="BI90" s="78"/>
-      <c r="BJ90" s="78"/>
-      <c r="BK90" s="78"/>
-      <c r="BL90" s="78"/>
-      <c r="BN90" s="116"/>
-      <c r="BO90" s="116"/>
+      <c r="BI90" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="BJ90" s="133" t="s">
+        <v>453</v>
+      </c>
+      <c r="BK90" s="133"/>
+      <c r="BL90" s="133"/>
+      <c r="BM90" s="134"/>
+      <c r="BN90" s="135"/>
+      <c r="BO90" s="29"/>
       <c r="BP90" s="77"/>
       <c r="BQ90" s="77"/>
       <c r="BR90" s="119"/>
+    </row>
+    <row r="91" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="116"/>
+      <c r="C91" s="116"/>
+      <c r="D91" s="116"/>
+      <c r="E91" s="116"/>
+      <c r="F91" s="116"/>
+      <c r="G91" s="116"/>
+      <c r="H91" s="77"/>
+      <c r="K91" s="116"/>
+      <c r="L91" s="116"/>
+      <c r="N91" s="77"/>
+      <c r="O91" s="77"/>
+      <c r="P91" s="77"/>
+      <c r="Q91" s="77"/>
+      <c r="W91" s="77"/>
+      <c r="X91" s="77"/>
+      <c r="Y91" s="77"/>
+      <c r="Z91" s="77"/>
+      <c r="AA91" s="77"/>
+      <c r="AB91" s="77"/>
+      <c r="AC91" s="77"/>
+      <c r="AD91" s="77"/>
+      <c r="AI91" s="77"/>
+      <c r="AJ91" s="77"/>
+      <c r="AK91" s="77"/>
+      <c r="AL91" s="116"/>
+      <c r="AM91" s="117"/>
+      <c r="AN91" s="78"/>
+      <c r="AO91" s="78"/>
+      <c r="AP91" s="117"/>
+      <c r="AQ91" s="117"/>
+      <c r="AR91" s="78"/>
+      <c r="AS91" s="78"/>
+      <c r="AT91" s="78"/>
+      <c r="AU91" s="78"/>
+      <c r="AV91" s="117"/>
+      <c r="AW91" s="78"/>
+      <c r="AX91" s="78"/>
+      <c r="AY91" s="78"/>
+      <c r="AZ91" s="78"/>
+      <c r="BA91" s="78"/>
+      <c r="BB91" s="78"/>
+      <c r="BC91" s="78"/>
+      <c r="BD91" s="78"/>
+      <c r="BE91" s="78"/>
+      <c r="BF91" s="78"/>
+      <c r="BG91" s="117"/>
+      <c r="BH91" s="118"/>
+      <c r="BI91" s="38" t="s">
+        <v>515</v>
+      </c>
+      <c r="BJ91" s="152" t="s">
+        <v>516</v>
+      </c>
+      <c r="BK91" s="38"/>
+      <c r="BL91" s="38"/>
+      <c r="BM91" s="3"/>
+      <c r="BN91" s="29"/>
+      <c r="BO91" s="93"/>
+      <c r="BP91" s="77"/>
+      <c r="BQ91" s="77"/>
+      <c r="BR91" s="119"/>
+    </row>
+    <row r="92" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="116"/>
+      <c r="C92" s="116"/>
+      <c r="D92" s="116"/>
+      <c r="E92" s="116"/>
+      <c r="F92" s="116"/>
+      <c r="G92" s="116"/>
+      <c r="H92" s="77"/>
+      <c r="K92" s="116"/>
+      <c r="L92" s="116"/>
+      <c r="N92" s="77"/>
+      <c r="O92" s="77"/>
+      <c r="P92" s="77"/>
+      <c r="Q92" s="77"/>
+      <c r="W92" s="77"/>
+      <c r="X92" s="77"/>
+      <c r="Y92" s="77"/>
+      <c r="Z92" s="77"/>
+      <c r="AA92" s="77"/>
+      <c r="AB92" s="77"/>
+      <c r="AC92" s="77"/>
+      <c r="AD92" s="77"/>
+      <c r="AI92" s="77"/>
+      <c r="AJ92" s="77"/>
+      <c r="AK92" s="77"/>
+      <c r="AL92" s="116"/>
+      <c r="AM92" s="117"/>
+      <c r="AN92" s="78"/>
+      <c r="AO92" s="78"/>
+      <c r="AP92" s="117"/>
+      <c r="AQ92" s="117"/>
+      <c r="AR92" s="78"/>
+      <c r="AS92" s="78"/>
+      <c r="AT92" s="78"/>
+      <c r="AU92" s="78"/>
+      <c r="AV92" s="117"/>
+      <c r="AW92" s="78"/>
+      <c r="AX92" s="78"/>
+      <c r="AY92" s="78"/>
+      <c r="AZ92" s="78"/>
+      <c r="BA92" s="78"/>
+      <c r="BB92" s="78"/>
+      <c r="BC92" s="78"/>
+      <c r="BD92" s="78"/>
+      <c r="BE92" s="78"/>
+      <c r="BF92" s="78"/>
+      <c r="BG92" s="117"/>
+      <c r="BH92" s="118"/>
+      <c r="BI92" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="BJ92" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK92" s="38"/>
+      <c r="BL92" s="38"/>
+      <c r="BM92" s="3"/>
+      <c r="BN92" s="29"/>
+      <c r="BO92" s="29"/>
+      <c r="BP92" s="77"/>
+      <c r="BQ92" s="77"/>
+      <c r="BR92" s="119"/>
+    </row>
+    <row r="93" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B93" s="116"/>
+      <c r="C93" s="116"/>
+      <c r="D93" s="116"/>
+      <c r="E93" s="116"/>
+      <c r="F93" s="116"/>
+      <c r="G93" s="116"/>
+      <c r="H93" s="77"/>
+      <c r="K93" s="116"/>
+      <c r="L93" s="116"/>
+      <c r="N93" s="77"/>
+      <c r="O93" s="77"/>
+      <c r="P93" s="77"/>
+      <c r="Q93" s="77"/>
+      <c r="W93" s="77"/>
+      <c r="X93" s="77"/>
+      <c r="Y93" s="77"/>
+      <c r="Z93" s="77"/>
+      <c r="AA93" s="77"/>
+      <c r="AB93" s="77"/>
+      <c r="AC93" s="77"/>
+      <c r="AD93" s="77"/>
+      <c r="AI93" s="77"/>
+      <c r="AJ93" s="77"/>
+      <c r="AK93" s="77"/>
+      <c r="AL93" s="116"/>
+      <c r="AM93" s="117"/>
+      <c r="AN93" s="78"/>
+      <c r="AO93" s="78"/>
+      <c r="AP93" s="117"/>
+      <c r="AQ93" s="117"/>
+      <c r="AR93" s="78"/>
+      <c r="AS93" s="78"/>
+      <c r="AT93" s="78"/>
+      <c r="AU93" s="78"/>
+      <c r="AV93" s="117"/>
+      <c r="AW93" s="78"/>
+      <c r="AX93" s="78"/>
+      <c r="AY93" s="78"/>
+      <c r="AZ93" s="78"/>
+      <c r="BA93" s="78"/>
+      <c r="BB93" s="78"/>
+      <c r="BC93" s="78"/>
+      <c r="BD93" s="78"/>
+      <c r="BE93" s="78"/>
+      <c r="BF93" s="78"/>
+      <c r="BG93" s="117"/>
+      <c r="BH93" s="118"/>
+      <c r="BI93" s="46"/>
+      <c r="BJ93" s="46"/>
+      <c r="BK93" s="46"/>
+      <c r="BL93" s="46"/>
+      <c r="BM93" s="48"/>
+      <c r="BN93" s="29"/>
+      <c r="BO93" s="29"/>
+      <c r="BP93" s="77"/>
+      <c r="BQ93" s="77"/>
+      <c r="BR93" s="119"/>
+    </row>
+    <row r="94" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B94" s="116"/>
+      <c r="C94" s="116"/>
+      <c r="D94" s="116"/>
+      <c r="E94" s="116"/>
+      <c r="F94" s="116"/>
+      <c r="G94" s="116"/>
+      <c r="H94" s="77"/>
+      <c r="K94" s="116"/>
+      <c r="L94" s="116"/>
+      <c r="N94" s="77"/>
+      <c r="O94" s="77"/>
+      <c r="P94" s="77"/>
+      <c r="Q94" s="77"/>
+      <c r="W94" s="77"/>
+      <c r="X94" s="77"/>
+      <c r="Y94" s="77"/>
+      <c r="Z94" s="77"/>
+      <c r="AA94" s="77"/>
+      <c r="AB94" s="77"/>
+      <c r="AC94" s="77"/>
+      <c r="AD94" s="77"/>
+      <c r="AI94" s="77"/>
+      <c r="AJ94" s="77"/>
+      <c r="AK94" s="77"/>
+      <c r="AL94" s="116"/>
+      <c r="AM94" s="117"/>
+      <c r="AN94" s="78"/>
+      <c r="AO94" s="78"/>
+      <c r="AP94" s="117"/>
+      <c r="AQ94" s="117"/>
+      <c r="AR94" s="78"/>
+      <c r="AS94" s="78"/>
+      <c r="AT94" s="78"/>
+      <c r="AU94" s="78"/>
+      <c r="AV94" s="117"/>
+      <c r="AW94" s="78"/>
+      <c r="AX94" s="78"/>
+      <c r="AY94" s="78"/>
+      <c r="AZ94" s="78"/>
+      <c r="BA94" s="78"/>
+      <c r="BB94" s="78"/>
+      <c r="BC94" s="78"/>
+      <c r="BD94" s="78"/>
+      <c r="BE94" s="78"/>
+      <c r="BF94" s="78"/>
+      <c r="BG94" s="117"/>
+      <c r="BH94" s="118"/>
+      <c r="BI94" s="78"/>
+      <c r="BJ94" s="78"/>
+      <c r="BK94" s="78"/>
+      <c r="BL94" s="78"/>
+      <c r="BN94" s="116"/>
+      <c r="BO94" s="116"/>
+      <c r="BP94" s="77"/>
+      <c r="BQ94" s="77"/>
+      <c r="BR94" s="119"/>
+    </row>
+    <row r="95" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B95" s="116"/>
+      <c r="C95" s="116"/>
+      <c r="D95" s="116"/>
+      <c r="E95" s="116"/>
+      <c r="F95" s="116"/>
+      <c r="G95" s="116"/>
+      <c r="H95" s="77"/>
+      <c r="K95" s="116"/>
+      <c r="L95" s="116"/>
+      <c r="N95" s="77"/>
+      <c r="O95" s="77"/>
+      <c r="P95" s="77"/>
+      <c r="Q95" s="77"/>
+      <c r="W95" s="77"/>
+      <c r="X95" s="77"/>
+      <c r="Y95" s="77"/>
+      <c r="Z95" s="77"/>
+      <c r="AA95" s="77"/>
+      <c r="AB95" s="77"/>
+      <c r="AC95" s="77"/>
+      <c r="AD95" s="77"/>
+      <c r="AI95" s="77"/>
+      <c r="AJ95" s="77"/>
+      <c r="AK95" s="77"/>
+      <c r="AL95" s="116"/>
+      <c r="AM95" s="117"/>
+      <c r="AN95" s="78"/>
+      <c r="AO95" s="78"/>
+      <c r="AP95" s="117"/>
+      <c r="AQ95" s="117"/>
+      <c r="AR95" s="78"/>
+      <c r="AS95" s="78"/>
+      <c r="AT95" s="78"/>
+      <c r="AU95" s="78"/>
+      <c r="AV95" s="117"/>
+      <c r="AW95" s="78"/>
+      <c r="AX95" s="78"/>
+      <c r="AY95" s="78"/>
+      <c r="AZ95" s="78"/>
+      <c r="BA95" s="78"/>
+      <c r="BB95" s="78"/>
+      <c r="BC95" s="78"/>
+      <c r="BD95" s="78"/>
+      <c r="BE95" s="78"/>
+      <c r="BF95" s="78"/>
+      <c r="BG95" s="117"/>
+      <c r="BH95" s="118"/>
+      <c r="BI95" s="78"/>
+      <c r="BJ95" s="78"/>
+      <c r="BK95" s="78"/>
+      <c r="BL95" s="78"/>
+      <c r="BN95" s="116"/>
+      <c r="BO95" s="116"/>
+      <c r="BP95" s="77"/>
+      <c r="BQ95" s="77"/>
+      <c r="BR95" s="119"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18240,19 +18683,19 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="128" t="s">
+        <v>536</v>
+      </c>
+      <c r="C1" s="129" t="s">
+        <v>537</v>
+      </c>
+      <c r="D1" s="129" t="s">
         <v>538</v>
       </c>
-      <c r="C1" s="129" t="s">
+      <c r="E1" s="129" t="s">
         <v>539</v>
       </c>
-      <c r="D1" s="129" t="s">
+      <c r="F1" s="130" t="s">
         <v>540</v>
-      </c>
-      <c r="E1" s="129" t="s">
-        <v>541</v>
-      </c>
-      <c r="F1" s="130" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.35">
@@ -18269,7 +18712,7 @@
         <v>36</v>
       </c>
       <c r="F2" s="127" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
@@ -18286,7 +18729,7 @@
         <v>43</v>
       </c>
       <c r="F3" s="125" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.35">
@@ -18303,7 +18746,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="125" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.35">
@@ -18320,7 +18763,7 @@
         <v>49</v>
       </c>
       <c r="F5" s="125" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.35">
@@ -18337,7 +18780,7 @@
         <v>33</v>
       </c>
       <c r="F6" s="125" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.35">
@@ -18354,7 +18797,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="125" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.35">
@@ -18371,7 +18814,7 @@
         <v>32</v>
       </c>
       <c r="F8" s="125" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.35">
@@ -18388,7 +18831,7 @@
         <v>54</v>
       </c>
       <c r="F9" s="125" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.35">
@@ -18405,7 +18848,7 @@
         <v>32</v>
       </c>
       <c r="F10" s="125" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.35">
@@ -18422,7 +18865,7 @@
         <v>26</v>
       </c>
       <c r="F11" s="125" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.35">
@@ -18439,7 +18882,7 @@
         <v>34</v>
       </c>
       <c r="F12" s="125" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.35">
@@ -18456,7 +18899,7 @@
         <v>39</v>
       </c>
       <c r="F13" s="125" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.35">
@@ -18480,7 +18923,7 @@
         <v>30</v>
       </c>
       <c r="F15" s="125" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.35">
@@ -18497,7 +18940,7 @@
         <v>49</v>
       </c>
       <c r="F16" s="125" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
@@ -18514,7 +18957,7 @@
         <v>58</v>
       </c>
       <c r="F17" s="127" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -18531,7 +18974,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="125" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
@@ -18548,7 +18991,7 @@
         <v>60</v>
       </c>
       <c r="F19" s="127" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.35">
@@ -18565,7 +19008,7 @@
         <v>38</v>
       </c>
       <c r="F20" s="125" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
@@ -18582,7 +19025,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="125" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
@@ -18599,7 +19042,7 @@
         <v>44</v>
       </c>
       <c r="F22" s="125" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.35">
@@ -18616,7 +19059,7 @@
         <v>46</v>
       </c>
       <c r="F23" s="125" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.35">
@@ -18633,7 +19076,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="125" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
@@ -18650,7 +19093,7 @@
         <v>54</v>
       </c>
       <c r="F25" s="125" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
@@ -18667,7 +19110,7 @@
         <v>48</v>
       </c>
       <c r="F26" s="125" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
@@ -18684,7 +19127,7 @@
         <v>43</v>
       </c>
       <c r="F27" s="125" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
@@ -18701,7 +19144,7 @@
         <v>72</v>
       </c>
       <c r="F28" s="127" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.35">
@@ -18718,7 +19161,7 @@
         <v>43</v>
       </c>
       <c r="F29" s="125" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.35">
@@ -18735,7 +19178,7 @@
         <v>45</v>
       </c>
       <c r="F30" s="125" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
@@ -18759,7 +19202,7 @@
         <v>76</v>
       </c>
       <c r="F32" s="127" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
@@ -18776,7 +19219,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="125" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
@@ -18793,7 +19236,7 @@
         <v>78</v>
       </c>
       <c r="F34" s="127" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.35">
@@ -18810,7 +19253,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="125" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
@@ -18827,7 +19270,7 @@
         <v>46</v>
       </c>
       <c r="F36" s="125" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
@@ -18844,7 +19287,7 @@
         <v>58</v>
       </c>
       <c r="F37" s="125" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
@@ -18861,7 +19304,7 @@
         <v>60</v>
       </c>
       <c r="F38" s="125" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
@@ -18878,7 +19321,7 @@
         <v>61</v>
       </c>
       <c r="F39" s="125" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
@@ -18895,7 +19338,7 @@
         <v>84</v>
       </c>
       <c r="F40" s="127" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
@@ -18912,7 +19355,7 @@
         <v>51</v>
       </c>
       <c r="F41" s="125" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
@@ -18936,7 +19379,7 @@
         <v>57</v>
       </c>
       <c r="F43" s="125" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
@@ -18953,7 +19396,7 @@
         <v>64</v>
       </c>
       <c r="F44" s="125" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
@@ -18970,7 +19413,7 @@
         <v>59</v>
       </c>
       <c r="F45" s="125" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
@@ -18987,7 +19430,7 @@
         <v>94</v>
       </c>
       <c r="F46" s="127" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
@@ -19004,7 +19447,7 @@
         <v>66</v>
       </c>
       <c r="F47" s="125" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
@@ -19021,7 +19464,7 @@
         <v>60</v>
       </c>
       <c r="F48" s="125" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.35">
@@ -19038,7 +19481,7 @@
         <v>63</v>
       </c>
       <c r="F49" s="125" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
@@ -19055,7 +19498,7 @@
         <v>68</v>
       </c>
       <c r="F50" s="125" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
@@ -19072,7 +19515,7 @@
         <v>62</v>
       </c>
       <c r="F51" s="125" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
@@ -19089,7 +19532,7 @@
         <v>65</v>
       </c>
       <c r="F52" s="125" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.35">
@@ -19106,7 +19549,7 @@
         <v>67</v>
       </c>
       <c r="F53" s="125" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.35">
@@ -19123,7 +19566,7 @@
         <v>70</v>
       </c>
       <c r="F54" s="125" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
@@ -19140,7 +19583,7 @@
         <v>65</v>
       </c>
       <c r="F55" s="125" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
@@ -19157,7 +19600,7 @@
         <v>69</v>
       </c>
       <c r="F56" s="125" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
@@ -19174,7 +19617,7 @@
         <v>97</v>
       </c>
       <c r="F57" s="127" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
@@ -19198,7 +19641,7 @@
         <v>105</v>
       </c>
       <c r="F59" s="127" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.35">
@@ -19215,7 +19658,7 @@
         <v>72</v>
       </c>
       <c r="F60" s="125" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.35">
@@ -19232,7 +19675,7 @@
         <v>81</v>
       </c>
       <c r="F61" s="125" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.35">
@@ -19249,7 +19692,7 @@
         <v>88</v>
       </c>
       <c r="F62" s="125" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.35">
@@ -19266,7 +19709,7 @@
         <v>73</v>
       </c>
       <c r="F63" s="125" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE407FCC-A0AB-4842-959D-94F6C2AD0C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1DB13E-474D-4423-8562-2C14B7C99245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2580" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="758">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2305,19 +2305,28 @@
     <t>206711</t>
   </si>
   <si>
-    <t>Another firmware updrade with many changes like showing humidity inside glider with X3 board, and many more little things. GPCTD possibly clogged</t>
-  </si>
-  <si>
     <t>GLI2025_SEA022_104</t>
   </si>
   <si>
     <t>20240916</t>
   </si>
   <si>
-    <t>duet T.ODO</t>
-  </si>
-  <si>
     <t>feb 2025</t>
+  </si>
+  <si>
+    <t>Another firmware updrade with many changes like showing humidity inside glider with X3 board, and many more little things. GPCTD possibly clogged or pump failure</t>
+  </si>
+  <si>
+    <t>GPCTD possibly clogged or pump failure</t>
+  </si>
+  <si>
+    <t>with Legato and T.ODO</t>
+  </si>
+  <si>
+    <t>20241217</t>
+  </si>
+  <si>
+    <t>20241123</t>
   </si>
 </sst>
 </file>
@@ -17288,7 +17297,9 @@
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
-      <c r="V80" s="3"/>
+      <c r="V80" s="3">
+        <v>-4</v>
+      </c>
       <c r="W80" s="37" t="s">
         <v>36</v>
       </c>
@@ -17391,9 +17402,11 @@
       <c r="BP80" s="37" t="s">
         <v>747</v>
       </c>
-      <c r="BQ80" s="37"/>
+      <c r="BQ80" s="37" t="s">
+        <v>754</v>
+      </c>
       <c r="BR80" s="43" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="81" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -17415,7 +17428,7 @@
         <v>15</v>
       </c>
       <c r="H81" s="37" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
@@ -17470,22 +17483,22 @@
         <v>30</v>
       </c>
       <c r="AM81" s="144" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="AN81" s="46" t="s">
-        <v>678</v>
+        <v>756</v>
       </c>
       <c r="AO81" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="AP81" s="41" t="s">
-        <v>70</v>
+      <c r="AP81" s="34" t="s">
+        <v>77</v>
       </c>
       <c r="AQ81" s="41" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AR81" s="46" t="s">
-        <v>681</v>
+        <v>757</v>
       </c>
       <c r="AS81" s="38"/>
       <c r="AT81" s="38"/>
@@ -17505,7 +17518,7 @@
         <v>451</v>
       </c>
       <c r="BB81" s="38" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="BC81" s="38" t="s">
         <v>420</v>
@@ -17541,7 +17554,7 @@
       <c r="BP81" s="37"/>
       <c r="BQ81" s="37"/>
       <c r="BR81" s="43" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="82" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -17895,7 +17908,7 @@
       <c r="BH86" s="139"/>
       <c r="BI86" s="38"/>
       <c r="BJ86" s="38" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="BK86" s="38"/>
       <c r="BL86" s="38"/>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1DB13E-474D-4423-8562-2C14B7C99245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F88571-2032-4DC8-9921-519CC1F6DDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="765">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2092,12 +2092,6 @@
     <t>20240428</t>
   </si>
   <si>
-    <t>3276</t>
-  </si>
-  <si>
-    <t>3338</t>
-  </si>
-  <si>
     <t>20240424</t>
   </si>
   <si>
@@ -2119,12 +2113,6 @@
     <t>with sea021 GPCTD (43F), very fast speed for less than 2 weeks</t>
   </si>
   <si>
-    <t>20240510</t>
-  </si>
-  <si>
-    <t>20240515</t>
-  </si>
-  <si>
     <t>Duet data 1hz, legato top puck</t>
   </si>
   <si>
@@ -2296,9 +2284,6 @@
     <t>3.8.2-r humidity</t>
   </si>
   <si>
-    <t>Sigma-T/</t>
-  </si>
-  <si>
     <t>HL2 day after deployment, 4.2km appart</t>
   </si>
   <si>
@@ -2314,19 +2299,55 @@
     <t>feb 2025</t>
   </si>
   <si>
-    <t>Another firmware updrade with many changes like showing humidity inside glider with X3 board, and many more little things. GPCTD possibly clogged or pump failure</t>
-  </si>
-  <si>
-    <t>GPCTD possibly clogged or pump failure</t>
-  </si>
-  <si>
-    <t>with Legato and T.ODO</t>
-  </si>
-  <si>
     <t>20241217</t>
   </si>
   <si>
     <t>20241123</t>
+  </si>
+  <si>
+    <t>25u0518</t>
+  </si>
+  <si>
+    <t>25u0517</t>
+  </si>
+  <si>
+    <t>TRI-GL1-GL2-GL3-GL7-GL3-GL2-GL1-NSC-TRI-DR</t>
+  </si>
+  <si>
+    <t>Another firmware updrade with many changes like showing humidity inside glider with X3 board, and many more little things. GPCTD possibly clogged or pump failure, we tried to turn GPCTD off multiple time to clear the possible clog (12 dives total ishh), base of antenna broken, might have been hit by a boat</t>
+  </si>
+  <si>
+    <t>GPCTD possibly clogged or pump failure, gpctd turned off multiple times to try to clear the clog</t>
+  </si>
+  <si>
+    <t>sigma-T/</t>
+  </si>
+  <si>
+    <t>3.8.2-r</t>
+  </si>
+  <si>
+    <t>3-Dec-24</t>
+  </si>
+  <si>
+    <t>5-Dec-24</t>
+  </si>
+  <si>
+    <t>20241221</t>
+  </si>
+  <si>
+    <t>20241211</t>
+  </si>
+  <si>
+    <t>with Legato and T.ODO, CDOM negative values</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA032_089</t>
+  </si>
+  <si>
+    <t>AZMP spring 2025</t>
+  </si>
+  <si>
+    <t>with T.ODO</t>
   </si>
 </sst>
 </file>
@@ -2423,7 +2444,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2460,12 +2481,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2658,7 +2673,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2995,13 +3010,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3677,7 +3685,7 @@
         <v>222</v>
       </c>
       <c r="BL2" s="70" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="BM2" s="32" t="s">
         <v>41</v>
@@ -3692,7 +3700,7 @@
         <v>661</v>
       </c>
       <c r="BQ2" s="75" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="BR2" s="76" t="s">
         <v>12</v>
@@ -4040,10 +4048,10 @@
         <v>198</v>
       </c>
       <c r="BQ4" s="18" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="BR4" s="21" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="5" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
@@ -4391,7 +4399,7 @@
         <v>197</v>
       </c>
       <c r="BQ6" s="37" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="BR6" s="43" t="s">
         <v>220</v>
@@ -4568,7 +4576,7 @@
         <v>197</v>
       </c>
       <c r="BQ7" s="37" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="BR7" s="43" t="s">
         <v>217</v>
@@ -4743,7 +4751,7 @@
         <v>197</v>
       </c>
       <c r="BQ8" s="37" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="BR8" s="43" t="s">
         <v>218</v>
@@ -4918,7 +4926,7 @@
         <v>197</v>
       </c>
       <c r="BQ9" s="37" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="BR9" s="43" t="s">
         <v>49</v>
@@ -5093,7 +5101,7 @@
         <v>201</v>
       </c>
       <c r="BQ10" s="37" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="BR10" s="51" t="s">
         <v>219</v>
@@ -5268,7 +5276,7 @@
         <v>197</v>
       </c>
       <c r="BQ11" s="37" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="BR11" s="51" t="s">
         <v>106</v>
@@ -5447,7 +5455,7 @@
         <v>197</v>
       </c>
       <c r="BQ12" s="37" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="BR12" s="51" t="s">
         <v>107</v>
@@ -5623,8 +5631,8 @@
       <c r="BP13" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="BQ13" s="148" t="s">
-        <v>719</v>
+      <c r="BQ13" s="143" t="s">
+        <v>715</v>
       </c>
       <c r="BR13" s="52" t="s">
         <v>242</v>
@@ -5799,7 +5807,7 @@
         <v>197</v>
       </c>
       <c r="BQ14" s="37" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="BR14" s="43" t="s">
         <v>91</v>
@@ -5977,8 +5985,8 @@
       <c r="BP15" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ15" s="147" t="s">
-        <v>720</v>
+      <c r="BQ15" s="142" t="s">
+        <v>716</v>
       </c>
       <c r="BR15" s="43" t="s">
         <v>221</v>
@@ -6155,7 +6163,7 @@
         <v>197</v>
       </c>
       <c r="BQ16" s="37" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="BR16" s="43" t="s">
         <v>223</v>
@@ -6331,7 +6339,7 @@
         <v>197</v>
       </c>
       <c r="BQ17" s="37" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="BR17" s="43" t="s">
         <v>125</v>
@@ -6507,7 +6515,7 @@
         <v>197</v>
       </c>
       <c r="BQ18" s="18" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="BR18" s="21" t="s">
         <v>128</v>
@@ -6677,7 +6685,7 @@
         <v>197</v>
       </c>
       <c r="BQ19" s="18" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="BR19" s="21" t="s">
         <v>133</v>
@@ -6852,8 +6860,8 @@
       <c r="BP20" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ20" s="146" t="s">
-        <v>697</v>
+      <c r="BQ20" s="141" t="s">
+        <v>693</v>
       </c>
       <c r="BR20" s="21" t="s">
         <v>224</v>
@@ -7030,7 +7038,7 @@
         <v>197</v>
       </c>
       <c r="BQ21" s="18" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="BR21" s="21" t="s">
         <v>167</v>
@@ -7207,7 +7215,7 @@
         <v>197</v>
       </c>
       <c r="BQ22" s="18" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="BR22" s="21" t="s">
         <v>154</v>
@@ -7383,8 +7391,8 @@
       <c r="BP23" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="BQ23" s="146" t="s">
-        <v>725</v>
+      <c r="BQ23" s="141" t="s">
+        <v>721</v>
       </c>
       <c r="BR23" s="21" t="s">
         <v>173</v>
@@ -7558,8 +7566,8 @@
       <c r="BP24" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="BQ24" s="145" t="s">
-        <v>723</v>
+      <c r="BQ24" s="140" t="s">
+        <v>719</v>
       </c>
       <c r="BR24" s="50" t="s">
         <v>243</v>
@@ -7732,11 +7740,11 @@
       <c r="BP25" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="BQ25" s="146" t="s">
-        <v>740</v>
+      <c r="BQ25" s="141" t="s">
+        <v>736</v>
       </c>
       <c r="BR25" s="21" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="26" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
@@ -7911,7 +7919,7 @@
         <v>200</v>
       </c>
       <c r="BQ26" s="18" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="BR26" s="21" t="s">
         <v>179</v>
@@ -8084,8 +8092,8 @@
       <c r="BP27" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="BQ27" s="145" t="s">
-        <v>723</v>
+      <c r="BQ27" s="140" t="s">
+        <v>719</v>
       </c>
       <c r="BR27" s="50" t="s">
         <v>244</v>
@@ -8262,7 +8270,7 @@
         <v>197</v>
       </c>
       <c r="BQ28" s="18" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="BR28" s="21" t="s">
         <v>191</v>
@@ -8599,7 +8607,7 @@
         <v>197</v>
       </c>
       <c r="BQ30" s="18" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="BR30" s="21" t="s">
         <v>196</v>
@@ -8775,7 +8783,7 @@
         <v>197</v>
       </c>
       <c r="BQ31" s="18" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR31" s="21" t="s">
         <v>227</v>
@@ -9281,7 +9289,7 @@
         <v>262</v>
       </c>
       <c r="BQ35" s="37" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="BR35" s="43" t="s">
         <v>263</v>
@@ -9459,7 +9467,7 @@
         <v>197</v>
       </c>
       <c r="BQ36" s="37" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR36" s="43" t="s">
         <v>255</v>
@@ -9625,7 +9633,7 @@
         <v>197</v>
       </c>
       <c r="BQ37" s="37" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="BR37" s="43" t="s">
         <v>271</v>
@@ -10158,7 +10166,7 @@
         <v>208</v>
       </c>
       <c r="BQ40" s="37" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="BR40" s="43" t="s">
         <v>288</v>
@@ -10344,7 +10352,7 @@
         <v>197</v>
       </c>
       <c r="BQ41" s="37" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="BR41" s="43" t="s">
         <v>295</v>
@@ -10519,8 +10527,8 @@
       <c r="BP42" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ42" s="147" t="s">
-        <v>729</v>
+      <c r="BQ42" s="142" t="s">
+        <v>725</v>
       </c>
       <c r="BR42" s="43" t="s">
         <v>297</v>
@@ -10694,7 +10702,7 @@
         <v>354</v>
       </c>
       <c r="BQ43" s="37" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR43" s="43" t="s">
         <v>349</v>
@@ -10872,7 +10880,7 @@
         <v>358</v>
       </c>
       <c r="BQ44" s="37" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR44" s="43" t="s">
         <v>657</v>
@@ -11048,7 +11056,7 @@
         <v>197</v>
       </c>
       <c r="BQ45" s="18" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR45" s="21" t="s">
         <v>369</v>
@@ -11225,7 +11233,7 @@
         <v>376</v>
       </c>
       <c r="BQ46" s="18" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="BR46" s="21" t="s">
         <v>377</v>
@@ -11401,7 +11409,7 @@
         <v>197</v>
       </c>
       <c r="BQ47" s="18" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR47" s="21" t="s">
         <v>383</v>
@@ -11577,7 +11585,7 @@
         <v>197</v>
       </c>
       <c r="BQ48" s="18" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="BR48" s="21" t="s">
         <v>400</v>
@@ -11603,7 +11611,7 @@
         <v>4800994</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="H49" s="12" t="s">
         <v>635</v>
@@ -11938,7 +11946,7 @@
         <v>354</v>
       </c>
       <c r="BQ50" s="18" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR50" s="21" t="s">
         <v>398</v>
@@ -12114,7 +12122,7 @@
         <v>354</v>
       </c>
       <c r="BQ51" s="18" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="BR51" s="21" t="s">
         <v>399</v>
@@ -12485,7 +12493,7 @@
         <v>208</v>
       </c>
       <c r="BQ53" s="18" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="BR53" s="21" t="s">
         <v>417</v>
@@ -12663,7 +12671,7 @@
         <v>197</v>
       </c>
       <c r="BQ54" s="18" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR54" s="21" t="s">
         <v>409</v>
@@ -12841,7 +12849,7 @@
         <v>197</v>
       </c>
       <c r="BQ55" s="18" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="BR55" s="21" t="s">
         <v>419</v>
@@ -13032,7 +13040,7 @@
         <v>424</v>
       </c>
       <c r="BQ56" s="18" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="BR56" s="21" t="s">
         <v>426</v>
@@ -13209,7 +13217,7 @@
         <v>197</v>
       </c>
       <c r="BQ57" s="18" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR57" s="21" t="s">
         <v>427</v>
@@ -13385,7 +13393,7 @@
         <v>354</v>
       </c>
       <c r="BQ58" s="18" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="BR58" s="21" t="s">
         <v>509</v>
@@ -13573,7 +13581,7 @@
         <v>202</v>
       </c>
       <c r="BQ59" s="18" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR59" s="21" t="s">
         <v>396</v>
@@ -13749,7 +13757,7 @@
         <v>197</v>
       </c>
       <c r="BQ60" s="37" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR60" s="43" t="s">
         <v>442</v>
@@ -13925,7 +13933,7 @@
         <v>197</v>
       </c>
       <c r="BQ61" s="37" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="BR61" s="43" t="s">
         <v>677</v>
@@ -14111,7 +14119,7 @@
         <v>208</v>
       </c>
       <c r="BQ62" s="37" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="BR62" s="43" t="s">
         <v>663</v>
@@ -14296,7 +14304,7 @@
       </c>
       <c r="BQ63" s="37"/>
       <c r="BR63" s="43" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="64" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
@@ -14469,7 +14477,7 @@
         <v>202</v>
       </c>
       <c r="BQ64" s="37" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="BR64" s="43" t="s">
         <v>510</v>
@@ -14657,7 +14665,7 @@
       </c>
       <c r="BQ65" s="18"/>
       <c r="BR65" s="21" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="66" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.35">
@@ -14833,7 +14841,7 @@
         <v>197</v>
       </c>
       <c r="BQ66" s="18" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="BR66" s="21" t="s">
         <v>518</v>
@@ -15012,7 +15020,7 @@
         <v>503</v>
       </c>
       <c r="BQ67" s="18" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="BR67" s="21" t="s">
         <v>505</v>
@@ -15201,7 +15209,7 @@
         <v>513</v>
       </c>
       <c r="BQ68" s="18" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="BR68" s="21" t="s">
         <v>662</v>
@@ -15751,7 +15759,7 @@
       </c>
       <c r="BQ71" s="18"/>
       <c r="BR71" s="21" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="BS71" s="88"/>
       <c r="BT71" s="88"/>
@@ -15957,7 +15965,7 @@
         <v>197</v>
       </c>
       <c r="BQ72" s="18" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="BR72" s="21" t="s">
         <v>672</v>
@@ -16347,7 +16355,7 @@
       </c>
       <c r="BQ74" s="37"/>
       <c r="BR74" s="43" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="75" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -16373,7 +16381,7 @@
         <v>129</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="I75" s="3">
         <v>29.1</v>
@@ -16403,7 +16411,7 @@
         <v>-51.84</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="S75" s="3">
         <v>11</v>
@@ -16526,11 +16534,11 @@
         <v>205</v>
       </c>
       <c r="BP75" s="37" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="BQ75" s="37"/>
       <c r="BR75" s="43" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="76" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -16556,7 +16564,7 @@
         <v>15</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="I76" s="3">
         <v>29.1</v>
@@ -16731,7 +16739,7 @@
         <v>15</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="I77" s="3">
         <v>29.2</v>
@@ -16761,7 +16769,7 @@
         <v>-61.46</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="S77" s="3">
         <v>25</v>
@@ -16880,13 +16888,13 @@
         <v>205</v>
       </c>
       <c r="BP77" s="37" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="BQ77" s="37" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="BR77" s="43" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="78" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -16912,7 +16920,7 @@
         <v>15</v>
       </c>
       <c r="H78" s="37" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="I78" s="3">
         <v>29.1</v>
@@ -16997,10 +17005,10 @@
       <c r="AL78" s="35">
         <v>32</v>
       </c>
-      <c r="AM78" s="144" t="s">
+      <c r="AM78" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="AN78" s="46" t="s">
+      <c r="AN78" s="38" t="s">
         <v>678</v>
       </c>
       <c r="AO78" s="38" t="s">
@@ -17012,8 +17020,8 @@
       <c r="AQ78" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="AR78" s="46" t="s">
-        <v>681</v>
+      <c r="AR78" s="38" t="s">
+        <v>679</v>
       </c>
       <c r="AS78" s="38"/>
       <c r="AT78" s="38"/>
@@ -17054,7 +17062,7 @@
         <v>1272212</v>
       </c>
       <c r="BM78" s="3" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="BN78" s="3" t="s">
         <v>670</v>
@@ -17067,7 +17075,7 @@
       </c>
       <c r="BQ78" s="37"/>
       <c r="BR78" s="43" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="79" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -17093,7 +17101,7 @@
         <v>15</v>
       </c>
       <c r="H79" s="37" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="I79" s="3">
         <v>29.1</v>
@@ -17101,10 +17109,10 @@
       <c r="J79" s="3">
         <v>24</v>
       </c>
-      <c r="K79" s="149">
+      <c r="K79" s="144">
         <v>44.273600000000002</v>
       </c>
-      <c r="L79" s="149">
+      <c r="L79" s="144">
         <v>-63.318199999999997</v>
       </c>
       <c r="M79" s="138">
@@ -17123,7 +17131,7 @@
         <v>-61.44</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="S79" s="3">
         <v>26</v>
@@ -17170,18 +17178,18 @@
         <v>20241015</v>
       </c>
       <c r="AJ79" s="37" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="AK79" s="37" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="AL79" s="35">
         <v>33</v>
       </c>
-      <c r="AM79" s="144" t="s">
+      <c r="AM79" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="AN79" s="46" t="s">
+      <c r="AN79" s="38" t="s">
         <v>678</v>
       </c>
       <c r="AO79" s="38" t="s">
@@ -17193,8 +17201,8 @@
       <c r="AQ79" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="AR79" s="46" t="s">
-        <v>681</v>
+      <c r="AR79" s="38" t="s">
+        <v>679</v>
       </c>
       <c r="AS79" s="38"/>
       <c r="AT79" s="38"/>
@@ -17232,10 +17240,10 @@
         <v>138</v>
       </c>
       <c r="BL79" s="38" t="s">
+        <v>702</v>
+      </c>
+      <c r="BM79" s="3" t="s">
         <v>706</v>
-      </c>
-      <c r="BM79" s="3" t="s">
-        <v>710</v>
       </c>
       <c r="BN79" s="3" t="s">
         <v>670</v>
@@ -17248,7 +17256,7 @@
       </c>
       <c r="BQ79" s="37"/>
       <c r="BR79" s="43" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="80" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -17258,7 +17266,9 @@
       <c r="B80" s="35">
         <v>20250211</v>
       </c>
-      <c r="C80" s="35"/>
+      <c r="C80" s="35">
+        <v>20250304</v>
+      </c>
       <c r="D80" s="35" t="s">
         <v>13</v>
       </c>
@@ -17272,12 +17282,14 @@
         <v>15</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="I80" s="3">
         <v>29.1</v>
       </c>
-      <c r="J80" s="3"/>
+      <c r="J80" s="3">
+        <v>25.1</v>
+      </c>
       <c r="K80" s="35">
         <v>44.488300000000002</v>
       </c>
@@ -17287,18 +17299,33 @@
       <c r="M80" s="138">
         <v>0.68819444444444444</v>
       </c>
-      <c r="N80" s="37"/>
-      <c r="O80" s="37"/>
-      <c r="P80" s="37"/>
-      <c r="Q80" s="37"/>
+      <c r="N80" s="37">
+        <v>42.47</v>
+      </c>
+      <c r="O80" s="37">
+        <v>-63.39</v>
+      </c>
+      <c r="P80" s="37">
+        <v>44.5</v>
+      </c>
+      <c r="Q80" s="37">
+        <v>-61.43</v>
+      </c>
       <c r="R80" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="S80" s="3"/>
-      <c r="T80" s="3"/>
-      <c r="U80" s="3"/>
+        <v>752</v>
+      </c>
+      <c r="S80" s="3">
+        <v>21</v>
+      </c>
+      <c r="T80" s="3">
+        <v>574</v>
+      </c>
+      <c r="U80" s="3">
+        <v>876</v>
+      </c>
       <c r="V80" s="3">
-        <v>-4</v>
+        <f>U80*2-12</f>
+        <v>1740</v>
       </c>
       <c r="W80" s="37" t="s">
         <v>36</v>
@@ -17316,9 +17343,15 @@
       <c r="AB80" s="37"/>
       <c r="AC80" s="37"/>
       <c r="AD80" s="37"/>
-      <c r="AE80" s="3"/>
-      <c r="AF80" s="3"/>
-      <c r="AG80" s="3"/>
+      <c r="AE80" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="3">
+        <v>0.5</v>
+      </c>
       <c r="AH80" s="3">
         <v>1024.8</v>
       </c>
@@ -17326,18 +17359,18 @@
         <v>20250131</v>
       </c>
       <c r="AJ80" s="37" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="AK80" s="37" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="AL80" s="35">
         <v>33</v>
       </c>
-      <c r="AM80" s="144" t="s">
+      <c r="AM80" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="AN80" s="46" t="s">
+      <c r="AN80" s="38" t="s">
         <v>678</v>
       </c>
       <c r="AO80" s="38" t="s">
@@ -17349,8 +17382,8 @@
       <c r="AQ80" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="AR80" s="46" t="s">
-        <v>681</v>
+      <c r="AR80" s="38" t="s">
+        <v>679</v>
       </c>
       <c r="AS80" s="38"/>
       <c r="AT80" s="38"/>
@@ -17388,10 +17421,10 @@
         <v>138</v>
       </c>
       <c r="BL80" s="38" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="BM80" s="3" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="BN80" s="3" t="s">
         <v>670</v>
@@ -17400,7 +17433,7 @@
         <v>205</v>
       </c>
       <c r="BP80" s="37" t="s">
-        <v>747</v>
+        <v>197</v>
       </c>
       <c r="BQ80" s="37" t="s">
         <v>754</v>
@@ -17413,7 +17446,9 @@
       <c r="A81" s="137">
         <v>9</v>
       </c>
-      <c r="B81" s="35"/>
+      <c r="B81" s="35">
+        <v>20250304</v>
+      </c>
       <c r="C81" s="35"/>
       <c r="D81" s="35" t="s">
         <v>44</v>
@@ -17428,13 +17463,21 @@
         <v>15</v>
       </c>
       <c r="H81" s="37" t="s">
-        <v>750</v>
-      </c>
-      <c r="I81" s="3"/>
+        <v>745</v>
+      </c>
+      <c r="I81" s="3">
+        <v>28.9</v>
+      </c>
       <c r="J81" s="3"/>
-      <c r="K81" s="35"/>
-      <c r="L81" s="35"/>
-      <c r="M81" s="138"/>
+      <c r="K81" s="35">
+        <v>44.452500000000001</v>
+      </c>
+      <c r="L81" s="35">
+        <v>-63.382199999999997</v>
+      </c>
+      <c r="M81" s="138">
+        <v>0.62847222222222221</v>
+      </c>
       <c r="N81" s="37"/>
       <c r="O81" s="37"/>
       <c r="P81" s="37"/>
@@ -17474,19 +17517,19 @@
         <v>20250218</v>
       </c>
       <c r="AJ81" s="37" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
       <c r="AK81" s="37" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="AL81" s="35">
         <v>30</v>
       </c>
-      <c r="AM81" s="144" t="s">
+      <c r="AM81" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="AN81" s="46" t="s">
-        <v>756</v>
+      <c r="AN81" s="38" t="s">
+        <v>748</v>
       </c>
       <c r="AO81" s="38" t="s">
         <v>212</v>
@@ -17497,8 +17540,8 @@
       <c r="AQ81" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="AR81" s="46" t="s">
-        <v>757</v>
+      <c r="AR81" s="38" t="s">
+        <v>749</v>
       </c>
       <c r="AS81" s="38"/>
       <c r="AT81" s="38"/>
@@ -17518,7 +17561,7 @@
         <v>451</v>
       </c>
       <c r="BB81" s="38" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="BC81" s="38" t="s">
         <v>420</v>
@@ -17539,7 +17582,7 @@
         <v>588</v>
       </c>
       <c r="BK81" s="38" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="BL81" s="3">
         <v>1540746</v>
@@ -17551,21 +17594,33 @@
       <c r="BO81" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP81" s="37"/>
+      <c r="BP81" s="37" t="s">
+        <v>755</v>
+      </c>
       <c r="BQ81" s="37"/>
       <c r="BR81" s="43" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
     </row>
     <row r="82" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="137"/>
       <c r="B82" s="35"/>
       <c r="C82" s="35"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="35"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="37"/>
+      <c r="D82" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E82" s="35">
+        <v>89</v>
+      </c>
+      <c r="F82" s="35">
+        <v>4800937</v>
+      </c>
+      <c r="G82" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="37" t="s">
+        <v>762</v>
+      </c>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="35"/>
@@ -17575,15 +17630,25 @@
       <c r="O82" s="37"/>
       <c r="P82" s="37"/>
       <c r="Q82" s="37"/>
-      <c r="R82" s="3"/>
+      <c r="R82" s="3" t="s">
+        <v>444</v>
+      </c>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-      <c r="W82" s="37"/>
-      <c r="X82" s="37"/>
-      <c r="Y82" s="37"/>
-      <c r="Z82" s="37"/>
+      <c r="W82" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="X82" s="37">
+        <v>1</v>
+      </c>
+      <c r="Y82" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z82" s="37" t="s">
+        <v>183</v>
+      </c>
       <c r="AA82" s="37"/>
       <c r="AB82" s="37"/>
       <c r="AC82" s="37"/>
@@ -17591,23 +17656,51 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-      <c r="AH82" s="3"/>
-      <c r="AI82" s="37"/>
-      <c r="AJ82" s="37"/>
-      <c r="AK82" s="37"/>
-      <c r="AL82" s="35"/>
-      <c r="AM82" s="144"/>
-      <c r="AN82" s="46"/>
-      <c r="AO82" s="38"/>
-      <c r="AP82" s="41"/>
-      <c r="AQ82" s="41"/>
-      <c r="AR82" s="46"/>
+      <c r="AH82" s="3">
+        <v>1024.9000000000001</v>
+      </c>
+      <c r="AI82" s="37">
+        <v>20250305</v>
+      </c>
+      <c r="AJ82" s="37" t="s">
+        <v>756</v>
+      </c>
+      <c r="AK82" s="37" t="s">
+        <v>740</v>
+      </c>
+      <c r="AL82" s="35">
+        <v>32</v>
+      </c>
+      <c r="AM82" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN82" s="38" t="s">
+        <v>760</v>
+      </c>
+      <c r="AO82" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="AP82" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ82" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR82" s="38" t="s">
+        <v>759</v>
+      </c>
       <c r="AS82" s="38"/>
       <c r="AT82" s="38"/>
       <c r="AU82" s="38"/>
-      <c r="AV82" s="41"/>
-      <c r="AW82" s="39"/>
-      <c r="AX82" s="38"/>
+      <c r="AV82" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW82" s="39">
+        <v>42711</v>
+      </c>
+      <c r="AX82" s="38" t="s">
+        <v>461</v>
+      </c>
       <c r="AY82" s="38"/>
       <c r="AZ82" s="38"/>
       <c r="BA82" s="38"/>
@@ -17616,18 +17709,36 @@
       <c r="BD82" s="38"/>
       <c r="BE82" s="38"/>
       <c r="BF82" s="38"/>
-      <c r="BG82" s="34"/>
-      <c r="BH82" s="139"/>
-      <c r="BI82" s="38"/>
-      <c r="BJ82" s="38"/>
+      <c r="BG82" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="BH82" s="96" t="s">
+        <v>171</v>
+      </c>
+      <c r="BI82" s="38" t="s">
+        <v>515</v>
+      </c>
+      <c r="BJ82" s="38" t="s">
+        <v>516</v>
+      </c>
       <c r="BK82" s="133"/>
-      <c r="BL82" s="133"/>
-      <c r="BM82" s="3"/>
-      <c r="BN82" s="151"/>
-      <c r="BO82" s="3"/>
+      <c r="BL82" s="134">
+        <v>1272212</v>
+      </c>
+      <c r="BM82" s="134" t="s">
+        <v>763</v>
+      </c>
+      <c r="BN82" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="BO82" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="BP82" s="37"/>
       <c r="BQ82" s="37"/>
-      <c r="BR82" s="43"/>
+      <c r="BR82" s="43" t="s">
+        <v>764</v>
+      </c>
     </row>
     <row r="83" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="137"/>
@@ -17668,12 +17779,12 @@
       <c r="AJ83" s="37"/>
       <c r="AK83" s="37"/>
       <c r="AL83" s="35"/>
-      <c r="AM83" s="144"/>
-      <c r="AN83" s="46"/>
+      <c r="AM83" s="34"/>
+      <c r="AN83" s="38"/>
       <c r="AO83" s="38"/>
       <c r="AP83" s="41"/>
       <c r="AQ83" s="41"/>
-      <c r="AR83" s="46"/>
+      <c r="AR83" s="38"/>
       <c r="AS83" s="38"/>
       <c r="AT83" s="38"/>
       <c r="AU83" s="38"/>
@@ -17695,7 +17806,7 @@
       <c r="BK83" s="133"/>
       <c r="BL83" s="133"/>
       <c r="BM83" s="3"/>
-      <c r="BN83" s="151"/>
+      <c r="BN83" s="146"/>
       <c r="BO83" s="3"/>
       <c r="BP83" s="37"/>
       <c r="BQ83" s="37"/>
@@ -17740,12 +17851,12 @@
       <c r="AJ84" s="37"/>
       <c r="AK84" s="37"/>
       <c r="AL84" s="35"/>
-      <c r="AM84" s="144"/>
-      <c r="AN84" s="46"/>
+      <c r="AM84" s="34"/>
+      <c r="AN84" s="38"/>
       <c r="AO84" s="38"/>
       <c r="AP84" s="41"/>
       <c r="AQ84" s="41"/>
-      <c r="AR84" s="46"/>
+      <c r="AR84" s="38"/>
       <c r="AS84" s="38"/>
       <c r="AT84" s="38"/>
       <c r="AU84" s="38"/>
@@ -17767,7 +17878,7 @@
       <c r="BK84" s="133"/>
       <c r="BL84" s="133"/>
       <c r="BM84" s="3"/>
-      <c r="BN84" s="151"/>
+      <c r="BN84" s="146"/>
       <c r="BO84" s="3"/>
       <c r="BP84" s="37"/>
       <c r="BQ84" s="37"/>
@@ -17812,12 +17923,12 @@
       <c r="AJ85" s="37"/>
       <c r="AK85" s="37"/>
       <c r="AL85" s="35"/>
-      <c r="AM85" s="144"/>
-      <c r="AN85" s="46"/>
+      <c r="AM85" s="34"/>
+      <c r="AN85" s="38"/>
       <c r="AO85" s="38"/>
       <c r="AP85" s="41"/>
       <c r="AQ85" s="41"/>
-      <c r="AR85" s="46"/>
+      <c r="AR85" s="38"/>
       <c r="AS85" s="38"/>
       <c r="AT85" s="38"/>
       <c r="AU85" s="38"/>
@@ -17839,7 +17950,7 @@
       <c r="BK85" s="133"/>
       <c r="BL85" s="133"/>
       <c r="BM85" s="3"/>
-      <c r="BN85" s="151"/>
+      <c r="BN85" s="146"/>
       <c r="BO85" s="3"/>
       <c r="BP85" s="37"/>
       <c r="BQ85" s="37"/>
@@ -17908,7 +18019,7 @@
       <c r="BH86" s="139"/>
       <c r="BI86" s="38"/>
       <c r="BJ86" s="38" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="BK86" s="38"/>
       <c r="BL86" s="38"/>
@@ -17983,8 +18094,8 @@
       <c r="BI87" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BJ87" s="133" t="s">
-        <v>287</v>
+      <c r="BJ87" s="147" t="s">
+        <v>751</v>
       </c>
       <c r="BK87" s="38"/>
       <c r="BL87" s="38"/>
@@ -18021,20 +18132,12 @@
       <c r="AJ88" s="77"/>
       <c r="AK88" s="77"/>
       <c r="AL88" s="116"/>
-      <c r="AM88" s="140" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN88" s="141" t="s">
-        <v>689</v>
-      </c>
-      <c r="AO88" s="142"/>
-      <c r="AP88" s="143"/>
-      <c r="AQ88" s="140" t="s">
-        <v>679</v>
-      </c>
-      <c r="AR88" s="141" t="s">
-        <v>688</v>
-      </c>
+      <c r="AM88" s="27"/>
+      <c r="AN88" s="26"/>
+      <c r="AO88" s="78"/>
+      <c r="AP88" s="117"/>
+      <c r="AQ88" s="27"/>
+      <c r="AR88" s="26"/>
       <c r="AS88" s="78"/>
       <c r="AT88" s="78"/>
       <c r="AU88" s="78"/>
@@ -18054,7 +18157,7 @@
       <c r="BI88" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="BJ88" s="150" t="s">
+      <c r="BJ88" s="145" t="s">
         <v>588</v>
       </c>
       <c r="BK88" s="38"/>
@@ -18092,25 +18195,21 @@
       <c r="AJ89" s="77"/>
       <c r="AK89" s="77"/>
       <c r="AL89" s="116"/>
-      <c r="AM89" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN89" s="26" t="s">
-        <v>678</v>
-      </c>
+      <c r="AM89" s="27"/>
+      <c r="AN89" s="26"/>
       <c r="AO89" s="78"/>
       <c r="AP89" s="117"/>
-      <c r="AQ89" s="27" t="s">
-        <v>680</v>
-      </c>
-      <c r="AR89" s="26" t="s">
-        <v>681</v>
-      </c>
+      <c r="AQ89" s="27"/>
+      <c r="AR89" s="26"/>
       <c r="AS89" s="78"/>
       <c r="AT89" s="78"/>
       <c r="AU89" s="78"/>
-      <c r="AV89" s="117"/>
-      <c r="AW89" s="78"/>
+      <c r="AV89" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW89" s="26" t="s">
+        <v>758</v>
+      </c>
       <c r="AX89" s="78"/>
       <c r="AY89" s="78"/>
       <c r="AZ89" s="78"/>
@@ -18125,7 +18224,7 @@
       <c r="BI89" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="BJ89" s="150" t="s">
+      <c r="BJ89" s="145" t="s">
         <v>589</v>
       </c>
       <c r="BK89" s="38"/>
@@ -18172,8 +18271,12 @@
       <c r="AS90" s="78"/>
       <c r="AT90" s="78"/>
       <c r="AU90" s="78"/>
-      <c r="AV90" s="117"/>
-      <c r="AW90" s="78"/>
+      <c r="AV90" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW90" s="26" t="s">
+        <v>757</v>
+      </c>
       <c r="AX90" s="78"/>
       <c r="AY90" s="78"/>
       <c r="AZ90" s="78"/>
@@ -18188,8 +18291,8 @@
       <c r="BI90" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="BJ90" s="133" t="s">
-        <v>453</v>
+      <c r="BJ90" s="147" t="s">
+        <v>750</v>
       </c>
       <c r="BK90" s="133"/>
       <c r="BL90" s="133"/>
@@ -18251,7 +18354,7 @@
       <c r="BI91" s="38" t="s">
         <v>515</v>
       </c>
-      <c r="BJ91" s="152" t="s">
+      <c r="BJ91" s="147" t="s">
         <v>516</v>
       </c>
       <c r="BK91" s="38"/>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F88571-2032-4DC8-9921-519CC1F6DDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F1E973-0B8A-47F1-9D55-190D4262700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="786">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2314,15 +2314,9 @@
     <t>TRI-GL1-GL2-GL3-GL7-GL3-GL2-GL1-NSC-TRI-DR</t>
   </si>
   <si>
-    <t>Another firmware updrade with many changes like showing humidity inside glider with X3 board, and many more little things. GPCTD possibly clogged or pump failure, we tried to turn GPCTD off multiple time to clear the possible clog (12 dives total ishh), base of antenna broken, might have been hit by a boat</t>
-  </si>
-  <si>
     <t>GPCTD possibly clogged or pump failure, gpctd turned off multiple times to try to clear the clog</t>
   </si>
   <si>
-    <t>sigma-T/</t>
-  </si>
-  <si>
     <t>3.8.2-r</t>
   </si>
   <si>
@@ -2338,16 +2332,85 @@
     <t>20241211</t>
   </si>
   <si>
-    <t>with Legato and T.ODO, CDOM negative values</t>
-  </si>
-  <si>
     <t>GLI2025_SEA032_089</t>
   </si>
   <si>
     <t>AZMP spring 2025</t>
   </si>
   <si>
-    <t>with T.ODO</t>
+    <t>sigma-T/M.Perley</t>
+  </si>
+  <si>
+    <t>212536</t>
+  </si>
+  <si>
+    <t>214389</t>
+  </si>
+  <si>
+    <t>212531</t>
+  </si>
+  <si>
+    <t>214386</t>
+  </si>
+  <si>
+    <t>rbr</t>
+  </si>
+  <si>
+    <t>alseamar</t>
+  </si>
+  <si>
+    <t>Another firmware updrade with many changes like showing humidity inside glider with X3 board, and many more little things. GPCTD possibly clogged or pump failure, we tried to turn GPCTD off multiple time to clear the possible clog (12 dives total ishh) need to send to SBE, base of antenna broken, might have been hit by a boat</t>
+  </si>
+  <si>
+    <t>GPCTD failled half way through the mission</t>
+  </si>
+  <si>
+    <t>CDOM in the negative range (will be flagged I guess, so maybe not needed in the comments)</t>
+  </si>
+  <si>
+    <t>237958</t>
+  </si>
+  <si>
+    <t>with Legato and T.ODO, CDOM negative values, can't load the T.ODO values, wrong battery was inside, need to send to RBR, TODO data not recoverable</t>
+  </si>
+  <si>
+    <t>M.Perley/Sigma-T</t>
+  </si>
+  <si>
+    <t>with T.ODO, GPCTD failed on the way out between HL6 and HL7 (before AZMP sampling), used the LARS on recovery for the first time</t>
+  </si>
+  <si>
+    <t>212279</t>
+  </si>
+  <si>
+    <t>212973</t>
+  </si>
+  <si>
+    <t>CODA cal date</t>
+  </si>
+  <si>
+    <t>CODA s/n</t>
+  </si>
+  <si>
+    <t>20250417</t>
+  </si>
+  <si>
+    <t>first mission with wet legato</t>
+  </si>
+  <si>
+    <t>old</t>
+  </si>
+  <si>
+    <t>wood new</t>
+  </si>
+  <si>
+    <t>20250325</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>old for now</t>
   </si>
 </sst>
 </file>
@@ -2673,7 +2736,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3030,11 +3093,20 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3365,7 +3437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CW95"/>
+  <dimension ref="A1:CY95"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.1796875" customWidth="1"/>
@@ -3420,22 +3492,22 @@
     <col min="53" max="53" width="11.81640625" style="78" customWidth="1"/>
     <col min="54" max="54" width="14.81640625" style="78" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="15.1796875" style="78" bestFit="1" customWidth="1"/>
-    <col min="56" max="58" width="15.1796875" style="78" customWidth="1"/>
-    <col min="59" max="59" width="11.81640625" style="5" customWidth="1"/>
-    <col min="60" max="60" width="11.81640625" style="1" customWidth="1"/>
-    <col min="61" max="61" width="12.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="12.81640625" style="6" customWidth="1"/>
-    <col min="63" max="63" width="7" style="6" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="7.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="19" style="4" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="20" style="4" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="25.81640625" style="7" customWidth="1"/>
-    <col min="69" max="69" width="64.453125" style="7" customWidth="1"/>
-    <col min="70" max="70" width="78.81640625" style="8" customWidth="1"/>
+    <col min="56" max="60" width="15.1796875" style="78" customWidth="1"/>
+    <col min="61" max="61" width="11.81640625" style="5" customWidth="1"/>
+    <col min="62" max="62" width="11.81640625" style="1" customWidth="1"/>
+    <col min="63" max="63" width="12.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="12.81640625" style="6" customWidth="1"/>
+    <col min="65" max="65" width="7" style="6" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="7.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="19" style="4" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="20" style="4" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="25.81640625" style="7" customWidth="1"/>
+    <col min="71" max="71" width="64.453125" style="7" customWidth="1"/>
+    <col min="72" max="72" width="78.81640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
       <c r="D1" s="94" t="s">
@@ -3485,19 +3557,21 @@
       <c r="BD1" s="26"/>
       <c r="BE1" s="26"/>
       <c r="BF1" s="26"/>
-      <c r="BG1" s="27"/>
-      <c r="BH1" s="28"/>
-      <c r="BI1" s="26"/>
-      <c r="BJ1" s="26"/>
+      <c r="BG1" s="26"/>
+      <c r="BH1" s="26"/>
+      <c r="BI1" s="27"/>
+      <c r="BJ1" s="28"/>
       <c r="BK1" s="26"/>
       <c r="BL1" s="26"/>
-      <c r="BN1" s="29"/>
-      <c r="BO1" s="29"/>
-      <c r="BP1" s="25"/>
-      <c r="BQ1" s="25"/>
-      <c r="BR1" s="30"/>
+      <c r="BM1" s="26"/>
+      <c r="BN1" s="26"/>
+      <c r="BP1" s="29"/>
+      <c r="BQ1" s="29"/>
+      <c r="BR1" s="25"/>
+      <c r="BS1" s="25"/>
+      <c r="BT1" s="30"/>
     </row>
-    <row r="2" spans="1:70" s="63" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:72" s="63" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="64" t="s">
         <v>0</v>
       </c>
@@ -3661,52 +3735,58 @@
         <v>312</v>
       </c>
       <c r="BD2" s="70" t="s">
+        <v>778</v>
+      </c>
+      <c r="BE2" s="70" t="s">
+        <v>777</v>
+      </c>
+      <c r="BF2" s="70" t="s">
         <v>364</v>
       </c>
-      <c r="BE2" s="70" t="s">
+      <c r="BG2" s="70" t="s">
         <v>365</v>
       </c>
-      <c r="BF2" s="70" t="s">
+      <c r="BH2" s="70" t="s">
         <v>366</v>
       </c>
-      <c r="BG2" s="73" t="s">
+      <c r="BI2" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="BH2" s="33" t="s">
+      <c r="BJ2" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="BI2" s="70" t="s">
+      <c r="BK2" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="BJ2" s="70" t="s">
+      <c r="BL2" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="BK2" s="70" t="s">
+      <c r="BM2" s="70" t="s">
         <v>222</v>
       </c>
-      <c r="BL2" s="70" t="s">
+      <c r="BN2" s="70" t="s">
         <v>690</v>
       </c>
-      <c r="BM2" s="32" t="s">
+      <c r="BO2" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="BN2" s="74" t="s">
+      <c r="BP2" s="74" t="s">
         <v>192</v>
       </c>
-      <c r="BO2" s="74" t="s">
+      <c r="BQ2" s="74" t="s">
         <v>193</v>
       </c>
-      <c r="BP2" s="75" t="s">
+      <c r="BR2" s="75" t="s">
         <v>661</v>
       </c>
-      <c r="BQ2" s="75" t="s">
+      <c r="BS2" s="75" t="s">
         <v>691</v>
       </c>
-      <c r="BR2" s="76" t="s">
+      <c r="BT2" s="76" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:70" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9">
         <v>1</v>
       </c>
@@ -3850,36 +3930,38 @@
       <c r="BD3" s="15"/>
       <c r="BE3" s="15"/>
       <c r="BF3" s="15"/>
-      <c r="BG3" s="10" t="s">
+      <c r="BG3" s="15"/>
+      <c r="BH3" s="15"/>
+      <c r="BI3" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH3" s="17" t="s">
+      <c r="BJ3" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BI3" s="15" t="s">
+      <c r="BK3" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ3" s="15" t="s">
+      <c r="BL3" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="BK3" s="15"/>
-      <c r="BL3" s="15"/>
-      <c r="BM3" s="13"/>
-      <c r="BN3" s="14" t="s">
+      <c r="BM3" s="15"/>
+      <c r="BN3" s="15"/>
+      <c r="BO3" s="13"/>
+      <c r="BP3" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO3" s="14" t="s">
+      <c r="BQ3" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP3" s="18" t="s">
+      <c r="BR3" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ3" s="12"/>
-      <c r="BR3" s="19" t="s">
+      <c r="BS3" s="12"/>
+      <c r="BT3" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="4" spans="1:70" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="82">
         <v>2</v>
       </c>
@@ -4023,38 +4105,40 @@
       <c r="BD4" s="15"/>
       <c r="BE4" s="15"/>
       <c r="BF4" s="15"/>
-      <c r="BG4" s="10" t="s">
+      <c r="BG4" s="15"/>
+      <c r="BH4" s="15"/>
+      <c r="BI4" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH4" s="17" t="s">
+      <c r="BJ4" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BI4" s="15" t="s">
+      <c r="BK4" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ4" s="15" t="s">
+      <c r="BL4" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="BK4" s="15"/>
-      <c r="BL4" s="15"/>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="14" t="s">
+      <c r="BM4" s="15"/>
+      <c r="BN4" s="15"/>
+      <c r="BO4" s="2"/>
+      <c r="BP4" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO4" s="14" t="s">
+      <c r="BQ4" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP4" s="18" t="s">
+      <c r="BR4" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="BQ4" s="18" t="s">
+      <c r="BS4" s="18" t="s">
         <v>709</v>
       </c>
-      <c r="BR4" s="21" t="s">
+      <c r="BT4" s="21" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="5" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="23">
         <v>1</v>
       </c>
@@ -4198,38 +4282,40 @@
       <c r="BD5" s="40"/>
       <c r="BE5" s="40"/>
       <c r="BF5" s="40"/>
-      <c r="BG5" s="41" t="s">
+      <c r="BG5" s="40"/>
+      <c r="BH5" s="40"/>
+      <c r="BI5" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH5" s="42" t="s">
+      <c r="BJ5" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI5" s="40" t="s">
+      <c r="BK5" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BJ5" s="40" t="s">
+      <c r="BL5" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="BK5" s="40"/>
-      <c r="BL5" s="40"/>
-      <c r="BM5" s="3" t="s">
+      <c r="BM5" s="40"/>
+      <c r="BN5" s="40"/>
+      <c r="BO5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="BN5" s="35" t="s">
+      <c r="BP5" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO5" s="35" t="s">
+      <c r="BQ5" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP5" s="37" t="s">
+      <c r="BR5" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ5" s="37"/>
-      <c r="BR5" s="43" t="s">
+      <c r="BS5" s="37"/>
+      <c r="BT5" s="43" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="23">
         <v>2</v>
       </c>
@@ -4374,38 +4460,40 @@
       <c r="BD6" s="40"/>
       <c r="BE6" s="40"/>
       <c r="BF6" s="40"/>
-      <c r="BG6" s="41" t="s">
+      <c r="BG6" s="40"/>
+      <c r="BH6" s="40"/>
+      <c r="BI6" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH6" s="42" t="s">
+      <c r="BJ6" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI6" s="40" t="s">
+      <c r="BK6" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BJ6" s="40" t="s">
+      <c r="BL6" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="BK6" s="40"/>
-      <c r="BL6" s="40"/>
-      <c r="BM6" s="3"/>
-      <c r="BN6" s="35" t="s">
+      <c r="BM6" s="40"/>
+      <c r="BN6" s="40"/>
+      <c r="BO6" s="3"/>
+      <c r="BP6" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO6" s="35" t="s">
+      <c r="BQ6" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP6" s="37" t="s">
+      <c r="BR6" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ6" s="37" t="s">
+      <c r="BS6" s="37" t="s">
         <v>710</v>
       </c>
-      <c r="BR6" s="43" t="s">
+      <c r="BT6" s="43" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="23">
         <v>3</v>
       </c>
@@ -4549,40 +4637,42 @@
       <c r="BD7" s="40"/>
       <c r="BE7" s="40"/>
       <c r="BF7" s="40"/>
-      <c r="BG7" s="41" t="s">
+      <c r="BG7" s="40"/>
+      <c r="BH7" s="40"/>
+      <c r="BI7" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH7" s="42" t="s">
+      <c r="BJ7" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI7" s="40" t="s">
+      <c r="BK7" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BJ7" s="40" t="s">
+      <c r="BL7" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="BK7" s="40"/>
-      <c r="BL7" s="40"/>
-      <c r="BM7" s="3" t="s">
+      <c r="BM7" s="40"/>
+      <c r="BN7" s="40"/>
+      <c r="BO7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BN7" s="35" t="s">
+      <c r="BP7" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO7" s="35" t="s">
+      <c r="BQ7" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP7" s="37" t="s">
+      <c r="BR7" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ7" s="37" t="s">
+      <c r="BS7" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="BR7" s="43" t="s">
+      <c r="BT7" s="43" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="8" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="23">
         <v>4</v>
       </c>
@@ -4726,38 +4816,40 @@
       <c r="BD8" s="40"/>
       <c r="BE8" s="40"/>
       <c r="BF8" s="40"/>
-      <c r="BG8" s="41" t="s">
+      <c r="BG8" s="40"/>
+      <c r="BH8" s="40"/>
+      <c r="BI8" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH8" s="42" t="s">
+      <c r="BJ8" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI8" s="40" t="s">
+      <c r="BK8" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BJ8" s="40" t="s">
+      <c r="BL8" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BK8" s="40"/>
-      <c r="BL8" s="40"/>
-      <c r="BM8" s="3"/>
-      <c r="BN8" s="35" t="s">
+      <c r="BM8" s="40"/>
+      <c r="BN8" s="40"/>
+      <c r="BO8" s="3"/>
+      <c r="BP8" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO8" s="35" t="s">
+      <c r="BQ8" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP8" s="37" t="s">
+      <c r="BR8" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ8" s="37" t="s">
+      <c r="BS8" s="37" t="s">
         <v>712</v>
       </c>
-      <c r="BR8" s="43" t="s">
+      <c r="BT8" s="43" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="9" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="23">
         <v>5</v>
       </c>
@@ -4901,38 +4993,40 @@
       <c r="BD9" s="40"/>
       <c r="BE9" s="40"/>
       <c r="BF9" s="40"/>
-      <c r="BG9" s="41" t="s">
+      <c r="BG9" s="40"/>
+      <c r="BH9" s="40"/>
+      <c r="BI9" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH9" s="42" t="s">
+      <c r="BJ9" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI9" s="40" t="s">
+      <c r="BK9" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BJ9" s="40" t="s">
+      <c r="BL9" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="BK9" s="40"/>
-      <c r="BL9" s="40"/>
-      <c r="BM9" s="3"/>
-      <c r="BN9" s="35" t="s">
+      <c r="BM9" s="40"/>
+      <c r="BN9" s="40"/>
+      <c r="BO9" s="3"/>
+      <c r="BP9" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO9" s="35" t="s">
+      <c r="BQ9" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP9" s="37" t="s">
+      <c r="BR9" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ9" s="37" t="s">
+      <c r="BS9" s="37" t="s">
         <v>713</v>
       </c>
-      <c r="BR9" s="43" t="s">
+      <c r="BT9" s="43" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="23">
         <v>6</v>
       </c>
@@ -5076,38 +5170,40 @@
       <c r="BD10" s="40"/>
       <c r="BE10" s="40"/>
       <c r="BF10" s="40"/>
-      <c r="BG10" s="41" t="s">
+      <c r="BG10" s="40"/>
+      <c r="BH10" s="40"/>
+      <c r="BI10" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH10" s="42" t="s">
+      <c r="BJ10" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI10" s="40" t="s">
+      <c r="BK10" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BJ10" s="40" t="s">
+      <c r="BL10" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BK10" s="40"/>
-      <c r="BL10" s="40"/>
-      <c r="BM10" s="3"/>
-      <c r="BN10" s="35" t="s">
+      <c r="BM10" s="40"/>
+      <c r="BN10" s="40"/>
+      <c r="BO10" s="3"/>
+      <c r="BP10" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO10" s="35" t="s">
+      <c r="BQ10" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP10" s="37" t="s">
+      <c r="BR10" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="BQ10" s="37" t="s">
+      <c r="BS10" s="37" t="s">
         <v>713</v>
       </c>
-      <c r="BR10" s="51" t="s">
+      <c r="BT10" s="51" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="11" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="23">
         <v>7</v>
       </c>
@@ -5251,38 +5347,40 @@
       <c r="BD11" s="40"/>
       <c r="BE11" s="40"/>
       <c r="BF11" s="40"/>
-      <c r="BG11" s="41" t="s">
+      <c r="BG11" s="40"/>
+      <c r="BH11" s="40"/>
+      <c r="BI11" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH11" s="42" t="s">
+      <c r="BJ11" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI11" s="40" t="s">
+      <c r="BK11" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BJ11" s="40" t="s">
+      <c r="BL11" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BK11" s="40"/>
-      <c r="BL11" s="40"/>
-      <c r="BM11" s="3"/>
-      <c r="BN11" s="35" t="s">
+      <c r="BM11" s="40"/>
+      <c r="BN11" s="40"/>
+      <c r="BO11" s="3"/>
+      <c r="BP11" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO11" s="35" t="s">
+      <c r="BQ11" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP11" s="37" t="s">
+      <c r="BR11" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ11" s="37" t="s">
+      <c r="BS11" s="37" t="s">
         <v>714</v>
       </c>
-      <c r="BR11" s="51" t="s">
+      <c r="BT11" s="51" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="23">
         <v>8</v>
       </c>
@@ -5430,38 +5528,40 @@
       <c r="BD12" s="40"/>
       <c r="BE12" s="40"/>
       <c r="BF12" s="40"/>
-      <c r="BG12" s="41" t="s">
+      <c r="BG12" s="40"/>
+      <c r="BH12" s="40"/>
+      <c r="BI12" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH12" s="42" t="s">
+      <c r="BJ12" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI12" s="40" t="s">
+      <c r="BK12" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BJ12" s="40" t="s">
+      <c r="BL12" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="BK12" s="40"/>
-      <c r="BL12" s="40"/>
-      <c r="BM12" s="3"/>
-      <c r="BN12" s="35" t="s">
+      <c r="BM12" s="40"/>
+      <c r="BN12" s="40"/>
+      <c r="BO12" s="3"/>
+      <c r="BP12" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO12" s="35" t="s">
+      <c r="BQ12" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP12" s="37" t="s">
+      <c r="BR12" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ12" s="37" t="s">
+      <c r="BS12" s="37" t="s">
         <v>714</v>
       </c>
-      <c r="BR12" s="51" t="s">
+      <c r="BT12" s="51" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="23">
         <v>9</v>
       </c>
@@ -5605,40 +5705,42 @@
       <c r="BD13" s="40"/>
       <c r="BE13" s="40"/>
       <c r="BF13" s="40"/>
-      <c r="BG13" s="41" t="s">
+      <c r="BG13" s="40"/>
+      <c r="BH13" s="40"/>
+      <c r="BI13" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH13" s="42" t="s">
+      <c r="BJ13" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI13" s="38" t="s">
+      <c r="BK13" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BJ13" s="38" t="s">
+      <c r="BL13" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="BK13" s="38"/>
-      <c r="BL13" s="38"/>
-      <c r="BM13" s="3" t="s">
+      <c r="BM13" s="38"/>
+      <c r="BN13" s="38"/>
+      <c r="BO13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="BN13" s="35" t="s">
+      <c r="BP13" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO13" s="35" t="s">
+      <c r="BQ13" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP13" s="37" t="s">
+      <c r="BR13" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="BQ13" s="143" t="s">
+      <c r="BS13" s="143" t="s">
         <v>715</v>
       </c>
-      <c r="BR13" s="52" t="s">
+      <c r="BT13" s="52" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="14" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="23">
         <v>10</v>
       </c>
@@ -5782,38 +5884,40 @@
       <c r="BD14" s="40"/>
       <c r="BE14" s="40"/>
       <c r="BF14" s="40"/>
-      <c r="BG14" s="41" t="s">
+      <c r="BG14" s="40"/>
+      <c r="BH14" s="40"/>
+      <c r="BI14" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH14" s="42" t="s">
+      <c r="BJ14" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI14" s="40" t="s">
+      <c r="BK14" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BJ14" s="40" t="s">
+      <c r="BL14" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BK14" s="40"/>
-      <c r="BL14" s="40"/>
-      <c r="BM14" s="3"/>
-      <c r="BN14" s="35" t="s">
+      <c r="BM14" s="40"/>
+      <c r="BN14" s="40"/>
+      <c r="BO14" s="3"/>
+      <c r="BP14" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO14" s="35" t="s">
+      <c r="BQ14" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP14" s="37" t="s">
+      <c r="BR14" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ14" s="37" t="s">
+      <c r="BS14" s="37" t="s">
         <v>713</v>
       </c>
-      <c r="BR14" s="43" t="s">
+      <c r="BT14" s="43" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="23">
         <v>11</v>
       </c>
@@ -5961,38 +6065,40 @@
       <c r="BD15" s="40"/>
       <c r="BE15" s="40"/>
       <c r="BF15" s="40"/>
-      <c r="BG15" s="41" t="s">
+      <c r="BG15" s="40"/>
+      <c r="BH15" s="40"/>
+      <c r="BI15" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH15" s="42" t="s">
+      <c r="BJ15" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI15" s="40" t="s">
+      <c r="BK15" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BJ15" s="40" t="s">
+      <c r="BL15" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BK15" s="40"/>
-      <c r="BL15" s="40"/>
-      <c r="BM15" s="3"/>
-      <c r="BN15" s="35" t="s">
+      <c r="BM15" s="40"/>
+      <c r="BN15" s="40"/>
+      <c r="BO15" s="3"/>
+      <c r="BP15" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO15" s="35" t="s">
+      <c r="BQ15" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP15" s="37" t="s">
+      <c r="BR15" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ15" s="142" t="s">
+      <c r="BS15" s="142" t="s">
         <v>716</v>
       </c>
-      <c r="BR15" s="43" t="s">
+      <c r="BT15" s="43" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="16" spans="1:70" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="23">
         <v>12</v>
       </c>
@@ -6136,40 +6242,42 @@
       <c r="BD16" s="40"/>
       <c r="BE16" s="40"/>
       <c r="BF16" s="40"/>
-      <c r="BG16" s="41" t="s">
+      <c r="BG16" s="40"/>
+      <c r="BH16" s="40"/>
+      <c r="BI16" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH16" s="42" t="s">
+      <c r="BJ16" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI16" s="38" t="s">
+      <c r="BK16" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BJ16" s="38" t="s">
+      <c r="BL16" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="BK16" s="92" t="s">
+      <c r="BM16" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL16" s="38"/>
-      <c r="BM16" s="3"/>
-      <c r="BN16" s="35" t="s">
+      <c r="BN16" s="38"/>
+      <c r="BO16" s="3"/>
+      <c r="BP16" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO16" s="35" t="s">
+      <c r="BQ16" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP16" s="37" t="s">
+      <c r="BR16" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ16" s="37" t="s">
+      <c r="BS16" s="37" t="s">
         <v>717</v>
       </c>
-      <c r="BR16" s="43" t="s">
+      <c r="BT16" s="43" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="17" spans="1:70" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="84">
         <v>13</v>
       </c>
@@ -6312,40 +6420,42 @@
       <c r="BD17" s="40"/>
       <c r="BE17" s="40"/>
       <c r="BF17" s="40"/>
-      <c r="BG17" s="41" t="s">
+      <c r="BG17" s="40"/>
+      <c r="BH17" s="40"/>
+      <c r="BI17" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH17" s="42" t="s">
+      <c r="BJ17" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI17" s="40" t="s">
+      <c r="BK17" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BJ17" s="38" t="s">
+      <c r="BL17" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="BK17" s="92" t="s">
+      <c r="BM17" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL17" s="38"/>
-      <c r="BM17" s="3"/>
-      <c r="BN17" s="35" t="s">
+      <c r="BN17" s="38"/>
+      <c r="BO17" s="3"/>
+      <c r="BP17" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO17" s="35" t="s">
+      <c r="BQ17" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP17" s="37" t="s">
+      <c r="BR17" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ17" s="37" t="s">
+      <c r="BS17" s="37" t="s">
         <v>718</v>
       </c>
-      <c r="BR17" s="43" t="s">
+      <c r="BT17" s="43" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>1</v>
       </c>
@@ -6488,40 +6598,42 @@
       <c r="BD18" s="15"/>
       <c r="BE18" s="15"/>
       <c r="BF18" s="15"/>
-      <c r="BG18" s="10" t="s">
+      <c r="BG18" s="15"/>
+      <c r="BH18" s="15"/>
+      <c r="BI18" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH18" s="17" t="s">
+      <c r="BJ18" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI18" s="22" t="s">
+      <c r="BK18" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BJ18" s="22" t="s">
+      <c r="BL18" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BK18" s="22"/>
-      <c r="BL18" s="22"/>
-      <c r="BM18" s="2" t="s">
+      <c r="BM18" s="22"/>
+      <c r="BN18" s="22"/>
+      <c r="BO18" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="BN18" s="14" t="s">
+      <c r="BP18" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO18" s="14" t="s">
+      <c r="BQ18" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP18" s="18" t="s">
+      <c r="BR18" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ18" s="18" t="s">
+      <c r="BS18" s="18" t="s">
         <v>718</v>
       </c>
-      <c r="BR18" s="21" t="s">
+      <c r="BT18" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>2</v>
       </c>
@@ -6660,38 +6772,40 @@
       <c r="BD19" s="15"/>
       <c r="BE19" s="15"/>
       <c r="BF19" s="15"/>
-      <c r="BG19" s="10" t="s">
+      <c r="BG19" s="15"/>
+      <c r="BH19" s="15"/>
+      <c r="BI19" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH19" s="17" t="s">
+      <c r="BJ19" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI19" s="54" t="s">
+      <c r="BK19" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="BJ19" s="54" t="s">
+      <c r="BL19" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="BK19" s="22"/>
-      <c r="BL19" s="22"/>
-      <c r="BM19" s="2"/>
-      <c r="BN19" s="14" t="s">
+      <c r="BM19" s="22"/>
+      <c r="BN19" s="22"/>
+      <c r="BO19" s="2"/>
+      <c r="BP19" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO19" s="14" t="s">
+      <c r="BQ19" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="BP19" s="18" t="s">
+      <c r="BR19" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ19" s="18" t="s">
+      <c r="BS19" s="18" t="s">
         <v>718</v>
       </c>
-      <c r="BR19" s="21" t="s">
+      <c r="BT19" s="21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="80">
         <v>3</v>
       </c>
@@ -6834,40 +6948,42 @@
       <c r="BD20" s="15"/>
       <c r="BE20" s="15"/>
       <c r="BF20" s="15"/>
-      <c r="BG20" s="10" t="s">
+      <c r="BG20" s="15"/>
+      <c r="BH20" s="15"/>
+      <c r="BI20" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH20" s="17" t="s">
+      <c r="BJ20" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI20" s="22" t="s">
+      <c r="BK20" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BJ20" s="22" t="s">
+      <c r="BL20" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BK20" s="92" t="s">
+      <c r="BM20" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL20" s="22"/>
-      <c r="BM20" s="2"/>
-      <c r="BN20" s="14" t="s">
+      <c r="BN20" s="22"/>
+      <c r="BO20" s="2"/>
+      <c r="BP20" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO20" s="14" t="s">
+      <c r="BQ20" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP20" s="18" t="s">
+      <c r="BR20" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ20" s="141" t="s">
+      <c r="BS20" s="141" t="s">
         <v>693</v>
       </c>
-      <c r="BR20" s="21" t="s">
+      <c r="BT20" s="21" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="80">
         <v>3</v>
       </c>
@@ -7011,40 +7127,42 @@
       <c r="BD21" s="15"/>
       <c r="BE21" s="15"/>
       <c r="BF21" s="15"/>
-      <c r="BG21" s="10" t="s">
+      <c r="BG21" s="15"/>
+      <c r="BH21" s="15"/>
+      <c r="BI21" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH21" s="17" t="s">
+      <c r="BJ21" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI21" s="22" t="s">
+      <c r="BK21" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BJ21" s="22" t="s">
+      <c r="BL21" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BK21" s="92" t="s">
+      <c r="BM21" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL21" s="22"/>
-      <c r="BM21" s="2"/>
-      <c r="BN21" s="14" t="s">
+      <c r="BN21" s="22"/>
+      <c r="BO21" s="2"/>
+      <c r="BP21" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO21" s="14" t="s">
+      <c r="BQ21" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP21" s="18" t="s">
+      <c r="BR21" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ21" s="18" t="s">
+      <c r="BS21" s="18" t="s">
         <v>719</v>
       </c>
-      <c r="BR21" s="21" t="s">
+      <c r="BT21" s="21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="22" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
         <v>4</v>
       </c>
@@ -7188,40 +7306,42 @@
       <c r="BD22" s="15"/>
       <c r="BE22" s="15"/>
       <c r="BF22" s="15"/>
-      <c r="BG22" s="10" t="s">
+      <c r="BG22" s="15"/>
+      <c r="BH22" s="15"/>
+      <c r="BI22" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH22" s="17" t="s">
+      <c r="BJ22" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI22" s="22" t="s">
+      <c r="BK22" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BJ22" s="22" t="s">
+      <c r="BL22" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BK22" s="92" t="s">
+      <c r="BM22" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL22" s="22"/>
-      <c r="BM22" s="2"/>
-      <c r="BN22" s="14" t="s">
+      <c r="BN22" s="22"/>
+      <c r="BO22" s="2"/>
+      <c r="BP22" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO22" s="14" t="s">
+      <c r="BQ22" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP22" s="18" t="s">
+      <c r="BR22" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ22" s="18" t="s">
+      <c r="BS22" s="18" t="s">
         <v>720</v>
       </c>
-      <c r="BR22" s="21" t="s">
+      <c r="BT22" s="21" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>5</v>
       </c>
@@ -7365,40 +7485,42 @@
       <c r="BD23" s="15"/>
       <c r="BE23" s="15"/>
       <c r="BF23" s="15"/>
-      <c r="BG23" s="10" t="s">
+      <c r="BG23" s="15"/>
+      <c r="BH23" s="15"/>
+      <c r="BI23" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH23" s="17" t="s">
+      <c r="BJ23" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI23" s="22" t="s">
+      <c r="BK23" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BJ23" s="22" t="s">
+      <c r="BL23" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BK23" s="92" t="s">
+      <c r="BM23" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL23" s="22"/>
-      <c r="BM23" s="2"/>
-      <c r="BN23" s="14" t="s">
+      <c r="BN23" s="22"/>
+      <c r="BO23" s="2"/>
+      <c r="BP23" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO23" s="14" t="s">
+      <c r="BQ23" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP23" s="18" t="s">
+      <c r="BR23" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="BQ23" s="141" t="s">
+      <c r="BS23" s="141" t="s">
         <v>721</v>
       </c>
-      <c r="BR23" s="21" t="s">
+      <c r="BT23" s="21" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>6</v>
       </c>
@@ -7542,38 +7664,40 @@
       <c r="BD24" s="15"/>
       <c r="BE24" s="15"/>
       <c r="BF24" s="15"/>
-      <c r="BG24" s="10" t="s">
+      <c r="BG24" s="15"/>
+      <c r="BH24" s="15"/>
+      <c r="BI24" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH24" s="17" t="s">
+      <c r="BJ24" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI24" s="15" t="s">
+      <c r="BK24" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ24" s="22" t="s">
+      <c r="BL24" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="BK24" s="22"/>
-      <c r="BL24" s="22"/>
-      <c r="BM24" s="2"/>
-      <c r="BN24" s="14" t="s">
+      <c r="BM24" s="22"/>
+      <c r="BN24" s="22"/>
+      <c r="BO24" s="2"/>
+      <c r="BP24" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="BO24" s="14" t="s">
+      <c r="BQ24" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP24" s="18" t="s">
+      <c r="BR24" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="BQ24" s="140" t="s">
+      <c r="BS24" s="140" t="s">
         <v>719</v>
       </c>
-      <c r="BR24" s="50" t="s">
+      <c r="BT24" s="50" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="25" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>7</v>
       </c>
@@ -7714,40 +7838,42 @@
       <c r="BD25" s="15"/>
       <c r="BE25" s="15"/>
       <c r="BF25" s="15"/>
-      <c r="BG25" s="10" t="s">
+      <c r="BG25" s="15"/>
+      <c r="BH25" s="15"/>
+      <c r="BI25" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH25" s="17" t="s">
+      <c r="BJ25" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI25" s="54" t="s">
+      <c r="BK25" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="BJ25" s="54" t="s">
+      <c r="BL25" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="BK25" s="92" t="s">
+      <c r="BM25" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL25" s="22"/>
-      <c r="BM25" s="2"/>
-      <c r="BN25" s="14" t="s">
+      <c r="BN25" s="22"/>
+      <c r="BO25" s="2"/>
+      <c r="BP25" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO25" s="14" t="s">
+      <c r="BQ25" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP25" s="18" t="s">
+      <c r="BR25" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="BQ25" s="141" t="s">
+      <c r="BS25" s="141" t="s">
         <v>736</v>
       </c>
-      <c r="BR25" s="21" t="s">
+      <c r="BT25" s="21" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="26" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>8</v>
       </c>
@@ -7892,40 +8018,42 @@
       <c r="BD26" s="15"/>
       <c r="BE26" s="15"/>
       <c r="BF26" s="15"/>
-      <c r="BG26" s="10" t="s">
+      <c r="BG26" s="15"/>
+      <c r="BH26" s="15"/>
+      <c r="BI26" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH26" s="17" t="s">
+      <c r="BJ26" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI26" s="22" t="s">
+      <c r="BK26" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BJ26" s="22" t="s">
+      <c r="BL26" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BK26" s="92" t="s">
+      <c r="BM26" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL26" s="22"/>
-      <c r="BM26" s="2"/>
-      <c r="BN26" s="14" t="s">
+      <c r="BN26" s="22"/>
+      <c r="BO26" s="2"/>
+      <c r="BP26" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO26" s="14" t="s">
+      <c r="BQ26" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP26" s="18" t="s">
+      <c r="BR26" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="BQ26" s="18" t="s">
+      <c r="BS26" s="18" t="s">
         <v>720</v>
       </c>
-      <c r="BR26" s="21" t="s">
+      <c r="BT26" s="21" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="27" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
         <v>9</v>
       </c>
@@ -8068,38 +8196,40 @@
       <c r="BD27" s="15"/>
       <c r="BE27" s="15"/>
       <c r="BF27" s="15"/>
-      <c r="BG27" s="10" t="s">
+      <c r="BG27" s="15"/>
+      <c r="BH27" s="15"/>
+      <c r="BI27" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH27" s="17" t="s">
+      <c r="BJ27" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI27" s="15" t="s">
+      <c r="BK27" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ27" s="22" t="s">
+      <c r="BL27" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="BK27" s="22"/>
-      <c r="BL27" s="22"/>
-      <c r="BM27" s="2"/>
-      <c r="BN27" s="14" t="s">
+      <c r="BM27" s="22"/>
+      <c r="BN27" s="22"/>
+      <c r="BO27" s="2"/>
+      <c r="BP27" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="BO27" s="14" t="s">
+      <c r="BQ27" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP27" s="18" t="s">
+      <c r="BR27" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="BQ27" s="140" t="s">
+      <c r="BS27" s="140" t="s">
         <v>719</v>
       </c>
-      <c r="BR27" s="50" t="s">
+      <c r="BT27" s="50" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="28" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9">
         <v>10</v>
       </c>
@@ -8243,40 +8373,42 @@
       <c r="BD28" s="15"/>
       <c r="BE28" s="15"/>
       <c r="BF28" s="15"/>
-      <c r="BG28" s="10" t="s">
+      <c r="BG28" s="15"/>
+      <c r="BH28" s="15"/>
+      <c r="BI28" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH28" s="49" t="s">
+      <c r="BJ28" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="BI28" s="15" t="s">
+      <c r="BK28" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BJ28" s="22" t="s">
+      <c r="BL28" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BK28" s="92" t="s">
+      <c r="BM28" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL28" s="22"/>
-      <c r="BM28" s="2"/>
-      <c r="BN28" s="14" t="s">
+      <c r="BN28" s="22"/>
+      <c r="BO28" s="2"/>
+      <c r="BP28" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO28" s="14" t="s">
+      <c r="BQ28" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP28" s="18" t="s">
+      <c r="BR28" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ28" s="18" t="s">
+      <c r="BS28" s="18" t="s">
         <v>713</v>
       </c>
-      <c r="BR28" s="21" t="s">
+      <c r="BT28" s="21" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="29" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>11</v>
       </c>
@@ -8407,36 +8539,38 @@
       <c r="BD29" s="15"/>
       <c r="BE29" s="15"/>
       <c r="BF29" s="15"/>
-      <c r="BG29" s="10" t="s">
+      <c r="BG29" s="15"/>
+      <c r="BH29" s="15"/>
+      <c r="BI29" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH29" s="49" t="s">
+      <c r="BJ29" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="BI29" s="22" t="s">
+      <c r="BK29" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="BJ29" s="22" t="s">
+      <c r="BL29" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="BK29" s="22"/>
-      <c r="BL29" s="22"/>
-      <c r="BM29" s="2"/>
-      <c r="BN29" s="14" t="s">
+      <c r="BM29" s="22"/>
+      <c r="BN29" s="22"/>
+      <c r="BO29" s="2"/>
+      <c r="BP29" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO29" s="14" t="s">
+      <c r="BQ29" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP29" s="18" t="s">
+      <c r="BR29" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ29" s="18"/>
-      <c r="BR29" s="21" t="s">
+      <c r="BS29" s="18"/>
+      <c r="BT29" s="21" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="30" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>12</v>
       </c>
@@ -8580,40 +8714,42 @@
       <c r="BD30" s="15"/>
       <c r="BE30" s="15"/>
       <c r="BF30" s="15"/>
-      <c r="BG30" s="10" t="s">
+      <c r="BG30" s="15"/>
+      <c r="BH30" s="15"/>
+      <c r="BI30" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH30" s="17" t="s">
+      <c r="BJ30" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="BI30" s="15" t="s">
+      <c r="BK30" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ30" s="15" t="s">
+      <c r="BL30" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="BK30" s="92" t="s">
+      <c r="BM30" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL30" s="22"/>
-      <c r="BM30" s="2"/>
-      <c r="BN30" s="14" t="s">
+      <c r="BN30" s="22"/>
+      <c r="BO30" s="2"/>
+      <c r="BP30" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO30" s="14" t="s">
+      <c r="BQ30" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP30" s="18" t="s">
+      <c r="BR30" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ30" s="18" t="s">
+      <c r="BS30" s="18" t="s">
         <v>713</v>
       </c>
-      <c r="BR30" s="21" t="s">
+      <c r="BT30" s="21" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:70" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="9">
         <v>13</v>
       </c>
@@ -8756,40 +8892,42 @@
       <c r="BD31" s="15"/>
       <c r="BE31" s="15"/>
       <c r="BF31" s="15"/>
-      <c r="BG31" s="10" t="s">
+      <c r="BG31" s="15"/>
+      <c r="BH31" s="15"/>
+      <c r="BI31" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH31" s="17" t="s">
+      <c r="BJ31" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="BI31" s="22" t="s">
+      <c r="BK31" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="BJ31" s="22" t="s">
+      <c r="BL31" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="BK31" s="92" t="s">
+      <c r="BM31" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL31" s="22"/>
-      <c r="BM31" s="2"/>
-      <c r="BN31" s="14" t="s">
+      <c r="BN31" s="22"/>
+      <c r="BO31" s="2"/>
+      <c r="BP31" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO31" s="14" t="s">
+      <c r="BQ31" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP31" s="18" t="s">
+      <c r="BR31" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ31" s="18" t="s">
+      <c r="BS31" s="18" t="s">
         <v>694</v>
       </c>
-      <c r="BR31" s="21" t="s">
+      <c r="BT31" s="21" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="32" spans="1:70" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="82">
         <v>14</v>
       </c>
@@ -8937,38 +9075,40 @@
       <c r="BD32" s="15"/>
       <c r="BE32" s="15"/>
       <c r="BF32" s="15"/>
-      <c r="BG32" s="10" t="s">
+      <c r="BG32" s="15"/>
+      <c r="BH32" s="15"/>
+      <c r="BI32" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH32" s="17" t="s">
+      <c r="BJ32" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="BI32" s="15" t="s">
+      <c r="BK32" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ32" s="22" t="s">
+      <c r="BL32" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="BK32" s="92" t="s">
+      <c r="BM32" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL32" s="22"/>
-      <c r="BM32" s="2"/>
-      <c r="BN32" s="14" t="s">
+      <c r="BN32" s="22"/>
+      <c r="BO32" s="2"/>
+      <c r="BP32" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO32" s="14" t="s">
+      <c r="BQ32" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP32" s="18" t="s">
+      <c r="BR32" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="BQ32" s="18"/>
-      <c r="BR32" s="21" t="s">
+      <c r="BS32" s="18"/>
+      <c r="BT32" s="21" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="33" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
         <v>247</v>
       </c>
@@ -9030,20 +9170,22 @@
       <c r="BD33" s="40"/>
       <c r="BE33" s="40"/>
       <c r="BF33" s="40"/>
-      <c r="BG33" s="41"/>
-      <c r="BH33" s="42"/>
-      <c r="BI33" s="40"/>
-      <c r="BJ33" s="38"/>
-      <c r="BK33" s="38"/>
+      <c r="BG33" s="40"/>
+      <c r="BH33" s="40"/>
+      <c r="BI33" s="41"/>
+      <c r="BJ33" s="42"/>
+      <c r="BK33" s="40"/>
       <c r="BL33" s="38"/>
-      <c r="BM33" s="3"/>
-      <c r="BN33" s="35"/>
-      <c r="BO33" s="35"/>
-      <c r="BP33" s="37"/>
-      <c r="BQ33" s="37"/>
-      <c r="BR33" s="43"/>
+      <c r="BM33" s="38"/>
+      <c r="BN33" s="38"/>
+      <c r="BO33" s="3"/>
+      <c r="BP33" s="35"/>
+      <c r="BQ33" s="35"/>
+      <c r="BR33" s="37"/>
+      <c r="BS33" s="37"/>
+      <c r="BT33" s="43"/>
     </row>
-    <row r="34" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B34" s="47" t="s">
         <v>248</v>
       </c>
@@ -9105,20 +9247,22 @@
       <c r="BD34" s="40"/>
       <c r="BE34" s="40"/>
       <c r="BF34" s="40"/>
-      <c r="BG34" s="41"/>
-      <c r="BH34" s="42"/>
-      <c r="BI34" s="40"/>
-      <c r="BJ34" s="38"/>
-      <c r="BK34" s="38"/>
+      <c r="BG34" s="40"/>
+      <c r="BH34" s="40"/>
+      <c r="BI34" s="41"/>
+      <c r="BJ34" s="42"/>
+      <c r="BK34" s="40"/>
       <c r="BL34" s="38"/>
-      <c r="BM34" s="3"/>
-      <c r="BN34" s="35"/>
-      <c r="BO34" s="35"/>
-      <c r="BP34" s="37"/>
-      <c r="BQ34" s="37"/>
-      <c r="BR34" s="43"/>
+      <c r="BM34" s="38"/>
+      <c r="BN34" s="38"/>
+      <c r="BO34" s="3"/>
+      <c r="BP34" s="35"/>
+      <c r="BQ34" s="35"/>
+      <c r="BR34" s="37"/>
+      <c r="BS34" s="37"/>
+      <c r="BT34" s="43"/>
     </row>
-    <row r="35" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="23">
         <v>1</v>
       </c>
@@ -9262,40 +9406,42 @@
       <c r="BD35" s="40"/>
       <c r="BE35" s="40"/>
       <c r="BF35" s="40"/>
-      <c r="BG35" s="41" t="s">
+      <c r="BG35" s="40"/>
+      <c r="BH35" s="40"/>
+      <c r="BI35" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH35" s="42" t="s">
+      <c r="BJ35" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="BI35" s="38" t="s">
+      <c r="BK35" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BJ35" s="38" t="s">
+      <c r="BL35" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="BK35" s="92" t="s">
+      <c r="BM35" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL35" s="38"/>
-      <c r="BM35" s="3"/>
-      <c r="BN35" s="35" t="s">
+      <c r="BN35" s="38"/>
+      <c r="BO35" s="3"/>
+      <c r="BP35" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO35" s="35" t="s">
+      <c r="BQ35" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP35" s="37" t="s">
+      <c r="BR35" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="BQ35" s="37" t="s">
+      <c r="BS35" s="37" t="s">
         <v>722</v>
       </c>
-      <c r="BR35" s="43" t="s">
+      <c r="BT35" s="43" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="36" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="23">
         <v>2</v>
       </c>
@@ -9438,42 +9584,44 @@
       <c r="BD36" s="40"/>
       <c r="BE36" s="40"/>
       <c r="BF36" s="40"/>
-      <c r="BG36" s="41" t="s">
+      <c r="BG36" s="40"/>
+      <c r="BH36" s="40"/>
+      <c r="BI36" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH36" s="42" t="s">
+      <c r="BJ36" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="BI36" s="38" t="s">
+      <c r="BK36" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BJ36" s="38" t="s">
+      <c r="BL36" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="BK36" s="92" t="s">
+      <c r="BM36" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL36" s="38"/>
-      <c r="BM36" s="3" t="s">
+      <c r="BN36" s="38"/>
+      <c r="BO36" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="BN36" s="35" t="s">
+      <c r="BP36" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO36" s="35" t="s">
+      <c r="BQ36" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP36" s="37" t="s">
+      <c r="BR36" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ36" s="37" t="s">
+      <c r="BS36" s="37" t="s">
         <v>694</v>
       </c>
-      <c r="BR36" s="43" t="s">
+      <c r="BT36" s="43" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="37" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="23">
         <v>3</v>
       </c>
@@ -9604,42 +9752,44 @@
       <c r="BD37" s="40"/>
       <c r="BE37" s="40"/>
       <c r="BF37" s="40"/>
-      <c r="BG37" s="41" t="s">
+      <c r="BG37" s="40"/>
+      <c r="BH37" s="40"/>
+      <c r="BI37" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH37" s="42" t="s">
+      <c r="BJ37" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="BI37" s="46" t="s">
+      <c r="BK37" s="46" t="s">
         <v>246</v>
       </c>
-      <c r="BJ37" s="38" t="s">
+      <c r="BL37" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="BK37" s="92" t="s">
+      <c r="BM37" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL37" s="38"/>
-      <c r="BM37" s="3" t="s">
+      <c r="BN37" s="38"/>
+      <c r="BO37" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="BN37" s="35" t="s">
+      <c r="BP37" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="BO37" s="35" t="s">
+      <c r="BQ37" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP37" s="37" t="s">
+      <c r="BR37" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ37" s="37" t="s">
+      <c r="BS37" s="37" t="s">
         <v>697</v>
       </c>
-      <c r="BR37" s="43" t="s">
+      <c r="BT37" s="43" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="38" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="23">
         <v>4</v>
       </c>
@@ -9787,36 +9937,38 @@
       <c r="BD38" s="40"/>
       <c r="BE38" s="40"/>
       <c r="BF38" s="40"/>
-      <c r="BG38" s="41" t="s">
+      <c r="BG38" s="40"/>
+      <c r="BH38" s="40"/>
+      <c r="BI38" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BH38" s="42" t="s">
+      <c r="BJ38" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="BI38" s="40" t="s">
+      <c r="BK38" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BJ38" s="40" t="s">
+      <c r="BL38" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="BK38" s="38"/>
-      <c r="BL38" s="38"/>
-      <c r="BM38" s="3"/>
-      <c r="BN38" s="35" t="s">
+      <c r="BM38" s="38"/>
+      <c r="BN38" s="38"/>
+      <c r="BO38" s="3"/>
+      <c r="BP38" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="BO38" s="35" t="s">
+      <c r="BQ38" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP38" s="37" t="s">
+      <c r="BR38" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="BQ38" s="37"/>
-      <c r="BR38" s="43" t="s">
+      <c r="BS38" s="37"/>
+      <c r="BT38" s="43" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="39" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="23">
         <v>5</v>
       </c>
@@ -9964,36 +10116,38 @@
       <c r="BD39" s="40"/>
       <c r="BE39" s="40"/>
       <c r="BF39" s="40"/>
-      <c r="BG39" s="41" t="s">
+      <c r="BG39" s="40"/>
+      <c r="BH39" s="40"/>
+      <c r="BI39" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BH39" s="42" t="s">
+      <c r="BJ39" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="BI39" s="40" t="s">
+      <c r="BK39" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BJ39" s="40" t="s">
+      <c r="BL39" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="BK39" s="38"/>
-      <c r="BL39" s="38"/>
-      <c r="BM39" s="3"/>
-      <c r="BN39" s="35" t="s">
+      <c r="BM39" s="38"/>
+      <c r="BN39" s="38"/>
+      <c r="BO39" s="3"/>
+      <c r="BP39" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="BO39" s="35" t="s">
+      <c r="BQ39" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP39" s="37" t="s">
+      <c r="BR39" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="BQ39" s="37"/>
-      <c r="BR39" s="43" t="s">
+      <c r="BS39" s="37"/>
+      <c r="BT39" s="43" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="40" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="23">
         <v>6</v>
       </c>
@@ -10141,38 +10295,40 @@
       <c r="BD40" s="40"/>
       <c r="BE40" s="40"/>
       <c r="BF40" s="40"/>
-      <c r="BG40" s="41" t="s">
+      <c r="BG40" s="40"/>
+      <c r="BH40" s="40"/>
+      <c r="BI40" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BH40" s="42" t="s">
+      <c r="BJ40" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="BI40" s="40" t="s">
+      <c r="BK40" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BJ40" s="40" t="s">
+      <c r="BL40" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="BK40" s="38"/>
-      <c r="BL40" s="38"/>
-      <c r="BM40" s="3"/>
-      <c r="BN40" s="35" t="s">
+      <c r="BM40" s="38"/>
+      <c r="BN40" s="38"/>
+      <c r="BO40" s="3"/>
+      <c r="BP40" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="BO40" s="35" t="s">
+      <c r="BQ40" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP40" s="37" t="s">
+      <c r="BR40" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="BQ40" s="37" t="s">
+      <c r="BS40" s="37" t="s">
         <v>723</v>
       </c>
-      <c r="BR40" s="43" t="s">
+      <c r="BT40" s="43" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="41" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="23">
         <v>7</v>
       </c>
@@ -10323,42 +10479,44 @@
       <c r="BD41" s="40"/>
       <c r="BE41" s="40"/>
       <c r="BF41" s="40"/>
-      <c r="BG41" s="41" t="s">
+      <c r="BG41" s="40"/>
+      <c r="BH41" s="40"/>
+      <c r="BI41" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH41" s="42" t="s">
+      <c r="BJ41" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="BI41" s="46" t="s">
+      <c r="BK41" s="46" t="s">
         <v>246</v>
       </c>
-      <c r="BJ41" s="38" t="s">
+      <c r="BL41" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="BK41" s="92" t="s">
+      <c r="BM41" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL41" s="38"/>
-      <c r="BM41" s="3" t="s">
+      <c r="BN41" s="38"/>
+      <c r="BO41" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="BN41" s="35" t="s">
+      <c r="BP41" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO41" s="35" t="s">
+      <c r="BQ41" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP41" s="37" t="s">
+      <c r="BR41" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ41" s="37" t="s">
+      <c r="BS41" s="37" t="s">
         <v>724</v>
       </c>
-      <c r="BR41" s="43" t="s">
+      <c r="BT41" s="43" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="42" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="23">
         <v>8</v>
       </c>
@@ -10501,40 +10659,42 @@
       <c r="BD42" s="40"/>
       <c r="BE42" s="40"/>
       <c r="BF42" s="40"/>
-      <c r="BG42" s="41" t="s">
+      <c r="BG42" s="40"/>
+      <c r="BH42" s="40"/>
+      <c r="BI42" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="BH42" s="42" t="s">
+      <c r="BJ42" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="BI42" s="58" t="s">
+      <c r="BK42" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="BJ42" s="58" t="s">
+      <c r="BL42" s="58" t="s">
         <v>285</v>
       </c>
-      <c r="BK42" s="92" t="s">
+      <c r="BM42" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL42" s="38"/>
-      <c r="BM42" s="3"/>
-      <c r="BN42" s="35" t="s">
+      <c r="BN42" s="38"/>
+      <c r="BO42" s="3"/>
+      <c r="BP42" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO42" s="35" t="s">
+      <c r="BQ42" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP42" s="37" t="s">
+      <c r="BR42" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ42" s="142" t="s">
+      <c r="BS42" s="142" t="s">
         <v>725</v>
       </c>
-      <c r="BR42" s="43" t="s">
+      <c r="BT42" s="43" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="43" spans="1:70" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="23">
         <v>9</v>
       </c>
@@ -10677,38 +10837,40 @@
       <c r="BD43" s="40"/>
       <c r="BE43" s="40"/>
       <c r="BF43" s="40"/>
-      <c r="BG43" s="41" t="s">
+      <c r="BG43" s="40"/>
+      <c r="BH43" s="40"/>
+      <c r="BI43" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BH43" s="42" t="s">
+      <c r="BJ43" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="BI43" s="40" t="s">
+      <c r="BK43" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BJ43" s="40" t="s">
+      <c r="BL43" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="BK43" s="38"/>
-      <c r="BL43" s="38"/>
-      <c r="BM43" s="3"/>
-      <c r="BN43" s="35" t="s">
+      <c r="BM43" s="38"/>
+      <c r="BN43" s="38"/>
+      <c r="BO43" s="3"/>
+      <c r="BP43" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO43" s="35" t="s">
+      <c r="BQ43" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP43" s="37" t="s">
+      <c r="BR43" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="BQ43" s="37" t="s">
+      <c r="BS43" s="37" t="s">
         <v>694</v>
       </c>
-      <c r="BR43" s="43" t="s">
+      <c r="BT43" s="43" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="44" spans="1:70" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="84">
         <v>10</v>
       </c>
@@ -10855,38 +11017,40 @@
       <c r="BD44" s="40"/>
       <c r="BE44" s="40"/>
       <c r="BF44" s="40"/>
-      <c r="BG44" s="41" t="s">
+      <c r="BG44" s="40"/>
+      <c r="BH44" s="40"/>
+      <c r="BI44" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BH44" s="42" t="s">
+      <c r="BJ44" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="BI44" s="40" t="s">
+      <c r="BK44" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BJ44" s="38" t="s">
+      <c r="BL44" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="BK44" s="38"/>
-      <c r="BL44" s="38"/>
-      <c r="BM44" s="3"/>
-      <c r="BN44" s="35" t="s">
+      <c r="BM44" s="38"/>
+      <c r="BN44" s="38"/>
+      <c r="BO44" s="3"/>
+      <c r="BP44" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO44" s="35" t="s">
+      <c r="BQ44" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP44" s="37" t="s">
+      <c r="BR44" s="37" t="s">
         <v>358</v>
       </c>
-      <c r="BQ44" s="37" t="s">
+      <c r="BS44" s="37" t="s">
         <v>694</v>
       </c>
-      <c r="BR44" s="43" t="s">
+      <c r="BT44" s="43" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="45" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9">
         <v>1</v>
       </c>
@@ -11029,40 +11193,42 @@
       <c r="BD45" s="86"/>
       <c r="BE45" s="86"/>
       <c r="BF45" s="86"/>
-      <c r="BG45" s="10" t="s">
+      <c r="BG45" s="86"/>
+      <c r="BH45" s="86"/>
+      <c r="BI45" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH45" s="17" t="s">
+      <c r="BJ45" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="BI45" s="15" t="s">
+      <c r="BK45" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="BJ45" s="15" t="s">
+      <c r="BL45" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="BK45" s="92" t="s">
+      <c r="BM45" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL45" s="22"/>
-      <c r="BM45" s="2"/>
-      <c r="BN45" s="14" t="s">
+      <c r="BN45" s="22"/>
+      <c r="BO45" s="2"/>
+      <c r="BP45" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO45" s="14" t="s">
+      <c r="BQ45" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP45" s="18" t="s">
+      <c r="BR45" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ45" s="18" t="s">
+      <c r="BS45" s="18" t="s">
         <v>694</v>
       </c>
-      <c r="BR45" s="21" t="s">
+      <c r="BT45" s="21" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="46" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9">
         <v>2</v>
       </c>
@@ -11203,43 +11369,45 @@
       <c r="BA46" s="79"/>
       <c r="BB46" s="79"/>
       <c r="BC46" s="79"/>
-      <c r="BD46" s="15"/>
-      <c r="BE46" s="15"/>
+      <c r="BD46" s="86"/>
+      <c r="BE46" s="86"/>
       <c r="BF46" s="15"/>
-      <c r="BG46" s="10" t="s">
+      <c r="BG46" s="15"/>
+      <c r="BH46" s="15"/>
+      <c r="BI46" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH46" s="17" t="s">
+      <c r="BJ46" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="BI46" s="54" t="s">
+      <c r="BK46" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="BJ46" s="22" t="s">
+      <c r="BL46" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="BK46" s="92" t="s">
+      <c r="BM46" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL46" s="22"/>
-      <c r="BM46" s="2"/>
-      <c r="BN46" s="14" t="s">
+      <c r="BN46" s="22"/>
+      <c r="BO46" s="2"/>
+      <c r="BP46" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO46" s="14" t="s">
+      <c r="BQ46" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP46" s="18" t="s">
+      <c r="BR46" s="18" t="s">
         <v>376</v>
       </c>
-      <c r="BQ46" s="18" t="s">
+      <c r="BS46" s="18" t="s">
         <v>698</v>
       </c>
-      <c r="BR46" s="21" t="s">
+      <c r="BT46" s="21" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="47" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9">
         <v>3</v>
       </c>
@@ -11379,43 +11547,45 @@
       <c r="BA47" s="79"/>
       <c r="BB47" s="79"/>
       <c r="BC47" s="79"/>
-      <c r="BD47" s="15"/>
-      <c r="BE47" s="15"/>
+      <c r="BD47" s="86"/>
+      <c r="BE47" s="86"/>
       <c r="BF47" s="15"/>
-      <c r="BG47" s="10" t="s">
+      <c r="BG47" s="15"/>
+      <c r="BH47" s="15"/>
+      <c r="BI47" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH47" s="17" t="s">
+      <c r="BJ47" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="BI47" s="15" t="s">
+      <c r="BK47" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ47" s="22" t="s">
+      <c r="BL47" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="BK47" s="92" t="s">
+      <c r="BM47" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL47" s="22"/>
-      <c r="BM47" s="2"/>
-      <c r="BN47" s="14" t="s">
+      <c r="BN47" s="22"/>
+      <c r="BO47" s="2"/>
+      <c r="BP47" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO47" s="14" t="s">
+      <c r="BQ47" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP47" s="18" t="s">
+      <c r="BR47" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ47" s="18" t="s">
+      <c r="BS47" s="18" t="s">
         <v>694</v>
       </c>
-      <c r="BR47" s="21" t="s">
+      <c r="BT47" s="21" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="48" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
         <v>4</v>
       </c>
@@ -11558,40 +11728,42 @@
       <c r="BD48" s="15"/>
       <c r="BE48" s="15"/>
       <c r="BF48" s="15"/>
-      <c r="BG48" s="10" t="s">
+      <c r="BG48" s="15"/>
+      <c r="BH48" s="15"/>
+      <c r="BI48" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH48" s="17" t="s">
+      <c r="BJ48" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="BI48" s="15" t="s">
+      <c r="BK48" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="BJ48" s="15" t="s">
+      <c r="BL48" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="BK48" s="92" t="s">
+      <c r="BM48" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL48" s="22"/>
-      <c r="BM48" s="2"/>
-      <c r="BN48" s="14" t="s">
+      <c r="BN48" s="22"/>
+      <c r="BO48" s="2"/>
+      <c r="BP48" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="BO48" s="14" t="s">
+      <c r="BQ48" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP48" s="18" t="s">
+      <c r="BR48" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ48" s="18" t="s">
+      <c r="BS48" s="18" t="s">
         <v>726</v>
       </c>
-      <c r="BR48" s="21" t="s">
+      <c r="BT48" s="21" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>5</v>
       </c>
@@ -11738,45 +11910,47 @@
       <c r="BA49" s="79"/>
       <c r="BB49" s="79"/>
       <c r="BC49" s="79"/>
-      <c r="BD49" s="15" t="s">
+      <c r="BD49" s="86"/>
+      <c r="BE49" s="86"/>
+      <c r="BF49" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="BE49" s="15" t="s">
+      <c r="BG49" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="BF49" s="15" t="s">
+      <c r="BH49" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="BG49" s="10" t="s">
+      <c r="BI49" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH49" s="17" t="s">
+      <c r="BJ49" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="BI49" s="15" t="s">
+      <c r="BK49" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BJ49" s="15" t="s">
+      <c r="BL49" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="BK49" s="22"/>
-      <c r="BL49" s="22"/>
-      <c r="BM49" s="2"/>
-      <c r="BN49" s="14" t="s">
+      <c r="BM49" s="22"/>
+      <c r="BN49" s="22"/>
+      <c r="BO49" s="2"/>
+      <c r="BP49" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="BO49" s="14" t="s">
+      <c r="BQ49" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP49" s="18" t="s">
+      <c r="BR49" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="BQ49" s="18"/>
-      <c r="BR49" s="21" t="s">
+      <c r="BS49" s="18"/>
+      <c r="BT49" s="21" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="50" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9">
         <v>6</v>
       </c>
@@ -11916,43 +12090,45 @@
       <c r="BA50" s="79"/>
       <c r="BB50" s="79"/>
       <c r="BC50" s="79"/>
-      <c r="BD50" s="15"/>
-      <c r="BE50" s="15"/>
+      <c r="BD50" s="86"/>
+      <c r="BE50" s="86"/>
       <c r="BF50" s="15"/>
-      <c r="BG50" s="10" t="s">
+      <c r="BG50" s="15"/>
+      <c r="BH50" s="15"/>
+      <c r="BI50" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH50" s="17" t="s">
+      <c r="BJ50" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="BI50" s="15" t="s">
+      <c r="BK50" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ50" s="22" t="s">
+      <c r="BL50" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="BK50" s="92" t="s">
+      <c r="BM50" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL50" s="22"/>
-      <c r="BM50" s="2"/>
-      <c r="BN50" s="14" t="s">
+      <c r="BN50" s="22"/>
+      <c r="BO50" s="2"/>
+      <c r="BP50" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO50" s="14" t="s">
+      <c r="BQ50" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP50" s="18" t="s">
+      <c r="BR50" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="BQ50" s="18" t="s">
+      <c r="BS50" s="18" t="s">
         <v>694</v>
       </c>
-      <c r="BR50" s="21" t="s">
+      <c r="BT50" s="21" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="51" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9">
         <v>7</v>
       </c>
@@ -12095,40 +12271,42 @@
       <c r="BD51" s="15"/>
       <c r="BE51" s="15"/>
       <c r="BF51" s="15"/>
-      <c r="BG51" s="10" t="s">
+      <c r="BG51" s="15"/>
+      <c r="BH51" s="15"/>
+      <c r="BI51" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH51" s="17" t="s">
+      <c r="BJ51" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="BI51" s="15" t="s">
+      <c r="BK51" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="BJ51" s="15" t="s">
+      <c r="BL51" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="BK51" s="92" t="s">
+      <c r="BM51" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL51" s="22"/>
-      <c r="BM51" s="2"/>
-      <c r="BN51" s="14" t="s">
+      <c r="BN51" s="22"/>
+      <c r="BO51" s="2"/>
+      <c r="BP51" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="BO51" s="14" t="s">
+      <c r="BQ51" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP51" s="18" t="s">
+      <c r="BR51" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="BQ51" s="18" t="s">
+      <c r="BS51" s="18" t="s">
         <v>726</v>
       </c>
-      <c r="BR51" s="21" t="s">
+      <c r="BT51" s="21" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="52" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9">
         <v>8</v>
       </c>
@@ -12275,45 +12453,47 @@
       <c r="BA52" s="15"/>
       <c r="BB52" s="15"/>
       <c r="BC52" s="15"/>
-      <c r="BD52" s="15" t="s">
+      <c r="BD52" s="15"/>
+      <c r="BE52" s="15"/>
+      <c r="BF52" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="BE52" s="15" t="s">
+      <c r="BG52" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="BF52" s="15" t="s">
+      <c r="BH52" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="BG52" s="10" t="s">
+      <c r="BI52" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH52" s="17" t="s">
+      <c r="BJ52" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="BI52" s="15" t="s">
+      <c r="BK52" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BJ52" s="15" t="s">
+      <c r="BL52" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="BK52" s="22"/>
-      <c r="BL52" s="22"/>
-      <c r="BM52" s="2"/>
-      <c r="BN52" s="14" t="s">
+      <c r="BM52" s="22"/>
+      <c r="BN52" s="22"/>
+      <c r="BO52" s="2"/>
+      <c r="BP52" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="BO52" s="14" t="s">
+      <c r="BQ52" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP52" s="18" t="s">
+      <c r="BR52" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="BQ52" s="18"/>
-      <c r="BR52" s="21" t="s">
+      <c r="BS52" s="18"/>
+      <c r="BT52" s="21" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="53" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
         <v>9</v>
       </c>
@@ -12459,47 +12639,49 @@
       <c r="BA53" s="15"/>
       <c r="BB53" s="15"/>
       <c r="BC53" s="15"/>
-      <c r="BD53" s="15" t="s">
+      <c r="BD53" s="15"/>
+      <c r="BE53" s="15"/>
+      <c r="BF53" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="BE53" s="15" t="s">
+      <c r="BG53" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="BF53" s="15" t="s">
+      <c r="BH53" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="BG53" s="10" t="s">
+      <c r="BI53" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH53" s="17" t="s">
+      <c r="BJ53" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="BI53" s="15" t="s">
+      <c r="BK53" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BJ53" s="15" t="s">
+      <c r="BL53" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="BK53" s="22"/>
-      <c r="BL53" s="22"/>
-      <c r="BM53" s="2"/>
-      <c r="BN53" s="14" t="s">
+      <c r="BM53" s="22"/>
+      <c r="BN53" s="22"/>
+      <c r="BO53" s="2"/>
+      <c r="BP53" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="BO53" s="14" t="s">
+      <c r="BQ53" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP53" s="18" t="s">
+      <c r="BR53" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="BQ53" s="18" t="s">
+      <c r="BS53" s="18" t="s">
         <v>735</v>
       </c>
-      <c r="BR53" s="21" t="s">
+      <c r="BT53" s="21" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="54" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9">
         <v>10</v>
       </c>
@@ -12639,45 +12821,47 @@
       <c r="BA54" s="79"/>
       <c r="BB54" s="79"/>
       <c r="BC54" s="79"/>
-      <c r="BD54" s="15"/>
-      <c r="BE54" s="15"/>
+      <c r="BD54" s="86"/>
+      <c r="BE54" s="86"/>
       <c r="BF54" s="15"/>
-      <c r="BG54" s="10" t="s">
+      <c r="BG54" s="15"/>
+      <c r="BH54" s="15"/>
+      <c r="BI54" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH54" s="17" t="s">
+      <c r="BJ54" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="BI54" s="15" t="s">
+      <c r="BK54" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ54" s="22" t="s">
+      <c r="BL54" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="BK54" s="92" t="s">
+      <c r="BM54" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL54" s="22"/>
-      <c r="BM54" s="2" t="s">
+      <c r="BN54" s="22"/>
+      <c r="BO54" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="BN54" s="14" t="s">
+      <c r="BP54" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO54" s="14" t="s">
+      <c r="BQ54" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP54" s="18" t="s">
+      <c r="BR54" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ54" s="18" t="s">
+      <c r="BS54" s="18" t="s">
         <v>694</v>
       </c>
-      <c r="BR54" s="21" t="s">
+      <c r="BT54" s="21" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="55" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9">
         <v>11</v>
       </c>
@@ -12820,42 +13004,44 @@
       <c r="BD55" s="15"/>
       <c r="BE55" s="15"/>
       <c r="BF55" s="15"/>
-      <c r="BG55" s="10" t="s">
+      <c r="BG55" s="15"/>
+      <c r="BH55" s="15"/>
+      <c r="BI55" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="BH55" s="17" t="s">
+      <c r="BJ55" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="BI55" s="15" t="s">
+      <c r="BK55" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="BJ55" s="15" t="s">
+      <c r="BL55" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="BK55" s="92" t="s">
+      <c r="BM55" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL55" s="22"/>
-      <c r="BM55" s="2" t="s">
+      <c r="BN55" s="22"/>
+      <c r="BO55" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="BN55" s="14" t="s">
+      <c r="BP55" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="BO55" s="14" t="s">
+      <c r="BQ55" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP55" s="18" t="s">
+      <c r="BR55" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ55" s="18" t="s">
+      <c r="BS55" s="18" t="s">
         <v>726</v>
       </c>
-      <c r="BR55" s="21" t="s">
+      <c r="BT55" s="21" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="56" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9">
         <v>12</v>
       </c>
@@ -13006,47 +13192,49 @@
       <c r="BA56" s="22"/>
       <c r="BB56" s="22"/>
       <c r="BC56" s="22"/>
-      <c r="BD56" s="15" t="s">
+      <c r="BD56" s="15"/>
+      <c r="BE56" s="15"/>
+      <c r="BF56" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="BE56" s="15" t="s">
+      <c r="BG56" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="BF56" s="15" t="s">
+      <c r="BH56" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="BG56" s="10" t="s">
+      <c r="BI56" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH56" s="17" t="s">
+      <c r="BJ56" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="BI56" s="15" t="s">
+      <c r="BK56" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BJ56" s="15" t="s">
+      <c r="BL56" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="BK56" s="22"/>
-      <c r="BL56" s="22"/>
-      <c r="BM56" s="2"/>
-      <c r="BN56" s="14" t="s">
+      <c r="BM56" s="22"/>
+      <c r="BN56" s="22"/>
+      <c r="BO56" s="2"/>
+      <c r="BP56" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="BO56" s="14" t="s">
+      <c r="BQ56" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP56" s="18" t="s">
+      <c r="BR56" s="18" t="s">
         <v>424</v>
       </c>
-      <c r="BQ56" s="18" t="s">
+      <c r="BS56" s="18" t="s">
         <v>710</v>
       </c>
-      <c r="BR56" s="21" t="s">
+      <c r="BT56" s="21" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="57" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9">
         <v>13</v>
       </c>
@@ -13190,40 +13378,42 @@
       <c r="BD57" s="15"/>
       <c r="BE57" s="15"/>
       <c r="BF57" s="15"/>
-      <c r="BG57" s="10" t="s">
+      <c r="BG57" s="15"/>
+      <c r="BH57" s="15"/>
+      <c r="BI57" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH57" s="17" t="s">
+      <c r="BJ57" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="BI57" s="22" t="s">
+      <c r="BK57" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="BJ57" s="22" t="s">
+      <c r="BL57" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="BK57" s="92" t="s">
+      <c r="BM57" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL57" s="22"/>
-      <c r="BM57" s="2"/>
-      <c r="BN57" s="14" t="s">
+      <c r="BN57" s="22"/>
+      <c r="BO57" s="2"/>
+      <c r="BP57" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO57" s="14" t="s">
+      <c r="BQ57" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP57" s="18" t="s">
+      <c r="BR57" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ57" s="18" t="s">
+      <c r="BS57" s="18" t="s">
         <v>694</v>
       </c>
-      <c r="BR57" s="21" t="s">
+      <c r="BT57" s="21" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="58" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9">
         <v>14</v>
       </c>
@@ -13366,40 +13556,42 @@
       <c r="BD58" s="22"/>
       <c r="BE58" s="22"/>
       <c r="BF58" s="22"/>
-      <c r="BG58" s="10" t="s">
+      <c r="BG58" s="22"/>
+      <c r="BH58" s="22"/>
+      <c r="BI58" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH58" s="17" t="s">
+      <c r="BJ58" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="BI58" s="15" t="s">
+      <c r="BK58" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ58" s="22" t="s">
+      <c r="BL58" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="BK58" s="92" t="s">
+      <c r="BM58" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL58" s="22"/>
-      <c r="BM58" s="2"/>
-      <c r="BN58" s="14" t="s">
+      <c r="BN58" s="22"/>
+      <c r="BO58" s="2"/>
+      <c r="BP58" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO58" s="14" t="s">
+      <c r="BQ58" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP58" s="18" t="s">
+      <c r="BR58" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="BQ58" s="18" t="s">
+      <c r="BS58" s="18" t="s">
         <v>727</v>
       </c>
-      <c r="BR58" s="21" t="s">
+      <c r="BT58" s="21" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="59" spans="1:70" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="80">
         <v>15</v>
       </c>
@@ -13545,49 +13737,51 @@
       <c r="BA59" s="22"/>
       <c r="BB59" s="22"/>
       <c r="BC59" s="22"/>
-      <c r="BD59" s="22" t="s">
+      <c r="BD59" s="22"/>
+      <c r="BE59" s="22"/>
+      <c r="BF59" s="22" t="s">
         <v>367</v>
       </c>
-      <c r="BE59" s="15" t="s">
+      <c r="BG59" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="BF59" s="22" t="s">
+      <c r="BH59" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="BG59" s="10" t="s">
+      <c r="BI59" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH59" s="17" t="s">
+      <c r="BJ59" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="BI59" s="15" t="s">
+      <c r="BK59" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BJ59" s="22" t="s">
+      <c r="BL59" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="BK59" s="92" t="s">
+      <c r="BM59" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL59" s="22"/>
-      <c r="BM59" s="2"/>
-      <c r="BN59" s="14" t="s">
+      <c r="BN59" s="22"/>
+      <c r="BO59" s="2"/>
+      <c r="BP59" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BO59" s="14" t="s">
+      <c r="BQ59" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BP59" s="18" t="s">
+      <c r="BR59" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="BQ59" s="18" t="s">
+      <c r="BS59" s="18" t="s">
         <v>694</v>
       </c>
-      <c r="BR59" s="21" t="s">
+      <c r="BT59" s="21" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="60" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="23">
         <v>1</v>
       </c>
@@ -13728,42 +13922,44 @@
       <c r="BB60" s="38"/>
       <c r="BC60" s="38"/>
       <c r="BD60" s="38"/>
-      <c r="BE60" s="40"/>
+      <c r="BE60" s="38"/>
       <c r="BF60" s="38"/>
-      <c r="BG60" s="41" t="s">
+      <c r="BG60" s="40"/>
+      <c r="BH60" s="38"/>
+      <c r="BI60" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BH60" s="42" t="s">
+      <c r="BJ60" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="BI60" s="40" t="s">
+      <c r="BK60" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BJ60" s="38" t="s">
+      <c r="BL60" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="BK60" s="131">
+      <c r="BM60" s="131">
         <v>200206</v>
       </c>
-      <c r="BL60" s="95"/>
-      <c r="BM60" s="3"/>
-      <c r="BN60" s="35" t="s">
+      <c r="BN60" s="95"/>
+      <c r="BO60" s="3"/>
+      <c r="BP60" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO60" s="35" t="s">
+      <c r="BQ60" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BP60" s="37" t="s">
+      <c r="BR60" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ60" s="37" t="s">
+      <c r="BS60" s="37" t="s">
         <v>694</v>
       </c>
-      <c r="BR60" s="43" t="s">
+      <c r="BT60" s="43" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="61" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="23">
         <v>2</v>
       </c>
@@ -13906,40 +14102,42 @@
       <c r="BD61" s="38"/>
       <c r="BE61" s="38"/>
       <c r="BF61" s="38"/>
-      <c r="BG61" s="41" t="s">
+      <c r="BG61" s="38"/>
+      <c r="BH61" s="38"/>
+      <c r="BI61" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BH61" s="42" t="s">
+      <c r="BJ61" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="BI61" s="40" t="s">
+      <c r="BK61" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BJ61" s="38" t="s">
+      <c r="BL61" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="BK61" s="95" t="s">
+      <c r="BM61" s="95" t="s">
         <v>502</v>
       </c>
-      <c r="BL61" s="95"/>
-      <c r="BM61" s="95"/>
-      <c r="BN61" s="35" t="s">
+      <c r="BN61" s="95"/>
+      <c r="BO61" s="95"/>
+      <c r="BP61" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="BO61" s="3" t="s">
+      <c r="BQ61" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="BP61" s="37" t="s">
+      <c r="BR61" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ61" s="37" t="s">
+      <c r="BS61" s="37" t="s">
         <v>694</v>
       </c>
-      <c r="BR61" s="43" t="s">
+      <c r="BT61" s="43" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="62" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="23">
         <v>3</v>
       </c>
@@ -14085,47 +14283,49 @@
       <c r="BA62" s="38"/>
       <c r="BB62" s="38"/>
       <c r="BC62" s="38"/>
-      <c r="BD62" s="38" t="s">
+      <c r="BD62" s="38"/>
+      <c r="BE62" s="38"/>
+      <c r="BF62" s="38" t="s">
         <v>367</v>
       </c>
-      <c r="BE62" s="40" t="s">
+      <c r="BG62" s="40" t="s">
         <v>368</v>
       </c>
-      <c r="BF62" s="38" t="s">
+      <c r="BH62" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="BG62" s="41" t="s">
+      <c r="BI62" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BH62" s="42" t="s">
+      <c r="BJ62" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="BI62" s="40" t="s">
+      <c r="BK62" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="BJ62" s="3" t="s">
+      <c r="BL62" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="BK62" s="38"/>
-      <c r="BL62" s="38"/>
-      <c r="BM62" s="3"/>
-      <c r="BN62" s="35" t="s">
+      <c r="BM62" s="38"/>
+      <c r="BN62" s="38"/>
+      <c r="BO62" s="3"/>
+      <c r="BP62" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="BO62" s="35" t="s">
+      <c r="BQ62" s="35" t="s">
         <v>446</v>
       </c>
-      <c r="BP62" s="37" t="s">
+      <c r="BR62" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="BQ62" s="37" t="s">
+      <c r="BS62" s="37" t="s">
         <v>728</v>
       </c>
-      <c r="BR62" s="43" t="s">
+      <c r="BT62" s="43" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="63" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="23">
         <v>4</v>
       </c>
@@ -14276,38 +14476,40 @@
       <c r="BD63" s="40"/>
       <c r="BE63" s="40"/>
       <c r="BF63" s="40"/>
-      <c r="BG63" s="41" t="s">
+      <c r="BG63" s="40"/>
+      <c r="BH63" s="40"/>
+      <c r="BI63" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BH63" s="42" t="s">
+      <c r="BJ63" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="BI63" s="96" t="s">
+      <c r="BK63" s="96" t="s">
         <v>246</v>
       </c>
-      <c r="BJ63" s="3" t="s">
+      <c r="BL63" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="BK63" s="131">
+      <c r="BM63" s="131">
         <v>200206</v>
       </c>
-      <c r="BL63" s="95"/>
-      <c r="BM63" s="95"/>
-      <c r="BN63" s="3" t="s">
+      <c r="BN63" s="95"/>
+      <c r="BO63" s="95"/>
+      <c r="BP63" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="BO63" s="3" t="s">
+      <c r="BQ63" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="BP63" s="37" t="s">
+      <c r="BR63" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ63" s="37"/>
-      <c r="BR63" s="43" t="s">
+      <c r="BS63" s="37"/>
+      <c r="BT63" s="43" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="64" spans="1:70" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="63">
         <v>5</v>
       </c>
@@ -14450,40 +14652,42 @@
       <c r="BD64" s="40"/>
       <c r="BE64" s="40"/>
       <c r="BF64" s="40"/>
-      <c r="BG64" s="41" t="s">
+      <c r="BG64" s="40"/>
+      <c r="BH64" s="40"/>
+      <c r="BI64" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BH64" s="42" t="s">
+      <c r="BJ64" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="BI64" s="96">
+      <c r="BK64" s="96">
         <v>162640</v>
       </c>
-      <c r="BJ64" s="3" t="s">
+      <c r="BL64" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="BK64" s="132">
+      <c r="BM64" s="132">
         <v>201189</v>
       </c>
-      <c r="BL64" s="3"/>
-      <c r="BM64" s="95"/>
-      <c r="BN64" s="3" t="s">
+      <c r="BN64" s="3"/>
+      <c r="BO64" s="95"/>
+      <c r="BP64" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="BO64" s="3" t="s">
+      <c r="BQ64" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="BP64" s="37" t="s">
+      <c r="BR64" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="BQ64" s="37" t="s">
+      <c r="BS64" s="37" t="s">
         <v>729</v>
       </c>
-      <c r="BR64" s="43" t="s">
+      <c r="BT64" s="43" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="65" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -14635,40 +14839,42 @@
       <c r="BD65" s="22"/>
       <c r="BE65" s="22"/>
       <c r="BF65" s="22"/>
-      <c r="BG65" s="20" t="s">
+      <c r="BG65" s="22"/>
+      <c r="BH65" s="22"/>
+      <c r="BI65" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="BH65" s="49" t="s">
+      <c r="BJ65" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="BI65" s="49">
+      <c r="BK65" s="49">
         <v>201383</v>
       </c>
-      <c r="BJ65" s="2" t="s">
+      <c r="BL65" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="BK65" s="131">
+      <c r="BM65" s="131">
         <v>200206</v>
       </c>
-      <c r="BL65" s="97"/>
-      <c r="BM65" s="97" t="s">
+      <c r="BN65" s="97"/>
+      <c r="BO65" s="97" t="s">
         <v>498</v>
       </c>
-      <c r="BN65" s="2" t="s">
+      <c r="BP65" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BO65" s="2" t="s">
+      <c r="BQ65" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="BP65" s="18" t="s">
+      <c r="BR65" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ65" s="18"/>
-      <c r="BR65" s="21" t="s">
+      <c r="BS65" s="18"/>
+      <c r="BT65" s="21" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="66" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9">
         <v>2</v>
       </c>
@@ -14812,42 +15018,44 @@
       <c r="BD66" s="22"/>
       <c r="BE66" s="22"/>
       <c r="BF66" s="22"/>
-      <c r="BG66" s="10" t="s">
+      <c r="BG66" s="22"/>
+      <c r="BH66" s="22"/>
+      <c r="BI66" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH66" s="17" t="s">
+      <c r="BJ66" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="BI66" s="49">
+      <c r="BK66" s="49">
         <v>162640</v>
       </c>
-      <c r="BJ66" s="2" t="s">
+      <c r="BL66" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="BK66" s="92" t="s">
+      <c r="BM66" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL66" s="22"/>
-      <c r="BM66" s="97" t="s">
+      <c r="BN66" s="22"/>
+      <c r="BO66" s="97" t="s">
         <v>473</v>
       </c>
-      <c r="BN66" s="2" t="s">
+      <c r="BP66" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BO66" s="2" t="s">
+      <c r="BQ66" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BP66" s="18" t="s">
+      <c r="BR66" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ66" s="18" t="s">
+      <c r="BS66" s="18" t="s">
         <v>730</v>
       </c>
-      <c r="BR66" s="21" t="s">
+      <c r="BT66" s="21" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="67" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9">
         <v>3</v>
       </c>
@@ -14993,40 +15201,42 @@
       <c r="BD67" s="22"/>
       <c r="BE67" s="22"/>
       <c r="BF67" s="22"/>
-      <c r="BG67" s="10" t="s">
+      <c r="BG67" s="22"/>
+      <c r="BH67" s="22"/>
+      <c r="BI67" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BH67" s="17" t="s">
+      <c r="BJ67" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="BI67" s="49" t="s">
+      <c r="BK67" s="49" t="s">
         <v>246</v>
       </c>
-      <c r="BJ67" s="2" t="s">
+      <c r="BL67" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="BK67" s="97" t="s">
+      <c r="BM67" s="97" t="s">
         <v>508</v>
       </c>
-      <c r="BL67" s="97"/>
-      <c r="BM67" s="97"/>
-      <c r="BN67" s="2" t="s">
+      <c r="BN67" s="97"/>
+      <c r="BO67" s="97"/>
+      <c r="BP67" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BO67" s="2" t="s">
+      <c r="BQ67" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BP67" s="18" t="s">
+      <c r="BR67" s="18" t="s">
         <v>503</v>
       </c>
-      <c r="BQ67" s="18" t="s">
+      <c r="BS67" s="18" t="s">
         <v>731</v>
       </c>
-      <c r="BR67" s="21" t="s">
+      <c r="BT67" s="21" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="68" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9">
         <v>4</v>
       </c>
@@ -15175,47 +15385,49 @@
       <c r="BA68" s="22"/>
       <c r="BB68" s="22"/>
       <c r="BC68" s="22"/>
-      <c r="BD68" s="22" t="s">
+      <c r="BD68" s="22"/>
+      <c r="BE68" s="22"/>
+      <c r="BF68" s="22" t="s">
         <v>367</v>
       </c>
-      <c r="BE68" s="22" t="s">
+      <c r="BG68" s="22" t="s">
         <v>368</v>
       </c>
-      <c r="BF68" s="22" t="s">
+      <c r="BH68" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="BG68" s="20" t="s">
+      <c r="BI68" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="BH68" s="49" t="s">
+      <c r="BJ68" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="BI68" s="49">
+      <c r="BK68" s="49">
         <v>162642</v>
       </c>
-      <c r="BJ68" s="2" t="s">
+      <c r="BL68" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="BK68" s="97"/>
-      <c r="BL68" s="97"/>
       <c r="BM68" s="97"/>
-      <c r="BN68" s="2" t="s">
+      <c r="BN68" s="97"/>
+      <c r="BO68" s="97"/>
+      <c r="BP68" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="BO68" s="2" t="s">
+      <c r="BQ68" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BP68" s="18" t="s">
+      <c r="BR68" s="18" t="s">
         <v>513</v>
       </c>
-      <c r="BQ68" s="18" t="s">
+      <c r="BS68" s="18" t="s">
         <v>732</v>
       </c>
-      <c r="BR68" s="21" t="s">
+      <c r="BT68" s="21" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="69" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9">
         <v>5</v>
       </c>
@@ -15359,40 +15571,42 @@
       <c r="BD69" s="22"/>
       <c r="BE69" s="22"/>
       <c r="BF69" s="22"/>
-      <c r="BG69" s="20" t="s">
+      <c r="BG69" s="22"/>
+      <c r="BH69" s="22"/>
+      <c r="BI69" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="BH69" s="49" t="s">
+      <c r="BJ69" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="BI69" s="15" t="s">
+      <c r="BK69" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BJ69" s="15" t="s">
+      <c r="BL69" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="BK69" s="92" t="s">
+      <c r="BM69" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL69" s="22"/>
-      <c r="BM69" s="97" t="s">
+      <c r="BN69" s="22"/>
+      <c r="BO69" s="97" t="s">
         <v>522</v>
       </c>
-      <c r="BN69" s="2" t="s">
+      <c r="BP69" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BO69" s="2" t="s">
+      <c r="BQ69" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BP69" s="18" t="s">
+      <c r="BR69" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ69" s="18"/>
-      <c r="BR69" s="21" t="s">
+      <c r="BS69" s="18"/>
+      <c r="BT69" s="21" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="70" spans="1:101" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:103" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="124">
         <v>6</v>
       </c>
@@ -15546,38 +15760,40 @@
       <c r="BD70" s="22"/>
       <c r="BE70" s="22"/>
       <c r="BF70" s="22"/>
-      <c r="BG70" s="20" t="s">
+      <c r="BG70" s="22"/>
+      <c r="BH70" s="22"/>
+      <c r="BI70" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="BH70" s="49" t="s">
+      <c r="BJ70" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="BI70" s="22" t="s">
+      <c r="BK70" s="22" t="s">
         <v>515</v>
       </c>
-      <c r="BJ70" s="22" t="s">
+      <c r="BL70" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="BK70" s="92" t="s">
+      <c r="BM70" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL70" s="22"/>
-      <c r="BM70" s="2"/>
-      <c r="BN70" s="2" t="s">
+      <c r="BN70" s="22"/>
+      <c r="BO70" s="2"/>
+      <c r="BP70" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BO70" s="2" t="s">
+      <c r="BQ70" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BP70" s="18" t="s">
+      <c r="BR70" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ70" s="18"/>
-      <c r="BR70" s="21" t="s">
+      <c r="BS70" s="18"/>
+      <c r="BT70" s="21" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="71" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="124">
         <v>7</v>
       </c>
@@ -15731,38 +15947,38 @@
       <c r="BD71" s="22"/>
       <c r="BE71" s="22"/>
       <c r="BF71" s="22"/>
-      <c r="BG71" s="20" t="s">
+      <c r="BG71" s="22"/>
+      <c r="BH71" s="22"/>
+      <c r="BI71" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="BH71" s="49" t="s">
+      <c r="BJ71" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="BI71" s="22" t="s">
+      <c r="BK71" s="22" t="s">
         <v>515</v>
       </c>
-      <c r="BJ71" s="22" t="s">
+      <c r="BL71" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="BK71" s="92" t="s">
+      <c r="BM71" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL71" s="22"/>
-      <c r="BM71" s="2"/>
-      <c r="BN71" s="2" t="s">
+      <c r="BN71" s="22"/>
+      <c r="BO71" s="2"/>
+      <c r="BP71" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BO71" s="2" t="s">
+      <c r="BQ71" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BP71" s="18" t="s">
+      <c r="BR71" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ71" s="18"/>
-      <c r="BR71" s="21" t="s">
+      <c r="BS71" s="18"/>
+      <c r="BT71" s="21" t="s">
         <v>687</v>
       </c>
-      <c r="BS71" s="88"/>
-      <c r="BT71" s="88"/>
       <c r="BU71" s="88"/>
       <c r="BV71" s="88"/>
       <c r="BW71" s="88"/>
@@ -15792,8 +16008,10 @@
       <c r="CU71" s="88"/>
       <c r="CV71" s="88"/>
       <c r="CW71" s="88"/>
+      <c r="CX71" s="88"/>
+      <c r="CY71" s="88"/>
     </row>
-    <row r="72" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="136">
         <v>8</v>
       </c>
@@ -15938,40 +16156,40 @@
       <c r="BD72" s="22"/>
       <c r="BE72" s="22"/>
       <c r="BF72" s="22"/>
-      <c r="BG72" s="20" t="s">
+      <c r="BG72" s="22"/>
+      <c r="BH72" s="22"/>
+      <c r="BI72" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="BH72" s="49" t="s">
+      <c r="BJ72" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="BI72" s="49" t="s">
+      <c r="BK72" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="BJ72" s="2" t="s">
+      <c r="BL72" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="BK72" s="92" t="s">
+      <c r="BM72" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL72" s="22"/>
-      <c r="BM72" s="2"/>
-      <c r="BN72" s="2" t="s">
+      <c r="BN72" s="22"/>
+      <c r="BO72" s="2"/>
+      <c r="BP72" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="BO72" s="2" t="s">
+      <c r="BQ72" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BP72" s="18" t="s">
+      <c r="BR72" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BQ72" s="18" t="s">
+      <c r="BS72" s="18" t="s">
         <v>733</v>
       </c>
-      <c r="BR72" s="21" t="s">
+      <c r="BT72" s="21" t="s">
         <v>672</v>
       </c>
-      <c r="BS72" s="88"/>
-      <c r="BT72" s="88"/>
       <c r="BU72" s="88"/>
       <c r="BV72" s="88"/>
       <c r="BW72" s="88"/>
@@ -16001,8 +16219,10 @@
       <c r="CU72" s="88"/>
       <c r="CV72" s="88"/>
       <c r="CW72" s="88"/>
+      <c r="CX72" s="88"/>
+      <c r="CY72" s="88"/>
     </row>
-    <row r="73" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="137">
         <v>1</v>
       </c>
@@ -16148,40 +16368,42 @@
       <c r="BD73" s="38"/>
       <c r="BE73" s="38"/>
       <c r="BF73" s="38"/>
-      <c r="BG73" s="34" t="s">
+      <c r="BG73" s="38"/>
+      <c r="BH73" s="38"/>
+      <c r="BI73" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="BH73" s="96" t="s">
+      <c r="BJ73" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="BI73" s="38" t="s">
+      <c r="BK73" s="38" t="s">
         <v>515</v>
       </c>
-      <c r="BJ73" s="38" t="s">
+      <c r="BL73" s="38" t="s">
         <v>516</v>
       </c>
-      <c r="BK73" s="92" t="s">
+      <c r="BM73" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL73" s="38"/>
-      <c r="BM73" s="3" t="s">
+      <c r="BN73" s="38"/>
+      <c r="BO73" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="BN73" s="3" t="s">
+      <c r="BP73" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="BO73" s="3" t="s">
+      <c r="BQ73" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP73" s="37" t="s">
+      <c r="BR73" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ73" s="37"/>
-      <c r="BR73" s="43" t="s">
+      <c r="BS73" s="37"/>
+      <c r="BT73" s="43" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="74" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="137">
         <v>2</v>
       </c>
@@ -16327,38 +16549,40 @@
       <c r="BD74" s="38"/>
       <c r="BE74" s="38"/>
       <c r="BF74" s="38"/>
-      <c r="BG74" s="34" t="s">
+      <c r="BG74" s="38"/>
+      <c r="BH74" s="38"/>
+      <c r="BI74" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="BH74" s="96" t="s">
+      <c r="BJ74" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="BI74" s="38" t="s">
+      <c r="BK74" s="38" t="s">
         <v>515</v>
       </c>
-      <c r="BJ74" s="38" t="s">
+      <c r="BL74" s="38" t="s">
         <v>516</v>
       </c>
-      <c r="BK74" s="92" t="s">
+      <c r="BM74" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL74" s="38"/>
-      <c r="BM74" s="3"/>
-      <c r="BN74" s="3" t="s">
+      <c r="BN74" s="38"/>
+      <c r="BO74" s="3"/>
+      <c r="BP74" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="BO74" s="3" t="s">
+      <c r="BQ74" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP74" s="37" t="s">
+      <c r="BR74" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ74" s="37"/>
-      <c r="BR74" s="43" t="s">
+      <c r="BS74" s="37"/>
+      <c r="BT74" s="43" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="75" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="137">
         <v>3</v>
       </c>
@@ -16503,45 +16727,47 @@
       <c r="BA75" s="38"/>
       <c r="BB75" s="38"/>
       <c r="BC75" s="38"/>
-      <c r="BD75" s="38" t="s">
+      <c r="BD75" s="38"/>
+      <c r="BE75" s="38"/>
+      <c r="BF75" s="38" t="s">
         <v>367</v>
       </c>
-      <c r="BE75" s="38" t="s">
+      <c r="BG75" s="38" t="s">
         <v>368</v>
       </c>
-      <c r="BF75" s="38" t="s">
+      <c r="BH75" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="BG75" s="34" t="s">
+      <c r="BI75" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="BH75" s="96" t="s">
+      <c r="BJ75" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="BI75" s="38" t="s">
+      <c r="BK75" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="BJ75" s="38" t="s">
+      <c r="BL75" s="38" t="s">
         <v>588</v>
       </c>
-      <c r="BK75" s="38"/>
-      <c r="BL75" s="38"/>
-      <c r="BM75" s="3"/>
-      <c r="BN75" s="3" t="s">
+      <c r="BM75" s="38"/>
+      <c r="BN75" s="38"/>
+      <c r="BO75" s="3"/>
+      <c r="BP75" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="BO75" s="3" t="s">
+      <c r="BQ75" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP75" s="37" t="s">
+      <c r="BR75" s="37" t="s">
         <v>683</v>
       </c>
-      <c r="BQ75" s="37"/>
-      <c r="BR75" s="43" t="s">
+      <c r="BS75" s="37"/>
+      <c r="BT75" s="43" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="76" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="137">
         <v>4</v>
       </c>
@@ -16687,36 +16913,38 @@
       <c r="BD76" s="38"/>
       <c r="BE76" s="38"/>
       <c r="BF76" s="38"/>
-      <c r="BG76" s="34" t="s">
+      <c r="BG76" s="38"/>
+      <c r="BH76" s="38"/>
+      <c r="BI76" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="BH76" s="96" t="s">
+      <c r="BJ76" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="BI76" s="38" t="s">
+      <c r="BK76" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="BJ76" s="38" t="s">
+      <c r="BL76" s="38" t="s">
         <v>589</v>
       </c>
-      <c r="BK76" s="92" t="s">
+      <c r="BM76" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL76" s="38"/>
-      <c r="BM76" s="3"/>
-      <c r="BN76" s="3" t="s">
+      <c r="BN76" s="38"/>
+      <c r="BO76" s="3"/>
+      <c r="BP76" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="BO76" s="3" t="s">
+      <c r="BQ76" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP76" s="37" t="s">
+      <c r="BR76" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ76" s="37"/>
-      <c r="BR76" s="43"/>
+      <c r="BS76" s="37"/>
+      <c r="BT76" s="43"/>
     </row>
-    <row r="77" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="137">
         <v>5</v>
       </c>
@@ -16862,42 +17090,44 @@
       <c r="BD77" s="38"/>
       <c r="BE77" s="38"/>
       <c r="BF77" s="38"/>
-      <c r="BG77" s="34" t="s">
+      <c r="BG77" s="38"/>
+      <c r="BH77" s="38"/>
+      <c r="BI77" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="BH77" s="96" t="s">
+      <c r="BJ77" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="BI77" s="38" t="s">
+      <c r="BK77" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BJ77" s="38" t="s">
+      <c r="BL77" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="BK77" s="92" t="s">
+      <c r="BM77" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL77" s="3">
+      <c r="BN77" s="3">
         <v>1540746</v>
       </c>
-      <c r="BM77" s="3"/>
-      <c r="BN77" s="3" t="s">
+      <c r="BO77" s="3"/>
+      <c r="BP77" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="BO77" s="3" t="s">
+      <c r="BQ77" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP77" s="37" t="s">
+      <c r="BR77" s="37" t="s">
         <v>699</v>
       </c>
-      <c r="BQ77" s="37" t="s">
+      <c r="BS77" s="37" t="s">
         <v>734</v>
       </c>
-      <c r="BR77" s="43" t="s">
+      <c r="BT77" s="43" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="78" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="137">
         <v>6</v>
       </c>
@@ -17043,42 +17273,44 @@
       <c r="BD78" s="38"/>
       <c r="BE78" s="38"/>
       <c r="BF78" s="38"/>
-      <c r="BG78" s="34" t="s">
+      <c r="BG78" s="38"/>
+      <c r="BH78" s="38"/>
+      <c r="BI78" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="BH78" s="96" t="s">
+      <c r="BJ78" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="BI78" s="38" t="s">
+      <c r="BK78" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="BJ78" s="38" t="s">
+      <c r="BL78" s="38" t="s">
         <v>589</v>
       </c>
-      <c r="BK78" s="92" t="s">
+      <c r="BM78" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BL78" s="3">
+      <c r="BN78" s="3">
         <v>1272212</v>
       </c>
-      <c r="BM78" s="3" t="s">
+      <c r="BO78" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="BN78" s="3" t="s">
+      <c r="BP78" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="BO78" s="3" t="s">
+      <c r="BQ78" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP78" s="37" t="s">
+      <c r="BR78" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ78" s="37"/>
-      <c r="BR78" s="43" t="s">
+      <c r="BS78" s="37"/>
+      <c r="BT78" s="43" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="79" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="137">
         <v>7</v>
       </c>
@@ -17224,42 +17456,44 @@
       <c r="BD79" s="38"/>
       <c r="BE79" s="38"/>
       <c r="BF79" s="38"/>
-      <c r="BG79" s="34" t="s">
+      <c r="BG79" s="38"/>
+      <c r="BH79" s="38"/>
+      <c r="BI79" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="BH79" s="96" t="s">
+      <c r="BJ79" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="BI79" s="38" t="s">
+      <c r="BK79" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="BJ79" s="38" t="s">
+      <c r="BL79" s="38" t="s">
         <v>588</v>
       </c>
-      <c r="BK79" s="92" t="s">
+      <c r="BM79" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="BL79" s="38" t="s">
+      <c r="BN79" s="38" t="s">
         <v>702</v>
       </c>
-      <c r="BM79" s="3" t="s">
+      <c r="BO79" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="BN79" s="3" t="s">
+      <c r="BP79" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="BO79" s="3" t="s">
+      <c r="BQ79" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP79" s="37" t="s">
+      <c r="BR79" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ79" s="37"/>
-      <c r="BR79" s="43" t="s">
+      <c r="BS79" s="37"/>
+      <c r="BT79" s="43" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="80" spans="1:101" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A80" s="137">
         <v>8</v>
       </c>
@@ -17405,51 +17639,55 @@
       <c r="BD80" s="38"/>
       <c r="BE80" s="38"/>
       <c r="BF80" s="38"/>
-      <c r="BG80" s="34" t="s">
+      <c r="BG80" s="38"/>
+      <c r="BH80" s="38"/>
+      <c r="BI80" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="BH80" s="96" t="s">
+      <c r="BJ80" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="BI80" s="38" t="s">
+      <c r="BK80" s="38" t="s">
         <v>515</v>
       </c>
-      <c r="BJ80" s="38" t="s">
+      <c r="BL80" s="38" t="s">
         <v>516</v>
       </c>
-      <c r="BK80" s="38" t="s">
+      <c r="BM80" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="BL80" s="38" t="s">
+      <c r="BN80" s="38" t="s">
         <v>702</v>
       </c>
-      <c r="BM80" s="3" t="s">
+      <c r="BO80" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="BN80" s="3" t="s">
+      <c r="BP80" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="BO80" s="3" t="s">
+      <c r="BQ80" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP80" s="37" t="s">
+      <c r="BR80" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BQ80" s="37" t="s">
-        <v>754</v>
-      </c>
-      <c r="BR80" s="43" t="s">
+      <c r="BS80" s="37" t="s">
         <v>753</v>
       </c>
+      <c r="BT80" s="43" t="s">
+        <v>768</v>
+      </c>
     </row>
-    <row r="81" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="137">
+    <row r="81" spans="1:72" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="149">
         <v>9</v>
       </c>
       <c r="B81" s="35">
         <v>20250304</v>
       </c>
-      <c r="C81" s="35"/>
+      <c r="C81" s="35">
+        <v>20250324</v>
+      </c>
       <c r="D81" s="35" t="s">
         <v>44</v>
       </c>
@@ -17468,7 +17706,9 @@
       <c r="I81" s="3">
         <v>28.9</v>
       </c>
-      <c r="J81" s="3"/>
+      <c r="J81" s="3">
+        <v>23.8</v>
+      </c>
       <c r="K81" s="35">
         <v>44.452500000000001</v>
       </c>
@@ -17478,17 +17718,34 @@
       <c r="M81" s="138">
         <v>0.62847222222222221</v>
       </c>
-      <c r="N81" s="37"/>
-      <c r="O81" s="37"/>
-      <c r="P81" s="37"/>
-      <c r="Q81" s="37"/>
+      <c r="N81" s="37">
+        <v>42.46</v>
+      </c>
+      <c r="O81" s="37">
+        <v>-63.39</v>
+      </c>
+      <c r="P81" s="37">
+        <v>44.46</v>
+      </c>
+      <c r="Q81" s="37">
+        <v>-61.42</v>
+      </c>
       <c r="R81" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="S81" s="3"/>
-      <c r="T81" s="3"/>
-      <c r="U81" s="3"/>
-      <c r="V81" s="3"/>
+      <c r="S81" s="3">
+        <v>20</v>
+      </c>
+      <c r="T81" s="3">
+        <v>604</v>
+      </c>
+      <c r="U81" s="3">
+        <v>1004</v>
+      </c>
+      <c r="V81" s="3">
+        <f>906*2</f>
+        <v>1812</v>
+      </c>
       <c r="W81" s="37" t="s">
         <v>36</v>
       </c>
@@ -17507,9 +17764,15 @@
         <v>462</v>
       </c>
       <c r="AD81" s="37"/>
-      <c r="AE81" s="3"/>
-      <c r="AF81" s="3"/>
-      <c r="AG81" s="3"/>
+      <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
       <c r="AH81" s="3">
         <v>1024.9000000000001</v>
       </c>
@@ -17517,7 +17780,7 @@
         <v>20250218</v>
       </c>
       <c r="AJ81" s="37" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="AK81" s="37" t="s">
         <v>740</v>
@@ -17569,394 +17832,515 @@
       <c r="BD81" s="38"/>
       <c r="BE81" s="38"/>
       <c r="BF81" s="38"/>
-      <c r="BG81" s="34" t="s">
+      <c r="BG81" s="38"/>
+      <c r="BH81" s="38"/>
+      <c r="BI81" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="BH81" s="96" t="s">
+      <c r="BJ81" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="BI81" s="38" t="s">
+      <c r="BK81" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="BJ81" s="38" t="s">
+      <c r="BL81" s="38" t="s">
         <v>588</v>
       </c>
-      <c r="BK81" s="38" t="s">
+      <c r="BM81" s="38" t="s">
         <v>744</v>
       </c>
-      <c r="BL81" s="3">
+      <c r="BN81" s="3">
         <v>1540746</v>
       </c>
-      <c r="BM81" s="3"/>
-      <c r="BN81" s="3" t="s">
+      <c r="BO81" s="3"/>
+      <c r="BP81" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="BO81" s="3" t="s">
+      <c r="BQ81" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BP81" s="37" t="s">
-        <v>755</v>
-      </c>
-      <c r="BQ81" s="37"/>
-      <c r="BR81" s="43" t="s">
+      <c r="BR81" s="37" t="s">
         <v>761</v>
       </c>
+      <c r="BS81" s="37" t="s">
+        <v>770</v>
+      </c>
+      <c r="BT81" s="43" t="s">
+        <v>772</v>
+      </c>
     </row>
-    <row r="82" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="137"/>
-      <c r="B82" s="35"/>
-      <c r="C82" s="35"/>
-      <c r="D82" s="35" t="s">
+    <row r="82" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="124">
+        <v>1</v>
+      </c>
+      <c r="B82" s="14">
+        <v>20250324</v>
+      </c>
+      <c r="C82" s="14">
+        <v>20250415</v>
+      </c>
+      <c r="D82" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E82" s="35">
+      <c r="E82" s="14">
         <v>89</v>
       </c>
-      <c r="F82" s="35">
+      <c r="F82" s="14">
         <v>4800937</v>
       </c>
-      <c r="G82" s="35" t="s">
+      <c r="G82" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H82" s="37" t="s">
-        <v>762</v>
-      </c>
-      <c r="I82" s="3"/>
-      <c r="J82" s="3"/>
-      <c r="K82" s="35"/>
-      <c r="L82" s="35"/>
-      <c r="M82" s="138"/>
-      <c r="N82" s="37"/>
-      <c r="O82" s="37"/>
-      <c r="P82" s="37"/>
-      <c r="Q82" s="37"/>
-      <c r="R82" s="3" t="s">
+      <c r="H82" s="18" t="s">
+        <v>759</v>
+      </c>
+      <c r="I82" s="2">
+        <v>29.1</v>
+      </c>
+      <c r="J82" s="2">
+        <v>25.4</v>
+      </c>
+      <c r="K82" s="14">
+        <v>44.372500000000002</v>
+      </c>
+      <c r="L82" s="14">
+        <v>-63.310200000000002</v>
+      </c>
+      <c r="M82" s="100">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="N82" s="18">
+        <v>42.47</v>
+      </c>
+      <c r="O82" s="18">
+        <v>-63.43</v>
+      </c>
+      <c r="P82" s="18">
+        <v>44.53</v>
+      </c>
+      <c r="Q82" s="18">
+        <v>-61.45</v>
+      </c>
+      <c r="R82" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S82" s="3"/>
-      <c r="T82" s="3"/>
-      <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
-      <c r="W82" s="37" t="s">
+      <c r="S82" s="2">
+        <v>22</v>
+      </c>
+      <c r="T82" s="2">
+        <v>582</v>
+      </c>
+      <c r="U82" s="2">
+        <v>998</v>
+      </c>
+      <c r="V82" s="2">
+        <f>413*2</f>
+        <v>826</v>
+      </c>
+      <c r="W82" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="X82" s="37">
+      <c r="X82" s="18">
         <v>1</v>
       </c>
-      <c r="Y82" s="37" t="s">
+      <c r="Y82" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="Z82" s="37" t="s">
+      <c r="Z82" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="AA82" s="37"/>
-      <c r="AB82" s="37"/>
-      <c r="AC82" s="37"/>
-      <c r="AD82" s="37"/>
-      <c r="AE82" s="3"/>
-      <c r="AF82" s="3"/>
-      <c r="AG82" s="3"/>
-      <c r="AH82" s="3">
+      <c r="AA82" s="18"/>
+      <c r="AB82" s="18"/>
+      <c r="AC82" s="18"/>
+      <c r="AD82" s="18"/>
+      <c r="AE82" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="2">
+        <v>5</v>
+      </c>
+      <c r="AH82" s="2">
         <v>1024.9000000000001</v>
       </c>
-      <c r="AI82" s="37">
+      <c r="AI82" s="18">
         <v>20250305</v>
       </c>
-      <c r="AJ82" s="37" t="s">
-        <v>756</v>
-      </c>
-      <c r="AK82" s="37" t="s">
+      <c r="AJ82" s="18" t="s">
+        <v>754</v>
+      </c>
+      <c r="AK82" s="18" t="s">
         <v>740</v>
       </c>
-      <c r="AL82" s="35">
+      <c r="AL82" s="14">
         <v>32</v>
       </c>
-      <c r="AM82" s="34" t="s">
+      <c r="AM82" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="AN82" s="38" t="s">
+      <c r="AN82" s="22" t="s">
+        <v>758</v>
+      </c>
+      <c r="AO82" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="AP82" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ82" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR82" s="22" t="s">
+        <v>757</v>
+      </c>
+      <c r="AS82" s="22"/>
+      <c r="AT82" s="22"/>
+      <c r="AU82" s="22"/>
+      <c r="AV82" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW82" s="16">
+        <v>42711</v>
+      </c>
+      <c r="AX82" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="AY82" s="22"/>
+      <c r="AZ82" s="22"/>
+      <c r="BA82" s="22"/>
+      <c r="BB82" s="22"/>
+      <c r="BC82" s="22"/>
+      <c r="BD82" s="22"/>
+      <c r="BE82" s="22"/>
+      <c r="BF82" s="22"/>
+      <c r="BG82" s="22"/>
+      <c r="BH82" s="22"/>
+      <c r="BI82" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ82" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK82" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="BL82" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="BM82" s="22" t="s">
+        <v>771</v>
+      </c>
+      <c r="BN82" s="2">
+        <v>1272212</v>
+      </c>
+      <c r="BO82" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="AO82" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="AP82" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ82" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="AR82" s="38" t="s">
-        <v>759</v>
-      </c>
-      <c r="AS82" s="38"/>
-      <c r="AT82" s="38"/>
-      <c r="AU82" s="38"/>
-      <c r="AV82" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="AW82" s="39">
-        <v>42711</v>
-      </c>
-      <c r="AX82" s="38" t="s">
+      <c r="BP82" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="BQ82" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="BR82" s="18" t="s">
+        <v>773</v>
+      </c>
+      <c r="BS82" s="18" t="s">
+        <v>769</v>
+      </c>
+      <c r="BT82" s="21" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="83" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="124"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="14">
+        <v>137</v>
+      </c>
+      <c r="F83" s="14">
+        <v>4800925</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" s="18" t="s">
+        <v>741</v>
+      </c>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="14"/>
+      <c r="L83" s="14"/>
+      <c r="M83" s="100"/>
+      <c r="N83" s="18"/>
+      <c r="O83" s="18"/>
+      <c r="P83" s="18"/>
+      <c r="Q83" s="18"/>
+      <c r="R83" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="S83" s="2"/>
+      <c r="T83" s="2"/>
+      <c r="U83" s="2"/>
+      <c r="V83" s="2"/>
+      <c r="W83" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X83" s="18">
+        <v>1</v>
+      </c>
+      <c r="Y83" s="18"/>
+      <c r="Z83" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA83" s="18"/>
+      <c r="AB83" s="18"/>
+      <c r="AC83" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="AD83" s="18"/>
+      <c r="AE83" s="2"/>
+      <c r="AF83" s="2"/>
+      <c r="AG83" s="2"/>
+      <c r="AH83" s="2">
+        <v>1024.3</v>
+      </c>
+      <c r="AI83" s="18"/>
+      <c r="AJ83" s="18"/>
+      <c r="AK83" s="18"/>
+      <c r="AL83" s="14">
+        <v>33</v>
+      </c>
+      <c r="AM83" s="20"/>
+      <c r="AN83" s="22"/>
+      <c r="AO83" s="22"/>
+      <c r="AP83" s="10"/>
+      <c r="AQ83" s="10"/>
+      <c r="AR83" s="22"/>
+      <c r="AS83" s="22"/>
+      <c r="AT83" s="22"/>
+      <c r="AU83" s="22"/>
+      <c r="AV83" s="10">
+        <v>4551</v>
+      </c>
+      <c r="AW83" s="16">
+        <v>42691</v>
+      </c>
+      <c r="AX83" s="22" t="s">
         <v>461</v>
       </c>
-      <c r="AY82" s="38"/>
-      <c r="AZ82" s="38"/>
-      <c r="BA82" s="38"/>
-      <c r="BB82" s="38"/>
-      <c r="BC82" s="38"/>
-      <c r="BD82" s="38"/>
-      <c r="BE82" s="38"/>
-      <c r="BF82" s="38"/>
-      <c r="BG82" s="34" t="s">
+      <c r="AY83" s="22"/>
+      <c r="AZ83" s="22"/>
+      <c r="BA83" s="22" t="s">
+        <v>765</v>
+      </c>
+      <c r="BB83" s="22" t="s">
+        <v>779</v>
+      </c>
+      <c r="BC83" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="BD83" s="22" t="s">
+        <v>776</v>
+      </c>
+      <c r="BE83" s="22" t="s">
+        <v>783</v>
+      </c>
+      <c r="BF83" s="22"/>
+      <c r="BG83" s="22"/>
+      <c r="BH83" s="22"/>
+      <c r="BI83" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="BH82" s="96" t="s">
+      <c r="BJ83" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="BI82" s="38" t="s">
-        <v>515</v>
-      </c>
-      <c r="BJ82" s="38" t="s">
-        <v>516</v>
-      </c>
-      <c r="BK82" s="133"/>
-      <c r="BL82" s="134">
-        <v>1272212</v>
-      </c>
-      <c r="BM82" s="134" t="s">
-        <v>763</v>
-      </c>
-      <c r="BN82" s="3" t="s">
+      <c r="BK83" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="BL83" s="38" t="s">
+        <v>588</v>
+      </c>
+      <c r="BM83" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BN83" s="38" t="s">
+        <v>702</v>
+      </c>
+      <c r="BO83" s="2"/>
+      <c r="BP83" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="BO82" s="3" t="s">
+      <c r="BQ83" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BP82" s="37"/>
-      <c r="BQ82" s="37"/>
-      <c r="BR82" s="43" t="s">
+      <c r="BR83" s="18"/>
+      <c r="BS83" s="18"/>
+      <c r="BT83" s="21" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="84" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="124"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="14"/>
+      <c r="L84" s="14"/>
+      <c r="M84" s="100"/>
+      <c r="N84" s="18"/>
+      <c r="O84" s="18"/>
+      <c r="P84" s="18"/>
+      <c r="Q84" s="18"/>
+      <c r="R84" s="2"/>
+      <c r="S84" s="2"/>
+      <c r="T84" s="2"/>
+      <c r="U84" s="2"/>
+      <c r="V84" s="2"/>
+      <c r="W84" s="18"/>
+      <c r="X84" s="18"/>
+      <c r="Y84" s="18"/>
+      <c r="Z84" s="18"/>
+      <c r="AA84" s="18"/>
+      <c r="AB84" s="18"/>
+      <c r="AC84" s="18"/>
+      <c r="AD84" s="18"/>
+      <c r="AE84" s="2"/>
+      <c r="AF84" s="2"/>
+      <c r="AG84" s="2"/>
+      <c r="AH84" s="2"/>
+      <c r="AI84" s="18"/>
+      <c r="AJ84" s="18"/>
+      <c r="AK84" s="18"/>
+      <c r="AL84" s="14"/>
+      <c r="AM84" s="20"/>
+      <c r="AN84" s="22"/>
+      <c r="AO84" s="22"/>
+      <c r="AP84" s="10"/>
+      <c r="AQ84" s="10"/>
+      <c r="AR84" s="22"/>
+      <c r="AS84" s="22"/>
+      <c r="AT84" s="22"/>
+      <c r="AU84" s="22"/>
+      <c r="AV84" s="10"/>
+      <c r="AW84" s="16"/>
+      <c r="AX84" s="22"/>
+      <c r="AY84" s="22"/>
+      <c r="AZ84" s="22"/>
+      <c r="BA84" s="22" t="s">
         <v>764</v>
       </c>
+      <c r="BB84" s="22"/>
+      <c r="BC84" s="22"/>
+      <c r="BD84" s="22" t="s">
+        <v>775</v>
+      </c>
+      <c r="BE84" s="22"/>
+      <c r="BF84" s="22"/>
+      <c r="BG84" s="22"/>
+      <c r="BH84" s="22"/>
+      <c r="BI84" s="20"/>
+      <c r="BJ84" s="147"/>
+      <c r="BK84" s="22"/>
+      <c r="BL84" s="22"/>
+      <c r="BM84" s="79"/>
+      <c r="BN84" s="79"/>
+      <c r="BO84" s="2"/>
+      <c r="BP84" s="148"/>
+      <c r="BQ84" s="2"/>
+      <c r="BR84" s="18"/>
+      <c r="BS84" s="18"/>
+      <c r="BT84" s="21"/>
     </row>
-    <row r="83" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="137"/>
-      <c r="B83" s="35"/>
-      <c r="C83" s="35"/>
-      <c r="D83" s="35"/>
-      <c r="E83" s="35"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="35"/>
-      <c r="H83" s="37"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="3"/>
-      <c r="K83" s="35"/>
-      <c r="L83" s="35"/>
-      <c r="M83" s="138"/>
-      <c r="N83" s="37"/>
-      <c r="O83" s="37"/>
-      <c r="P83" s="37"/>
-      <c r="Q83" s="37"/>
-      <c r="R83" s="3"/>
-      <c r="S83" s="3"/>
-      <c r="T83" s="3"/>
-      <c r="U83" s="3"/>
-      <c r="V83" s="3"/>
-      <c r="W83" s="37"/>
-      <c r="X83" s="37"/>
-      <c r="Y83" s="37"/>
-      <c r="Z83" s="37"/>
-      <c r="AA83" s="37"/>
-      <c r="AB83" s="37"/>
-      <c r="AC83" s="37"/>
-      <c r="AD83" s="37"/>
-      <c r="AE83" s="3"/>
-      <c r="AF83" s="3"/>
-      <c r="AG83" s="3"/>
-      <c r="AH83" s="3"/>
-      <c r="AI83" s="37"/>
-      <c r="AJ83" s="37"/>
-      <c r="AK83" s="37"/>
-      <c r="AL83" s="35"/>
-      <c r="AM83" s="34"/>
-      <c r="AN83" s="38"/>
-      <c r="AO83" s="38"/>
-      <c r="AP83" s="41"/>
-      <c r="AQ83" s="41"/>
-      <c r="AR83" s="38"/>
-      <c r="AS83" s="38"/>
-      <c r="AT83" s="38"/>
-      <c r="AU83" s="38"/>
-      <c r="AV83" s="41"/>
-      <c r="AW83" s="39"/>
-      <c r="AX83" s="38"/>
-      <c r="AY83" s="38"/>
-      <c r="AZ83" s="38"/>
-      <c r="BA83" s="38"/>
-      <c r="BB83" s="38"/>
-      <c r="BC83" s="38"/>
-      <c r="BD83" s="38"/>
-      <c r="BE83" s="38"/>
-      <c r="BF83" s="38"/>
-      <c r="BG83" s="34"/>
-      <c r="BH83" s="139"/>
-      <c r="BI83" s="38"/>
-      <c r="BJ83" s="38"/>
-      <c r="BK83" s="133"/>
-      <c r="BL83" s="133"/>
-      <c r="BM83" s="3"/>
-      <c r="BN83" s="146"/>
-      <c r="BO83" s="3"/>
-      <c r="BP83" s="37"/>
-      <c r="BQ83" s="37"/>
-      <c r="BR83" s="43"/>
+    <row r="85" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="124"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="18"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="14"/>
+      <c r="L85" s="14"/>
+      <c r="M85" s="100"/>
+      <c r="N85" s="18"/>
+      <c r="O85" s="18"/>
+      <c r="P85" s="18"/>
+      <c r="Q85" s="18"/>
+      <c r="R85" s="2"/>
+      <c r="S85" s="2"/>
+      <c r="T85" s="2"/>
+      <c r="U85" s="2"/>
+      <c r="V85" s="2"/>
+      <c r="W85" s="18"/>
+      <c r="X85" s="18"/>
+      <c r="Y85" s="18"/>
+      <c r="Z85" s="18"/>
+      <c r="AA85" s="18"/>
+      <c r="AB85" s="18"/>
+      <c r="AC85" s="18"/>
+      <c r="AD85" s="18"/>
+      <c r="AE85" s="2"/>
+      <c r="AF85" s="2"/>
+      <c r="AG85" s="2"/>
+      <c r="AH85" s="2"/>
+      <c r="AI85" s="18"/>
+      <c r="AJ85" s="18"/>
+      <c r="AK85" s="18"/>
+      <c r="AL85" s="14"/>
+      <c r="AM85" s="20"/>
+      <c r="AN85" s="22"/>
+      <c r="AO85" s="22"/>
+      <c r="AP85" s="10"/>
+      <c r="AQ85" s="10"/>
+      <c r="AR85" s="22"/>
+      <c r="AS85" s="22"/>
+      <c r="AT85" s="22"/>
+      <c r="AU85" s="22"/>
+      <c r="AV85" s="10"/>
+      <c r="AW85" s="16"/>
+      <c r="AX85" s="22"/>
+      <c r="AY85" s="22"/>
+      <c r="AZ85" s="22"/>
+      <c r="BA85" s="22"/>
+      <c r="BB85" s="22"/>
+      <c r="BC85" s="22"/>
+      <c r="BD85" s="22"/>
+      <c r="BE85" s="22"/>
+      <c r="BF85" s="22"/>
+      <c r="BG85" s="22"/>
+      <c r="BH85" s="22"/>
+      <c r="BI85" s="20"/>
+      <c r="BJ85" s="147"/>
+      <c r="BK85" s="22"/>
+      <c r="BL85" s="22"/>
+      <c r="BM85" s="79"/>
+      <c r="BN85" s="79"/>
+      <c r="BO85" s="2"/>
+      <c r="BP85" s="148"/>
+      <c r="BQ85" s="2"/>
+      <c r="BR85" s="18"/>
+      <c r="BS85" s="18"/>
+      <c r="BT85" s="21"/>
     </row>
-    <row r="84" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="137"/>
-      <c r="B84" s="35"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="35"/>
-      <c r="E84" s="35"/>
-      <c r="F84" s="35"/>
-      <c r="G84" s="35"/>
-      <c r="H84" s="37"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3"/>
-      <c r="K84" s="35"/>
-      <c r="L84" s="35"/>
-      <c r="M84" s="138"/>
-      <c r="N84" s="37"/>
-      <c r="O84" s="37"/>
-      <c r="P84" s="37"/>
-      <c r="Q84" s="37"/>
-      <c r="R84" s="3"/>
-      <c r="S84" s="3"/>
-      <c r="T84" s="3"/>
-      <c r="U84" s="3"/>
-      <c r="V84" s="3"/>
-      <c r="W84" s="37"/>
-      <c r="X84" s="37"/>
-      <c r="Y84" s="37"/>
-      <c r="Z84" s="37"/>
-      <c r="AA84" s="37"/>
-      <c r="AB84" s="37"/>
-      <c r="AC84" s="37"/>
-      <c r="AD84" s="37"/>
-      <c r="AE84" s="3"/>
-      <c r="AF84" s="3"/>
-      <c r="AG84" s="3"/>
-      <c r="AH84" s="3"/>
-      <c r="AI84" s="37"/>
-      <c r="AJ84" s="37"/>
-      <c r="AK84" s="37"/>
-      <c r="AL84" s="35"/>
-      <c r="AM84" s="34"/>
-      <c r="AN84" s="38"/>
-      <c r="AO84" s="38"/>
-      <c r="AP84" s="41"/>
-      <c r="AQ84" s="41"/>
-      <c r="AR84" s="38"/>
-      <c r="AS84" s="38"/>
-      <c r="AT84" s="38"/>
-      <c r="AU84" s="38"/>
-      <c r="AV84" s="41"/>
-      <c r="AW84" s="39"/>
-      <c r="AX84" s="38"/>
-      <c r="AY84" s="38"/>
-      <c r="AZ84" s="38"/>
-      <c r="BA84" s="38"/>
-      <c r="BB84" s="38"/>
-      <c r="BC84" s="38"/>
-      <c r="BD84" s="38"/>
-      <c r="BE84" s="38"/>
-      <c r="BF84" s="38"/>
-      <c r="BG84" s="34"/>
-      <c r="BH84" s="139"/>
-      <c r="BI84" s="38"/>
-      <c r="BJ84" s="38"/>
-      <c r="BK84" s="133"/>
-      <c r="BL84" s="133"/>
-      <c r="BM84" s="3"/>
-      <c r="BN84" s="146"/>
-      <c r="BO84" s="3"/>
-      <c r="BP84" s="37"/>
-      <c r="BQ84" s="37"/>
-      <c r="BR84" s="43"/>
-    </row>
-    <row r="85" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="137"/>
-      <c r="B85" s="35"/>
-      <c r="C85" s="35"/>
-      <c r="D85" s="35"/>
-      <c r="E85" s="35"/>
-      <c r="F85" s="35"/>
-      <c r="G85" s="35"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
-      <c r="K85" s="35"/>
-      <c r="L85" s="35"/>
-      <c r="M85" s="138"/>
-      <c r="N85" s="37"/>
-      <c r="O85" s="37"/>
-      <c r="P85" s="37"/>
-      <c r="Q85" s="37"/>
-      <c r="R85" s="3"/>
-      <c r="S85" s="3"/>
-      <c r="T85" s="3"/>
-      <c r="U85" s="3"/>
-      <c r="V85" s="3"/>
-      <c r="W85" s="37"/>
-      <c r="X85" s="37"/>
-      <c r="Y85" s="37"/>
-      <c r="Z85" s="37"/>
-      <c r="AA85" s="37"/>
-      <c r="AB85" s="37"/>
-      <c r="AC85" s="37"/>
-      <c r="AD85" s="37"/>
-      <c r="AE85" s="3"/>
-      <c r="AF85" s="3"/>
-      <c r="AG85" s="3"/>
-      <c r="AH85" s="3"/>
-      <c r="AI85" s="37"/>
-      <c r="AJ85" s="37"/>
-      <c r="AK85" s="37"/>
-      <c r="AL85" s="35"/>
-      <c r="AM85" s="34"/>
-      <c r="AN85" s="38"/>
-      <c r="AO85" s="38"/>
-      <c r="AP85" s="41"/>
-      <c r="AQ85" s="41"/>
-      <c r="AR85" s="38"/>
-      <c r="AS85" s="38"/>
-      <c r="AT85" s="38"/>
-      <c r="AU85" s="38"/>
-      <c r="AV85" s="41"/>
-      <c r="AW85" s="39"/>
-      <c r="AX85" s="38"/>
-      <c r="AY85" s="38"/>
-      <c r="AZ85" s="38"/>
-      <c r="BA85" s="38"/>
-      <c r="BB85" s="38"/>
-      <c r="BC85" s="38"/>
-      <c r="BD85" s="38"/>
-      <c r="BE85" s="38"/>
-      <c r="BF85" s="38"/>
-      <c r="BG85" s="34"/>
-      <c r="BH85" s="139"/>
-      <c r="BI85" s="38"/>
-      <c r="BJ85" s="38"/>
-      <c r="BK85" s="133"/>
-      <c r="BL85" s="133"/>
-      <c r="BM85" s="3"/>
-      <c r="BN85" s="146"/>
-      <c r="BO85" s="3"/>
-      <c r="BP85" s="37"/>
-      <c r="BQ85" s="37"/>
-      <c r="BR85" s="43"/>
-    </row>
-    <row r="86" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:72" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="137"/>
       <c r="B86" s="35"/>
       <c r="C86" s="35"/>
@@ -18015,22 +18399,24 @@
       <c r="BD86" s="38"/>
       <c r="BE86" s="38"/>
       <c r="BF86" s="38"/>
-      <c r="BG86" s="34"/>
-      <c r="BH86" s="139"/>
-      <c r="BI86" s="38"/>
-      <c r="BJ86" s="38" t="s">
+      <c r="BG86" s="38"/>
+      <c r="BH86" s="38"/>
+      <c r="BI86" s="34"/>
+      <c r="BJ86" s="139"/>
+      <c r="BK86" s="38"/>
+      <c r="BL86" s="38" t="s">
         <v>747</v>
       </c>
-      <c r="BK86" s="38"/>
-      <c r="BL86" s="38"/>
-      <c r="BM86" s="3"/>
-      <c r="BN86" s="120"/>
-      <c r="BO86" s="35"/>
-      <c r="BP86" s="37"/>
-      <c r="BQ86" s="37"/>
-      <c r="BR86" s="43"/>
+      <c r="BM86" s="38"/>
+      <c r="BN86" s="38"/>
+      <c r="BO86" s="3"/>
+      <c r="BP86" s="120"/>
+      <c r="BQ86" s="35"/>
+      <c r="BR86" s="37"/>
+      <c r="BS86" s="37"/>
+      <c r="BT86" s="43"/>
     </row>
-    <row r="87" spans="1:70" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:72" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="137"/>
       <c r="B87" s="35"/>
       <c r="C87" s="35"/>
@@ -18089,24 +18475,26 @@
       <c r="BD87" s="38"/>
       <c r="BE87" s="38"/>
       <c r="BF87" s="38"/>
-      <c r="BG87" s="34"/>
-      <c r="BH87" s="139"/>
-      <c r="BI87" s="38" t="s">
+      <c r="BG87" s="38"/>
+      <c r="BH87" s="38"/>
+      <c r="BI87" s="34"/>
+      <c r="BJ87" s="139"/>
+      <c r="BK87" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BJ87" s="147" t="s">
+      <c r="BL87" s="146" t="s">
         <v>751</v>
       </c>
-      <c r="BK87" s="38"/>
-      <c r="BL87" s="38"/>
-      <c r="BM87" s="3"/>
-      <c r="BN87" s="120"/>
-      <c r="BO87" s="35"/>
-      <c r="BP87" s="37"/>
-      <c r="BQ87" s="37"/>
-      <c r="BR87" s="43"/>
+      <c r="BM87" s="38"/>
+      <c r="BN87" s="38"/>
+      <c r="BO87" s="3"/>
+      <c r="BP87" s="120"/>
+      <c r="BQ87" s="35"/>
+      <c r="BR87" s="37"/>
+      <c r="BS87" s="37"/>
+      <c r="BT87" s="43"/>
     </row>
-    <row r="88" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="116"/>
       <c r="C88" s="116"/>
       <c r="D88" s="116"/>
@@ -18145,31 +18533,39 @@
       <c r="AW88" s="78"/>
       <c r="AX88" s="78"/>
       <c r="AY88" s="78"/>
-      <c r="AZ88" s="78"/>
-      <c r="BA88" s="78"/>
-      <c r="BB88" s="78"/>
+      <c r="AZ88" s="150" t="s">
+        <v>767</v>
+      </c>
+      <c r="BA88" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="BB88" s="78" t="s">
+        <v>785</v>
+      </c>
       <c r="BC88" s="78"/>
       <c r="BD88" s="78"/>
       <c r="BE88" s="78"/>
       <c r="BF88" s="78"/>
-      <c r="BG88" s="117"/>
-      <c r="BH88" s="118"/>
-      <c r="BI88" s="38" t="s">
+      <c r="BG88" s="78"/>
+      <c r="BH88" s="78"/>
+      <c r="BI88" s="117"/>
+      <c r="BJ88" s="118"/>
+      <c r="BK88" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="BJ88" s="145" t="s">
+      <c r="BL88" s="145" t="s">
         <v>588</v>
       </c>
-      <c r="BK88" s="38"/>
-      <c r="BL88" s="38"/>
-      <c r="BM88" s="3"/>
-      <c r="BN88" s="121"/>
-      <c r="BO88" s="45"/>
-      <c r="BP88" s="77"/>
-      <c r="BQ88" s="77"/>
-      <c r="BR88" s="119"/>
+      <c r="BM88" s="38"/>
+      <c r="BN88" s="38"/>
+      <c r="BO88" s="3"/>
+      <c r="BP88" s="121"/>
+      <c r="BQ88" s="45"/>
+      <c r="BR88" s="77"/>
+      <c r="BS88" s="77"/>
+      <c r="BT88" s="119"/>
     </row>
-    <row r="89" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="116"/>
       <c r="C89" s="116"/>
       <c r="D89" s="116"/>
@@ -18208,35 +18604,41 @@
         <v>74</v>
       </c>
       <c r="AW89" s="26" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AX89" s="78"/>
       <c r="AY89" s="78"/>
-      <c r="AZ89" s="78"/>
-      <c r="BA89" s="78"/>
-      <c r="BB89" s="78"/>
+      <c r="AZ89" s="150"/>
+      <c r="BA89" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="BB89" s="78" t="s">
+        <v>784</v>
+      </c>
       <c r="BC89" s="78"/>
       <c r="BD89" s="78"/>
       <c r="BE89" s="78"/>
       <c r="BF89" s="78"/>
-      <c r="BG89" s="117"/>
-      <c r="BH89" s="118"/>
-      <c r="BI89" s="38" t="s">
+      <c r="BG89" s="78"/>
+      <c r="BH89" s="78"/>
+      <c r="BI89" s="117"/>
+      <c r="BJ89" s="118"/>
+      <c r="BK89" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="BJ89" s="145" t="s">
+      <c r="BL89" s="133" t="s">
         <v>589</v>
       </c>
-      <c r="BK89" s="38"/>
-      <c r="BL89" s="38"/>
-      <c r="BM89" s="3"/>
-      <c r="BN89" s="120"/>
-      <c r="BO89" s="35"/>
-      <c r="BP89" s="77"/>
-      <c r="BQ89" s="77"/>
-      <c r="BR89" s="119"/>
+      <c r="BM89" s="38"/>
+      <c r="BN89" s="38"/>
+      <c r="BO89" s="3"/>
+      <c r="BP89" s="120"/>
+      <c r="BQ89" s="35"/>
+      <c r="BR89" s="77"/>
+      <c r="BS89" s="77"/>
+      <c r="BT89" s="119"/>
     </row>
-    <row r="90" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B90" s="116"/>
       <c r="C90" s="116"/>
       <c r="D90" s="116"/>
@@ -18275,35 +18677,43 @@
         <v>86</v>
       </c>
       <c r="AW90" s="26" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AX90" s="78"/>
       <c r="AY90" s="78"/>
-      <c r="AZ90" s="78"/>
-      <c r="BA90" s="78"/>
-      <c r="BB90" s="78"/>
+      <c r="AZ90" s="150" t="s">
+        <v>766</v>
+      </c>
+      <c r="BA90" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="BB90" s="78" t="s">
+        <v>781</v>
+      </c>
       <c r="BC90" s="78"/>
       <c r="BD90" s="78"/>
       <c r="BE90" s="78"/>
       <c r="BF90" s="78"/>
-      <c r="BG90" s="117"/>
-      <c r="BH90" s="118"/>
-      <c r="BI90" s="38" t="s">
+      <c r="BG90" s="78"/>
+      <c r="BH90" s="78"/>
+      <c r="BI90" s="117"/>
+      <c r="BJ90" s="118"/>
+      <c r="BK90" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="BJ90" s="147" t="s">
+      <c r="BL90" s="146" t="s">
         <v>750</v>
       </c>
-      <c r="BK90" s="133"/>
-      <c r="BL90" s="133"/>
-      <c r="BM90" s="134"/>
-      <c r="BN90" s="135"/>
-      <c r="BO90" s="29"/>
-      <c r="BP90" s="77"/>
-      <c r="BQ90" s="77"/>
-      <c r="BR90" s="119"/>
+      <c r="BM90" s="133"/>
+      <c r="BN90" s="133"/>
+      <c r="BO90" s="134"/>
+      <c r="BP90" s="135"/>
+      <c r="BQ90" s="29"/>
+      <c r="BR90" s="77"/>
+      <c r="BS90" s="77"/>
+      <c r="BT90" s="119"/>
     </row>
-    <row r="91" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="116"/>
       <c r="C91" s="116"/>
       <c r="D91" s="116"/>
@@ -18343,30 +18753,36 @@
       <c r="AX91" s="78"/>
       <c r="AY91" s="78"/>
       <c r="AZ91" s="78"/>
-      <c r="BA91" s="78"/>
-      <c r="BB91" s="78"/>
+      <c r="BA91" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="BB91" s="78" t="s">
+        <v>782</v>
+      </c>
       <c r="BC91" s="78"/>
       <c r="BD91" s="78"/>
       <c r="BE91" s="78"/>
       <c r="BF91" s="78"/>
-      <c r="BG91" s="117"/>
-      <c r="BH91" s="118"/>
-      <c r="BI91" s="38" t="s">
+      <c r="BG91" s="78"/>
+      <c r="BH91" s="78"/>
+      <c r="BI91" s="117"/>
+      <c r="BJ91" s="118"/>
+      <c r="BK91" s="38" t="s">
         <v>515</v>
       </c>
-      <c r="BJ91" s="147" t="s">
+      <c r="BL91" s="146" t="s">
         <v>516</v>
       </c>
-      <c r="BK91" s="38"/>
-      <c r="BL91" s="38"/>
-      <c r="BM91" s="3"/>
-      <c r="BN91" s="29"/>
-      <c r="BO91" s="93"/>
-      <c r="BP91" s="77"/>
-      <c r="BQ91" s="77"/>
-      <c r="BR91" s="119"/>
+      <c r="BM91" s="38"/>
+      <c r="BN91" s="38"/>
+      <c r="BO91" s="3"/>
+      <c r="BP91" s="29"/>
+      <c r="BQ91" s="93"/>
+      <c r="BR91" s="77"/>
+      <c r="BS91" s="77"/>
+      <c r="BT91" s="119"/>
     </row>
-    <row r="92" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="116"/>
       <c r="C92" s="116"/>
       <c r="D92" s="116"/>
@@ -18412,24 +18828,26 @@
       <c r="BD92" s="78"/>
       <c r="BE92" s="78"/>
       <c r="BF92" s="78"/>
-      <c r="BG92" s="117"/>
-      <c r="BH92" s="118"/>
-      <c r="BI92" s="38" t="s">
+      <c r="BG92" s="78"/>
+      <c r="BH92" s="78"/>
+      <c r="BI92" s="117"/>
+      <c r="BJ92" s="118"/>
+      <c r="BK92" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="BJ92" s="38" t="s">
+      <c r="BL92" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="BK92" s="38"/>
-      <c r="BL92" s="38"/>
-      <c r="BM92" s="3"/>
-      <c r="BN92" s="29"/>
-      <c r="BO92" s="29"/>
-      <c r="BP92" s="77"/>
-      <c r="BQ92" s="77"/>
-      <c r="BR92" s="119"/>
+      <c r="BM92" s="38"/>
+      <c r="BN92" s="38"/>
+      <c r="BO92" s="3"/>
+      <c r="BP92" s="29"/>
+      <c r="BQ92" s="29"/>
+      <c r="BR92" s="77"/>
+      <c r="BS92" s="77"/>
+      <c r="BT92" s="119"/>
     </row>
-    <row r="93" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="116"/>
       <c r="C93" s="116"/>
       <c r="D93" s="116"/>
@@ -18475,20 +18893,22 @@
       <c r="BD93" s="78"/>
       <c r="BE93" s="78"/>
       <c r="BF93" s="78"/>
-      <c r="BG93" s="117"/>
-      <c r="BH93" s="118"/>
-      <c r="BI93" s="46"/>
-      <c r="BJ93" s="46"/>
+      <c r="BG93" s="78"/>
+      <c r="BH93" s="78"/>
+      <c r="BI93" s="117"/>
+      <c r="BJ93" s="118"/>
       <c r="BK93" s="46"/>
       <c r="BL93" s="46"/>
-      <c r="BM93" s="48"/>
-      <c r="BN93" s="29"/>
-      <c r="BO93" s="29"/>
-      <c r="BP93" s="77"/>
-      <c r="BQ93" s="77"/>
-      <c r="BR93" s="119"/>
+      <c r="BM93" s="46"/>
+      <c r="BN93" s="46"/>
+      <c r="BO93" s="48"/>
+      <c r="BP93" s="29"/>
+      <c r="BQ93" s="29"/>
+      <c r="BR93" s="77"/>
+      <c r="BS93" s="77"/>
+      <c r="BT93" s="119"/>
     </row>
-    <row r="94" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B94" s="116"/>
       <c r="C94" s="116"/>
       <c r="D94" s="116"/>
@@ -18534,19 +18954,21 @@
       <c r="BD94" s="78"/>
       <c r="BE94" s="78"/>
       <c r="BF94" s="78"/>
-      <c r="BG94" s="117"/>
-      <c r="BH94" s="118"/>
-      <c r="BI94" s="78"/>
-      <c r="BJ94" s="78"/>
+      <c r="BG94" s="78"/>
+      <c r="BH94" s="78"/>
+      <c r="BI94" s="117"/>
+      <c r="BJ94" s="118"/>
       <c r="BK94" s="78"/>
       <c r="BL94" s="78"/>
-      <c r="BN94" s="116"/>
-      <c r="BO94" s="116"/>
-      <c r="BP94" s="77"/>
-      <c r="BQ94" s="77"/>
-      <c r="BR94" s="119"/>
+      <c r="BM94" s="78"/>
+      <c r="BN94" s="78"/>
+      <c r="BP94" s="116"/>
+      <c r="BQ94" s="116"/>
+      <c r="BR94" s="77"/>
+      <c r="BS94" s="77"/>
+      <c r="BT94" s="119"/>
     </row>
-    <row r="95" spans="1:70" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B95" s="116"/>
       <c r="C95" s="116"/>
       <c r="D95" s="116"/>
@@ -18592,17 +19014,19 @@
       <c r="BD95" s="78"/>
       <c r="BE95" s="78"/>
       <c r="BF95" s="78"/>
-      <c r="BG95" s="117"/>
-      <c r="BH95" s="118"/>
-      <c r="BI95" s="78"/>
-      <c r="BJ95" s="78"/>
+      <c r="BG95" s="78"/>
+      <c r="BH95" s="78"/>
+      <c r="BI95" s="117"/>
+      <c r="BJ95" s="118"/>
       <c r="BK95" s="78"/>
       <c r="BL95" s="78"/>
-      <c r="BN95" s="116"/>
-      <c r="BO95" s="116"/>
-      <c r="BP95" s="77"/>
-      <c r="BQ95" s="77"/>
-      <c r="BR95" s="119"/>
+      <c r="BM95" s="78"/>
+      <c r="BN95" s="78"/>
+      <c r="BP95" s="116"/>
+      <c r="BQ95" s="116"/>
+      <c r="BR95" s="77"/>
+      <c r="BS95" s="77"/>
+      <c r="BT95" s="119"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F1E973-0B8A-47F1-9D55-190D4262700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982B276E-F3AC-493A-9580-E96D5BE2E9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2666" uniqueCount="794">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2275,9 +2275,6 @@
     <t>Firmware upgrade to read sensors in lab. GPCTD swap at sea. Back and forth on Emerald basin. Rough recovery</t>
   </si>
   <si>
-    <t>2.24.2</t>
-  </si>
-  <si>
     <t>GLI2025_SEA019_134</t>
   </si>
   <si>
@@ -2395,9 +2392,6 @@
     <t>20250417</t>
   </si>
   <si>
-    <t>first mission with wet legato</t>
-  </si>
-  <si>
     <t>old</t>
   </si>
   <si>
@@ -2411,6 +2405,36 @@
   </si>
   <si>
     <t>old for now</t>
+  </si>
+  <si>
+    <t>AFAP(1/2)</t>
+  </si>
+  <si>
+    <t>2.25.1-r</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA019_141</t>
+  </si>
+  <si>
+    <t>2.24.2-r</t>
+  </si>
+  <si>
+    <t>Sigma-T/</t>
+  </si>
+  <si>
+    <t>first mission with wet legato+coda, lots happened before deployment (following the glider falling from the LARS on the Sigma deck)</t>
+  </si>
+  <si>
+    <t>20250416</t>
+  </si>
+  <si>
+    <t>20250326</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA032_92</t>
+  </si>
+  <si>
+    <t>2.25.2-r</t>
   </si>
 </sst>
 </file>
@@ -2736,7 +2760,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3107,6 +3131,12 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3735,10 +3765,10 @@
         <v>312</v>
       </c>
       <c r="BD2" s="70" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="BE2" s="70" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="BF2" s="70" t="s">
         <v>364</v>
@@ -17516,7 +17546,7 @@
         <v>15</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="I80" s="3">
         <v>29.1</v>
@@ -17546,7 +17576,7 @@
         <v>-61.43</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="S80" s="3">
         <v>21</v>
@@ -17593,10 +17623,10 @@
         <v>20250131</v>
       </c>
       <c r="AJ80" s="37" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AK80" s="37" t="s">
-        <v>740</v>
+        <v>787</v>
       </c>
       <c r="AL80" s="35">
         <v>33</v>
@@ -17660,7 +17690,7 @@
         <v>702</v>
       </c>
       <c r="BO80" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="BP80" s="3" t="s">
         <v>670</v>
@@ -17672,10 +17702,10 @@
         <v>197</v>
       </c>
       <c r="BS80" s="37" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="BT80" s="43" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="81" spans="1:72" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -17701,7 +17731,7 @@
         <v>15</v>
       </c>
       <c r="H81" s="37" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="I81" s="3">
         <v>28.9</v>
@@ -17780,10 +17810,10 @@
         <v>20250218</v>
       </c>
       <c r="AJ81" s="37" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AK81" s="37" t="s">
-        <v>740</v>
+        <v>787</v>
       </c>
       <c r="AL81" s="35">
         <v>30</v>
@@ -17792,7 +17822,7 @@
         <v>76</v>
       </c>
       <c r="AN81" s="38" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AO81" s="38" t="s">
         <v>212</v>
@@ -17804,7 +17834,7 @@
         <v>78</v>
       </c>
       <c r="AR81" s="38" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AS81" s="38"/>
       <c r="AT81" s="38"/>
@@ -17824,7 +17854,7 @@
         <v>451</v>
       </c>
       <c r="BB81" s="38" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="BC81" s="38" t="s">
         <v>420</v>
@@ -17847,7 +17877,7 @@
         <v>588</v>
       </c>
       <c r="BM81" s="38" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="BN81" s="3">
         <v>1540746</v>
@@ -17860,13 +17890,13 @@
         <v>205</v>
       </c>
       <c r="BR81" s="37" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="BS81" s="37" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="BT81" s="43" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="82" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -17892,7 +17922,7 @@
         <v>15</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="I82" s="2">
         <v>29.1</v>
@@ -17969,10 +17999,10 @@
         <v>20250305</v>
       </c>
       <c r="AJ82" s="18" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AK82" s="18" t="s">
-        <v>740</v>
+        <v>787</v>
       </c>
       <c r="AL82" s="14">
         <v>32</v>
@@ -17981,7 +18011,7 @@
         <v>75</v>
       </c>
       <c r="AN82" s="22" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AO82" s="22" t="s">
         <v>212</v>
@@ -17993,7 +18023,7 @@
         <v>72</v>
       </c>
       <c r="AR82" s="22" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AS82" s="22"/>
       <c r="AT82" s="22"/>
@@ -18030,13 +18060,13 @@
         <v>516</v>
       </c>
       <c r="BM82" s="22" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="BN82" s="2">
         <v>1272212</v>
       </c>
       <c r="BO82" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="BP82" s="2" t="s">
         <v>670</v>
@@ -18045,24 +18075,26 @@
         <v>205</v>
       </c>
       <c r="BR82" s="18" t="s">
+        <v>772</v>
+      </c>
+      <c r="BS82" s="18" t="s">
+        <v>768</v>
+      </c>
+      <c r="BT82" s="21" t="s">
         <v>773</v>
-      </c>
-      <c r="BS82" s="18" t="s">
-        <v>769</v>
-      </c>
-      <c r="BT82" s="21" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="83" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="124"/>
-      <c r="B83" s="14"/>
+      <c r="B83" s="14">
+        <v>20250515</v>
+      </c>
       <c r="C83" s="14"/>
       <c r="D83" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="14">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F83" s="14">
         <v>4800925</v>
@@ -18071,13 +18103,21 @@
         <v>15</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>741</v>
-      </c>
-      <c r="I83" s="2"/>
+        <v>786</v>
+      </c>
+      <c r="I83" s="2">
+        <v>29.2</v>
+      </c>
       <c r="J83" s="2"/>
-      <c r="K83" s="14"/>
-      <c r="L83" s="14"/>
-      <c r="M83" s="100"/>
+      <c r="K83" s="14">
+        <v>44.391300000000001</v>
+      </c>
+      <c r="L83" s="14">
+        <v>-63.341900000000003</v>
+      </c>
+      <c r="M83" s="100">
+        <v>0.59097222222222223</v>
+      </c>
       <c r="N83" s="18"/>
       <c r="O83" s="18"/>
       <c r="P83" s="18"/>
@@ -18102,7 +18142,7 @@
       <c r="AA83" s="18"/>
       <c r="AB83" s="18"/>
       <c r="AC83" s="18" t="s">
-        <v>183</v>
+        <v>784</v>
       </c>
       <c r="AD83" s="18"/>
       <c r="AE83" s="2"/>
@@ -18111,9 +18151,15 @@
       <c r="AH83" s="2">
         <v>1024.3</v>
       </c>
-      <c r="AI83" s="18"/>
-      <c r="AJ83" s="18"/>
-      <c r="AK83" s="18"/>
+      <c r="AI83" s="18">
+        <v>20250514</v>
+      </c>
+      <c r="AJ83" s="18" t="s">
+        <v>753</v>
+      </c>
+      <c r="AK83" s="18" t="s">
+        <v>785</v>
+      </c>
       <c r="AL83" s="14">
         <v>33</v>
       </c>
@@ -18138,19 +18184,19 @@
       <c r="AY83" s="22"/>
       <c r="AZ83" s="22"/>
       <c r="BA83" s="22" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="BB83" s="22" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="BC83" s="22" t="s">
         <v>420</v>
       </c>
       <c r="BD83" s="22" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="BE83" s="22" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="BF83" s="22"/>
       <c r="BG83" s="22"/>
@@ -18161,16 +18207,16 @@
       <c r="BJ83" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="BK83" s="38" t="s">
+      <c r="BK83" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="BL83" s="38" t="s">
+      <c r="BL83" s="22" t="s">
         <v>588</v>
       </c>
       <c r="BM83" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="BN83" s="38" t="s">
+      <c r="BN83" s="22" t="s">
         <v>702</v>
       </c>
       <c r="BO83" s="2"/>
@@ -18180,10 +18226,12 @@
       <c r="BQ83" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BR83" s="18"/>
+      <c r="BR83" s="18" t="s">
+        <v>788</v>
+      </c>
       <c r="BS83" s="18"/>
       <c r="BT83" s="21" t="s">
-        <v>780</v>
+        <v>789</v>
       </c>
     </row>
     <row r="84" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -18193,10 +18241,18 @@
       <c r="D84" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="18"/>
+      <c r="E84" s="14">
+        <v>92</v>
+      </c>
+      <c r="F84" s="14">
+        <v>4800937</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="18" t="s">
+        <v>792</v>
+      </c>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="14"/>
@@ -18206,27 +18262,45 @@
       <c r="O84" s="18"/>
       <c r="P84" s="18"/>
       <c r="Q84" s="18"/>
-      <c r="R84" s="2"/>
+      <c r="R84" s="2" t="s">
+        <v>444</v>
+      </c>
       <c r="S84" s="2"/>
       <c r="T84" s="2"/>
       <c r="U84" s="2"/>
       <c r="V84" s="2"/>
-      <c r="W84" s="18"/>
-      <c r="X84" s="18"/>
+      <c r="W84" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X84" s="18">
+        <v>1</v>
+      </c>
       <c r="Y84" s="18"/>
-      <c r="Z84" s="18"/>
+      <c r="Z84" s="18" t="s">
+        <v>183</v>
+      </c>
       <c r="AA84" s="18"/>
       <c r="AB84" s="18"/>
-      <c r="AC84" s="18"/>
+      <c r="AC84" s="18" t="s">
+        <v>784</v>
+      </c>
       <c r="AD84" s="18"/>
       <c r="AE84" s="2"/>
       <c r="AF84" s="2"/>
       <c r="AG84" s="2"/>
-      <c r="AH84" s="2"/>
+      <c r="AH84" s="2">
+        <v>1023.75</v>
+      </c>
       <c r="AI84" s="18"/>
-      <c r="AJ84" s="18"/>
-      <c r="AK84" s="18"/>
-      <c r="AL84" s="14"/>
+      <c r="AJ84" s="18" t="s">
+        <v>753</v>
+      </c>
+      <c r="AK84" s="18" t="s">
+        <v>793</v>
+      </c>
+      <c r="AL84" s="14">
+        <v>32</v>
+      </c>
       <c r="AM84" s="20"/>
       <c r="AN84" s="22"/>
       <c r="AO84" s="22"/>
@@ -18236,32 +18310,56 @@
       <c r="AS84" s="22"/>
       <c r="AT84" s="22"/>
       <c r="AU84" s="22"/>
-      <c r="AV84" s="10"/>
-      <c r="AW84" s="16"/>
-      <c r="AX84" s="22"/>
+      <c r="AV84" s="151" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW84" s="152">
+        <v>42711</v>
+      </c>
+      <c r="AX84" s="79" t="s">
+        <v>461</v>
+      </c>
       <c r="AY84" s="22"/>
       <c r="AZ84" s="22"/>
       <c r="BA84" s="22" t="s">
-        <v>764</v>
-      </c>
-      <c r="BB84" s="22"/>
-      <c r="BC84" s="22"/>
+        <v>763</v>
+      </c>
+      <c r="BB84" s="22" t="s">
+        <v>790</v>
+      </c>
+      <c r="BC84" s="22" t="s">
+        <v>420</v>
+      </c>
       <c r="BD84" s="22" t="s">
-        <v>775</v>
-      </c>
-      <c r="BE84" s="22"/>
+        <v>774</v>
+      </c>
+      <c r="BE84" s="22" t="s">
+        <v>791</v>
+      </c>
       <c r="BF84" s="22"/>
       <c r="BG84" s="22"/>
       <c r="BH84" s="22"/>
-      <c r="BI84" s="20"/>
-      <c r="BJ84" s="147"/>
-      <c r="BK84" s="22"/>
-      <c r="BL84" s="22"/>
+      <c r="BI84" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ84" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK84" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="BL84" s="22" t="s">
+        <v>516</v>
+      </c>
       <c r="BM84" s="79"/>
       <c r="BN84" s="79"/>
       <c r="BO84" s="2"/>
-      <c r="BP84" s="148"/>
-      <c r="BQ84" s="2"/>
+      <c r="BP84" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="BQ84" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="BR84" s="18"/>
       <c r="BS84" s="18"/>
       <c r="BT84" s="21"/>
@@ -18359,10 +18457,22 @@
       <c r="P86" s="37"/>
       <c r="Q86" s="37"/>
       <c r="R86" s="3"/>
-      <c r="S86" s="3"/>
-      <c r="T86" s="3"/>
-      <c r="U86" s="3"/>
-      <c r="V86" s="3"/>
+      <c r="S86" s="3">
+        <f t="shared" ref="S86:V86" si="0">SUM(S73:S81)</f>
+        <v>186</v>
+      </c>
+      <c r="T86" s="3">
+        <f>SUM(T73:T81)</f>
+        <v>4937</v>
+      </c>
+      <c r="U86" s="3">
+        <f>SUM(U73:U81)-U75</f>
+        <v>7441</v>
+      </c>
+      <c r="V86" s="3">
+        <f t="shared" si="0"/>
+        <v>15106</v>
+      </c>
       <c r="W86" s="37"/>
       <c r="X86" s="37"/>
       <c r="Y86" s="37"/>
@@ -18405,7 +18515,7 @@
       <c r="BJ86" s="139"/>
       <c r="BK86" s="38"/>
       <c r="BL86" s="38" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="BM86" s="38"/>
       <c r="BN86" s="38"/>
@@ -18483,7 +18593,7 @@
         <v>98</v>
       </c>
       <c r="BL87" s="146" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="BM87" s="38"/>
       <c r="BN87" s="38"/>
@@ -18534,13 +18644,13 @@
       <c r="AX88" s="78"/>
       <c r="AY88" s="78"/>
       <c r="AZ88" s="150" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="BA88" s="6" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="BB88" s="78" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="BC88" s="78"/>
       <c r="BD88" s="78"/>
@@ -18604,16 +18714,16 @@
         <v>74</v>
       </c>
       <c r="AW89" s="26" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AX89" s="78"/>
       <c r="AY89" s="78"/>
       <c r="AZ89" s="150"/>
       <c r="BA89" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="BB89" s="78" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="BC89" s="78"/>
       <c r="BD89" s="78"/>
@@ -18677,18 +18787,18 @@
         <v>86</v>
       </c>
       <c r="AW90" s="26" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AX90" s="78"/>
       <c r="AY90" s="78"/>
       <c r="AZ90" s="150" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="BA90" s="5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="BB90" s="78" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="BC90" s="78"/>
       <c r="BD90" s="78"/>
@@ -18702,7 +18812,7 @@
         <v>246</v>
       </c>
       <c r="BL90" s="146" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="BM90" s="133"/>
       <c r="BN90" s="133"/>
@@ -18754,10 +18864,10 @@
       <c r="AY91" s="78"/>
       <c r="AZ91" s="78"/>
       <c r="BA91" s="5" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="BB91" s="78" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="BC91" s="78"/>
       <c r="BD91" s="78"/>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982B276E-F3AC-493A-9580-E96D5BE2E9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A51252B-FE09-45D3-8174-A2146AC8BA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2666" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2697" uniqueCount="800">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2293,9 +2293,6 @@
     <t>20240916</t>
   </si>
   <si>
-    <t>feb 2025</t>
-  </si>
-  <si>
     <t>20241217</t>
   </si>
   <si>
@@ -2419,12 +2416,6 @@
     <t>2.24.2-r</t>
   </si>
   <si>
-    <t>Sigma-T/</t>
-  </si>
-  <si>
-    <t>first mission with wet legato+coda, lots happened before deployment (following the glider falling from the LARS on the Sigma deck)</t>
-  </si>
-  <si>
     <t>20250416</t>
   </si>
   <si>
@@ -2435,6 +2426,33 @@
   </si>
   <si>
     <t>2.25.2-r</t>
+  </si>
+  <si>
+    <t>CDOM negative values</t>
+  </si>
+  <si>
+    <t>44.38.71</t>
+  </si>
+  <si>
+    <t>GL1-TRI</t>
+  </si>
+  <si>
+    <t>Sigma-T(zodiak)/</t>
+  </si>
+  <si>
+    <t>Sigma-T/Sigma-T(zodiak)</t>
+  </si>
+  <si>
+    <t>first mission with wet legato+coda, lots happened before deployment (following the glider falling from the LARS on the Sigma deck), went through a warm core ring at the very end of the line, possible internal waves as well on the shelf break, leaking ballader at recovery</t>
+  </si>
+  <si>
+    <t>no DO data, Questionnable CDOM data (negative range)</t>
+  </si>
+  <si>
+    <t>CDOM negative values, no CODA data because of config file duplicate, recovered after 3 days to fix it</t>
+  </si>
+  <si>
+    <t>Questionnable CDOM data (negative range)</t>
   </si>
 </sst>
 </file>
@@ -2760,7 +2778,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3096,9 +3114,6 @@
     <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3123,20 +3138,20 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3467,7 +3482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CY95"/>
+  <dimension ref="A1:CY98"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.1796875" customWidth="1"/>
@@ -3765,10 +3780,10 @@
         <v>312</v>
       </c>
       <c r="BD2" s="70" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="BE2" s="70" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="BF2" s="70" t="s">
         <v>364</v>
@@ -5763,7 +5778,7 @@
       <c r="BR13" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="BS13" s="143" t="s">
+      <c r="BS13" s="142" t="s">
         <v>715</v>
       </c>
       <c r="BT13" s="52" t="s">
@@ -6121,7 +6136,7 @@
       <c r="BR15" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BS15" s="142" t="s">
+      <c r="BS15" s="141" t="s">
         <v>716</v>
       </c>
       <c r="BT15" s="43" t="s">
@@ -7006,7 +7021,7 @@
       <c r="BR20" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BS20" s="141" t="s">
+      <c r="BS20" s="140" t="s">
         <v>693</v>
       </c>
       <c r="BT20" s="21" t="s">
@@ -7543,7 +7558,7 @@
       <c r="BR23" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="BS23" s="141" t="s">
+      <c r="BS23" s="140" t="s">
         <v>721</v>
       </c>
       <c r="BT23" s="21" t="s">
@@ -7720,7 +7735,7 @@
       <c r="BR24" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="BS24" s="140" t="s">
+      <c r="BS24" s="139" t="s">
         <v>719</v>
       </c>
       <c r="BT24" s="50" t="s">
@@ -7896,7 +7911,7 @@
       <c r="BR25" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="BS25" s="141" t="s">
+      <c r="BS25" s="140" t="s">
         <v>736</v>
       </c>
       <c r="BT25" s="21" t="s">
@@ -8252,7 +8267,7 @@
       <c r="BR27" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="BS27" s="140" t="s">
+      <c r="BS27" s="139" t="s">
         <v>719</v>
       </c>
       <c r="BT27" s="50" t="s">
@@ -10717,7 +10732,7 @@
       <c r="BR42" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="BS42" s="142" t="s">
+      <c r="BS42" s="141" t="s">
         <v>725</v>
       </c>
       <c r="BT42" s="43" t="s">
@@ -17371,10 +17386,10 @@
       <c r="J79" s="3">
         <v>24</v>
       </c>
-      <c r="K79" s="144">
+      <c r="K79" s="143">
         <v>44.273600000000002</v>
       </c>
-      <c r="L79" s="144">
+      <c r="L79" s="143">
         <v>-63.318199999999997</v>
       </c>
       <c r="M79" s="138">
@@ -17576,7 +17591,7 @@
         <v>-61.43</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="S80" s="3">
         <v>21</v>
@@ -17626,7 +17641,7 @@
         <v>741</v>
       </c>
       <c r="AK80" s="37" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AL80" s="35">
         <v>33</v>
@@ -17702,14 +17717,14 @@
         <v>197</v>
       </c>
       <c r="BS80" s="37" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="BT80" s="43" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="81" spans="1:72" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="149">
+      <c r="A81" s="147">
         <v>9</v>
       </c>
       <c r="B81" s="35">
@@ -17810,10 +17825,10 @@
         <v>20250218</v>
       </c>
       <c r="AJ81" s="37" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AK81" s="37" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AL81" s="35">
         <v>30</v>
@@ -17822,7 +17837,7 @@
         <v>76</v>
       </c>
       <c r="AN81" s="38" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AO81" s="38" t="s">
         <v>212</v>
@@ -17834,7 +17849,7 @@
         <v>78</v>
       </c>
       <c r="AR81" s="38" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AS81" s="38"/>
       <c r="AT81" s="38"/>
@@ -17890,13 +17905,13 @@
         <v>205</v>
       </c>
       <c r="BR81" s="37" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="BS81" s="37" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="BT81" s="43" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="82" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -17922,7 +17937,7 @@
         <v>15</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="I82" s="2">
         <v>29.1</v>
@@ -17999,10 +18014,10 @@
         <v>20250305</v>
       </c>
       <c r="AJ82" s="18" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AK82" s="18" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AL82" s="14">
         <v>32</v>
@@ -18011,7 +18026,7 @@
         <v>75</v>
       </c>
       <c r="AN82" s="22" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AO82" s="22" t="s">
         <v>212</v>
@@ -18023,7 +18038,7 @@
         <v>72</v>
       </c>
       <c r="AR82" s="22" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AS82" s="22"/>
       <c r="AT82" s="22"/>
@@ -18060,13 +18075,13 @@
         <v>516</v>
       </c>
       <c r="BM82" s="22" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="BN82" s="2">
         <v>1272212</v>
       </c>
       <c r="BO82" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="BP82" s="2" t="s">
         <v>670</v>
@@ -18075,21 +18090,25 @@
         <v>205</v>
       </c>
       <c r="BR82" s="18" t="s">
+        <v>771</v>
+      </c>
+      <c r="BS82" s="18" t="s">
+        <v>767</v>
+      </c>
+      <c r="BT82" s="21" t="s">
         <v>772</v>
-      </c>
-      <c r="BS82" s="18" t="s">
-        <v>768</v>
-      </c>
-      <c r="BT82" s="21" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="83" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="124"/>
+      <c r="A83" s="124">
+        <v>2</v>
+      </c>
       <c r="B83" s="14">
         <v>20250515</v>
       </c>
-      <c r="C83" s="14"/>
+      <c r="C83" s="14">
+        <v>20250606</v>
+      </c>
       <c r="D83" s="14" t="s">
         <v>13</v>
       </c>
@@ -18103,7 +18122,7 @@
         <v>15</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="I83" s="2">
         <v>29.2</v>
@@ -18142,7 +18161,7 @@
       <c r="AA83" s="18"/>
       <c r="AB83" s="18"/>
       <c r="AC83" s="18" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AD83" s="18"/>
       <c r="AE83" s="2"/>
@@ -18155,10 +18174,10 @@
         <v>20250514</v>
       </c>
       <c r="AJ83" s="18" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AK83" s="18" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AL83" s="14">
         <v>33</v>
@@ -18184,19 +18203,19 @@
       <c r="AY83" s="22"/>
       <c r="AZ83" s="22"/>
       <c r="BA83" s="22" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="BB83" s="22" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="BC83" s="22" t="s">
         <v>420</v>
       </c>
       <c r="BD83" s="22" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="BE83" s="22" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="BF83" s="22"/>
       <c r="BG83" s="22"/>
@@ -18227,17 +18246,23 @@
         <v>205</v>
       </c>
       <c r="BR83" s="18" t="s">
-        <v>788</v>
+        <v>197</v>
       </c>
       <c r="BS83" s="18"/>
       <c r="BT83" s="21" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="84" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="124"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
+      <c r="A84" s="124" t="s">
+        <v>189</v>
+      </c>
+      <c r="B84" s="14">
+        <v>20250606</v>
+      </c>
+      <c r="C84" s="14">
+        <v>20250609</v>
+      </c>
       <c r="D84" s="14" t="s">
         <v>53</v>
       </c>
@@ -18251,24 +18276,51 @@
         <v>15</v>
       </c>
       <c r="H84" s="18" t="s">
+        <v>789</v>
+      </c>
+      <c r="I84" s="2">
+        <v>29.3</v>
+      </c>
+      <c r="J84" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="K84" s="14" t="s">
         <v>792</v>
       </c>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="14"/>
-      <c r="L84" s="14"/>
-      <c r="M84" s="100"/>
-      <c r="N84" s="18"/>
-      <c r="O84" s="18"/>
-      <c r="P84" s="18"/>
-      <c r="Q84" s="18"/>
+      <c r="L84" s="14">
+        <v>-63.369900000000001</v>
+      </c>
+      <c r="M84" s="100">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="N84" s="18">
+        <v>44.07</v>
+      </c>
+      <c r="O84" s="18">
+        <v>-63.37</v>
+      </c>
+      <c r="P84" s="18">
+        <v>44.43</v>
+      </c>
+      <c r="Q84" s="18">
+        <v>-63.13</v>
+      </c>
       <c r="R84" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="S84" s="2"/>
-      <c r="T84" s="2"/>
-      <c r="U84" s="2"/>
-      <c r="V84" s="2"/>
+        <v>793</v>
+      </c>
+      <c r="S84" s="2">
+        <v>3</v>
+      </c>
+      <c r="T84" s="2">
+        <v>83</v>
+      </c>
+      <c r="U84" s="2">
+        <v>136</v>
+      </c>
+      <c r="V84" s="2">
+        <f>U84*2</f>
+        <v>272</v>
+      </c>
       <c r="W84" s="18" t="s">
         <v>36</v>
       </c>
@@ -18282,21 +18334,29 @@
       <c r="AA84" s="18"/>
       <c r="AB84" s="18"/>
       <c r="AC84" s="18" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AD84" s="18"/>
-      <c r="AE84" s="2"/>
-      <c r="AF84" s="2"/>
-      <c r="AG84" s="2"/>
+      <c r="AE84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="2">
+        <v>0</v>
+      </c>
       <c r="AH84" s="2">
         <v>1023.75</v>
       </c>
-      <c r="AI84" s="18"/>
+      <c r="AI84" s="140">
+        <v>2025</v>
+      </c>
       <c r="AJ84" s="18" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AK84" s="18" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="AL84" s="14">
         <v>32</v>
@@ -18310,31 +18370,31 @@
       <c r="AS84" s="22"/>
       <c r="AT84" s="22"/>
       <c r="AU84" s="22"/>
-      <c r="AV84" s="151" t="s">
+      <c r="AV84" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="AW84" s="152">
+      <c r="AW84" s="16">
         <v>42711</v>
       </c>
-      <c r="AX84" s="79" t="s">
+      <c r="AX84" s="22" t="s">
         <v>461</v>
       </c>
       <c r="AY84" s="22"/>
       <c r="AZ84" s="22"/>
       <c r="BA84" s="22" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="BB84" s="22" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="BC84" s="22" t="s">
         <v>420</v>
       </c>
       <c r="BD84" s="22" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="BE84" s="22" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="BF84" s="22"/>
       <c r="BG84" s="22"/>
@@ -18351,8 +18411,12 @@
       <c r="BL84" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="BM84" s="79"/>
-      <c r="BN84" s="79"/>
+      <c r="BM84" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="BN84" s="151">
+        <v>1272212</v>
+      </c>
       <c r="BO84" s="2"/>
       <c r="BP84" s="2" t="s">
         <v>670</v>
@@ -18360,49 +18424,97 @@
       <c r="BQ84" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BR84" s="18"/>
-      <c r="BS84" s="18"/>
-      <c r="BT84" s="21"/>
+      <c r="BR84" s="18" t="s">
+        <v>795</v>
+      </c>
+      <c r="BS84" s="18" t="s">
+        <v>797</v>
+      </c>
+      <c r="BT84" s="21" t="s">
+        <v>798</v>
+      </c>
     </row>
     <row r="85" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="124"/>
-      <c r="B85" s="14"/>
+      <c r="A85" s="124">
+        <v>3</v>
+      </c>
+      <c r="B85" s="14">
+        <v>20250609</v>
+      </c>
       <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="18"/>
-      <c r="I85" s="2"/>
+      <c r="D85" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E85" s="14">
+        <v>93</v>
+      </c>
+      <c r="F85" s="14">
+        <v>4800937</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="18" t="s">
+        <v>789</v>
+      </c>
+      <c r="I85" s="2">
+        <v>28.5</v>
+      </c>
       <c r="J85" s="2"/>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="100"/>
+      <c r="K85" s="14">
+        <v>44.4223</v>
+      </c>
+      <c r="L85" s="14">
+        <v>-63.3795</v>
+      </c>
+      <c r="M85" s="100">
+        <v>0.6972222222222223</v>
+      </c>
       <c r="N85" s="18"/>
       <c r="O85" s="18"/>
       <c r="P85" s="18"/>
       <c r="Q85" s="18"/>
-      <c r="R85" s="2"/>
+      <c r="R85" s="2" t="s">
+        <v>444</v>
+      </c>
       <c r="S85" s="2"/>
       <c r="T85" s="2"/>
       <c r="U85" s="2"/>
       <c r="V85" s="2"/>
-      <c r="W85" s="18"/>
-      <c r="X85" s="18"/>
+      <c r="W85" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X85" s="18">
+        <v>1</v>
+      </c>
       <c r="Y85" s="18"/>
-      <c r="Z85" s="18"/>
+      <c r="Z85" s="18" t="s">
+        <v>183</v>
+      </c>
       <c r="AA85" s="18"/>
       <c r="AB85" s="18"/>
-      <c r="AC85" s="18"/>
+      <c r="AC85" s="18" t="s">
+        <v>783</v>
+      </c>
       <c r="AD85" s="18"/>
       <c r="AE85" s="2"/>
       <c r="AF85" s="2"/>
       <c r="AG85" s="2"/>
-      <c r="AH85" s="2"/>
-      <c r="AI85" s="18"/>
-      <c r="AJ85" s="18"/>
-      <c r="AK85" s="18"/>
-      <c r="AL85" s="14"/>
+      <c r="AH85" s="2">
+        <v>1023.75</v>
+      </c>
+      <c r="AI85" s="140">
+        <v>2025</v>
+      </c>
+      <c r="AJ85" s="18" t="s">
+        <v>752</v>
+      </c>
+      <c r="AK85" s="18" t="s">
+        <v>790</v>
+      </c>
+      <c r="AL85" s="14">
+        <v>32</v>
+      </c>
       <c r="AM85" s="20"/>
       <c r="AN85" s="22"/>
       <c r="AO85" s="22"/>
@@ -18412,416 +18524,443 @@
       <c r="AS85" s="22"/>
       <c r="AT85" s="22"/>
       <c r="AU85" s="22"/>
-      <c r="AV85" s="10"/>
-      <c r="AW85" s="16"/>
-      <c r="AX85" s="22"/>
+      <c r="AV85" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW85" s="16">
+        <v>42711</v>
+      </c>
+      <c r="AX85" s="22" t="s">
+        <v>461</v>
+      </c>
       <c r="AY85" s="22"/>
       <c r="AZ85" s="22"/>
-      <c r="BA85" s="22"/>
-      <c r="BB85" s="22"/>
-      <c r="BC85" s="22"/>
-      <c r="BD85" s="22"/>
-      <c r="BE85" s="22"/>
+      <c r="BA85" s="22" t="s">
+        <v>762</v>
+      </c>
+      <c r="BB85" s="22" t="s">
+        <v>787</v>
+      </c>
+      <c r="BC85" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="BD85" s="22" t="s">
+        <v>773</v>
+      </c>
+      <c r="BE85" s="22" t="s">
+        <v>788</v>
+      </c>
       <c r="BF85" s="22"/>
       <c r="BG85" s="22"/>
       <c r="BH85" s="22"/>
-      <c r="BI85" s="20"/>
-      <c r="BJ85" s="147"/>
-      <c r="BK85" s="22"/>
-      <c r="BL85" s="22"/>
-      <c r="BM85" s="79"/>
-      <c r="BN85" s="79"/>
+      <c r="BI85" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ85" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK85" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="BL85" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="BM85" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="BN85" s="151">
+        <v>1272212</v>
+      </c>
       <c r="BO85" s="2"/>
-      <c r="BP85" s="148"/>
-      <c r="BQ85" s="2"/>
-      <c r="BR85" s="18"/>
-      <c r="BS85" s="18"/>
-      <c r="BT85" s="21"/>
+      <c r="BP85" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="BQ85" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="BR85" s="18" t="s">
+        <v>794</v>
+      </c>
+      <c r="BS85" s="18" t="s">
+        <v>799</v>
+      </c>
+      <c r="BT85" s="21" t="s">
+        <v>791</v>
+      </c>
     </row>
-    <row r="86" spans="1:72" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="137"/>
-      <c r="B86" s="35"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="35"/>
-      <c r="G86" s="35"/>
-      <c r="H86" s="37"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="35"/>
-      <c r="L86" s="35"/>
-      <c r="M86" s="138"/>
-      <c r="N86" s="37"/>
-      <c r="O86" s="37"/>
-      <c r="P86" s="37"/>
-      <c r="Q86" s="37"/>
-      <c r="R86" s="3"/>
-      <c r="S86" s="3">
-        <f t="shared" ref="S86:V86" si="0">SUM(S73:S81)</f>
-        <v>186</v>
-      </c>
-      <c r="T86" s="3">
-        <f>SUM(T73:T81)</f>
-        <v>4937</v>
-      </c>
-      <c r="U86" s="3">
-        <f>SUM(U73:U81)-U75</f>
-        <v>7441</v>
-      </c>
-      <c r="V86" s="3">
-        <f t="shared" si="0"/>
-        <v>15106</v>
-      </c>
-      <c r="W86" s="37"/>
-      <c r="X86" s="37"/>
-      <c r="Y86" s="37"/>
-      <c r="Z86" s="37"/>
-      <c r="AA86" s="37"/>
-      <c r="AB86" s="37"/>
-      <c r="AC86" s="37"/>
-      <c r="AD86" s="37"/>
-      <c r="AE86" s="3"/>
-      <c r="AF86" s="3"/>
-      <c r="AG86" s="3"/>
-      <c r="AH86" s="3"/>
-      <c r="AI86" s="37"/>
-      <c r="AJ86" s="37"/>
-      <c r="AK86" s="37"/>
-      <c r="AL86" s="35"/>
-      <c r="AM86" s="34"/>
-      <c r="AN86" s="38"/>
-      <c r="AO86" s="38"/>
-      <c r="AP86" s="34"/>
-      <c r="AQ86" s="34"/>
-      <c r="AR86" s="38"/>
-      <c r="AS86" s="38"/>
-      <c r="AT86" s="38"/>
-      <c r="AU86" s="38"/>
-      <c r="AV86" s="41"/>
-      <c r="AW86" s="39"/>
-      <c r="AX86" s="38"/>
-      <c r="AY86" s="38"/>
-      <c r="AZ86" s="38"/>
-      <c r="BA86" s="38"/>
-      <c r="BB86" s="38"/>
-      <c r="BC86" s="38"/>
-      <c r="BD86" s="38"/>
-      <c r="BE86" s="38"/>
-      <c r="BF86" s="38"/>
-      <c r="BG86" s="38"/>
-      <c r="BH86" s="38"/>
-      <c r="BI86" s="34"/>
-      <c r="BJ86" s="139"/>
-      <c r="BK86" s="38"/>
-      <c r="BL86" s="38" t="s">
-        <v>746</v>
-      </c>
-      <c r="BM86" s="38"/>
-      <c r="BN86" s="38"/>
-      <c r="BO86" s="3"/>
-      <c r="BP86" s="120"/>
-      <c r="BQ86" s="35"/>
-      <c r="BR86" s="37"/>
-      <c r="BS86" s="37"/>
-      <c r="BT86" s="43"/>
+    <row r="86" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="124"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="14"/>
+      <c r="L86" s="14"/>
+      <c r="M86" s="100"/>
+      <c r="N86" s="18"/>
+      <c r="O86" s="18"/>
+      <c r="P86" s="18"/>
+      <c r="Q86" s="18"/>
+      <c r="R86" s="2"/>
+      <c r="S86" s="2"/>
+      <c r="T86" s="2"/>
+      <c r="U86" s="2"/>
+      <c r="V86" s="2"/>
+      <c r="W86" s="18"/>
+      <c r="X86" s="18"/>
+      <c r="Y86" s="18"/>
+      <c r="Z86" s="18"/>
+      <c r="AA86" s="18"/>
+      <c r="AB86" s="18"/>
+      <c r="AC86" s="18"/>
+      <c r="AD86" s="18"/>
+      <c r="AE86" s="2"/>
+      <c r="AF86" s="2"/>
+      <c r="AG86" s="2"/>
+      <c r="AH86" s="2"/>
+      <c r="AI86" s="18"/>
+      <c r="AJ86" s="18"/>
+      <c r="AK86" s="18"/>
+      <c r="AL86" s="14"/>
+      <c r="AM86" s="20"/>
+      <c r="AN86" s="22"/>
+      <c r="AO86" s="22"/>
+      <c r="AP86" s="20"/>
+      <c r="AQ86" s="20"/>
+      <c r="AR86" s="22"/>
+      <c r="AS86" s="22"/>
+      <c r="AT86" s="22"/>
+      <c r="AU86" s="22"/>
+      <c r="AV86" s="10"/>
+      <c r="AW86" s="16"/>
+      <c r="AX86" s="22"/>
+      <c r="AY86" s="22"/>
+      <c r="AZ86" s="22"/>
+      <c r="BA86" s="22"/>
+      <c r="BB86" s="22"/>
+      <c r="BC86" s="22"/>
+      <c r="BD86" s="22"/>
+      <c r="BE86" s="22"/>
+      <c r="BF86" s="22"/>
+      <c r="BG86" s="22"/>
+      <c r="BH86" s="22"/>
+      <c r="BI86" s="20"/>
+      <c r="BJ86" s="146"/>
+      <c r="BK86" s="22"/>
+      <c r="BL86" s="22"/>
+      <c r="BM86" s="22"/>
+      <c r="BN86" s="22"/>
+      <c r="BO86" s="2"/>
+      <c r="BP86" s="149"/>
+      <c r="BQ86" s="14"/>
+      <c r="BR86" s="18"/>
+      <c r="BS86" s="18"/>
+      <c r="BT86" s="21"/>
     </row>
-    <row r="87" spans="1:72" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="137"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="3"/>
-      <c r="K87" s="35"/>
-      <c r="L87" s="35"/>
-      <c r="M87" s="3"/>
-      <c r="N87" s="37"/>
-      <c r="O87" s="37"/>
-      <c r="P87" s="37"/>
-      <c r="Q87" s="37"/>
-      <c r="R87" s="3"/>
-      <c r="S87" s="3"/>
-      <c r="T87" s="3"/>
-      <c r="U87" s="3"/>
-      <c r="V87" s="3"/>
-      <c r="W87" s="37"/>
-      <c r="X87" s="37"/>
-      <c r="Y87" s="37"/>
-      <c r="Z87" s="37"/>
-      <c r="AA87" s="37"/>
-      <c r="AB87" s="37"/>
-      <c r="AC87" s="37"/>
-      <c r="AD87" s="37"/>
-      <c r="AE87" s="3"/>
-      <c r="AF87" s="3"/>
-      <c r="AG87" s="3"/>
-      <c r="AH87" s="3"/>
-      <c r="AI87" s="37"/>
-      <c r="AJ87" s="37"/>
-      <c r="AK87" s="37"/>
-      <c r="AL87" s="35"/>
-      <c r="AM87" s="34"/>
-      <c r="AN87" s="38"/>
-      <c r="AO87" s="38"/>
-      <c r="AP87" s="34"/>
-      <c r="AQ87" s="34"/>
-      <c r="AR87" s="38"/>
-      <c r="AS87" s="38"/>
-      <c r="AT87" s="38"/>
-      <c r="AU87" s="38"/>
-      <c r="AV87" s="34"/>
-      <c r="AW87" s="38"/>
-      <c r="AX87" s="38"/>
-      <c r="AY87" s="38"/>
-      <c r="AZ87" s="38"/>
-      <c r="BA87" s="38"/>
-      <c r="BB87" s="38"/>
-      <c r="BC87" s="38"/>
-      <c r="BD87" s="38"/>
-      <c r="BE87" s="38"/>
-      <c r="BF87" s="38"/>
-      <c r="BG87" s="38"/>
-      <c r="BH87" s="38"/>
-      <c r="BI87" s="34"/>
-      <c r="BJ87" s="139"/>
-      <c r="BK87" s="38" t="s">
+    <row r="87" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="124"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="18"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="14"/>
+      <c r="L87" s="14"/>
+      <c r="M87" s="100"/>
+      <c r="N87" s="18"/>
+      <c r="O87" s="18"/>
+      <c r="P87" s="18"/>
+      <c r="Q87" s="18"/>
+      <c r="R87" s="2"/>
+      <c r="S87" s="2"/>
+      <c r="T87" s="2"/>
+      <c r="U87" s="2"/>
+      <c r="V87" s="2"/>
+      <c r="W87" s="18"/>
+      <c r="X87" s="18"/>
+      <c r="Y87" s="18"/>
+      <c r="Z87" s="18"/>
+      <c r="AA87" s="18"/>
+      <c r="AB87" s="18"/>
+      <c r="AC87" s="18"/>
+      <c r="AD87" s="18"/>
+      <c r="AE87" s="2"/>
+      <c r="AF87" s="2"/>
+      <c r="AG87" s="2"/>
+      <c r="AH87" s="2"/>
+      <c r="AI87" s="18"/>
+      <c r="AJ87" s="18"/>
+      <c r="AK87" s="18"/>
+      <c r="AL87" s="14"/>
+      <c r="AM87" s="20"/>
+      <c r="AN87" s="22"/>
+      <c r="AO87" s="22"/>
+      <c r="AP87" s="20"/>
+      <c r="AQ87" s="20"/>
+      <c r="AR87" s="22"/>
+      <c r="AS87" s="22"/>
+      <c r="AT87" s="22"/>
+      <c r="AU87" s="22"/>
+      <c r="AV87" s="10"/>
+      <c r="AW87" s="16"/>
+      <c r="AX87" s="22"/>
+      <c r="AY87" s="22"/>
+      <c r="AZ87" s="22"/>
+      <c r="BA87" s="22"/>
+      <c r="BB87" s="22"/>
+      <c r="BC87" s="22"/>
+      <c r="BD87" s="22"/>
+      <c r="BE87" s="22"/>
+      <c r="BF87" s="22"/>
+      <c r="BG87" s="22"/>
+      <c r="BH87" s="22"/>
+      <c r="BI87" s="20"/>
+      <c r="BJ87" s="146"/>
+      <c r="BK87" s="22"/>
+      <c r="BL87" s="22"/>
+      <c r="BM87" s="22"/>
+      <c r="BN87" s="22"/>
+      <c r="BO87" s="2"/>
+      <c r="BP87" s="149"/>
+      <c r="BQ87" s="14"/>
+      <c r="BR87" s="18"/>
+      <c r="BS87" s="18"/>
+      <c r="BT87" s="21"/>
+    </row>
+    <row r="88" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="124"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="18"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="14"/>
+      <c r="L88" s="14"/>
+      <c r="M88" s="100"/>
+      <c r="N88" s="18"/>
+      <c r="O88" s="18"/>
+      <c r="P88" s="18"/>
+      <c r="Q88" s="18"/>
+      <c r="R88" s="2"/>
+      <c r="S88" s="2"/>
+      <c r="T88" s="2"/>
+      <c r="U88" s="2"/>
+      <c r="V88" s="2"/>
+      <c r="W88" s="18"/>
+      <c r="X88" s="18"/>
+      <c r="Y88" s="18"/>
+      <c r="Z88" s="18"/>
+      <c r="AA88" s="18"/>
+      <c r="AB88" s="18"/>
+      <c r="AC88" s="18"/>
+      <c r="AD88" s="18"/>
+      <c r="AE88" s="2"/>
+      <c r="AF88" s="2"/>
+      <c r="AG88" s="2"/>
+      <c r="AH88" s="2"/>
+      <c r="AI88" s="18"/>
+      <c r="AJ88" s="18"/>
+      <c r="AK88" s="18"/>
+      <c r="AL88" s="14"/>
+      <c r="AM88" s="20"/>
+      <c r="AN88" s="22"/>
+      <c r="AO88" s="22"/>
+      <c r="AP88" s="20"/>
+      <c r="AQ88" s="20"/>
+      <c r="AR88" s="22"/>
+      <c r="AS88" s="22"/>
+      <c r="AT88" s="22"/>
+      <c r="AU88" s="22"/>
+      <c r="AV88" s="10"/>
+      <c r="AW88" s="16"/>
+      <c r="AX88" s="22"/>
+      <c r="AY88" s="22"/>
+      <c r="AZ88" s="22"/>
+      <c r="BA88" s="22"/>
+      <c r="BB88" s="22"/>
+      <c r="BC88" s="22"/>
+      <c r="BD88" s="22"/>
+      <c r="BE88" s="22"/>
+      <c r="BF88" s="22"/>
+      <c r="BG88" s="22"/>
+      <c r="BH88" s="22"/>
+      <c r="BI88" s="20"/>
+      <c r="BJ88" s="146"/>
+      <c r="BK88" s="22"/>
+      <c r="BL88" s="22"/>
+      <c r="BM88" s="22"/>
+      <c r="BN88" s="22"/>
+      <c r="BO88" s="2"/>
+      <c r="BP88" s="149"/>
+      <c r="BQ88" s="14"/>
+      <c r="BR88" s="18"/>
+      <c r="BS88" s="18"/>
+      <c r="BT88" s="21"/>
+    </row>
+    <row r="89" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="124"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="18"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="14"/>
+      <c r="L89" s="14"/>
+      <c r="M89" s="100"/>
+      <c r="N89" s="18"/>
+      <c r="O89" s="18"/>
+      <c r="P89" s="18"/>
+      <c r="Q89" s="18"/>
+      <c r="R89" s="2"/>
+      <c r="S89" s="2"/>
+      <c r="T89" s="2"/>
+      <c r="U89" s="2"/>
+      <c r="V89" s="2"/>
+      <c r="W89" s="18"/>
+      <c r="X89" s="18"/>
+      <c r="Y89" s="18"/>
+      <c r="Z89" s="18"/>
+      <c r="AA89" s="18"/>
+      <c r="AB89" s="18"/>
+      <c r="AC89" s="18"/>
+      <c r="AD89" s="18"/>
+      <c r="AE89" s="2"/>
+      <c r="AF89" s="2"/>
+      <c r="AG89" s="2"/>
+      <c r="AH89" s="2"/>
+      <c r="AI89" s="18"/>
+      <c r="AJ89" s="18"/>
+      <c r="AK89" s="18"/>
+      <c r="AL89" s="14"/>
+      <c r="AM89" s="20"/>
+      <c r="AN89" s="22"/>
+      <c r="AO89" s="22"/>
+      <c r="AP89" s="20"/>
+      <c r="AQ89" s="20"/>
+      <c r="AR89" s="22"/>
+      <c r="AS89" s="22"/>
+      <c r="AT89" s="22"/>
+      <c r="AU89" s="22"/>
+      <c r="AV89" s="10"/>
+      <c r="AW89" s="16"/>
+      <c r="AX89" s="22"/>
+      <c r="AY89" s="22"/>
+      <c r="AZ89" s="22"/>
+      <c r="BA89" s="22"/>
+      <c r="BB89" s="22"/>
+      <c r="BC89" s="22"/>
+      <c r="BD89" s="22"/>
+      <c r="BE89" s="22"/>
+      <c r="BF89" s="22"/>
+      <c r="BG89" s="22"/>
+      <c r="BH89" s="22"/>
+      <c r="BI89" s="20"/>
+      <c r="BJ89" s="146"/>
+      <c r="BK89" s="22"/>
+      <c r="BL89" s="22"/>
+      <c r="BM89" s="22"/>
+      <c r="BN89" s="22"/>
+      <c r="BO89" s="2"/>
+      <c r="BP89" s="149"/>
+      <c r="BQ89" s="14"/>
+      <c r="BR89" s="18"/>
+      <c r="BS89" s="18"/>
+      <c r="BT89" s="21"/>
+    </row>
+    <row r="90" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="124"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="18"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="14"/>
+      <c r="L90" s="14"/>
+      <c r="M90" s="2"/>
+      <c r="N90" s="18"/>
+      <c r="O90" s="18"/>
+      <c r="P90" s="18"/>
+      <c r="Q90" s="18"/>
+      <c r="R90" s="2"/>
+      <c r="S90" s="2"/>
+      <c r="T90" s="2"/>
+      <c r="U90" s="2"/>
+      <c r="V90" s="2"/>
+      <c r="W90" s="18"/>
+      <c r="X90" s="18"/>
+      <c r="Y90" s="18"/>
+      <c r="Z90" s="18"/>
+      <c r="AA90" s="18"/>
+      <c r="AB90" s="18"/>
+      <c r="AC90" s="18"/>
+      <c r="AD90" s="18"/>
+      <c r="AE90" s="2"/>
+      <c r="AF90" s="2"/>
+      <c r="AG90" s="2"/>
+      <c r="AH90" s="2"/>
+      <c r="AI90" s="18"/>
+      <c r="AJ90" s="18"/>
+      <c r="AK90" s="18"/>
+      <c r="AL90" s="14"/>
+      <c r="AM90" s="20"/>
+      <c r="AN90" s="22"/>
+      <c r="AO90" s="22"/>
+      <c r="AP90" s="20"/>
+      <c r="AQ90" s="20"/>
+      <c r="AR90" s="22"/>
+      <c r="AS90" s="22"/>
+      <c r="AT90" s="22"/>
+      <c r="AU90" s="22"/>
+      <c r="AV90" s="20"/>
+      <c r="AW90" s="22"/>
+      <c r="AX90" s="22"/>
+      <c r="AY90" s="22"/>
+      <c r="AZ90" s="22"/>
+      <c r="BA90" s="22"/>
+      <c r="BB90" s="22"/>
+      <c r="BC90" s="22"/>
+      <c r="BD90" s="22"/>
+      <c r="BE90" s="22"/>
+      <c r="BF90" s="22"/>
+      <c r="BG90" s="22"/>
+      <c r="BH90" s="22"/>
+      <c r="BI90" s="20"/>
+      <c r="BJ90" s="146"/>
+      <c r="BK90" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BL87" s="146" t="s">
-        <v>750</v>
-      </c>
-      <c r="BM87" s="38"/>
-      <c r="BN87" s="38"/>
-      <c r="BO87" s="3"/>
-      <c r="BP87" s="120"/>
-      <c r="BQ87" s="35"/>
-      <c r="BR87" s="37"/>
-      <c r="BS87" s="37"/>
-      <c r="BT87" s="43"/>
-    </row>
-    <row r="88" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="116"/>
-      <c r="C88" s="116"/>
-      <c r="D88" s="116"/>
-      <c r="E88" s="116"/>
-      <c r="F88" s="116"/>
-      <c r="G88" s="116"/>
-      <c r="H88" s="77"/>
-      <c r="K88" s="116"/>
-      <c r="L88" s="116"/>
-      <c r="N88" s="77"/>
-      <c r="O88" s="77"/>
-      <c r="P88" s="77"/>
-      <c r="Q88" s="77"/>
-      <c r="W88" s="77"/>
-      <c r="X88" s="77"/>
-      <c r="Y88" s="77"/>
-      <c r="Z88" s="77"/>
-      <c r="AA88" s="77"/>
-      <c r="AB88" s="77"/>
-      <c r="AC88" s="77"/>
-      <c r="AD88" s="77"/>
-      <c r="AI88" s="77"/>
-      <c r="AJ88" s="77"/>
-      <c r="AK88" s="77"/>
-      <c r="AL88" s="116"/>
-      <c r="AM88" s="27"/>
-      <c r="AN88" s="26"/>
-      <c r="AO88" s="78"/>
-      <c r="AP88" s="117"/>
-      <c r="AQ88" s="27"/>
-      <c r="AR88" s="26"/>
-      <c r="AS88" s="78"/>
-      <c r="AT88" s="78"/>
-      <c r="AU88" s="78"/>
-      <c r="AV88" s="117"/>
-      <c r="AW88" s="78"/>
-      <c r="AX88" s="78"/>
-      <c r="AY88" s="78"/>
-      <c r="AZ88" s="150" t="s">
-        <v>766</v>
-      </c>
-      <c r="BA88" s="6" t="s">
-        <v>761</v>
-      </c>
-      <c r="BB88" s="78" t="s">
-        <v>783</v>
-      </c>
-      <c r="BC88" s="78"/>
-      <c r="BD88" s="78"/>
-      <c r="BE88" s="78"/>
-      <c r="BF88" s="78"/>
-      <c r="BG88" s="78"/>
-      <c r="BH88" s="78"/>
-      <c r="BI88" s="117"/>
-      <c r="BJ88" s="118"/>
-      <c r="BK88" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="BL88" s="145" t="s">
-        <v>588</v>
-      </c>
-      <c r="BM88" s="38"/>
-      <c r="BN88" s="38"/>
-      <c r="BO88" s="3"/>
-      <c r="BP88" s="121"/>
-      <c r="BQ88" s="45"/>
-      <c r="BR88" s="77"/>
-      <c r="BS88" s="77"/>
-      <c r="BT88" s="119"/>
-    </row>
-    <row r="89" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="116"/>
-      <c r="C89" s="116"/>
-      <c r="D89" s="116"/>
-      <c r="E89" s="116"/>
-      <c r="F89" s="116"/>
-      <c r="G89" s="116"/>
-      <c r="H89" s="77"/>
-      <c r="K89" s="116"/>
-      <c r="L89" s="116"/>
-      <c r="N89" s="77"/>
-      <c r="O89" s="77"/>
-      <c r="P89" s="77"/>
-      <c r="Q89" s="77"/>
-      <c r="W89" s="77"/>
-      <c r="X89" s="77"/>
-      <c r="Y89" s="77"/>
-      <c r="Z89" s="77"/>
-      <c r="AA89" s="77"/>
-      <c r="AB89" s="77"/>
-      <c r="AC89" s="77"/>
-      <c r="AD89" s="77"/>
-      <c r="AI89" s="77"/>
-      <c r="AJ89" s="77"/>
-      <c r="AK89" s="77"/>
-      <c r="AL89" s="116"/>
-      <c r="AM89" s="27"/>
-      <c r="AN89" s="26"/>
-      <c r="AO89" s="78"/>
-      <c r="AP89" s="117"/>
-      <c r="AQ89" s="27"/>
-      <c r="AR89" s="26"/>
-      <c r="AS89" s="78"/>
-      <c r="AT89" s="78"/>
-      <c r="AU89" s="78"/>
-      <c r="AV89" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW89" s="26" t="s">
-        <v>755</v>
-      </c>
-      <c r="AX89" s="78"/>
-      <c r="AY89" s="78"/>
-      <c r="AZ89" s="150"/>
-      <c r="BA89" s="6" t="s">
-        <v>762</v>
-      </c>
-      <c r="BB89" s="78" t="s">
-        <v>782</v>
-      </c>
-      <c r="BC89" s="78"/>
-      <c r="BD89" s="78"/>
-      <c r="BE89" s="78"/>
-      <c r="BF89" s="78"/>
-      <c r="BG89" s="78"/>
-      <c r="BH89" s="78"/>
-      <c r="BI89" s="117"/>
-      <c r="BJ89" s="118"/>
-      <c r="BK89" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="BL89" s="133" t="s">
-        <v>589</v>
-      </c>
-      <c r="BM89" s="38"/>
-      <c r="BN89" s="38"/>
-      <c r="BO89" s="3"/>
-      <c r="BP89" s="120"/>
-      <c r="BQ89" s="35"/>
-      <c r="BR89" s="77"/>
-      <c r="BS89" s="77"/>
-      <c r="BT89" s="119"/>
-    </row>
-    <row r="90" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="116"/>
-      <c r="C90" s="116"/>
-      <c r="D90" s="116"/>
-      <c r="E90" s="116"/>
-      <c r="F90" s="116"/>
-      <c r="G90" s="116"/>
-      <c r="H90" s="77"/>
-      <c r="K90" s="116"/>
-      <c r="L90" s="116"/>
-      <c r="N90" s="77"/>
-      <c r="O90" s="77"/>
-      <c r="P90" s="77"/>
-      <c r="Q90" s="77"/>
-      <c r="W90" s="77"/>
-      <c r="X90" s="77"/>
-      <c r="Y90" s="77"/>
-      <c r="Z90" s="77"/>
-      <c r="AA90" s="77"/>
-      <c r="AB90" s="77"/>
-      <c r="AC90" s="77"/>
-      <c r="AD90" s="77"/>
-      <c r="AI90" s="77"/>
-      <c r="AJ90" s="77"/>
-      <c r="AK90" s="77"/>
-      <c r="AL90" s="116"/>
-      <c r="AM90" s="117"/>
-      <c r="AN90" s="78"/>
-      <c r="AO90" s="78"/>
-      <c r="AP90" s="117"/>
-      <c r="AQ90" s="117"/>
-      <c r="AR90" s="78"/>
-      <c r="AS90" s="78"/>
-      <c r="AT90" s="78"/>
-      <c r="AU90" s="78"/>
-      <c r="AV90" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW90" s="26" t="s">
-        <v>754</v>
-      </c>
-      <c r="AX90" s="78"/>
-      <c r="AY90" s="78"/>
-      <c r="AZ90" s="150" t="s">
-        <v>765</v>
-      </c>
-      <c r="BA90" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="BB90" s="78" t="s">
-        <v>779</v>
-      </c>
-      <c r="BC90" s="78"/>
-      <c r="BD90" s="78"/>
-      <c r="BE90" s="78"/>
-      <c r="BF90" s="78"/>
-      <c r="BG90" s="78"/>
-      <c r="BH90" s="78"/>
-      <c r="BI90" s="117"/>
-      <c r="BJ90" s="118"/>
-      <c r="BK90" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="BL90" s="146" t="s">
+      <c r="BL90" s="150" t="s">
         <v>749</v>
       </c>
-      <c r="BM90" s="133"/>
-      <c r="BN90" s="133"/>
-      <c r="BO90" s="134"/>
-      <c r="BP90" s="135"/>
-      <c r="BQ90" s="29"/>
-      <c r="BR90" s="77"/>
-      <c r="BS90" s="77"/>
-      <c r="BT90" s="119"/>
+      <c r="BM90" s="22"/>
+      <c r="BN90" s="22"/>
+      <c r="BO90" s="2"/>
+      <c r="BP90" s="149"/>
+      <c r="BQ90" s="14"/>
+      <c r="BR90" s="18"/>
+      <c r="BS90" s="18"/>
+      <c r="BT90" s="21"/>
     </row>
     <row r="91" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="116"/>
@@ -18849,12 +18988,12 @@
       <c r="AJ91" s="77"/>
       <c r="AK91" s="77"/>
       <c r="AL91" s="116"/>
-      <c r="AM91" s="117"/>
-      <c r="AN91" s="78"/>
+      <c r="AM91" s="27"/>
+      <c r="AN91" s="26"/>
       <c r="AO91" s="78"/>
       <c r="AP91" s="117"/>
-      <c r="AQ91" s="117"/>
-      <c r="AR91" s="78"/>
+      <c r="AQ91" s="27"/>
+      <c r="AR91" s="26"/>
       <c r="AS91" s="78"/>
       <c r="AT91" s="78"/>
       <c r="AU91" s="78"/>
@@ -18862,12 +19001,14 @@
       <c r="AW91" s="78"/>
       <c r="AX91" s="78"/>
       <c r="AY91" s="78"/>
-      <c r="AZ91" s="78"/>
-      <c r="BA91" s="5" t="s">
-        <v>764</v>
+      <c r="AZ91" s="148" t="s">
+        <v>765</v>
+      </c>
+      <c r="BA91" s="6" t="s">
+        <v>760</v>
       </c>
       <c r="BB91" s="78" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="BC91" s="78"/>
       <c r="BD91" s="78"/>
@@ -18878,16 +19019,16 @@
       <c r="BI91" s="117"/>
       <c r="BJ91" s="118"/>
       <c r="BK91" s="38" t="s">
-        <v>515</v>
-      </c>
-      <c r="BL91" s="146" t="s">
-        <v>516</v>
+        <v>95</v>
+      </c>
+      <c r="BL91" s="144" t="s">
+        <v>588</v>
       </c>
       <c r="BM91" s="38"/>
       <c r="BN91" s="38"/>
       <c r="BO91" s="3"/>
-      <c r="BP91" s="29"/>
-      <c r="BQ91" s="93"/>
+      <c r="BP91" s="121"/>
+      <c r="BQ91" s="45"/>
       <c r="BR91" s="77"/>
       <c r="BS91" s="77"/>
       <c r="BT91" s="119"/>
@@ -18918,22 +19059,30 @@
       <c r="AJ92" s="77"/>
       <c r="AK92" s="77"/>
       <c r="AL92" s="116"/>
-      <c r="AM92" s="117"/>
-      <c r="AN92" s="78"/>
+      <c r="AM92" s="27"/>
+      <c r="AN92" s="26"/>
       <c r="AO92" s="78"/>
       <c r="AP92" s="117"/>
-      <c r="AQ92" s="117"/>
-      <c r="AR92" s="78"/>
+      <c r="AQ92" s="27"/>
+      <c r="AR92" s="26"/>
       <c r="AS92" s="78"/>
       <c r="AT92" s="78"/>
       <c r="AU92" s="78"/>
-      <c r="AV92" s="117"/>
-      <c r="AW92" s="78"/>
+      <c r="AV92" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW92" s="26" t="s">
+        <v>754</v>
+      </c>
       <c r="AX92" s="78"/>
       <c r="AY92" s="78"/>
-      <c r="AZ92" s="78"/>
-      <c r="BA92" s="78"/>
-      <c r="BB92" s="78"/>
+      <c r="AZ92" s="148"/>
+      <c r="BA92" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="BB92" s="78" t="s">
+        <v>781</v>
+      </c>
       <c r="BC92" s="78"/>
       <c r="BD92" s="78"/>
       <c r="BE92" s="78"/>
@@ -18943,16 +19092,16 @@
       <c r="BI92" s="117"/>
       <c r="BJ92" s="118"/>
       <c r="BK92" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="BL92" s="38" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="BL92" s="133" t="s">
+        <v>589</v>
       </c>
       <c r="BM92" s="38"/>
       <c r="BN92" s="38"/>
       <c r="BO92" s="3"/>
-      <c r="BP92" s="29"/>
-      <c r="BQ92" s="29"/>
+      <c r="BP92" s="120"/>
+      <c r="BQ92" s="35"/>
       <c r="BR92" s="77"/>
       <c r="BS92" s="77"/>
       <c r="BT92" s="119"/>
@@ -18992,13 +19141,23 @@
       <c r="AS93" s="78"/>
       <c r="AT93" s="78"/>
       <c r="AU93" s="78"/>
-      <c r="AV93" s="117"/>
-      <c r="AW93" s="78"/>
+      <c r="AV93" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW93" s="26" t="s">
+        <v>753</v>
+      </c>
       <c r="AX93" s="78"/>
       <c r="AY93" s="78"/>
-      <c r="AZ93" s="78"/>
-      <c r="BA93" s="78"/>
-      <c r="BB93" s="78"/>
+      <c r="AZ93" s="148" t="s">
+        <v>764</v>
+      </c>
+      <c r="BA93" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="BB93" s="78" t="s">
+        <v>778</v>
+      </c>
       <c r="BC93" s="78"/>
       <c r="BD93" s="78"/>
       <c r="BE93" s="78"/>
@@ -19007,12 +19166,16 @@
       <c r="BH93" s="78"/>
       <c r="BI93" s="117"/>
       <c r="BJ93" s="118"/>
-      <c r="BK93" s="46"/>
-      <c r="BL93" s="46"/>
-      <c r="BM93" s="46"/>
-      <c r="BN93" s="46"/>
-      <c r="BO93" s="48"/>
-      <c r="BP93" s="29"/>
+      <c r="BK93" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="BL93" s="145" t="s">
+        <v>748</v>
+      </c>
+      <c r="BM93" s="133"/>
+      <c r="BN93" s="133"/>
+      <c r="BO93" s="134"/>
+      <c r="BP93" s="135"/>
       <c r="BQ93" s="29"/>
       <c r="BR93" s="77"/>
       <c r="BS93" s="77"/>
@@ -19058,8 +19221,12 @@
       <c r="AX94" s="78"/>
       <c r="AY94" s="78"/>
       <c r="AZ94" s="78"/>
-      <c r="BA94" s="78"/>
-      <c r="BB94" s="78"/>
+      <c r="BA94" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="BB94" s="78" t="s">
+        <v>779</v>
+      </c>
       <c r="BC94" s="78"/>
       <c r="BD94" s="78"/>
       <c r="BE94" s="78"/>
@@ -19068,12 +19235,17 @@
       <c r="BH94" s="78"/>
       <c r="BI94" s="117"/>
       <c r="BJ94" s="118"/>
-      <c r="BK94" s="78"/>
-      <c r="BL94" s="78"/>
-      <c r="BM94" s="78"/>
-      <c r="BN94" s="78"/>
-      <c r="BP94" s="116"/>
-      <c r="BQ94" s="116"/>
+      <c r="BK94" s="38" t="s">
+        <v>515</v>
+      </c>
+      <c r="BL94" s="145" t="s">
+        <v>516</v>
+      </c>
+      <c r="BM94" s="38"/>
+      <c r="BN94" s="38"/>
+      <c r="BO94" s="3"/>
+      <c r="BP94" s="29"/>
+      <c r="BQ94" s="93"/>
       <c r="BR94" s="77"/>
       <c r="BS94" s="77"/>
       <c r="BT94" s="119"/>
@@ -19128,15 +19300,201 @@
       <c r="BH95" s="78"/>
       <c r="BI95" s="117"/>
       <c r="BJ95" s="118"/>
-      <c r="BK95" s="78"/>
-      <c r="BL95" s="78"/>
-      <c r="BM95" s="78"/>
-      <c r="BN95" s="78"/>
-      <c r="BP95" s="116"/>
-      <c r="BQ95" s="116"/>
+      <c r="BK95" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="BL95" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="BM95" s="38"/>
+      <c r="BN95" s="38"/>
+      <c r="BO95" s="3"/>
+      <c r="BP95" s="29"/>
+      <c r="BQ95" s="29"/>
       <c r="BR95" s="77"/>
       <c r="BS95" s="77"/>
       <c r="BT95" s="119"/>
+    </row>
+    <row r="96" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B96" s="116"/>
+      <c r="C96" s="116"/>
+      <c r="D96" s="116"/>
+      <c r="E96" s="116"/>
+      <c r="F96" s="116"/>
+      <c r="G96" s="116"/>
+      <c r="H96" s="77"/>
+      <c r="K96" s="116"/>
+      <c r="L96" s="116"/>
+      <c r="N96" s="77"/>
+      <c r="O96" s="77"/>
+      <c r="P96" s="77"/>
+      <c r="Q96" s="77"/>
+      <c r="W96" s="77"/>
+      <c r="X96" s="77"/>
+      <c r="Y96" s="77"/>
+      <c r="Z96" s="77"/>
+      <c r="AA96" s="77"/>
+      <c r="AB96" s="77"/>
+      <c r="AC96" s="77"/>
+      <c r="AD96" s="77"/>
+      <c r="AI96" s="77"/>
+      <c r="AJ96" s="77"/>
+      <c r="AK96" s="77"/>
+      <c r="AL96" s="116"/>
+      <c r="AM96" s="117"/>
+      <c r="AN96" s="78"/>
+      <c r="AO96" s="78"/>
+      <c r="AP96" s="117"/>
+      <c r="AQ96" s="117"/>
+      <c r="AR96" s="78"/>
+      <c r="AS96" s="78"/>
+      <c r="AT96" s="78"/>
+      <c r="AU96" s="78"/>
+      <c r="AV96" s="117"/>
+      <c r="AW96" s="78"/>
+      <c r="AX96" s="78"/>
+      <c r="AY96" s="78"/>
+      <c r="AZ96" s="78"/>
+      <c r="BA96" s="78"/>
+      <c r="BB96" s="78"/>
+      <c r="BC96" s="78"/>
+      <c r="BD96" s="78"/>
+      <c r="BE96" s="78"/>
+      <c r="BF96" s="78"/>
+      <c r="BG96" s="78"/>
+      <c r="BH96" s="78"/>
+      <c r="BI96" s="117"/>
+      <c r="BJ96" s="118"/>
+      <c r="BK96" s="46"/>
+      <c r="BL96" s="46"/>
+      <c r="BM96" s="46"/>
+      <c r="BN96" s="46"/>
+      <c r="BO96" s="48"/>
+      <c r="BP96" s="29"/>
+      <c r="BQ96" s="29"/>
+      <c r="BR96" s="77"/>
+      <c r="BS96" s="77"/>
+      <c r="BT96" s="119"/>
+    </row>
+    <row r="97" spans="2:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B97" s="116"/>
+      <c r="C97" s="116"/>
+      <c r="D97" s="116"/>
+      <c r="E97" s="116"/>
+      <c r="F97" s="116"/>
+      <c r="G97" s="116"/>
+      <c r="H97" s="77"/>
+      <c r="K97" s="116"/>
+      <c r="L97" s="116"/>
+      <c r="N97" s="77"/>
+      <c r="O97" s="77"/>
+      <c r="P97" s="77"/>
+      <c r="Q97" s="77"/>
+      <c r="W97" s="77"/>
+      <c r="X97" s="77"/>
+      <c r="Y97" s="77"/>
+      <c r="Z97" s="77"/>
+      <c r="AA97" s="77"/>
+      <c r="AB97" s="77"/>
+      <c r="AC97" s="77"/>
+      <c r="AD97" s="77"/>
+      <c r="AI97" s="77"/>
+      <c r="AJ97" s="77"/>
+      <c r="AK97" s="77"/>
+      <c r="AL97" s="116"/>
+      <c r="AM97" s="117"/>
+      <c r="AN97" s="78"/>
+      <c r="AO97" s="78"/>
+      <c r="AP97" s="117"/>
+      <c r="AQ97" s="117"/>
+      <c r="AR97" s="78"/>
+      <c r="AS97" s="78"/>
+      <c r="AT97" s="78"/>
+      <c r="AU97" s="78"/>
+      <c r="AV97" s="117"/>
+      <c r="AW97" s="78"/>
+      <c r="AX97" s="78"/>
+      <c r="AY97" s="78"/>
+      <c r="AZ97" s="78"/>
+      <c r="BA97" s="78"/>
+      <c r="BB97" s="78"/>
+      <c r="BC97" s="78"/>
+      <c r="BD97" s="78"/>
+      <c r="BE97" s="78"/>
+      <c r="BF97" s="78"/>
+      <c r="BG97" s="78"/>
+      <c r="BH97" s="78"/>
+      <c r="BI97" s="117"/>
+      <c r="BJ97" s="118"/>
+      <c r="BK97" s="78"/>
+      <c r="BL97" s="78"/>
+      <c r="BM97" s="78"/>
+      <c r="BN97" s="78"/>
+      <c r="BP97" s="116"/>
+      <c r="BQ97" s="116"/>
+      <c r="BR97" s="77"/>
+      <c r="BS97" s="77"/>
+      <c r="BT97" s="119"/>
+    </row>
+    <row r="98" spans="2:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B98" s="116"/>
+      <c r="C98" s="116"/>
+      <c r="D98" s="116"/>
+      <c r="E98" s="116"/>
+      <c r="F98" s="116"/>
+      <c r="G98" s="116"/>
+      <c r="H98" s="77"/>
+      <c r="K98" s="116"/>
+      <c r="L98" s="116"/>
+      <c r="N98" s="77"/>
+      <c r="O98" s="77"/>
+      <c r="P98" s="77"/>
+      <c r="Q98" s="77"/>
+      <c r="W98" s="77"/>
+      <c r="X98" s="77"/>
+      <c r="Y98" s="77"/>
+      <c r="Z98" s="77"/>
+      <c r="AA98" s="77"/>
+      <c r="AB98" s="77"/>
+      <c r="AC98" s="77"/>
+      <c r="AD98" s="77"/>
+      <c r="AI98" s="77"/>
+      <c r="AJ98" s="77"/>
+      <c r="AK98" s="77"/>
+      <c r="AL98" s="116"/>
+      <c r="AM98" s="117"/>
+      <c r="AN98" s="78"/>
+      <c r="AO98" s="78"/>
+      <c r="AP98" s="117"/>
+      <c r="AQ98" s="117"/>
+      <c r="AR98" s="78"/>
+      <c r="AS98" s="78"/>
+      <c r="AT98" s="78"/>
+      <c r="AU98" s="78"/>
+      <c r="AV98" s="117"/>
+      <c r="AW98" s="78"/>
+      <c r="AX98" s="78"/>
+      <c r="AY98" s="78"/>
+      <c r="AZ98" s="78"/>
+      <c r="BA98" s="78"/>
+      <c r="BB98" s="78"/>
+      <c r="BC98" s="78"/>
+      <c r="BD98" s="78"/>
+      <c r="BE98" s="78"/>
+      <c r="BF98" s="78"/>
+      <c r="BG98" s="78"/>
+      <c r="BH98" s="78"/>
+      <c r="BI98" s="117"/>
+      <c r="BJ98" s="118"/>
+      <c r="BK98" s="78"/>
+      <c r="BL98" s="78"/>
+      <c r="BM98" s="78"/>
+      <c r="BN98" s="78"/>
+      <c r="BP98" s="116"/>
+      <c r="BQ98" s="116"/>
+      <c r="BR98" s="77"/>
+      <c r="BS98" s="77"/>
+      <c r="BT98" s="119"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A51252B-FE09-45D3-8174-A2146AC8BA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2AB487-4BE6-4F1E-89B5-DE62A9F18F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2697" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="805">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2398,12 +2398,6 @@
     <t>20250325</t>
   </si>
   <si>
-    <t>new</t>
-  </si>
-  <si>
-    <t>old for now</t>
-  </si>
-  <si>
     <t>AFAP(1/2)</t>
   </si>
   <si>
@@ -2422,9 +2416,6 @@
     <t>20250326</t>
   </si>
   <si>
-    <t>GLI2025_SEA032_92</t>
-  </si>
-  <si>
     <t>2.25.2-r</t>
   </si>
   <si>
@@ -2437,9 +2428,6 @@
     <t>GL1-TRI</t>
   </si>
   <si>
-    <t>Sigma-T(zodiak)/</t>
-  </si>
-  <si>
     <t>Sigma-T/Sigma-T(zodiak)</t>
   </si>
   <si>
@@ -2449,10 +2437,37 @@
     <t>no DO data, Questionnable CDOM data (negative range)</t>
   </si>
   <si>
-    <t>CDOM negative values, no CODA data because of config file duplicate, recovered after 3 days to fix it</t>
-  </si>
-  <si>
     <t>Questionnable CDOM data (negative range)</t>
+  </si>
+  <si>
+    <t>211391</t>
+  </si>
+  <si>
+    <t>212970</t>
+  </si>
+  <si>
+    <t>old still</t>
+  </si>
+  <si>
+    <t>20250612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+  </si>
+  <si>
+    <t>GLI2025_SEA032_092</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA032_093</t>
+  </si>
+  <si>
+    <t>Sigma-T(zodiak)/Sigma-T</t>
+  </si>
+  <si>
+    <t>CDOM negative values, no CODA data because of in config file duplicate, recovered after 3 days to fix it, also no legato files at 2hz</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA022_110</t>
   </si>
 </sst>
 </file>
@@ -2778,7 +2793,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3148,9 +3163,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -17641,7 +17653,7 @@
         <v>741</v>
       </c>
       <c r="AK80" s="37" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AL80" s="35">
         <v>33</v>
@@ -17828,7 +17840,7 @@
         <v>752</v>
       </c>
       <c r="AK81" s="37" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AL81" s="35">
         <v>30</v>
@@ -18017,7 +18029,7 @@
         <v>752</v>
       </c>
       <c r="AK82" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AL82" s="14">
         <v>32</v>
@@ -18122,12 +18134,14 @@
         <v>15</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="I83" s="2">
         <v>29.2</v>
       </c>
-      <c r="J83" s="2"/>
+      <c r="J83" s="2">
+        <v>25.2</v>
+      </c>
       <c r="K83" s="14">
         <v>44.391300000000001</v>
       </c>
@@ -18137,17 +18151,34 @@
       <c r="M83" s="100">
         <v>0.59097222222222223</v>
       </c>
-      <c r="N83" s="18"/>
-      <c r="O83" s="18"/>
-      <c r="P83" s="18"/>
-      <c r="Q83" s="18"/>
+      <c r="N83" s="18">
+        <v>42.48</v>
+      </c>
+      <c r="O83" s="18">
+        <v>-63.38</v>
+      </c>
+      <c r="P83" s="18">
+        <v>44.4</v>
+      </c>
+      <c r="Q83" s="18">
+        <v>-61.42</v>
+      </c>
       <c r="R83" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="S83" s="2"/>
-      <c r="T83" s="2"/>
-      <c r="U83" s="2"/>
-      <c r="V83" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="S83" s="2">
+        <v>22</v>
+      </c>
+      <c r="T83" s="2">
+        <v>559</v>
+      </c>
+      <c r="U83" s="2">
+        <v>902</v>
+      </c>
+      <c r="V83" s="2">
+        <f>U83*2</f>
+        <v>1804</v>
+      </c>
       <c r="W83" s="18" t="s">
         <v>36</v>
       </c>
@@ -18161,12 +18192,18 @@
       <c r="AA83" s="18"/>
       <c r="AB83" s="18"/>
       <c r="AC83" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AD83" s="18"/>
-      <c r="AE83" s="2"/>
-      <c r="AF83" s="2"/>
-      <c r="AG83" s="2"/>
+      <c r="AE83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="2">
+        <v>0</v>
+      </c>
       <c r="AH83" s="2">
         <v>1024.3</v>
       </c>
@@ -18177,7 +18214,7 @@
         <v>752</v>
       </c>
       <c r="AK83" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AL83" s="14">
         <v>33</v>
@@ -18250,7 +18287,7 @@
       </c>
       <c r="BS83" s="18"/>
       <c r="BT83" s="21" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
     </row>
     <row r="84" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -18276,7 +18313,7 @@
         <v>15</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>789</v>
+        <v>800</v>
       </c>
       <c r="I84" s="2">
         <v>29.3</v>
@@ -18285,7 +18322,7 @@
         <v>28.5</v>
       </c>
       <c r="K84" s="14" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="L84" s="14">
         <v>-63.369900000000001</v>
@@ -18306,7 +18343,7 @@
         <v>-63.13</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="S84" s="2">
         <v>3</v>
@@ -18334,7 +18371,7 @@
       <c r="AA84" s="18"/>
       <c r="AB84" s="18"/>
       <c r="AC84" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AD84" s="18"/>
       <c r="AE84" s="2">
@@ -18349,14 +18386,14 @@
       <c r="AH84" s="2">
         <v>1023.75</v>
       </c>
-      <c r="AI84" s="140">
-        <v>2025</v>
+      <c r="AI84" s="18">
+        <v>20250529</v>
       </c>
       <c r="AJ84" s="18" t="s">
         <v>752</v>
       </c>
       <c r="AK84" s="18" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="AL84" s="14">
         <v>32</v>
@@ -18385,7 +18422,7 @@
         <v>762</v>
       </c>
       <c r="BB84" s="22" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="BC84" s="22" t="s">
         <v>420</v>
@@ -18394,7 +18431,7 @@
         <v>773</v>
       </c>
       <c r="BE84" s="22" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="BF84" s="22"/>
       <c r="BG84" s="22"/>
@@ -18411,10 +18448,10 @@
       <c r="BL84" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="BM84" s="79" t="s">
+      <c r="BM84" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="BN84" s="151">
+      <c r="BN84" s="2">
         <v>1272212</v>
       </c>
       <c r="BO84" s="2"/>
@@ -18425,13 +18462,13 @@
         <v>205</v>
       </c>
       <c r="BR84" s="18" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="BS84" s="18" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="BT84" s="21" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
     </row>
     <row r="85" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -18441,7 +18478,9 @@
       <c r="B85" s="14">
         <v>20250609</v>
       </c>
-      <c r="C85" s="14"/>
+      <c r="C85" s="14">
+        <v>20250703</v>
+      </c>
       <c r="D85" s="14" t="s">
         <v>53</v>
       </c>
@@ -18455,12 +18494,14 @@
         <v>15</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="I85" s="2">
         <v>28.5</v>
       </c>
-      <c r="J85" s="2"/>
+      <c r="J85" s="2">
+        <v>24.5</v>
+      </c>
       <c r="K85" s="14">
         <v>44.4223</v>
       </c>
@@ -18470,17 +18511,34 @@
       <c r="M85" s="100">
         <v>0.6972222222222223</v>
       </c>
-      <c r="N85" s="18"/>
-      <c r="O85" s="18"/>
-      <c r="P85" s="18"/>
-      <c r="Q85" s="18"/>
+      <c r="N85" s="18">
+        <v>42.46</v>
+      </c>
+      <c r="O85" s="18">
+        <v>-63.41</v>
+      </c>
+      <c r="P85" s="18">
+        <v>44.53</v>
+      </c>
+      <c r="Q85" s="18">
+        <v>-61.43</v>
+      </c>
       <c r="R85" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S85" s="2"/>
-      <c r="T85" s="2"/>
-      <c r="U85" s="2"/>
-      <c r="V85" s="2"/>
+      <c r="S85" s="2">
+        <v>24</v>
+      </c>
+      <c r="T85" s="2">
+        <v>639</v>
+      </c>
+      <c r="U85" s="2">
+        <v>1068</v>
+      </c>
+      <c r="V85" s="2">
+        <f>U85*2</f>
+        <v>2136</v>
+      </c>
       <c r="W85" s="18" t="s">
         <v>36</v>
       </c>
@@ -18494,23 +18552,29 @@
       <c r="AA85" s="18"/>
       <c r="AB85" s="18"/>
       <c r="AC85" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AD85" s="18"/>
-      <c r="AE85" s="2"/>
-      <c r="AF85" s="2"/>
-      <c r="AG85" s="2"/>
+      <c r="AE85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="2">
+        <v>0</v>
+      </c>
       <c r="AH85" s="2">
         <v>1023.75</v>
       </c>
-      <c r="AI85" s="140">
-        <v>2025</v>
+      <c r="AI85" s="18">
+        <v>20250529</v>
       </c>
       <c r="AJ85" s="18" t="s">
         <v>752</v>
       </c>
       <c r="AK85" s="18" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="AL85" s="14">
         <v>32</v>
@@ -18539,7 +18603,7 @@
         <v>762</v>
       </c>
       <c r="BB85" s="22" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="BC85" s="22" t="s">
         <v>420</v>
@@ -18548,7 +18612,7 @@
         <v>773</v>
       </c>
       <c r="BE85" s="22" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="BF85" s="22"/>
       <c r="BG85" s="22"/>
@@ -18565,10 +18629,10 @@
       <c r="BL85" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="BM85" s="79" t="s">
+      <c r="BM85" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="BN85" s="151">
+      <c r="BN85" s="2">
         <v>1272212</v>
       </c>
       <c r="BO85" s="2"/>
@@ -18579,24 +18643,34 @@
         <v>205</v>
       </c>
       <c r="BR85" s="18" t="s">
+        <v>802</v>
+      </c>
+      <c r="BS85" s="18" t="s">
         <v>794</v>
       </c>
-      <c r="BS85" s="18" t="s">
-        <v>799</v>
-      </c>
       <c r="BT85" s="21" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="86" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="124"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="18"/>
+      <c r="D86" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E86" s="14">
+        <v>110</v>
+      </c>
+      <c r="F86" s="14">
+        <v>4800993</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="18" t="s">
+        <v>804</v>
+      </c>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="14"/>
@@ -18606,27 +18680,47 @@
       <c r="O86" s="18"/>
       <c r="P86" s="18"/>
       <c r="Q86" s="18"/>
-      <c r="R86" s="2"/>
+      <c r="R86" s="2" t="s">
+        <v>444</v>
+      </c>
       <c r="S86" s="2"/>
       <c r="T86" s="2"/>
       <c r="U86" s="2"/>
       <c r="V86" s="2"/>
-      <c r="W86" s="18"/>
-      <c r="X86" s="18"/>
+      <c r="W86" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X86" s="18">
+        <v>1</v>
+      </c>
       <c r="Y86" s="18"/>
-      <c r="Z86" s="18"/>
+      <c r="Z86" s="18" t="s">
+        <v>183</v>
+      </c>
       <c r="AA86" s="18"/>
       <c r="AB86" s="18"/>
-      <c r="AC86" s="18"/>
+      <c r="AC86" s="18" t="s">
+        <v>781</v>
+      </c>
       <c r="AD86" s="18"/>
       <c r="AE86" s="2"/>
       <c r="AF86" s="2"/>
       <c r="AG86" s="2"/>
-      <c r="AH86" s="2"/>
-      <c r="AI86" s="18"/>
-      <c r="AJ86" s="18"/>
-      <c r="AK86" s="18"/>
-      <c r="AL86" s="14"/>
+      <c r="AH86" s="2">
+        <v>1022.25</v>
+      </c>
+      <c r="AI86" s="18">
+        <v>20250620</v>
+      </c>
+      <c r="AJ86" s="18" t="s">
+        <v>752</v>
+      </c>
+      <c r="AK86" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="AL86" s="14">
+        <v>30</v>
+      </c>
       <c r="AM86" s="20"/>
       <c r="AN86" s="22"/>
       <c r="AO86" s="22"/>
@@ -18636,28 +18730,60 @@
       <c r="AS86" s="22"/>
       <c r="AT86" s="22"/>
       <c r="AU86" s="22"/>
-      <c r="AV86" s="10"/>
-      <c r="AW86" s="16"/>
-      <c r="AX86" s="22"/>
+      <c r="AV86" s="10">
+        <v>4551</v>
+      </c>
+      <c r="AW86" s="16">
+        <v>42691</v>
+      </c>
+      <c r="AX86" s="22" t="s">
+        <v>461</v>
+      </c>
       <c r="AY86" s="22"/>
       <c r="AZ86" s="22"/>
-      <c r="BA86" s="22"/>
-      <c r="BB86" s="22"/>
-      <c r="BC86" s="22"/>
-      <c r="BD86" s="22"/>
-      <c r="BE86" s="22"/>
+      <c r="BA86" s="22" t="s">
+        <v>761</v>
+      </c>
+      <c r="BB86" s="22" t="s">
+        <v>798</v>
+      </c>
+      <c r="BC86" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="BD86" s="22" t="s">
+        <v>796</v>
+      </c>
+      <c r="BE86" s="22" t="s">
+        <v>798</v>
+      </c>
       <c r="BF86" s="22"/>
       <c r="BG86" s="22"/>
       <c r="BH86" s="22"/>
-      <c r="BI86" s="20"/>
-      <c r="BJ86" s="146"/>
-      <c r="BK86" s="22"/>
-      <c r="BL86" s="22"/>
-      <c r="BM86" s="22"/>
-      <c r="BN86" s="22"/>
+      <c r="BI86" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ86" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK86" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="BL86" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="BM86" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BN86" s="22" t="s">
+        <v>702</v>
+      </c>
       <c r="BO86" s="2"/>
-      <c r="BP86" s="149"/>
-      <c r="BQ86" s="14"/>
+      <c r="BP86" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="BQ86" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="BR86" s="18"/>
       <c r="BS86" s="18"/>
       <c r="BT86" s="21"/>
@@ -18858,7 +18984,9 @@
       <c r="AS89" s="22"/>
       <c r="AT89" s="22"/>
       <c r="AU89" s="22"/>
-      <c r="AV89" s="10"/>
+      <c r="AV89" s="10" t="s">
+        <v>799</v>
+      </c>
       <c r="AW89" s="16"/>
       <c r="AX89" s="22"/>
       <c r="AY89" s="22"/>
@@ -19008,10 +19136,12 @@
         <v>760</v>
       </c>
       <c r="BB91" s="78" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="BC91" s="78"/>
-      <c r="BD91" s="78"/>
+      <c r="BD91" s="78" t="s">
+        <v>795</v>
+      </c>
       <c r="BE91" s="78"/>
       <c r="BF91" s="78"/>
       <c r="BG91" s="78"/>
@@ -19081,10 +19211,12 @@
         <v>761</v>
       </c>
       <c r="BB92" s="78" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="BC92" s="78"/>
-      <c r="BD92" s="78"/>
+      <c r="BD92" s="78" t="s">
+        <v>796</v>
+      </c>
       <c r="BE92" s="78"/>
       <c r="BF92" s="78"/>
       <c r="BG92" s="78"/>
@@ -19159,7 +19291,9 @@
         <v>778</v>
       </c>
       <c r="BC93" s="78"/>
-      <c r="BD93" s="78"/>
+      <c r="BD93" s="78" t="s">
+        <v>773</v>
+      </c>
       <c r="BE93" s="78"/>
       <c r="BF93" s="78"/>
       <c r="BG93" s="78"/>
@@ -19228,7 +19362,9 @@
         <v>779</v>
       </c>
       <c r="BC94" s="78"/>
-      <c r="BD94" s="78"/>
+      <c r="BD94" s="78" t="s">
+        <v>774</v>
+      </c>
       <c r="BE94" s="78"/>
       <c r="BF94" s="78"/>
       <c r="BG94" s="78"/>
@@ -19499,6 +19635,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -19674,6 +19813,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -20733,5 +20875,8 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2AB487-4BE6-4F1E-89B5-DE62A9F18F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08C273C-E22C-453C-8614-A8A9C912E416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2753" uniqueCount="812">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2446,9 +2446,6 @@
     <t>212970</t>
   </si>
   <si>
-    <t>old still</t>
-  </si>
-  <si>
     <t>20250612</t>
   </si>
   <si>
@@ -2467,7 +2464,31 @@
     <t>CDOM negative values, no CODA data because of in config file duplicate, recovered after 3 days to fix it, also no legato files at 2hz</t>
   </si>
   <si>
-    <t>GLI2025_SEA022_110</t>
+    <t>GLI2025_SEA022_111</t>
+  </si>
+  <si>
+    <t>not fully cal</t>
+  </si>
+  <si>
+    <t>copied on ext dr to empty dropbox</t>
+  </si>
+  <si>
+    <t>GL1-GL2-GL3-GL7-GL3-GL2-GL1-GL2-GL1-TRI-DR</t>
+  </si>
+  <si>
+    <t>internal waves on shelf break, back and forth Emerald basin</t>
+  </si>
+  <si>
+    <t>shipped</t>
+  </si>
+  <si>
+    <t>20250613</t>
+  </si>
+  <si>
+    <t>25u2955</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA032_095</t>
   </si>
 </sst>
 </file>
@@ -2478,7 +2499,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2563,8 +2584,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2601,6 +2629,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2793,7 +2827,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3163,6 +3197,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3566,7 +3607,9 @@
   <sheetData>
     <row r="1" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="C1" s="152" t="s">
+        <v>805</v>
+      </c>
       <c r="D1" s="94" t="s">
         <v>432</v>
       </c>
@@ -17563,7 +17606,7 @@
       <c r="D80" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E80" s="35">
+      <c r="E80" s="151">
         <v>134</v>
       </c>
       <c r="F80" s="35">
@@ -17748,7 +17791,7 @@
       <c r="D81" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E81" s="35">
+      <c r="E81" s="151">
         <v>104</v>
       </c>
       <c r="F81" s="35">
@@ -17939,7 +17982,7 @@
       <c r="D82" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E82" s="14">
+      <c r="E82" s="151">
         <v>89</v>
       </c>
       <c r="F82" s="14">
@@ -18124,7 +18167,7 @@
       <c r="D83" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E83" s="14">
+      <c r="E83" s="151">
         <v>141</v>
       </c>
       <c r="F83" s="14">
@@ -18303,7 +18346,7 @@
       <c r="D84" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E84" s="14">
+      <c r="E84" s="151">
         <v>92</v>
       </c>
       <c r="F84" s="14">
@@ -18313,7 +18356,7 @@
         <v>15</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="I84" s="2">
         <v>29.3</v>
@@ -18468,7 +18511,7 @@
         <v>793</v>
       </c>
       <c r="BT84" s="21" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="85" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -18484,7 +18527,7 @@
       <c r="D85" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E85" s="14">
+      <c r="E85" s="151">
         <v>93</v>
       </c>
       <c r="F85" s="14">
@@ -18494,7 +18537,7 @@
         <v>15</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="I85" s="2">
         <v>28.5</v>
@@ -18643,7 +18686,7 @@
         <v>205</v>
       </c>
       <c r="BR85" s="18" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="BS85" s="18" t="s">
         <v>794</v>
@@ -18654,13 +18697,17 @@
     </row>
     <row r="86" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="124"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
+      <c r="B86" s="14">
+        <v>20250721</v>
+      </c>
+      <c r="C86" s="14">
+        <v>20250812</v>
+      </c>
       <c r="D86" s="14" t="s">
         <v>44</v>
       </c>
       <c r="E86" s="14">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F86" s="14">
         <v>4800993</v>
@@ -18669,21 +18716,35 @@
         <v>15</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>804</v>
-      </c>
-      <c r="I86" s="2"/>
+        <v>803</v>
+      </c>
+      <c r="I86" s="2">
+        <v>29</v>
+      </c>
       <c r="J86" s="2"/>
-      <c r="K86" s="14"/>
-      <c r="L86" s="14"/>
-      <c r="M86" s="100"/>
-      <c r="N86" s="18"/>
+      <c r="K86" s="14">
+        <v>44.389000000000003</v>
+      </c>
+      <c r="L86" s="14">
+        <v>-63.354599999999998</v>
+      </c>
+      <c r="M86" s="100">
+        <v>0.58194444444444449</v>
+      </c>
+      <c r="N86" s="18">
+        <v>42.47</v>
+      </c>
       <c r="O86" s="18"/>
       <c r="P86" s="18"/>
-      <c r="Q86" s="18"/>
+      <c r="Q86" s="18">
+        <v>-61.44</v>
+      </c>
       <c r="R86" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="S86" s="2"/>
+        <v>806</v>
+      </c>
+      <c r="S86" s="2">
+        <v>22</v>
+      </c>
       <c r="T86" s="2"/>
       <c r="U86" s="2"/>
       <c r="V86" s="2"/>
@@ -18703,9 +18764,15 @@
         <v>781</v>
       </c>
       <c r="AD86" s="18"/>
-      <c r="AE86" s="2"/>
-      <c r="AF86" s="2"/>
-      <c r="AG86" s="2"/>
+      <c r="AE86" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF86" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG86" s="2">
+        <v>2</v>
+      </c>
       <c r="AH86" s="2">
         <v>1022.25</v>
       </c>
@@ -18745,7 +18812,7 @@
         <v>761</v>
       </c>
       <c r="BB86" s="22" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="BC86" s="22" t="s">
         <v>420</v>
@@ -18754,7 +18821,7 @@
         <v>796</v>
       </c>
       <c r="BE86" s="22" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="BF86" s="22"/>
       <c r="BG86" s="22"/>
@@ -18784,19 +18851,33 @@
       <c r="BQ86" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BR86" s="18"/>
+      <c r="BR86" s="18" t="s">
+        <v>791</v>
+      </c>
       <c r="BS86" s="18"/>
-      <c r="BT86" s="21"/>
+      <c r="BT86" s="21" t="s">
+        <v>807</v>
+      </c>
     </row>
     <row r="87" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="124"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="18"/>
+      <c r="D87" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E87" s="14">
+        <v>95</v>
+      </c>
+      <c r="F87" s="14">
+        <v>4800937</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" s="18" t="s">
+        <v>811</v>
+      </c>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="14"/>
@@ -18806,27 +18887,47 @@
       <c r="O87" s="18"/>
       <c r="P87" s="18"/>
       <c r="Q87" s="18"/>
-      <c r="R87" s="2"/>
+      <c r="R87" s="2" t="s">
+        <v>444</v>
+      </c>
       <c r="S87" s="2"/>
       <c r="T87" s="2"/>
       <c r="U87" s="2"/>
       <c r="V87" s="2"/>
-      <c r="W87" s="18"/>
-      <c r="X87" s="18"/>
+      <c r="W87" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X87" s="18">
+        <v>1</v>
+      </c>
       <c r="Y87" s="18"/>
-      <c r="Z87" s="18"/>
+      <c r="Z87" s="18" t="s">
+        <v>183</v>
+      </c>
       <c r="AA87" s="18"/>
       <c r="AB87" s="18"/>
-      <c r="AC87" s="18"/>
+      <c r="AC87" s="18" t="s">
+        <v>781</v>
+      </c>
       <c r="AD87" s="18"/>
       <c r="AE87" s="2"/>
       <c r="AF87" s="2"/>
       <c r="AG87" s="2"/>
-      <c r="AH87" s="2"/>
-      <c r="AI87" s="18"/>
-      <c r="AJ87" s="18"/>
-      <c r="AK87" s="18"/>
-      <c r="AL87" s="14"/>
+      <c r="AH87" s="2">
+        <v>1022</v>
+      </c>
+      <c r="AI87" s="18">
+        <v>20250811</v>
+      </c>
+      <c r="AJ87" s="18" t="s">
+        <v>752</v>
+      </c>
+      <c r="AK87" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="AL87" s="14">
+        <v>32</v>
+      </c>
       <c r="AM87" s="20"/>
       <c r="AN87" s="22"/>
       <c r="AO87" s="22"/>
@@ -18836,28 +18937,60 @@
       <c r="AS87" s="22"/>
       <c r="AT87" s="22"/>
       <c r="AU87" s="22"/>
-      <c r="AV87" s="10"/>
-      <c r="AW87" s="16"/>
-      <c r="AX87" s="22"/>
+      <c r="AV87" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW87" s="16">
+        <v>45629</v>
+      </c>
+      <c r="AX87" s="22" t="s">
+        <v>461</v>
+      </c>
       <c r="AY87" s="22"/>
       <c r="AZ87" s="22"/>
-      <c r="BA87" s="22"/>
-      <c r="BB87" s="22"/>
-      <c r="BC87" s="22"/>
-      <c r="BD87" s="22"/>
-      <c r="BE87" s="22"/>
+      <c r="BA87" s="22" t="s">
+        <v>760</v>
+      </c>
+      <c r="BB87" s="22" t="s">
+        <v>809</v>
+      </c>
+      <c r="BC87" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="BD87" s="22" t="s">
+        <v>795</v>
+      </c>
+      <c r="BE87" s="22" t="s">
+        <v>797</v>
+      </c>
       <c r="BF87" s="22"/>
       <c r="BG87" s="22"/>
       <c r="BH87" s="22"/>
-      <c r="BI87" s="20"/>
-      <c r="BJ87" s="146"/>
-      <c r="BK87" s="22"/>
-      <c r="BL87" s="22"/>
-      <c r="BM87" s="22"/>
-      <c r="BN87" s="22"/>
+      <c r="BI87" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ87" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK87" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="BL87" s="22" t="s">
+        <v>749</v>
+      </c>
+      <c r="BM87" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="BN87" s="2">
+        <v>1272212</v>
+      </c>
       <c r="BO87" s="2"/>
-      <c r="BP87" s="149"/>
-      <c r="BQ87" s="14"/>
+      <c r="BP87" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="BQ87" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="BR87" s="18"/>
       <c r="BS87" s="18"/>
       <c r="BT87" s="21"/>
@@ -18985,7 +19118,7 @@
       <c r="AT89" s="22"/>
       <c r="AU89" s="22"/>
       <c r="AV89" s="10" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AW89" s="16"/>
       <c r="AX89" s="22"/>
@@ -19136,7 +19269,7 @@
         <v>760</v>
       </c>
       <c r="BB91" s="78" t="s">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="BC91" s="78"/>
       <c r="BD91" s="78" t="s">
@@ -19226,8 +19359,8 @@
       <c r="BK92" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="BL92" s="133" t="s">
-        <v>589</v>
+      <c r="BL92" s="145" t="s">
+        <v>810</v>
       </c>
       <c r="BM92" s="38"/>
       <c r="BN92" s="38"/>
@@ -19294,7 +19427,9 @@
       <c r="BD93" s="78" t="s">
         <v>773</v>
       </c>
-      <c r="BE93" s="78"/>
+      <c r="BE93" s="78" t="s">
+        <v>804</v>
+      </c>
       <c r="BF93" s="78"/>
       <c r="BG93" s="78"/>
       <c r="BH93" s="78"/>
@@ -19365,7 +19500,9 @@
       <c r="BD94" s="78" t="s">
         <v>774</v>
       </c>
-      <c r="BE94" s="78"/>
+      <c r="BE94" s="78" t="s">
+        <v>808</v>
+      </c>
       <c r="BF94" s="78"/>
       <c r="BG94" s="78"/>
       <c r="BH94" s="78"/>
@@ -19374,7 +19511,7 @@
       <c r="BK94" s="38" t="s">
         <v>515</v>
       </c>
-      <c r="BL94" s="145" t="s">
+      <c r="BL94" s="153" t="s">
         <v>516</v>
       </c>
       <c r="BM94" s="38"/>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08C273C-E22C-453C-8614-A8A9C912E416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D70DB76-4A74-486B-B568-66C99E5F145C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2753" uniqueCount="812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="816">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2467,9 +2467,6 @@
     <t>GLI2025_SEA022_111</t>
   </si>
   <si>
-    <t>not fully cal</t>
-  </si>
-  <si>
     <t>copied on ext dr to empty dropbox</t>
   </si>
   <si>
@@ -2489,6 +2486,21 @@
   </si>
   <si>
     <t>GLI2025_SEA032_095</t>
+  </si>
+  <si>
+    <t>20250825</t>
+  </si>
+  <si>
+    <t>Sigma-T(zodiak)/</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA022_113</t>
+  </si>
+  <si>
+    <t>1540746</t>
+  </si>
+  <si>
+    <t>internal waves on shelf break</t>
   </si>
 </sst>
 </file>
@@ -2639,7 +2651,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -2820,6 +2832,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2827,7 +2852,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3205,6 +3230,18 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3608,7 +3645,7 @@
     <row r="1" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="24"/>
       <c r="C1" s="152" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D1" s="94" t="s">
         <v>432</v>
@@ -18334,8 +18371,8 @@
       </c>
     </row>
     <row r="84" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="124" t="s">
-        <v>189</v>
+      <c r="A84" s="124">
+        <v>3</v>
       </c>
       <c r="B84" s="14">
         <v>20250606</v>
@@ -18696,7 +18733,9 @@
       </c>
     </row>
     <row r="86" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="124"/>
+      <c r="A86" s="124">
+        <v>4</v>
+      </c>
       <c r="B86" s="14">
         <v>20250721</v>
       </c>
@@ -18721,11 +18760,13 @@
       <c r="I86" s="2">
         <v>29</v>
       </c>
-      <c r="J86" s="2"/>
-      <c r="K86" s="14">
+      <c r="J86" s="2">
+        <v>23.9</v>
+      </c>
+      <c r="K86" s="156">
         <v>44.389000000000003</v>
       </c>
-      <c r="L86" s="14">
+      <c r="L86" s="156">
         <v>-63.354599999999998</v>
       </c>
       <c r="M86" s="100">
@@ -18734,20 +18775,31 @@
       <c r="N86" s="18">
         <v>42.47</v>
       </c>
-      <c r="O86" s="18"/>
-      <c r="P86" s="18"/>
+      <c r="O86" s="18">
+        <v>-63.39</v>
+      </c>
+      <c r="P86" s="18">
+        <v>44.51</v>
+      </c>
       <c r="Q86" s="18">
         <v>-61.44</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="S86" s="2">
         <v>22</v>
       </c>
-      <c r="T86" s="2"/>
-      <c r="U86" s="2"/>
-      <c r="V86" s="2"/>
+      <c r="T86" s="2">
+        <v>724</v>
+      </c>
+      <c r="U86" s="2">
+        <v>1068</v>
+      </c>
+      <c r="V86" s="2">
+        <f>925*2</f>
+        <v>1850</v>
+      </c>
       <c r="W86" s="18" t="s">
         <v>36</v>
       </c>
@@ -18841,7 +18893,7 @@
       <c r="BM86" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="BN86" s="22" t="s">
+      <c r="BN86" s="79" t="s">
         <v>702</v>
       </c>
       <c r="BO86" s="2"/>
@@ -18856,12 +18908,16 @@
       </c>
       <c r="BS86" s="18"/>
       <c r="BT86" s="21" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="87" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="124"/>
-      <c r="B87" s="14"/>
+      <c r="A87" s="124">
+        <v>5</v>
+      </c>
+      <c r="B87" s="14">
+        <v>20250904</v>
+      </c>
       <c r="C87" s="14"/>
       <c r="D87" s="14" t="s">
         <v>53</v>
@@ -18876,13 +18932,21 @@
         <v>15</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>811</v>
-      </c>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="14"/>
-      <c r="L87" s="14"/>
-      <c r="M87" s="100"/>
+        <v>810</v>
+      </c>
+      <c r="I87" s="2">
+        <v>29.1</v>
+      </c>
+      <c r="J87" s="154"/>
+      <c r="K87" s="157">
+        <v>44.389499999999998</v>
+      </c>
+      <c r="L87" s="157">
+        <v>-63.362900000000003</v>
+      </c>
+      <c r="M87" s="155">
+        <v>0.56597222222222221</v>
+      </c>
       <c r="N87" s="18"/>
       <c r="O87" s="18"/>
       <c r="P87" s="18"/>
@@ -18910,9 +18974,15 @@
         <v>781</v>
       </c>
       <c r="AD87" s="18"/>
-      <c r="AE87" s="2"/>
-      <c r="AF87" s="2"/>
-      <c r="AG87" s="2"/>
+      <c r="AE87" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF87" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG87" s="2">
+        <v>0</v>
+      </c>
       <c r="AH87" s="2">
         <v>1022</v>
       </c>
@@ -18952,7 +19022,7 @@
         <v>760</v>
       </c>
       <c r="BB87" s="22" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="BC87" s="22" t="s">
         <v>420</v>
@@ -18991,49 +19061,85 @@
       <c r="BQ87" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BR87" s="18"/>
+      <c r="BR87" s="18" t="s">
+        <v>812</v>
+      </c>
       <c r="BS87" s="18"/>
-      <c r="BT87" s="21"/>
+      <c r="BT87" s="21" t="s">
+        <v>815</v>
+      </c>
     </row>
     <row r="88" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="124"/>
+      <c r="A88" s="124">
+        <v>6</v>
+      </c>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="H88" s="18"/>
+      <c r="D88" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E88" s="14">
+        <v>113</v>
+      </c>
+      <c r="F88" s="14">
+        <v>4800993</v>
+      </c>
+      <c r="G88" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="18" t="s">
+        <v>813</v>
+      </c>
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
-      <c r="K88" s="14"/>
-      <c r="L88" s="14"/>
+      <c r="K88" s="11"/>
+      <c r="L88" s="11"/>
       <c r="M88" s="100"/>
       <c r="N88" s="18"/>
       <c r="O88" s="18"/>
       <c r="P88" s="18"/>
       <c r="Q88" s="18"/>
-      <c r="R88" s="2"/>
+      <c r="R88" s="2" t="s">
+        <v>444</v>
+      </c>
       <c r="S88" s="2"/>
       <c r="T88" s="2"/>
       <c r="U88" s="2"/>
       <c r="V88" s="2"/>
-      <c r="W88" s="18"/>
-      <c r="X88" s="18"/>
+      <c r="W88" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X88" s="18">
+        <v>1</v>
+      </c>
       <c r="Y88" s="18"/>
-      <c r="Z88" s="18"/>
+      <c r="Z88" s="18" t="s">
+        <v>183</v>
+      </c>
       <c r="AA88" s="18"/>
       <c r="AB88" s="18"/>
-      <c r="AC88" s="18"/>
+      <c r="AC88" s="18" t="s">
+        <v>781</v>
+      </c>
       <c r="AD88" s="18"/>
       <c r="AE88" s="2"/>
       <c r="AF88" s="2"/>
       <c r="AG88" s="2"/>
-      <c r="AH88" s="2"/>
-      <c r="AI88" s="18"/>
-      <c r="AJ88" s="18"/>
-      <c r="AK88" s="18"/>
-      <c r="AL88" s="14"/>
+      <c r="AH88" s="2">
+        <v>1022.5</v>
+      </c>
+      <c r="AI88" s="18">
+        <v>20250908</v>
+      </c>
+      <c r="AJ88" s="18" t="s">
+        <v>752</v>
+      </c>
+      <c r="AK88" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="AL88" s="14">
+        <v>30</v>
+      </c>
       <c r="AM88" s="20"/>
       <c r="AN88" s="22"/>
       <c r="AO88" s="22"/>
@@ -19043,34 +19149,68 @@
       <c r="AS88" s="22"/>
       <c r="AT88" s="22"/>
       <c r="AU88" s="22"/>
-      <c r="AV88" s="10"/>
-      <c r="AW88" s="16"/>
-      <c r="AX88" s="22"/>
+      <c r="AV88" s="10">
+        <v>4551</v>
+      </c>
+      <c r="AW88" s="16">
+        <v>42691</v>
+      </c>
+      <c r="AX88" s="22" t="s">
+        <v>461</v>
+      </c>
       <c r="AY88" s="22"/>
       <c r="AZ88" s="22"/>
-      <c r="BA88" s="22"/>
-      <c r="BB88" s="22"/>
-      <c r="BC88" s="22"/>
-      <c r="BD88" s="22"/>
-      <c r="BE88" s="22"/>
+      <c r="BA88" s="22" t="s">
+        <v>761</v>
+      </c>
+      <c r="BB88" s="22" t="s">
+        <v>797</v>
+      </c>
+      <c r="BC88" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="BD88" s="22" t="s">
+        <v>796</v>
+      </c>
+      <c r="BE88" s="22" t="s">
+        <v>797</v>
+      </c>
       <c r="BF88" s="22"/>
       <c r="BG88" s="22"/>
       <c r="BH88" s="22"/>
-      <c r="BI88" s="20"/>
-      <c r="BJ88" s="146"/>
-      <c r="BK88" s="22"/>
-      <c r="BL88" s="22"/>
-      <c r="BM88" s="22"/>
-      <c r="BN88" s="22"/>
+      <c r="BI88" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ88" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK88" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="BL88" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="BM88" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BN88" s="22" t="s">
+        <v>814</v>
+      </c>
       <c r="BO88" s="2"/>
-      <c r="BP88" s="149"/>
-      <c r="BQ88" s="14"/>
+      <c r="BP88" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="BQ88" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="BR88" s="18"/>
       <c r="BS88" s="18"/>
       <c r="BT88" s="21"/>
     </row>
     <row r="89" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="124"/>
+      <c r="A89" s="124">
+        <v>7</v>
+      </c>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
@@ -19146,7 +19286,9 @@
       <c r="BT89" s="21"/>
     </row>
     <row r="90" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="124"/>
+      <c r="A90" s="124">
+        <v>8</v>
+      </c>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -19360,7 +19502,7 @@
         <v>117</v>
       </c>
       <c r="BL92" s="145" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="BM92" s="38"/>
       <c r="BN92" s="38"/>
@@ -19428,7 +19570,7 @@
         <v>773</v>
       </c>
       <c r="BE93" s="78" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="BF93" s="78"/>
       <c r="BG93" s="78"/>
@@ -19501,7 +19643,7 @@
         <v>774</v>
       </c>
       <c r="BE94" s="78" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="BF94" s="78"/>
       <c r="BG94" s="78"/>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D70DB76-4A74-486B-B568-66C99E5F145C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F91BC11-E862-4C92-8A0D-F26EC4617911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="827">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2449,9 +2450,6 @@
     <t>20250612</t>
   </si>
   <si>
-    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
-  </si>
-  <si>
     <t>GLI2025_SEA032_092</t>
   </si>
   <si>
@@ -2491,16 +2489,52 @@
     <t>20250825</t>
   </si>
   <si>
-    <t>Sigma-T(zodiak)/</t>
-  </si>
-  <si>
     <t>GLI2025_SEA022_113</t>
   </si>
   <si>
     <t>1540746</t>
   </si>
   <si>
-    <t>internal waves on shelf break</t>
+    <t>GL1-GL2-GL3-GL7-Further-GL7-GL3-GL2-GL1-TRI-DR</t>
+  </si>
+  <si>
+    <t>battery min</t>
+  </si>
+  <si>
+    <t>battery max</t>
+  </si>
+  <si>
+    <t>battery min (%)</t>
+  </si>
+  <si>
+    <t>GPCTD</t>
+  </si>
+  <si>
+    <t>LEGATO</t>
+  </si>
+  <si>
+    <t>ranked</t>
+  </si>
+  <si>
+    <t>internal waves on shelf break, glider going further than HL7 for the first time ever, might be in a warm core ring  (23.8C at surface at HL7), lost 1 day coming back to HL7, increased pitch and speed to get out of eddy</t>
+  </si>
+  <si>
+    <t>AZMP fall 2025</t>
+  </si>
+  <si>
+    <t>Sigma-T</t>
+  </si>
+  <si>
+    <t>AZMP cruise sampled HL2 right during glider deployment</t>
+  </si>
+  <si>
+    <t>Burned wire-2</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA032_097</t>
+  </si>
+  <si>
+    <t>with TCM on nose</t>
   </si>
 </sst>
 </file>
@@ -2852,7 +2886,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3243,6 +3277,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3572,7 +3618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CY98"/>
+  <dimension ref="A1:CY100"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.1796875" customWidth="1"/>
@@ -3645,7 +3691,7 @@
     <row r="1" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="24"/>
       <c r="C1" s="152" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D1" s="94" t="s">
         <v>432</v>
@@ -14619,7 +14665,7 @@
         <v>229</v>
       </c>
       <c r="BJ63" s="42" t="s">
-        <v>171</v>
+        <v>824</v>
       </c>
       <c r="BK63" s="96" t="s">
         <v>246</v>
@@ -14982,7 +15028,7 @@
         <v>229</v>
       </c>
       <c r="BJ65" s="49" t="s">
-        <v>171</v>
+        <v>824</v>
       </c>
       <c r="BK65" s="49">
         <v>201383</v>
@@ -15903,7 +15949,7 @@
         <v>229</v>
       </c>
       <c r="BJ70" s="49" t="s">
-        <v>171</v>
+        <v>824</v>
       </c>
       <c r="BK70" s="22" t="s">
         <v>515</v>
@@ -16090,7 +16136,7 @@
         <v>229</v>
       </c>
       <c r="BJ71" s="49" t="s">
-        <v>171</v>
+        <v>824</v>
       </c>
       <c r="BK71" s="22" t="s">
         <v>515</v>
@@ -17233,7 +17279,7 @@
         <v>229</v>
       </c>
       <c r="BJ77" s="96" t="s">
-        <v>171</v>
+        <v>824</v>
       </c>
       <c r="BK77" s="38" t="s">
         <v>98</v>
@@ -18393,7 +18439,7 @@
         <v>15</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="I84" s="2">
         <v>29.3</v>
@@ -18548,7 +18594,7 @@
         <v>793</v>
       </c>
       <c r="BT84" s="21" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="85" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -18574,7 +18620,7 @@
         <v>15</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="I85" s="2">
         <v>28.5</v>
@@ -18723,7 +18769,7 @@
         <v>205</v>
       </c>
       <c r="BR85" s="18" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="BS85" s="18" t="s">
         <v>794</v>
@@ -18755,7 +18801,7 @@
         <v>15</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I86" s="2">
         <v>29</v>
@@ -18785,7 +18831,7 @@
         <v>-61.44</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="S86" s="2">
         <v>22</v>
@@ -18893,7 +18939,7 @@
       <c r="BM86" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="BN86" s="79" t="s">
+      <c r="BN86" s="22" t="s">
         <v>702</v>
       </c>
       <c r="BO86" s="2"/>
@@ -18908,7 +18954,7 @@
       </c>
       <c r="BS86" s="18"/>
       <c r="BT86" s="21" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="87" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -18918,7 +18964,9 @@
       <c r="B87" s="14">
         <v>20250904</v>
       </c>
-      <c r="C87" s="14"/>
+      <c r="C87" s="14">
+        <v>20250929</v>
+      </c>
       <c r="D87" s="14" t="s">
         <v>53</v>
       </c>
@@ -18932,12 +18980,14 @@
         <v>15</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="I87" s="2">
         <v>29.1</v>
       </c>
-      <c r="J87" s="154"/>
+      <c r="J87" s="154">
+        <v>25</v>
+      </c>
       <c r="K87" s="157">
         <v>44.389499999999998</v>
       </c>
@@ -18947,17 +18997,34 @@
       <c r="M87" s="155">
         <v>0.56597222222222221</v>
       </c>
-      <c r="N87" s="18"/>
-      <c r="O87" s="18"/>
-      <c r="P87" s="18"/>
-      <c r="Q87" s="18"/>
+      <c r="N87" s="18">
+        <v>42.23</v>
+      </c>
+      <c r="O87" s="18">
+        <v>-63.37</v>
+      </c>
+      <c r="P87" s="18">
+        <v>44.4</v>
+      </c>
+      <c r="Q87" s="18">
+        <v>-61.18</v>
+      </c>
       <c r="R87" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="S87" s="2"/>
-      <c r="T87" s="2"/>
-      <c r="U87" s="2"/>
-      <c r="V87" s="2"/>
+        <v>813</v>
+      </c>
+      <c r="S87" s="2">
+        <v>25</v>
+      </c>
+      <c r="T87" s="2">
+        <v>658</v>
+      </c>
+      <c r="U87" s="2">
+        <v>934</v>
+      </c>
+      <c r="V87" s="2">
+        <f>U87*2</f>
+        <v>1868</v>
+      </c>
       <c r="W87" s="18" t="s">
         <v>36</v>
       </c>
@@ -18975,13 +19042,13 @@
       </c>
       <c r="AD87" s="18"/>
       <c r="AE87" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF87" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG87" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH87" s="2">
         <v>1022</v>
@@ -19022,7 +19089,7 @@
         <v>760</v>
       </c>
       <c r="BB87" s="22" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="BC87" s="22" t="s">
         <v>420</v>
@@ -19051,7 +19118,7 @@
       <c r="BM87" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="BN87" s="2">
+      <c r="BN87" s="163">
         <v>1272212</v>
       </c>
       <c r="BO87" s="2"/>
@@ -19062,24 +19129,26 @@
         <v>205</v>
       </c>
       <c r="BR87" s="18" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="BS87" s="18"/>
       <c r="BT87" s="21" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
     </row>
     <row r="88" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" s="124">
         <v>6</v>
       </c>
-      <c r="B88" s="14"/>
+      <c r="B88" s="14">
+        <v>20251006</v>
+      </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14" t="s">
         <v>44</v>
       </c>
       <c r="E88" s="14">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F88" s="14">
         <v>4800993</v>
@@ -19088,13 +19157,21 @@
         <v>15</v>
       </c>
       <c r="H88" s="18" t="s">
-        <v>813</v>
-      </c>
-      <c r="I88" s="2"/>
+        <v>811</v>
+      </c>
+      <c r="I88" s="2">
+        <v>29.2</v>
+      </c>
       <c r="J88" s="2"/>
-      <c r="K88" s="11"/>
-      <c r="L88" s="11"/>
-      <c r="M88" s="100"/>
+      <c r="K88" s="11">
+        <v>44.476999999999997</v>
+      </c>
+      <c r="L88" s="11">
+        <v>-63.432499999999997</v>
+      </c>
+      <c r="M88" s="100">
+        <v>0.55694444444444446</v>
+      </c>
       <c r="N88" s="18"/>
       <c r="O88" s="18"/>
       <c r="P88" s="18"/>
@@ -19194,18 +19271,24 @@
         <v>137</v>
       </c>
       <c r="BN88" s="22" t="s">
-        <v>814</v>
-      </c>
-      <c r="BO88" s="2"/>
+        <v>812</v>
+      </c>
+      <c r="BO88" s="2" t="s">
+        <v>821</v>
+      </c>
       <c r="BP88" s="2" t="s">
         <v>670</v>
       </c>
       <c r="BQ88" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BR88" s="18"/>
+      <c r="BR88" s="18" t="s">
+        <v>822</v>
+      </c>
       <c r="BS88" s="18"/>
-      <c r="BT88" s="21"/>
+      <c r="BT88" s="21" t="s">
+        <v>823</v>
+      </c>
     </row>
     <row r="89" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="124">
@@ -19213,11 +19296,21 @@
       </c>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
-      <c r="D89" s="14"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="14"/>
-      <c r="H89" s="18"/>
+      <c r="D89" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E89" s="14">
+        <v>97</v>
+      </c>
+      <c r="F89" s="14">
+        <v>4800937</v>
+      </c>
+      <c r="G89" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="18" t="s">
+        <v>825</v>
+      </c>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="14"/>
@@ -19227,27 +19320,47 @@
       <c r="O89" s="18"/>
       <c r="P89" s="18"/>
       <c r="Q89" s="18"/>
-      <c r="R89" s="2"/>
+      <c r="R89" s="2" t="s">
+        <v>444</v>
+      </c>
       <c r="S89" s="2"/>
       <c r="T89" s="2"/>
       <c r="U89" s="2"/>
       <c r="V89" s="2"/>
-      <c r="W89" s="18"/>
-      <c r="X89" s="18"/>
+      <c r="W89" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X89" s="18">
+        <v>1</v>
+      </c>
       <c r="Y89" s="18"/>
-      <c r="Z89" s="18"/>
+      <c r="Z89" s="18" t="s">
+        <v>183</v>
+      </c>
       <c r="AA89" s="18"/>
       <c r="AB89" s="18"/>
-      <c r="AC89" s="18"/>
+      <c r="AC89" s="18" t="s">
+        <v>781</v>
+      </c>
       <c r="AD89" s="18"/>
       <c r="AE89" s="2"/>
       <c r="AF89" s="2"/>
       <c r="AG89" s="2"/>
-      <c r="AH89" s="2"/>
-      <c r="AI89" s="18"/>
-      <c r="AJ89" s="18"/>
-      <c r="AK89" s="18"/>
-      <c r="AL89" s="14"/>
+      <c r="AH89" s="2">
+        <v>1023</v>
+      </c>
+      <c r="AI89" s="18">
+        <v>20251014</v>
+      </c>
+      <c r="AJ89" s="18" t="s">
+        <v>752</v>
+      </c>
+      <c r="AK89" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="AL89" s="14">
+        <v>32</v>
+      </c>
       <c r="AM89" s="20"/>
       <c r="AN89" s="22"/>
       <c r="AO89" s="22"/>
@@ -19258,37 +19371,67 @@
       <c r="AT89" s="22"/>
       <c r="AU89" s="22"/>
       <c r="AV89" s="10" t="s">
-        <v>798</v>
-      </c>
-      <c r="AW89" s="16"/>
-      <c r="AX89" s="22"/>
+        <v>86</v>
+      </c>
+      <c r="AW89" s="16">
+        <v>45629</v>
+      </c>
+      <c r="AX89" s="22" t="s">
+        <v>461</v>
+      </c>
       <c r="AY89" s="22"/>
       <c r="AZ89" s="22"/>
-      <c r="BA89" s="22"/>
-      <c r="BB89" s="22"/>
-      <c r="BC89" s="22"/>
-      <c r="BD89" s="22"/>
-      <c r="BE89" s="22"/>
+      <c r="BA89" s="22" t="s">
+        <v>760</v>
+      </c>
+      <c r="BB89" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="BC89" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="BD89" s="22" t="s">
+        <v>795</v>
+      </c>
+      <c r="BE89" s="22" t="s">
+        <v>797</v>
+      </c>
       <c r="BF89" s="22"/>
       <c r="BG89" s="22"/>
       <c r="BH89" s="22"/>
-      <c r="BI89" s="20"/>
-      <c r="BJ89" s="146"/>
-      <c r="BK89" s="22"/>
-      <c r="BL89" s="22"/>
-      <c r="BM89" s="22"/>
-      <c r="BN89" s="22"/>
+      <c r="BI89" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ89" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK89" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="BL89" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="BM89" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="BN89" s="2">
+        <v>1272212</v>
+      </c>
       <c r="BO89" s="2"/>
-      <c r="BP89" s="149"/>
-      <c r="BQ89" s="14"/>
+      <c r="BP89" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="BQ89" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="BR89" s="18"/>
       <c r="BS89" s="18"/>
-      <c r="BT89" s="21"/>
+      <c r="BT89" s="21" t="s">
+        <v>826</v>
+      </c>
     </row>
     <row r="90" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="124">
-        <v>8</v>
-      </c>
+      <c r="A90" s="124"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -19300,7 +19443,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="14"/>
       <c r="L90" s="14"/>
-      <c r="M90" s="2"/>
+      <c r="M90" s="100"/>
       <c r="N90" s="18"/>
       <c r="O90" s="18"/>
       <c r="P90" s="18"/>
@@ -19335,8 +19478,8 @@
       <c r="AS90" s="22"/>
       <c r="AT90" s="22"/>
       <c r="AU90" s="22"/>
-      <c r="AV90" s="20"/>
-      <c r="AW90" s="22"/>
+      <c r="AV90" s="10"/>
+      <c r="AW90" s="16"/>
       <c r="AX90" s="22"/>
       <c r="AY90" s="22"/>
       <c r="AZ90" s="22"/>
@@ -19350,12 +19493,8 @@
       <c r="BH90" s="22"/>
       <c r="BI90" s="20"/>
       <c r="BJ90" s="146"/>
-      <c r="BK90" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="BL90" s="150" t="s">
-        <v>749</v>
-      </c>
+      <c r="BK90" s="22"/>
+      <c r="BL90" s="22"/>
       <c r="BM90" s="22"/>
       <c r="BN90" s="22"/>
       <c r="BO90" s="2"/>
@@ -19365,153 +19504,159 @@
       <c r="BS90" s="18"/>
       <c r="BT90" s="21"/>
     </row>
-    <row r="91" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="116"/>
-      <c r="C91" s="116"/>
-      <c r="D91" s="116"/>
-      <c r="E91" s="116"/>
-      <c r="F91" s="116"/>
-      <c r="G91" s="116"/>
-      <c r="H91" s="77"/>
-      <c r="K91" s="116"/>
-      <c r="L91" s="116"/>
-      <c r="N91" s="77"/>
-      <c r="O91" s="77"/>
-      <c r="P91" s="77"/>
-      <c r="Q91" s="77"/>
-      <c r="W91" s="77"/>
-      <c r="X91" s="77"/>
-      <c r="Y91" s="77"/>
-      <c r="Z91" s="77"/>
-      <c r="AA91" s="77"/>
-      <c r="AB91" s="77"/>
-      <c r="AC91" s="77"/>
-      <c r="AD91" s="77"/>
-      <c r="AI91" s="77"/>
-      <c r="AJ91" s="77"/>
-      <c r="AK91" s="77"/>
-      <c r="AL91" s="116"/>
-      <c r="AM91" s="27"/>
-      <c r="AN91" s="26"/>
-      <c r="AO91" s="78"/>
-      <c r="AP91" s="117"/>
-      <c r="AQ91" s="27"/>
-      <c r="AR91" s="26"/>
-      <c r="AS91" s="78"/>
-      <c r="AT91" s="78"/>
-      <c r="AU91" s="78"/>
-      <c r="AV91" s="117"/>
-      <c r="AW91" s="78"/>
-      <c r="AX91" s="78"/>
-      <c r="AY91" s="78"/>
-      <c r="AZ91" s="148" t="s">
-        <v>765</v>
-      </c>
-      <c r="BA91" s="6" t="s">
-        <v>760</v>
-      </c>
-      <c r="BB91" s="78" t="s">
-        <v>778</v>
-      </c>
-      <c r="BC91" s="78"/>
-      <c r="BD91" s="78" t="s">
-        <v>795</v>
-      </c>
-      <c r="BE91" s="78"/>
-      <c r="BF91" s="78"/>
-      <c r="BG91" s="78"/>
-      <c r="BH91" s="78"/>
-      <c r="BI91" s="117"/>
-      <c r="BJ91" s="118"/>
-      <c r="BK91" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="BL91" s="144" t="s">
-        <v>588</v>
-      </c>
-      <c r="BM91" s="38"/>
-      <c r="BN91" s="38"/>
-      <c r="BO91" s="3"/>
-      <c r="BP91" s="121"/>
-      <c r="BQ91" s="45"/>
-      <c r="BR91" s="77"/>
-      <c r="BS91" s="77"/>
-      <c r="BT91" s="119"/>
+    <row r="91" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="124"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="18"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="14"/>
+      <c r="L91" s="14"/>
+      <c r="M91" s="100"/>
+      <c r="N91" s="18"/>
+      <c r="O91" s="18"/>
+      <c r="P91" s="18"/>
+      <c r="Q91" s="18"/>
+      <c r="R91" s="2"/>
+      <c r="S91" s="2"/>
+      <c r="T91" s="2"/>
+      <c r="U91" s="2"/>
+      <c r="V91" s="2"/>
+      <c r="W91" s="18"/>
+      <c r="X91" s="18"/>
+      <c r="Y91" s="18"/>
+      <c r="Z91" s="18"/>
+      <c r="AA91" s="18"/>
+      <c r="AB91" s="18"/>
+      <c r="AC91" s="18"/>
+      <c r="AD91" s="18"/>
+      <c r="AE91" s="2"/>
+      <c r="AF91" s="2"/>
+      <c r="AG91" s="2"/>
+      <c r="AH91" s="2"/>
+      <c r="AI91" s="18"/>
+      <c r="AJ91" s="18"/>
+      <c r="AK91" s="18"/>
+      <c r="AL91" s="14"/>
+      <c r="AM91" s="20"/>
+      <c r="AN91" s="22"/>
+      <c r="AO91" s="22"/>
+      <c r="AP91" s="20"/>
+      <c r="AQ91" s="20"/>
+      <c r="AR91" s="22"/>
+      <c r="AS91" s="22"/>
+      <c r="AT91" s="22"/>
+      <c r="AU91" s="22"/>
+      <c r="AV91" s="10"/>
+      <c r="AW91" s="16"/>
+      <c r="AX91" s="22"/>
+      <c r="AY91" s="22"/>
+      <c r="AZ91" s="22"/>
+      <c r="BA91" s="22"/>
+      <c r="BB91" s="22"/>
+      <c r="BC91" s="22"/>
+      <c r="BD91" s="22"/>
+      <c r="BE91" s="22"/>
+      <c r="BF91" s="22"/>
+      <c r="BG91" s="22"/>
+      <c r="BH91" s="22"/>
+      <c r="BI91" s="20"/>
+      <c r="BJ91" s="146"/>
+      <c r="BK91" s="22"/>
+      <c r="BL91" s="22"/>
+      <c r="BM91" s="22"/>
+      <c r="BN91" s="22"/>
+      <c r="BO91" s="2"/>
+      <c r="BP91" s="149"/>
+      <c r="BQ91" s="14"/>
+      <c r="BR91" s="18"/>
+      <c r="BS91" s="18"/>
+      <c r="BT91" s="21"/>
     </row>
-    <row r="92" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="116"/>
-      <c r="C92" s="116"/>
-      <c r="D92" s="116"/>
-      <c r="E92" s="116"/>
-      <c r="F92" s="116"/>
-      <c r="G92" s="116"/>
-      <c r="H92" s="77"/>
-      <c r="K92" s="116"/>
-      <c r="L92" s="116"/>
-      <c r="N92" s="77"/>
-      <c r="O92" s="77"/>
-      <c r="P92" s="77"/>
-      <c r="Q92" s="77"/>
-      <c r="W92" s="77"/>
-      <c r="X92" s="77"/>
-      <c r="Y92" s="77"/>
-      <c r="Z92" s="77"/>
-      <c r="AA92" s="77"/>
-      <c r="AB92" s="77"/>
-      <c r="AC92" s="77"/>
-      <c r="AD92" s="77"/>
-      <c r="AI92" s="77"/>
-      <c r="AJ92" s="77"/>
-      <c r="AK92" s="77"/>
-      <c r="AL92" s="116"/>
-      <c r="AM92" s="27"/>
-      <c r="AN92" s="26"/>
-      <c r="AO92" s="78"/>
-      <c r="AP92" s="117"/>
-      <c r="AQ92" s="27"/>
-      <c r="AR92" s="26"/>
-      <c r="AS92" s="78"/>
-      <c r="AT92" s="78"/>
-      <c r="AU92" s="78"/>
-      <c r="AV92" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW92" s="26" t="s">
-        <v>754</v>
-      </c>
-      <c r="AX92" s="78"/>
-      <c r="AY92" s="78"/>
-      <c r="AZ92" s="148"/>
-      <c r="BA92" s="6" t="s">
-        <v>761</v>
-      </c>
-      <c r="BB92" s="78" t="s">
-        <v>779</v>
-      </c>
-      <c r="BC92" s="78"/>
-      <c r="BD92" s="78" t="s">
-        <v>796</v>
-      </c>
-      <c r="BE92" s="78"/>
-      <c r="BF92" s="78"/>
-      <c r="BG92" s="78"/>
-      <c r="BH92" s="78"/>
-      <c r="BI92" s="117"/>
-      <c r="BJ92" s="118"/>
-      <c r="BK92" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="BL92" s="145" t="s">
-        <v>809</v>
-      </c>
-      <c r="BM92" s="38"/>
-      <c r="BN92" s="38"/>
-      <c r="BO92" s="3"/>
-      <c r="BP92" s="120"/>
-      <c r="BQ92" s="35"/>
-      <c r="BR92" s="77"/>
-      <c r="BS92" s="77"/>
-      <c r="BT92" s="119"/>
+    <row r="92" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="124">
+        <v>8</v>
+      </c>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="18"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="14"/>
+      <c r="L92" s="14"/>
+      <c r="M92" s="2"/>
+      <c r="N92" s="18"/>
+      <c r="O92" s="18"/>
+      <c r="P92" s="18"/>
+      <c r="Q92" s="18"/>
+      <c r="R92" s="2"/>
+      <c r="S92" s="2"/>
+      <c r="T92" s="2"/>
+      <c r="U92" s="2"/>
+      <c r="V92" s="2"/>
+      <c r="W92" s="18"/>
+      <c r="X92" s="18"/>
+      <c r="Y92" s="18"/>
+      <c r="Z92" s="18"/>
+      <c r="AA92" s="18"/>
+      <c r="AB92" s="18"/>
+      <c r="AC92" s="18"/>
+      <c r="AD92" s="18"/>
+      <c r="AE92" s="2"/>
+      <c r="AF92" s="2"/>
+      <c r="AG92" s="2"/>
+      <c r="AH92" s="2"/>
+      <c r="AI92" s="18"/>
+      <c r="AJ92" s="18"/>
+      <c r="AK92" s="18"/>
+      <c r="AL92" s="14"/>
+      <c r="AM92" s="20"/>
+      <c r="AN92" s="22"/>
+      <c r="AO92" s="22"/>
+      <c r="AP92" s="20"/>
+      <c r="AQ92" s="20"/>
+      <c r="AR92" s="22"/>
+      <c r="AS92" s="22"/>
+      <c r="AT92" s="22"/>
+      <c r="AU92" s="22"/>
+      <c r="AV92" s="20"/>
+      <c r="AW92" s="22"/>
+      <c r="AX92" s="22"/>
+      <c r="AY92" s="22"/>
+      <c r="AZ92" s="22"/>
+      <c r="BA92" s="22"/>
+      <c r="BB92" s="22"/>
+      <c r="BC92" s="22"/>
+      <c r="BD92" s="22"/>
+      <c r="BE92" s="22"/>
+      <c r="BF92" s="22"/>
+      <c r="BG92" s="22"/>
+      <c r="BH92" s="22"/>
+      <c r="BI92" s="20"/>
+      <c r="BJ92" s="146"/>
+      <c r="BK92" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="BL92" s="150" t="s">
+        <v>749</v>
+      </c>
+      <c r="BM92" s="22"/>
+      <c r="BN92" s="22"/>
+      <c r="BO92" s="2"/>
+      <c r="BP92" s="149"/>
+      <c r="BQ92" s="14"/>
+      <c r="BR92" s="18"/>
+      <c r="BS92" s="18"/>
+      <c r="BT92" s="21"/>
     </row>
     <row r="93" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="116"/>
@@ -19539,55 +19684,49 @@
       <c r="AJ93" s="77"/>
       <c r="AK93" s="77"/>
       <c r="AL93" s="116"/>
-      <c r="AM93" s="117"/>
-      <c r="AN93" s="78"/>
+      <c r="AM93" s="27"/>
+      <c r="AN93" s="26"/>
       <c r="AO93" s="78"/>
       <c r="AP93" s="117"/>
-      <c r="AQ93" s="117"/>
-      <c r="AR93" s="78"/>
+      <c r="AQ93" s="27"/>
+      <c r="AR93" s="26"/>
       <c r="AS93" s="78"/>
       <c r="AT93" s="78"/>
       <c r="AU93" s="78"/>
-      <c r="AV93" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW93" s="26" t="s">
-        <v>753</v>
-      </c>
+      <c r="AV93" s="117"/>
+      <c r="AW93" s="78"/>
       <c r="AX93" s="78"/>
       <c r="AY93" s="78"/>
       <c r="AZ93" s="148" t="s">
-        <v>764</v>
-      </c>
-      <c r="BA93" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
+      </c>
+      <c r="BA93" s="6" t="s">
+        <v>760</v>
       </c>
       <c r="BB93" s="78" t="s">
         <v>778</v>
       </c>
       <c r="BC93" s="78"/>
       <c r="BD93" s="78" t="s">
-        <v>773</v>
-      </c>
-      <c r="BE93" s="78" t="s">
-        <v>807</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="BE93" s="78"/>
       <c r="BF93" s="78"/>
       <c r="BG93" s="78"/>
       <c r="BH93" s="78"/>
       <c r="BI93" s="117"/>
       <c r="BJ93" s="118"/>
       <c r="BK93" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="BL93" s="145" t="s">
-        <v>748</v>
-      </c>
-      <c r="BM93" s="133"/>
-      <c r="BN93" s="133"/>
-      <c r="BO93" s="134"/>
-      <c r="BP93" s="135"/>
-      <c r="BQ93" s="29"/>
+        <v>95</v>
+      </c>
+      <c r="BL93" s="144" t="s">
+        <v>588</v>
+      </c>
+      <c r="BM93" s="38"/>
+      <c r="BN93" s="38"/>
+      <c r="BO93" s="3"/>
+      <c r="BP93" s="121"/>
+      <c r="BQ93" s="45"/>
       <c r="BR93" s="77"/>
       <c r="BS93" s="77"/>
       <c r="BT93" s="119"/>
@@ -19618,49 +19757,51 @@
       <c r="AJ94" s="77"/>
       <c r="AK94" s="77"/>
       <c r="AL94" s="116"/>
-      <c r="AM94" s="117"/>
-      <c r="AN94" s="78"/>
+      <c r="AM94" s="27"/>
+      <c r="AN94" s="26"/>
       <c r="AO94" s="78"/>
       <c r="AP94" s="117"/>
-      <c r="AQ94" s="117"/>
-      <c r="AR94" s="78"/>
+      <c r="AQ94" s="27"/>
+      <c r="AR94" s="26"/>
       <c r="AS94" s="78"/>
       <c r="AT94" s="78"/>
       <c r="AU94" s="78"/>
-      <c r="AV94" s="117"/>
-      <c r="AW94" s="78"/>
+      <c r="AV94" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW94" s="26" t="s">
+        <v>754</v>
+      </c>
       <c r="AX94" s="78"/>
       <c r="AY94" s="78"/>
-      <c r="AZ94" s="78"/>
-      <c r="BA94" s="5" t="s">
-        <v>763</v>
+      <c r="AZ94" s="148"/>
+      <c r="BA94" s="6" t="s">
+        <v>761</v>
       </c>
       <c r="BB94" s="78" t="s">
         <v>779</v>
       </c>
       <c r="BC94" s="78"/>
       <c r="BD94" s="78" t="s">
-        <v>774</v>
-      </c>
-      <c r="BE94" s="78" t="s">
-        <v>811</v>
-      </c>
+        <v>796</v>
+      </c>
+      <c r="BE94" s="78"/>
       <c r="BF94" s="78"/>
       <c r="BG94" s="78"/>
       <c r="BH94" s="78"/>
       <c r="BI94" s="117"/>
       <c r="BJ94" s="118"/>
       <c r="BK94" s="38" t="s">
-        <v>515</v>
-      </c>
-      <c r="BL94" s="153" t="s">
-        <v>516</v>
+        <v>117</v>
+      </c>
+      <c r="BL94" s="145" t="s">
+        <v>808</v>
       </c>
       <c r="BM94" s="38"/>
       <c r="BN94" s="38"/>
       <c r="BO94" s="3"/>
-      <c r="BP94" s="29"/>
-      <c r="BQ94" s="93"/>
+      <c r="BP94" s="120"/>
+      <c r="BQ94" s="35"/>
       <c r="BR94" s="77"/>
       <c r="BS94" s="77"/>
       <c r="BT94" s="119"/>
@@ -19700,31 +19841,45 @@
       <c r="AS95" s="78"/>
       <c r="AT95" s="78"/>
       <c r="AU95" s="78"/>
-      <c r="AV95" s="117"/>
-      <c r="AW95" s="78"/>
+      <c r="AV95" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW95" s="26" t="s">
+        <v>753</v>
+      </c>
       <c r="AX95" s="78"/>
       <c r="AY95" s="78"/>
-      <c r="AZ95" s="78"/>
-      <c r="BA95" s="78"/>
-      <c r="BB95" s="78"/>
+      <c r="AZ95" s="148" t="s">
+        <v>764</v>
+      </c>
+      <c r="BA95" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="BB95" s="78" t="s">
+        <v>778</v>
+      </c>
       <c r="BC95" s="78"/>
-      <c r="BD95" s="78"/>
-      <c r="BE95" s="78"/>
+      <c r="BD95" s="78" t="s">
+        <v>773</v>
+      </c>
+      <c r="BE95" s="78" t="s">
+        <v>806</v>
+      </c>
       <c r="BF95" s="78"/>
       <c r="BG95" s="78"/>
       <c r="BH95" s="78"/>
       <c r="BI95" s="117"/>
       <c r="BJ95" s="118"/>
       <c r="BK95" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="BL95" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="BM95" s="38"/>
-      <c r="BN95" s="38"/>
-      <c r="BO95" s="3"/>
-      <c r="BP95" s="29"/>
+        <v>246</v>
+      </c>
+      <c r="BL95" s="145" t="s">
+        <v>748</v>
+      </c>
+      <c r="BM95" s="133"/>
+      <c r="BN95" s="133"/>
+      <c r="BO95" s="134"/>
+      <c r="BP95" s="135"/>
       <c r="BQ95" s="29"/>
       <c r="BR95" s="77"/>
       <c r="BS95" s="77"/>
@@ -19770,23 +19925,35 @@
       <c r="AX96" s="78"/>
       <c r="AY96" s="78"/>
       <c r="AZ96" s="78"/>
-      <c r="BA96" s="78"/>
-      <c r="BB96" s="78"/>
+      <c r="BA96" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="BB96" s="78" t="s">
+        <v>779</v>
+      </c>
       <c r="BC96" s="78"/>
-      <c r="BD96" s="78"/>
-      <c r="BE96" s="78"/>
+      <c r="BD96" s="78" t="s">
+        <v>774</v>
+      </c>
+      <c r="BE96" s="78" t="s">
+        <v>810</v>
+      </c>
       <c r="BF96" s="78"/>
       <c r="BG96" s="78"/>
       <c r="BH96" s="78"/>
       <c r="BI96" s="117"/>
       <c r="BJ96" s="118"/>
-      <c r="BK96" s="46"/>
-      <c r="BL96" s="46"/>
-      <c r="BM96" s="46"/>
-      <c r="BN96" s="46"/>
-      <c r="BO96" s="48"/>
+      <c r="BK96" s="38" t="s">
+        <v>515</v>
+      </c>
+      <c r="BL96" s="153" t="s">
+        <v>516</v>
+      </c>
+      <c r="BM96" s="38"/>
+      <c r="BN96" s="38"/>
+      <c r="BO96" s="3"/>
       <c r="BP96" s="29"/>
-      <c r="BQ96" s="29"/>
+      <c r="BQ96" s="93"/>
       <c r="BR96" s="77"/>
       <c r="BS96" s="77"/>
       <c r="BT96" s="119"/>
@@ -19841,12 +20008,17 @@
       <c r="BH97" s="78"/>
       <c r="BI97" s="117"/>
       <c r="BJ97" s="118"/>
-      <c r="BK97" s="78"/>
-      <c r="BL97" s="78"/>
-      <c r="BM97" s="78"/>
-      <c r="BN97" s="78"/>
-      <c r="BP97" s="116"/>
-      <c r="BQ97" s="116"/>
+      <c r="BK97" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="BL97" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="BM97" s="38"/>
+      <c r="BN97" s="38"/>
+      <c r="BO97" s="3"/>
+      <c r="BP97" s="29"/>
+      <c r="BQ97" s="29"/>
       <c r="BR97" s="77"/>
       <c r="BS97" s="77"/>
       <c r="BT97" s="119"/>
@@ -19901,15 +20073,136 @@
       <c r="BH98" s="78"/>
       <c r="BI98" s="117"/>
       <c r="BJ98" s="118"/>
-      <c r="BK98" s="78"/>
-      <c r="BL98" s="78"/>
-      <c r="BM98" s="78"/>
-      <c r="BN98" s="78"/>
-      <c r="BP98" s="116"/>
-      <c r="BQ98" s="116"/>
+      <c r="BK98" s="46"/>
+      <c r="BL98" s="46"/>
+      <c r="BM98" s="46"/>
+      <c r="BN98" s="46"/>
+      <c r="BO98" s="48"/>
+      <c r="BP98" s="29"/>
+      <c r="BQ98" s="29"/>
       <c r="BR98" s="77"/>
       <c r="BS98" s="77"/>
       <c r="BT98" s="119"/>
+    </row>
+    <row r="99" spans="2:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B99" s="116"/>
+      <c r="C99" s="116"/>
+      <c r="D99" s="116"/>
+      <c r="E99" s="116"/>
+      <c r="F99" s="116"/>
+      <c r="G99" s="116"/>
+      <c r="H99" s="77"/>
+      <c r="K99" s="116"/>
+      <c r="L99" s="116"/>
+      <c r="N99" s="77"/>
+      <c r="O99" s="77"/>
+      <c r="P99" s="77"/>
+      <c r="Q99" s="77"/>
+      <c r="W99" s="77"/>
+      <c r="X99" s="77"/>
+      <c r="Y99" s="77"/>
+      <c r="Z99" s="77"/>
+      <c r="AA99" s="77"/>
+      <c r="AB99" s="77"/>
+      <c r="AC99" s="77"/>
+      <c r="AD99" s="77"/>
+      <c r="AI99" s="77"/>
+      <c r="AJ99" s="77"/>
+      <c r="AK99" s="77"/>
+      <c r="AL99" s="116"/>
+      <c r="AM99" s="117"/>
+      <c r="AN99" s="78"/>
+      <c r="AO99" s="78"/>
+      <c r="AP99" s="117"/>
+      <c r="AQ99" s="117"/>
+      <c r="AR99" s="78"/>
+      <c r="AS99" s="78"/>
+      <c r="AT99" s="78"/>
+      <c r="AU99" s="78"/>
+      <c r="AV99" s="117"/>
+      <c r="AW99" s="78"/>
+      <c r="AX99" s="78"/>
+      <c r="AY99" s="78"/>
+      <c r="AZ99" s="78"/>
+      <c r="BA99" s="78"/>
+      <c r="BB99" s="78"/>
+      <c r="BC99" s="78"/>
+      <c r="BD99" s="78"/>
+      <c r="BE99" s="78"/>
+      <c r="BF99" s="78"/>
+      <c r="BG99" s="78"/>
+      <c r="BH99" s="78"/>
+      <c r="BI99" s="117"/>
+      <c r="BJ99" s="118"/>
+      <c r="BK99" s="78"/>
+      <c r="BL99" s="78"/>
+      <c r="BM99" s="78"/>
+      <c r="BN99" s="78"/>
+      <c r="BP99" s="116"/>
+      <c r="BQ99" s="116"/>
+      <c r="BR99" s="77"/>
+      <c r="BS99" s="77"/>
+      <c r="BT99" s="119"/>
+    </row>
+    <row r="100" spans="2:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B100" s="116"/>
+      <c r="C100" s="116"/>
+      <c r="D100" s="116"/>
+      <c r="E100" s="116"/>
+      <c r="F100" s="116"/>
+      <c r="G100" s="116"/>
+      <c r="H100" s="77"/>
+      <c r="K100" s="116"/>
+      <c r="L100" s="116"/>
+      <c r="N100" s="77"/>
+      <c r="O100" s="77"/>
+      <c r="P100" s="77"/>
+      <c r="Q100" s="77"/>
+      <c r="W100" s="77"/>
+      <c r="X100" s="77"/>
+      <c r="Y100" s="77"/>
+      <c r="Z100" s="77"/>
+      <c r="AA100" s="77"/>
+      <c r="AB100" s="77"/>
+      <c r="AC100" s="77"/>
+      <c r="AD100" s="77"/>
+      <c r="AI100" s="77"/>
+      <c r="AJ100" s="77"/>
+      <c r="AK100" s="77"/>
+      <c r="AL100" s="116"/>
+      <c r="AM100" s="117"/>
+      <c r="AN100" s="78"/>
+      <c r="AO100" s="78"/>
+      <c r="AP100" s="117"/>
+      <c r="AQ100" s="117"/>
+      <c r="AR100" s="78"/>
+      <c r="AS100" s="78"/>
+      <c r="AT100" s="78"/>
+      <c r="AU100" s="78"/>
+      <c r="AV100" s="117"/>
+      <c r="AW100" s="78"/>
+      <c r="AX100" s="78"/>
+      <c r="AY100" s="78"/>
+      <c r="AZ100" s="78"/>
+      <c r="BA100" s="78"/>
+      <c r="BB100" s="78"/>
+      <c r="BC100" s="78"/>
+      <c r="BD100" s="78"/>
+      <c r="BE100" s="78"/>
+      <c r="BF100" s="78"/>
+      <c r="BG100" s="78"/>
+      <c r="BH100" s="78"/>
+      <c r="BI100" s="117"/>
+      <c r="BJ100" s="118"/>
+      <c r="BK100" s="78"/>
+      <c r="BL100" s="78"/>
+      <c r="BM100" s="78"/>
+      <c r="BN100" s="78"/>
+      <c r="BP100" s="116"/>
+      <c r="BQ100" s="116"/>
+      <c r="BR100" s="77"/>
+      <c r="BS100" s="77"/>
+      <c r="BT100" s="119"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21158,4 +21451,256 @@
     <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13133089-9C8E-40DB-8C04-5B07C5991D49}">
+  <dimension ref="B2:H13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.1796875" customWidth="1"/>
+    <col min="8" max="8" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D3" s="162"/>
+    </row>
+    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="161" t="s">
+        <v>815</v>
+      </c>
+      <c r="C4" s="158" t="s">
+        <v>814</v>
+      </c>
+      <c r="D4" s="158" t="s">
+        <v>816</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="159" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B5" s="44">
+        <v>28.9</v>
+      </c>
+      <c r="C5" s="44">
+        <v>23.8</v>
+      </c>
+      <c r="D5" s="44">
+        <v>15</v>
+      </c>
+      <c r="E5" s="44">
+        <v>20</v>
+      </c>
+      <c r="F5" s="44">
+        <v>604</v>
+      </c>
+      <c r="G5" s="44">
+        <v>1004</v>
+      </c>
+      <c r="H5" s="44">
+        <f>906*2</f>
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B6" s="2">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>23.9</v>
+      </c>
+      <c r="D6" s="2">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2">
+        <v>724</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1068</v>
+      </c>
+      <c r="H6" s="2">
+        <f>925*2</f>
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B7" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3">
+        <v>18</v>
+      </c>
+      <c r="E7" s="3">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3">
+        <v>709</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1109</v>
+      </c>
+      <c r="H7" s="3">
+        <f>G7*2</f>
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B8" s="160">
+        <v>28.5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2">
+        <v>24</v>
+      </c>
+      <c r="F8" s="2">
+        <v>639</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1068</v>
+      </c>
+      <c r="H8" s="2">
+        <f>G8*2</f>
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B9" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="C9" s="3">
+        <v>24.9</v>
+      </c>
+      <c r="D9" s="3">
+        <v>30</v>
+      </c>
+      <c r="E9" s="3">
+        <v>22</v>
+      </c>
+      <c r="F9" s="3">
+        <v>604</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1071</v>
+      </c>
+      <c r="H9" s="3">
+        <f>G9*2</f>
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B10" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="C10" s="3">
+        <v>25.1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>33</v>
+      </c>
+      <c r="E10" s="3">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3">
+        <v>574</v>
+      </c>
+      <c r="G10" s="3">
+        <v>876</v>
+      </c>
+      <c r="H10" s="3">
+        <f>G10*2-12</f>
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B11" s="2">
+        <v>29.2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2">
+        <v>22</v>
+      </c>
+      <c r="F11" s="2">
+        <v>559</v>
+      </c>
+      <c r="G11" s="2">
+        <v>902</v>
+      </c>
+      <c r="H11" s="2">
+        <f>G11*2</f>
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B12" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>25.7</v>
+      </c>
+      <c r="D12" s="3">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3">
+        <v>20</v>
+      </c>
+      <c r="F12" s="3">
+        <v>567</v>
+      </c>
+      <c r="G12" s="3">
+        <v>846</v>
+      </c>
+      <c r="H12" s="3">
+        <f>G12*2</f>
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>819</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:H12">
+    <sortCondition ref="D5:D12"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr showObjects="none" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D70DB76-4A74-486B-B568-66C99E5F145C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6390C872-06A3-4DD9-BDB5-EBF82EA511BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15420" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="827">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2449,9 +2450,6 @@
     <t>20250612</t>
   </si>
   <si>
-    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
-  </si>
-  <si>
     <t>GLI2025_SEA032_092</t>
   </si>
   <si>
@@ -2476,9 +2474,6 @@
     <t>internal waves on shelf break, back and forth Emerald basin</t>
   </si>
   <si>
-    <t>shipped</t>
-  </si>
-  <si>
     <t>20250613</t>
   </si>
   <si>
@@ -2491,16 +2486,55 @@
     <t>20250825</t>
   </si>
   <si>
-    <t>Sigma-T(zodiak)/</t>
-  </si>
-  <si>
-    <t>GLI2025_SEA022_113</t>
-  </si>
-  <si>
     <t>1540746</t>
   </si>
   <si>
-    <t>internal waves on shelf break</t>
+    <t>GL1-GL2-GL3-GL7-Further-GL7-GL3-GL2-GL1-TRI-DR</t>
+  </si>
+  <si>
+    <t>battery min</t>
+  </si>
+  <si>
+    <t>battery max</t>
+  </si>
+  <si>
+    <t>battery min (%)</t>
+  </si>
+  <si>
+    <t>GPCTD</t>
+  </si>
+  <si>
+    <t>LEGATO</t>
+  </si>
+  <si>
+    <t>ranked</t>
+  </si>
+  <si>
+    <t>internal waves on shelf break, glider going further than HL7 for the first time ever, might be in a warm core ring  (23.8C at surface at HL7), lost 1 day coming back to HL7, increased pitch and speed to get out of eddy</t>
+  </si>
+  <si>
+    <t>AZMP fall 2025</t>
+  </si>
+  <si>
+    <t>Burned wire-2</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA032_097</t>
+  </si>
+  <si>
+    <t>GL1-GL2-GL3-GL7-GL3-GL2-GL1-HL2-HL3-TRI-DR</t>
+  </si>
+  <si>
+    <t>AZMP cruise sampled HL2 right during glider deployment, back and forth between HL2 and HL3</t>
+  </si>
+  <si>
+    <t>20251021</t>
+  </si>
+  <si>
+    <t>with TCM on nose, hurricane Melissa</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA022_115</t>
   </si>
 </sst>
 </file>
@@ -2852,7 +2886,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3243,6 +3277,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3572,80 +3618,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CY98"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:CY100"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" customWidth="1"/>
-    <col min="2" max="3" width="15.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="5.21875" customWidth="1"/>
+    <col min="2" max="3" width="15.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="4" customWidth="1"/>
     <col min="6" max="6" width="14" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.81640625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.77734375" style="4" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7" style="7" customWidth="1"/>
-    <col min="15" max="15" width="7.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.81640625" style="7" customWidth="1"/>
-    <col min="17" max="17" width="10.1796875" style="7" customWidth="1"/>
-    <col min="18" max="18" width="78.81640625" customWidth="1"/>
-    <col min="19" max="19" width="8.1796875" customWidth="1"/>
-    <col min="20" max="20" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.77734375" style="7" customWidth="1"/>
+    <col min="17" max="17" width="10.21875" style="7" customWidth="1"/>
+    <col min="18" max="18" width="78.77734375" customWidth="1"/>
+    <col min="19" max="19" width="8.21875" customWidth="1"/>
+    <col min="20" max="20" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.81640625" customWidth="1"/>
-    <col min="23" max="23" width="11.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.77734375" customWidth="1"/>
+    <col min="23" max="23" width="11.21875" style="7" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="20" style="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.54296875" style="77" customWidth="1"/>
-    <col min="29" max="29" width="20.54296875" style="77" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.54296875" style="77" customWidth="1"/>
-    <col min="31" max="31" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.5546875" style="77" customWidth="1"/>
+    <col min="29" max="29" width="20.5546875" style="77" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.5546875" style="77" customWidth="1"/>
+    <col min="31" max="31" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.54296875" style="7" customWidth="1"/>
-    <col min="38" max="38" width="7.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="15.453125" style="78" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.81640625" style="78" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="11.81640625" style="78" customWidth="1"/>
-    <col min="46" max="46" width="12.81640625" style="78" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.81640625" style="78" customWidth="1"/>
-    <col min="48" max="48" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="14.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.81640625" style="6" customWidth="1"/>
-    <col min="51" max="52" width="12.81640625" style="78" customWidth="1"/>
-    <col min="53" max="53" width="11.81640625" style="78" customWidth="1"/>
-    <col min="54" max="54" width="14.81640625" style="78" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="15.1796875" style="78" bestFit="1" customWidth="1"/>
-    <col min="56" max="60" width="15.1796875" style="78" customWidth="1"/>
-    <col min="61" max="61" width="11.81640625" style="5" customWidth="1"/>
-    <col min="62" max="62" width="11.81640625" style="1" customWidth="1"/>
-    <col min="63" max="63" width="12.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="12.81640625" style="6" customWidth="1"/>
+    <col min="33" max="33" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.5546875" style="7" customWidth="1"/>
+    <col min="38" max="38" width="7.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.44140625" style="78" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.77734375" style="78" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.77734375" style="78" customWidth="1"/>
+    <col min="46" max="46" width="12.77734375" style="78" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.77734375" style="78" customWidth="1"/>
+    <col min="48" max="48" width="11.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="14.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.77734375" style="6" customWidth="1"/>
+    <col min="51" max="52" width="12.77734375" style="78" customWidth="1"/>
+    <col min="53" max="53" width="11.77734375" style="78" customWidth="1"/>
+    <col min="54" max="54" width="14.77734375" style="78" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="15.21875" style="78" bestFit="1" customWidth="1"/>
+    <col min="56" max="60" width="15.21875" style="78" customWidth="1"/>
+    <col min="61" max="61" width="11.77734375" style="5" customWidth="1"/>
+    <col min="62" max="62" width="11.77734375" style="1" customWidth="1"/>
+    <col min="63" max="63" width="12.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="12.77734375" style="6" customWidth="1"/>
     <col min="65" max="65" width="7" style="6" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="7.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="7.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="19" style="4" bestFit="1" customWidth="1"/>
     <col min="69" max="69" width="20" style="4" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="25.81640625" style="7" customWidth="1"/>
-    <col min="71" max="71" width="64.453125" style="7" customWidth="1"/>
-    <col min="72" max="72" width="78.81640625" style="8" customWidth="1"/>
+    <col min="70" max="70" width="25.77734375" style="7" customWidth="1"/>
+    <col min="71" max="71" width="64.44140625" style="7" customWidth="1"/>
+    <col min="72" max="72" width="78.77734375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="24"/>
       <c r="C1" s="152" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D1" s="94" t="s">
         <v>432</v>
@@ -3708,7 +3754,7 @@
       <c r="BS1" s="25"/>
       <c r="BT1" s="30"/>
     </row>
-    <row r="2" spans="1:72" s="63" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:72" s="63" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="64" t="s">
         <v>0</v>
       </c>
@@ -3923,7 +3969,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <v>1</v>
       </c>
@@ -4098,7 +4144,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="4" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="82">
         <v>2</v>
       </c>
@@ -4275,7 +4321,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="5" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23">
         <v>1</v>
       </c>
@@ -4452,7 +4498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23">
         <v>2</v>
       </c>
@@ -4630,7 +4676,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23">
         <v>3</v>
       </c>
@@ -4809,7 +4855,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="8" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23">
         <v>4</v>
       </c>
@@ -4986,7 +5032,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="9" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="23">
         <v>5</v>
       </c>
@@ -5163,7 +5209,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23">
         <v>6</v>
       </c>
@@ -5340,7 +5386,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="11" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="23">
         <v>7</v>
       </c>
@@ -5517,7 +5563,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23">
         <v>8</v>
       </c>
@@ -5698,7 +5744,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23">
         <v>9</v>
       </c>
@@ -5877,7 +5923,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="14" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23">
         <v>10</v>
       </c>
@@ -6054,7 +6100,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23">
         <v>11</v>
       </c>
@@ -6235,7 +6281,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="16" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="23">
         <v>12</v>
       </c>
@@ -6414,7 +6460,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="17" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="84">
         <v>13</v>
       </c>
@@ -6592,7 +6638,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>1</v>
       </c>
@@ -6770,7 +6816,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>2</v>
       </c>
@@ -6942,7 +6988,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="80">
         <v>3</v>
       </c>
@@ -7120,7 +7166,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="80">
         <v>3</v>
       </c>
@@ -7299,7 +7345,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="22" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>4</v>
       </c>
@@ -7478,7 +7524,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>5</v>
       </c>
@@ -7657,7 +7703,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>6</v>
       </c>
@@ -7834,7 +7880,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="25" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>7</v>
       </c>
@@ -8010,7 +8056,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="26" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>8</v>
       </c>
@@ -8190,7 +8236,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="27" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>9</v>
       </c>
@@ -8366,7 +8412,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="28" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>10</v>
       </c>
@@ -8545,7 +8591,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="29" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>11</v>
       </c>
@@ -8707,7 +8753,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="30" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>12</v>
       </c>
@@ -8886,7 +8932,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>13</v>
       </c>
@@ -9064,7 +9110,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="32" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:72" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="82">
         <v>14</v>
       </c>
@@ -9245,7 +9291,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="33" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B33" s="47" t="s">
         <v>247</v>
       </c>
@@ -9322,7 +9368,7 @@
       <c r="BS33" s="37"/>
       <c r="BT33" s="43"/>
     </row>
-    <row r="34" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B34" s="47" t="s">
         <v>248</v>
       </c>
@@ -9399,7 +9445,7 @@
       <c r="BS34" s="37"/>
       <c r="BT34" s="43"/>
     </row>
-    <row r="35" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="23">
         <v>1</v>
       </c>
@@ -9578,7 +9624,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="36" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="23">
         <v>2</v>
       </c>
@@ -9758,7 +9804,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="37" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="23">
         <v>3</v>
       </c>
@@ -9926,7 +9972,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="38" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="23">
         <v>4</v>
       </c>
@@ -10105,7 +10151,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="39" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23">
         <v>5</v>
       </c>
@@ -10284,7 +10330,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="40" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="23">
         <v>6</v>
       </c>
@@ -10465,7 +10511,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="41" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="23">
         <v>7</v>
       </c>
@@ -10653,7 +10699,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="42" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="23">
         <v>8</v>
       </c>
@@ -10831,7 +10877,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="43" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="23">
         <v>9</v>
       </c>
@@ -11007,7 +11053,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="44" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:72" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="84">
         <v>10</v>
       </c>
@@ -11187,7 +11233,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="45" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>1</v>
       </c>
@@ -11365,7 +11411,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="46" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>2</v>
       </c>
@@ -11544,7 +11590,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="47" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>3</v>
       </c>
@@ -11722,7 +11768,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="48" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>4</v>
       </c>
@@ -11900,7 +11946,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>5</v>
       </c>
@@ -12087,7 +12133,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="50" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>6</v>
       </c>
@@ -12265,7 +12311,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="51" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>7</v>
       </c>
@@ -12443,7 +12489,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="52" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>8</v>
       </c>
@@ -12630,7 +12676,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="53" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>9</v>
       </c>
@@ -12818,7 +12864,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="54" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>10</v>
       </c>
@@ -12998,7 +13044,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="55" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>11</v>
       </c>
@@ -13178,7 +13224,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="56" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>12</v>
       </c>
@@ -13371,7 +13417,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="57" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>13</v>
       </c>
@@ -13550,7 +13596,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="58" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>14</v>
       </c>
@@ -13728,7 +13774,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="59" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:72" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="80">
         <v>15</v>
       </c>
@@ -13918,7 +13964,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="60" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="23">
         <v>1</v>
       </c>
@@ -14096,7 +14142,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="61" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23">
         <v>2</v>
       </c>
@@ -14274,7 +14320,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="62" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="23">
         <v>3</v>
       </c>
@@ -14462,7 +14508,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="63" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="23">
         <v>4</v>
       </c>
@@ -14619,7 +14665,7 @@
         <v>229</v>
       </c>
       <c r="BJ63" s="42" t="s">
-        <v>171</v>
+        <v>820</v>
       </c>
       <c r="BK63" s="96" t="s">
         <v>246</v>
@@ -14646,7 +14692,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="64" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:72" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="63">
         <v>5</v>
       </c>
@@ -14824,7 +14870,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="65" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -14982,7 +15028,7 @@
         <v>229</v>
       </c>
       <c r="BJ65" s="49" t="s">
-        <v>171</v>
+        <v>820</v>
       </c>
       <c r="BK65" s="49">
         <v>201383</v>
@@ -15011,7 +15057,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="66" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>2</v>
       </c>
@@ -15192,7 +15238,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="67" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>3</v>
       </c>
@@ -15373,7 +15419,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="68" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>4</v>
       </c>
@@ -15564,7 +15610,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="69" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:103" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9">
         <v>5</v>
       </c>
@@ -15743,7 +15789,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="70" spans="1:103" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:103" s="88" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="124">
         <v>6</v>
       </c>
@@ -15903,7 +15949,7 @@
         <v>229</v>
       </c>
       <c r="BJ70" s="49" t="s">
-        <v>171</v>
+        <v>820</v>
       </c>
       <c r="BK70" s="22" t="s">
         <v>515</v>
@@ -15930,7 +15976,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="71" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="124">
         <v>7</v>
       </c>
@@ -16090,7 +16136,7 @@
         <v>229</v>
       </c>
       <c r="BJ71" s="49" t="s">
-        <v>171</v>
+        <v>820</v>
       </c>
       <c r="BK71" s="22" t="s">
         <v>515</v>
@@ -16148,7 +16194,7 @@
       <c r="CX71" s="88"/>
       <c r="CY71" s="88"/>
     </row>
-    <row r="72" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="136">
         <v>8</v>
       </c>
@@ -16359,7 +16405,7 @@
       <c r="CX72" s="88"/>
       <c r="CY72" s="88"/>
     </row>
-    <row r="73" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="137">
         <v>1</v>
       </c>
@@ -16540,7 +16586,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="74" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="137">
         <v>2</v>
       </c>
@@ -16719,7 +16765,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="75" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="137">
         <v>3</v>
       </c>
@@ -16904,7 +16950,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="76" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="137">
         <v>4</v>
       </c>
@@ -17081,7 +17127,7 @@
       <c r="BS76" s="37"/>
       <c r="BT76" s="43"/>
     </row>
-    <row r="77" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="137">
         <v>5</v>
       </c>
@@ -17233,7 +17279,7 @@
         <v>229</v>
       </c>
       <c r="BJ77" s="96" t="s">
-        <v>171</v>
+        <v>820</v>
       </c>
       <c r="BK77" s="38" t="s">
         <v>98</v>
@@ -17264,7 +17310,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="78" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="137">
         <v>6</v>
       </c>
@@ -17447,7 +17493,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="79" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="137">
         <v>7</v>
       </c>
@@ -17630,7 +17676,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="80" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:103" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="137">
         <v>8</v>
       </c>
@@ -17815,7 +17861,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="81" spans="1:72" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:72" s="48" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="147">
         <v>9</v>
       </c>
@@ -18006,7 +18052,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="82" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="124">
         <v>1</v>
       </c>
@@ -18191,7 +18237,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="83" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="124">
         <v>2</v>
       </c>
@@ -18370,7 +18416,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="84" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="124">
         <v>3</v>
       </c>
@@ -18393,7 +18439,7 @@
         <v>15</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="I84" s="2">
         <v>29.3</v>
@@ -18548,10 +18594,10 @@
         <v>793</v>
       </c>
       <c r="BT84" s="21" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
-    <row r="85" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="124">
         <v>3</v>
       </c>
@@ -18574,7 +18620,7 @@
         <v>15</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="I85" s="2">
         <v>28.5</v>
@@ -18723,7 +18769,7 @@
         <v>205</v>
       </c>
       <c r="BR85" s="18" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="BS85" s="18" t="s">
         <v>794</v>
@@ -18732,7 +18778,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="86" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="124">
         <v>4</v>
       </c>
@@ -18755,7 +18801,7 @@
         <v>15</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I86" s="2">
         <v>29</v>
@@ -18785,7 +18831,7 @@
         <v>-61.44</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="S86" s="2">
         <v>22</v>
@@ -18893,7 +18939,7 @@
       <c r="BM86" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="BN86" s="79" t="s">
+      <c r="BN86" s="22" t="s">
         <v>702</v>
       </c>
       <c r="BO86" s="2"/>
@@ -18908,17 +18954,19 @@
       </c>
       <c r="BS86" s="18"/>
       <c r="BT86" s="21" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
-    <row r="87" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="124">
         <v>5</v>
       </c>
       <c r="B87" s="14">
         <v>20250904</v>
       </c>
-      <c r="C87" s="14"/>
+      <c r="C87" s="14">
+        <v>20250929</v>
+      </c>
       <c r="D87" s="14" t="s">
         <v>53</v>
       </c>
@@ -18932,12 +18980,14 @@
         <v>15</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="I87" s="2">
         <v>29.1</v>
       </c>
-      <c r="J87" s="154"/>
+      <c r="J87" s="154">
+        <v>25</v>
+      </c>
       <c r="K87" s="157">
         <v>44.389499999999998</v>
       </c>
@@ -18947,17 +18997,34 @@
       <c r="M87" s="155">
         <v>0.56597222222222221</v>
       </c>
-      <c r="N87" s="18"/>
-      <c r="O87" s="18"/>
-      <c r="P87" s="18"/>
-      <c r="Q87" s="18"/>
+      <c r="N87" s="18">
+        <v>42.23</v>
+      </c>
+      <c r="O87" s="18">
+        <v>-63.37</v>
+      </c>
+      <c r="P87" s="18">
+        <v>44.4</v>
+      </c>
+      <c r="Q87" s="18">
+        <v>-61.18</v>
+      </c>
       <c r="R87" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="S87" s="2"/>
-      <c r="T87" s="2"/>
-      <c r="U87" s="2"/>
-      <c r="V87" s="2"/>
+        <v>811</v>
+      </c>
+      <c r="S87" s="2">
+        <v>25</v>
+      </c>
+      <c r="T87" s="2">
+        <v>658</v>
+      </c>
+      <c r="U87" s="2">
+        <v>934</v>
+      </c>
+      <c r="V87" s="2">
+        <f>U87*2</f>
+        <v>1868</v>
+      </c>
       <c r="W87" s="18" t="s">
         <v>36</v>
       </c>
@@ -18975,13 +19042,13 @@
       </c>
       <c r="AD87" s="18"/>
       <c r="AE87" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF87" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG87" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH87" s="2">
         <v>1022</v>
@@ -19022,7 +19089,7 @@
         <v>760</v>
       </c>
       <c r="BB87" s="22" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="BC87" s="22" t="s">
         <v>420</v>
@@ -19051,7 +19118,7 @@
       <c r="BM87" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="BN87" s="2">
+      <c r="BN87" s="163">
         <v>1272212</v>
       </c>
       <c r="BO87" s="2"/>
@@ -19062,24 +19129,28 @@
         <v>205</v>
       </c>
       <c r="BR87" s="18" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="BS87" s="18"/>
       <c r="BT87" s="21" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
-    <row r="88" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="124">
         <v>6</v>
       </c>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14"/>
+      <c r="B88" s="14">
+        <v>20251006</v>
+      </c>
+      <c r="C88" s="14">
+        <v>20251027</v>
+      </c>
       <c r="D88" s="14" t="s">
         <v>44</v>
       </c>
       <c r="E88" s="14">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F88" s="14">
         <v>4800993</v>
@@ -19088,24 +19159,51 @@
         <v>15</v>
       </c>
       <c r="H88" s="18" t="s">
-        <v>813</v>
-      </c>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="11"/>
-      <c r="L88" s="11"/>
-      <c r="M88" s="100"/>
-      <c r="N88" s="18"/>
-      <c r="O88" s="18"/>
-      <c r="P88" s="18"/>
-      <c r="Q88" s="18"/>
+        <v>826</v>
+      </c>
+      <c r="I88" s="2">
+        <v>29.2</v>
+      </c>
+      <c r="J88" s="2">
+        <v>23.6</v>
+      </c>
+      <c r="K88" s="11">
+        <v>44.476999999999997</v>
+      </c>
+      <c r="L88" s="11">
+        <v>-63.432499999999997</v>
+      </c>
+      <c r="M88" s="100">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="N88" s="18">
+        <v>42.46</v>
+      </c>
+      <c r="O88" s="18">
+        <v>-63.44</v>
+      </c>
+      <c r="P88" s="18">
+        <v>44.54</v>
+      </c>
+      <c r="Q88" s="18">
+        <v>-61.42</v>
+      </c>
       <c r="R88" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="S88" s="2"/>
-      <c r="T88" s="2"/>
-      <c r="U88" s="2"/>
-      <c r="V88" s="2"/>
+        <v>822</v>
+      </c>
+      <c r="S88" s="2">
+        <v>21</v>
+      </c>
+      <c r="T88" s="2">
+        <v>708</v>
+      </c>
+      <c r="U88" s="2">
+        <v>1174</v>
+      </c>
+      <c r="V88" s="2">
+        <f>U88*2</f>
+        <v>2348</v>
+      </c>
       <c r="W88" s="18" t="s">
         <v>36</v>
       </c>
@@ -19122,9 +19220,15 @@
         <v>781</v>
       </c>
       <c r="AD88" s="18"/>
-      <c r="AE88" s="2"/>
-      <c r="AF88" s="2"/>
-      <c r="AG88" s="2"/>
+      <c r="AE88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="2">
+        <v>0</v>
+      </c>
       <c r="AH88" s="2">
         <v>1022.5</v>
       </c>
@@ -19194,30 +19298,48 @@
         <v>137</v>
       </c>
       <c r="BN88" s="22" t="s">
-        <v>814</v>
-      </c>
-      <c r="BO88" s="2"/>
+        <v>810</v>
+      </c>
+      <c r="BO88" s="2" t="s">
+        <v>819</v>
+      </c>
       <c r="BP88" s="2" t="s">
         <v>670</v>
       </c>
       <c r="BQ88" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BR88" s="18"/>
+      <c r="BR88" s="18" t="s">
+        <v>197</v>
+      </c>
       <c r="BS88" s="18"/>
-      <c r="BT88" s="21"/>
+      <c r="BT88" s="21" t="s">
+        <v>823</v>
+      </c>
     </row>
-    <row r="89" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="124">
         <v>7</v>
       </c>
-      <c r="B89" s="14"/>
+      <c r="B89" s="14">
+        <v>20251027</v>
+      </c>
       <c r="C89" s="14"/>
-      <c r="D89" s="14"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="14"/>
-      <c r="H89" s="18"/>
+      <c r="D89" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E89" s="14">
+        <v>97</v>
+      </c>
+      <c r="F89" s="14">
+        <v>4800937</v>
+      </c>
+      <c r="G89" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="18" t="s">
+        <v>821</v>
+      </c>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="14"/>
@@ -19227,27 +19349,47 @@
       <c r="O89" s="18"/>
       <c r="P89" s="18"/>
       <c r="Q89" s="18"/>
-      <c r="R89" s="2"/>
+      <c r="R89" s="2" t="s">
+        <v>444</v>
+      </c>
       <c r="S89" s="2"/>
       <c r="T89" s="2"/>
       <c r="U89" s="2"/>
       <c r="V89" s="2"/>
-      <c r="W89" s="18"/>
-      <c r="X89" s="18"/>
+      <c r="W89" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X89" s="18">
+        <v>1</v>
+      </c>
       <c r="Y89" s="18"/>
-      <c r="Z89" s="18"/>
+      <c r="Z89" s="18" t="s">
+        <v>183</v>
+      </c>
       <c r="AA89" s="18"/>
       <c r="AB89" s="18"/>
-      <c r="AC89" s="18"/>
+      <c r="AC89" s="18" t="s">
+        <v>781</v>
+      </c>
       <c r="AD89" s="18"/>
       <c r="AE89" s="2"/>
       <c r="AF89" s="2"/>
       <c r="AG89" s="2"/>
-      <c r="AH89" s="2"/>
-      <c r="AI89" s="18"/>
-      <c r="AJ89" s="18"/>
-      <c r="AK89" s="18"/>
-      <c r="AL89" s="14"/>
+      <c r="AH89" s="2">
+        <v>1023</v>
+      </c>
+      <c r="AI89" s="18">
+        <v>20251014</v>
+      </c>
+      <c r="AJ89" s="18" t="s">
+        <v>752</v>
+      </c>
+      <c r="AK89" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="AL89" s="14">
+        <v>32</v>
+      </c>
       <c r="AM89" s="20"/>
       <c r="AN89" s="22"/>
       <c r="AO89" s="22"/>
@@ -19258,37 +19400,67 @@
       <c r="AT89" s="22"/>
       <c r="AU89" s="22"/>
       <c r="AV89" s="10" t="s">
-        <v>798</v>
-      </c>
-      <c r="AW89" s="16"/>
-      <c r="AX89" s="22"/>
+        <v>86</v>
+      </c>
+      <c r="AW89" s="16">
+        <v>45629</v>
+      </c>
+      <c r="AX89" s="22" t="s">
+        <v>461</v>
+      </c>
       <c r="AY89" s="22"/>
       <c r="AZ89" s="22"/>
-      <c r="BA89" s="22"/>
-      <c r="BB89" s="22"/>
-      <c r="BC89" s="22"/>
-      <c r="BD89" s="22"/>
-      <c r="BE89" s="22"/>
+      <c r="BA89" s="22" t="s">
+        <v>760</v>
+      </c>
+      <c r="BB89" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="BC89" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="BD89" s="22" t="s">
+        <v>795</v>
+      </c>
+      <c r="BE89" s="22" t="s">
+        <v>797</v>
+      </c>
       <c r="BF89" s="22"/>
       <c r="BG89" s="22"/>
       <c r="BH89" s="22"/>
-      <c r="BI89" s="20"/>
-      <c r="BJ89" s="146"/>
-      <c r="BK89" s="22"/>
-      <c r="BL89" s="22"/>
-      <c r="BM89" s="22"/>
-      <c r="BN89" s="22"/>
+      <c r="BI89" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ89" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK89" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="BL89" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="BM89" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="BN89" s="2">
+        <v>1272212</v>
+      </c>
       <c r="BO89" s="2"/>
-      <c r="BP89" s="149"/>
-      <c r="BQ89" s="14"/>
+      <c r="BP89" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="BQ89" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="BR89" s="18"/>
       <c r="BS89" s="18"/>
-      <c r="BT89" s="21"/>
+      <c r="BT89" s="21" t="s">
+        <v>825</v>
+      </c>
     </row>
-    <row r="90" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="124">
-        <v>8</v>
-      </c>
+    <row r="90" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="124"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -19300,7 +19472,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="14"/>
       <c r="L90" s="14"/>
-      <c r="M90" s="2"/>
+      <c r="M90" s="100"/>
       <c r="N90" s="18"/>
       <c r="O90" s="18"/>
       <c r="P90" s="18"/>
@@ -19335,8 +19507,8 @@
       <c r="AS90" s="22"/>
       <c r="AT90" s="22"/>
       <c r="AU90" s="22"/>
-      <c r="AV90" s="20"/>
-      <c r="AW90" s="22"/>
+      <c r="AV90" s="10"/>
+      <c r="AW90" s="16"/>
       <c r="AX90" s="22"/>
       <c r="AY90" s="22"/>
       <c r="AZ90" s="22"/>
@@ -19350,12 +19522,8 @@
       <c r="BH90" s="22"/>
       <c r="BI90" s="20"/>
       <c r="BJ90" s="146"/>
-      <c r="BK90" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="BL90" s="150" t="s">
-        <v>749</v>
-      </c>
+      <c r="BK90" s="22"/>
+      <c r="BL90" s="22"/>
       <c r="BM90" s="22"/>
       <c r="BN90" s="22"/>
       <c r="BO90" s="2"/>
@@ -19365,155 +19533,161 @@
       <c r="BS90" s="18"/>
       <c r="BT90" s="21"/>
     </row>
-    <row r="91" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="116"/>
-      <c r="C91" s="116"/>
-      <c r="D91" s="116"/>
-      <c r="E91" s="116"/>
-      <c r="F91" s="116"/>
-      <c r="G91" s="116"/>
-      <c r="H91" s="77"/>
-      <c r="K91" s="116"/>
-      <c r="L91" s="116"/>
-      <c r="N91" s="77"/>
-      <c r="O91" s="77"/>
-      <c r="P91" s="77"/>
-      <c r="Q91" s="77"/>
-      <c r="W91" s="77"/>
-      <c r="X91" s="77"/>
-      <c r="Y91" s="77"/>
-      <c r="Z91" s="77"/>
-      <c r="AA91" s="77"/>
-      <c r="AB91" s="77"/>
-      <c r="AC91" s="77"/>
-      <c r="AD91" s="77"/>
-      <c r="AI91" s="77"/>
-      <c r="AJ91" s="77"/>
-      <c r="AK91" s="77"/>
-      <c r="AL91" s="116"/>
-      <c r="AM91" s="27"/>
-      <c r="AN91" s="26"/>
-      <c r="AO91" s="78"/>
-      <c r="AP91" s="117"/>
-      <c r="AQ91" s="27"/>
-      <c r="AR91" s="26"/>
-      <c r="AS91" s="78"/>
-      <c r="AT91" s="78"/>
-      <c r="AU91" s="78"/>
-      <c r="AV91" s="117"/>
-      <c r="AW91" s="78"/>
-      <c r="AX91" s="78"/>
-      <c r="AY91" s="78"/>
-      <c r="AZ91" s="148" t="s">
-        <v>765</v>
-      </c>
-      <c r="BA91" s="6" t="s">
-        <v>760</v>
-      </c>
-      <c r="BB91" s="78" t="s">
-        <v>778</v>
-      </c>
-      <c r="BC91" s="78"/>
-      <c r="BD91" s="78" t="s">
-        <v>795</v>
-      </c>
-      <c r="BE91" s="78"/>
-      <c r="BF91" s="78"/>
-      <c r="BG91" s="78"/>
-      <c r="BH91" s="78"/>
-      <c r="BI91" s="117"/>
-      <c r="BJ91" s="118"/>
-      <c r="BK91" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="BL91" s="144" t="s">
-        <v>588</v>
-      </c>
-      <c r="BM91" s="38"/>
-      <c r="BN91" s="38"/>
-      <c r="BO91" s="3"/>
-      <c r="BP91" s="121"/>
-      <c r="BQ91" s="45"/>
-      <c r="BR91" s="77"/>
-      <c r="BS91" s="77"/>
-      <c r="BT91" s="119"/>
+    <row r="91" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="124"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="18"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="14"/>
+      <c r="L91" s="14"/>
+      <c r="M91" s="100"/>
+      <c r="N91" s="18"/>
+      <c r="O91" s="18"/>
+      <c r="P91" s="18"/>
+      <c r="Q91" s="18"/>
+      <c r="R91" s="2"/>
+      <c r="S91" s="2"/>
+      <c r="T91" s="2"/>
+      <c r="U91" s="2"/>
+      <c r="V91" s="2"/>
+      <c r="W91" s="18"/>
+      <c r="X91" s="18"/>
+      <c r="Y91" s="18"/>
+      <c r="Z91" s="18"/>
+      <c r="AA91" s="18"/>
+      <c r="AB91" s="18"/>
+      <c r="AC91" s="18"/>
+      <c r="AD91" s="18"/>
+      <c r="AE91" s="2"/>
+      <c r="AF91" s="2"/>
+      <c r="AG91" s="2"/>
+      <c r="AH91" s="2"/>
+      <c r="AI91" s="18"/>
+      <c r="AJ91" s="18"/>
+      <c r="AK91" s="18"/>
+      <c r="AL91" s="14"/>
+      <c r="AM91" s="20"/>
+      <c r="AN91" s="22"/>
+      <c r="AO91" s="22"/>
+      <c r="AP91" s="20"/>
+      <c r="AQ91" s="20"/>
+      <c r="AR91" s="22"/>
+      <c r="AS91" s="22"/>
+      <c r="AT91" s="22"/>
+      <c r="AU91" s="22"/>
+      <c r="AV91" s="10"/>
+      <c r="AW91" s="16"/>
+      <c r="AX91" s="22"/>
+      <c r="AY91" s="22"/>
+      <c r="AZ91" s="22"/>
+      <c r="BA91" s="22"/>
+      <c r="BB91" s="22"/>
+      <c r="BC91" s="22"/>
+      <c r="BD91" s="22"/>
+      <c r="BE91" s="22"/>
+      <c r="BF91" s="22"/>
+      <c r="BG91" s="22"/>
+      <c r="BH91" s="22"/>
+      <c r="BI91" s="20"/>
+      <c r="BJ91" s="146"/>
+      <c r="BK91" s="22"/>
+      <c r="BL91" s="22"/>
+      <c r="BM91" s="22"/>
+      <c r="BN91" s="22"/>
+      <c r="BO91" s="2"/>
+      <c r="BP91" s="149"/>
+      <c r="BQ91" s="14"/>
+      <c r="BR91" s="18"/>
+      <c r="BS91" s="18"/>
+      <c r="BT91" s="21"/>
     </row>
-    <row r="92" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="116"/>
-      <c r="C92" s="116"/>
-      <c r="D92" s="116"/>
-      <c r="E92" s="116"/>
-      <c r="F92" s="116"/>
-      <c r="G92" s="116"/>
-      <c r="H92" s="77"/>
-      <c r="K92" s="116"/>
-      <c r="L92" s="116"/>
-      <c r="N92" s="77"/>
-      <c r="O92" s="77"/>
-      <c r="P92" s="77"/>
-      <c r="Q92" s="77"/>
-      <c r="W92" s="77"/>
-      <c r="X92" s="77"/>
-      <c r="Y92" s="77"/>
-      <c r="Z92" s="77"/>
-      <c r="AA92" s="77"/>
-      <c r="AB92" s="77"/>
-      <c r="AC92" s="77"/>
-      <c r="AD92" s="77"/>
-      <c r="AI92" s="77"/>
-      <c r="AJ92" s="77"/>
-      <c r="AK92" s="77"/>
-      <c r="AL92" s="116"/>
-      <c r="AM92" s="27"/>
-      <c r="AN92" s="26"/>
-      <c r="AO92" s="78"/>
-      <c r="AP92" s="117"/>
-      <c r="AQ92" s="27"/>
-      <c r="AR92" s="26"/>
-      <c r="AS92" s="78"/>
-      <c r="AT92" s="78"/>
-      <c r="AU92" s="78"/>
-      <c r="AV92" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW92" s="26" t="s">
-        <v>754</v>
-      </c>
-      <c r="AX92" s="78"/>
-      <c r="AY92" s="78"/>
-      <c r="AZ92" s="148"/>
-      <c r="BA92" s="6" t="s">
-        <v>761</v>
-      </c>
-      <c r="BB92" s="78" t="s">
-        <v>779</v>
-      </c>
-      <c r="BC92" s="78"/>
-      <c r="BD92" s="78" t="s">
-        <v>796</v>
-      </c>
-      <c r="BE92" s="78"/>
-      <c r="BF92" s="78"/>
-      <c r="BG92" s="78"/>
-      <c r="BH92" s="78"/>
-      <c r="BI92" s="117"/>
-      <c r="BJ92" s="118"/>
-      <c r="BK92" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="BL92" s="145" t="s">
-        <v>809</v>
-      </c>
-      <c r="BM92" s="38"/>
-      <c r="BN92" s="38"/>
-      <c r="BO92" s="3"/>
-      <c r="BP92" s="120"/>
-      <c r="BQ92" s="35"/>
-      <c r="BR92" s="77"/>
-      <c r="BS92" s="77"/>
-      <c r="BT92" s="119"/>
+    <row r="92" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="124">
+        <v>8</v>
+      </c>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="18"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="14"/>
+      <c r="L92" s="14"/>
+      <c r="M92" s="2"/>
+      <c r="N92" s="18"/>
+      <c r="O92" s="18"/>
+      <c r="P92" s="18"/>
+      <c r="Q92" s="18"/>
+      <c r="R92" s="2"/>
+      <c r="S92" s="2"/>
+      <c r="T92" s="2"/>
+      <c r="U92" s="2"/>
+      <c r="V92" s="2"/>
+      <c r="W92" s="18"/>
+      <c r="X92" s="18"/>
+      <c r="Y92" s="18"/>
+      <c r="Z92" s="18"/>
+      <c r="AA92" s="18"/>
+      <c r="AB92" s="18"/>
+      <c r="AC92" s="18"/>
+      <c r="AD92" s="18"/>
+      <c r="AE92" s="2"/>
+      <c r="AF92" s="2"/>
+      <c r="AG92" s="2"/>
+      <c r="AH92" s="2"/>
+      <c r="AI92" s="18"/>
+      <c r="AJ92" s="18"/>
+      <c r="AK92" s="18"/>
+      <c r="AL92" s="14"/>
+      <c r="AM92" s="20"/>
+      <c r="AN92" s="22"/>
+      <c r="AO92" s="22"/>
+      <c r="AP92" s="20"/>
+      <c r="AQ92" s="20"/>
+      <c r="AR92" s="22"/>
+      <c r="AS92" s="22"/>
+      <c r="AT92" s="22"/>
+      <c r="AU92" s="22"/>
+      <c r="AV92" s="20"/>
+      <c r="AW92" s="22"/>
+      <c r="AX92" s="22"/>
+      <c r="AY92" s="22"/>
+      <c r="AZ92" s="22"/>
+      <c r="BA92" s="22"/>
+      <c r="BB92" s="22"/>
+      <c r="BC92" s="22"/>
+      <c r="BD92" s="22"/>
+      <c r="BE92" s="22"/>
+      <c r="BF92" s="22"/>
+      <c r="BG92" s="22"/>
+      <c r="BH92" s="22"/>
+      <c r="BI92" s="20"/>
+      <c r="BJ92" s="146"/>
+      <c r="BK92" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="BL92" s="150" t="s">
+        <v>749</v>
+      </c>
+      <c r="BM92" s="22"/>
+      <c r="BN92" s="22"/>
+      <c r="BO92" s="2"/>
+      <c r="BP92" s="149"/>
+      <c r="BQ92" s="14"/>
+      <c r="BR92" s="18"/>
+      <c r="BS92" s="18"/>
+      <c r="BT92" s="21"/>
     </row>
-    <row r="93" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B93" s="116"/>
       <c r="C93" s="116"/>
       <c r="D93" s="116"/>
@@ -19539,60 +19713,54 @@
       <c r="AJ93" s="77"/>
       <c r="AK93" s="77"/>
       <c r="AL93" s="116"/>
-      <c r="AM93" s="117"/>
-      <c r="AN93" s="78"/>
+      <c r="AM93" s="27"/>
+      <c r="AN93" s="26"/>
       <c r="AO93" s="78"/>
       <c r="AP93" s="117"/>
-      <c r="AQ93" s="117"/>
-      <c r="AR93" s="78"/>
+      <c r="AQ93" s="27"/>
+      <c r="AR93" s="26"/>
       <c r="AS93" s="78"/>
       <c r="AT93" s="78"/>
       <c r="AU93" s="78"/>
-      <c r="AV93" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW93" s="26" t="s">
-        <v>753</v>
-      </c>
+      <c r="AV93" s="117"/>
+      <c r="AW93" s="78"/>
       <c r="AX93" s="78"/>
       <c r="AY93" s="78"/>
       <c r="AZ93" s="148" t="s">
-        <v>764</v>
-      </c>
-      <c r="BA93" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
+      </c>
+      <c r="BA93" s="6" t="s">
+        <v>760</v>
       </c>
       <c r="BB93" s="78" t="s">
         <v>778</v>
       </c>
       <c r="BC93" s="78"/>
       <c r="BD93" s="78" t="s">
-        <v>773</v>
-      </c>
-      <c r="BE93" s="78" t="s">
-        <v>807</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="BE93" s="78"/>
       <c r="BF93" s="78"/>
       <c r="BG93" s="78"/>
       <c r="BH93" s="78"/>
       <c r="BI93" s="117"/>
       <c r="BJ93" s="118"/>
       <c r="BK93" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="BL93" s="145" t="s">
-        <v>748</v>
-      </c>
-      <c r="BM93" s="133"/>
-      <c r="BN93" s="133"/>
-      <c r="BO93" s="134"/>
-      <c r="BP93" s="135"/>
-      <c r="BQ93" s="29"/>
+        <v>95</v>
+      </c>
+      <c r="BL93" s="144" t="s">
+        <v>588</v>
+      </c>
+      <c r="BM93" s="38"/>
+      <c r="BN93" s="38"/>
+      <c r="BO93" s="3"/>
+      <c r="BP93" s="121"/>
+      <c r="BQ93" s="45"/>
       <c r="BR93" s="77"/>
       <c r="BS93" s="77"/>
       <c r="BT93" s="119"/>
     </row>
-    <row r="94" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B94" s="116"/>
       <c r="C94" s="116"/>
       <c r="D94" s="116"/>
@@ -19618,54 +19786,56 @@
       <c r="AJ94" s="77"/>
       <c r="AK94" s="77"/>
       <c r="AL94" s="116"/>
-      <c r="AM94" s="117"/>
-      <c r="AN94" s="78"/>
+      <c r="AM94" s="27"/>
+      <c r="AN94" s="26"/>
       <c r="AO94" s="78"/>
       <c r="AP94" s="117"/>
-      <c r="AQ94" s="117"/>
-      <c r="AR94" s="78"/>
+      <c r="AQ94" s="27"/>
+      <c r="AR94" s="26"/>
       <c r="AS94" s="78"/>
       <c r="AT94" s="78"/>
       <c r="AU94" s="78"/>
-      <c r="AV94" s="117"/>
-      <c r="AW94" s="78"/>
+      <c r="AV94" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW94" s="26" t="s">
+        <v>754</v>
+      </c>
       <c r="AX94" s="78"/>
       <c r="AY94" s="78"/>
-      <c r="AZ94" s="78"/>
-      <c r="BA94" s="5" t="s">
-        <v>763</v>
+      <c r="AZ94" s="148"/>
+      <c r="BA94" s="6" t="s">
+        <v>761</v>
       </c>
       <c r="BB94" s="78" t="s">
         <v>779</v>
       </c>
       <c r="BC94" s="78"/>
       <c r="BD94" s="78" t="s">
-        <v>774</v>
-      </c>
-      <c r="BE94" s="78" t="s">
-        <v>811</v>
-      </c>
+        <v>796</v>
+      </c>
+      <c r="BE94" s="78"/>
       <c r="BF94" s="78"/>
       <c r="BG94" s="78"/>
       <c r="BH94" s="78"/>
       <c r="BI94" s="117"/>
       <c r="BJ94" s="118"/>
       <c r="BK94" s="38" t="s">
-        <v>515</v>
-      </c>
-      <c r="BL94" s="153" t="s">
-        <v>516</v>
+        <v>117</v>
+      </c>
+      <c r="BL94" s="145" t="s">
+        <v>807</v>
       </c>
       <c r="BM94" s="38"/>
       <c r="BN94" s="38"/>
       <c r="BO94" s="3"/>
-      <c r="BP94" s="29"/>
-      <c r="BQ94" s="93"/>
+      <c r="BP94" s="120"/>
+      <c r="BQ94" s="35"/>
       <c r="BR94" s="77"/>
       <c r="BS94" s="77"/>
       <c r="BT94" s="119"/>
     </row>
-    <row r="95" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B95" s="116"/>
       <c r="C95" s="116"/>
       <c r="D95" s="116"/>
@@ -19700,37 +19870,51 @@
       <c r="AS95" s="78"/>
       <c r="AT95" s="78"/>
       <c r="AU95" s="78"/>
-      <c r="AV95" s="117"/>
-      <c r="AW95" s="78"/>
+      <c r="AV95" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW95" s="26" t="s">
+        <v>753</v>
+      </c>
       <c r="AX95" s="78"/>
       <c r="AY95" s="78"/>
-      <c r="AZ95" s="78"/>
-      <c r="BA95" s="78"/>
-      <c r="BB95" s="78"/>
+      <c r="AZ95" s="148" t="s">
+        <v>764</v>
+      </c>
+      <c r="BA95" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="BB95" s="78" t="s">
+        <v>778</v>
+      </c>
       <c r="BC95" s="78"/>
-      <c r="BD95" s="78"/>
-      <c r="BE95" s="78"/>
+      <c r="BD95" s="78" t="s">
+        <v>773</v>
+      </c>
+      <c r="BE95" s="78" t="s">
+        <v>824</v>
+      </c>
       <c r="BF95" s="78"/>
       <c r="BG95" s="78"/>
       <c r="BH95" s="78"/>
       <c r="BI95" s="117"/>
       <c r="BJ95" s="118"/>
       <c r="BK95" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="BL95" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="BM95" s="38"/>
-      <c r="BN95" s="38"/>
-      <c r="BO95" s="3"/>
-      <c r="BP95" s="29"/>
+        <v>246</v>
+      </c>
+      <c r="BL95" s="145" t="s">
+        <v>748</v>
+      </c>
+      <c r="BM95" s="133"/>
+      <c r="BN95" s="133"/>
+      <c r="BO95" s="134"/>
+      <c r="BP95" s="135"/>
       <c r="BQ95" s="29"/>
       <c r="BR95" s="77"/>
       <c r="BS95" s="77"/>
       <c r="BT95" s="119"/>
     </row>
-    <row r="96" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B96" s="116"/>
       <c r="C96" s="116"/>
       <c r="D96" s="116"/>
@@ -19770,28 +19954,40 @@
       <c r="AX96" s="78"/>
       <c r="AY96" s="78"/>
       <c r="AZ96" s="78"/>
-      <c r="BA96" s="78"/>
-      <c r="BB96" s="78"/>
+      <c r="BA96" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="BB96" s="78" t="s">
+        <v>779</v>
+      </c>
       <c r="BC96" s="78"/>
-      <c r="BD96" s="78"/>
-      <c r="BE96" s="78"/>
+      <c r="BD96" s="78" t="s">
+        <v>774</v>
+      </c>
+      <c r="BE96" s="78" t="s">
+        <v>809</v>
+      </c>
       <c r="BF96" s="78"/>
       <c r="BG96" s="78"/>
       <c r="BH96" s="78"/>
       <c r="BI96" s="117"/>
       <c r="BJ96" s="118"/>
-      <c r="BK96" s="46"/>
-      <c r="BL96" s="46"/>
-      <c r="BM96" s="46"/>
-      <c r="BN96" s="46"/>
-      <c r="BO96" s="48"/>
+      <c r="BK96" s="38" t="s">
+        <v>515</v>
+      </c>
+      <c r="BL96" s="153" t="s">
+        <v>516</v>
+      </c>
+      <c r="BM96" s="38"/>
+      <c r="BN96" s="38"/>
+      <c r="BO96" s="3"/>
       <c r="BP96" s="29"/>
-      <c r="BQ96" s="29"/>
+      <c r="BQ96" s="93"/>
       <c r="BR96" s="77"/>
       <c r="BS96" s="77"/>
       <c r="BT96" s="119"/>
     </row>
-    <row r="97" spans="2:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:72" s="115" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B97" s="116"/>
       <c r="C97" s="116"/>
       <c r="D97" s="116"/>
@@ -19841,17 +20037,22 @@
       <c r="BH97" s="78"/>
       <c r="BI97" s="117"/>
       <c r="BJ97" s="118"/>
-      <c r="BK97" s="78"/>
-      <c r="BL97" s="78"/>
-      <c r="BM97" s="78"/>
-      <c r="BN97" s="78"/>
-      <c r="BP97" s="116"/>
-      <c r="BQ97" s="116"/>
+      <c r="BK97" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="BL97" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="BM97" s="38"/>
+      <c r="BN97" s="38"/>
+      <c r="BO97" s="3"/>
+      <c r="BP97" s="29"/>
+      <c r="BQ97" s="29"/>
       <c r="BR97" s="77"/>
       <c r="BS97" s="77"/>
       <c r="BT97" s="119"/>
     </row>
-    <row r="98" spans="2:72" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:72" s="115" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B98" s="116"/>
       <c r="C98" s="116"/>
       <c r="D98" s="116"/>
@@ -19901,15 +20102,136 @@
       <c r="BH98" s="78"/>
       <c r="BI98" s="117"/>
       <c r="BJ98" s="118"/>
-      <c r="BK98" s="78"/>
-      <c r="BL98" s="78"/>
-      <c r="BM98" s="78"/>
-      <c r="BN98" s="78"/>
-      <c r="BP98" s="116"/>
-      <c r="BQ98" s="116"/>
+      <c r="BK98" s="46"/>
+      <c r="BL98" s="46"/>
+      <c r="BM98" s="46"/>
+      <c r="BN98" s="46"/>
+      <c r="BO98" s="48"/>
+      <c r="BP98" s="29"/>
+      <c r="BQ98" s="29"/>
       <c r="BR98" s="77"/>
       <c r="BS98" s="77"/>
       <c r="BT98" s="119"/>
+    </row>
+    <row r="99" spans="2:72" s="115" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="116"/>
+      <c r="C99" s="116"/>
+      <c r="D99" s="116"/>
+      <c r="E99" s="116"/>
+      <c r="F99" s="116"/>
+      <c r="G99" s="116"/>
+      <c r="H99" s="77"/>
+      <c r="K99" s="116"/>
+      <c r="L99" s="116"/>
+      <c r="N99" s="77"/>
+      <c r="O99" s="77"/>
+      <c r="P99" s="77"/>
+      <c r="Q99" s="77"/>
+      <c r="W99" s="77"/>
+      <c r="X99" s="77"/>
+      <c r="Y99" s="77"/>
+      <c r="Z99" s="77"/>
+      <c r="AA99" s="77"/>
+      <c r="AB99" s="77"/>
+      <c r="AC99" s="77"/>
+      <c r="AD99" s="77"/>
+      <c r="AI99" s="77"/>
+      <c r="AJ99" s="77"/>
+      <c r="AK99" s="77"/>
+      <c r="AL99" s="116"/>
+      <c r="AM99" s="117"/>
+      <c r="AN99" s="78"/>
+      <c r="AO99" s="78"/>
+      <c r="AP99" s="117"/>
+      <c r="AQ99" s="117"/>
+      <c r="AR99" s="78"/>
+      <c r="AS99" s="78"/>
+      <c r="AT99" s="78"/>
+      <c r="AU99" s="78"/>
+      <c r="AV99" s="117"/>
+      <c r="AW99" s="78"/>
+      <c r="AX99" s="78"/>
+      <c r="AY99" s="78"/>
+      <c r="AZ99" s="78"/>
+      <c r="BA99" s="78"/>
+      <c r="BB99" s="78"/>
+      <c r="BC99" s="78"/>
+      <c r="BD99" s="78"/>
+      <c r="BE99" s="78"/>
+      <c r="BF99" s="78"/>
+      <c r="BG99" s="78"/>
+      <c r="BH99" s="78"/>
+      <c r="BI99" s="117"/>
+      <c r="BJ99" s="118"/>
+      <c r="BK99" s="78"/>
+      <c r="BL99" s="78"/>
+      <c r="BM99" s="78"/>
+      <c r="BN99" s="78"/>
+      <c r="BP99" s="116"/>
+      <c r="BQ99" s="116"/>
+      <c r="BR99" s="77"/>
+      <c r="BS99" s="77"/>
+      <c r="BT99" s="119"/>
+    </row>
+    <row r="100" spans="2:72" s="115" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="116"/>
+      <c r="C100" s="116"/>
+      <c r="D100" s="116"/>
+      <c r="E100" s="116"/>
+      <c r="F100" s="116"/>
+      <c r="G100" s="116"/>
+      <c r="H100" s="77"/>
+      <c r="K100" s="116"/>
+      <c r="L100" s="116"/>
+      <c r="N100" s="77"/>
+      <c r="O100" s="77"/>
+      <c r="P100" s="77"/>
+      <c r="Q100" s="77"/>
+      <c r="W100" s="77"/>
+      <c r="X100" s="77"/>
+      <c r="Y100" s="77"/>
+      <c r="Z100" s="77"/>
+      <c r="AA100" s="77"/>
+      <c r="AB100" s="77"/>
+      <c r="AC100" s="77"/>
+      <c r="AD100" s="77"/>
+      <c r="AI100" s="77"/>
+      <c r="AJ100" s="77"/>
+      <c r="AK100" s="77"/>
+      <c r="AL100" s="116"/>
+      <c r="AM100" s="117"/>
+      <c r="AN100" s="78"/>
+      <c r="AO100" s="78"/>
+      <c r="AP100" s="117"/>
+      <c r="AQ100" s="117"/>
+      <c r="AR100" s="78"/>
+      <c r="AS100" s="78"/>
+      <c r="AT100" s="78"/>
+      <c r="AU100" s="78"/>
+      <c r="AV100" s="117"/>
+      <c r="AW100" s="78"/>
+      <c r="AX100" s="78"/>
+      <c r="AY100" s="78"/>
+      <c r="AZ100" s="78"/>
+      <c r="BA100" s="78"/>
+      <c r="BB100" s="78"/>
+      <c r="BC100" s="78"/>
+      <c r="BD100" s="78"/>
+      <c r="BE100" s="78"/>
+      <c r="BF100" s="78"/>
+      <c r="BG100" s="78"/>
+      <c r="BH100" s="78"/>
+      <c r="BI100" s="117"/>
+      <c r="BJ100" s="118"/>
+      <c r="BK100" s="78"/>
+      <c r="BL100" s="78"/>
+      <c r="BM100" s="78"/>
+      <c r="BN100" s="78"/>
+      <c r="BP100" s="116"/>
+      <c r="BQ100" s="116"/>
+      <c r="BR100" s="77"/>
+      <c r="BS100" s="77"/>
+      <c r="BT100" s="119"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19923,17 +20245,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:E14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="73" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:5" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:5" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="107" t="s">
         <v>477</v>
       </c>
@@ -19950,7 +20272,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="104" t="s">
         <v>19</v>
       </c>
@@ -19967,7 +20289,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34" t="s">
         <v>60</v>
       </c>
@@ -19984,7 +20306,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="111" t="s">
         <v>123</v>
       </c>
@@ -20001,7 +20323,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
         <v>177</v>
       </c>
@@ -20018,7 +20340,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="111" t="s">
         <v>235</v>
       </c>
@@ -20035,7 +20357,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="111" t="s">
         <v>273</v>
       </c>
@@ -20052,7 +20374,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
         <v>374</v>
       </c>
@@ -20069,7 +20391,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34" t="s">
         <v>435</v>
       </c>
@@ -20086,7 +20408,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="101"/>
     </row>
   </sheetData>
@@ -20101,16 +20423,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:F63"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="128" t="s">
         <v>536</v>
       </c>
@@ -20127,7 +20449,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="41" t="s">
         <v>16</v>
       </c>
@@ -20144,7 +20466,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="34" t="s">
         <v>17</v>
       </c>
@@ -20161,7 +20483,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="34" t="s">
         <v>23</v>
       </c>
@@ -20178,7 +20500,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="34" t="s">
         <v>30</v>
       </c>
@@ -20195,7 +20517,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="34" t="s">
         <v>31</v>
       </c>
@@ -20212,7 +20534,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="34" t="s">
         <v>33</v>
       </c>
@@ -20229,7 +20551,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="34" t="s">
         <v>45</v>
       </c>
@@ -20246,7 +20568,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="34" t="s">
         <v>50</v>
       </c>
@@ -20263,7 +20585,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="34" t="s">
         <v>54</v>
       </c>
@@ -20280,7 +20602,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="34" t="s">
         <v>54</v>
       </c>
@@ -20297,7 +20619,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="34" t="s">
         <v>63</v>
       </c>
@@ -20314,7 +20636,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="34" t="s">
         <v>65</v>
       </c>
@@ -20331,14 +20653,14 @@
         <v>535</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="126"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="34" t="s">
         <v>100</v>
       </c>
@@ -20355,7 +20677,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="34" t="s">
         <v>105</v>
       </c>
@@ -20372,7 +20694,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="34" t="s">
         <v>110</v>
       </c>
@@ -20389,7 +20711,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="34" t="s">
         <v>119</v>
       </c>
@@ -20406,7 +20728,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="34" t="s">
         <v>130</v>
       </c>
@@ -20423,7 +20745,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="34" t="s">
         <v>134</v>
       </c>
@@ -20440,7 +20762,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="34" t="s">
         <v>135</v>
       </c>
@@ -20457,7 +20779,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="34" t="s">
         <v>141</v>
       </c>
@@ -20474,7 +20796,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="34" t="s">
         <v>155</v>
       </c>
@@ -20491,7 +20813,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="34" t="s">
         <v>156</v>
       </c>
@@ -20508,7 +20830,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="34" t="s">
         <v>172</v>
       </c>
@@ -20525,7 +20847,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="34" t="s">
         <v>172</v>
       </c>
@@ -20542,7 +20864,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="34" t="s">
         <v>174</v>
       </c>
@@ -20559,7 +20881,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="34" t="s">
         <v>182</v>
       </c>
@@ -20576,7 +20898,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="34" t="s">
         <v>182</v>
       </c>
@@ -20593,7 +20915,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="34" t="s">
         <v>190</v>
       </c>
@@ -20610,14 +20932,14 @@
         <v>551</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="126"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="34" t="s">
         <v>215</v>
       </c>
@@ -20634,7 +20956,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="34" t="s">
         <v>225</v>
       </c>
@@ -20651,7 +20973,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="34" t="s">
         <v>249</v>
       </c>
@@ -20668,7 +20990,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="34" t="s">
         <v>258</v>
       </c>
@@ -20685,7 +21007,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="34" t="s">
         <v>258</v>
       </c>
@@ -20702,7 +21024,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="34" t="s">
         <v>267</v>
       </c>
@@ -20719,7 +21041,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="34" t="s">
         <v>274</v>
       </c>
@@ -20736,7 +21058,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="34" t="s">
         <v>281</v>
       </c>
@@ -20753,7 +21075,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="34" t="s">
         <v>283</v>
       </c>
@@ -20770,7 +21092,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="34" t="s">
         <v>294</v>
       </c>
@@ -20787,14 +21109,14 @@
         <v>566</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="126"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="34" t="s">
         <v>347</v>
       </c>
@@ -20811,7 +21133,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="34" t="s">
         <v>350</v>
       </c>
@@ -20828,7 +21150,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="34" t="s">
         <v>359</v>
       </c>
@@ -20845,7 +21167,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="34" t="s">
         <v>373</v>
       </c>
@@ -20862,7 +21184,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="34" t="s">
         <v>380</v>
       </c>
@@ -20879,7 +21201,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="34" t="s">
         <v>384</v>
       </c>
@@ -20896,7 +21218,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="34" t="s">
         <v>386</v>
       </c>
@@ -20913,7 +21235,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="34" t="s">
         <v>394</v>
       </c>
@@ -20930,7 +21252,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="34" t="s">
         <v>394</v>
       </c>
@@ -20947,7 +21269,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="34" t="s">
         <v>395</v>
       </c>
@@ -20964,7 +21286,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="34" t="s">
         <v>404</v>
       </c>
@@ -20981,7 +21303,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="34" t="s">
         <v>410</v>
       </c>
@@ -20998,7 +21320,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="34" t="s">
         <v>410</v>
       </c>
@@ -21015,7 +21337,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="34" t="s">
         <v>413</v>
       </c>
@@ -21032,7 +21354,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="34" t="s">
         <v>421</v>
       </c>
@@ -21049,14 +21371,14 @@
         <v>574</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
       <c r="D58" s="14"/>
       <c r="E58" s="14"/>
       <c r="F58" s="126"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="34" t="s">
         <v>434</v>
       </c>
@@ -21073,7 +21395,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="3">
         <v>20220303</v>
       </c>
@@ -21090,7 +21412,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B61" s="3">
         <v>20220406</v>
       </c>
@@ -21107,7 +21429,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62" s="3">
         <v>20220908</v>
       </c>
@@ -21124,7 +21446,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="3">
         <v>20220915</v>
       </c>
@@ -21158,4 +21480,256 @@
     <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13133089-9C8E-40DB-8C04-5B07C5991D49}">
+  <dimension ref="B2:H13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.21875" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D3" s="162"/>
+    </row>
+    <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="161" t="s">
+        <v>813</v>
+      </c>
+      <c r="C4" s="158" t="s">
+        <v>812</v>
+      </c>
+      <c r="D4" s="158" t="s">
+        <v>814</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="159" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="44">
+        <v>28.9</v>
+      </c>
+      <c r="C5" s="44">
+        <v>23.8</v>
+      </c>
+      <c r="D5" s="44">
+        <v>15</v>
+      </c>
+      <c r="E5" s="44">
+        <v>20</v>
+      </c>
+      <c r="F5" s="44">
+        <v>604</v>
+      </c>
+      <c r="G5" s="44">
+        <v>1004</v>
+      </c>
+      <c r="H5" s="44">
+        <f>906*2</f>
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>23.9</v>
+      </c>
+      <c r="D6" s="2">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2">
+        <v>724</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1068</v>
+      </c>
+      <c r="H6" s="2">
+        <f>925*2</f>
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3">
+        <v>18</v>
+      </c>
+      <c r="E7" s="3">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3">
+        <v>709</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1109</v>
+      </c>
+      <c r="H7" s="3">
+        <f>G7*2</f>
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="160">
+        <v>28.5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2">
+        <v>24</v>
+      </c>
+      <c r="F8" s="2">
+        <v>639</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1068</v>
+      </c>
+      <c r="H8" s="2">
+        <f>G8*2</f>
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="C9" s="3">
+        <v>24.9</v>
+      </c>
+      <c r="D9" s="3">
+        <v>30</v>
+      </c>
+      <c r="E9" s="3">
+        <v>22</v>
+      </c>
+      <c r="F9" s="3">
+        <v>604</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1071</v>
+      </c>
+      <c r="H9" s="3">
+        <f>G9*2</f>
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="C10" s="3">
+        <v>25.1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>33</v>
+      </c>
+      <c r="E10" s="3">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3">
+        <v>574</v>
+      </c>
+      <c r="G10" s="3">
+        <v>876</v>
+      </c>
+      <c r="H10" s="3">
+        <f>G10*2-12</f>
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>29.2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2">
+        <v>22</v>
+      </c>
+      <c r="F11" s="2">
+        <v>559</v>
+      </c>
+      <c r="G11" s="2">
+        <v>902</v>
+      </c>
+      <c r="H11" s="2">
+        <f>G11*2</f>
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>25.7</v>
+      </c>
+      <c r="D12" s="3">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3">
+        <v>20</v>
+      </c>
+      <c r="F12" s="3">
+        <v>567</v>
+      </c>
+      <c r="G12" s="3">
+        <v>846</v>
+      </c>
+      <c r="H12" s="3">
+        <f>G12*2</f>
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>817</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:H12">
+    <sortCondition ref="D5:D12"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr showObjects="none" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F91BC11-E862-4C92-8A0D-F26EC4617911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31331451-9524-4D23-AB50-9E35DBD5E91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="829">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2474,9 +2474,6 @@
     <t>internal waves on shelf break, back and forth Emerald basin</t>
   </si>
   <si>
-    <t>shipped</t>
-  </si>
-  <si>
     <t>20250613</t>
   </si>
   <si>
@@ -2489,9 +2486,6 @@
     <t>20250825</t>
   </si>
   <si>
-    <t>GLI2025_SEA022_113</t>
-  </si>
-  <si>
     <t>1540746</t>
   </si>
   <si>
@@ -2522,16 +2516,28 @@
     <t>AZMP fall 2025</t>
   </si>
   <si>
-    <t>Sigma-T</t>
-  </si>
-  <si>
-    <t>AZMP cruise sampled HL2 right during glider deployment</t>
-  </si>
-  <si>
     <t>Burned wire-2</t>
   </si>
   <si>
     <t>GLI2025_SEA032_097</t>
+  </si>
+  <si>
+    <t>GL1-GL2-GL3-GL7-GL3-GL2-GL1-HL2-HL3-TRI-DR</t>
+  </si>
+  <si>
+    <t>AZMP cruise sampled HL2 right during glider deployment, back and forth between HL2 and HL3</t>
+  </si>
+  <si>
+    <t>20251021</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA022_115</t>
+  </si>
+  <si>
+    <t>with TCM on nose, hurricane Melissa,back and forth Emerald basin</t>
+  </si>
+  <si>
+    <t>GLI2025_SEA032_098</t>
   </si>
   <si>
     <t>with TCM on nose</t>
@@ -14665,7 +14671,7 @@
         <v>229</v>
       </c>
       <c r="BJ63" s="42" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="BK63" s="96" t="s">
         <v>246</v>
@@ -15028,7 +15034,7 @@
         <v>229</v>
       </c>
       <c r="BJ65" s="49" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="BK65" s="49">
         <v>201383</v>
@@ -15949,7 +15955,7 @@
         <v>229</v>
       </c>
       <c r="BJ70" s="49" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="BK70" s="22" t="s">
         <v>515</v>
@@ -16136,7 +16142,7 @@
         <v>229</v>
       </c>
       <c r="BJ71" s="49" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="BK71" s="22" t="s">
         <v>515</v>
@@ -17279,7 +17285,7 @@
         <v>229</v>
       </c>
       <c r="BJ77" s="96" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="BK77" s="38" t="s">
         <v>98</v>
@@ -18980,7 +18986,7 @@
         <v>15</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="I87" s="2">
         <v>29.1</v>
@@ -19010,7 +19016,7 @@
         <v>-61.18</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="S87" s="2">
         <v>25</v>
@@ -19089,7 +19095,7 @@
         <v>760</v>
       </c>
       <c r="BB87" s="22" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="BC87" s="22" t="s">
         <v>420</v>
@@ -19133,7 +19139,7 @@
       </c>
       <c r="BS87" s="18"/>
       <c r="BT87" s="21" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="88" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -19143,7 +19149,9 @@
       <c r="B88" s="14">
         <v>20251006</v>
       </c>
-      <c r="C88" s="14"/>
+      <c r="C88" s="14">
+        <v>20251027</v>
+      </c>
       <c r="D88" s="14" t="s">
         <v>44</v>
       </c>
@@ -19157,12 +19165,14 @@
         <v>15</v>
       </c>
       <c r="H88" s="18" t="s">
-        <v>811</v>
+        <v>825</v>
       </c>
       <c r="I88" s="2">
         <v>29.2</v>
       </c>
-      <c r="J88" s="2"/>
+      <c r="J88" s="2">
+        <v>23.6</v>
+      </c>
       <c r="K88" s="11">
         <v>44.476999999999997</v>
       </c>
@@ -19172,17 +19182,34 @@
       <c r="M88" s="100">
         <v>0.55694444444444446</v>
       </c>
-      <c r="N88" s="18"/>
-      <c r="O88" s="18"/>
-      <c r="P88" s="18"/>
-      <c r="Q88" s="18"/>
+      <c r="N88" s="18">
+        <v>42.46</v>
+      </c>
+      <c r="O88" s="18">
+        <v>-63.44</v>
+      </c>
+      <c r="P88" s="18">
+        <v>44.54</v>
+      </c>
+      <c r="Q88" s="18">
+        <v>-61.42</v>
+      </c>
       <c r="R88" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="S88" s="2"/>
-      <c r="T88" s="2"/>
-      <c r="U88" s="2"/>
-      <c r="V88" s="2"/>
+        <v>822</v>
+      </c>
+      <c r="S88" s="2">
+        <v>21</v>
+      </c>
+      <c r="T88" s="2">
+        <v>708</v>
+      </c>
+      <c r="U88" s="2">
+        <v>1174</v>
+      </c>
+      <c r="V88" s="2">
+        <f>U88*2</f>
+        <v>2348</v>
+      </c>
       <c r="W88" s="18" t="s">
         <v>36</v>
       </c>
@@ -19199,9 +19226,15 @@
         <v>781</v>
       </c>
       <c r="AD88" s="18"/>
-      <c r="AE88" s="2"/>
-      <c r="AF88" s="2"/>
-      <c r="AG88" s="2"/>
+      <c r="AE88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="2">
+        <v>0</v>
+      </c>
       <c r="AH88" s="2">
         <v>1022.5</v>
       </c>
@@ -19271,10 +19304,10 @@
         <v>137</v>
       </c>
       <c r="BN88" s="22" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="BO88" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="BP88" s="2" t="s">
         <v>670</v>
@@ -19283,7 +19316,7 @@
         <v>205</v>
       </c>
       <c r="BR88" s="18" t="s">
-        <v>822</v>
+        <v>197</v>
       </c>
       <c r="BS88" s="18"/>
       <c r="BT88" s="21" t="s">
@@ -19294,8 +19327,12 @@
       <c r="A89" s="124">
         <v>7</v>
       </c>
-      <c r="B89" s="14"/>
-      <c r="C89" s="14"/>
+      <c r="B89" s="14">
+        <v>20251027</v>
+      </c>
+      <c r="C89" s="14">
+        <v>20251120</v>
+      </c>
       <c r="D89" s="14" t="s">
         <v>53</v>
       </c>
@@ -19309,24 +19346,51 @@
         <v>15</v>
       </c>
       <c r="H89" s="18" t="s">
-        <v>825</v>
-      </c>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="14"/>
-      <c r="L89" s="14"/>
-      <c r="M89" s="100"/>
-      <c r="N89" s="18"/>
-      <c r="O89" s="18"/>
-      <c r="P89" s="18"/>
-      <c r="Q89" s="18"/>
+        <v>821</v>
+      </c>
+      <c r="I89" s="2">
+        <v>29.2</v>
+      </c>
+      <c r="J89" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="K89" s="14">
+        <v>44.5152</v>
+      </c>
+      <c r="L89" s="14">
+        <v>-63.418599999999998</v>
+      </c>
+      <c r="M89" s="100">
+        <v>0.55069444444444449</v>
+      </c>
+      <c r="N89" s="18">
+        <v>42.46</v>
+      </c>
+      <c r="O89" s="18">
+        <v>-63.38</v>
+      </c>
+      <c r="P89" s="18">
+        <v>44.52</v>
+      </c>
+      <c r="Q89" s="18">
+        <v>-61.41</v>
+      </c>
       <c r="R89" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="S89" s="2"/>
-      <c r="T89" s="2"/>
-      <c r="U89" s="2"/>
-      <c r="V89" s="2"/>
+        <v>804</v>
+      </c>
+      <c r="S89" s="2">
+        <v>24</v>
+      </c>
+      <c r="T89" s="2">
+        <v>662</v>
+      </c>
+      <c r="U89" s="2">
+        <v>958</v>
+      </c>
+      <c r="V89" s="2">
+        <f>U89*2</f>
+        <v>1916</v>
+      </c>
       <c r="W89" s="18" t="s">
         <v>36</v>
       </c>
@@ -19343,9 +19407,15 @@
         <v>781</v>
       </c>
       <c r="AD89" s="18"/>
-      <c r="AE89" s="2"/>
-      <c r="AF89" s="2"/>
-      <c r="AG89" s="2"/>
+      <c r="AE89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="2">
+        <v>0</v>
+      </c>
       <c r="AH89" s="2">
         <v>1023</v>
       </c>
@@ -19385,7 +19455,7 @@
         <v>760</v>
       </c>
       <c r="BB89" s="22" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="BC89" s="22" t="s">
         <v>420</v>
@@ -19424,7 +19494,9 @@
       <c r="BQ89" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BR89" s="18"/>
+      <c r="BR89" s="18" t="s">
+        <v>197</v>
+      </c>
       <c r="BS89" s="18"/>
       <c r="BT89" s="21" t="s">
         <v>826</v>
@@ -19434,11 +19506,21 @@
       <c r="A90" s="124"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
-      <c r="H90" s="18"/>
+      <c r="D90" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E90" s="14">
+        <v>98</v>
+      </c>
+      <c r="F90" s="14">
+        <v>4800937</v>
+      </c>
+      <c r="G90" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="18" t="s">
+        <v>827</v>
+      </c>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="14"/>
@@ -19448,27 +19530,47 @@
       <c r="O90" s="18"/>
       <c r="P90" s="18"/>
       <c r="Q90" s="18"/>
-      <c r="R90" s="2"/>
+      <c r="R90" s="2" t="s">
+        <v>444</v>
+      </c>
       <c r="S90" s="2"/>
       <c r="T90" s="2"/>
       <c r="U90" s="2"/>
       <c r="V90" s="2"/>
-      <c r="W90" s="18"/>
-      <c r="X90" s="18"/>
+      <c r="W90" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="X90" s="18">
+        <v>1</v>
+      </c>
       <c r="Y90" s="18"/>
-      <c r="Z90" s="18"/>
+      <c r="Z90" s="18" t="s">
+        <v>183</v>
+      </c>
       <c r="AA90" s="18"/>
       <c r="AB90" s="18"/>
-      <c r="AC90" s="18"/>
+      <c r="AC90" s="18" t="s">
+        <v>781</v>
+      </c>
       <c r="AD90" s="18"/>
       <c r="AE90" s="2"/>
       <c r="AF90" s="2"/>
       <c r="AG90" s="2"/>
-      <c r="AH90" s="2"/>
-      <c r="AI90" s="18"/>
-      <c r="AJ90" s="18"/>
-      <c r="AK90" s="18"/>
-      <c r="AL90" s="14"/>
+      <c r="AH90" s="2">
+        <v>1023</v>
+      </c>
+      <c r="AI90" s="18">
+        <v>20251014</v>
+      </c>
+      <c r="AJ90" s="18" t="s">
+        <v>752</v>
+      </c>
+      <c r="AK90" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="AL90" s="14">
+        <v>32</v>
+      </c>
       <c r="AM90" s="20"/>
       <c r="AN90" s="22"/>
       <c r="AO90" s="22"/>
@@ -19478,31 +19580,65 @@
       <c r="AS90" s="22"/>
       <c r="AT90" s="22"/>
       <c r="AU90" s="22"/>
-      <c r="AV90" s="10"/>
-      <c r="AW90" s="16"/>
-      <c r="AX90" s="22"/>
+      <c r="AV90" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW90" s="16">
+        <v>45629</v>
+      </c>
+      <c r="AX90" s="22" t="s">
+        <v>461</v>
+      </c>
       <c r="AY90" s="22"/>
       <c r="AZ90" s="22"/>
-      <c r="BA90" s="22"/>
-      <c r="BB90" s="22"/>
-      <c r="BC90" s="22"/>
-      <c r="BD90" s="22"/>
-      <c r="BE90" s="22"/>
+      <c r="BA90" s="22" t="s">
+        <v>760</v>
+      </c>
+      <c r="BB90" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="BC90" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="BD90" s="22" t="s">
+        <v>795</v>
+      </c>
+      <c r="BE90" s="22" t="s">
+        <v>797</v>
+      </c>
       <c r="BF90" s="22"/>
       <c r="BG90" s="22"/>
       <c r="BH90" s="22"/>
-      <c r="BI90" s="20"/>
-      <c r="BJ90" s="146"/>
-      <c r="BK90" s="22"/>
-      <c r="BL90" s="22"/>
-      <c r="BM90" s="22"/>
-      <c r="BN90" s="22"/>
+      <c r="BI90" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ90" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK90" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="BL90" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="BM90" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="BN90" s="2">
+        <v>1272212</v>
+      </c>
       <c r="BO90" s="2"/>
-      <c r="BP90" s="149"/>
-      <c r="BQ90" s="14"/>
+      <c r="BP90" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="BQ90" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="BR90" s="18"/>
       <c r="BS90" s="18"/>
-      <c r="BT90" s="21"/>
+      <c r="BT90" s="21" t="s">
+        <v>828</v>
+      </c>
     </row>
     <row r="91" spans="1:72" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A91" s="124"/>
@@ -19672,6 +19808,22 @@
       <c r="O93" s="77"/>
       <c r="P93" s="77"/>
       <c r="Q93" s="77"/>
+      <c r="S93" s="115">
+        <f>SUM(S3:S89)</f>
+        <v>1632</v>
+      </c>
+      <c r="T93" s="115">
+        <f>SUM(T3:T89)</f>
+        <v>41669</v>
+      </c>
+      <c r="U93" s="115">
+        <f>SUM(U3:U89)</f>
+        <v>74897</v>
+      </c>
+      <c r="V93" s="115">
+        <f>SUM(V3:V89)</f>
+        <v>88621</v>
+      </c>
       <c r="W93" s="77"/>
       <c r="X93" s="77"/>
       <c r="Y93" s="77"/>
@@ -19795,7 +19947,7 @@
         <v>117</v>
       </c>
       <c r="BL94" s="145" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="BM94" s="38"/>
       <c r="BN94" s="38"/>
@@ -19863,7 +20015,7 @@
         <v>773</v>
       </c>
       <c r="BE95" s="78" t="s">
-        <v>806</v>
+        <v>824</v>
       </c>
       <c r="BF95" s="78"/>
       <c r="BG95" s="78"/>
@@ -19936,7 +20088,7 @@
         <v>774</v>
       </c>
       <c r="BE96" s="78" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="BF96" s="78"/>
       <c r="BG96" s="78"/>
@@ -21459,7 +21611,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.1796875" customWidth="1"/>
@@ -21468,10 +21620,10 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21479,13 +21631,13 @@
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="161" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C4" s="158" t="s">
+        <v>812</v>
+      </c>
+      <c r="D4" s="158" t="s">
         <v>814</v>
-      </c>
-      <c r="D4" s="158" t="s">
-        <v>816</v>
       </c>
       <c r="E4" s="31" t="s">
         <v>22</v>
@@ -21694,7 +21846,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31331451-9524-4D23-AB50-9E35DBD5E91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2041914E-BA5D-43EA-B6EA-7621AA1EF2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2839" uniqueCount="830">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2541,6 +2541,9 @@
   </si>
   <si>
     <t>with TCM on nose</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -19880,7 +19883,9 @@
       <c r="BP93" s="121"/>
       <c r="BQ93" s="45"/>
       <c r="BR93" s="77"/>
-      <c r="BS93" s="77"/>
+      <c r="BS93" s="77" t="s">
+        <v>829</v>
+      </c>
       <c r="BT93" s="119"/>
     </row>
     <row r="94" spans="1:72" s="115" customFormat="1" x14ac:dyDescent="0.35">

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEE2E4D-6BCD-4C86-BA6F-6F55991E96E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC6E060-FF3D-4A01-B8B3-7AE26EDB07A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3001" uniqueCount="846">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2558,13 +2558,40 @@
     <t>BB</t>
   </si>
   <si>
-    <t>GL1-GL2-GL3-GL6.5-GL3-GL2-GL1-TRI-DR</t>
-  </si>
-  <si>
-    <t>Turned around before HL7 (17.3km before) for filming  weather window, +/-500 in deep water</t>
-  </si>
-  <si>
     <t>Burned wire-3</t>
+  </si>
+  <si>
+    <t>GL1-GL2-GL3-GL6.7-GL3-GL2-GL1-TRI-DR</t>
+  </si>
+  <si>
+    <t>2- slightly diff than 1</t>
+  </si>
+  <si>
+    <t>3- camemberg with ind battery</t>
+  </si>
+  <si>
+    <t>Turned around before HL7 (17.3km before) for filming  weather window, +/-500ml in deep water, ecopuck spike</t>
+  </si>
+  <si>
+    <t>Ecopuck visual spikes</t>
+  </si>
+  <si>
+    <t>Depth rating</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>first mission at 1000m depth</t>
+  </si>
+  <si>
+    <t>GLI2026_SEA019_148</t>
+  </si>
+  <si>
+    <t>3.9.4-r</t>
   </si>
 </sst>
 </file>
@@ -2575,7 +2602,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2663,6 +2690,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2916,7 +2949,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3313,9 +3346,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3645,7 +3675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DA101"/>
+  <dimension ref="A1:DB101"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.54296875" customWidth="1"/>
@@ -3703,20 +3733,20 @@
     <col min="56" max="56" width="15.1796875" style="78" bestFit="1" customWidth="1"/>
     <col min="57" max="62" width="15.1796875" style="78" customWidth="1"/>
     <col min="63" max="63" width="11.81640625" style="5" customWidth="1"/>
-    <col min="64" max="64" width="16.36328125" style="1" customWidth="1"/>
-    <col min="65" max="65" width="12.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="12.81640625" style="6" customWidth="1"/>
-    <col min="67" max="67" width="7" style="6" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="7.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="19" style="4" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="20" style="4" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="25.81640625" style="7" customWidth="1"/>
-    <col min="73" max="73" width="64.453125" style="7" customWidth="1"/>
-    <col min="74" max="74" width="78.81640625" style="8" customWidth="1"/>
+    <col min="64" max="65" width="16.36328125" style="1" customWidth="1"/>
+    <col min="66" max="66" width="12.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="12.81640625" style="6" customWidth="1"/>
+    <col min="68" max="68" width="7" style="6" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="7.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="19" style="4" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="20" style="4" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="25.81640625" style="7" customWidth="1"/>
+    <col min="74" max="74" width="64.453125" style="7" customWidth="1"/>
+    <col min="75" max="75" width="78.81640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:75" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C1" s="24"/>
       <c r="D1" s="148" t="s">
         <v>799</v>
@@ -3773,17 +3803,18 @@
       <c r="BJ1" s="26"/>
       <c r="BK1" s="27"/>
       <c r="BL1" s="28"/>
-      <c r="BM1" s="26"/>
+      <c r="BM1" s="28"/>
       <c r="BN1" s="26"/>
       <c r="BO1" s="26"/>
       <c r="BP1" s="26"/>
-      <c r="BR1" s="29"/>
+      <c r="BQ1" s="26"/>
       <c r="BS1" s="29"/>
-      <c r="BT1" s="25"/>
+      <c r="BT1" s="29"/>
       <c r="BU1" s="25"/>
-      <c r="BV1" s="30"/>
+      <c r="BV1" s="25"/>
+      <c r="BW1" s="30"/>
     </row>
-    <row r="2" spans="1:74" s="63" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:75" s="63" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C2" s="64" t="s">
         <v>0</v>
       </c>
@@ -3970,38 +4001,41 @@
       <c r="BL2" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="BM2" s="70" t="s">
+      <c r="BM2" s="33" t="s">
+        <v>840</v>
+      </c>
+      <c r="BN2" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="BN2" s="70" t="s">
+      <c r="BO2" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="BO2" s="70" t="s">
+      <c r="BP2" s="70" t="s">
         <v>221</v>
       </c>
-      <c r="BP2" s="70" t="s">
+      <c r="BQ2" s="70" t="s">
         <v>688</v>
       </c>
-      <c r="BQ2" s="32" t="s">
+      <c r="BR2" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="BR2" s="74" t="s">
+      <c r="BS2" s="74" t="s">
         <v>191</v>
       </c>
-      <c r="BS2" s="74" t="s">
+      <c r="BT2" s="74" t="s">
         <v>192</v>
       </c>
-      <c r="BT2" s="75" t="s">
+      <c r="BU2" s="75" t="s">
         <v>659</v>
       </c>
-      <c r="BU2" s="75" t="s">
+      <c r="BV2" s="75" t="s">
         <v>689</v>
       </c>
-      <c r="BV2" s="76" t="s">
+      <c r="BW2" s="76" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:74" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:75" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="124">
         <v>1</v>
       </c>
@@ -4157,30 +4191,33 @@
       <c r="BL3" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="BM3" s="15" t="s">
+      <c r="BM3" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN3" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN3" s="15" t="s">
+      <c r="BO3" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="BO3" s="15"/>
       <c r="BP3" s="15"/>
-      <c r="BQ3" s="13"/>
-      <c r="BR3" s="14" t="s">
+      <c r="BQ3" s="15"/>
+      <c r="BR3" s="13"/>
+      <c r="BS3" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS3" s="14" t="s">
+      <c r="BT3" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT3" s="18" t="s">
+      <c r="BU3" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU3" s="12"/>
-      <c r="BV3" s="19" t="s">
+      <c r="BV3" s="12"/>
+      <c r="BW3" s="19" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:74" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:75" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="124">
         <v>2</v>
       </c>
@@ -4336,32 +4373,35 @@
       <c r="BL4" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="BM4" s="15" t="s">
+      <c r="BM4" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN4" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN4" s="15" t="s">
+      <c r="BO4" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="BO4" s="15"/>
       <c r="BP4" s="15"/>
-      <c r="BQ4" s="2"/>
-      <c r="BR4" s="14" t="s">
+      <c r="BQ4" s="15"/>
+      <c r="BR4" s="2"/>
+      <c r="BS4" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS4" s="14" t="s">
+      <c r="BT4" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT4" s="18" t="s">
+      <c r="BU4" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="BU4" s="18" t="s">
+      <c r="BV4" s="18" t="s">
         <v>707</v>
       </c>
-      <c r="BV4" s="21" t="s">
+      <c r="BW4" s="21" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="5" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="137">
         <v>3</v>
       </c>
@@ -4517,32 +4557,35 @@
       <c r="BL5" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM5" s="40" t="s">
+      <c r="BM5" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN5" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BN5" s="40" t="s">
+      <c r="BO5" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="BO5" s="40"/>
       <c r="BP5" s="40"/>
-      <c r="BQ5" s="3" t="s">
+      <c r="BQ5" s="40"/>
+      <c r="BR5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="BR5" s="35" t="s">
+      <c r="BS5" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS5" s="35" t="s">
+      <c r="BT5" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT5" s="37" t="s">
+      <c r="BU5" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU5" s="37"/>
-      <c r="BV5" s="43" t="s">
+      <c r="BV5" s="37"/>
+      <c r="BW5" s="43" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="137">
         <v>4</v>
       </c>
@@ -4699,32 +4742,35 @@
       <c r="BL6" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM6" s="40" t="s">
+      <c r="BM6" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN6" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BN6" s="40" t="s">
+      <c r="BO6" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="BO6" s="40"/>
       <c r="BP6" s="40"/>
-      <c r="BQ6" s="3"/>
-      <c r="BR6" s="35" t="s">
+      <c r="BQ6" s="40"/>
+      <c r="BR6" s="3"/>
+      <c r="BS6" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS6" s="35" t="s">
+      <c r="BT6" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT6" s="37" t="s">
+      <c r="BU6" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU6" s="37" t="s">
+      <c r="BV6" s="37" t="s">
         <v>708</v>
       </c>
-      <c r="BV6" s="43" t="s">
+      <c r="BW6" s="43" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="137">
         <v>5</v>
       </c>
@@ -4880,34 +4926,37 @@
       <c r="BL7" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM7" s="40" t="s">
+      <c r="BM7" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN7" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BN7" s="40" t="s">
+      <c r="BO7" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="BO7" s="40"/>
       <c r="BP7" s="40"/>
-      <c r="BQ7" s="3" t="s">
+      <c r="BQ7" s="40"/>
+      <c r="BR7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="BR7" s="35" t="s">
+      <c r="BS7" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS7" s="35" t="s">
+      <c r="BT7" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT7" s="37" t="s">
+      <c r="BU7" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU7" s="37" t="s">
+      <c r="BV7" s="37" t="s">
         <v>709</v>
       </c>
-      <c r="BV7" s="43" t="s">
+      <c r="BW7" s="43" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="8" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="137">
         <v>6</v>
       </c>
@@ -5063,32 +5112,35 @@
       <c r="BL8" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM8" s="40" t="s">
+      <c r="BM8" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN8" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BN8" s="40" t="s">
+      <c r="BO8" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BO8" s="40"/>
       <c r="BP8" s="40"/>
-      <c r="BQ8" s="3"/>
-      <c r="BR8" s="35" t="s">
+      <c r="BQ8" s="40"/>
+      <c r="BR8" s="3"/>
+      <c r="BS8" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS8" s="35" t="s">
+      <c r="BT8" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT8" s="37" t="s">
+      <c r="BU8" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU8" s="37" t="s">
+      <c r="BV8" s="37" t="s">
         <v>710</v>
       </c>
-      <c r="BV8" s="43" t="s">
+      <c r="BW8" s="43" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="9" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="137">
         <v>7</v>
       </c>
@@ -5244,32 +5296,35 @@
       <c r="BL9" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM9" s="40" t="s">
+      <c r="BM9" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN9" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BN9" s="40" t="s">
+      <c r="BO9" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="BO9" s="40"/>
       <c r="BP9" s="40"/>
-      <c r="BQ9" s="3"/>
-      <c r="BR9" s="35" t="s">
+      <c r="BQ9" s="40"/>
+      <c r="BR9" s="3"/>
+      <c r="BS9" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS9" s="35" t="s">
+      <c r="BT9" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT9" s="37" t="s">
+      <c r="BU9" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU9" s="37" t="s">
+      <c r="BV9" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="BV9" s="43" t="s">
+      <c r="BW9" s="43" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="137">
         <v>8</v>
       </c>
@@ -5425,32 +5480,35 @@
       <c r="BL10" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM10" s="40" t="s">
+      <c r="BM10" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN10" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BN10" s="40" t="s">
+      <c r="BO10" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BO10" s="40"/>
       <c r="BP10" s="40"/>
-      <c r="BQ10" s="3"/>
-      <c r="BR10" s="35" t="s">
+      <c r="BQ10" s="40"/>
+      <c r="BR10" s="3"/>
+      <c r="BS10" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS10" s="35" t="s">
+      <c r="BT10" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT10" s="37" t="s">
+      <c r="BU10" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="BU10" s="37" t="s">
+      <c r="BV10" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="BV10" s="51" t="s">
+      <c r="BW10" s="51" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="137">
         <v>9</v>
       </c>
@@ -5606,32 +5664,35 @@
       <c r="BL11" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM11" s="40" t="s">
+      <c r="BM11" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN11" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BN11" s="40" t="s">
+      <c r="BO11" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BO11" s="40"/>
       <c r="BP11" s="40"/>
-      <c r="BQ11" s="3"/>
-      <c r="BR11" s="35" t="s">
+      <c r="BQ11" s="40"/>
+      <c r="BR11" s="3"/>
+      <c r="BS11" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS11" s="35" t="s">
+      <c r="BT11" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT11" s="37" t="s">
+      <c r="BU11" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU11" s="37" t="s">
+      <c r="BV11" s="37" t="s">
         <v>712</v>
       </c>
-      <c r="BV11" s="51" t="s">
+      <c r="BW11" s="51" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="137">
         <v>10</v>
       </c>
@@ -5791,32 +5852,35 @@
       <c r="BL12" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM12" s="40" t="s">
+      <c r="BM12" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN12" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BN12" s="40" t="s">
+      <c r="BO12" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="BO12" s="40"/>
       <c r="BP12" s="40"/>
-      <c r="BQ12" s="3"/>
-      <c r="BR12" s="35" t="s">
+      <c r="BQ12" s="40"/>
+      <c r="BR12" s="3"/>
+      <c r="BS12" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS12" s="35" t="s">
+      <c r="BT12" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT12" s="37" t="s">
+      <c r="BU12" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU12" s="37" t="s">
+      <c r="BV12" s="37" t="s">
         <v>712</v>
       </c>
-      <c r="BV12" s="51" t="s">
+      <c r="BW12" s="51" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="137">
         <v>11</v>
       </c>
@@ -5975,34 +6039,37 @@
       <c r="BL13" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM13" s="38" t="s">
+      <c r="BM13" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN13" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BN13" s="38" t="s">
+      <c r="BO13" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="BO13" s="38"/>
       <c r="BP13" s="38"/>
-      <c r="BQ13" s="3" t="s">
+      <c r="BQ13" s="38"/>
+      <c r="BR13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="BR13" s="35" t="s">
+      <c r="BS13" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS13" s="35" t="s">
+      <c r="BT13" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT13" s="37" t="s">
+      <c r="BU13" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="BU13" s="142" t="s">
+      <c r="BV13" s="142" t="s">
         <v>713</v>
       </c>
-      <c r="BV13" s="52" t="s">
+      <c r="BW13" s="52" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="14" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="137">
         <v>12</v>
       </c>
@@ -6158,32 +6225,35 @@
       <c r="BL14" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM14" s="40" t="s">
+      <c r="BM14" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN14" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BN14" s="40" t="s">
+      <c r="BO14" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BO14" s="40"/>
       <c r="BP14" s="40"/>
-      <c r="BQ14" s="3"/>
-      <c r="BR14" s="35" t="s">
+      <c r="BQ14" s="40"/>
+      <c r="BR14" s="3"/>
+      <c r="BS14" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS14" s="35" t="s">
+      <c r="BT14" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT14" s="37" t="s">
+      <c r="BU14" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU14" s="37" t="s">
+      <c r="BV14" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="BV14" s="43" t="s">
+      <c r="BW14" s="43" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="137">
         <v>13</v>
       </c>
@@ -6343,32 +6413,35 @@
       <c r="BL15" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM15" s="40" t="s">
+      <c r="BM15" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN15" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BN15" s="40" t="s">
+      <c r="BO15" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="BO15" s="40"/>
       <c r="BP15" s="40"/>
-      <c r="BQ15" s="3"/>
-      <c r="BR15" s="35" t="s">
+      <c r="BQ15" s="40"/>
+      <c r="BR15" s="3"/>
+      <c r="BS15" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS15" s="35" t="s">
+      <c r="BT15" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT15" s="37" t="s">
+      <c r="BU15" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU15" s="141" t="s">
+      <c r="BV15" s="141" t="s">
         <v>714</v>
       </c>
-      <c r="BV15" s="43" t="s">
+      <c r="BW15" s="43" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="16" spans="1:74" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:75" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="137">
         <v>14</v>
       </c>
@@ -6524,34 +6597,37 @@
       <c r="BL16" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM16" s="38" t="s">
+      <c r="BM16" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN16" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BN16" s="38" t="s">
+      <c r="BO16" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="BO16" s="92" t="s">
+      <c r="BP16" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP16" s="38"/>
-      <c r="BQ16" s="3"/>
-      <c r="BR16" s="35" t="s">
+      <c r="BQ16" s="38"/>
+      <c r="BR16" s="3"/>
+      <c r="BS16" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS16" s="35" t="s">
+      <c r="BT16" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT16" s="37" t="s">
+      <c r="BU16" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU16" s="37" t="s">
+      <c r="BV16" s="37" t="s">
         <v>715</v>
       </c>
-      <c r="BV16" s="43" t="s">
+      <c r="BW16" s="43" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="17" spans="1:74" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:75" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="137">
         <v>15</v>
       </c>
@@ -6706,34 +6782,37 @@
       <c r="BL17" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM17" s="40" t="s">
+      <c r="BM17" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN17" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BN17" s="38" t="s">
+      <c r="BO17" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="BO17" s="92" t="s">
+      <c r="BP17" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP17" s="38"/>
-      <c r="BQ17" s="3"/>
-      <c r="BR17" s="35" t="s">
+      <c r="BQ17" s="38"/>
+      <c r="BR17" s="3"/>
+      <c r="BS17" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS17" s="35" t="s">
+      <c r="BT17" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT17" s="37" t="s">
+      <c r="BU17" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU17" s="37" t="s">
+      <c r="BV17" s="37" t="s">
         <v>716</v>
       </c>
-      <c r="BV17" s="43" t="s">
+      <c r="BW17" s="43" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="124">
         <v>16</v>
       </c>
@@ -6888,34 +6967,37 @@
       <c r="BL18" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM18" s="22" t="s">
+      <c r="BM18" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN18" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BN18" s="22" t="s">
+      <c r="BO18" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BO18" s="22"/>
       <c r="BP18" s="22"/>
-      <c r="BQ18" s="2" t="s">
+      <c r="BQ18" s="22"/>
+      <c r="BR18" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="BR18" s="14" t="s">
+      <c r="BS18" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS18" s="14" t="s">
+      <c r="BT18" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT18" s="18" t="s">
+      <c r="BU18" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU18" s="18" t="s">
+      <c r="BV18" s="18" t="s">
         <v>716</v>
       </c>
-      <c r="BV18" s="21" t="s">
+      <c r="BW18" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="124">
         <v>17</v>
       </c>
@@ -7066,32 +7148,35 @@
       <c r="BL19" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM19" s="54" t="s">
+      <c r="BM19" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN19" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="BN19" s="54" t="s">
+      <c r="BO19" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="BO19" s="22"/>
       <c r="BP19" s="22"/>
-      <c r="BQ19" s="2"/>
-      <c r="BR19" s="14" t="s">
+      <c r="BQ19" s="22"/>
+      <c r="BR19" s="2"/>
+      <c r="BS19" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS19" s="14" t="s">
+      <c r="BT19" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="BT19" s="18" t="s">
+      <c r="BU19" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU19" s="18" t="s">
+      <c r="BV19" s="18" t="s">
         <v>716</v>
       </c>
-      <c r="BV19" s="21" t="s">
+      <c r="BW19" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="124">
         <v>18</v>
       </c>
@@ -7246,34 +7331,37 @@
       <c r="BL20" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM20" s="22" t="s">
+      <c r="BM20" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN20" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BN20" s="22" t="s">
+      <c r="BO20" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BO20" s="92" t="s">
+      <c r="BP20" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP20" s="22"/>
-      <c r="BQ20" s="2"/>
-      <c r="BR20" s="14" t="s">
+      <c r="BQ20" s="22"/>
+      <c r="BR20" s="2"/>
+      <c r="BS20" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS20" s="14" t="s">
+      <c r="BT20" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT20" s="18" t="s">
+      <c r="BU20" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU20" s="140" t="s">
+      <c r="BV20" s="140" t="s">
         <v>691</v>
       </c>
-      <c r="BV20" s="21" t="s">
+      <c r="BW20" s="21" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="124">
         <v>18</v>
       </c>
@@ -7429,34 +7517,37 @@
       <c r="BL21" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM21" s="22" t="s">
+      <c r="BM21" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN21" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BN21" s="22" t="s">
+      <c r="BO21" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BO21" s="92" t="s">
+      <c r="BP21" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP21" s="22"/>
-      <c r="BQ21" s="2"/>
-      <c r="BR21" s="14" t="s">
+      <c r="BQ21" s="22"/>
+      <c r="BR21" s="2"/>
+      <c r="BS21" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS21" s="14" t="s">
+      <c r="BT21" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT21" s="18" t="s">
+      <c r="BU21" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU21" s="18" t="s">
+      <c r="BV21" s="18" t="s">
         <v>717</v>
       </c>
-      <c r="BV21" s="21" t="s">
+      <c r="BW21" s="21" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="22" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="124">
         <v>19</v>
       </c>
@@ -7612,34 +7703,37 @@
       <c r="BL22" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM22" s="22" t="s">
+      <c r="BM22" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN22" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BN22" s="22" t="s">
+      <c r="BO22" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BO22" s="92" t="s">
+      <c r="BP22" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP22" s="22"/>
-      <c r="BQ22" s="2"/>
-      <c r="BR22" s="14" t="s">
+      <c r="BQ22" s="22"/>
+      <c r="BR22" s="2"/>
+      <c r="BS22" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS22" s="14" t="s">
+      <c r="BT22" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT22" s="18" t="s">
+      <c r="BU22" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU22" s="18" t="s">
+      <c r="BV22" s="18" t="s">
         <v>718</v>
       </c>
-      <c r="BV22" s="21" t="s">
+      <c r="BW22" s="21" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="23" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="124">
         <v>20</v>
       </c>
@@ -7795,34 +7889,37 @@
       <c r="BL23" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM23" s="22" t="s">
+      <c r="BM23" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN23" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BN23" s="22" t="s">
+      <c r="BO23" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BO23" s="92" t="s">
+      <c r="BP23" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP23" s="22"/>
-      <c r="BQ23" s="2"/>
-      <c r="BR23" s="14" t="s">
+      <c r="BQ23" s="22"/>
+      <c r="BR23" s="2"/>
+      <c r="BS23" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS23" s="14" t="s">
+      <c r="BT23" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT23" s="18" t="s">
+      <c r="BU23" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="BU23" s="140" t="s">
+      <c r="BV23" s="140" t="s">
         <v>719</v>
       </c>
-      <c r="BV23" s="21" t="s">
+      <c r="BW23" s="21" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="124">
         <v>21</v>
       </c>
@@ -7978,32 +8075,35 @@
       <c r="BL24" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM24" s="15" t="s">
+      <c r="BM24" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN24" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN24" s="22" t="s">
+      <c r="BO24" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="BO24" s="22"/>
       <c r="BP24" s="22"/>
-      <c r="BQ24" s="2"/>
-      <c r="BR24" s="14" t="s">
+      <c r="BQ24" s="22"/>
+      <c r="BR24" s="2"/>
+      <c r="BS24" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="BS24" s="14" t="s">
+      <c r="BT24" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT24" s="18" t="s">
+      <c r="BU24" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="BU24" s="139" t="s">
+      <c r="BV24" s="139" t="s">
         <v>717</v>
       </c>
-      <c r="BV24" s="50" t="s">
+      <c r="BW24" s="50" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="25" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="124">
         <v>22</v>
       </c>
@@ -8156,34 +8256,37 @@
       <c r="BL25" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM25" s="54" t="s">
+      <c r="BM25" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN25" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="BN25" s="54" t="s">
+      <c r="BO25" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="BO25" s="92" t="s">
+      <c r="BP25" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP25" s="22"/>
-      <c r="BQ25" s="2"/>
-      <c r="BR25" s="14" t="s">
+      <c r="BQ25" s="22"/>
+      <c r="BR25" s="2"/>
+      <c r="BS25" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS25" s="14" t="s">
+      <c r="BT25" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT25" s="18" t="s">
+      <c r="BU25" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="BU25" s="140" t="s">
+      <c r="BV25" s="140" t="s">
         <v>734</v>
       </c>
-      <c r="BV25" s="21" t="s">
+      <c r="BW25" s="21" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="26" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="124">
         <v>23</v>
       </c>
@@ -8340,34 +8443,37 @@
       <c r="BL26" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM26" s="22" t="s">
+      <c r="BM26" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN26" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BN26" s="22" t="s">
+      <c r="BO26" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BO26" s="92" t="s">
+      <c r="BP26" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP26" s="22"/>
-      <c r="BQ26" s="2"/>
-      <c r="BR26" s="14" t="s">
+      <c r="BQ26" s="22"/>
+      <c r="BR26" s="2"/>
+      <c r="BS26" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS26" s="14" t="s">
+      <c r="BT26" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT26" s="18" t="s">
+      <c r="BU26" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="BU26" s="18" t="s">
+      <c r="BV26" s="18" t="s">
         <v>718</v>
       </c>
-      <c r="BV26" s="21" t="s">
+      <c r="BW26" s="21" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="124">
         <v>24</v>
       </c>
@@ -8522,32 +8628,35 @@
       <c r="BL27" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM27" s="15" t="s">
+      <c r="BM27" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN27" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN27" s="22" t="s">
+      <c r="BO27" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="BO27" s="22"/>
       <c r="BP27" s="22"/>
-      <c r="BQ27" s="2"/>
-      <c r="BR27" s="14" t="s">
+      <c r="BQ27" s="22"/>
+      <c r="BR27" s="2"/>
+      <c r="BS27" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="BS27" s="14" t="s">
+      <c r="BT27" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT27" s="18" t="s">
+      <c r="BU27" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="BU27" s="139" t="s">
+      <c r="BV27" s="139" t="s">
         <v>717</v>
       </c>
-      <c r="BV27" s="50" t="s">
+      <c r="BW27" s="50" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="28" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="124">
         <v>25</v>
       </c>
@@ -8703,34 +8812,37 @@
       <c r="BL28" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM28" s="15" t="s">
+      <c r="BM28" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN28" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BN28" s="22" t="s">
+      <c r="BO28" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="BO28" s="92" t="s">
+      <c r="BP28" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP28" s="22"/>
-      <c r="BQ28" s="2"/>
-      <c r="BR28" s="14" t="s">
+      <c r="BQ28" s="22"/>
+      <c r="BR28" s="2"/>
+      <c r="BS28" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS28" s="14" t="s">
+      <c r="BT28" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT28" s="18" t="s">
+      <c r="BU28" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU28" s="18" t="s">
+      <c r="BV28" s="18" t="s">
         <v>711</v>
       </c>
-      <c r="BV28" s="21" t="s">
+      <c r="BW28" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="29" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="124">
         <v>26</v>
       </c>
@@ -8873,30 +8985,33 @@
       <c r="BL29" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM29" s="22" t="s">
+      <c r="BM29" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN29" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="BN29" s="22" t="s">
+      <c r="BO29" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="BO29" s="22"/>
       <c r="BP29" s="22"/>
-      <c r="BQ29" s="2"/>
-      <c r="BR29" s="14" t="s">
+      <c r="BQ29" s="22"/>
+      <c r="BR29" s="2"/>
+      <c r="BS29" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS29" s="14" t="s">
+      <c r="BT29" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT29" s="18" t="s">
+      <c r="BU29" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU29" s="18"/>
-      <c r="BV29" s="21" t="s">
+      <c r="BV29" s="18"/>
+      <c r="BW29" s="21" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="124">
         <v>27</v>
       </c>
@@ -9052,34 +9167,37 @@
       <c r="BL30" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BM30" s="15" t="s">
+      <c r="BM30" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN30" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN30" s="15" t="s">
+      <c r="BO30" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="BO30" s="92" t="s">
+      <c r="BP30" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP30" s="22"/>
-      <c r="BQ30" s="2"/>
-      <c r="BR30" s="14" t="s">
+      <c r="BQ30" s="22"/>
+      <c r="BR30" s="2"/>
+      <c r="BS30" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS30" s="14" t="s">
+      <c r="BT30" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT30" s="18" t="s">
+      <c r="BU30" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU30" s="18" t="s">
+      <c r="BV30" s="18" t="s">
         <v>711</v>
       </c>
-      <c r="BV30" s="21" t="s">
+      <c r="BW30" s="21" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="31" spans="1:74" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:75" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="124">
         <v>28</v>
       </c>
@@ -9234,34 +9352,37 @@
       <c r="BL31" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BM31" s="22" t="s">
+      <c r="BM31" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN31" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="BN31" s="22" t="s">
+      <c r="BO31" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="BO31" s="92" t="s">
+      <c r="BP31" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP31" s="22"/>
-      <c r="BQ31" s="2"/>
-      <c r="BR31" s="14" t="s">
+      <c r="BQ31" s="22"/>
+      <c r="BR31" s="2"/>
+      <c r="BS31" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS31" s="14" t="s">
+      <c r="BT31" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT31" s="18" t="s">
+      <c r="BU31" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU31" s="18" t="s">
+      <c r="BV31" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="BV31" s="21" t="s">
+      <c r="BW31" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:74" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:75" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="124">
         <v>29</v>
       </c>
@@ -9421,32 +9542,35 @@
       <c r="BL32" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BM32" s="15" t="s">
+      <c r="BM32" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN32" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN32" s="22" t="s">
+      <c r="BO32" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="BO32" s="92" t="s">
+      <c r="BP32" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP32" s="22"/>
-      <c r="BQ32" s="2"/>
-      <c r="BR32" s="14" t="s">
+      <c r="BQ32" s="22"/>
+      <c r="BR32" s="2"/>
+      <c r="BS32" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS32" s="14" t="s">
+      <c r="BT32" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT32" s="18" t="s">
+      <c r="BU32" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="BU32" s="18"/>
-      <c r="BV32" s="21" t="s">
+      <c r="BV32" s="18"/>
+      <c r="BW32" s="21" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="124"/>
       <c r="C33" s="47" t="s">
         <v>246</v>
@@ -9514,18 +9638,21 @@
       <c r="BJ33" s="40"/>
       <c r="BK33" s="41"/>
       <c r="BL33" s="42"/>
-      <c r="BM33" s="40"/>
-      <c r="BN33" s="38"/>
+      <c r="BM33" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN33" s="40"/>
       <c r="BO33" s="38"/>
       <c r="BP33" s="38"/>
-      <c r="BQ33" s="3"/>
-      <c r="BR33" s="35"/>
+      <c r="BQ33" s="38"/>
+      <c r="BR33" s="3"/>
       <c r="BS33" s="35"/>
-      <c r="BT33" s="37"/>
+      <c r="BT33" s="35"/>
       <c r="BU33" s="37"/>
-      <c r="BV33" s="43"/>
+      <c r="BV33" s="37"/>
+      <c r="BW33" s="43"/>
     </row>
-    <row r="34" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="124"/>
       <c r="C34" s="47" t="s">
         <v>247</v>
@@ -9593,18 +9720,21 @@
       <c r="BJ34" s="40"/>
       <c r="BK34" s="41"/>
       <c r="BL34" s="42"/>
-      <c r="BM34" s="40"/>
-      <c r="BN34" s="38"/>
+      <c r="BM34" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN34" s="40"/>
       <c r="BO34" s="38"/>
       <c r="BP34" s="38"/>
-      <c r="BQ34" s="3"/>
-      <c r="BR34" s="35"/>
+      <c r="BQ34" s="38"/>
+      <c r="BR34" s="3"/>
       <c r="BS34" s="35"/>
-      <c r="BT34" s="37"/>
+      <c r="BT34" s="35"/>
       <c r="BU34" s="37"/>
-      <c r="BV34" s="43"/>
+      <c r="BV34" s="37"/>
+      <c r="BW34" s="43"/>
     </row>
-    <row r="35" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="124">
         <v>30</v>
       </c>
@@ -9760,34 +9890,37 @@
       <c r="BL35" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BM35" s="38" t="s">
+      <c r="BM35" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN35" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BN35" s="38" t="s">
+      <c r="BO35" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="BO35" s="92" t="s">
+      <c r="BP35" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP35" s="38"/>
-      <c r="BQ35" s="3"/>
-      <c r="BR35" s="35" t="s">
+      <c r="BQ35" s="38"/>
+      <c r="BR35" s="3"/>
+      <c r="BS35" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS35" s="35" t="s">
+      <c r="BT35" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT35" s="37" t="s">
+      <c r="BU35" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="BU35" s="37" t="s">
+      <c r="BV35" s="37" t="s">
         <v>720</v>
       </c>
-      <c r="BV35" s="43" t="s">
+      <c r="BW35" s="43" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="36" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="124">
         <v>31</v>
       </c>
@@ -9942,36 +10075,39 @@
       <c r="BL36" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BM36" s="38" t="s">
+      <c r="BM36" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN36" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BN36" s="38" t="s">
+      <c r="BO36" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="BO36" s="92" t="s">
+      <c r="BP36" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP36" s="38"/>
-      <c r="BQ36" s="3" t="s">
+      <c r="BQ36" s="38"/>
+      <c r="BR36" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="BR36" s="35" t="s">
+      <c r="BS36" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS36" s="35" t="s">
+      <c r="BT36" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT36" s="37" t="s">
+      <c r="BU36" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU36" s="37" t="s">
+      <c r="BV36" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="BV36" s="43" t="s">
+      <c r="BW36" s="43" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="37" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="124">
         <v>32</v>
       </c>
@@ -10114,36 +10250,39 @@
       <c r="BL37" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BM37" s="46" t="s">
+      <c r="BM37" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN37" s="46" t="s">
         <v>245</v>
       </c>
-      <c r="BN37" s="38" t="s">
+      <c r="BO37" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="BO37" s="92" t="s">
+      <c r="BP37" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP37" s="38"/>
-      <c r="BQ37" s="3" t="s">
+      <c r="BQ37" s="38"/>
+      <c r="BR37" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="BR37" s="35" t="s">
+      <c r="BS37" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="BS37" s="35" t="s">
+      <c r="BT37" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT37" s="37" t="s">
+      <c r="BU37" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU37" s="37" t="s">
+      <c r="BV37" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="BV37" s="43" t="s">
+      <c r="BW37" s="43" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="38" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="124">
         <v>33</v>
       </c>
@@ -10303,30 +10442,33 @@
       <c r="BL38" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BM38" s="40" t="s">
+      <c r="BM38" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN38" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BN38" s="40" t="s">
+      <c r="BO38" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="BO38" s="38"/>
       <c r="BP38" s="38"/>
-      <c r="BQ38" s="3"/>
-      <c r="BR38" s="35" t="s">
+      <c r="BQ38" s="38"/>
+      <c r="BR38" s="3"/>
+      <c r="BS38" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="BS38" s="35" t="s">
+      <c r="BT38" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT38" s="37" t="s">
+      <c r="BU38" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="BU38" s="37"/>
-      <c r="BV38" s="43" t="s">
+      <c r="BV38" s="37"/>
+      <c r="BW38" s="43" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="39" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="124">
         <v>34</v>
       </c>
@@ -10486,30 +10628,33 @@
       <c r="BL39" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BM39" s="40" t="s">
+      <c r="BM39" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN39" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BN39" s="40" t="s">
+      <c r="BO39" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="BO39" s="38"/>
       <c r="BP39" s="38"/>
-      <c r="BQ39" s="3"/>
-      <c r="BR39" s="35" t="s">
+      <c r="BQ39" s="38"/>
+      <c r="BR39" s="3"/>
+      <c r="BS39" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="BS39" s="35" t="s">
+      <c r="BT39" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT39" s="37" t="s">
+      <c r="BU39" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="BU39" s="37"/>
-      <c r="BV39" s="43" t="s">
+      <c r="BV39" s="37"/>
+      <c r="BW39" s="43" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="40" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="124">
         <v>35</v>
       </c>
@@ -10669,32 +10814,35 @@
       <c r="BL40" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BM40" s="40" t="s">
+      <c r="BM40" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN40" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BN40" s="40" t="s">
+      <c r="BO40" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="BO40" s="38"/>
       <c r="BP40" s="38"/>
-      <c r="BQ40" s="3"/>
-      <c r="BR40" s="35" t="s">
+      <c r="BQ40" s="38"/>
+      <c r="BR40" s="3"/>
+      <c r="BS40" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="BS40" s="35" t="s">
+      <c r="BT40" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT40" s="37" t="s">
+      <c r="BU40" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="BU40" s="37" t="s">
+      <c r="BV40" s="37" t="s">
         <v>721</v>
       </c>
-      <c r="BV40" s="43" t="s">
+      <c r="BW40" s="43" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="41" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="124">
         <v>36</v>
       </c>
@@ -10857,36 +11005,39 @@
       <c r="BL41" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BM41" s="46" t="s">
+      <c r="BM41" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN41" s="46" t="s">
         <v>245</v>
       </c>
-      <c r="BN41" s="38" t="s">
+      <c r="BO41" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="BO41" s="92" t="s">
+      <c r="BP41" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP41" s="38"/>
-      <c r="BQ41" s="3" t="s">
+      <c r="BQ41" s="38"/>
+      <c r="BR41" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="BR41" s="35" t="s">
+      <c r="BS41" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS41" s="35" t="s">
+      <c r="BT41" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT41" s="37" t="s">
+      <c r="BU41" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU41" s="37" t="s">
+      <c r="BV41" s="37" t="s">
         <v>722</v>
       </c>
-      <c r="BV41" s="43" t="s">
+      <c r="BW41" s="43" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="42" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="124">
         <v>37</v>
       </c>
@@ -11041,34 +11192,37 @@
       <c r="BL42" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BM42" s="58" t="s">
+      <c r="BM42" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN42" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="BN42" s="58" t="s">
+      <c r="BO42" s="58" t="s">
         <v>284</v>
       </c>
-      <c r="BO42" s="92" t="s">
+      <c r="BP42" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP42" s="38"/>
-      <c r="BQ42" s="3"/>
-      <c r="BR42" s="35" t="s">
+      <c r="BQ42" s="38"/>
+      <c r="BR42" s="3"/>
+      <c r="BS42" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS42" s="35" t="s">
+      <c r="BT42" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT42" s="37" t="s">
+      <c r="BU42" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU42" s="141" t="s">
+      <c r="BV42" s="141" t="s">
         <v>723</v>
       </c>
-      <c r="BV42" s="43" t="s">
+      <c r="BW42" s="43" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="43" spans="1:74" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:75" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="124">
         <v>38</v>
       </c>
@@ -11223,32 +11377,35 @@
       <c r="BL43" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BM43" s="40" t="s">
+      <c r="BM43" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN43" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="BN43" s="40" t="s">
+      <c r="BO43" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="BO43" s="38"/>
       <c r="BP43" s="38"/>
-      <c r="BQ43" s="3"/>
-      <c r="BR43" s="35" t="s">
+      <c r="BQ43" s="38"/>
+      <c r="BR43" s="3"/>
+      <c r="BS43" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS43" s="35" t="s">
+      <c r="BT43" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT43" s="37" t="s">
+      <c r="BU43" s="37" t="s">
         <v>353</v>
       </c>
-      <c r="BU43" s="37" t="s">
+      <c r="BV43" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="BV43" s="43" t="s">
+      <c r="BW43" s="43" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="44" spans="1:74" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:75" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="124">
         <v>39</v>
       </c>
@@ -11407,32 +11564,35 @@
       <c r="BL44" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BM44" s="40" t="s">
+      <c r="BM44" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN44" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BN44" s="38" t="s">
+      <c r="BO44" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="BO44" s="38"/>
       <c r="BP44" s="38"/>
-      <c r="BQ44" s="3"/>
-      <c r="BR44" s="35" t="s">
+      <c r="BQ44" s="38"/>
+      <c r="BR44" s="3"/>
+      <c r="BS44" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS44" s="35" t="s">
+      <c r="BT44" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT44" s="37" t="s">
+      <c r="BU44" s="37" t="s">
         <v>357</v>
       </c>
-      <c r="BU44" s="37" t="s">
+      <c r="BV44" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="BV44" s="43" t="s">
+      <c r="BW44" s="43" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="45" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="124">
         <v>40</v>
       </c>
@@ -11587,34 +11747,37 @@
       <c r="BL45" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BM45" s="15" t="s">
+      <c r="BM45" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN45" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="BN45" s="15" t="s">
+      <c r="BO45" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="BO45" s="92" t="s">
+      <c r="BP45" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP45" s="22"/>
-      <c r="BQ45" s="2"/>
-      <c r="BR45" s="14" t="s">
+      <c r="BQ45" s="22"/>
+      <c r="BR45" s="2"/>
+      <c r="BS45" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS45" s="14" t="s">
+      <c r="BT45" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT45" s="18" t="s">
+      <c r="BU45" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU45" s="18" t="s">
+      <c r="BV45" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="BV45" s="21" t="s">
+      <c r="BW45" s="21" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="46" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="124">
         <v>41</v>
       </c>
@@ -11770,34 +11933,37 @@
       <c r="BL46" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BM46" s="54" t="s">
+      <c r="BM46" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN46" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="BN46" s="22" t="s">
+      <c r="BO46" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="BO46" s="92" t="s">
+      <c r="BP46" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP46" s="22"/>
-      <c r="BQ46" s="2"/>
-      <c r="BR46" s="14" t="s">
+      <c r="BQ46" s="22"/>
+      <c r="BR46" s="2"/>
+      <c r="BS46" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS46" s="14" t="s">
+      <c r="BT46" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT46" s="18" t="s">
+      <c r="BU46" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="BU46" s="18" t="s">
+      <c r="BV46" s="18" t="s">
         <v>696</v>
       </c>
-      <c r="BV46" s="21" t="s">
+      <c r="BW46" s="21" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="47" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="124">
         <v>42</v>
       </c>
@@ -11952,34 +12118,37 @@
       <c r="BL47" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BM47" s="15" t="s">
+      <c r="BM47" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN47" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN47" s="22" t="s">
+      <c r="BO47" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="BO47" s="92" t="s">
+      <c r="BP47" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP47" s="22"/>
-      <c r="BQ47" s="2"/>
-      <c r="BR47" s="14" t="s">
+      <c r="BQ47" s="22"/>
+      <c r="BR47" s="2"/>
+      <c r="BS47" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS47" s="14" t="s">
+      <c r="BT47" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT47" s="18" t="s">
+      <c r="BU47" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU47" s="18" t="s">
+      <c r="BV47" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="BV47" s="21" t="s">
+      <c r="BW47" s="21" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="48" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="124">
         <v>43</v>
       </c>
@@ -12134,34 +12303,37 @@
       <c r="BL48" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BM48" s="15" t="s">
+      <c r="BM48" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN48" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="BN48" s="15" t="s">
+      <c r="BO48" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="BO48" s="92" t="s">
+      <c r="BP48" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP48" s="22"/>
-      <c r="BQ48" s="2"/>
-      <c r="BR48" s="14" t="s">
+      <c r="BQ48" s="22"/>
+      <c r="BR48" s="2"/>
+      <c r="BS48" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="BS48" s="14" t="s">
+      <c r="BT48" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT48" s="18" t="s">
+      <c r="BU48" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU48" s="18" t="s">
+      <c r="BV48" s="18" t="s">
         <v>724</v>
       </c>
-      <c r="BV48" s="21" t="s">
+      <c r="BW48" s="21" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="49" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="124">
         <v>44</v>
       </c>
@@ -12329,30 +12501,33 @@
       <c r="BL49" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BM49" s="15" t="s">
+      <c r="BM49" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN49" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BN49" s="15" t="s">
+      <c r="BO49" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="BO49" s="22"/>
       <c r="BP49" s="22"/>
-      <c r="BQ49" s="2"/>
-      <c r="BR49" s="14" t="s">
+      <c r="BQ49" s="22"/>
+      <c r="BR49" s="2"/>
+      <c r="BS49" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="BS49" s="14" t="s">
+      <c r="BT49" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT49" s="18" t="s">
+      <c r="BU49" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="BU49" s="18"/>
-      <c r="BV49" s="21" t="s">
+      <c r="BV49" s="18"/>
+      <c r="BW49" s="21" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="50" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="124">
         <v>45</v>
       </c>
@@ -12507,34 +12682,37 @@
       <c r="BL50" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BM50" s="15" t="s">
+      <c r="BM50" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN50" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN50" s="22" t="s">
+      <c r="BO50" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="BO50" s="92" t="s">
+      <c r="BP50" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP50" s="22"/>
-      <c r="BQ50" s="2"/>
-      <c r="BR50" s="14" t="s">
+      <c r="BQ50" s="22"/>
+      <c r="BR50" s="2"/>
+      <c r="BS50" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS50" s="14" t="s">
+      <c r="BT50" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT50" s="18" t="s">
+      <c r="BU50" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="BU50" s="18" t="s">
+      <c r="BV50" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="BV50" s="21" t="s">
+      <c r="BW50" s="21" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="51" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="124">
         <v>46</v>
       </c>
@@ -12689,34 +12867,37 @@
       <c r="BL51" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BM51" s="15" t="s">
+      <c r="BM51" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN51" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="BN51" s="15" t="s">
+      <c r="BO51" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="BO51" s="92" t="s">
+      <c r="BP51" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP51" s="22"/>
-      <c r="BQ51" s="2"/>
-      <c r="BR51" s="14" t="s">
+      <c r="BQ51" s="22"/>
+      <c r="BR51" s="2"/>
+      <c r="BS51" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="BS51" s="14" t="s">
+      <c r="BT51" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT51" s="18" t="s">
+      <c r="BU51" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="BU51" s="18" t="s">
+      <c r="BV51" s="18" t="s">
         <v>724</v>
       </c>
-      <c r="BV51" s="21" t="s">
+      <c r="BW51" s="21" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="52" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="124">
         <v>47</v>
       </c>
@@ -12884,30 +13065,33 @@
       <c r="BL52" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BM52" s="15" t="s">
+      <c r="BM52" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN52" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BN52" s="15" t="s">
+      <c r="BO52" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="BO52" s="22"/>
       <c r="BP52" s="22"/>
-      <c r="BQ52" s="2"/>
-      <c r="BR52" s="14" t="s">
+      <c r="BQ52" s="22"/>
+      <c r="BR52" s="2"/>
+      <c r="BS52" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="BS52" s="14" t="s">
+      <c r="BT52" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT52" s="18" t="s">
+      <c r="BU52" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="BU52" s="18"/>
-      <c r="BV52" s="21" t="s">
+      <c r="BV52" s="18"/>
+      <c r="BW52" s="21" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="53" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="124">
         <v>48</v>
       </c>
@@ -13074,32 +13258,35 @@
       <c r="BL53" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BM53" s="15" t="s">
+      <c r="BM53" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN53" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BN53" s="15" t="s">
+      <c r="BO53" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="BO53" s="22"/>
       <c r="BP53" s="22"/>
-      <c r="BQ53" s="2"/>
-      <c r="BR53" s="14" t="s">
+      <c r="BQ53" s="22"/>
+      <c r="BR53" s="2"/>
+      <c r="BS53" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="BS53" s="14" t="s">
+      <c r="BT53" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT53" s="18" t="s">
+      <c r="BU53" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="BU53" s="18" t="s">
+      <c r="BV53" s="18" t="s">
         <v>733</v>
       </c>
-      <c r="BV53" s="21" t="s">
+      <c r="BW53" s="21" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="54" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="124">
         <v>49</v>
       </c>
@@ -13254,36 +13441,39 @@
       <c r="BL54" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BM54" s="15" t="s">
+      <c r="BM54" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN54" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN54" s="22" t="s">
+      <c r="BO54" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="BO54" s="92" t="s">
+      <c r="BP54" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP54" s="22"/>
-      <c r="BQ54" s="2" t="s">
+      <c r="BQ54" s="22"/>
+      <c r="BR54" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="BR54" s="14" t="s">
+      <c r="BS54" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS54" s="14" t="s">
+      <c r="BT54" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT54" s="18" t="s">
+      <c r="BU54" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU54" s="18" t="s">
+      <c r="BV54" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="BV54" s="21" t="s">
+      <c r="BW54" s="21" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="55" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="124">
         <v>50</v>
       </c>
@@ -13438,36 +13628,39 @@
       <c r="BL55" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BM55" s="15" t="s">
+      <c r="BM55" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN55" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="BN55" s="15" t="s">
+      <c r="BO55" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="BO55" s="92" t="s">
+      <c r="BP55" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP55" s="22"/>
-      <c r="BQ55" s="2" t="s">
+      <c r="BQ55" s="22"/>
+      <c r="BR55" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="BR55" s="14" t="s">
+      <c r="BS55" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="BS55" s="14" t="s">
+      <c r="BT55" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT55" s="18" t="s">
+      <c r="BU55" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU55" s="18" t="s">
+      <c r="BV55" s="18" t="s">
         <v>724</v>
       </c>
-      <c r="BV55" s="21" t="s">
+      <c r="BW55" s="21" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="56" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="124">
         <v>51</v>
       </c>
@@ -13639,32 +13832,35 @@
       <c r="BL56" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BM56" s="15" t="s">
+      <c r="BM56" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN56" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BN56" s="15" t="s">
+      <c r="BO56" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="BO56" s="22"/>
       <c r="BP56" s="22"/>
-      <c r="BQ56" s="2"/>
-      <c r="BR56" s="14" t="s">
+      <c r="BQ56" s="22"/>
+      <c r="BR56" s="2"/>
+      <c r="BS56" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="BS56" s="14" t="s">
+      <c r="BT56" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT56" s="18" t="s">
+      <c r="BU56" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="BU56" s="18" t="s">
+      <c r="BV56" s="18" t="s">
         <v>708</v>
       </c>
-      <c r="BV56" s="21" t="s">
+      <c r="BW56" s="21" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="57" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="124">
         <v>52</v>
       </c>
@@ -13820,34 +14016,37 @@
       <c r="BL57" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BM57" s="22" t="s">
+      <c r="BM57" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN57" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="BN57" s="22" t="s">
+      <c r="BO57" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="BO57" s="92" t="s">
+      <c r="BP57" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP57" s="22"/>
-      <c r="BQ57" s="2"/>
-      <c r="BR57" s="14" t="s">
+      <c r="BQ57" s="22"/>
+      <c r="BR57" s="2"/>
+      <c r="BS57" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS57" s="14" t="s">
+      <c r="BT57" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT57" s="18" t="s">
+      <c r="BU57" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU57" s="18" t="s">
+      <c r="BV57" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="BV57" s="21" t="s">
+      <c r="BW57" s="21" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="58" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="124">
         <v>53</v>
       </c>
@@ -14002,34 +14201,37 @@
       <c r="BL58" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BM58" s="15" t="s">
+      <c r="BM58" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN58" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN58" s="22" t="s">
+      <c r="BO58" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="BO58" s="92" t="s">
+      <c r="BP58" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP58" s="22"/>
-      <c r="BQ58" s="2"/>
-      <c r="BR58" s="14" t="s">
+      <c r="BQ58" s="22"/>
+      <c r="BR58" s="2"/>
+      <c r="BS58" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS58" s="14" t="s">
+      <c r="BT58" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT58" s="18" t="s">
+      <c r="BU58" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="BU58" s="18" t="s">
+      <c r="BV58" s="18" t="s">
         <v>725</v>
       </c>
-      <c r="BV58" s="21" t="s">
+      <c r="BW58" s="21" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="59" spans="1:74" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:75" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="124">
         <v>54</v>
       </c>
@@ -14196,34 +14398,37 @@
       <c r="BL59" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BM59" s="15" t="s">
+      <c r="BM59" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN59" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="BN59" s="22" t="s">
+      <c r="BO59" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="BO59" s="92" t="s">
+      <c r="BP59" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP59" s="22"/>
-      <c r="BQ59" s="2"/>
-      <c r="BR59" s="14" t="s">
+      <c r="BQ59" s="22"/>
+      <c r="BR59" s="2"/>
+      <c r="BS59" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="BS59" s="14" t="s">
+      <c r="BT59" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="BT59" s="18" t="s">
+      <c r="BU59" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="BU59" s="18" t="s">
+      <c r="BV59" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="BV59" s="21" t="s">
+      <c r="BW59" s="21" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="60" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="124">
         <v>55</v>
       </c>
@@ -14378,34 +14583,37 @@
       <c r="BL60" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="BM60" s="40" t="s">
+      <c r="BM60" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN60" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BN60" s="38" t="s">
+      <c r="BO60" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="BO60" s="131">
+      <c r="BP60" s="131">
         <v>200206</v>
       </c>
-      <c r="BP60" s="95"/>
-      <c r="BQ60" s="3"/>
-      <c r="BR60" s="35" t="s">
+      <c r="BQ60" s="95"/>
+      <c r="BR60" s="3"/>
+      <c r="BS60" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS60" s="35" t="s">
+      <c r="BT60" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="BT60" s="37" t="s">
+      <c r="BU60" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU60" s="37" t="s">
+      <c r="BV60" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="BV60" s="43" t="s">
+      <c r="BW60" s="43" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="61" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="124">
         <v>56</v>
       </c>
@@ -14560,34 +14768,37 @@
       <c r="BL61" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="BM61" s="40" t="s">
+      <c r="BM61" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN61" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="BN61" s="38" t="s">
+      <c r="BO61" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="BO61" s="95" t="s">
+      <c r="BP61" s="95" t="s">
         <v>500</v>
       </c>
-      <c r="BP61" s="95"/>
       <c r="BQ61" s="95"/>
-      <c r="BR61" s="35" t="s">
+      <c r="BR61" s="95"/>
+      <c r="BS61" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="BS61" s="3" t="s">
+      <c r="BT61" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="BT61" s="37" t="s">
+      <c r="BU61" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU61" s="37" t="s">
+      <c r="BV61" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="BV61" s="43" t="s">
+      <c r="BW61" s="43" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="62" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="124">
         <v>57</v>
       </c>
@@ -14754,32 +14965,35 @@
       <c r="BL62" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="BM62" s="40" t="s">
+      <c r="BM62" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN62" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="BN62" s="3" t="s">
+      <c r="BO62" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="BO62" s="38"/>
       <c r="BP62" s="38"/>
-      <c r="BQ62" s="3"/>
-      <c r="BR62" s="35" t="s">
+      <c r="BQ62" s="38"/>
+      <c r="BR62" s="3"/>
+      <c r="BS62" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="BS62" s="35" t="s">
+      <c r="BT62" s="35" t="s">
         <v>444</v>
       </c>
-      <c r="BT62" s="37" t="s">
+      <c r="BU62" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="BU62" s="37" t="s">
+      <c r="BV62" s="37" t="s">
         <v>726</v>
       </c>
-      <c r="BV62" s="43" t="s">
+      <c r="BW62" s="43" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="63" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="124">
         <v>58</v>
       </c>
@@ -14942,32 +15156,35 @@
       <c r="BL63" s="42" t="s">
         <v>815</v>
       </c>
-      <c r="BM63" s="96" t="s">
+      <c r="BM63" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN63" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="BN63" s="3" t="s">
+      <c r="BO63" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="BO63" s="131">
+      <c r="BP63" s="131">
         <v>200206</v>
       </c>
-      <c r="BP63" s="95"/>
       <c r="BQ63" s="95"/>
-      <c r="BR63" s="3" t="s">
+      <c r="BR63" s="95"/>
+      <c r="BS63" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BS63" s="3" t="s">
+      <c r="BT63" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="BT63" s="37" t="s">
+      <c r="BU63" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU63" s="37"/>
-      <c r="BV63" s="43" t="s">
+      <c r="BV63" s="37"/>
+      <c r="BW63" s="43" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="64" spans="1:74" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:75" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="124">
         <v>59</v>
       </c>
@@ -15122,34 +15339,37 @@
       <c r="BL64" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="BM64" s="96">
+      <c r="BM64" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN64" s="96">
         <v>162640</v>
       </c>
-      <c r="BN64" s="3" t="s">
+      <c r="BO64" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="BO64" s="132">
+      <c r="BP64" s="132">
         <v>201189</v>
       </c>
-      <c r="BP64" s="3"/>
-      <c r="BQ64" s="95"/>
-      <c r="BR64" s="3" t="s">
+      <c r="BQ64" s="3"/>
+      <c r="BR64" s="95"/>
+      <c r="BS64" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="BS64" s="3" t="s">
+      <c r="BT64" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="BT64" s="37" t="s">
+      <c r="BU64" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="BU64" s="37" t="s">
+      <c r="BV64" s="37" t="s">
         <v>727</v>
       </c>
-      <c r="BV64" s="43" t="s">
+      <c r="BW64" s="43" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="65" spans="1:105" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="124">
         <v>60</v>
       </c>
@@ -15313,34 +15533,37 @@
       <c r="BL65" s="49" t="s">
         <v>815</v>
       </c>
-      <c r="BM65" s="49">
+      <c r="BM65" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN65" s="49">
         <v>201383</v>
       </c>
-      <c r="BN65" s="2" t="s">
+      <c r="BO65" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="BO65" s="131">
+      <c r="BP65" s="131">
         <v>200206</v>
       </c>
-      <c r="BP65" s="97"/>
-      <c r="BQ65" s="97" t="s">
+      <c r="BQ65" s="97"/>
+      <c r="BR65" s="97" t="s">
         <v>496</v>
       </c>
-      <c r="BR65" s="2" t="s">
+      <c r="BS65" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BS65" s="2" t="s">
+      <c r="BT65" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="BT65" s="18" t="s">
+      <c r="BU65" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU65" s="18"/>
-      <c r="BV65" s="21" t="s">
+      <c r="BV65" s="18"/>
+      <c r="BW65" s="21" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="66" spans="1:105" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="124">
         <v>61</v>
       </c>
@@ -15496,36 +15719,39 @@
       <c r="BL66" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BM66" s="49">
+      <c r="BM66" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN66" s="49">
         <v>162640</v>
       </c>
-      <c r="BN66" s="2" t="s">
+      <c r="BO66" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="BO66" s="92" t="s">
+      <c r="BP66" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP66" s="22"/>
-      <c r="BQ66" s="97" t="s">
+      <c r="BQ66" s="22"/>
+      <c r="BR66" s="97" t="s">
         <v>471</v>
       </c>
-      <c r="BR66" s="2" t="s">
+      <c r="BS66" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BS66" s="2" t="s">
+      <c r="BT66" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT66" s="18" t="s">
+      <c r="BU66" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU66" s="18" t="s">
+      <c r="BV66" s="18" t="s">
         <v>728</v>
       </c>
-      <c r="BV66" s="21" t="s">
+      <c r="BW66" s="21" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="67" spans="1:105" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="124">
         <v>62</v>
       </c>
@@ -15684,33 +15910,36 @@
         <v>170</v>
       </c>
       <c r="BM67" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN67" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="BN67" s="2" t="s">
+      <c r="BO67" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="BO67" s="97" t="s">
+      <c r="BP67" s="97" t="s">
         <v>506</v>
       </c>
-      <c r="BP67" s="97"/>
       <c r="BQ67" s="97"/>
-      <c r="BR67" s="2" t="s">
+      <c r="BR67" s="97"/>
+      <c r="BS67" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BS67" s="2" t="s">
+      <c r="BT67" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT67" s="18" t="s">
+      <c r="BU67" s="18" t="s">
         <v>501</v>
       </c>
-      <c r="BU67" s="18" t="s">
+      <c r="BV67" s="18" t="s">
         <v>729</v>
       </c>
-      <c r="BV67" s="21" t="s">
+      <c r="BW67" s="21" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="68" spans="1:105" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="124">
         <v>63</v>
       </c>
@@ -15880,32 +16109,35 @@
       <c r="BL68" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM68" s="49">
+      <c r="BM68" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN68" s="49">
         <v>162642</v>
       </c>
-      <c r="BN68" s="2" t="s">
+      <c r="BO68" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="BO68" s="97"/>
       <c r="BP68" s="97"/>
       <c r="BQ68" s="97"/>
-      <c r="BR68" s="2" t="s">
+      <c r="BR68" s="97"/>
+      <c r="BS68" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="BS68" s="2" t="s">
+      <c r="BT68" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT68" s="18" t="s">
+      <c r="BU68" s="18" t="s">
         <v>511</v>
       </c>
-      <c r="BU68" s="18" t="s">
+      <c r="BV68" s="18" t="s">
         <v>730</v>
       </c>
-      <c r="BV68" s="21" t="s">
+      <c r="BW68" s="21" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="69" spans="1:105" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="124">
         <v>64</v>
       </c>
@@ -16061,34 +16293,37 @@
       <c r="BL69" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM69" s="15" t="s">
+      <c r="BM69" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN69" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="BN69" s="15" t="s">
+      <c r="BO69" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="BO69" s="92" t="s">
+      <c r="BP69" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP69" s="22"/>
-      <c r="BQ69" s="97" t="s">
+      <c r="BQ69" s="22"/>
+      <c r="BR69" s="97" t="s">
         <v>520</v>
       </c>
-      <c r="BR69" s="2" t="s">
+      <c r="BS69" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BS69" s="2" t="s">
+      <c r="BT69" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT69" s="18" t="s">
+      <c r="BU69" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU69" s="18"/>
-      <c r="BV69" s="21" t="s">
+      <c r="BV69" s="18"/>
+      <c r="BW69" s="21" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="70" spans="1:105" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:106" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="124">
         <v>65</v>
       </c>
@@ -16254,32 +16489,35 @@
       <c r="BL70" s="49" t="s">
         <v>815</v>
       </c>
-      <c r="BM70" s="22" t="s">
+      <c r="BM70" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN70" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="BN70" s="22" t="s">
+      <c r="BO70" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="BO70" s="92" t="s">
+      <c r="BP70" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP70" s="22"/>
-      <c r="BQ70" s="2"/>
-      <c r="BR70" s="2" t="s">
+      <c r="BQ70" s="22"/>
+      <c r="BR70" s="2"/>
+      <c r="BS70" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BS70" s="2" t="s">
+      <c r="BT70" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT70" s="18" t="s">
+      <c r="BU70" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU70" s="18"/>
-      <c r="BV70" s="21" t="s">
+      <c r="BV70" s="18"/>
+      <c r="BW70" s="21" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="71" spans="1:105" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:106" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="124">
         <v>66</v>
       </c>
@@ -16445,31 +16683,33 @@
       <c r="BL71" s="49" t="s">
         <v>815</v>
       </c>
-      <c r="BM71" s="22" t="s">
+      <c r="BM71" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN71" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="BN71" s="22" t="s">
+      <c r="BO71" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="BO71" s="92" t="s">
+      <c r="BP71" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP71" s="22"/>
-      <c r="BQ71" s="2"/>
-      <c r="BR71" s="2" t="s">
+      <c r="BQ71" s="22"/>
+      <c r="BR71" s="2"/>
+      <c r="BS71" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BS71" s="2" t="s">
+      <c r="BT71" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT71" s="18" t="s">
+      <c r="BU71" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU71" s="18"/>
-      <c r="BV71" s="21" t="s">
+      <c r="BV71" s="18"/>
+      <c r="BW71" s="21" t="s">
         <v>685</v>
       </c>
-      <c r="BW71" s="88"/>
       <c r="BX71" s="88"/>
       <c r="BY71" s="88"/>
       <c r="BZ71" s="88"/>
@@ -16500,8 +16740,9 @@
       <c r="CY71" s="88"/>
       <c r="CZ71" s="88"/>
       <c r="DA71" s="88"/>
+      <c r="DB71" s="88"/>
     </row>
-    <row r="72" spans="1:105" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:106" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="124">
         <v>67</v>
       </c>
@@ -16659,32 +16900,34 @@
         <v>170</v>
       </c>
       <c r="BM72" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN72" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="BN72" s="2" t="s">
+      <c r="BO72" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="BO72" s="92" t="s">
+      <c r="BP72" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP72" s="22"/>
-      <c r="BQ72" s="2"/>
-      <c r="BR72" s="2" t="s">
+      <c r="BQ72" s="22"/>
+      <c r="BR72" s="2"/>
+      <c r="BS72" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="BS72" s="2" t="s">
+      <c r="BT72" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT72" s="18" t="s">
+      <c r="BU72" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU72" s="18" t="s">
+      <c r="BV72" s="18" t="s">
         <v>731</v>
       </c>
-      <c r="BV72" s="21" t="s">
+      <c r="BW72" s="21" t="s">
         <v>670</v>
       </c>
-      <c r="BW72" s="88"/>
       <c r="BX72" s="88"/>
       <c r="BY72" s="88"/>
       <c r="BZ72" s="88"/>
@@ -16715,8 +16958,9 @@
       <c r="CY72" s="88"/>
       <c r="CZ72" s="88"/>
       <c r="DA72" s="88"/>
+      <c r="DB72" s="88"/>
     </row>
-    <row r="73" spans="1:105" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:106" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="124">
         <v>68</v>
       </c>
@@ -16874,34 +17118,37 @@
       <c r="BL73" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BM73" s="38" t="s">
+      <c r="BM73" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN73" s="38" t="s">
         <v>513</v>
       </c>
-      <c r="BN73" s="38" t="s">
+      <c r="BO73" s="38" t="s">
         <v>514</v>
       </c>
-      <c r="BO73" s="92" t="s">
+      <c r="BP73" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP73" s="38"/>
-      <c r="BQ73" s="3" t="s">
+      <c r="BQ73" s="38"/>
+      <c r="BR73" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="BR73" s="3" t="s">
+      <c r="BS73" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="BS73" s="3" t="s">
+      <c r="BT73" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BT73" s="37" t="s">
+      <c r="BU73" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU73" s="37"/>
-      <c r="BV73" s="43" t="s">
+      <c r="BV73" s="37"/>
+      <c r="BW73" s="43" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="74" spans="1:105" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:106" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="124">
         <v>69</v>
       </c>
@@ -17059,32 +17306,35 @@
       <c r="BL74" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BM74" s="38" t="s">
+      <c r="BM74" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN74" s="38" t="s">
         <v>513</v>
       </c>
-      <c r="BN74" s="38" t="s">
+      <c r="BO74" s="38" t="s">
         <v>514</v>
       </c>
-      <c r="BO74" s="92" t="s">
+      <c r="BP74" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP74" s="38"/>
-      <c r="BQ74" s="3"/>
-      <c r="BR74" s="3" t="s">
+      <c r="BQ74" s="38"/>
+      <c r="BR74" s="3"/>
+      <c r="BS74" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="BS74" s="3" t="s">
+      <c r="BT74" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BT74" s="37" t="s">
+      <c r="BU74" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU74" s="37"/>
-      <c r="BV74" s="43" t="s">
+      <c r="BV74" s="37"/>
+      <c r="BW74" s="43" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="75" spans="1:105" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:106" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="124">
         <v>70</v>
       </c>
@@ -17250,30 +17500,33 @@
       <c r="BL75" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BM75" s="38" t="s">
+      <c r="BM75" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN75" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="BN75" s="38" t="s">
+      <c r="BO75" s="38" t="s">
         <v>586</v>
       </c>
-      <c r="BO75" s="38"/>
       <c r="BP75" s="38"/>
-      <c r="BQ75" s="3"/>
-      <c r="BR75" s="3" t="s">
+      <c r="BQ75" s="38"/>
+      <c r="BR75" s="3"/>
+      <c r="BS75" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="BS75" s="3" t="s">
+      <c r="BT75" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BT75" s="37" t="s">
+      <c r="BU75" s="37" t="s">
         <v>681</v>
       </c>
-      <c r="BU75" s="37"/>
-      <c r="BV75" s="43" t="s">
+      <c r="BV75" s="37"/>
+      <c r="BW75" s="43" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="76" spans="1:105" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:106" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="124">
         <v>71</v>
       </c>
@@ -17431,30 +17684,33 @@
       <c r="BL76" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BM76" s="38" t="s">
+      <c r="BM76" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN76" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="BN76" s="38" t="s">
+      <c r="BO76" s="38" t="s">
         <v>587</v>
       </c>
-      <c r="BO76" s="92" t="s">
+      <c r="BP76" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP76" s="38"/>
-      <c r="BQ76" s="3"/>
-      <c r="BR76" s="3" t="s">
+      <c r="BQ76" s="38"/>
+      <c r="BR76" s="3"/>
+      <c r="BS76" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="BS76" s="3" t="s">
+      <c r="BT76" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BT76" s="37" t="s">
+      <c r="BU76" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU76" s="37"/>
-      <c r="BV76" s="43"/>
+      <c r="BV76" s="37"/>
+      <c r="BW76" s="43"/>
     </row>
-    <row r="77" spans="1:105" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:106" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="124">
         <v>72</v>
       </c>
@@ -17612,36 +17868,39 @@
       <c r="BL77" s="96" t="s">
         <v>815</v>
       </c>
-      <c r="BM77" s="38" t="s">
+      <c r="BM77" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN77" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="BN77" s="38" t="s">
+      <c r="BO77" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="BO77" s="92" t="s">
+      <c r="BP77" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP77" s="3">
+      <c r="BQ77" s="3">
         <v>1540746</v>
       </c>
-      <c r="BQ77" s="3"/>
-      <c r="BR77" s="3" t="s">
+      <c r="BR77" s="3"/>
+      <c r="BS77" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="BS77" s="3" t="s">
+      <c r="BT77" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BT77" s="37" t="s">
+      <c r="BU77" s="37" t="s">
         <v>697</v>
       </c>
-      <c r="BU77" s="37" t="s">
+      <c r="BV77" s="37" t="s">
         <v>732</v>
       </c>
-      <c r="BV77" s="43" t="s">
+      <c r="BW77" s="43" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="78" spans="1:105" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:106" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="124">
         <v>73</v>
       </c>
@@ -17799,36 +18058,39 @@
       <c r="BL78" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BM78" s="38" t="s">
+      <c r="BM78" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN78" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="BN78" s="38" t="s">
+      <c r="BO78" s="38" t="s">
         <v>587</v>
       </c>
-      <c r="BO78" s="92" t="s">
+      <c r="BP78" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP78" s="3">
+      <c r="BQ78" s="3">
         <v>1272212</v>
       </c>
-      <c r="BQ78" s="3" t="s">
+      <c r="BR78" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="BR78" s="3" t="s">
+      <c r="BS78" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="BS78" s="3" t="s">
+      <c r="BT78" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BT78" s="37" t="s">
+      <c r="BU78" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU78" s="37"/>
-      <c r="BV78" s="43" t="s">
+      <c r="BV78" s="37"/>
+      <c r="BW78" s="43" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="79" spans="1:105" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:106" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="124">
         <v>74</v>
       </c>
@@ -17986,36 +18248,39 @@
       <c r="BL79" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BM79" s="38" t="s">
+      <c r="BM79" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN79" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="BN79" s="38" t="s">
+      <c r="BO79" s="38" t="s">
         <v>586</v>
       </c>
-      <c r="BO79" s="92" t="s">
+      <c r="BP79" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP79" s="38" t="s">
+      <c r="BQ79" s="38" t="s">
         <v>700</v>
       </c>
-      <c r="BQ79" s="3" t="s">
+      <c r="BR79" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="BR79" s="3" t="s">
+      <c r="BS79" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="BS79" s="3" t="s">
+      <c r="BT79" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BT79" s="37" t="s">
+      <c r="BU79" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU79" s="37"/>
-      <c r="BV79" s="43" t="s">
+      <c r="BV79" s="37"/>
+      <c r="BW79" s="43" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="80" spans="1:105" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:106" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A80" s="124">
         <v>75</v>
       </c>
@@ -18173,38 +18438,41 @@
       <c r="BL80" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BM80" s="38" t="s">
+      <c r="BM80" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN80" s="38" t="s">
         <v>513</v>
       </c>
-      <c r="BN80" s="38" t="s">
+      <c r="BO80" s="38" t="s">
         <v>514</v>
       </c>
-      <c r="BO80" s="92" t="s">
+      <c r="BP80" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP80" s="38" t="s">
+      <c r="BQ80" s="38" t="s">
         <v>700</v>
       </c>
-      <c r="BQ80" s="3" t="s">
+      <c r="BR80" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="BR80" s="3" t="s">
+      <c r="BS80" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="BS80" s="3" t="s">
+      <c r="BT80" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BT80" s="37" t="s">
+      <c r="BU80" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="BU80" s="37" t="s">
+      <c r="BV80" s="37" t="s">
         <v>749</v>
       </c>
-      <c r="BV80" s="43" t="s">
+      <c r="BW80" s="43" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="81" spans="1:74" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:75" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A81" s="124">
         <v>76</v>
       </c>
@@ -18372,36 +18640,39 @@
       <c r="BL81" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BM81" s="38" t="s">
+      <c r="BM81" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN81" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="BN81" s="38" t="s">
+      <c r="BO81" s="38" t="s">
         <v>586</v>
       </c>
-      <c r="BO81" s="149" t="s">
+      <c r="BP81" s="149" t="s">
         <v>741</v>
       </c>
-      <c r="BP81" s="3">
+      <c r="BQ81" s="3">
         <v>1540746</v>
       </c>
-      <c r="BQ81" s="3"/>
-      <c r="BR81" s="3" t="s">
+      <c r="BR81" s="3"/>
+      <c r="BS81" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="BS81" s="3" t="s">
+      <c r="BT81" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="BT81" s="37" t="s">
+      <c r="BU81" s="37" t="s">
         <v>756</v>
       </c>
-      <c r="BU81" s="37" t="s">
+      <c r="BV81" s="37" t="s">
         <v>765</v>
       </c>
-      <c r="BV81" s="43" t="s">
+      <c r="BW81" s="43" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="82" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="124">
         <v>77</v>
       </c>
@@ -18559,38 +18830,41 @@
       <c r="BL82" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM82" s="22" t="s">
+      <c r="BM82" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN82" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="BN82" s="22" t="s">
+      <c r="BO82" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="BO82" s="92" t="s">
+      <c r="BP82" s="92" t="s">
         <v>766</v>
       </c>
-      <c r="BP82" s="2">
+      <c r="BQ82" s="2">
         <v>1272212</v>
       </c>
-      <c r="BQ82" s="159" t="s">
+      <c r="BR82" s="159" t="s">
         <v>755</v>
       </c>
-      <c r="BR82" s="2" t="s">
+      <c r="BS82" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS82" s="2" t="s">
+      <c r="BT82" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT82" s="18" t="s">
+      <c r="BU82" s="18" t="s">
         <v>768</v>
       </c>
-      <c r="BU82" s="18" t="s">
+      <c r="BV82" s="18" t="s">
         <v>764</v>
       </c>
-      <c r="BV82" s="21" t="s">
+      <c r="BW82" s="21" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="83" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="124">
         <v>78</v>
       </c>
@@ -18748,34 +19022,37 @@
       <c r="BL83" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM83" s="22" t="s">
+      <c r="BM83" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN83" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="BN83" s="22" t="s">
+      <c r="BO83" s="22" t="s">
         <v>586</v>
       </c>
-      <c r="BO83" s="92" t="s">
+      <c r="BP83" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP83" s="22" t="s">
+      <c r="BQ83" s="22" t="s">
         <v>700</v>
       </c>
-      <c r="BQ83" s="2"/>
-      <c r="BR83" s="2" t="s">
+      <c r="BR83" s="2"/>
+      <c r="BS83" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS83" s="2" t="s">
+      <c r="BT83" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT83" s="18" t="s">
+      <c r="BU83" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU83" s="18"/>
-      <c r="BV83" s="21" t="s">
+      <c r="BV83" s="18"/>
+      <c r="BW83" s="21" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="84" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="124">
         <v>79</v>
       </c>
@@ -18933,36 +19210,39 @@
       <c r="BL84" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM84" s="22" t="s">
+      <c r="BM84" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN84" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="BN84" s="22" t="s">
+      <c r="BO84" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="BO84" s="92" t="s">
+      <c r="BP84" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP84" s="2">
+      <c r="BQ84" s="2">
         <v>1272212</v>
       </c>
-      <c r="BQ84" s="2"/>
-      <c r="BR84" s="2" t="s">
+      <c r="BR84" s="2"/>
+      <c r="BS84" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS84" s="2" t="s">
+      <c r="BT84" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT84" s="18" t="s">
+      <c r="BU84" s="18" t="s">
         <v>787</v>
       </c>
-      <c r="BU84" s="18" t="s">
+      <c r="BV84" s="18" t="s">
         <v>789</v>
       </c>
-      <c r="BV84" s="21" t="s">
+      <c r="BW84" s="21" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="85" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="124">
         <v>79</v>
       </c>
@@ -19120,36 +19400,39 @@
       <c r="BL85" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM85" s="22" t="s">
+      <c r="BM85" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN85" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="BN85" s="22" t="s">
+      <c r="BO85" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="BO85" s="92" t="s">
+      <c r="BP85" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP85" s="2">
+      <c r="BQ85" s="2">
         <v>1272212</v>
       </c>
-      <c r="BQ85" s="2"/>
-      <c r="BR85" s="2" t="s">
+      <c r="BR85" s="2"/>
+      <c r="BS85" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS85" s="2" t="s">
+      <c r="BT85" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT85" s="18" t="s">
+      <c r="BU85" s="18" t="s">
         <v>796</v>
       </c>
-      <c r="BU85" s="18" t="s">
+      <c r="BV85" s="18" t="s">
         <v>790</v>
       </c>
-      <c r="BV85" s="21" t="s">
+      <c r="BW85" s="21" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="86" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="124">
         <v>80</v>
       </c>
@@ -19307,34 +19590,37 @@
       <c r="BL86" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM86" s="22" t="s">
+      <c r="BM86" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN86" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="BN86" s="22" t="s">
+      <c r="BO86" s="22" t="s">
         <v>586</v>
       </c>
-      <c r="BO86" s="92" t="s">
+      <c r="BP86" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP86" s="22" t="s">
+      <c r="BQ86" s="22" t="s">
         <v>700</v>
       </c>
-      <c r="BQ86" s="2"/>
-      <c r="BR86" s="2" t="s">
+      <c r="BR86" s="2"/>
+      <c r="BS86" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS86" s="2" t="s">
+      <c r="BT86" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT86" s="18" t="s">
+      <c r="BU86" s="18" t="s">
         <v>787</v>
       </c>
-      <c r="BU86" s="18"/>
-      <c r="BV86" s="21" t="s">
+      <c r="BV86" s="18"/>
+      <c r="BW86" s="21" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="87" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="124">
         <v>81</v>
       </c>
@@ -19492,34 +19778,37 @@
       <c r="BL87" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM87" s="22" t="s">
+      <c r="BM87" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN87" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="BN87" s="22" t="s">
+      <c r="BO87" s="22" t="s">
         <v>747</v>
       </c>
-      <c r="BO87" s="92" t="s">
+      <c r="BP87" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP87" s="159">
+      <c r="BQ87" s="159">
         <v>1272212</v>
       </c>
-      <c r="BQ87" s="2"/>
-      <c r="BR87" s="2" t="s">
+      <c r="BR87" s="2"/>
+      <c r="BS87" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS87" s="2" t="s">
+      <c r="BT87" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT87" s="18" t="s">
+      <c r="BU87" s="18" t="s">
         <v>796</v>
       </c>
-      <c r="BU87" s="18"/>
-      <c r="BV87" s="21" t="s">
+      <c r="BV87" s="18"/>
+      <c r="BW87" s="21" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="88" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" s="124">
         <v>82</v>
       </c>
@@ -19677,36 +19966,39 @@
       <c r="BL88" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM88" s="22" t="s">
+      <c r="BM88" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN88" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="BN88" s="22" t="s">
+      <c r="BO88" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="BO88" s="92" t="s">
+      <c r="BP88" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="BP88" s="22" t="s">
+      <c r="BQ88" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="BQ88" s="2" t="s">
+      <c r="BR88" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="BR88" s="2" t="s">
+      <c r="BS88" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS88" s="2" t="s">
+      <c r="BT88" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT88" s="18" t="s">
+      <c r="BU88" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU88" s="18"/>
-      <c r="BV88" s="21" t="s">
+      <c r="BV88" s="18"/>
+      <c r="BW88" s="21" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="89" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="124">
         <v>83</v>
       </c>
@@ -19864,34 +20156,37 @@
       <c r="BL89" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM89" s="22" t="s">
+      <c r="BM89" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN89" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="BN89" s="22" t="s">
+      <c r="BO89" s="22" t="s">
         <v>586</v>
       </c>
-      <c r="BO89" s="92" t="s">
+      <c r="BP89" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP89" s="2">
+      <c r="BQ89" s="2">
         <v>1272212</v>
       </c>
-      <c r="BQ89" s="2"/>
-      <c r="BR89" s="2" t="s">
+      <c r="BR89" s="2"/>
+      <c r="BS89" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS89" s="2" t="s">
+      <c r="BT89" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT89" s="18" t="s">
+      <c r="BU89" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU89" s="18"/>
-      <c r="BV89" s="21" t="s">
+      <c r="BV89" s="18"/>
+      <c r="BW89" s="21" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="90" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A90" s="124">
         <v>84</v>
       </c>
@@ -20049,34 +20344,37 @@
       <c r="BL90" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM90" s="22" t="s">
+      <c r="BM90" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN90" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="BN90" s="22" t="s">
+      <c r="BO90" s="22" t="s">
         <v>586</v>
       </c>
-      <c r="BO90" s="92" t="s">
+      <c r="BP90" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="BP90" s="2">
+      <c r="BQ90" s="2">
         <v>1272212</v>
       </c>
-      <c r="BQ90" s="2"/>
-      <c r="BR90" s="2" t="s">
+      <c r="BR90" s="2"/>
+      <c r="BS90" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS90" s="2" t="s">
+      <c r="BT90" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT90" s="18" t="s">
+      <c r="BU90" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU90" s="18"/>
-      <c r="BV90" s="21" t="s">
+      <c r="BV90" s="18"/>
+      <c r="BW90" s="21" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="91" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A91" s="124">
         <v>85</v>
       </c>
@@ -20086,7 +20384,9 @@
       <c r="C91" s="14">
         <v>20260129</v>
       </c>
-      <c r="D91" s="14"/>
+      <c r="D91" s="14">
+        <v>20260217</v>
+      </c>
       <c r="E91" s="14" t="s">
         <v>53</v>
       </c>
@@ -20102,22 +20402,49 @@
       <c r="I91" s="18" t="s">
         <v>827</v>
       </c>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="14"/>
-      <c r="M91" s="14"/>
-      <c r="N91" s="100"/>
-      <c r="O91" s="18"/>
-      <c r="P91" s="18"/>
-      <c r="Q91" s="18"/>
-      <c r="R91" s="18"/>
+      <c r="J91" s="2">
+        <v>29.1</v>
+      </c>
+      <c r="K91" s="2">
+        <v>25.4</v>
+      </c>
+      <c r="L91" s="14">
+        <v>44.473799999999997</v>
+      </c>
+      <c r="M91" s="14">
+        <v>-63.398800000000001</v>
+      </c>
+      <c r="N91" s="100">
+        <v>0.57916666666666672</v>
+      </c>
+      <c r="O91" s="18">
+        <v>42.59</v>
+      </c>
+      <c r="P91" s="18">
+        <v>-63.41</v>
+      </c>
+      <c r="Q91" s="18">
+        <v>44.51</v>
+      </c>
+      <c r="R91" s="18">
+        <v>-61.56</v>
+      </c>
       <c r="S91" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="T91" s="2"/>
-      <c r="U91" s="2"/>
-      <c r="V91" s="2"/>
-      <c r="W91" s="2"/>
+        <v>835</v>
+      </c>
+      <c r="T91" s="2">
+        <v>19</v>
+      </c>
+      <c r="U91" s="2">
+        <v>543</v>
+      </c>
+      <c r="V91" s="2">
+        <v>948</v>
+      </c>
+      <c r="W91" s="2">
+        <f>V91*2</f>
+        <v>1896</v>
+      </c>
       <c r="X91" s="18" t="s">
         <v>36</v>
       </c>
@@ -20205,34 +20532,39 @@
       <c r="BL91" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BM91" s="22" t="s">
+      <c r="BM91" s="49" t="s">
+        <v>842</v>
+      </c>
+      <c r="BN91" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="BN91" s="22" t="s">
+      <c r="BO91" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="BO91" s="22" t="s">
+      <c r="BP91" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="BP91" s="2">
+      <c r="BQ91" s="2">
         <v>1272212</v>
       </c>
-      <c r="BQ91" s="2"/>
-      <c r="BR91" s="2" t="s">
+      <c r="BR91" s="2"/>
+      <c r="BS91" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS91" s="2" t="s">
+      <c r="BT91" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT91" s="18" t="s">
+      <c r="BU91" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="BU91" s="18"/>
-      <c r="BV91" s="21" t="s">
-        <v>835</v>
+      <c r="BV91" s="18" t="s">
+        <v>839</v>
+      </c>
+      <c r="BW91" s="21" t="s">
+        <v>838</v>
       </c>
     </row>
-    <row r="92" spans="1:74" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:75" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A92" s="124">
         <v>86</v>
       </c>
@@ -20244,12 +20576,18 @@
       <c r="E92" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
+      <c r="F92" s="14">
+        <v>148</v>
+      </c>
+      <c r="G92" s="14">
+        <v>4800925</v>
+      </c>
       <c r="H92" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I92" s="18"/>
+      <c r="I92" s="18" t="s">
+        <v>844</v>
+      </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
       <c r="L92" s="14"/>
@@ -20259,7 +20597,9 @@
       <c r="P92" s="18"/>
       <c r="Q92" s="18"/>
       <c r="R92" s="18"/>
-      <c r="S92" s="2"/>
+      <c r="S92" s="2" t="s">
+        <v>442</v>
+      </c>
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
       <c r="V92" s="2"/>
@@ -20283,11 +20623,21 @@
       <c r="AF92" s="2"/>
       <c r="AG92" s="2"/>
       <c r="AH92" s="2"/>
-      <c r="AI92" s="2"/>
-      <c r="AJ92" s="18"/>
-      <c r="AK92" s="18"/>
-      <c r="AL92" s="18"/>
-      <c r="AM92" s="14"/>
+      <c r="AI92" s="2">
+        <v>1024.9000000000001</v>
+      </c>
+      <c r="AJ92" s="18">
+        <v>20260219</v>
+      </c>
+      <c r="AK92" s="18" t="s">
+        <v>845</v>
+      </c>
+      <c r="AL92" s="18" t="s">
+        <v>779</v>
+      </c>
+      <c r="AM92" s="14">
+        <v>33</v>
+      </c>
       <c r="AN92" s="20"/>
       <c r="AO92" s="22"/>
       <c r="AP92" s="22"/>
@@ -20298,10 +20648,10 @@
       <c r="AU92" s="22"/>
       <c r="AV92" s="22"/>
       <c r="AW92" s="161" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AX92" s="54" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AY92" s="22" t="s">
         <v>459</v>
@@ -20329,28 +20679,41 @@
       <c r="BH92" s="22"/>
       <c r="BI92" s="22"/>
       <c r="BJ92" s="22"/>
-      <c r="BK92" s="20"/>
-      <c r="BL92" s="162" t="s">
-        <v>836</v>
-      </c>
-      <c r="BM92" s="22"/>
-      <c r="BN92" s="22"/>
-      <c r="BO92" s="22"/>
+      <c r="BK92" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="BL92" s="49" t="s">
+        <v>834</v>
+      </c>
+      <c r="BM92" s="49" t="s">
+        <v>841</v>
+      </c>
+      <c r="BN92" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="BO92" s="22" t="s">
+        <v>747</v>
+      </c>
       <c r="BP92" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BQ92" s="22" t="s">
         <v>700</v>
       </c>
-      <c r="BQ92" s="2"/>
-      <c r="BR92" s="2" t="s">
+      <c r="BR92" s="2"/>
+      <c r="BS92" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="BS92" s="2" t="s">
+      <c r="BT92" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="BT92" s="18"/>
       <c r="BU92" s="18"/>
-      <c r="BV92" s="21"/>
+      <c r="BV92" s="18"/>
+      <c r="BW92" s="21" t="s">
+        <v>843</v>
+      </c>
     </row>
-    <row r="93" spans="1:74" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:75" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" s="124">
         <v>87</v>
       </c>
@@ -20419,22 +20782,19 @@
       <c r="BJ93" s="38"/>
       <c r="BK93" s="34"/>
       <c r="BL93" s="160"/>
-      <c r="BM93" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="BN93" s="145" t="s">
-        <v>747</v>
-      </c>
-      <c r="BO93" s="38"/>
+      <c r="BM93" s="160"/>
+      <c r="BN93" s="38"/>
+      <c r="BO93" s="145"/>
       <c r="BP93" s="38"/>
-      <c r="BQ93" s="3"/>
-      <c r="BR93" s="120"/>
-      <c r="BS93" s="35"/>
-      <c r="BT93" s="37"/>
+      <c r="BQ93" s="38"/>
+      <c r="BR93" s="3"/>
+      <c r="BS93" s="120"/>
+      <c r="BT93" s="35"/>
       <c r="BU93" s="37"/>
-      <c r="BV93" s="43"/>
+      <c r="BV93" s="37"/>
+      <c r="BW93" s="43"/>
     </row>
-    <row r="94" spans="1:74" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:75" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C94" s="116"/>
       <c r="D94" s="116"/>
       <c r="E94" s="116"/>
@@ -20492,25 +20852,28 @@
       <c r="BI94" s="78"/>
       <c r="BJ94" s="78"/>
       <c r="BK94" s="117"/>
-      <c r="BL94" s="118"/>
-      <c r="BM94" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="BN94" s="144" t="s">
-        <v>586</v>
-      </c>
-      <c r="BO94" s="38"/>
+      <c r="BL94" s="118" t="s">
+        <v>836</v>
+      </c>
+      <c r="BM94" s="118"/>
+      <c r="BN94" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="BO94" s="145" t="s">
+        <v>747</v>
+      </c>
       <c r="BP94" s="38"/>
-      <c r="BQ94" s="3"/>
-      <c r="BR94" s="121"/>
-      <c r="BS94" s="45"/>
-      <c r="BT94" s="77"/>
-      <c r="BU94" s="77" t="s">
+      <c r="BQ94" s="38"/>
+      <c r="BR94" s="3"/>
+      <c r="BS94" s="121"/>
+      <c r="BT94" s="45"/>
+      <c r="BU94" s="77"/>
+      <c r="BV94" s="77" t="s">
         <v>824</v>
       </c>
-      <c r="BV94" s="119"/>
+      <c r="BW94" s="119"/>
     </row>
-    <row r="95" spans="1:74" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:75" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C95" s="116"/>
       <c r="D95" s="116"/>
       <c r="E95" s="116"/>
@@ -20572,23 +20935,26 @@
       <c r="BI95" s="78"/>
       <c r="BJ95" s="78"/>
       <c r="BK95" s="117"/>
-      <c r="BL95" s="118"/>
-      <c r="BM95" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="BN95" s="145" t="s">
-        <v>803</v>
-      </c>
-      <c r="BO95" s="38"/>
+      <c r="BL95" s="118" t="s">
+        <v>837</v>
+      </c>
+      <c r="BM95" s="118"/>
+      <c r="BN95" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO95" s="144" t="s">
+        <v>586</v>
+      </c>
       <c r="BP95" s="38"/>
-      <c r="BQ95" s="3"/>
-      <c r="BR95" s="120"/>
-      <c r="BS95" s="35"/>
-      <c r="BT95" s="77"/>
+      <c r="BQ95" s="38"/>
+      <c r="BR95" s="3"/>
+      <c r="BS95" s="120"/>
+      <c r="BT95" s="35"/>
       <c r="BU95" s="77"/>
-      <c r="BV95" s="119"/>
+      <c r="BV95" s="77"/>
+      <c r="BW95" s="119"/>
     </row>
-    <row r="96" spans="1:74" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:75" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C96" s="116"/>
       <c r="D96" s="116"/>
       <c r="E96" s="116"/>
@@ -20655,22 +21021,23 @@
       <c r="BJ96" s="78"/>
       <c r="BK96" s="117"/>
       <c r="BL96" s="118"/>
-      <c r="BM96" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="BN96" s="145" t="s">
-        <v>746</v>
-      </c>
-      <c r="BO96" s="133"/>
+      <c r="BM96" s="118"/>
+      <c r="BN96" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="BO96" s="145" t="s">
+        <v>803</v>
+      </c>
       <c r="BP96" s="133"/>
-      <c r="BQ96" s="134"/>
-      <c r="BR96" s="135"/>
-      <c r="BS96" s="29"/>
-      <c r="BT96" s="77"/>
+      <c r="BQ96" s="133"/>
+      <c r="BR96" s="134"/>
+      <c r="BS96" s="135"/>
+      <c r="BT96" s="29"/>
       <c r="BU96" s="77"/>
-      <c r="BV96" s="119"/>
+      <c r="BV96" s="77"/>
+      <c r="BW96" s="119"/>
     </row>
-    <row r="97" spans="3:74" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="3:75" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C97" s="116"/>
       <c r="D97" s="116"/>
       <c r="E97" s="116"/>
@@ -20735,22 +21102,23 @@
       <c r="BJ97" s="78"/>
       <c r="BK97" s="117"/>
       <c r="BL97" s="118"/>
-      <c r="BM97" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="BN97" s="149" t="s">
-        <v>514</v>
-      </c>
-      <c r="BO97" s="38"/>
+      <c r="BM97" s="118"/>
+      <c r="BN97" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="BO97" s="145" t="s">
+        <v>746</v>
+      </c>
       <c r="BP97" s="38"/>
-      <c r="BQ97" s="3"/>
-      <c r="BR97" s="29"/>
-      <c r="BS97" s="93"/>
-      <c r="BT97" s="77"/>
+      <c r="BQ97" s="38"/>
+      <c r="BR97" s="3"/>
+      <c r="BS97" s="29"/>
+      <c r="BT97" s="93"/>
       <c r="BU97" s="77"/>
-      <c r="BV97" s="119"/>
+      <c r="BV97" s="77"/>
+      <c r="BW97" s="119"/>
     </row>
-    <row r="98" spans="3:74" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="3:75" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C98" s="116"/>
       <c r="D98" s="116"/>
       <c r="E98" s="116"/>
@@ -20801,22 +21169,23 @@
       <c r="BJ98" s="78"/>
       <c r="BK98" s="117"/>
       <c r="BL98" s="118"/>
-      <c r="BM98" s="38" t="s">
-        <v>283</v>
-      </c>
+      <c r="BM98" s="118"/>
       <c r="BN98" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="BO98" s="38"/>
+        <v>513</v>
+      </c>
+      <c r="BO98" s="144" t="s">
+        <v>514</v>
+      </c>
       <c r="BP98" s="38"/>
-      <c r="BQ98" s="3"/>
-      <c r="BR98" s="29"/>
+      <c r="BQ98" s="38"/>
+      <c r="BR98" s="3"/>
       <c r="BS98" s="29"/>
-      <c r="BT98" s="77"/>
+      <c r="BT98" s="29"/>
       <c r="BU98" s="77"/>
-      <c r="BV98" s="119"/>
+      <c r="BV98" s="77"/>
+      <c r="BW98" s="119"/>
     </row>
-    <row r="99" spans="3:74" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="3:75" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C99" s="116"/>
       <c r="D99" s="116"/>
       <c r="E99" s="116"/>
@@ -20867,18 +21236,23 @@
       <c r="BJ99" s="78"/>
       <c r="BK99" s="117"/>
       <c r="BL99" s="118"/>
-      <c r="BM99" s="46"/>
-      <c r="BN99" s="46"/>
-      <c r="BO99" s="46"/>
+      <c r="BM99" s="118"/>
+      <c r="BN99" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="BO99" s="38" t="s">
+        <v>118</v>
+      </c>
       <c r="BP99" s="46"/>
-      <c r="BQ99" s="48"/>
-      <c r="BR99" s="29"/>
+      <c r="BQ99" s="46"/>
+      <c r="BR99" s="48"/>
       <c r="BS99" s="29"/>
-      <c r="BT99" s="77"/>
+      <c r="BT99" s="29"/>
       <c r="BU99" s="77"/>
-      <c r="BV99" s="119"/>
+      <c r="BV99" s="77"/>
+      <c r="BW99" s="119"/>
     </row>
-    <row r="100" spans="3:74" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="3:75" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C100" s="116"/>
       <c r="D100" s="116"/>
       <c r="E100" s="116"/>
@@ -20929,17 +21303,18 @@
       <c r="BJ100" s="78"/>
       <c r="BK100" s="117"/>
       <c r="BL100" s="118"/>
-      <c r="BM100" s="78"/>
+      <c r="BM100" s="118"/>
       <c r="BN100" s="78"/>
       <c r="BO100" s="78"/>
       <c r="BP100" s="78"/>
-      <c r="BR100" s="116"/>
+      <c r="BQ100" s="78"/>
       <c r="BS100" s="116"/>
-      <c r="BT100" s="77"/>
+      <c r="BT100" s="116"/>
       <c r="BU100" s="77"/>
-      <c r="BV100" s="119"/>
+      <c r="BV100" s="77"/>
+      <c r="BW100" s="119"/>
     </row>
-    <row r="101" spans="3:74" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="3:75" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C101" s="116"/>
       <c r="D101" s="116"/>
       <c r="E101" s="116"/>
@@ -20990,17 +21365,19 @@
       <c r="BJ101" s="78"/>
       <c r="BK101" s="117"/>
       <c r="BL101" s="118"/>
-      <c r="BM101" s="78"/>
+      <c r="BM101" s="118"/>
       <c r="BN101" s="78"/>
       <c r="BO101" s="78"/>
       <c r="BP101" s="78"/>
-      <c r="BR101" s="116"/>
+      <c r="BQ101" s="78"/>
       <c r="BS101" s="116"/>
-      <c r="BT101" s="77"/>
+      <c r="BT101" s="116"/>
       <c r="BU101" s="77"/>
-      <c r="BV101" s="119"/>
+      <c r="BV101" s="77"/>
+      <c r="BW101" s="119"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA8E16F-D4A2-48CC-9DBD-C90779F8D20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A573BBF2-1148-4C6F-B995-EDC0F0BFC8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3141" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="901">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2351,15 +2351,9 @@
     <t>GPCTD failled half way through the mission</t>
   </si>
   <si>
-    <t>CDOM in the negative range (will be flagged I guess, so maybe not needed in the comments)</t>
-  </si>
-  <si>
     <t>237958</t>
   </si>
   <si>
-    <t>with Legato and T.ODO, CDOM negative values, can't load the T.ODO values, wrong battery was inside, need to send to RBR, TODO data not recoverable</t>
-  </si>
-  <si>
     <t>M.Perley/Sigma-T</t>
   </si>
   <si>
@@ -2459,9 +2453,6 @@
     <t>GL1-GL2-GL3-GL7-GL3-GL2-GL1-GL2-GL1-TRI-DR</t>
   </si>
   <si>
-    <t>internal waves on shelf break, back and forth Emerald basin</t>
-  </si>
-  <si>
     <t>20250613</t>
   </si>
   <si>
@@ -2510,9 +2501,6 @@
     <t>GL1-GL2-GL3-GL7-GL3-GL2-GL1-HL2-HL3-TRI-DR</t>
   </si>
   <si>
-    <t>AZMP cruise sampled HL2 right during glider deployment, back and forth between HL2 and HL3</t>
-  </si>
-  <si>
     <t>20251021</t>
   </si>
   <si>
@@ -2546,9 +2534,6 @@
     <t>bon coeff in conf file SEA021?</t>
   </si>
   <si>
-    <t>04-Nov-25</t>
-  </si>
-  <si>
     <t>03-Nov-25</t>
   </si>
   <si>
@@ -2642,9 +2627,6 @@
     <t>Microrider S/N</t>
   </si>
   <si>
-    <t>Microrider cal date</t>
-  </si>
-  <si>
     <t>Release last charge</t>
   </si>
   <si>
@@ -2654,10 +2636,127 @@
     <t>2 - with 5deg pitch</t>
   </si>
   <si>
-    <t>first mission at 1000m depth, Alseamar sim card, crossed path with Dal glider on the way out just after Hl4</t>
-  </si>
-  <si>
     <t>GLI2026_SEA032_102</t>
+  </si>
+  <si>
+    <t>first mission at 1000m depth, Alseamar sim card, crossed path with Dal glider on the way out just after Hl4, CDOM jum in deep water</t>
+  </si>
+  <si>
+    <t>Ecopuck jump in deep water</t>
+  </si>
+  <si>
+    <t>AZMP cruise sampled HL2 right during glider deployment, back and forth between HL2 and HL3, glider went to 817m because of wrong pressure sensor coef</t>
+  </si>
+  <si>
+    <t>internal waves on shelf break, back and forth Emerald basin,glider went to 817m because of wrong pressure sensor coef</t>
+  </si>
+  <si>
+    <t>with Legato and T.ODO, CDOM negative values, can't load the T.ODO values, wrong battery was inside, need to send to RBR, TODO data not recoverable,glider went to 817m because of wrong pressure sensor coef</t>
+  </si>
+  <si>
+    <t>CDOM in the negative range (will be flagged I guess, so maybe not needed in the comments), glider and sensor pressure missmatch, trust CTD pressure</t>
+  </si>
+  <si>
+    <t>glider and sensor pressure missmatch, trust CTD pressure</t>
+  </si>
+  <si>
+    <t>new pld</t>
+  </si>
+  <si>
+    <t>241286</t>
+  </si>
+  <si>
+    <t>240440</t>
+  </si>
+  <si>
+    <t>107453</t>
+  </si>
+  <si>
+    <t>241970 puck new pld</t>
+  </si>
+  <si>
+    <t>519</t>
+  </si>
+  <si>
+    <t>163 new</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>241049</t>
+  </si>
+  <si>
+    <t>240444</t>
+  </si>
+  <si>
+    <t>239559</t>
+  </si>
+  <si>
+    <t>45-624-18</t>
+  </si>
+  <si>
+    <t>45-623-18</t>
+  </si>
+  <si>
+    <t>240447</t>
+  </si>
+  <si>
+    <t>240453</t>
+  </si>
+  <si>
+    <t>241050</t>
+  </si>
+  <si>
+    <t>241983</t>
+  </si>
+  <si>
+    <t>20260130</t>
+  </si>
+  <si>
+    <t>HL part</t>
+  </si>
+  <si>
+    <t>4551</t>
+  </si>
+  <si>
+    <t>Feb 2026?</t>
+  </si>
+  <si>
+    <t>Back from maintenance seal trial,</t>
+  </si>
+  <si>
+    <t>Back from maintenance seal trial, First mission with thrusters</t>
+  </si>
+  <si>
+    <t>20260120</t>
+  </si>
+  <si>
+    <t>20251216</t>
+  </si>
+  <si>
+    <t>241970</t>
+  </si>
+  <si>
+    <t>20260312</t>
+  </si>
+  <si>
+    <t>20260220</t>
+  </si>
+  <si>
+    <t>Microrider probes cal date</t>
+  </si>
+  <si>
+    <t>First microrider/ADCP/Tridente mission</t>
+  </si>
+  <si>
+    <t>Sigma-T/Halmar</t>
+  </si>
+  <si>
+    <t>Halmar/</t>
   </si>
 </sst>
 </file>
@@ -3015,7 +3114,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3430,6 +3529,12 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3759,7 +3864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DQ103"/>
+  <dimension ref="A1:DQ106"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.54296875" customWidth="1"/>
@@ -3791,7 +3896,8 @@
     <col min="29" max="29" width="20.54296875" style="77" customWidth="1"/>
     <col min="30" max="30" width="20.54296875" style="77" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="18.81640625" style="7" customWidth="1"/>
-    <col min="32" max="35" width="20.54296875" style="77" customWidth="1"/>
+    <col min="32" max="34" width="20.54296875" style="77" customWidth="1"/>
+    <col min="35" max="35" width="24.90625" style="77" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="10" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="7.1796875" bestFit="1" customWidth="1"/>
@@ -3819,7 +3925,8 @@
     <col min="61" max="61" width="15.1796875" style="78" bestFit="1" customWidth="1"/>
     <col min="62" max="64" width="15.1796875" style="78" customWidth="1"/>
     <col min="65" max="66" width="17.81640625" style="6" customWidth="1"/>
-    <col min="67" max="75" width="15.1796875" style="78" customWidth="1"/>
+    <col min="67" max="74" width="15.1796875" style="78" customWidth="1"/>
+    <col min="75" max="75" width="23.54296875" style="78" bestFit="1" customWidth="1"/>
     <col min="76" max="76" width="11.81640625" style="5" customWidth="1"/>
     <col min="77" max="80" width="16.36328125" style="1" customWidth="1"/>
     <col min="81" max="81" width="12.81640625" style="6" bestFit="1" customWidth="1"/>
@@ -3837,13 +3944,13 @@
     <row r="1" spans="1:90" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C1" s="24"/>
       <c r="D1" s="146" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="E1" s="94" t="s">
         <v>430</v>
       </c>
       <c r="F1" s="91" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="G1" s="24"/>
       <c r="H1" s="24"/>
@@ -4003,19 +4110,19 @@
         <v>301</v>
       </c>
       <c r="AE2" s="68" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="AF2" s="68" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="AG2" s="68" t="s">
         <v>360</v>
       </c>
       <c r="AH2" s="68" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="AI2" s="68" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="AJ2" s="32" t="s">
         <v>55</v>
@@ -4033,7 +4140,7 @@
         <v>109</v>
       </c>
       <c r="AO2" s="68" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="AP2" s="68" t="s">
         <v>141</v>
@@ -4096,25 +4203,25 @@
         <v>311</v>
       </c>
       <c r="BJ2" s="70" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="BK2" s="70" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="BL2" s="70" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="BM2" s="72" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="BN2" s="72" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="BO2" s="70" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="BP2" s="70" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="BQ2" s="70" t="s">
         <v>363</v>
@@ -4126,16 +4233,16 @@
         <v>365</v>
       </c>
       <c r="BT2" s="161" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="BU2" s="161" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="BV2" s="161" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="BW2" s="161" t="s">
-        <v>862</v>
+        <v>897</v>
       </c>
       <c r="BX2" s="73" t="s">
         <v>167</v>
@@ -4144,13 +4251,13 @@
         <v>168</v>
       </c>
       <c r="BZ2" s="33" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="CA2" s="33" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="CB2" s="33" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="CC2" s="70" t="s">
         <v>92</v>
@@ -4356,10 +4463,10 @@
       </c>
       <c r="BZ3" s="17"/>
       <c r="CA3" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB3" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC3" s="15" t="s">
         <v>95</v>
@@ -4557,10 +4664,10 @@
       </c>
       <c r="BZ4" s="17"/>
       <c r="CA4" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB4" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC4" s="15" t="s">
         <v>95</v>
@@ -4760,10 +4867,10 @@
       </c>
       <c r="BZ5" s="42"/>
       <c r="CA5" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB5" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC5" s="40" t="s">
         <v>95</v>
@@ -4964,10 +5071,10 @@
       </c>
       <c r="BZ6" s="42"/>
       <c r="CA6" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB6" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC6" s="40" t="s">
         <v>95</v>
@@ -5167,10 +5274,10 @@
       </c>
       <c r="BZ7" s="42"/>
       <c r="CA7" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB7" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC7" s="40" t="s">
         <v>95</v>
@@ -5372,10 +5479,10 @@
       </c>
       <c r="BZ8" s="42"/>
       <c r="CA8" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB8" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC8" s="40" t="s">
         <v>96</v>
@@ -5575,10 +5682,10 @@
       </c>
       <c r="BZ9" s="42"/>
       <c r="CA9" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB9" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC9" s="40" t="s">
         <v>95</v>
@@ -5778,10 +5885,10 @@
       </c>
       <c r="BZ10" s="42"/>
       <c r="CA10" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB10" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC10" s="40" t="s">
         <v>96</v>
@@ -5981,10 +6088,10 @@
       </c>
       <c r="BZ11" s="42"/>
       <c r="CA11" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB11" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC11" s="40" t="s">
         <v>96</v>
@@ -6188,10 +6295,10 @@
       </c>
       <c r="BZ12" s="42"/>
       <c r="CA12" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB12" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC12" s="40" t="s">
         <v>95</v>
@@ -6241,7 +6348,7 @@
         <v>4800993</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I13" s="36" t="s">
         <v>599</v>
@@ -6391,10 +6498,10 @@
       </c>
       <c r="BZ13" s="42"/>
       <c r="CA13" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB13" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC13" s="38" t="s">
         <v>98</v>
@@ -6596,10 +6703,10 @@
       </c>
       <c r="BZ14" s="42"/>
       <c r="CA14" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB14" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC14" s="40" t="s">
         <v>96</v>
@@ -6803,10 +6910,10 @@
       </c>
       <c r="BZ15" s="42"/>
       <c r="CA15" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB15" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC15" s="40" t="s">
         <v>96</v>
@@ -7006,10 +7113,10 @@
       </c>
       <c r="BZ16" s="42"/>
       <c r="CA16" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB16" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC16" s="38" t="s">
         <v>98</v>
@@ -7210,10 +7317,10 @@
       </c>
       <c r="BZ17" s="42"/>
       <c r="CA17" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB17" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC17" s="40" t="s">
         <v>95</v>
@@ -7414,10 +7521,10 @@
       </c>
       <c r="BZ18" s="17"/>
       <c r="CA18" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB18" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC18" s="22" t="s">
         <v>98</v>
@@ -7614,10 +7721,10 @@
       </c>
       <c r="BZ19" s="17"/>
       <c r="CA19" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB19" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC19" s="54" t="s">
         <v>117</v>
@@ -7816,10 +7923,10 @@
       </c>
       <c r="BZ20" s="17"/>
       <c r="CA20" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB20" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC20" s="22" t="s">
         <v>98</v>
@@ -8021,10 +8128,10 @@
       </c>
       <c r="BZ21" s="17"/>
       <c r="CA21" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB21" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC21" s="22" t="s">
         <v>98</v>
@@ -8226,10 +8333,10 @@
       </c>
       <c r="BZ22" s="17"/>
       <c r="CA22" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB22" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC22" s="22" t="s">
         <v>98</v>
@@ -8431,10 +8538,10 @@
       </c>
       <c r="BZ23" s="17"/>
       <c r="CA23" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB23" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC23" s="22" t="s">
         <v>98</v>
@@ -8486,7 +8593,7 @@
         <v>4800994</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>610</v>
@@ -8636,10 +8743,10 @@
       </c>
       <c r="BZ24" s="17"/>
       <c r="CA24" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB24" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC24" s="15" t="s">
         <v>95</v>
@@ -8836,10 +8943,10 @@
       </c>
       <c r="BZ25" s="17"/>
       <c r="CA25" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB25" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC25" s="54" t="s">
         <v>117</v>
@@ -9042,10 +9149,10 @@
       </c>
       <c r="BZ26" s="17"/>
       <c r="CA26" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB26" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC26" s="22" t="s">
         <v>98</v>
@@ -9097,7 +9204,7 @@
         <v>4800994</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I27" s="12" t="s">
         <v>613</v>
@@ -9246,10 +9353,10 @@
       </c>
       <c r="BZ27" s="17"/>
       <c r="CA27" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB27" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC27" s="15" t="s">
         <v>95</v>
@@ -9449,10 +9556,10 @@
       </c>
       <c r="BZ28" s="17"/>
       <c r="CA28" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB28" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC28" s="15" t="s">
         <v>98</v>
@@ -9641,10 +9748,10 @@
       </c>
       <c r="BZ29" s="17"/>
       <c r="CA29" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB29" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC29" s="22" t="s">
         <v>117</v>
@@ -9842,10 +9949,10 @@
       </c>
       <c r="BZ30" s="17"/>
       <c r="CA30" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB30" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC30" s="15" t="s">
         <v>95</v>
@@ -10046,10 +10153,10 @@
       </c>
       <c r="BZ31" s="17"/>
       <c r="CA31" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB31" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC31" s="22" t="s">
         <v>117</v>
@@ -10255,10 +10362,10 @@
       </c>
       <c r="BZ32" s="17"/>
       <c r="CA32" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB32" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC32" s="15" t="s">
         <v>95</v>
@@ -10368,10 +10475,10 @@
       <c r="BY33" s="42"/>
       <c r="BZ33" s="42"/>
       <c r="CA33" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB33" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC33" s="40"/>
       <c r="CD33" s="38"/>
@@ -10394,7 +10501,7 @@
       <c r="F34" s="35"/>
       <c r="G34" s="35"/>
       <c r="H34" s="35" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I34" s="37"/>
       <c r="J34" s="3"/>
@@ -10467,10 +10574,10 @@
       <c r="BY34" s="42"/>
       <c r="BZ34" s="42"/>
       <c r="CA34" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB34" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC34" s="40"/>
       <c r="CD34" s="38"/>
@@ -10656,10 +10763,10 @@
       </c>
       <c r="BZ35" s="42"/>
       <c r="CA35" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB35" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC35" s="38" t="s">
         <v>98</v>
@@ -10860,10 +10967,10 @@
       </c>
       <c r="BZ36" s="42"/>
       <c r="CA36" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB36" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC36" s="38" t="s">
         <v>98</v>
@@ -11054,10 +11161,10 @@
       </c>
       <c r="BZ37" s="42"/>
       <c r="CA37" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB37" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC37" s="46" t="s">
         <v>245</v>
@@ -11111,7 +11218,7 @@
         <v>4800993</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I38" s="36" t="s">
         <v>622</v>
@@ -11265,10 +11372,10 @@
       </c>
       <c r="BZ38" s="42"/>
       <c r="CA38" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB38" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC38" s="40" t="s">
         <v>96</v>
@@ -11316,7 +11423,7 @@
         <v>4800993</v>
       </c>
       <c r="H39" s="35" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I39" s="36" t="s">
         <v>623</v>
@@ -11470,10 +11577,10 @@
       </c>
       <c r="BZ39" s="42"/>
       <c r="CA39" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB39" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC39" s="40" t="s">
         <v>96</v>
@@ -11521,7 +11628,7 @@
         <v>4800993</v>
       </c>
       <c r="H40" s="35" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I40" s="36" t="s">
         <v>624</v>
@@ -11675,10 +11782,10 @@
       </c>
       <c r="BZ40" s="42"/>
       <c r="CA40" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB40" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC40" s="40" t="s">
         <v>96</v>
@@ -11885,10 +11992,10 @@
       </c>
       <c r="BZ41" s="42"/>
       <c r="CA41" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB41" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC41" s="46" t="s">
         <v>245</v>
@@ -12091,10 +12198,10 @@
       </c>
       <c r="BZ42" s="42"/>
       <c r="CA42" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB42" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC42" s="58" t="s">
         <v>117</v>
@@ -12295,10 +12402,10 @@
       </c>
       <c r="BZ43" s="42"/>
       <c r="CA43" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB43" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC43" s="40" t="s">
         <v>96</v>
@@ -12501,10 +12608,10 @@
       </c>
       <c r="BZ44" s="42"/>
       <c r="CA44" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB44" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC44" s="40" t="s">
         <v>95</v>
@@ -12703,10 +12810,10 @@
       </c>
       <c r="BZ45" s="17"/>
       <c r="CA45" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB45" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC45" s="15" t="s">
         <v>96</v>
@@ -12908,10 +13015,10 @@
       </c>
       <c r="BZ46" s="17"/>
       <c r="CA46" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB46" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC46" s="54" t="s">
         <v>245</v>
@@ -13112,10 +13219,10 @@
       </c>
       <c r="BZ47" s="17"/>
       <c r="CA47" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB47" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC47" s="15" t="s">
         <v>95</v>
@@ -13316,10 +13423,10 @@
       </c>
       <c r="BZ48" s="17"/>
       <c r="CA48" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB48" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC48" s="15" t="s">
         <v>96</v>
@@ -13533,10 +13640,10 @@
       </c>
       <c r="BZ49" s="17"/>
       <c r="CA49" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB49" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC49" s="15" t="s">
         <v>98</v>
@@ -13733,10 +13840,10 @@
       </c>
       <c r="BZ50" s="17"/>
       <c r="CA50" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB50" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC50" s="15" t="s">
         <v>95</v>
@@ -13937,10 +14044,10 @@
       </c>
       <c r="BZ51" s="17"/>
       <c r="CA51" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB51" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC51" s="15" t="s">
         <v>96</v>
@@ -13992,7 +14099,7 @@
         <v>4800994</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I52" s="12" t="s">
         <v>636</v>
@@ -14154,10 +14261,10 @@
       </c>
       <c r="BZ52" s="17"/>
       <c r="CA52" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB52" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC52" s="15" t="s">
         <v>98</v>
@@ -14205,7 +14312,7 @@
         <v>4800994</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>637</v>
@@ -14366,10 +14473,10 @@
       </c>
       <c r="BZ53" s="17"/>
       <c r="CA53" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB53" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC53" s="15" t="s">
         <v>98</v>
@@ -14568,10 +14675,10 @@
       </c>
       <c r="BZ54" s="17"/>
       <c r="CA54" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB54" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC54" s="15" t="s">
         <v>95</v>
@@ -14774,10 +14881,10 @@
       </c>
       <c r="BZ55" s="17"/>
       <c r="CA55" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB55" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC55" s="15" t="s">
         <v>96</v>
@@ -14831,7 +14938,7 @@
         <v>4800994</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I56" s="12" t="s">
         <v>640</v>
@@ -14997,10 +15104,10 @@
       </c>
       <c r="BZ56" s="17"/>
       <c r="CA56" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB56" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC56" s="15" t="s">
         <v>98</v>
@@ -15200,10 +15307,10 @@
       </c>
       <c r="BZ57" s="17"/>
       <c r="CA57" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB57" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC57" s="22" t="s">
         <v>117</v>
@@ -15404,10 +15511,10 @@
       </c>
       <c r="BZ58" s="17"/>
       <c r="CA58" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB58" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC58" s="15" t="s">
         <v>95</v>
@@ -15620,10 +15727,10 @@
       </c>
       <c r="BZ59" s="17"/>
       <c r="CA59" s="17" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB59" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC59" s="15" t="s">
         <v>95</v>
@@ -15824,10 +15931,10 @@
       </c>
       <c r="BZ60" s="42"/>
       <c r="CA60" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB60" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC60" s="40" t="s">
         <v>95</v>
@@ -16028,10 +16135,10 @@
       </c>
       <c r="BZ61" s="42"/>
       <c r="CA61" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB61" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC61" s="40" t="s">
         <v>95</v>
@@ -16083,7 +16190,7 @@
         <v>4800937</v>
       </c>
       <c r="H62" s="35" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I62" s="37" t="s">
         <v>645</v>
@@ -16244,10 +16351,10 @@
       </c>
       <c r="BZ62" s="42"/>
       <c r="CA62" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB62" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC62" s="40" t="s">
         <v>245</v>
@@ -16450,14 +16557,14 @@
         <v>228</v>
       </c>
       <c r="BY63" s="42" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="BZ63" s="42"/>
       <c r="CA63" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB63" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC63" s="96" t="s">
         <v>245</v>
@@ -16656,10 +16763,10 @@
       </c>
       <c r="BZ64" s="42"/>
       <c r="CA64" s="42" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB64" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC64" s="96">
         <v>162640</v>
@@ -16865,14 +16972,14 @@
         <v>228</v>
       </c>
       <c r="BY65" s="49" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="BZ65" s="49"/>
       <c r="CA65" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB65" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC65" s="49">
         <v>201383</v>
@@ -17074,10 +17181,10 @@
       </c>
       <c r="BZ66" s="17"/>
       <c r="CA66" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB66" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC66" s="49">
         <v>162640</v>
@@ -17283,10 +17390,10 @@
       </c>
       <c r="BZ67" s="17"/>
       <c r="CA67" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB67" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC67" s="49" t="s">
         <v>245</v>
@@ -17338,7 +17445,7 @@
         <v>4800994</v>
       </c>
       <c r="H68" s="14" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I68" s="18" t="s">
         <v>651</v>
@@ -17502,10 +17609,10 @@
       </c>
       <c r="BZ68" s="49"/>
       <c r="CA68" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB68" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC68" s="49">
         <v>162642</v>
@@ -17705,10 +17812,10 @@
       </c>
       <c r="BZ69" s="49"/>
       <c r="CA69" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB69" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC69" s="15" t="s">
         <v>98</v>
@@ -17916,14 +18023,14 @@
         <v>228</v>
       </c>
       <c r="BY70" s="49" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="BZ70" s="49"/>
       <c r="CA70" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB70" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC70" s="22" t="s">
         <v>513</v>
@@ -18129,14 +18236,14 @@
         <v>228</v>
       </c>
       <c r="BY71" s="49" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="BZ71" s="49"/>
       <c r="CA71" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB71" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC71" s="22" t="s">
         <v>513</v>
@@ -18368,10 +18475,10 @@
       </c>
       <c r="BZ72" s="49"/>
       <c r="CA72" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB72" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC72" s="49" t="s">
         <v>98</v>
@@ -18606,10 +18713,10 @@
       </c>
       <c r="BZ73" s="96"/>
       <c r="CA73" s="96" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB73" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC73" s="38" t="s">
         <v>513</v>
@@ -18813,10 +18920,10 @@
       </c>
       <c r="BZ74" s="96"/>
       <c r="CA74" s="96" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB74" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC74" s="38" t="s">
         <v>513</v>
@@ -18866,7 +18973,7 @@
         <v>4800993</v>
       </c>
       <c r="H75" s="35" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="I75" s="37" t="s">
         <v>679</v>
@@ -19026,10 +19133,10 @@
       </c>
       <c r="BZ75" s="96"/>
       <c r="CA75" s="96" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB75" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC75" s="38" t="s">
         <v>95</v>
@@ -19229,10 +19336,10 @@
       </c>
       <c r="BZ76" s="96"/>
       <c r="CA76" s="96" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB76" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC76" s="38" t="s">
         <v>117</v>
@@ -19428,14 +19535,14 @@
         <v>228</v>
       </c>
       <c r="BY77" s="96" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="BZ77" s="96"/>
       <c r="CA77" s="96" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB77" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC77" s="38" t="s">
         <v>98</v>
@@ -19641,10 +19748,10 @@
       </c>
       <c r="BZ78" s="96"/>
       <c r="CA78" s="96" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB78" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC78" s="38" t="s">
         <v>117</v>
@@ -19850,10 +19957,10 @@
       </c>
       <c r="BZ79" s="96"/>
       <c r="CA79" s="96" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB79" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC79" s="38" t="s">
         <v>95</v>
@@ -19997,7 +20104,7 @@
         <v>739</v>
       </c>
       <c r="AQ80" s="37" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AR80" s="35">
         <v>33</v>
@@ -20059,10 +20166,10 @@
       </c>
       <c r="BZ80" s="96"/>
       <c r="CA80" s="96" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB80" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC80" s="38" t="s">
         <v>513</v>
@@ -20210,7 +20317,7 @@
         <v>750</v>
       </c>
       <c r="AQ81" s="37" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AR81" s="35">
         <v>30</v>
@@ -20280,10 +20387,10 @@
       </c>
       <c r="BZ81" s="96"/>
       <c r="CA81" s="96" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB81" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC81" s="38" t="s">
         <v>95</v>
@@ -20308,10 +20415,10 @@
         <v>756</v>
       </c>
       <c r="CK81" s="37" t="s">
-        <v>765</v>
+        <v>866</v>
       </c>
       <c r="CL81" s="43" t="s">
-        <v>767</v>
+        <v>865</v>
       </c>
     </row>
     <row r="82" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -20427,7 +20534,7 @@
         <v>750</v>
       </c>
       <c r="AQ82" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AR82" s="14">
         <v>32</v>
@@ -20489,10 +20596,10 @@
       </c>
       <c r="BZ82" s="49"/>
       <c r="CA82" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB82" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC82" s="22" t="s">
         <v>513</v>
@@ -20501,7 +20608,7 @@
         <v>514</v>
       </c>
       <c r="CE82" s="92" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="CF82" s="2">
         <v>1272212</v>
@@ -20516,13 +20623,13 @@
         <v>204</v>
       </c>
       <c r="CJ82" s="18" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="CK82" s="18" t="s">
         <v>764</v>
       </c>
       <c r="CL82" s="21" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="83" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -20551,7 +20658,7 @@
         <v>15</v>
       </c>
       <c r="I83" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="J83" s="2">
         <v>29.2</v>
@@ -20609,7 +20716,7 @@
       <c r="AB83" s="18"/>
       <c r="AC83" s="18"/>
       <c r="AD83" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE83" s="18"/>
       <c r="AF83" s="18"/>
@@ -20638,7 +20745,7 @@
         <v>750</v>
       </c>
       <c r="AQ83" s="18" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="AR83" s="14">
         <v>33</v>
@@ -20667,7 +20774,7 @@
         <v>760</v>
       </c>
       <c r="BH83" s="22" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="BI83" s="22" t="s">
         <v>418</v>
@@ -20676,10 +20783,10 @@
         <v>299</v>
       </c>
       <c r="BK83" s="22" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="BL83" s="22" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="BM83" s="22"/>
       <c r="BN83" s="22"/>
@@ -20700,10 +20807,10 @@
       </c>
       <c r="BZ83" s="49"/>
       <c r="CA83" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB83" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC83" s="22" t="s">
         <v>95</v>
@@ -20729,7 +20836,7 @@
       </c>
       <c r="CK83" s="18"/>
       <c r="CL83" s="21" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="84" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -20758,7 +20865,7 @@
         <v>15</v>
       </c>
       <c r="I84" s="18" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="J84" s="2">
         <v>29.3</v>
@@ -20788,7 +20895,7 @@
         <v>-63.13</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="T84" s="2">
         <v>3</v>
@@ -20816,7 +20923,7 @@
       <c r="AB84" s="18"/>
       <c r="AC84" s="18"/>
       <c r="AD84" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE84" s="18"/>
       <c r="AF84" s="18"/>
@@ -20845,7 +20952,7 @@
         <v>750</v>
       </c>
       <c r="AQ84" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AR84" s="14">
         <v>32</v>
@@ -20874,7 +20981,7 @@
         <v>759</v>
       </c>
       <c r="BH84" s="22" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="BI84" s="22" t="s">
         <v>418</v>
@@ -20883,10 +20990,10 @@
         <v>299</v>
       </c>
       <c r="BK84" s="22" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="BL84" s="22" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="BM84" s="22"/>
       <c r="BN84" s="22"/>
@@ -20907,10 +21014,10 @@
       </c>
       <c r="BZ84" s="49"/>
       <c r="CA84" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB84" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC84" s="22" t="s">
         <v>513</v>
@@ -20932,13 +21039,13 @@
         <v>204</v>
       </c>
       <c r="CJ84" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="CK84" s="18" t="s">
         <v>787</v>
       </c>
-      <c r="CK84" s="18" t="s">
-        <v>789</v>
-      </c>
       <c r="CL84" s="21" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="85" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -20967,7 +21074,7 @@
         <v>15</v>
       </c>
       <c r="I85" s="18" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="J85" s="2">
         <v>28.5</v>
@@ -21025,7 +21132,7 @@
       <c r="AB85" s="18"/>
       <c r="AC85" s="18"/>
       <c r="AD85" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE85" s="18"/>
       <c r="AF85" s="18"/>
@@ -21054,7 +21161,7 @@
         <v>750</v>
       </c>
       <c r="AQ85" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AR85" s="14">
         <v>32</v>
@@ -21083,7 +21190,7 @@
         <v>759</v>
       </c>
       <c r="BH85" s="22" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="BI85" s="22" t="s">
         <v>418</v>
@@ -21092,10 +21199,10 @@
         <v>299</v>
       </c>
       <c r="BK85" s="22" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="BL85" s="22" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="BM85" s="22"/>
       <c r="BN85" s="22"/>
@@ -21116,10 +21223,10 @@
       </c>
       <c r="BZ85" s="49"/>
       <c r="CA85" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB85" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC85" s="22" t="s">
         <v>513</v>
@@ -21141,13 +21248,13 @@
         <v>204</v>
       </c>
       <c r="CJ85" s="18" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="CK85" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="CL85" s="21" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="86" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -21176,7 +21283,7 @@
         <v>15</v>
       </c>
       <c r="I86" s="18" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="J86" s="2">
         <v>29</v>
@@ -21206,7 +21313,7 @@
         <v>-61.44</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="T86" s="2">
         <v>22</v>
@@ -21234,7 +21341,7 @@
       <c r="AB86" s="18"/>
       <c r="AC86" s="18"/>
       <c r="AD86" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE86" s="18"/>
       <c r="AF86" s="18"/>
@@ -21263,7 +21370,7 @@
         <v>750</v>
       </c>
       <c r="AQ86" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AR86" s="14">
         <v>30</v>
@@ -21292,7 +21399,7 @@
         <v>758</v>
       </c>
       <c r="BH86" s="22" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="BI86" s="22" t="s">
         <v>418</v>
@@ -21301,10 +21408,10 @@
         <v>299</v>
       </c>
       <c r="BK86" s="22" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="BL86" s="22" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="BM86" s="22"/>
       <c r="BN86" s="22"/>
@@ -21325,10 +21432,10 @@
       </c>
       <c r="BZ86" s="49"/>
       <c r="CA86" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB86" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC86" s="22" t="s">
         <v>95</v>
@@ -21350,11 +21457,13 @@
         <v>204</v>
       </c>
       <c r="CJ86" s="18" t="s">
-        <v>787</v>
-      </c>
-      <c r="CK86" s="18"/>
+        <v>785</v>
+      </c>
+      <c r="CK86" s="18" t="s">
+        <v>867</v>
+      </c>
       <c r="CL86" s="21" t="s">
-        <v>801</v>
+        <v>864</v>
       </c>
     </row>
     <row r="87" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -21383,7 +21492,7 @@
         <v>15</v>
       </c>
       <c r="I87" s="18" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="J87" s="2">
         <v>29.1</v>
@@ -21413,7 +21522,7 @@
         <v>-61.18</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="T87" s="2">
         <v>25</v>
@@ -21425,7 +21534,7 @@
         <v>934</v>
       </c>
       <c r="W87" s="2">
-        <f>V87*2</f>
+        <f t="shared" ref="W87:W92" si="0">V87*2</f>
         <v>1868</v>
       </c>
       <c r="X87" s="18" t="s">
@@ -21441,7 +21550,7 @@
       <c r="AB87" s="18"/>
       <c r="AC87" s="18"/>
       <c r="AD87" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE87" s="18"/>
       <c r="AF87" s="18"/>
@@ -21470,7 +21579,7 @@
         <v>750</v>
       </c>
       <c r="AQ87" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AR87" s="14">
         <v>32</v>
@@ -21499,7 +21608,7 @@
         <v>757</v>
       </c>
       <c r="BH87" s="22" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="BI87" s="22" t="s">
         <v>418</v>
@@ -21508,10 +21617,10 @@
         <v>299</v>
       </c>
       <c r="BK87" s="22" t="s">
+        <v>789</v>
+      </c>
+      <c r="BL87" s="22" t="s">
         <v>791</v>
-      </c>
-      <c r="BL87" s="22" t="s">
-        <v>793</v>
       </c>
       <c r="BM87" s="22"/>
       <c r="BN87" s="22"/>
@@ -21532,10 +21641,10 @@
       </c>
       <c r="BZ87" s="49"/>
       <c r="CA87" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB87" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC87" s="22" t="s">
         <v>98</v>
@@ -21557,11 +21666,11 @@
         <v>204</v>
       </c>
       <c r="CJ87" s="18" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="CK87" s="18"/>
       <c r="CL87" s="21" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="88" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -21590,7 +21699,7 @@
         <v>15</v>
       </c>
       <c r="I88" s="18" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="J88" s="2">
         <v>29.2</v>
@@ -21620,7 +21729,7 @@
         <v>-61.42</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="T88" s="2">
         <v>21</v>
@@ -21632,7 +21741,7 @@
         <v>1174</v>
       </c>
       <c r="W88" s="2">
-        <f>V88*2</f>
+        <f t="shared" si="0"/>
         <v>2348</v>
       </c>
       <c r="X88" s="18" t="s">
@@ -21648,7 +21757,7 @@
       <c r="AB88" s="18"/>
       <c r="AC88" s="18"/>
       <c r="AD88" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE88" s="18"/>
       <c r="AF88" s="18"/>
@@ -21677,7 +21786,7 @@
         <v>750</v>
       </c>
       <c r="AQ88" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AR88" s="14">
         <v>30</v>
@@ -21706,7 +21815,7 @@
         <v>758</v>
       </c>
       <c r="BH88" s="22" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="BI88" s="22" t="s">
         <v>418</v>
@@ -21715,10 +21824,10 @@
         <v>299</v>
       </c>
       <c r="BK88" s="22" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="BL88" s="22" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="BM88" s="22"/>
       <c r="BN88" s="22"/>
@@ -21739,10 +21848,10 @@
       </c>
       <c r="BZ88" s="49"/>
       <c r="CA88" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB88" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC88" s="22" t="s">
         <v>513</v>
@@ -21754,10 +21863,10 @@
         <v>136</v>
       </c>
       <c r="CF88" s="22" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="CG88" s="2" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="CH88" s="2" t="s">
         <v>668</v>
@@ -21768,9 +21877,11 @@
       <c r="CJ88" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK88" s="18"/>
+      <c r="CK88" s="18" t="s">
+        <v>867</v>
+      </c>
       <c r="CL88" s="21" t="s">
-        <v>818</v>
+        <v>863</v>
       </c>
     </row>
     <row r="89" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -21799,7 +21910,7 @@
         <v>15</v>
       </c>
       <c r="I89" s="18" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="J89" s="2">
         <v>29.2</v>
@@ -21829,7 +21940,7 @@
         <v>-61.41</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="T89" s="2">
         <v>24</v>
@@ -21841,7 +21952,7 @@
         <v>958</v>
       </c>
       <c r="W89" s="2">
-        <f>V89*2</f>
+        <f t="shared" si="0"/>
         <v>1916</v>
       </c>
       <c r="X89" s="18" t="s">
@@ -21857,7 +21968,7 @@
       <c r="AB89" s="18"/>
       <c r="AC89" s="18"/>
       <c r="AD89" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE89" s="18"/>
       <c r="AF89" s="18"/>
@@ -21886,7 +21997,7 @@
         <v>750</v>
       </c>
       <c r="AQ89" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AR89" s="14">
         <v>32</v>
@@ -21915,7 +22026,7 @@
         <v>757</v>
       </c>
       <c r="BH89" s="22" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="BI89" s="22" t="s">
         <v>418</v>
@@ -21924,10 +22035,10 @@
         <v>299</v>
       </c>
       <c r="BK89" s="22" t="s">
+        <v>789</v>
+      </c>
+      <c r="BL89" s="22" t="s">
         <v>791</v>
-      </c>
-      <c r="BL89" s="22" t="s">
-        <v>793</v>
       </c>
       <c r="BM89" s="22"/>
       <c r="BN89" s="22"/>
@@ -21948,10 +22059,10 @@
       </c>
       <c r="BZ89" s="49"/>
       <c r="CA89" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB89" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC89" s="22" t="s">
         <v>95</v>
@@ -21977,7 +22088,7 @@
       </c>
       <c r="CK89" s="18"/>
       <c r="CL89" s="21" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="90" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
@@ -22006,7 +22117,7 @@
         <v>15</v>
       </c>
       <c r="I90" s="18" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="J90" s="2">
         <v>29.2</v>
@@ -22048,7 +22159,7 @@
         <v>1202</v>
       </c>
       <c r="W90" s="2">
-        <f>V90*2</f>
+        <f t="shared" si="0"/>
         <v>2404</v>
       </c>
       <c r="X90" s="18" t="s">
@@ -22064,7 +22175,7 @@
       <c r="AB90" s="18"/>
       <c r="AC90" s="18"/>
       <c r="AD90" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE90" s="18"/>
       <c r="AF90" s="18"/>
@@ -22093,7 +22204,7 @@
         <v>750</v>
       </c>
       <c r="AQ90" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AR90" s="14">
         <v>32</v>
@@ -22122,7 +22233,7 @@
         <v>757</v>
       </c>
       <c r="BH90" s="22" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="BI90" s="22" t="s">
         <v>418</v>
@@ -22131,10 +22242,10 @@
         <v>299</v>
       </c>
       <c r="BK90" s="22" t="s">
+        <v>789</v>
+      </c>
+      <c r="BL90" s="22" t="s">
         <v>791</v>
-      </c>
-      <c r="BL90" s="22" t="s">
-        <v>793</v>
       </c>
       <c r="BM90" s="22"/>
       <c r="BN90" s="22"/>
@@ -22155,10 +22266,10 @@
       </c>
       <c r="BZ90" s="49"/>
       <c r="CA90" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB90" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC90" s="22" t="s">
         <v>95</v>
@@ -22184,7 +22295,7 @@
       </c>
       <c r="CK90" s="18"/>
       <c r="CL90" s="21" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
     </row>
     <row r="91" spans="1:90" s="88" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22213,7 +22324,7 @@
         <v>15</v>
       </c>
       <c r="I91" s="18" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="J91" s="2">
         <v>29.1</v>
@@ -22243,7 +22354,7 @@
         <v>-61.56</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="T91" s="2">
         <v>19</v>
@@ -22255,7 +22366,7 @@
         <v>948</v>
       </c>
       <c r="W91" s="2">
-        <f>V91*2</f>
+        <f t="shared" si="0"/>
         <v>1896</v>
       </c>
       <c r="X91" s="18" t="s">
@@ -22271,7 +22382,7 @@
       <c r="AB91" s="18"/>
       <c r="AC91" s="18"/>
       <c r="AD91" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE91" s="18"/>
       <c r="AF91" s="18"/>
@@ -22300,7 +22411,7 @@
         <v>750</v>
       </c>
       <c r="AQ91" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AR91" s="14">
         <v>32</v>
@@ -22329,7 +22440,7 @@
         <v>757</v>
       </c>
       <c r="BH91" s="22" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="BI91" s="22" t="s">
         <v>418</v>
@@ -22338,10 +22449,10 @@
         <v>299</v>
       </c>
       <c r="BK91" s="22" t="s">
+        <v>789</v>
+      </c>
+      <c r="BL91" s="22" t="s">
         <v>791</v>
-      </c>
-      <c r="BL91" s="22" t="s">
-        <v>793</v>
       </c>
       <c r="BM91" s="22"/>
       <c r="BN91" s="22"/>
@@ -22362,10 +22473,10 @@
       </c>
       <c r="BZ91" s="49"/>
       <c r="CA91" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB91" s="49" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC91" s="22" t="s">
         <v>513</v>
@@ -22390,10 +22501,10 @@
         <v>196</v>
       </c>
       <c r="CK91" s="18" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="CL91" s="21" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
     </row>
     <row r="92" spans="1:90" s="88" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -22403,8 +22514,12 @@
       <c r="B92" s="165">
         <v>10</v>
       </c>
-      <c r="C92" s="164"/>
-      <c r="D92" s="14"/>
+      <c r="C92" s="164">
+        <v>20260310</v>
+      </c>
+      <c r="D92" s="14">
+        <v>20260331</v>
+      </c>
       <c r="E92" s="14" t="s">
         <v>13</v>
       </c>
@@ -22418,24 +22533,51 @@
         <v>15</v>
       </c>
       <c r="I92" s="18" t="s">
-        <v>843</v>
-      </c>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-      <c r="L92" s="14"/>
-      <c r="M92" s="14"/>
-      <c r="N92" s="100"/>
-      <c r="O92" s="18"/>
-      <c r="P92" s="18"/>
-      <c r="Q92" s="18"/>
-      <c r="R92" s="18"/>
+        <v>838</v>
+      </c>
+      <c r="J92" s="2">
+        <v>29.3</v>
+      </c>
+      <c r="K92" s="2">
+        <v>25.3</v>
+      </c>
+      <c r="L92" s="14">
+        <v>44.488900000000001</v>
+      </c>
+      <c r="M92" s="14">
+        <v>-63.447600000000001</v>
+      </c>
+      <c r="N92" s="100">
+        <v>0.55277777777777781</v>
+      </c>
+      <c r="O92" s="18">
+        <v>42.48</v>
+      </c>
+      <c r="P92" s="18">
+        <v>-63.45</v>
+      </c>
+      <c r="Q92" s="18">
+        <v>44.53</v>
+      </c>
+      <c r="R92" s="18">
+        <v>-61.41</v>
+      </c>
       <c r="S92" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="T92" s="2"/>
-      <c r="U92" s="2"/>
-      <c r="V92" s="2"/>
-      <c r="W92" s="2"/>
+      <c r="T92" s="2">
+        <v>21</v>
+      </c>
+      <c r="U92" s="2">
+        <v>599</v>
+      </c>
+      <c r="V92" s="2">
+        <v>1049</v>
+      </c>
+      <c r="W92" s="2">
+        <f t="shared" si="0"/>
+        <v>2098</v>
+      </c>
       <c r="X92" s="18" t="s">
         <v>36</v>
       </c>
@@ -22449,16 +22591,22 @@
       <c r="AB92" s="18"/>
       <c r="AC92" s="18"/>
       <c r="AD92" s="18" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE92" s="18"/>
       <c r="AF92" s="18"/>
       <c r="AG92" s="18"/>
       <c r="AH92" s="18"/>
       <c r="AI92" s="18"/>
-      <c r="AJ92" s="2"/>
-      <c r="AK92" s="2"/>
-      <c r="AL92" s="2"/>
+      <c r="AJ92" s="2">
+        <v>1</v>
+      </c>
+      <c r="AK92" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL92" s="2">
+        <v>0.5</v>
+      </c>
       <c r="AM92" s="2">
         <v>1024.9000000000001</v>
       </c>
@@ -22469,10 +22617,10 @@
         <v>2</v>
       </c>
       <c r="AP92" s="18" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="AQ92" s="18" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="AR92" s="14">
         <v>33</v>
@@ -22490,7 +22638,7 @@
         <v>79</v>
       </c>
       <c r="BC92" s="54" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="BD92" s="22" t="s">
         <v>459</v>
@@ -22501,7 +22649,7 @@
         <v>758</v>
       </c>
       <c r="BH92" s="22" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="BI92" s="22" t="s">
         <v>418</v>
@@ -22510,10 +22658,10 @@
         <v>299</v>
       </c>
       <c r="BK92" s="22" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="BL92" s="22" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="BM92" s="22"/>
       <c r="BN92" s="22"/>
@@ -22530,16 +22678,16 @@
         <v>228</v>
       </c>
       <c r="BY92" s="49" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="BZ92" s="49" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="CA92" s="49" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB92" s="49" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="CC92" s="22" t="s">
         <v>98</v>
@@ -22560,10 +22708,14 @@
       <c r="CI92" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ92" s="18"/>
-      <c r="CK92" s="18"/>
+      <c r="CJ92" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="CK92" s="18" t="s">
+        <v>862</v>
+      </c>
       <c r="CL92" s="21" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="93" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
@@ -22573,8 +22725,12 @@
       <c r="B93" s="136">
         <v>1</v>
       </c>
-      <c r="C93" s="35"/>
-      <c r="D93" s="35"/>
+      <c r="C93" s="35">
+        <v>20260331</v>
+      </c>
+      <c r="D93" s="35">
+        <v>20260423</v>
+      </c>
       <c r="E93" s="35" t="s">
         <v>53</v>
       </c>
@@ -22588,7 +22744,7 @@
         <v>15</v>
       </c>
       <c r="I93" s="37" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
@@ -22619,7 +22775,7 @@
       <c r="AB93" s="37"/>
       <c r="AC93" s="37"/>
       <c r="AD93" s="37" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AE93" s="37"/>
       <c r="AF93" s="37"/>
@@ -22633,7 +22789,7 @@
         <v>1024.9000000000001</v>
       </c>
       <c r="AN93" s="37">
-        <v>20260318</v>
+        <v>20260317</v>
       </c>
       <c r="AO93" s="37">
         <v>1</v>
@@ -22642,7 +22798,7 @@
         <v>750</v>
       </c>
       <c r="AQ93" s="37" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AR93" s="35">
         <v>32</v>
@@ -22671,7 +22827,7 @@
         <v>757</v>
       </c>
       <c r="BH93" s="38" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="BI93" s="38" t="s">
         <v>418</v>
@@ -22680,10 +22836,10 @@
         <v>299</v>
       </c>
       <c r="BK93" s="38" t="s">
+        <v>789</v>
+      </c>
+      <c r="BL93" s="38" t="s">
         <v>791</v>
-      </c>
-      <c r="BL93" s="38" t="s">
-        <v>793</v>
       </c>
       <c r="BM93" s="38"/>
       <c r="BN93" s="38"/>
@@ -22704,10 +22860,10 @@
       </c>
       <c r="BZ93" s="96"/>
       <c r="CA93" s="96" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="CB93" s="96" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="CC93" s="38" t="s">
         <v>245</v>
@@ -22721,28 +22877,42 @@
       <c r="CF93" s="3">
         <v>1272212</v>
       </c>
-      <c r="CG93" s="3"/>
+      <c r="CG93" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="CH93" s="3" t="s">
         <v>668</v>
       </c>
       <c r="CI93" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ93" s="37"/>
+      <c r="CJ93" s="37" t="s">
+        <v>899</v>
+      </c>
       <c r="CK93" s="37"/>
       <c r="CL93" s="43"/>
     </row>
     <row r="94" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="124"/>
-      <c r="B94" s="136"/>
+      <c r="A94" s="136">
+        <v>88</v>
+      </c>
+      <c r="B94" s="136">
+        <v>2</v>
+      </c>
       <c r="C94" s="35"/>
       <c r="D94" s="35"/>
       <c r="E94" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="35"/>
-      <c r="G94" s="35"/>
-      <c r="H94" s="35"/>
+        <v>35</v>
+      </c>
+      <c r="F94" s="35">
+        <v>94</v>
+      </c>
+      <c r="G94" s="35">
+        <v>4800994</v>
+      </c>
+      <c r="H94" s="35" t="s">
+        <v>887</v>
+      </c>
       <c r="I94" s="37"/>
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
@@ -22758,13 +22928,21 @@
       <c r="U94" s="3"/>
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
-      <c r="X94" s="37"/>
-      <c r="Y94" s="37"/>
+      <c r="X94" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y94" s="37">
+        <v>1</v>
+      </c>
       <c r="Z94" s="37"/>
-      <c r="AA94" s="37"/>
+      <c r="AA94" s="37" t="s">
+        <v>182</v>
+      </c>
       <c r="AB94" s="37"/>
       <c r="AC94" s="37"/>
-      <c r="AD94" s="37"/>
+      <c r="AD94" s="37" t="s">
+        <v>776</v>
+      </c>
       <c r="AE94" s="37"/>
       <c r="AF94" s="37"/>
       <c r="AG94" s="37"/>
@@ -22773,12 +22951,24 @@
       <c r="AJ94" s="3"/>
       <c r="AK94" s="3"/>
       <c r="AL94" s="3"/>
-      <c r="AM94" s="3"/>
-      <c r="AN94" s="37"/>
-      <c r="AO94" s="37"/>
-      <c r="AP94" s="37"/>
-      <c r="AQ94" s="37"/>
-      <c r="AR94" s="35"/>
+      <c r="AM94" s="3">
+        <v>1024.7</v>
+      </c>
+      <c r="AN94" s="37">
+        <v>20260414</v>
+      </c>
+      <c r="AO94" s="37">
+        <v>1</v>
+      </c>
+      <c r="AP94" s="37" t="s">
+        <v>839</v>
+      </c>
+      <c r="AQ94" s="37" t="s">
+        <v>782</v>
+      </c>
+      <c r="AR94" s="35">
+        <v>42</v>
+      </c>
       <c r="AS94" s="34"/>
       <c r="AT94" s="38"/>
       <c r="AU94" s="38"/>
@@ -22788,17 +22978,35 @@
       <c r="AY94" s="38"/>
       <c r="AZ94" s="38"/>
       <c r="BA94" s="38"/>
-      <c r="BB94" s="34"/>
-      <c r="BC94" s="38"/>
-      <c r="BD94" s="38"/>
+      <c r="BB94" s="34" t="s">
+        <v>888</v>
+      </c>
+      <c r="BC94" s="39">
+        <v>42691</v>
+      </c>
+      <c r="BD94" s="38" t="s">
+        <v>459</v>
+      </c>
       <c r="BE94" s="38"/>
       <c r="BF94" s="38"/>
-      <c r="BG94" s="38"/>
-      <c r="BH94" s="38"/>
-      <c r="BI94" s="38"/>
-      <c r="BJ94" s="38"/>
-      <c r="BK94" s="38"/>
-      <c r="BL94" s="38"/>
+      <c r="BG94" s="38" t="s">
+        <v>760</v>
+      </c>
+      <c r="BH94" s="38" t="s">
+        <v>772</v>
+      </c>
+      <c r="BI94" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="BJ94" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="BK94" s="38" t="s">
+        <v>769</v>
+      </c>
+      <c r="BL94" s="38" t="s">
+        <v>775</v>
+      </c>
       <c r="BM94" s="38"/>
       <c r="BN94" s="38"/>
       <c r="BO94" s="38"/>
@@ -22810,35 +23018,71 @@
       <c r="BU94" s="38"/>
       <c r="BV94" s="38"/>
       <c r="BW94" s="38"/>
-      <c r="BX94" s="34"/>
-      <c r="BY94" s="96"/>
-      <c r="BZ94" s="96"/>
+      <c r="BX94" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="BY94" s="96" t="s">
+        <v>829</v>
+      </c>
+      <c r="BZ94" s="96" t="s">
+        <v>889</v>
+      </c>
       <c r="CA94" s="96" t="s">
-        <v>850</v>
-      </c>
-      <c r="CB94" s="96"/>
-      <c r="CC94" s="38"/>
-      <c r="CD94" s="144"/>
-      <c r="CE94" s="38"/>
-      <c r="CF94" s="38"/>
-      <c r="CG94" s="3"/>
-      <c r="CH94" s="35"/>
-      <c r="CI94" s="35"/>
-      <c r="CJ94" s="37"/>
+        <v>845</v>
+      </c>
+      <c r="CB94" s="96" t="s">
+        <v>836</v>
+      </c>
+      <c r="CC94" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="CD94" s="38" t="s">
+        <v>800</v>
+      </c>
+      <c r="CE94" s="38" t="s">
+        <v>885</v>
+      </c>
+      <c r="CF94" s="40" t="s">
+        <v>700</v>
+      </c>
+      <c r="CG94" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="CH94" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="CI94" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="CJ94" s="37" t="s">
+        <v>900</v>
+      </c>
       <c r="CK94" s="37"/>
-      <c r="CL94" s="43"/>
+      <c r="CL94" s="43" t="s">
+        <v>890</v>
+      </c>
     </row>
     <row r="95" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="124"/>
-      <c r="B95" s="136"/>
+      <c r="A95" s="136">
+        <v>89</v>
+      </c>
+      <c r="B95" s="136">
+        <v>3</v>
+      </c>
       <c r="C95" s="35"/>
       <c r="D95" s="35"/>
       <c r="E95" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F95" s="35"/>
-      <c r="G95" s="35"/>
-      <c r="H95" s="35"/>
+      <c r="F95" s="35">
+        <v>89</v>
+      </c>
+      <c r="G95" s="35">
+        <v>4800926</v>
+      </c>
+      <c r="H95" s="35" t="s">
+        <v>887</v>
+      </c>
       <c r="I95" s="37"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
@@ -22854,13 +23098,21 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-      <c r="X95" s="37"/>
-      <c r="Y95" s="37"/>
+      <c r="X95" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y95" s="37">
+        <v>1</v>
+      </c>
       <c r="Z95" s="37"/>
-      <c r="AA95" s="37"/>
+      <c r="AA95" s="37" t="s">
+        <v>182</v>
+      </c>
       <c r="AB95" s="37"/>
       <c r="AC95" s="37"/>
-      <c r="AD95" s="37"/>
+      <c r="AD95" s="37" t="s">
+        <v>776</v>
+      </c>
       <c r="AE95" s="37"/>
       <c r="AF95" s="37"/>
       <c r="AG95" s="37"/>
@@ -22869,12 +23121,24 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
-      <c r="AM95" s="3"/>
-      <c r="AN95" s="37"/>
-      <c r="AO95" s="37"/>
-      <c r="AP95" s="37"/>
-      <c r="AQ95" s="37"/>
-      <c r="AR95" s="35"/>
+      <c r="AM95" s="3">
+        <v>1024.7</v>
+      </c>
+      <c r="AN95" s="37">
+        <v>20260414</v>
+      </c>
+      <c r="AO95" s="37">
+        <v>1</v>
+      </c>
+      <c r="AP95" s="37" t="s">
+        <v>839</v>
+      </c>
+      <c r="AQ95" s="37" t="s">
+        <v>782</v>
+      </c>
+      <c r="AR95" s="35">
+        <v>29</v>
+      </c>
       <c r="AS95" s="34"/>
       <c r="AT95" s="38"/>
       <c r="AU95" s="38"/>
@@ -22884,17 +23148,35 @@
       <c r="AY95" s="38"/>
       <c r="AZ95" s="38"/>
       <c r="BA95" s="38"/>
-      <c r="BB95" s="34"/>
-      <c r="BC95" s="38"/>
-      <c r="BD95" s="38"/>
+      <c r="BB95" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC95" s="38" t="s">
+        <v>751</v>
+      </c>
+      <c r="BD95" s="38" t="s">
+        <v>459</v>
+      </c>
       <c r="BE95" s="38"/>
       <c r="BF95" s="38"/>
-      <c r="BG95" s="38"/>
-      <c r="BH95" s="38"/>
-      <c r="BI95" s="38"/>
-      <c r="BJ95" s="38"/>
-      <c r="BK95" s="38"/>
-      <c r="BL95" s="38"/>
+      <c r="BG95" s="38" t="s">
+        <v>759</v>
+      </c>
+      <c r="BH95" s="38" t="s">
+        <v>780</v>
+      </c>
+      <c r="BI95" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="BJ95" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="BK95" s="38" t="s">
+        <v>768</v>
+      </c>
+      <c r="BL95" s="38" t="s">
+        <v>781</v>
+      </c>
       <c r="BM95" s="38"/>
       <c r="BN95" s="38"/>
       <c r="BO95" s="38"/>
@@ -22906,315 +23188,411 @@
       <c r="BU95" s="38"/>
       <c r="BV95" s="38"/>
       <c r="BW95" s="38"/>
-      <c r="BX95" s="34"/>
-      <c r="BY95" s="96"/>
-      <c r="BZ95" s="96"/>
+      <c r="BX95" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="BY95" s="96" t="s">
+        <v>829</v>
+      </c>
+      <c r="BZ95" s="96" t="s">
+        <v>889</v>
+      </c>
       <c r="CA95" s="96" t="s">
         <v>165</v>
       </c>
-      <c r="CB95" s="96"/>
-      <c r="CC95" s="38"/>
-      <c r="CD95" s="144"/>
-      <c r="CE95" s="38"/>
-      <c r="CF95" s="38"/>
-      <c r="CG95" s="3"/>
-      <c r="CH95" s="35"/>
-      <c r="CI95" s="35"/>
-      <c r="CJ95" s="37"/>
+      <c r="CB95" s="96" t="s">
+        <v>836</v>
+      </c>
+      <c r="CC95" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="CD95" s="40" t="s">
+        <v>747</v>
+      </c>
+      <c r="CE95" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="CF95" s="38" t="s">
+        <v>803</v>
+      </c>
+      <c r="CG95" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="CH95" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="CI95" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="CJ95" s="37" t="s">
+        <v>900</v>
+      </c>
       <c r="CK95" s="37"/>
-      <c r="CL95" s="43"/>
+      <c r="CL95" s="43" t="s">
+        <v>891</v>
+      </c>
     </row>
-    <row r="96" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C96" s="116"/>
-      <c r="D96" s="116"/>
-      <c r="E96" s="116"/>
-      <c r="F96" s="116"/>
-      <c r="G96" s="116"/>
-      <c r="H96" s="116"/>
-      <c r="I96" s="77"/>
-      <c r="L96" s="116"/>
-      <c r="M96" s="116"/>
-      <c r="O96" s="77"/>
-      <c r="P96" s="77"/>
-      <c r="Q96" s="77"/>
-      <c r="R96" s="77"/>
-      <c r="X96" s="77"/>
-      <c r="Y96" s="77"/>
-      <c r="Z96" s="77"/>
-      <c r="AA96" s="77"/>
-      <c r="AB96" s="77"/>
-      <c r="AC96" s="77"/>
-      <c r="AD96" s="77"/>
-      <c r="AE96" s="77"/>
-      <c r="AF96" s="77"/>
-      <c r="AG96" s="77"/>
-      <c r="AH96" s="77"/>
-      <c r="AI96" s="77"/>
-      <c r="AN96" s="77"/>
-      <c r="AO96" s="25" t="s">
-        <v>865</v>
-      </c>
-      <c r="AP96" s="77"/>
-      <c r="AQ96" s="77"/>
-      <c r="AR96" s="116"/>
-      <c r="AS96" s="27"/>
-      <c r="AT96" s="26"/>
-      <c r="AU96" s="78"/>
-      <c r="AV96" s="117"/>
-      <c r="AW96" s="27"/>
-      <c r="AX96" s="26"/>
-      <c r="AY96" s="78"/>
-      <c r="AZ96" s="78"/>
-      <c r="BA96" s="78"/>
-      <c r="BB96" s="117"/>
-      <c r="BC96" s="78"/>
-      <c r="BD96" s="78"/>
-      <c r="BE96" s="78"/>
-      <c r="BF96" s="145" t="s">
-        <v>762</v>
-      </c>
-      <c r="BG96" s="6" t="s">
-        <v>757</v>
-      </c>
-      <c r="BH96" s="78" t="s">
-        <v>775</v>
-      </c>
-      <c r="BI96" s="78"/>
-      <c r="BJ96" s="78"/>
-      <c r="BK96" s="78" t="s">
-        <v>791</v>
-      </c>
-      <c r="BL96" s="78"/>
-      <c r="BM96" s="78"/>
-      <c r="BN96" s="78"/>
-      <c r="BO96" s="78"/>
-      <c r="BP96" s="78"/>
-      <c r="BQ96" s="78"/>
-      <c r="BR96" s="78"/>
-      <c r="BS96" s="78"/>
-      <c r="BT96" s="78"/>
-      <c r="BU96" s="78"/>
-      <c r="BV96" s="78"/>
-      <c r="BW96" s="78"/>
-      <c r="BX96" s="117"/>
-      <c r="BY96" s="118" t="s">
+    <row r="96" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="136">
+        <v>90</v>
+      </c>
+      <c r="B96" s="136">
+        <v>4</v>
+      </c>
+      <c r="C96" s="35"/>
+      <c r="D96" s="35"/>
+      <c r="E96" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="169">
+        <v>151</v>
+      </c>
+      <c r="G96" s="35">
+        <v>4800925</v>
+      </c>
+      <c r="H96" s="35" t="s">
+        <v>887</v>
+      </c>
+      <c r="I96" s="37"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="35"/>
+      <c r="M96" s="35"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="37"/>
+      <c r="P96" s="37"/>
+      <c r="Q96" s="37"/>
+      <c r="R96" s="37"/>
+      <c r="S96" s="3"/>
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
+      <c r="X96" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y96" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z96" s="37"/>
+      <c r="AA96" s="37"/>
+      <c r="AB96" s="37"/>
+      <c r="AC96" s="37"/>
+      <c r="AD96" s="37" t="s">
+        <v>776</v>
+      </c>
+      <c r="AE96" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF96" s="37"/>
+      <c r="AG96" s="37"/>
+      <c r="AH96" s="37" t="s">
+        <v>299</v>
+      </c>
+      <c r="AI96" s="37" t="s">
+        <v>299</v>
+      </c>
+      <c r="AJ96" s="3"/>
+      <c r="AK96" s="3"/>
+      <c r="AL96" s="3"/>
+      <c r="AM96" s="3">
+        <v>1024.4000000000001</v>
+      </c>
+      <c r="AN96" s="37">
+        <v>20260421</v>
+      </c>
+      <c r="AO96" s="37">
+        <v>2</v>
+      </c>
+      <c r="AP96" s="37" t="s">
+        <v>839</v>
+      </c>
+      <c r="AQ96" s="37" t="s">
+        <v>782</v>
+      </c>
+      <c r="AR96" s="35">
+        <v>163</v>
+      </c>
+      <c r="AS96" s="34"/>
+      <c r="AT96" s="38"/>
+      <c r="AU96" s="38"/>
+      <c r="AV96" s="34"/>
+      <c r="AW96" s="34"/>
+      <c r="AX96" s="38"/>
+      <c r="AY96" s="38"/>
+      <c r="AZ96" s="38"/>
+      <c r="BA96" s="38"/>
+      <c r="BB96" s="34"/>
+      <c r="BC96" s="38"/>
+      <c r="BD96" s="38"/>
+      <c r="BE96" s="38"/>
+      <c r="BF96" s="38"/>
+      <c r="BG96" s="38" t="s">
+        <v>869</v>
+      </c>
+      <c r="BH96" s="38" t="s">
+        <v>892</v>
+      </c>
+      <c r="BI96" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="BJ96" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="BK96" s="46" t="s">
+        <v>870</v>
+      </c>
+      <c r="BL96" s="38" t="s">
+        <v>893</v>
+      </c>
+      <c r="BM96" s="38" t="s">
+        <v>894</v>
+      </c>
+      <c r="BN96" s="38" t="s">
+        <v>895</v>
+      </c>
+      <c r="BO96" s="38"/>
+      <c r="BP96" s="38"/>
+      <c r="BQ96" s="38"/>
+      <c r="BR96" s="38"/>
+      <c r="BS96" s="38"/>
+      <c r="BT96" s="38" t="s">
+        <v>871</v>
+      </c>
+      <c r="BU96" s="38" t="s">
+        <v>886</v>
+      </c>
+      <c r="BV96" s="38" t="s">
+        <v>873</v>
+      </c>
+      <c r="BW96" s="38" t="s">
+        <v>896</v>
+      </c>
+      <c r="BX96" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="BY96" s="96" t="s">
+        <v>829</v>
+      </c>
+      <c r="BZ96" s="49" t="s">
+        <v>858</v>
+      </c>
+      <c r="CA96" s="96" t="s">
+        <v>845</v>
+      </c>
+      <c r="CB96" s="96" t="s">
         <v>836</v>
       </c>
-      <c r="BZ96" s="118"/>
-      <c r="CA96" s="118"/>
-      <c r="CB96" s="118"/>
-      <c r="CC96" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="CD96" s="160" t="s">
-        <v>747</v>
-      </c>
-      <c r="CE96" s="40"/>
-      <c r="CF96" s="40"/>
-      <c r="CG96" s="44"/>
-      <c r="CH96" s="121"/>
-      <c r="CI96" s="45"/>
-      <c r="CJ96" s="77"/>
-      <c r="CK96" s="77" t="s">
-        <v>824</v>
-      </c>
-      <c r="CL96" s="119"/>
+      <c r="CC96" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="CD96" s="167" t="s">
+        <v>746</v>
+      </c>
+      <c r="CE96" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="CF96" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="CG96" s="3"/>
+      <c r="CH96" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="CI96" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="CJ96" s="37"/>
+      <c r="CK96" s="37"/>
+      <c r="CL96" s="43" t="s">
+        <v>898</v>
+      </c>
     </row>
-    <row r="97" spans="3:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C97" s="116"/>
-      <c r="D97" s="116"/>
-      <c r="E97" s="116"/>
-      <c r="F97" s="116"/>
-      <c r="G97" s="116"/>
-      <c r="H97" s="116"/>
-      <c r="I97" s="77"/>
-      <c r="L97" s="116"/>
-      <c r="M97" s="116"/>
-      <c r="O97" s="77"/>
-      <c r="P97" s="77"/>
-      <c r="Q97" s="77"/>
-      <c r="R97" s="77"/>
-      <c r="X97" s="77"/>
-      <c r="Y97" s="77"/>
-      <c r="Z97" s="77"/>
-      <c r="AA97" s="77"/>
-      <c r="AB97" s="77"/>
-      <c r="AC97" s="77"/>
-      <c r="AD97" s="77"/>
-      <c r="AE97" s="77"/>
-      <c r="AF97" s="77"/>
-      <c r="AG97" s="77"/>
-      <c r="AH97" s="77"/>
-      <c r="AI97" s="77"/>
-      <c r="AN97" s="77"/>
-      <c r="AO97" s="77"/>
-      <c r="AP97" s="77"/>
-      <c r="AQ97" s="77"/>
-      <c r="AR97" s="116"/>
-      <c r="AS97" s="27"/>
-      <c r="AT97" s="26"/>
-      <c r="AU97" s="78"/>
-      <c r="AV97" s="117"/>
-      <c r="AW97" s="27"/>
-      <c r="AX97" s="26"/>
-      <c r="AY97" s="78"/>
-      <c r="AZ97" s="78"/>
-      <c r="BA97" s="78"/>
-      <c r="BB97" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC97" s="26" t="s">
-        <v>751</v>
-      </c>
-      <c r="BD97" s="78" t="s">
-        <v>829</v>
-      </c>
-      <c r="BE97" s="78"/>
-      <c r="BF97" s="145"/>
-      <c r="BG97" s="6" t="s">
-        <v>758</v>
-      </c>
-      <c r="BH97" s="78" t="s">
-        <v>776</v>
-      </c>
-      <c r="BI97" s="78"/>
-      <c r="BJ97" s="78"/>
-      <c r="BK97" s="78" t="s">
-        <v>792</v>
-      </c>
-      <c r="BL97" s="78"/>
-      <c r="BM97" s="78"/>
-      <c r="BN97" s="78"/>
-      <c r="BO97" s="78"/>
-      <c r="BP97" s="78"/>
-      <c r="BQ97" s="78"/>
-      <c r="BR97" s="78"/>
-      <c r="BS97" s="78"/>
-      <c r="BT97" s="78"/>
-      <c r="BU97" s="78"/>
-      <c r="BV97" s="78"/>
-      <c r="BW97" s="78"/>
-      <c r="BX97" s="117"/>
-      <c r="BY97" s="118" t="s">
-        <v>837</v>
-      </c>
-      <c r="BZ97" s="118"/>
-      <c r="CA97" s="118"/>
-      <c r="CB97" s="118"/>
-      <c r="CC97" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="CD97" s="143" t="s">
-        <v>586</v>
-      </c>
+    <row r="97" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="136"/>
+      <c r="B97" s="136"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="35"/>
+      <c r="E97" s="35"/>
+      <c r="F97" s="35"/>
+      <c r="G97" s="35"/>
+      <c r="H97" s="35"/>
+      <c r="I97" s="37"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="35"/>
+      <c r="M97" s="35"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="37"/>
+      <c r="P97" s="37"/>
+      <c r="Q97" s="37"/>
+      <c r="R97" s="37"/>
+      <c r="S97" s="3"/>
+      <c r="T97" s="3"/>
+      <c r="U97" s="3"/>
+      <c r="V97" s="3"/>
+      <c r="W97" s="3"/>
+      <c r="X97" s="37"/>
+      <c r="Y97" s="37"/>
+      <c r="Z97" s="37"/>
+      <c r="AA97" s="37"/>
+      <c r="AB97" s="37"/>
+      <c r="AC97" s="37"/>
+      <c r="AD97" s="37"/>
+      <c r="AE97" s="37"/>
+      <c r="AF97" s="37"/>
+      <c r="AG97" s="37"/>
+      <c r="AH97" s="37"/>
+      <c r="AI97" s="37"/>
+      <c r="AJ97" s="3"/>
+      <c r="AK97" s="3"/>
+      <c r="AL97" s="3"/>
+      <c r="AM97" s="3"/>
+      <c r="AN97" s="37"/>
+      <c r="AO97" s="37"/>
+      <c r="AP97" s="37"/>
+      <c r="AQ97" s="37"/>
+      <c r="AR97" s="35"/>
+      <c r="AS97" s="34"/>
+      <c r="AT97" s="38"/>
+      <c r="AU97" s="38"/>
+      <c r="AV97" s="34"/>
+      <c r="AW97" s="34"/>
+      <c r="AX97" s="38"/>
+      <c r="AY97" s="38"/>
+      <c r="AZ97" s="38"/>
+      <c r="BA97" s="38"/>
+      <c r="BB97" s="34"/>
+      <c r="BC97" s="38"/>
+      <c r="BD97" s="38"/>
+      <c r="BE97" s="38"/>
+      <c r="BF97" s="38"/>
+      <c r="BG97" s="38"/>
+      <c r="BH97" s="38"/>
+      <c r="BI97" s="38"/>
+      <c r="BJ97" s="38"/>
+      <c r="BK97" s="38"/>
+      <c r="BL97" s="38"/>
+      <c r="BM97" s="38"/>
+      <c r="BN97" s="38"/>
+      <c r="BO97" s="38"/>
+      <c r="BP97" s="38"/>
+      <c r="BQ97" s="38"/>
+      <c r="BR97" s="38"/>
+      <c r="BS97" s="38"/>
+      <c r="BT97" s="38"/>
+      <c r="BU97" s="38"/>
+      <c r="BV97" s="38"/>
+      <c r="BW97" s="38"/>
+      <c r="BX97" s="34"/>
+      <c r="BY97" s="96"/>
+      <c r="BZ97" s="96"/>
+      <c r="CA97" s="96"/>
+      <c r="CB97" s="96"/>
+      <c r="CC97" s="38"/>
+      <c r="CD97" s="144"/>
       <c r="CE97" s="38"/>
       <c r="CF97" s="38"/>
       <c r="CG97" s="3"/>
-      <c r="CH97" s="120"/>
+      <c r="CH97" s="35"/>
       <c r="CI97" s="35"/>
-      <c r="CJ97" s="77"/>
-      <c r="CK97" s="77"/>
-      <c r="CL97" s="119"/>
+      <c r="CJ97" s="37"/>
+      <c r="CK97" s="37"/>
+      <c r="CL97" s="43"/>
     </row>
-    <row r="98" spans="3:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="116"/>
-      <c r="D98" s="116"/>
-      <c r="E98" s="116"/>
-      <c r="F98" s="116"/>
-      <c r="G98" s="116"/>
-      <c r="H98" s="116"/>
-      <c r="I98" s="77"/>
-      <c r="L98" s="116"/>
-      <c r="M98" s="116"/>
-      <c r="O98" s="77"/>
-      <c r="P98" s="77"/>
-      <c r="Q98" s="77"/>
-      <c r="R98" s="77"/>
-      <c r="X98" s="77"/>
-      <c r="Y98" s="77"/>
-      <c r="Z98" s="77"/>
-      <c r="AA98" s="77"/>
-      <c r="AB98" s="77"/>
-      <c r="AC98" s="77"/>
-      <c r="AD98" s="77"/>
-      <c r="AE98" s="77"/>
-      <c r="AF98" s="77"/>
-      <c r="AG98" s="77"/>
-      <c r="AH98" s="77"/>
-      <c r="AI98" s="77"/>
-      <c r="AN98" s="77"/>
-      <c r="AO98" s="77"/>
-      <c r="AP98" s="77"/>
-      <c r="AQ98" s="77"/>
-      <c r="AR98" s="116"/>
-      <c r="AS98" s="117"/>
-      <c r="AT98" s="78"/>
-      <c r="AU98" s="78"/>
-      <c r="AV98" s="117"/>
-      <c r="AW98" s="117"/>
-      <c r="AX98" s="78"/>
-      <c r="AY98" s="78"/>
-      <c r="AZ98" s="78"/>
-      <c r="BA98" s="78"/>
-      <c r="BB98" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="BC98" s="26" t="s">
-        <v>830</v>
-      </c>
-      <c r="BD98" s="78" t="s">
-        <v>832</v>
-      </c>
-      <c r="BE98" s="78"/>
-      <c r="BF98" s="145" t="s">
-        <v>761</v>
-      </c>
-      <c r="BG98" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="BH98" s="78" t="s">
-        <v>775</v>
-      </c>
-      <c r="BI98" s="78"/>
-      <c r="BJ98" s="78"/>
-      <c r="BK98" s="78" t="s">
-        <v>770</v>
-      </c>
-      <c r="BL98" s="78" t="s">
-        <v>819</v>
-      </c>
-      <c r="BM98" s="78"/>
-      <c r="BN98" s="78"/>
-      <c r="BO98" s="78"/>
-      <c r="BP98" s="78"/>
-      <c r="BQ98" s="78"/>
-      <c r="BR98" s="78"/>
-      <c r="BS98" s="78"/>
-      <c r="BT98" s="78"/>
-      <c r="BU98" s="78"/>
-      <c r="BV98" s="78"/>
-      <c r="BW98" s="78"/>
-      <c r="BX98" s="117"/>
-      <c r="BY98" s="118"/>
-      <c r="BZ98" s="118"/>
-      <c r="CA98" s="118"/>
-      <c r="CB98" s="118"/>
-      <c r="CC98" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="CD98" s="144" t="s">
-        <v>803</v>
-      </c>
-      <c r="CE98" s="133"/>
-      <c r="CF98" s="133"/>
-      <c r="CG98" s="134"/>
-      <c r="CH98" s="135"/>
-      <c r="CI98" s="29"/>
-      <c r="CJ98" s="77"/>
-      <c r="CK98" s="77"/>
-      <c r="CL98" s="119"/>
+    <row r="98" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="136"/>
+      <c r="B98" s="136"/>
+      <c r="C98" s="35"/>
+      <c r="D98" s="35"/>
+      <c r="E98" s="35"/>
+      <c r="F98" s="35"/>
+      <c r="G98" s="35"/>
+      <c r="H98" s="35"/>
+      <c r="I98" s="37"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="35"/>
+      <c r="M98" s="35"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="37"/>
+      <c r="P98" s="37"/>
+      <c r="Q98" s="37"/>
+      <c r="R98" s="37"/>
+      <c r="S98" s="3"/>
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3"/>
+      <c r="W98" s="3"/>
+      <c r="X98" s="37"/>
+      <c r="Y98" s="37"/>
+      <c r="Z98" s="37"/>
+      <c r="AA98" s="37"/>
+      <c r="AB98" s="37"/>
+      <c r="AC98" s="37"/>
+      <c r="AD98" s="37"/>
+      <c r="AE98" s="37"/>
+      <c r="AF98" s="37"/>
+      <c r="AG98" s="37"/>
+      <c r="AH98" s="37"/>
+      <c r="AI98" s="37"/>
+      <c r="AJ98" s="3"/>
+      <c r="AK98" s="3"/>
+      <c r="AL98" s="3"/>
+      <c r="AM98" s="3"/>
+      <c r="AN98" s="37"/>
+      <c r="AO98" s="37"/>
+      <c r="AP98" s="37"/>
+      <c r="AQ98" s="37"/>
+      <c r="AR98" s="35"/>
+      <c r="AS98" s="34"/>
+      <c r="AT98" s="38"/>
+      <c r="AU98" s="38"/>
+      <c r="AV98" s="34"/>
+      <c r="AW98" s="34"/>
+      <c r="AX98" s="38"/>
+      <c r="AY98" s="38"/>
+      <c r="AZ98" s="38"/>
+      <c r="BA98" s="38"/>
+      <c r="BB98" s="34"/>
+      <c r="BC98" s="38"/>
+      <c r="BD98" s="38"/>
+      <c r="BE98" s="38"/>
+      <c r="BF98" s="38"/>
+      <c r="BG98" s="38"/>
+      <c r="BH98" s="38"/>
+      <c r="BI98" s="38"/>
+      <c r="BJ98" s="38"/>
+      <c r="BK98" s="38"/>
+      <c r="BL98" s="38"/>
+      <c r="BM98" s="38"/>
+      <c r="BN98" s="38"/>
+      <c r="BO98" s="38"/>
+      <c r="BP98" s="38"/>
+      <c r="BQ98" s="38"/>
+      <c r="BR98" s="38"/>
+      <c r="BS98" s="38"/>
+      <c r="BT98" s="38"/>
+      <c r="BU98" s="38"/>
+      <c r="BV98" s="38"/>
+      <c r="BW98" s="38"/>
+      <c r="BX98" s="34"/>
+      <c r="BY98" s="96"/>
+      <c r="BZ98" s="96"/>
+      <c r="CA98" s="96"/>
+      <c r="CB98" s="96"/>
+      <c r="CC98" s="38"/>
+      <c r="CD98" s="144"/>
+      <c r="CE98" s="38"/>
+      <c r="CF98" s="38"/>
+      <c r="CG98" s="3"/>
+      <c r="CH98" s="35"/>
+      <c r="CI98" s="35"/>
+      <c r="CJ98" s="37"/>
+      <c r="CK98" s="37"/>
+      <c r="CL98" s="43"/>
     </row>
-    <row r="99" spans="3:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C99" s="116"/>
       <c r="D99" s="116"/>
       <c r="E99" s="116"/>
@@ -23241,44 +23619,40 @@
       <c r="AH99" s="77"/>
       <c r="AI99" s="77"/>
       <c r="AN99" s="77"/>
-      <c r="AO99" s="77"/>
+      <c r="AO99" s="25" t="s">
+        <v>859</v>
+      </c>
       <c r="AP99" s="77"/>
       <c r="AQ99" s="77"/>
       <c r="AR99" s="116"/>
-      <c r="AS99" s="117"/>
-      <c r="AT99" s="78"/>
+      <c r="AS99" s="27"/>
+      <c r="AT99" s="26"/>
       <c r="AU99" s="78"/>
       <c r="AV99" s="117"/>
-      <c r="AW99" s="117"/>
-      <c r="AX99" s="78"/>
+      <c r="AW99" s="27"/>
+      <c r="AX99" s="26"/>
       <c r="AY99" s="78"/>
       <c r="AZ99" s="78"/>
       <c r="BA99" s="78"/>
-      <c r="BB99" s="117" t="s">
-        <v>79</v>
-      </c>
-      <c r="BC99" s="26" t="s">
-        <v>831</v>
-      </c>
-      <c r="BD99" s="78" t="s">
-        <v>832</v>
-      </c>
+      <c r="BB99" s="117"/>
+      <c r="BC99" s="78"/>
+      <c r="BD99" s="78"/>
       <c r="BE99" s="78"/>
-      <c r="BF99" s="78"/>
-      <c r="BG99" s="5" t="s">
-        <v>760</v>
+      <c r="BF99" s="145" t="s">
+        <v>762</v>
+      </c>
+      <c r="BG99" s="6" t="s">
+        <v>757</v>
       </c>
       <c r="BH99" s="78" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="BI99" s="78"/>
       <c r="BJ99" s="78"/>
-      <c r="BK99" s="78" t="s">
-        <v>771</v>
-      </c>
-      <c r="BL99" s="78" t="s">
-        <v>805</v>
-      </c>
+      <c r="BK99" s="168" t="s">
+        <v>789</v>
+      </c>
+      <c r="BL99" s="78"/>
       <c r="BM99" s="78"/>
       <c r="BN99" s="78"/>
       <c r="BO99" s="78"/>
@@ -23291,26 +23665,32 @@
       <c r="BV99" s="78"/>
       <c r="BW99" s="78"/>
       <c r="BX99" s="117"/>
-      <c r="BY99" s="118"/>
+      <c r="BY99" s="118" t="s">
+        <v>831</v>
+      </c>
       <c r="BZ99" s="118"/>
       <c r="CA99" s="118"/>
       <c r="CB99" s="118"/>
-      <c r="CC99" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="CD99" s="144" t="s">
-        <v>746</v>
-      </c>
-      <c r="CE99" s="38"/>
-      <c r="CF99" s="38"/>
-      <c r="CG99" s="3"/>
-      <c r="CH99" s="29"/>
-      <c r="CI99" s="93"/>
+      <c r="CC99" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="CD99" s="160" t="s">
+        <v>747</v>
+      </c>
+      <c r="CE99" s="40" t="s">
+        <v>885</v>
+      </c>
+      <c r="CF99" s="40"/>
+      <c r="CG99" s="44"/>
+      <c r="CH99" s="121"/>
+      <c r="CI99" s="45"/>
       <c r="CJ99" s="77"/>
-      <c r="CK99" s="77"/>
+      <c r="CK99" s="77" t="s">
+        <v>820</v>
+      </c>
       <c r="CL99" s="119"/>
     </row>
-    <row r="100" spans="3:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C100" s="116"/>
       <c r="D100" s="116"/>
       <c r="E100" s="116"/>
@@ -23340,26 +23720,40 @@
       <c r="AO100" s="77"/>
       <c r="AP100" s="77"/>
       <c r="AQ100" s="77"/>
-      <c r="AR100" s="116"/>
-      <c r="AS100" s="117"/>
-      <c r="AT100" s="78"/>
+      <c r="AR100" s="116">
+        <v>161</v>
+      </c>
+      <c r="AS100" s="27"/>
+      <c r="AT100" s="26"/>
       <c r="AU100" s="78"/>
       <c r="AV100" s="117"/>
-      <c r="AW100" s="117"/>
-      <c r="AX100" s="78"/>
+      <c r="AW100" s="27"/>
+      <c r="AX100" s="26"/>
       <c r="AY100" s="78"/>
       <c r="AZ100" s="78"/>
       <c r="BA100" s="78"/>
-      <c r="BB100" s="117"/>
-      <c r="BC100" s="78"/>
-      <c r="BD100" s="78"/>
+      <c r="BB100" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC100" s="26" t="s">
+        <v>751</v>
+      </c>
+      <c r="BD100" s="78" t="s">
+        <v>825</v>
+      </c>
       <c r="BE100" s="78"/>
-      <c r="BF100" s="78"/>
-      <c r="BG100" s="78"/>
-      <c r="BH100" s="78"/>
+      <c r="BF100" s="145"/>
+      <c r="BG100" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="BH100" s="78" t="s">
+        <v>774</v>
+      </c>
       <c r="BI100" s="78"/>
       <c r="BJ100" s="78"/>
-      <c r="BK100" s="78"/>
+      <c r="BK100" s="168" t="s">
+        <v>790</v>
+      </c>
       <c r="BL100" s="78"/>
       <c r="BM100" s="78"/>
       <c r="BN100" s="78"/>
@@ -23373,26 +23767,28 @@
       <c r="BV100" s="78"/>
       <c r="BW100" s="78"/>
       <c r="BX100" s="117"/>
-      <c r="BY100" s="118"/>
+      <c r="BY100" s="118" t="s">
+        <v>832</v>
+      </c>
       <c r="BZ100" s="118"/>
       <c r="CA100" s="118"/>
       <c r="CB100" s="118"/>
       <c r="CC100" s="38" t="s">
-        <v>513</v>
+        <v>95</v>
       </c>
       <c r="CD100" s="143" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="CE100" s="38"/>
       <c r="CF100" s="38"/>
       <c r="CG100" s="3"/>
-      <c r="CH100" s="29"/>
-      <c r="CI100" s="29"/>
+      <c r="CH100" s="120"/>
+      <c r="CI100" s="35"/>
       <c r="CJ100" s="77"/>
       <c r="CK100" s="77"/>
       <c r="CL100" s="119"/>
     </row>
-    <row r="101" spans="3:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C101" s="116"/>
       <c r="D101" s="116"/>
       <c r="E101" s="116"/>
@@ -23422,7 +23818,9 @@
       <c r="AO101" s="77"/>
       <c r="AP101" s="77"/>
       <c r="AQ101" s="77"/>
-      <c r="AR101" s="116"/>
+      <c r="AR101" s="116">
+        <v>162</v>
+      </c>
       <c r="AS101" s="117"/>
       <c r="AT101" s="78"/>
       <c r="AU101" s="78"/>
@@ -23432,17 +23830,27 @@
       <c r="AY101" s="78"/>
       <c r="AZ101" s="78"/>
       <c r="BA101" s="78"/>
-      <c r="BB101" s="117"/>
-      <c r="BC101" s="78"/>
+      <c r="BB101" s="27"/>
+      <c r="BC101" s="26"/>
       <c r="BD101" s="78"/>
       <c r="BE101" s="78"/>
-      <c r="BF101" s="78"/>
-      <c r="BG101" s="78"/>
-      <c r="BH101" s="78"/>
+      <c r="BF101" s="145" t="s">
+        <v>761</v>
+      </c>
+      <c r="BG101" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="BH101" s="78" t="s">
+        <v>773</v>
+      </c>
       <c r="BI101" s="78"/>
       <c r="BJ101" s="78"/>
-      <c r="BK101" s="78"/>
-      <c r="BL101" s="78"/>
+      <c r="BK101" s="168" t="s">
+        <v>768</v>
+      </c>
+      <c r="BL101" s="78" t="s">
+        <v>815</v>
+      </c>
       <c r="BM101" s="78"/>
       <c r="BN101" s="78"/>
       <c r="BO101" s="78"/>
@@ -23460,21 +23868,21 @@
       <c r="CA101" s="118"/>
       <c r="CB101" s="118"/>
       <c r="CC101" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="CD101" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="CE101" s="46"/>
-      <c r="CF101" s="46"/>
-      <c r="CG101" s="48"/>
-      <c r="CH101" s="29"/>
+        <v>117</v>
+      </c>
+      <c r="CD101" s="144" t="s">
+        <v>800</v>
+      </c>
+      <c r="CE101" s="133"/>
+      <c r="CF101" s="133"/>
+      <c r="CG101" s="134"/>
+      <c r="CH101" s="135"/>
       <c r="CI101" s="29"/>
       <c r="CJ101" s="77"/>
       <c r="CK101" s="77"/>
       <c r="CL101" s="119"/>
     </row>
-    <row r="102" spans="3:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C102" s="116"/>
       <c r="D102" s="116"/>
       <c r="E102" s="116"/>
@@ -23504,7 +23912,9 @@
       <c r="AO102" s="77"/>
       <c r="AP102" s="77"/>
       <c r="AQ102" s="77"/>
-      <c r="AR102" s="116"/>
+      <c r="AR102" s="116" t="s">
+        <v>874</v>
+      </c>
       <c r="AS102" s="117"/>
       <c r="AT102" s="78"/>
       <c r="AU102" s="78"/>
@@ -23514,17 +23924,31 @@
       <c r="AY102" s="78"/>
       <c r="AZ102" s="78"/>
       <c r="BA102" s="78"/>
-      <c r="BB102" s="117"/>
-      <c r="BC102" s="78"/>
-      <c r="BD102" s="78"/>
+      <c r="BB102" s="117" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC102" s="26" t="s">
+        <v>826</v>
+      </c>
+      <c r="BD102" s="78" t="s">
+        <v>827</v>
+      </c>
       <c r="BE102" s="78"/>
       <c r="BF102" s="78"/>
-      <c r="BG102" s="78"/>
-      <c r="BH102" s="78"/>
+      <c r="BG102" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="BH102" s="78" t="s">
+        <v>774</v>
+      </c>
       <c r="BI102" s="78"/>
       <c r="BJ102" s="78"/>
-      <c r="BK102" s="78"/>
-      <c r="BL102" s="78"/>
+      <c r="BK102" s="168" t="s">
+        <v>769</v>
+      </c>
+      <c r="BL102" s="78" t="s">
+        <v>802</v>
+      </c>
       <c r="BM102" s="78"/>
       <c r="BN102" s="78"/>
       <c r="BO102" s="78"/>
@@ -23541,21 +23965,22 @@
       <c r="BZ102" s="118"/>
       <c r="CA102" s="118"/>
       <c r="CB102" s="118"/>
-      <c r="CC102" s="46" t="s">
-        <v>846</v>
-      </c>
-      <c r="CD102" s="159" t="s">
-        <v>845</v>
-      </c>
-      <c r="CE102" s="78"/>
-      <c r="CF102" s="78"/>
-      <c r="CH102" s="116"/>
-      <c r="CI102" s="116"/>
+      <c r="CC102" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="CD102" s="144" t="s">
+        <v>746</v>
+      </c>
+      <c r="CE102" s="38"/>
+      <c r="CF102" s="38"/>
+      <c r="CG102" s="3"/>
+      <c r="CH102" s="29"/>
+      <c r="CI102" s="93"/>
       <c r="CJ102" s="77"/>
       <c r="CK102" s="77"/>
       <c r="CL102" s="119"/>
     </row>
-    <row r="103" spans="3:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C103" s="116"/>
       <c r="D103" s="116"/>
       <c r="E103" s="116"/>
@@ -23599,42 +24024,321 @@
       <c r="BC103" s="78"/>
       <c r="BD103" s="78"/>
       <c r="BE103" s="78"/>
-      <c r="BF103" s="78"/>
-      <c r="BG103" s="78"/>
+      <c r="BF103" s="78" t="s">
+        <v>868</v>
+      </c>
+      <c r="BG103" s="78" t="s">
+        <v>869</v>
+      </c>
       <c r="BH103" s="78"/>
       <c r="BI103" s="78"/>
       <c r="BJ103" s="78"/>
-      <c r="BK103" s="78"/>
+      <c r="BK103" s="168" t="s">
+        <v>870</v>
+      </c>
       <c r="BL103" s="78"/>
-      <c r="BM103" s="78"/>
+      <c r="BM103" s="78" t="s">
+        <v>872</v>
+      </c>
       <c r="BN103" s="78"/>
       <c r="BO103" s="78"/>
       <c r="BP103" s="78"/>
       <c r="BQ103" s="78"/>
       <c r="BR103" s="78"/>
       <c r="BS103" s="78"/>
-      <c r="BT103" s="78"/>
-      <c r="BU103" s="78"/>
-      <c r="BV103" s="78"/>
+      <c r="BT103" s="78" t="s">
+        <v>871</v>
+      </c>
+      <c r="BU103" s="78" t="s">
+        <v>886</v>
+      </c>
+      <c r="BV103" s="78" t="s">
+        <v>873</v>
+      </c>
       <c r="BW103" s="78"/>
       <c r="BX103" s="117"/>
       <c r="BY103" s="118"/>
       <c r="BZ103" s="118"/>
       <c r="CA103" s="118"/>
       <c r="CB103" s="118"/>
-      <c r="CC103" s="142">
-        <v>286370</v>
-      </c>
-      <c r="CD103" s="162" t="s">
-        <v>847</v>
-      </c>
-      <c r="CE103" s="78"/>
-      <c r="CF103" s="78"/>
-      <c r="CH103" s="116"/>
-      <c r="CI103" s="116"/>
+      <c r="CC103" s="38" t="s">
+        <v>513</v>
+      </c>
+      <c r="CD103" s="143" t="s">
+        <v>514</v>
+      </c>
+      <c r="CE103" s="38"/>
+      <c r="CF103" s="38"/>
+      <c r="CG103" s="3"/>
+      <c r="CH103" s="29"/>
+      <c r="CI103" s="29"/>
       <c r="CJ103" s="77"/>
       <c r="CK103" s="77"/>
       <c r="CL103" s="119"/>
+    </row>
+    <row r="104" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C104" s="116"/>
+      <c r="D104" s="116"/>
+      <c r="E104" s="116"/>
+      <c r="F104" s="116"/>
+      <c r="G104" s="116"/>
+      <c r="H104" s="116"/>
+      <c r="I104" s="77"/>
+      <c r="L104" s="116"/>
+      <c r="M104" s="116"/>
+      <c r="O104" s="77"/>
+      <c r="P104" s="77"/>
+      <c r="Q104" s="77"/>
+      <c r="R104" s="77"/>
+      <c r="X104" s="77"/>
+      <c r="Y104" s="77"/>
+      <c r="Z104" s="77"/>
+      <c r="AA104" s="77"/>
+      <c r="AB104" s="77"/>
+      <c r="AC104" s="77"/>
+      <c r="AD104" s="77"/>
+      <c r="AE104" s="77"/>
+      <c r="AF104" s="77"/>
+      <c r="AG104" s="77"/>
+      <c r="AH104" s="77"/>
+      <c r="AI104" s="77"/>
+      <c r="AN104" s="77"/>
+      <c r="AO104" s="77"/>
+      <c r="AP104" s="77"/>
+      <c r="AQ104" s="77"/>
+      <c r="AR104" s="116"/>
+      <c r="AS104" s="117"/>
+      <c r="AT104" s="78"/>
+      <c r="AU104" s="78"/>
+      <c r="AV104" s="117"/>
+      <c r="AW104" s="117"/>
+      <c r="AX104" s="78"/>
+      <c r="AY104" s="78"/>
+      <c r="AZ104" s="78"/>
+      <c r="BA104" s="78"/>
+      <c r="BB104" s="117"/>
+      <c r="BC104" s="78"/>
+      <c r="BD104" s="78"/>
+      <c r="BE104" s="78"/>
+      <c r="BF104" s="78" t="s">
+        <v>875</v>
+      </c>
+      <c r="BG104" s="78" t="s">
+        <v>877</v>
+      </c>
+      <c r="BH104" s="78"/>
+      <c r="BI104" s="78"/>
+      <c r="BJ104" s="78"/>
+      <c r="BK104" s="168" t="s">
+        <v>878</v>
+      </c>
+      <c r="BL104" s="78"/>
+      <c r="BM104" s="78" t="s">
+        <v>879</v>
+      </c>
+      <c r="BN104" s="78"/>
+      <c r="BO104" s="78" t="s">
+        <v>880</v>
+      </c>
+      <c r="BP104" s="78"/>
+      <c r="BQ104" s="78"/>
+      <c r="BR104" s="78"/>
+      <c r="BS104" s="78"/>
+      <c r="BT104" s="78"/>
+      <c r="BU104" s="78"/>
+      <c r="BV104" s="78"/>
+      <c r="BW104" s="78"/>
+      <c r="BX104" s="117"/>
+      <c r="BY104" s="118"/>
+      <c r="BZ104" s="118"/>
+      <c r="CA104" s="118"/>
+      <c r="CB104" s="118"/>
+      <c r="CC104" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="CD104" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="CE104" s="46"/>
+      <c r="CF104" s="46"/>
+      <c r="CG104" s="48"/>
+      <c r="CH104" s="29"/>
+      <c r="CI104" s="29"/>
+      <c r="CJ104" s="77"/>
+      <c r="CK104" s="77"/>
+      <c r="CL104" s="119"/>
+    </row>
+    <row r="105" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C105" s="116"/>
+      <c r="D105" s="116"/>
+      <c r="E105" s="116"/>
+      <c r="F105" s="116"/>
+      <c r="G105" s="116"/>
+      <c r="H105" s="116"/>
+      <c r="I105" s="77"/>
+      <c r="L105" s="116"/>
+      <c r="M105" s="116"/>
+      <c r="O105" s="77"/>
+      <c r="P105" s="77"/>
+      <c r="Q105" s="77"/>
+      <c r="R105" s="77"/>
+      <c r="X105" s="77"/>
+      <c r="Y105" s="77"/>
+      <c r="Z105" s="77"/>
+      <c r="AA105" s="77"/>
+      <c r="AB105" s="77"/>
+      <c r="AC105" s="77"/>
+      <c r="AD105" s="77"/>
+      <c r="AE105" s="77"/>
+      <c r="AF105" s="77"/>
+      <c r="AG105" s="77"/>
+      <c r="AH105" s="77"/>
+      <c r="AI105" s="77"/>
+      <c r="AN105" s="77"/>
+      <c r="AO105" s="77"/>
+      <c r="AP105" s="77"/>
+      <c r="AQ105" s="77"/>
+      <c r="AR105" s="116"/>
+      <c r="AS105" s="117"/>
+      <c r="AT105" s="78"/>
+      <c r="AU105" s="78"/>
+      <c r="AV105" s="117"/>
+      <c r="AW105" s="117"/>
+      <c r="AX105" s="78"/>
+      <c r="AY105" s="78"/>
+      <c r="AZ105" s="78"/>
+      <c r="BA105" s="78"/>
+      <c r="BB105" s="117"/>
+      <c r="BC105" s="78"/>
+      <c r="BD105" s="78"/>
+      <c r="BE105" s="78"/>
+      <c r="BF105" s="78" t="s">
+        <v>876</v>
+      </c>
+      <c r="BG105" s="78" t="s">
+        <v>884</v>
+      </c>
+      <c r="BH105" s="78"/>
+      <c r="BI105" s="78"/>
+      <c r="BJ105" s="78"/>
+      <c r="BK105" s="168" t="s">
+        <v>882</v>
+      </c>
+      <c r="BL105" s="78"/>
+      <c r="BM105" s="78" t="s">
+        <v>883</v>
+      </c>
+      <c r="BN105" s="78"/>
+      <c r="BO105" s="78" t="s">
+        <v>881</v>
+      </c>
+      <c r="BP105" s="78"/>
+      <c r="BQ105" s="78"/>
+      <c r="BR105" s="78"/>
+      <c r="BS105" s="78"/>
+      <c r="BT105" s="78"/>
+      <c r="BU105" s="78"/>
+      <c r="BV105" s="78"/>
+      <c r="BW105" s="78"/>
+      <c r="BX105" s="117"/>
+      <c r="BY105" s="118"/>
+      <c r="BZ105" s="118"/>
+      <c r="CA105" s="118"/>
+      <c r="CB105" s="118"/>
+      <c r="CC105" s="46" t="s">
+        <v>841</v>
+      </c>
+      <c r="CD105" s="159" t="s">
+        <v>840</v>
+      </c>
+      <c r="CE105" s="78"/>
+      <c r="CF105" s="78"/>
+      <c r="CH105" s="116"/>
+      <c r="CI105" s="116"/>
+      <c r="CJ105" s="77"/>
+      <c r="CK105" s="77"/>
+      <c r="CL105" s="119"/>
+    </row>
+    <row r="106" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C106" s="116"/>
+      <c r="D106" s="116"/>
+      <c r="E106" s="116"/>
+      <c r="F106" s="116"/>
+      <c r="G106" s="116"/>
+      <c r="H106" s="116"/>
+      <c r="I106" s="77"/>
+      <c r="L106" s="116"/>
+      <c r="M106" s="116"/>
+      <c r="O106" s="77"/>
+      <c r="P106" s="77"/>
+      <c r="Q106" s="77"/>
+      <c r="R106" s="77"/>
+      <c r="X106" s="77"/>
+      <c r="Y106" s="77"/>
+      <c r="Z106" s="77"/>
+      <c r="AA106" s="77"/>
+      <c r="AB106" s="77"/>
+      <c r="AC106" s="77"/>
+      <c r="AD106" s="77"/>
+      <c r="AE106" s="77"/>
+      <c r="AF106" s="77"/>
+      <c r="AG106" s="77"/>
+      <c r="AH106" s="77"/>
+      <c r="AI106" s="77"/>
+      <c r="AN106" s="77"/>
+      <c r="AO106" s="77"/>
+      <c r="AP106" s="77"/>
+      <c r="AQ106" s="77"/>
+      <c r="AR106" s="116"/>
+      <c r="AS106" s="117"/>
+      <c r="AT106" s="78"/>
+      <c r="AU106" s="78"/>
+      <c r="AV106" s="117"/>
+      <c r="AW106" s="117"/>
+      <c r="AX106" s="78"/>
+      <c r="AY106" s="78"/>
+      <c r="AZ106" s="78"/>
+      <c r="BA106" s="78"/>
+      <c r="BB106" s="117"/>
+      <c r="BC106" s="78"/>
+      <c r="BD106" s="78"/>
+      <c r="BE106" s="78"/>
+      <c r="BF106" s="78"/>
+      <c r="BG106" s="78"/>
+      <c r="BH106" s="78"/>
+      <c r="BI106" s="78"/>
+      <c r="BJ106" s="78"/>
+      <c r="BK106" s="78"/>
+      <c r="BL106" s="78"/>
+      <c r="BM106" s="78"/>
+      <c r="BN106" s="78"/>
+      <c r="BO106" s="78"/>
+      <c r="BP106" s="78"/>
+      <c r="BQ106" s="78"/>
+      <c r="BR106" s="78"/>
+      <c r="BS106" s="78"/>
+      <c r="BT106" s="78"/>
+      <c r="BU106" s="78"/>
+      <c r="BV106" s="78"/>
+      <c r="BW106" s="78"/>
+      <c r="BX106" s="117"/>
+      <c r="BY106" s="118"/>
+      <c r="BZ106" s="118"/>
+      <c r="CA106" s="118"/>
+      <c r="CB106" s="118"/>
+      <c r="CC106" s="142">
+        <v>286370</v>
+      </c>
+      <c r="CD106" s="162" t="s">
+        <v>842</v>
+      </c>
+      <c r="CE106" s="78"/>
+      <c r="CF106" s="78"/>
+      <c r="CH106" s="116"/>
+      <c r="CI106" s="116"/>
+      <c r="CJ106" s="77"/>
+      <c r="CK106" s="77"/>
+      <c r="CL106" s="119"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
@@ -24901,10 +25605,10 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="C2" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24912,13 +25616,13 @@
     </row>
     <row r="4" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="155" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="C4" s="152" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="D4" s="152" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="E4" s="31" t="s">
         <v>22</v>
@@ -25127,7 +25831,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>

--- a/GliderMission.xlsx
+++ b/GliderMission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ent.dfo-mpo.ca\dfo-mpo\GROUP\MAR\BIO\EOS\OESD\OCSArchive\Gliders\MISSIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A573BBF2-1148-4C6F-B995-EDC0F0BFC8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABDFD72-E13D-4FF1-9B07-8ED67F030F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3286" uniqueCount="911">
   <si>
     <t>Deployment date</t>
   </si>
@@ -2726,9 +2726,6 @@
     <t>Feb 2026?</t>
   </si>
   <si>
-    <t>Back from maintenance seal trial,</t>
-  </si>
-  <si>
     <t>Back from maintenance seal trial, First mission with thrusters</t>
   </si>
   <si>
@@ -2750,13 +2747,46 @@
     <t>Microrider probes cal date</t>
   </si>
   <si>
-    <t>First microrider/ADCP/Tridente mission</t>
-  </si>
-  <si>
     <t>Sigma-T/Halmar</t>
   </si>
   <si>
-    <t>Halmar/</t>
+    <t>CODA 2pts cal date</t>
+  </si>
+  <si>
+    <t>AZMP Spring 2026</t>
+  </si>
+  <si>
+    <t>GLI2026_SEA024_094</t>
+  </si>
+  <si>
+    <t>GLI2026_SEA021_089</t>
+  </si>
+  <si>
+    <t>GL1-GL2-HL4-GL2-GL1-TRI-DR</t>
+  </si>
+  <si>
+    <t>Halmar/Halmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Halmar/ </t>
+  </si>
+  <si>
+    <t>Back from maintenance seal trial, Eco needs to be calibration, CDOM values weird compare to SEA021</t>
+  </si>
+  <si>
+    <t>GLI2026_SEA021_092</t>
+  </si>
+  <si>
+    <t>GLI2026_SEA019_151</t>
+  </si>
+  <si>
+    <t>GL1-GL2-HL4-GL2-HL3-GL1-TRI-GL1-TRI-DR</t>
+  </si>
+  <si>
+    <t>Thruster piloting experience towards the end</t>
+  </si>
+  <si>
+    <t>First microrider/ADCP/Tridente mission, statistic period too big changed mid mission,  linear issue where actuator doesn't follow command, lots of navigation tests. Lost ISDP after 2 days, fixed with MR OFF/ON mid mission</t>
   </si>
 </sst>
 </file>
@@ -3114,7 +3144,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3532,9 +3562,6 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3864,7 +3891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DQ106"/>
+  <dimension ref="A1:DR106"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.54296875" customWidth="1"/>
@@ -3924,24 +3951,25 @@
     <col min="60" max="60" width="14.81640625" style="78" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="15.1796875" style="78" bestFit="1" customWidth="1"/>
     <col min="62" max="64" width="15.1796875" style="78" customWidth="1"/>
-    <col min="65" max="66" width="17.81640625" style="6" customWidth="1"/>
-    <col min="67" max="74" width="15.1796875" style="78" customWidth="1"/>
-    <col min="75" max="75" width="23.54296875" style="78" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="11.81640625" style="5" customWidth="1"/>
-    <col min="77" max="80" width="16.36328125" style="1" customWidth="1"/>
-    <col min="81" max="81" width="12.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="12.81640625" style="6" customWidth="1"/>
-    <col min="83" max="83" width="7" style="6" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="7.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="19" style="4" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="20" style="4" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="25.81640625" style="7" customWidth="1"/>
-    <col min="89" max="89" width="64.453125" style="7" customWidth="1"/>
-    <col min="90" max="90" width="78.81640625" style="8" customWidth="1"/>
+    <col min="65" max="65" width="17" style="78" bestFit="1" customWidth="1"/>
+    <col min="66" max="67" width="17.81640625" style="6" customWidth="1"/>
+    <col min="68" max="75" width="15.1796875" style="78" customWidth="1"/>
+    <col min="76" max="76" width="23.54296875" style="78" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="11.81640625" style="5" customWidth="1"/>
+    <col min="78" max="81" width="16.36328125" style="1" customWidth="1"/>
+    <col min="82" max="82" width="12.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="12.81640625" style="6" customWidth="1"/>
+    <col min="84" max="84" width="7" style="6" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="7.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="19" style="4" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="20" style="4" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="25.81640625" style="7" customWidth="1"/>
+    <col min="90" max="90" width="64.453125" style="7" customWidth="1"/>
+    <col min="91" max="91" width="78.81640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:90" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C1" s="24"/>
       <c r="D1" s="146" t="s">
         <v>797</v>
@@ -4009,22 +4037,23 @@
       <c r="BU1" s="26"/>
       <c r="BV1" s="26"/>
       <c r="BW1" s="26"/>
-      <c r="BX1" s="27"/>
-      <c r="BY1" s="28"/>
+      <c r="BX1" s="26"/>
+      <c r="BY1" s="27"/>
       <c r="BZ1" s="28"/>
       <c r="CA1" s="28"/>
       <c r="CB1" s="28"/>
-      <c r="CC1" s="26"/>
+      <c r="CC1" s="28"/>
       <c r="CD1" s="26"/>
       <c r="CE1" s="26"/>
       <c r="CF1" s="26"/>
-      <c r="CH1" s="29"/>
+      <c r="CG1" s="26"/>
       <c r="CI1" s="29"/>
-      <c r="CJ1" s="25"/>
+      <c r="CJ1" s="29"/>
       <c r="CK1" s="25"/>
-      <c r="CL1" s="30"/>
+      <c r="CL1" s="25"/>
+      <c r="CM1" s="30"/>
     </row>
-    <row r="2" spans="1:90" s="63" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:91" s="63" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C2" s="64" t="s">
         <v>0</v>
       </c>
@@ -4211,86 +4240,89 @@
       <c r="BL2" s="70" t="s">
         <v>770</v>
       </c>
-      <c r="BM2" s="72" t="s">
+      <c r="BM2" s="161" t="s">
+        <v>898</v>
+      </c>
+      <c r="BN2" s="72" t="s">
         <v>848</v>
       </c>
-      <c r="BN2" s="72" t="s">
+      <c r="BO2" s="72" t="s">
         <v>847</v>
       </c>
-      <c r="BO2" s="70" t="s">
+      <c r="BP2" s="70" t="s">
         <v>849</v>
       </c>
-      <c r="BP2" s="70" t="s">
+      <c r="BQ2" s="70" t="s">
         <v>846</v>
       </c>
-      <c r="BQ2" s="70" t="s">
+      <c r="BR2" s="70" t="s">
         <v>363</v>
       </c>
-      <c r="BR2" s="70" t="s">
+      <c r="BS2" s="70" t="s">
         <v>364</v>
       </c>
-      <c r="BS2" s="70" t="s">
+      <c r="BT2" s="70" t="s">
         <v>365</v>
       </c>
-      <c r="BT2" s="161" t="s">
+      <c r="BU2" s="161" t="s">
         <v>854</v>
       </c>
-      <c r="BU2" s="161" t="s">
+      <c r="BV2" s="161" t="s">
         <v>855</v>
       </c>
-      <c r="BV2" s="161" t="s">
+      <c r="BW2" s="161" t="s">
         <v>856</v>
       </c>
-      <c r="BW2" s="161" t="s">
-        <v>897</v>
-      </c>
-      <c r="BX2" s="73" t="s">
+      <c r="BX2" s="161" t="s">
+        <v>896</v>
+      </c>
+      <c r="BY2" s="73" t="s">
         <v>167</v>
       </c>
-      <c r="BY2" s="33" t="s">
+      <c r="BZ2" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="BZ2" s="33" t="s">
+      <c r="CA2" s="33" t="s">
         <v>857</v>
       </c>
-      <c r="CA2" s="33" t="s">
+      <c r="CB2" s="33" t="s">
         <v>843</v>
       </c>
-      <c r="CB2" s="33" t="s">
+      <c r="CC2" s="33" t="s">
         <v>835</v>
       </c>
-      <c r="CC2" s="70" t="s">
+      <c r="CD2" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="CD2" s="70" t="s">
+      <c r="CE2" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="CE2" s="70" t="s">
+      <c r="CF2" s="70" t="s">
         <v>221</v>
       </c>
-      <c r="CF2" s="70" t="s">
+      <c r="CG2" s="70" t="s">
         <v>688</v>
       </c>
-      <c r="CG2" s="32" t="s">
+      <c r="CH2" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="CH2" s="74" t="s">
+      <c r="CI2" s="74" t="s">
         <v>191</v>
       </c>
-      <c r="CI2" s="74" t="s">
+      <c r="CJ2" s="74" t="s">
         <v>192</v>
       </c>
-      <c r="CJ2" s="75" t="s">
+      <c r="CK2" s="75" t="s">
         <v>659</v>
       </c>
-      <c r="CK2" s="75" t="s">
+      <c r="CL2" s="75" t="s">
         <v>689</v>
       </c>
-      <c r="CL2" s="76" t="s">
+      <c r="CM2" s="76" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:90" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="124">
         <v>1</v>
       </c>
@@ -4455,43 +4487,44 @@
       <c r="BU3" s="15"/>
       <c r="BV3" s="15"/>
       <c r="BW3" s="15"/>
-      <c r="BX3" s="10" t="s">
+      <c r="BX3" s="15"/>
+      <c r="BY3" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY3" s="17" t="s">
+      <c r="BZ3" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="BZ3" s="17"/>
-      <c r="CA3" s="17" t="s">
+      <c r="CA3" s="17"/>
+      <c r="CB3" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB3" s="49" t="s">
+      <c r="CC3" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC3" s="15" t="s">
+      <c r="CD3" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD3" s="15" t="s">
+      <c r="CE3" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="CE3" s="15"/>
       <c r="CF3" s="15"/>
-      <c r="CG3" s="13"/>
-      <c r="CH3" s="14" t="s">
+      <c r="CG3" s="15"/>
+      <c r="CH3" s="13"/>
+      <c r="CI3" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI3" s="14" t="s">
+      <c r="CJ3" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ3" s="18" t="s">
+      <c r="CK3" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK3" s="12"/>
-      <c r="CL3" s="19" t="s">
+      <c r="CL3" s="12"/>
+      <c r="CM3" s="19" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:90" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="124">
         <v>2</v>
       </c>
@@ -4656,45 +4689,46 @@
       <c r="BU4" s="15"/>
       <c r="BV4" s="15"/>
       <c r="BW4" s="15"/>
-      <c r="BX4" s="10" t="s">
+      <c r="BX4" s="15"/>
+      <c r="BY4" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY4" s="17" t="s">
+      <c r="BZ4" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="BZ4" s="17"/>
-      <c r="CA4" s="17" t="s">
+      <c r="CA4" s="17"/>
+      <c r="CB4" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB4" s="49" t="s">
+      <c r="CC4" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC4" s="15" t="s">
+      <c r="CD4" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD4" s="15" t="s">
+      <c r="CE4" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="CE4" s="15"/>
       <c r="CF4" s="15"/>
-      <c r="CG4" s="2"/>
-      <c r="CH4" s="14" t="s">
+      <c r="CG4" s="15"/>
+      <c r="CH4" s="2"/>
+      <c r="CI4" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI4" s="14" t="s">
+      <c r="CJ4" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ4" s="18" t="s">
+      <c r="CK4" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="CK4" s="18" t="s">
+      <c r="CL4" s="18" t="s">
         <v>707</v>
       </c>
-      <c r="CL4" s="21" t="s">
+      <c r="CM4" s="21" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="5" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="136">
         <v>3</v>
       </c>
@@ -4859,45 +4893,46 @@
       <c r="BU5" s="40"/>
       <c r="BV5" s="40"/>
       <c r="BW5" s="40"/>
-      <c r="BX5" s="41" t="s">
+      <c r="BX5" s="40"/>
+      <c r="BY5" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY5" s="42" t="s">
+      <c r="BZ5" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ5" s="42"/>
-      <c r="CA5" s="42" t="s">
+      <c r="CA5" s="42"/>
+      <c r="CB5" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB5" s="49" t="s">
+      <c r="CC5" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC5" s="40" t="s">
+      <c r="CD5" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="CD5" s="40" t="s">
+      <c r="CE5" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="CE5" s="40"/>
       <c r="CF5" s="40"/>
-      <c r="CG5" s="3" t="s">
+      <c r="CG5" s="40"/>
+      <c r="CH5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="CH5" s="35" t="s">
+      <c r="CI5" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI5" s="35" t="s">
+      <c r="CJ5" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ5" s="37" t="s">
+      <c r="CK5" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK5" s="37"/>
-      <c r="CL5" s="43" t="s">
+      <c r="CL5" s="37"/>
+      <c r="CM5" s="43" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="136">
         <v>4</v>
       </c>
@@ -5063,45 +5098,46 @@
       <c r="BU6" s="40"/>
       <c r="BV6" s="40"/>
       <c r="BW6" s="40"/>
-      <c r="BX6" s="41" t="s">
+      <c r="BX6" s="40"/>
+      <c r="BY6" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY6" s="42" t="s">
+      <c r="BZ6" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ6" s="42"/>
-      <c r="CA6" s="42" t="s">
+      <c r="CA6" s="42"/>
+      <c r="CB6" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB6" s="49" t="s">
+      <c r="CC6" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC6" s="40" t="s">
+      <c r="CD6" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="CD6" s="40" t="s">
+      <c r="CE6" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="CE6" s="40"/>
       <c r="CF6" s="40"/>
-      <c r="CG6" s="3"/>
-      <c r="CH6" s="35" t="s">
+      <c r="CG6" s="40"/>
+      <c r="CH6" s="3"/>
+      <c r="CI6" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI6" s="35" t="s">
+      <c r="CJ6" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ6" s="37" t="s">
+      <c r="CK6" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK6" s="37" t="s">
+      <c r="CL6" s="37" t="s">
         <v>708</v>
       </c>
-      <c r="CL6" s="43" t="s">
+      <c r="CM6" s="43" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="136">
         <v>5</v>
       </c>
@@ -5266,47 +5302,48 @@
       <c r="BU7" s="40"/>
       <c r="BV7" s="40"/>
       <c r="BW7" s="40"/>
-      <c r="BX7" s="41" t="s">
+      <c r="BX7" s="40"/>
+      <c r="BY7" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY7" s="42" t="s">
+      <c r="BZ7" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ7" s="42"/>
-      <c r="CA7" s="42" t="s">
+      <c r="CA7" s="42"/>
+      <c r="CB7" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB7" s="49" t="s">
+      <c r="CC7" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC7" s="40" t="s">
+      <c r="CD7" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="CD7" s="40" t="s">
+      <c r="CE7" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="CE7" s="40"/>
       <c r="CF7" s="40"/>
-      <c r="CG7" s="3" t="s">
+      <c r="CG7" s="40"/>
+      <c r="CH7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="CH7" s="35" t="s">
+      <c r="CI7" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI7" s="35" t="s">
+      <c r="CJ7" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ7" s="37" t="s">
+      <c r="CK7" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK7" s="37" t="s">
+      <c r="CL7" s="37" t="s">
         <v>709</v>
       </c>
-      <c r="CL7" s="43" t="s">
+      <c r="CM7" s="43" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="8" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="136">
         <v>6</v>
       </c>
@@ -5471,45 +5508,46 @@
       <c r="BU8" s="40"/>
       <c r="BV8" s="40"/>
       <c r="BW8" s="40"/>
-      <c r="BX8" s="41" t="s">
+      <c r="BX8" s="40"/>
+      <c r="BY8" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY8" s="42" t="s">
+      <c r="BZ8" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ8" s="42"/>
-      <c r="CA8" s="42" t="s">
+      <c r="CA8" s="42"/>
+      <c r="CB8" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB8" s="49" t="s">
+      <c r="CC8" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC8" s="40" t="s">
+      <c r="CD8" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="CD8" s="40" t="s">
+      <c r="CE8" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="CE8" s="40"/>
       <c r="CF8" s="40"/>
-      <c r="CG8" s="3"/>
-      <c r="CH8" s="35" t="s">
+      <c r="CG8" s="40"/>
+      <c r="CH8" s="3"/>
+      <c r="CI8" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI8" s="35" t="s">
+      <c r="CJ8" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ8" s="37" t="s">
+      <c r="CK8" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK8" s="37" t="s">
+      <c r="CL8" s="37" t="s">
         <v>710</v>
       </c>
-      <c r="CL8" s="43" t="s">
+      <c r="CM8" s="43" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="9" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="136">
         <v>7</v>
       </c>
@@ -5674,45 +5712,46 @@
       <c r="BU9" s="40"/>
       <c r="BV9" s="40"/>
       <c r="BW9" s="40"/>
-      <c r="BX9" s="41" t="s">
+      <c r="BX9" s="40"/>
+      <c r="BY9" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY9" s="42" t="s">
+      <c r="BZ9" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ9" s="42"/>
-      <c r="CA9" s="42" t="s">
+      <c r="CA9" s="42"/>
+      <c r="CB9" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB9" s="49" t="s">
+      <c r="CC9" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC9" s="40" t="s">
+      <c r="CD9" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="CD9" s="40" t="s">
+      <c r="CE9" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="CE9" s="40"/>
       <c r="CF9" s="40"/>
-      <c r="CG9" s="3"/>
-      <c r="CH9" s="35" t="s">
+      <c r="CG9" s="40"/>
+      <c r="CH9" s="3"/>
+      <c r="CI9" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI9" s="35" t="s">
+      <c r="CJ9" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ9" s="37" t="s">
+      <c r="CK9" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK9" s="37" t="s">
+      <c r="CL9" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="CL9" s="43" t="s">
+      <c r="CM9" s="43" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="136">
         <v>8</v>
       </c>
@@ -5877,45 +5916,46 @@
       <c r="BU10" s="40"/>
       <c r="BV10" s="40"/>
       <c r="BW10" s="40"/>
-      <c r="BX10" s="41" t="s">
+      <c r="BX10" s="40"/>
+      <c r="BY10" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY10" s="42" t="s">
+      <c r="BZ10" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ10" s="42"/>
-      <c r="CA10" s="42" t="s">
+      <c r="CA10" s="42"/>
+      <c r="CB10" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB10" s="49" t="s">
+      <c r="CC10" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC10" s="40" t="s">
+      <c r="CD10" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="CD10" s="40" t="s">
+      <c r="CE10" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="CE10" s="40"/>
       <c r="CF10" s="40"/>
-      <c r="CG10" s="3"/>
-      <c r="CH10" s="35" t="s">
+      <c r="CG10" s="40"/>
+      <c r="CH10" s="3"/>
+      <c r="CI10" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI10" s="35" t="s">
+      <c r="CJ10" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ10" s="37" t="s">
+      <c r="CK10" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="CK10" s="37" t="s">
+      <c r="CL10" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="CL10" s="51" t="s">
+      <c r="CM10" s="51" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="136">
         <v>9</v>
       </c>
@@ -6080,45 +6120,46 @@
       <c r="BU11" s="40"/>
       <c r="BV11" s="40"/>
       <c r="BW11" s="40"/>
-      <c r="BX11" s="41" t="s">
+      <c r="BX11" s="40"/>
+      <c r="BY11" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY11" s="42" t="s">
+      <c r="BZ11" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ11" s="42"/>
-      <c r="CA11" s="42" t="s">
+      <c r="CA11" s="42"/>
+      <c r="CB11" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB11" s="49" t="s">
+      <c r="CC11" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC11" s="40" t="s">
+      <c r="CD11" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="CD11" s="40" t="s">
+      <c r="CE11" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="CE11" s="40"/>
       <c r="CF11" s="40"/>
-      <c r="CG11" s="3"/>
-      <c r="CH11" s="35" t="s">
+      <c r="CG11" s="40"/>
+      <c r="CH11" s="3"/>
+      <c r="CI11" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI11" s="35" t="s">
+      <c r="CJ11" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ11" s="37" t="s">
+      <c r="CK11" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK11" s="37" t="s">
+      <c r="CL11" s="37" t="s">
         <v>712</v>
       </c>
-      <c r="CL11" s="51" t="s">
+      <c r="CM11" s="51" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="136">
         <v>10</v>
       </c>
@@ -6287,45 +6328,46 @@
       <c r="BU12" s="40"/>
       <c r="BV12" s="40"/>
       <c r="BW12" s="40"/>
-      <c r="BX12" s="41" t="s">
+      <c r="BX12" s="40"/>
+      <c r="BY12" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY12" s="42" t="s">
+      <c r="BZ12" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ12" s="42"/>
-      <c r="CA12" s="42" t="s">
+      <c r="CA12" s="42"/>
+      <c r="CB12" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB12" s="49" t="s">
+      <c r="CC12" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC12" s="40" t="s">
+      <c r="CD12" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="CD12" s="40" t="s">
+      <c r="CE12" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="CE12" s="40"/>
       <c r="CF12" s="40"/>
-      <c r="CG12" s="3"/>
-      <c r="CH12" s="35" t="s">
+      <c r="CG12" s="40"/>
+      <c r="CH12" s="3"/>
+      <c r="CI12" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI12" s="35" t="s">
+      <c r="CJ12" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ12" s="37" t="s">
+      <c r="CK12" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK12" s="37" t="s">
+      <c r="CL12" s="37" t="s">
         <v>712</v>
       </c>
-      <c r="CL12" s="51" t="s">
+      <c r="CM12" s="51" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="136">
         <v>11</v>
       </c>
@@ -6479,9 +6521,9 @@
       <c r="BJ13" s="40"/>
       <c r="BK13" s="40"/>
       <c r="BL13" s="40"/>
-      <c r="BM13" s="38"/>
+      <c r="BM13" s="40"/>
       <c r="BN13" s="38"/>
-      <c r="BO13" s="40"/>
+      <c r="BO13" s="38"/>
       <c r="BP13" s="40"/>
       <c r="BQ13" s="40"/>
       <c r="BR13" s="40"/>
@@ -6490,47 +6532,48 @@
       <c r="BU13" s="40"/>
       <c r="BV13" s="40"/>
       <c r="BW13" s="40"/>
-      <c r="BX13" s="41" t="s">
+      <c r="BX13" s="40"/>
+      <c r="BY13" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY13" s="42" t="s">
+      <c r="BZ13" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ13" s="42"/>
-      <c r="CA13" s="42" t="s">
+      <c r="CA13" s="42"/>
+      <c r="CB13" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB13" s="49" t="s">
+      <c r="CC13" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC13" s="38" t="s">
+      <c r="CD13" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="CD13" s="38" t="s">
+      <c r="CE13" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="CE13" s="38"/>
       <c r="CF13" s="38"/>
-      <c r="CG13" s="3" t="s">
+      <c r="CG13" s="38"/>
+      <c r="CH13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="CH13" s="35" t="s">
+      <c r="CI13" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI13" s="35" t="s">
+      <c r="CJ13" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ13" s="37" t="s">
+      <c r="CK13" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="CK13" s="141" t="s">
+      <c r="CL13" s="141" t="s">
         <v>713</v>
       </c>
-      <c r="CL13" s="52" t="s">
+      <c r="CM13" s="52" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="14" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="136">
         <v>12</v>
       </c>
@@ -6695,45 +6738,46 @@
       <c r="BU14" s="40"/>
       <c r="BV14" s="40"/>
       <c r="BW14" s="40"/>
-      <c r="BX14" s="41" t="s">
+      <c r="BX14" s="40"/>
+      <c r="BY14" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY14" s="42" t="s">
+      <c r="BZ14" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ14" s="42"/>
-      <c r="CA14" s="42" t="s">
+      <c r="CA14" s="42"/>
+      <c r="CB14" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB14" s="49" t="s">
+      <c r="CC14" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC14" s="40" t="s">
+      <c r="CD14" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="CD14" s="40" t="s">
+      <c r="CE14" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="CE14" s="40"/>
       <c r="CF14" s="40"/>
-      <c r="CG14" s="3"/>
-      <c r="CH14" s="35" t="s">
+      <c r="CG14" s="40"/>
+      <c r="CH14" s="3"/>
+      <c r="CI14" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI14" s="35" t="s">
+      <c r="CJ14" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ14" s="37" t="s">
+      <c r="CK14" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK14" s="37" t="s">
+      <c r="CL14" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="CL14" s="43" t="s">
+      <c r="CM14" s="43" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="136">
         <v>13</v>
       </c>
@@ -6902,45 +6946,46 @@
       <c r="BU15" s="40"/>
       <c r="BV15" s="40"/>
       <c r="BW15" s="40"/>
-      <c r="BX15" s="41" t="s">
+      <c r="BX15" s="40"/>
+      <c r="BY15" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY15" s="42" t="s">
+      <c r="BZ15" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ15" s="42"/>
-      <c r="CA15" s="42" t="s">
+      <c r="CA15" s="42"/>
+      <c r="CB15" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB15" s="49" t="s">
+      <c r="CC15" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC15" s="40" t="s">
+      <c r="CD15" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="CD15" s="40" t="s">
+      <c r="CE15" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="CE15" s="40"/>
       <c r="CF15" s="40"/>
-      <c r="CG15" s="3"/>
-      <c r="CH15" s="35" t="s">
+      <c r="CG15" s="40"/>
+      <c r="CH15" s="3"/>
+      <c r="CI15" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI15" s="35" t="s">
+      <c r="CJ15" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ15" s="37" t="s">
+      <c r="CK15" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK15" s="140" t="s">
+      <c r="CL15" s="140" t="s">
         <v>714</v>
       </c>
-      <c r="CL15" s="43" t="s">
+      <c r="CM15" s="43" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="16" spans="1:90" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="136">
         <v>14</v>
       </c>
@@ -7094,9 +7139,9 @@
       <c r="BJ16" s="40"/>
       <c r="BK16" s="40"/>
       <c r="BL16" s="40"/>
-      <c r="BM16" s="38"/>
+      <c r="BM16" s="40"/>
       <c r="BN16" s="38"/>
-      <c r="BO16" s="40"/>
+      <c r="BO16" s="38"/>
       <c r="BP16" s="40"/>
       <c r="BQ16" s="40"/>
       <c r="BR16" s="40"/>
@@ -7105,47 +7150,48 @@
       <c r="BU16" s="40"/>
       <c r="BV16" s="40"/>
       <c r="BW16" s="40"/>
-      <c r="BX16" s="41" t="s">
+      <c r="BX16" s="40"/>
+      <c r="BY16" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY16" s="42" t="s">
+      <c r="BZ16" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ16" s="42"/>
-      <c r="CA16" s="42" t="s">
+      <c r="CA16" s="42"/>
+      <c r="CB16" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB16" s="49" t="s">
+      <c r="CC16" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC16" s="38" t="s">
+      <c r="CD16" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="CD16" s="38" t="s">
+      <c r="CE16" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="CE16" s="92" t="s">
+      <c r="CF16" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF16" s="38"/>
-      <c r="CG16" s="3"/>
-      <c r="CH16" s="35" t="s">
+      <c r="CG16" s="38"/>
+      <c r="CH16" s="3"/>
+      <c r="CI16" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI16" s="35" t="s">
+      <c r="CJ16" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ16" s="37" t="s">
+      <c r="CK16" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK16" s="37" t="s">
+      <c r="CL16" s="37" t="s">
         <v>715</v>
       </c>
-      <c r="CL16" s="43" t="s">
+      <c r="CM16" s="43" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="17" spans="1:90" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="136">
         <v>15</v>
       </c>
@@ -7309,47 +7355,48 @@
       <c r="BU17" s="40"/>
       <c r="BV17" s="40"/>
       <c r="BW17" s="40"/>
-      <c r="BX17" s="41" t="s">
+      <c r="BX17" s="40"/>
+      <c r="BY17" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY17" s="42" t="s">
+      <c r="BZ17" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ17" s="42"/>
-      <c r="CA17" s="42" t="s">
+      <c r="CA17" s="42"/>
+      <c r="CB17" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB17" s="49" t="s">
+      <c r="CC17" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC17" s="40" t="s">
+      <c r="CD17" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="CD17" s="38" t="s">
+      <c r="CE17" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="CE17" s="92" t="s">
+      <c r="CF17" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF17" s="38"/>
-      <c r="CG17" s="3"/>
-      <c r="CH17" s="35" t="s">
+      <c r="CG17" s="38"/>
+      <c r="CH17" s="3"/>
+      <c r="CI17" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI17" s="35" t="s">
+      <c r="CJ17" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ17" s="37" t="s">
+      <c r="CK17" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK17" s="37" t="s">
+      <c r="CL17" s="37" t="s">
         <v>716</v>
       </c>
-      <c r="CL17" s="43" t="s">
+      <c r="CM17" s="43" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="124">
         <v>16</v>
       </c>
@@ -7502,9 +7549,9 @@
       <c r="BJ18" s="15"/>
       <c r="BK18" s="15"/>
       <c r="BL18" s="15"/>
-      <c r="BM18" s="22"/>
+      <c r="BM18" s="15"/>
       <c r="BN18" s="22"/>
-      <c r="BO18" s="15"/>
+      <c r="BO18" s="22"/>
       <c r="BP18" s="15"/>
       <c r="BQ18" s="15"/>
       <c r="BR18" s="15"/>
@@ -7513,47 +7560,48 @@
       <c r="BU18" s="15"/>
       <c r="BV18" s="15"/>
       <c r="BW18" s="15"/>
-      <c r="BX18" s="10" t="s">
+      <c r="BX18" s="15"/>
+      <c r="BY18" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY18" s="17" t="s">
+      <c r="BZ18" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ18" s="17"/>
-      <c r="CA18" s="17" t="s">
+      <c r="CA18" s="17"/>
+      <c r="CB18" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB18" s="49" t="s">
+      <c r="CC18" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC18" s="22" t="s">
+      <c r="CD18" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="CD18" s="22" t="s">
+      <c r="CE18" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="CE18" s="22"/>
       <c r="CF18" s="22"/>
-      <c r="CG18" s="2" t="s">
+      <c r="CG18" s="22"/>
+      <c r="CH18" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="CH18" s="14" t="s">
+      <c r="CI18" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI18" s="14" t="s">
+      <c r="CJ18" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ18" s="18" t="s">
+      <c r="CK18" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK18" s="18" t="s">
+      <c r="CL18" s="18" t="s">
         <v>716</v>
       </c>
-      <c r="CL18" s="21" t="s">
+      <c r="CM18" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="124">
         <v>17</v>
       </c>
@@ -7704,7 +7752,7 @@
       <c r="BL19" s="15"/>
       <c r="BM19" s="53"/>
       <c r="BN19" s="53"/>
-      <c r="BO19" s="15"/>
+      <c r="BO19" s="53"/>
       <c r="BP19" s="15"/>
       <c r="BQ19" s="15"/>
       <c r="BR19" s="15"/>
@@ -7713,45 +7761,46 @@
       <c r="BU19" s="15"/>
       <c r="BV19" s="15"/>
       <c r="BW19" s="15"/>
-      <c r="BX19" s="10" t="s">
+      <c r="BX19" s="15"/>
+      <c r="BY19" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY19" s="17" t="s">
+      <c r="BZ19" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ19" s="17"/>
-      <c r="CA19" s="17" t="s">
+      <c r="CA19" s="17"/>
+      <c r="CB19" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB19" s="49" t="s">
+      <c r="CC19" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC19" s="54" t="s">
+      <c r="CD19" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="CD19" s="54" t="s">
+      <c r="CE19" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="CE19" s="22"/>
       <c r="CF19" s="22"/>
-      <c r="CG19" s="2"/>
-      <c r="CH19" s="14" t="s">
+      <c r="CG19" s="22"/>
+      <c r="CH19" s="2"/>
+      <c r="CI19" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI19" s="14" t="s">
+      <c r="CJ19" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="CJ19" s="18" t="s">
+      <c r="CK19" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK19" s="18" t="s">
+      <c r="CL19" s="18" t="s">
         <v>716</v>
       </c>
-      <c r="CL19" s="21" t="s">
+      <c r="CM19" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="124">
         <v>18</v>
       </c>
@@ -7904,9 +7953,9 @@
       <c r="BJ20" s="15"/>
       <c r="BK20" s="15"/>
       <c r="BL20" s="15"/>
-      <c r="BM20" s="22"/>
+      <c r="BM20" s="15"/>
       <c r="BN20" s="22"/>
-      <c r="BO20" s="15"/>
+      <c r="BO20" s="22"/>
       <c r="BP20" s="15"/>
       <c r="BQ20" s="15"/>
       <c r="BR20" s="15"/>
@@ -7915,47 +7964,48 @@
       <c r="BU20" s="15"/>
       <c r="BV20" s="15"/>
       <c r="BW20" s="15"/>
-      <c r="BX20" s="10" t="s">
+      <c r="BX20" s="15"/>
+      <c r="BY20" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY20" s="17" t="s">
+      <c r="BZ20" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ20" s="17"/>
-      <c r="CA20" s="17" t="s">
+      <c r="CA20" s="17"/>
+      <c r="CB20" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB20" s="49" t="s">
+      <c r="CC20" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC20" s="22" t="s">
+      <c r="CD20" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="CD20" s="22" t="s">
+      <c r="CE20" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="CE20" s="92" t="s">
+      <c r="CF20" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF20" s="22"/>
-      <c r="CG20" s="2"/>
-      <c r="CH20" s="14" t="s">
+      <c r="CG20" s="22"/>
+      <c r="CH20" s="2"/>
+      <c r="CI20" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI20" s="14" t="s">
+      <c r="CJ20" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ20" s="18" t="s">
+      <c r="CK20" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK20" s="139" t="s">
+      <c r="CL20" s="139" t="s">
         <v>691</v>
       </c>
-      <c r="CL20" s="21" t="s">
+      <c r="CM20" s="21" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="124">
         <v>18</v>
       </c>
@@ -8109,9 +8159,9 @@
       <c r="BJ21" s="15"/>
       <c r="BK21" s="15"/>
       <c r="BL21" s="15"/>
-      <c r="BM21" s="22"/>
+      <c r="BM21" s="15"/>
       <c r="BN21" s="22"/>
-      <c r="BO21" s="15"/>
+      <c r="BO21" s="22"/>
       <c r="BP21" s="15"/>
       <c r="BQ21" s="15"/>
       <c r="BR21" s="15"/>
@@ -8120,47 +8170,48 @@
       <c r="BU21" s="15"/>
       <c r="BV21" s="15"/>
       <c r="BW21" s="15"/>
-      <c r="BX21" s="10" t="s">
+      <c r="BX21" s="15"/>
+      <c r="BY21" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY21" s="17" t="s">
+      <c r="BZ21" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ21" s="17"/>
-      <c r="CA21" s="17" t="s">
+      <c r="CA21" s="17"/>
+      <c r="CB21" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB21" s="49" t="s">
+      <c r="CC21" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC21" s="22" t="s">
+      <c r="CD21" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="CD21" s="22" t="s">
+      <c r="CE21" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="CE21" s="92" t="s">
+      <c r="CF21" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF21" s="22"/>
-      <c r="CG21" s="2"/>
-      <c r="CH21" s="14" t="s">
+      <c r="CG21" s="22"/>
+      <c r="CH21" s="2"/>
+      <c r="CI21" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI21" s="14" t="s">
+      <c r="CJ21" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ21" s="18" t="s">
+      <c r="CK21" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK21" s="18" t="s">
+      <c r="CL21" s="18" t="s">
         <v>717</v>
       </c>
-      <c r="CL21" s="21" t="s">
+      <c r="CM21" s="21" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="22" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="124">
         <v>19</v>
       </c>
@@ -8314,9 +8365,9 @@
       <c r="BJ22" s="15"/>
       <c r="BK22" s="15"/>
       <c r="BL22" s="15"/>
-      <c r="BM22" s="22"/>
+      <c r="BM22" s="15"/>
       <c r="BN22" s="22"/>
-      <c r="BO22" s="15"/>
+      <c r="BO22" s="22"/>
       <c r="BP22" s="15"/>
       <c r="BQ22" s="15"/>
       <c r="BR22" s="15"/>
@@ -8325,47 +8376,48 @@
       <c r="BU22" s="15"/>
       <c r="BV22" s="15"/>
       <c r="BW22" s="15"/>
-      <c r="BX22" s="10" t="s">
+      <c r="BX22" s="15"/>
+      <c r="BY22" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY22" s="17" t="s">
+      <c r="BZ22" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ22" s="17"/>
-      <c r="CA22" s="17" t="s">
+      <c r="CA22" s="17"/>
+      <c r="CB22" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB22" s="49" t="s">
+      <c r="CC22" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC22" s="22" t="s">
+      <c r="CD22" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="CD22" s="22" t="s">
+      <c r="CE22" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="CE22" s="92" t="s">
+      <c r="CF22" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF22" s="22"/>
-      <c r="CG22" s="2"/>
-      <c r="CH22" s="14" t="s">
+      <c r="CG22" s="22"/>
+      <c r="CH22" s="2"/>
+      <c r="CI22" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI22" s="14" t="s">
+      <c r="CJ22" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ22" s="18" t="s">
+      <c r="CK22" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK22" s="18" t="s">
+      <c r="CL22" s="18" t="s">
         <v>718</v>
       </c>
-      <c r="CL22" s="21" t="s">
+      <c r="CM22" s="21" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="23" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="124">
         <v>20</v>
       </c>
@@ -8519,9 +8571,9 @@
       <c r="BJ23" s="15"/>
       <c r="BK23" s="15"/>
       <c r="BL23" s="15"/>
-      <c r="BM23" s="22"/>
+      <c r="BM23" s="15"/>
       <c r="BN23" s="22"/>
-      <c r="BO23" s="15"/>
+      <c r="BO23" s="22"/>
       <c r="BP23" s="15"/>
       <c r="BQ23" s="15"/>
       <c r="BR23" s="15"/>
@@ -8530,47 +8582,48 @@
       <c r="BU23" s="15"/>
       <c r="BV23" s="15"/>
       <c r="BW23" s="15"/>
-      <c r="BX23" s="10" t="s">
+      <c r="BX23" s="15"/>
+      <c r="BY23" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY23" s="17" t="s">
+      <c r="BZ23" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ23" s="17"/>
-      <c r="CA23" s="17" t="s">
+      <c r="CA23" s="17"/>
+      <c r="CB23" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB23" s="49" t="s">
+      <c r="CC23" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC23" s="22" t="s">
+      <c r="CD23" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="CD23" s="22" t="s">
+      <c r="CE23" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="CE23" s="92" t="s">
+      <c r="CF23" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF23" s="22"/>
-      <c r="CG23" s="2"/>
-      <c r="CH23" s="14" t="s">
+      <c r="CG23" s="22"/>
+      <c r="CH23" s="2"/>
+      <c r="CI23" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI23" s="14" t="s">
+      <c r="CJ23" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ23" s="18" t="s">
+      <c r="CK23" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="CK23" s="139" t="s">
+      <c r="CL23" s="139" t="s">
         <v>719</v>
       </c>
-      <c r="CL23" s="21" t="s">
+      <c r="CM23" s="21" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="124">
         <v>21</v>
       </c>
@@ -8735,45 +8788,46 @@
       <c r="BU24" s="15"/>
       <c r="BV24" s="15"/>
       <c r="BW24" s="15"/>
-      <c r="BX24" s="10" t="s">
+      <c r="BX24" s="15"/>
+      <c r="BY24" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY24" s="17" t="s">
+      <c r="BZ24" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ24" s="17"/>
-      <c r="CA24" s="17" t="s">
+      <c r="CA24" s="17"/>
+      <c r="CB24" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB24" s="49" t="s">
+      <c r="CC24" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC24" s="15" t="s">
+      <c r="CD24" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD24" s="22" t="s">
+      <c r="CE24" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="CE24" s="22"/>
       <c r="CF24" s="22"/>
-      <c r="CG24" s="2"/>
-      <c r="CH24" s="14" t="s">
+      <c r="CG24" s="22"/>
+      <c r="CH24" s="2"/>
+      <c r="CI24" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="CI24" s="14" t="s">
+      <c r="CJ24" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ24" s="18" t="s">
+      <c r="CK24" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="CK24" s="138" t="s">
+      <c r="CL24" s="138" t="s">
         <v>717</v>
       </c>
-      <c r="CL24" s="50" t="s">
+      <c r="CM24" s="50" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="25" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="124">
         <v>22</v>
       </c>
@@ -8935,47 +8989,48 @@
       <c r="BU25" s="15"/>
       <c r="BV25" s="15"/>
       <c r="BW25" s="15"/>
-      <c r="BX25" s="10" t="s">
+      <c r="BX25" s="15"/>
+      <c r="BY25" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY25" s="17" t="s">
+      <c r="BZ25" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ25" s="17"/>
-      <c r="CA25" s="17" t="s">
+      <c r="CA25" s="17"/>
+      <c r="CB25" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB25" s="49" t="s">
+      <c r="CC25" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC25" s="54" t="s">
+      <c r="CD25" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="CD25" s="54" t="s">
+      <c r="CE25" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="CE25" s="92" t="s">
+      <c r="CF25" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF25" s="22"/>
-      <c r="CG25" s="2"/>
-      <c r="CH25" s="14" t="s">
+      <c r="CG25" s="22"/>
+      <c r="CH25" s="2"/>
+      <c r="CI25" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI25" s="14" t="s">
+      <c r="CJ25" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ25" s="18" t="s">
+      <c r="CK25" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="CK25" s="139" t="s">
+      <c r="CL25" s="139" t="s">
         <v>734</v>
       </c>
-      <c r="CL25" s="21" t="s">
+      <c r="CM25" s="21" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="26" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="124">
         <v>23</v>
       </c>
@@ -9141,47 +9196,48 @@
       <c r="BU26" s="15"/>
       <c r="BV26" s="15"/>
       <c r="BW26" s="15"/>
-      <c r="BX26" s="10" t="s">
+      <c r="BX26" s="15"/>
+      <c r="BY26" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY26" s="17" t="s">
+      <c r="BZ26" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ26" s="17"/>
-      <c r="CA26" s="17" t="s">
+      <c r="CA26" s="17"/>
+      <c r="CB26" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB26" s="49" t="s">
+      <c r="CC26" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC26" s="22" t="s">
+      <c r="CD26" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="CD26" s="22" t="s">
+      <c r="CE26" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="CE26" s="92" t="s">
+      <c r="CF26" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF26" s="22"/>
-      <c r="CG26" s="2"/>
-      <c r="CH26" s="14" t="s">
+      <c r="CG26" s="22"/>
+      <c r="CH26" s="2"/>
+      <c r="CI26" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI26" s="14" t="s">
+      <c r="CJ26" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ26" s="18" t="s">
+      <c r="CK26" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="CK26" s="18" t="s">
+      <c r="CL26" s="18" t="s">
         <v>718</v>
       </c>
-      <c r="CL26" s="21" t="s">
+      <c r="CM26" s="21" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="124">
         <v>24</v>
       </c>
@@ -9345,45 +9401,46 @@
       <c r="BU27" s="15"/>
       <c r="BV27" s="15"/>
       <c r="BW27" s="15"/>
-      <c r="BX27" s="10" t="s">
+      <c r="BX27" s="15"/>
+      <c r="BY27" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY27" s="17" t="s">
+      <c r="BZ27" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ27" s="17"/>
-      <c r="CA27" s="17" t="s">
+      <c r="CA27" s="17"/>
+      <c r="CB27" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB27" s="49" t="s">
+      <c r="CC27" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC27" s="15" t="s">
+      <c r="CD27" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD27" s="22" t="s">
+      <c r="CE27" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="CE27" s="22"/>
       <c r="CF27" s="22"/>
-      <c r="CG27" s="2"/>
-      <c r="CH27" s="14" t="s">
+      <c r="CG27" s="22"/>
+      <c r="CH27" s="2"/>
+      <c r="CI27" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="CI27" s="14" t="s">
+      <c r="CJ27" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ27" s="18" t="s">
+      <c r="CK27" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="CK27" s="138" t="s">
+      <c r="CL27" s="138" t="s">
         <v>717</v>
       </c>
-      <c r="CL27" s="50" t="s">
+      <c r="CM27" s="50" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="28" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="124">
         <v>25</v>
       </c>
@@ -9548,47 +9605,48 @@
       <c r="BU28" s="15"/>
       <c r="BV28" s="15"/>
       <c r="BW28" s="15"/>
-      <c r="BX28" s="10" t="s">
+      <c r="BX28" s="15"/>
+      <c r="BY28" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY28" s="49" t="s">
+      <c r="BZ28" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ28" s="17"/>
-      <c r="CA28" s="17" t="s">
+      <c r="CA28" s="17"/>
+      <c r="CB28" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB28" s="49" t="s">
+      <c r="CC28" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC28" s="15" t="s">
+      <c r="CD28" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="CD28" s="22" t="s">
+      <c r="CE28" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="CE28" s="92" t="s">
+      <c r="CF28" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF28" s="22"/>
-      <c r="CG28" s="2"/>
-      <c r="CH28" s="14" t="s">
+      <c r="CG28" s="22"/>
+      <c r="CH28" s="2"/>
+      <c r="CI28" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI28" s="14" t="s">
+      <c r="CJ28" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ28" s="18" t="s">
+      <c r="CK28" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK28" s="18" t="s">
+      <c r="CL28" s="18" t="s">
         <v>711</v>
       </c>
-      <c r="CL28" s="21" t="s">
+      <c r="CM28" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="29" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="124">
         <v>26</v>
       </c>
@@ -9740,43 +9798,44 @@
       <c r="BU29" s="15"/>
       <c r="BV29" s="15"/>
       <c r="BW29" s="15"/>
-      <c r="BX29" s="10" t="s">
+      <c r="BX29" s="15"/>
+      <c r="BY29" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY29" s="49" t="s">
+      <c r="BZ29" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ29" s="17"/>
-      <c r="CA29" s="17" t="s">
+      <c r="CA29" s="17"/>
+      <c r="CB29" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB29" s="49" t="s">
+      <c r="CC29" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC29" s="22" t="s">
+      <c r="CD29" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="CD29" s="22" t="s">
+      <c r="CE29" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="CE29" s="22"/>
       <c r="CF29" s="22"/>
-      <c r="CG29" s="2"/>
-      <c r="CH29" s="14" t="s">
+      <c r="CG29" s="22"/>
+      <c r="CH29" s="2"/>
+      <c r="CI29" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI29" s="14" t="s">
+      <c r="CJ29" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ29" s="18" t="s">
+      <c r="CK29" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK29" s="18"/>
-      <c r="CL29" s="21" t="s">
+      <c r="CL29" s="18"/>
+      <c r="CM29" s="21" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="124">
         <v>27</v>
       </c>
@@ -9941,47 +10000,48 @@
       <c r="BU30" s="15"/>
       <c r="BV30" s="15"/>
       <c r="BW30" s="15"/>
-      <c r="BX30" s="10" t="s">
+      <c r="BX30" s="15"/>
+      <c r="BY30" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY30" s="17" t="s">
+      <c r="BZ30" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="BZ30" s="17"/>
-      <c r="CA30" s="17" t="s">
+      <c r="CA30" s="17"/>
+      <c r="CB30" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB30" s="49" t="s">
+      <c r="CC30" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC30" s="15" t="s">
+      <c r="CD30" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD30" s="15" t="s">
+      <c r="CE30" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="CE30" s="92" t="s">
+      <c r="CF30" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF30" s="22"/>
-      <c r="CG30" s="2"/>
-      <c r="CH30" s="14" t="s">
+      <c r="CG30" s="22"/>
+      <c r="CH30" s="2"/>
+      <c r="CI30" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI30" s="14" t="s">
+      <c r="CJ30" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ30" s="18" t="s">
+      <c r="CK30" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK30" s="18" t="s">
+      <c r="CL30" s="18" t="s">
         <v>711</v>
       </c>
-      <c r="CL30" s="21" t="s">
+      <c r="CM30" s="21" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="31" spans="1:90" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="124">
         <v>28</v>
       </c>
@@ -10145,47 +10205,48 @@
       <c r="BU31" s="15"/>
       <c r="BV31" s="15"/>
       <c r="BW31" s="15"/>
-      <c r="BX31" s="10" t="s">
+      <c r="BX31" s="15"/>
+      <c r="BY31" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY31" s="17" t="s">
+      <c r="BZ31" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BZ31" s="17"/>
-      <c r="CA31" s="17" t="s">
+      <c r="CA31" s="17"/>
+      <c r="CB31" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB31" s="49" t="s">
+      <c r="CC31" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC31" s="22" t="s">
+      <c r="CD31" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="CD31" s="22" t="s">
+      <c r="CE31" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="CE31" s="92" t="s">
+      <c r="CF31" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF31" s="22"/>
-      <c r="CG31" s="2"/>
-      <c r="CH31" s="14" t="s">
+      <c r="CG31" s="22"/>
+      <c r="CH31" s="2"/>
+      <c r="CI31" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI31" s="14" t="s">
+      <c r="CJ31" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ31" s="18" t="s">
+      <c r="CK31" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK31" s="18" t="s">
+      <c r="CL31" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="CL31" s="21" t="s">
+      <c r="CM31" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:90" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="124">
         <v>29</v>
       </c>
@@ -10354,45 +10415,46 @@
       <c r="BU32" s="15"/>
       <c r="BV32" s="15"/>
       <c r="BW32" s="15"/>
-      <c r="BX32" s="10" t="s">
+      <c r="BX32" s="15"/>
+      <c r="BY32" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY32" s="17" t="s">
+      <c r="BZ32" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BZ32" s="17"/>
-      <c r="CA32" s="17" t="s">
+      <c r="CA32" s="17"/>
+      <c r="CB32" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB32" s="49" t="s">
+      <c r="CC32" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC32" s="15" t="s">
+      <c r="CD32" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD32" s="22" t="s">
+      <c r="CE32" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="CE32" s="92" t="s">
+      <c r="CF32" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF32" s="22"/>
-      <c r="CG32" s="2"/>
-      <c r="CH32" s="14" t="s">
+      <c r="CG32" s="22"/>
+      <c r="CH32" s="2"/>
+      <c r="CI32" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI32" s="14" t="s">
+      <c r="CJ32" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ32" s="18" t="s">
+      <c r="CK32" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="CK32" s="18"/>
-      <c r="CL32" s="21" t="s">
+      <c r="CL32" s="18"/>
+      <c r="CM32" s="21" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="33" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="124"/>
       <c r="C33" s="47" t="s">
         <v>246</v>
@@ -10471,27 +10533,28 @@
       <c r="BU33" s="40"/>
       <c r="BV33" s="40"/>
       <c r="BW33" s="40"/>
-      <c r="BX33" s="41"/>
-      <c r="BY33" s="42"/>
+      <c r="BX33" s="40"/>
+      <c r="BY33" s="41"/>
       <c r="BZ33" s="42"/>
-      <c r="CA33" s="42" t="s">
+      <c r="CA33" s="42"/>
+      <c r="CB33" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB33" s="49" t="s">
+      <c r="CC33" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC33" s="40"/>
-      <c r="CD33" s="38"/>
+      <c r="CD33" s="40"/>
       <c r="CE33" s="38"/>
       <c r="CF33" s="38"/>
-      <c r="CG33" s="3"/>
-      <c r="CH33" s="35"/>
+      <c r="CG33" s="38"/>
+      <c r="CH33" s="3"/>
       <c r="CI33" s="35"/>
-      <c r="CJ33" s="37"/>
+      <c r="CJ33" s="35"/>
       <c r="CK33" s="37"/>
-      <c r="CL33" s="43"/>
+      <c r="CL33" s="37"/>
+      <c r="CM33" s="43"/>
     </row>
-    <row r="34" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="124"/>
       <c r="C34" s="47" t="s">
         <v>247</v>
@@ -10570,27 +10633,28 @@
       <c r="BU34" s="40"/>
       <c r="BV34" s="40"/>
       <c r="BW34" s="40"/>
-      <c r="BX34" s="41"/>
-      <c r="BY34" s="42"/>
+      <c r="BX34" s="40"/>
+      <c r="BY34" s="41"/>
       <c r="BZ34" s="42"/>
-      <c r="CA34" s="42" t="s">
+      <c r="CA34" s="42"/>
+      <c r="CB34" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB34" s="49" t="s">
+      <c r="CC34" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC34" s="40"/>
-      <c r="CD34" s="38"/>
+      <c r="CD34" s="40"/>
       <c r="CE34" s="38"/>
       <c r="CF34" s="38"/>
-      <c r="CG34" s="3"/>
-      <c r="CH34" s="35"/>
+      <c r="CG34" s="38"/>
+      <c r="CH34" s="3"/>
       <c r="CI34" s="35"/>
-      <c r="CJ34" s="37"/>
+      <c r="CJ34" s="35"/>
       <c r="CK34" s="37"/>
-      <c r="CL34" s="43"/>
+      <c r="CL34" s="37"/>
+      <c r="CM34" s="43"/>
     </row>
-    <row r="35" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="124">
         <v>30</v>
       </c>
@@ -10755,47 +10819,48 @@
       <c r="BU35" s="40"/>
       <c r="BV35" s="40"/>
       <c r="BW35" s="40"/>
-      <c r="BX35" s="41" t="s">
+      <c r="BX35" s="40"/>
+      <c r="BY35" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY35" s="42" t="s">
+      <c r="BZ35" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BZ35" s="42"/>
-      <c r="CA35" s="42" t="s">
+      <c r="CA35" s="42"/>
+      <c r="CB35" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB35" s="49" t="s">
+      <c r="CC35" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC35" s="38" t="s">
+      <c r="CD35" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="CD35" s="38" t="s">
+      <c r="CE35" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="CE35" s="92" t="s">
+      <c r="CF35" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF35" s="38"/>
-      <c r="CG35" s="3"/>
-      <c r="CH35" s="35" t="s">
+      <c r="CG35" s="38"/>
+      <c r="CH35" s="3"/>
+      <c r="CI35" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI35" s="35" t="s">
+      <c r="CJ35" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ35" s="37" t="s">
+      <c r="CK35" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="CK35" s="37" t="s">
+      <c r="CL35" s="37" t="s">
         <v>720</v>
       </c>
-      <c r="CL35" s="43" t="s">
+      <c r="CM35" s="43" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="36" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="124">
         <v>31</v>
       </c>
@@ -10948,9 +11013,9 @@
       <c r="BJ36" s="40"/>
       <c r="BK36" s="40"/>
       <c r="BL36" s="40"/>
-      <c r="BM36" s="38"/>
+      <c r="BM36" s="40"/>
       <c r="BN36" s="38"/>
-      <c r="BO36" s="40"/>
+      <c r="BO36" s="38"/>
       <c r="BP36" s="40"/>
       <c r="BQ36" s="40"/>
       <c r="BR36" s="40"/>
@@ -10959,49 +11024,50 @@
       <c r="BU36" s="40"/>
       <c r="BV36" s="40"/>
       <c r="BW36" s="40"/>
-      <c r="BX36" s="41" t="s">
+      <c r="BX36" s="40"/>
+      <c r="BY36" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY36" s="42" t="s">
+      <c r="BZ36" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="BZ36" s="42"/>
-      <c r="CA36" s="42" t="s">
+      <c r="CA36" s="42"/>
+      <c r="CB36" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB36" s="49" t="s">
+      <c r="CC36" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC36" s="38" t="s">
+      <c r="CD36" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="CD36" s="38" t="s">
+      <c r="CE36" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="CE36" s="92" t="s">
+      <c r="CF36" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF36" s="38"/>
-      <c r="CG36" s="3" t="s">
+      <c r="CG36" s="38"/>
+      <c r="CH36" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="CH36" s="35" t="s">
+      <c r="CI36" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI36" s="35" t="s">
+      <c r="CJ36" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ36" s="37" t="s">
+      <c r="CK36" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK36" s="37" t="s">
+      <c r="CL36" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="CL36" s="43" t="s">
+      <c r="CM36" s="43" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="37" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="124">
         <v>32</v>
       </c>
@@ -11153,49 +11219,50 @@
       <c r="BU37" s="40"/>
       <c r="BV37" s="40"/>
       <c r="BW37" s="40"/>
-      <c r="BX37" s="41" t="s">
+      <c r="BX37" s="40"/>
+      <c r="BY37" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY37" s="42" t="s">
+      <c r="BZ37" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BZ37" s="42"/>
-      <c r="CA37" s="42" t="s">
+      <c r="CA37" s="42"/>
+      <c r="CB37" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB37" s="49" t="s">
+      <c r="CC37" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC37" s="46" t="s">
+      <c r="CD37" s="46" t="s">
         <v>245</v>
       </c>
-      <c r="CD37" s="38" t="s">
+      <c r="CE37" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="CE37" s="92" t="s">
+      <c r="CF37" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF37" s="38"/>
-      <c r="CG37" s="3" t="s">
+      <c r="CG37" s="38"/>
+      <c r="CH37" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="CH37" s="35" t="s">
+      <c r="CI37" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="CI37" s="35" t="s">
+      <c r="CJ37" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ37" s="37" t="s">
+      <c r="CK37" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK37" s="37" t="s">
+      <c r="CL37" s="37" t="s">
         <v>695</v>
       </c>
-      <c r="CL37" s="43" t="s">
+      <c r="CM37" s="43" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="38" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="124">
         <v>33</v>
       </c>
@@ -11364,43 +11431,44 @@
       <c r="BU38" s="40"/>
       <c r="BV38" s="40"/>
       <c r="BW38" s="40"/>
-      <c r="BX38" s="41" t="s">
+      <c r="BX38" s="40"/>
+      <c r="BY38" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="BY38" s="42" t="s">
+      <c r="BZ38" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BZ38" s="42"/>
-      <c r="CA38" s="42" t="s">
+      <c r="CA38" s="42"/>
+      <c r="CB38" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB38" s="49" t="s">
+      <c r="CC38" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC38" s="40" t="s">
+      <c r="CD38" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="CD38" s="40" t="s">
+      <c r="CE38" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="CE38" s="38"/>
       <c r="CF38" s="38"/>
-      <c r="CG38" s="3"/>
-      <c r="CH38" s="35" t="s">
+      <c r="CG38" s="38"/>
+      <c r="CH38" s="3"/>
+      <c r="CI38" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="CI38" s="35" t="s">
+      <c r="CJ38" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ38" s="37" t="s">
+      <c r="CK38" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="CK38" s="37"/>
-      <c r="CL38" s="43" t="s">
+      <c r="CL38" s="37"/>
+      <c r="CM38" s="43" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="39" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="124">
         <v>34</v>
       </c>
@@ -11569,43 +11637,44 @@
       <c r="BU39" s="40"/>
       <c r="BV39" s="40"/>
       <c r="BW39" s="40"/>
-      <c r="BX39" s="41" t="s">
+      <c r="BX39" s="40"/>
+      <c r="BY39" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="BY39" s="42" t="s">
+      <c r="BZ39" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BZ39" s="42"/>
-      <c r="CA39" s="42" t="s">
+      <c r="CA39" s="42"/>
+      <c r="CB39" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB39" s="49" t="s">
+      <c r="CC39" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC39" s="40" t="s">
+      <c r="CD39" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="CD39" s="40" t="s">
+      <c r="CE39" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="CE39" s="38"/>
       <c r="CF39" s="38"/>
-      <c r="CG39" s="3"/>
-      <c r="CH39" s="35" t="s">
+      <c r="CG39" s="38"/>
+      <c r="CH39" s="3"/>
+      <c r="CI39" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="CI39" s="35" t="s">
+      <c r="CJ39" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ39" s="37" t="s">
+      <c r="CK39" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="CK39" s="37"/>
-      <c r="CL39" s="43" t="s">
+      <c r="CL39" s="37"/>
+      <c r="CM39" s="43" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="40" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="124">
         <v>35</v>
       </c>
@@ -11774,45 +11843,46 @@
       <c r="BU40" s="40"/>
       <c r="BV40" s="40"/>
       <c r="BW40" s="40"/>
-      <c r="BX40" s="41" t="s">
+      <c r="BX40" s="40"/>
+      <c r="BY40" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="BY40" s="42" t="s">
+      <c r="BZ40" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BZ40" s="42"/>
-      <c r="CA40" s="42" t="s">
+      <c r="CA40" s="42"/>
+      <c r="CB40" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB40" s="49" t="s">
+      <c r="CC40" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC40" s="40" t="s">
+      <c r="CD40" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="CD40" s="40" t="s">
+      <c r="CE40" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="CE40" s="38"/>
       <c r="CF40" s="38"/>
-      <c r="CG40" s="3"/>
-      <c r="CH40" s="35" t="s">
+      <c r="CG40" s="38"/>
+      <c r="CH40" s="3"/>
+      <c r="CI40" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="CI40" s="35" t="s">
+      <c r="CJ40" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ40" s="37" t="s">
+      <c r="CK40" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="CK40" s="37" t="s">
+      <c r="CL40" s="37" t="s">
         <v>721</v>
       </c>
-      <c r="CL40" s="43" t="s">
+      <c r="CM40" s="43" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="41" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="124">
         <v>36</v>
       </c>
@@ -11973,9 +12043,9 @@
       <c r="BJ41" s="40"/>
       <c r="BK41" s="40"/>
       <c r="BL41" s="40"/>
-      <c r="BM41" s="41"/>
+      <c r="BM41" s="40"/>
       <c r="BN41" s="41"/>
-      <c r="BO41" s="40"/>
+      <c r="BO41" s="41"/>
       <c r="BP41" s="40"/>
       <c r="BQ41" s="40"/>
       <c r="BR41" s="40"/>
@@ -11984,49 +12054,50 @@
       <c r="BU41" s="40"/>
       <c r="BV41" s="40"/>
       <c r="BW41" s="40"/>
-      <c r="BX41" s="41" t="s">
+      <c r="BX41" s="40"/>
+      <c r="BY41" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY41" s="42" t="s">
+      <c r="BZ41" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BZ41" s="42"/>
-      <c r="CA41" s="42" t="s">
+      <c r="CA41" s="42"/>
+      <c r="CB41" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB41" s="49" t="s">
+      <c r="CC41" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC41" s="46" t="s">
+      <c r="CD41" s="46" t="s">
         <v>245</v>
       </c>
-      <c r="CD41" s="38" t="s">
+      <c r="CE41" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="CE41" s="92" t="s">
+      <c r="CF41" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF41" s="38"/>
-      <c r="CG41" s="3" t="s">
+      <c r="CG41" s="38"/>
+      <c r="CH41" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="CH41" s="35" t="s">
+      <c r="CI41" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI41" s="35" t="s">
+      <c r="CJ41" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ41" s="37" t="s">
+      <c r="CK41" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK41" s="37" t="s">
+      <c r="CL41" s="37" t="s">
         <v>722</v>
       </c>
-      <c r="CL41" s="43" t="s">
+      <c r="CM41" s="43" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="42" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="124">
         <v>37</v>
       </c>
@@ -12179,9 +12250,9 @@
       <c r="BJ42" s="40"/>
       <c r="BK42" s="40"/>
       <c r="BL42" s="40"/>
-      <c r="BM42" s="61"/>
+      <c r="BM42" s="40"/>
       <c r="BN42" s="61"/>
-      <c r="BO42" s="40"/>
+      <c r="BO42" s="61"/>
       <c r="BP42" s="40"/>
       <c r="BQ42" s="40"/>
       <c r="BR42" s="40"/>
@@ -12190,47 +12261,48 @@
       <c r="BU42" s="40"/>
       <c r="BV42" s="40"/>
       <c r="BW42" s="40"/>
-      <c r="BX42" s="41" t="s">
+      <c r="BX42" s="40"/>
+      <c r="BY42" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="BY42" s="42" t="s">
+      <c r="BZ42" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BZ42" s="42"/>
-      <c r="CA42" s="42" t="s">
+      <c r="CA42" s="42"/>
+      <c r="CB42" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB42" s="49" t="s">
+      <c r="CC42" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC42" s="58" t="s">
+      <c r="CD42" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="CD42" s="58" t="s">
+      <c r="CE42" s="58" t="s">
         <v>284</v>
       </c>
-      <c r="CE42" s="92" t="s">
+      <c r="CF42" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF42" s="38"/>
-      <c r="CG42" s="3"/>
-      <c r="CH42" s="35" t="s">
+      <c r="CG42" s="38"/>
+      <c r="CH42" s="3"/>
+      <c r="CI42" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI42" s="35" t="s">
+      <c r="CJ42" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ42" s="37" t="s">
+      <c r="CK42" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK42" s="140" t="s">
+      <c r="CL42" s="140" t="s">
         <v>723</v>
       </c>
-      <c r="CL42" s="43" t="s">
+      <c r="CM42" s="43" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="43" spans="1:90" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="124">
         <v>38</v>
       </c>
@@ -12394,45 +12466,46 @@
       <c r="BU43" s="40"/>
       <c r="BV43" s="40"/>
       <c r="BW43" s="40"/>
-      <c r="BX43" s="41" t="s">
+      <c r="BX43" s="40"/>
+      <c r="BY43" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="BY43" s="42" t="s">
+      <c r="BZ43" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BZ43" s="42"/>
-      <c r="CA43" s="42" t="s">
+      <c r="CA43" s="42"/>
+      <c r="CB43" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB43" s="49" t="s">
+      <c r="CC43" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC43" s="40" t="s">
+      <c r="CD43" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="CD43" s="40" t="s">
+      <c r="CE43" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="CE43" s="38"/>
       <c r="CF43" s="38"/>
-      <c r="CG43" s="3"/>
-      <c r="CH43" s="35" t="s">
+      <c r="CG43" s="38"/>
+      <c r="CH43" s="3"/>
+      <c r="CI43" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI43" s="35" t="s">
+      <c r="CJ43" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ43" s="37" t="s">
+      <c r="CK43" s="37" t="s">
         <v>353</v>
       </c>
-      <c r="CK43" s="37" t="s">
+      <c r="CL43" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="CL43" s="43" t="s">
+      <c r="CM43" s="43" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="44" spans="1:90" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="124">
         <v>39</v>
       </c>
@@ -12589,9 +12662,9 @@
       <c r="BJ44" s="40"/>
       <c r="BK44" s="40"/>
       <c r="BL44" s="40"/>
-      <c r="BM44" s="85"/>
+      <c r="BM44" s="40"/>
       <c r="BN44" s="85"/>
-      <c r="BO44" s="40"/>
+      <c r="BO44" s="85"/>
       <c r="BP44" s="40"/>
       <c r="BQ44" s="40"/>
       <c r="BR44" s="40"/>
@@ -12600,45 +12673,46 @@
       <c r="BU44" s="40"/>
       <c r="BV44" s="40"/>
       <c r="BW44" s="40"/>
-      <c r="BX44" s="41" t="s">
+      <c r="BX44" s="40"/>
+      <c r="BY44" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="BY44" s="42" t="s">
+      <c r="BZ44" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="BZ44" s="42"/>
-      <c r="CA44" s="42" t="s">
+      <c r="CA44" s="42"/>
+      <c r="CB44" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB44" s="49" t="s">
+      <c r="CC44" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC44" s="40" t="s">
+      <c r="CD44" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="CD44" s="38" t="s">
+      <c r="CE44" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="CE44" s="38"/>
       <c r="CF44" s="38"/>
-      <c r="CG44" s="3"/>
-      <c r="CH44" s="35" t="s">
+      <c r="CG44" s="38"/>
+      <c r="CH44" s="3"/>
+      <c r="CI44" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI44" s="35" t="s">
+      <c r="CJ44" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ44" s="37" t="s">
+      <c r="CK44" s="37" t="s">
         <v>357</v>
       </c>
-      <c r="CK44" s="37" t="s">
+      <c r="CL44" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="CL44" s="43" t="s">
+      <c r="CM44" s="43" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="45" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="124">
         <v>40</v>
       </c>
@@ -12791,9 +12865,9 @@
       <c r="BJ45" s="86"/>
       <c r="BK45" s="86"/>
       <c r="BL45" s="86"/>
-      <c r="BM45" s="15"/>
+      <c r="BM45" s="86"/>
       <c r="BN45" s="15"/>
-      <c r="BO45" s="86"/>
+      <c r="BO45" s="15"/>
       <c r="BP45" s="86"/>
       <c r="BQ45" s="86"/>
       <c r="BR45" s="86"/>
@@ -12802,47 +12876,48 @@
       <c r="BU45" s="86"/>
       <c r="BV45" s="86"/>
       <c r="BW45" s="86"/>
-      <c r="BX45" s="10" t="s">
+      <c r="BX45" s="86"/>
+      <c r="BY45" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY45" s="17" t="s">
+      <c r="BZ45" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BZ45" s="17"/>
-      <c r="CA45" s="17" t="s">
+      <c r="CA45" s="17"/>
+      <c r="CB45" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB45" s="49" t="s">
+      <c r="CC45" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC45" s="15" t="s">
+      <c r="CD45" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="CD45" s="15" t="s">
+      <c r="CE45" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="CE45" s="92" t="s">
+      <c r="CF45" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF45" s="22"/>
-      <c r="CG45" s="2"/>
-      <c r="CH45" s="14" t="s">
+      <c r="CG45" s="22"/>
+      <c r="CH45" s="2"/>
+      <c r="CI45" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI45" s="14" t="s">
+      <c r="CJ45" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ45" s="18" t="s">
+      <c r="CK45" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK45" s="18" t="s">
+      <c r="CL45" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="CL45" s="21" t="s">
+      <c r="CM45" s="21" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="46" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="124">
         <v>41</v>
       </c>
@@ -12996,58 +13071,59 @@
       <c r="BJ46" s="86"/>
       <c r="BK46" s="86"/>
       <c r="BL46" s="86"/>
-      <c r="BM46" s="22"/>
+      <c r="BM46" s="86"/>
       <c r="BN46" s="22"/>
-      <c r="BO46" s="86"/>
+      <c r="BO46" s="22"/>
       <c r="BP46" s="86"/>
-      <c r="BQ46" s="15"/>
+      <c r="BQ46" s="86"/>
       <c r="BR46" s="15"/>
       <c r="BS46" s="15"/>
       <c r="BT46" s="15"/>
       <c r="BU46" s="15"/>
       <c r="BV46" s="15"/>
       <c r="BW46" s="15"/>
-      <c r="BX46" s="10" t="s">
+      <c r="BX46" s="15"/>
+      <c r="BY46" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY46" s="17" t="s">
+      <c r="BZ46" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BZ46" s="17"/>
-      <c r="CA46" s="17" t="s">
+      <c r="CA46" s="17"/>
+      <c r="CB46" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB46" s="49" t="s">
+      <c r="CC46" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC46" s="54" t="s">
+      <c r="CD46" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="CD46" s="22" t="s">
+      <c r="CE46" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="CE46" s="92" t="s">
+      <c r="CF46" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF46" s="22"/>
-      <c r="CG46" s="2"/>
-      <c r="CH46" s="14" t="s">
+      <c r="CG46" s="22"/>
+      <c r="CH46" s="2"/>
+      <c r="CI46" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI46" s="14" t="s">
+      <c r="CJ46" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ46" s="18" t="s">
+      <c r="CK46" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="CK46" s="18" t="s">
+      <c r="CL46" s="18" t="s">
         <v>696</v>
       </c>
-      <c r="CL46" s="21" t="s">
+      <c r="CM46" s="21" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="47" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="124">
         <v>42</v>
       </c>
@@ -13200,58 +13276,59 @@
       <c r="BJ47" s="86"/>
       <c r="BK47" s="86"/>
       <c r="BL47" s="86"/>
-      <c r="BM47" s="15"/>
+      <c r="BM47" s="86"/>
       <c r="BN47" s="15"/>
-      <c r="BO47" s="86"/>
+      <c r="BO47" s="15"/>
       <c r="BP47" s="86"/>
-      <c r="BQ47" s="15"/>
+      <c r="BQ47" s="86"/>
       <c r="BR47" s="15"/>
       <c r="BS47" s="15"/>
       <c r="BT47" s="15"/>
       <c r="BU47" s="15"/>
       <c r="BV47" s="15"/>
       <c r="BW47" s="15"/>
-      <c r="BX47" s="10" t="s">
+      <c r="BX47" s="15"/>
+      <c r="BY47" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY47" s="17" t="s">
+      <c r="BZ47" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BZ47" s="17"/>
-      <c r="CA47" s="17" t="s">
+      <c r="CA47" s="17"/>
+      <c r="CB47" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB47" s="49" t="s">
+      <c r="CC47" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC47" s="15" t="s">
+      <c r="CD47" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD47" s="22" t="s">
+      <c r="CE47" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="CE47" s="92" t="s">
+      <c r="CF47" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF47" s="22"/>
-      <c r="CG47" s="2"/>
-      <c r="CH47" s="14" t="s">
+      <c r="CG47" s="22"/>
+      <c r="CH47" s="2"/>
+      <c r="CI47" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI47" s="14" t="s">
+      <c r="CJ47" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ47" s="18" t="s">
+      <c r="CK47" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK47" s="18" t="s">
+      <c r="CL47" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="CL47" s="21" t="s">
+      <c r="CM47" s="21" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="48" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="124">
         <v>43</v>
       </c>
@@ -13415,47 +13492,48 @@
       <c r="BU48" s="15"/>
       <c r="BV48" s="15"/>
       <c r="BW48" s="15"/>
-      <c r="BX48" s="10" t="s">
+      <c r="BX48" s="15"/>
+      <c r="BY48" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY48" s="17" t="s">
+      <c r="BZ48" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BZ48" s="17"/>
-      <c r="CA48" s="17" t="s">
+      <c r="CA48" s="17"/>
+      <c r="CB48" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB48" s="49" t="s">
+      <c r="CC48" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC48" s="15" t="s">
+      <c r="CD48" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="CD48" s="15" t="s">
+      <c r="CE48" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="CE48" s="92" t="s">
+      <c r="CF48" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF48" s="22"/>
-      <c r="CG48" s="2"/>
-      <c r="CH48" s="14" t="s">
+      <c r="CG48" s="22"/>
+      <c r="CH48" s="2"/>
+      <c r="CI48" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="CI48" s="14" t="s">
+      <c r="CJ48" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ48" s="18" t="s">
+      <c r="CK48" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK48" s="18" t="s">
+      <c r="CL48" s="18" t="s">
         <v>724</v>
       </c>
-      <c r="CL48" s="21" t="s">
+      <c r="CM48" s="21" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="49" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="124">
         <v>44</v>
       </c>
@@ -13615,60 +13693,61 @@
       <c r="BJ49" s="86"/>
       <c r="BK49" s="86"/>
       <c r="BL49" s="86"/>
-      <c r="BM49" s="87"/>
+      <c r="BM49" s="86"/>
       <c r="BN49" s="87"/>
-      <c r="BO49" s="86"/>
+      <c r="BO49" s="87"/>
       <c r="BP49" s="86"/>
-      <c r="BQ49" s="15" t="s">
+      <c r="BQ49" s="86"/>
+      <c r="BR49" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="BR49" s="15" t="s">
+      <c r="BS49" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="BS49" s="15" t="s">
+      <c r="BT49" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="BT49" s="15"/>
       <c r="BU49" s="15"/>
       <c r="BV49" s="15"/>
       <c r="BW49" s="15"/>
-      <c r="BX49" s="10" t="s">
+      <c r="BX49" s="15"/>
+      <c r="BY49" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY49" s="17" t="s">
+      <c r="BZ49" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BZ49" s="17"/>
-      <c r="CA49" s="17" t="s">
+      <c r="CA49" s="17"/>
+      <c r="CB49" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB49" s="49" t="s">
+      <c r="CC49" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC49" s="15" t="s">
+      <c r="CD49" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="CD49" s="15" t="s">
+      <c r="CE49" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="CE49" s="22"/>
       <c r="CF49" s="22"/>
-      <c r="CG49" s="2"/>
-      <c r="CH49" s="14" t="s">
+      <c r="CG49" s="22"/>
+      <c r="CH49" s="2"/>
+      <c r="CI49" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="CI49" s="14" t="s">
+      <c r="CJ49" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ49" s="18" t="s">
+      <c r="CK49" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="CK49" s="18"/>
-      <c r="CL49" s="21" t="s">
+      <c r="CL49" s="18"/>
+      <c r="CM49" s="21" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="50" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="124">
         <v>45</v>
       </c>
@@ -13821,58 +13900,59 @@
       <c r="BJ50" s="86"/>
       <c r="BK50" s="86"/>
       <c r="BL50" s="86"/>
-      <c r="BM50" s="15"/>
+      <c r="BM50" s="86"/>
       <c r="BN50" s="15"/>
-      <c r="BO50" s="86"/>
+      <c r="BO50" s="15"/>
       <c r="BP50" s="86"/>
-      <c r="BQ50" s="15"/>
+      <c r="BQ50" s="86"/>
       <c r="BR50" s="15"/>
       <c r="BS50" s="15"/>
       <c r="BT50" s="15"/>
       <c r="BU50" s="15"/>
       <c r="BV50" s="15"/>
       <c r="BW50" s="15"/>
-      <c r="BX50" s="10" t="s">
+      <c r="BX50" s="15"/>
+      <c r="BY50" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY50" s="17" t="s">
+      <c r="BZ50" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BZ50" s="17"/>
-      <c r="CA50" s="17" t="s">
+      <c r="CA50" s="17"/>
+      <c r="CB50" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB50" s="49" t="s">
+      <c r="CC50" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC50" s="15" t="s">
+      <c r="CD50" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD50" s="22" t="s">
+      <c r="CE50" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="CE50" s="92" t="s">
+      <c r="CF50" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF50" s="22"/>
-      <c r="CG50" s="2"/>
-      <c r="CH50" s="14" t="s">
+      <c r="CG50" s="22"/>
+      <c r="CH50" s="2"/>
+      <c r="CI50" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI50" s="14" t="s">
+      <c r="CJ50" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ50" s="18" t="s">
+      <c r="CK50" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="CK50" s="18" t="s">
+      <c r="CL50" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="CL50" s="21" t="s">
+      <c r="CM50" s="21" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="51" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="124">
         <v>46</v>
       </c>
@@ -14036,47 +14116,48 @@
       <c r="BU51" s="15"/>
       <c r="BV51" s="15"/>
       <c r="BW51" s="15"/>
-      <c r="BX51" s="10" t="s">
+      <c r="BX51" s="15"/>
+      <c r="BY51" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY51" s="17" t="s">
+      <c r="BZ51" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BZ51" s="17"/>
-      <c r="CA51" s="17" t="s">
+      <c r="CA51" s="17"/>
+      <c r="CB51" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB51" s="49" t="s">
+      <c r="CC51" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC51" s="15" t="s">
+      <c r="CD51" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="CD51" s="15" t="s">
+      <c r="CE51" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="CE51" s="92" t="s">
+      <c r="CF51" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF51" s="22"/>
-      <c r="CG51" s="2"/>
-      <c r="CH51" s="14" t="s">
+      <c r="CG51" s="22"/>
+      <c r="CH51" s="2"/>
+      <c r="CI51" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="CI51" s="14" t="s">
+      <c r="CJ51" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ51" s="18" t="s">
+      <c r="CK51" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="CK51" s="18" t="s">
+      <c r="CL51" s="18" t="s">
         <v>724</v>
       </c>
-      <c r="CL51" s="21" t="s">
+      <c r="CM51" s="21" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="52" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="124">
         <v>47</v>
       </c>
@@ -14236,60 +14317,61 @@
       <c r="BJ52" s="15"/>
       <c r="BK52" s="15"/>
       <c r="BL52" s="15"/>
-      <c r="BM52" s="87"/>
+      <c r="BM52" s="15"/>
       <c r="BN52" s="87"/>
-      <c r="BO52" s="15"/>
+      <c r="BO52" s="87"/>
       <c r="BP52" s="15"/>
-      <c r="BQ52" s="15" t="s">
+      <c r="BQ52" s="15"/>
+      <c r="BR52" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="BR52" s="15" t="s">
+      <c r="BS52" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="BS52" s="15" t="s">
+      <c r="BT52" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="BT52" s="15"/>
       <c r="BU52" s="15"/>
       <c r="BV52" s="15"/>
       <c r="BW52" s="15"/>
-      <c r="BX52" s="10" t="s">
+      <c r="BX52" s="15"/>
+      <c r="BY52" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY52" s="17" t="s">
+      <c r="BZ52" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BZ52" s="17"/>
-      <c r="CA52" s="17" t="s">
+      <c r="CA52" s="17"/>
+      <c r="CB52" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB52" s="49" t="s">
+      <c r="CC52" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC52" s="15" t="s">
+      <c r="CD52" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="CD52" s="15" t="s">
+      <c r="CE52" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="CE52" s="22"/>
       <c r="CF52" s="22"/>
-      <c r="CG52" s="2"/>
-      <c r="CH52" s="14" t="s">
+      <c r="CG52" s="22"/>
+      <c r="CH52" s="2"/>
+      <c r="CI52" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="CI52" s="14" t="s">
+      <c r="CJ52" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ52" s="18" t="s">
+      <c r="CK52" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="CK52" s="18"/>
-      <c r="CL52" s="21" t="s">
+      <c r="CL52" s="18"/>
+      <c r="CM52" s="21" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="53" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="124">
         <v>48</v>
       </c>
@@ -14448,62 +14530,63 @@
       <c r="BJ53" s="15"/>
       <c r="BK53" s="15"/>
       <c r="BL53" s="15"/>
-      <c r="BM53" s="87"/>
+      <c r="BM53" s="15"/>
       <c r="BN53" s="87"/>
-      <c r="BO53" s="15"/>
+      <c r="BO53" s="87"/>
       <c r="BP53" s="15"/>
-      <c r="BQ53" s="15" t="s">
+      <c r="BQ53" s="15"/>
+      <c r="BR53" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="BR53" s="15" t="s">
+      <c r="BS53" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="BS53" s="15" t="s">
+      <c r="BT53" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="BT53" s="15"/>
       <c r="BU53" s="15"/>
       <c r="BV53" s="15"/>
       <c r="BW53" s="15"/>
-      <c r="BX53" s="10" t="s">
+      <c r="BX53" s="15"/>
+      <c r="BY53" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY53" s="17" t="s">
+      <c r="BZ53" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BZ53" s="17"/>
-      <c r="CA53" s="17" t="s">
+      <c r="CA53" s="17"/>
+      <c r="CB53" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB53" s="49" t="s">
+      <c r="CC53" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC53" s="15" t="s">
+      <c r="CD53" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="CD53" s="15" t="s">
+      <c r="CE53" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="CE53" s="22"/>
       <c r="CF53" s="22"/>
-      <c r="CG53" s="2"/>
-      <c r="CH53" s="14" t="s">
+      <c r="CG53" s="22"/>
+      <c r="CH53" s="2"/>
+      <c r="CI53" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="CI53" s="14" t="s">
+      <c r="CJ53" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ53" s="18" t="s">
+      <c r="CK53" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="CK53" s="18" t="s">
+      <c r="CL53" s="18" t="s">
         <v>733</v>
       </c>
-      <c r="CL53" s="21" t="s">
+      <c r="CM53" s="21" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="54" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="124">
         <v>49</v>
       </c>
@@ -14656,60 +14739,61 @@
       <c r="BJ54" s="86"/>
       <c r="BK54" s="86"/>
       <c r="BL54" s="86"/>
-      <c r="BM54" s="15"/>
+      <c r="BM54" s="86"/>
       <c r="BN54" s="15"/>
-      <c r="BO54" s="86"/>
+      <c r="BO54" s="15"/>
       <c r="BP54" s="86"/>
-      <c r="BQ54" s="15"/>
+      <c r="BQ54" s="86"/>
       <c r="BR54" s="15"/>
       <c r="BS54" s="15"/>
       <c r="BT54" s="15"/>
       <c r="BU54" s="15"/>
       <c r="BV54" s="15"/>
       <c r="BW54" s="15"/>
-      <c r="BX54" s="10" t="s">
+      <c r="BX54" s="15"/>
+      <c r="BY54" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY54" s="17" t="s">
+      <c r="BZ54" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BZ54" s="17"/>
-      <c r="CA54" s="17" t="s">
+      <c r="CA54" s="17"/>
+      <c r="CB54" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB54" s="49" t="s">
+      <c r="CC54" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC54" s="15" t="s">
+      <c r="CD54" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD54" s="22" t="s">
+      <c r="CE54" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="CE54" s="92" t="s">
+      <c r="CF54" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF54" s="22"/>
-      <c r="CG54" s="2" t="s">
+      <c r="CG54" s="22"/>
+      <c r="CH54" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="CH54" s="14" t="s">
+      <c r="CI54" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI54" s="14" t="s">
+      <c r="CJ54" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ54" s="18" t="s">
+      <c r="CK54" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK54" s="18" t="s">
+      <c r="CL54" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="CL54" s="21" t="s">
+      <c r="CM54" s="21" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="55" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="124">
         <v>50</v>
       </c>
@@ -14873,49 +14957,50 @@
       <c r="BU55" s="15"/>
       <c r="BV55" s="15"/>
       <c r="BW55" s="15"/>
-      <c r="BX55" s="10" t="s">
+      <c r="BX55" s="15"/>
+      <c r="BY55" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="BY55" s="17" t="s">
+      <c r="BZ55" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="BZ55" s="17"/>
-      <c r="CA55" s="17" t="s">
+      <c r="CA55" s="17"/>
+      <c r="CB55" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB55" s="49" t="s">
+      <c r="CC55" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC55" s="15" t="s">
+      <c r="CD55" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="CD55" s="15" t="s">
+      <c r="CE55" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="CE55" s="92" t="s">
+      <c r="CF55" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF55" s="22"/>
-      <c r="CG55" s="2" t="s">
+      <c r="CG55" s="22"/>
+      <c r="CH55" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="CH55" s="14" t="s">
+      <c r="CI55" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="CI55" s="14" t="s">
+      <c r="CJ55" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ55" s="18" t="s">
+      <c r="CK55" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK55" s="18" t="s">
+      <c r="CL55" s="18" t="s">
         <v>724</v>
       </c>
-      <c r="CL55" s="21" t="s">
+      <c r="CM55" s="21" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="56" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="124">
         <v>51</v>
       </c>
@@ -15079,62 +15164,63 @@
       <c r="BJ56" s="15"/>
       <c r="BK56" s="15"/>
       <c r="BL56" s="15"/>
-      <c r="BM56" s="87"/>
+      <c r="BM56" s="15"/>
       <c r="BN56" s="87"/>
-      <c r="BO56" s="15"/>
+      <c r="BO56" s="87"/>
       <c r="BP56" s="15"/>
-      <c r="BQ56" s="15" t="s">
+      <c r="BQ56" s="15"/>
+      <c r="BR56" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="BR56" s="15" t="s">
+      <c r="BS56" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="BS56" s="15" t="s">
+      <c r="BT56" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="BT56" s="15"/>
       <c r="BU56" s="15"/>
       <c r="BV56" s="15"/>
       <c r="BW56" s="15"/>
-      <c r="BX56" s="10" t="s">
+      <c r="BX56" s="15"/>
+      <c r="BY56" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY56" s="17" t="s">
+      <c r="BZ56" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BZ56" s="17"/>
-      <c r="CA56" s="17" t="s">
+      <c r="CA56" s="17"/>
+      <c r="CB56" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB56" s="49" t="s">
+      <c r="CC56" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC56" s="15" t="s">
+      <c r="CD56" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="CD56" s="15" t="s">
+      <c r="CE56" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="CE56" s="22"/>
       <c r="CF56" s="22"/>
-      <c r="CG56" s="2"/>
-      <c r="CH56" s="14" t="s">
+      <c r="CG56" s="22"/>
+      <c r="CH56" s="2"/>
+      <c r="CI56" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="CI56" s="14" t="s">
+      <c r="CJ56" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ56" s="18" t="s">
+      <c r="CK56" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="CK56" s="18" t="s">
+      <c r="CL56" s="18" t="s">
         <v>708</v>
       </c>
-      <c r="CL56" s="21" t="s">
+      <c r="CM56" s="21" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="57" spans="1:90" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:91" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="124">
         <v>52</v>
       </c>
@@ -15299,47 +15385,48 @@
       <c r="BU57" s="15"/>
       <c r="BV57" s="15"/>
       <c r="BW57" s="15"/>
-      <c r="BX57" s="10" t="s">
+      <c r="BX57" s="15"/>
+      <c r="BY57" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY57" s="17" t="s">
+      <c r="BZ57" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BZ57" s="17"/>
-      <c r="CA57" s="17" t="s">
+      <c r="CA57" s="17"/>
+      <c r="CB57" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB57" s="49" t="s">
+      <c r="CC57" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC57" s="22" t="s">
+      <c r="CD57" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="CD57" s="22" t="s">
+      <c r="CE57" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="CE57" s="92" t="s">
+      <c r="CF57" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF57" s="22"/>
-      <c r="CG57" s="2"/>
-      <c r="CH57" s="14" t="s">
+      <c r="CG57" s="22"/>
+      <c r="CH57" s="2"/>
+      <c r="CI57" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI57" s="14" t="s">
+      <c r="CJ57" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ57" s="18" t="s">
+      <c r="CK57" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK57" s="18" t="s">
+      <c r="CL57" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="CL57" s="21" t="s">
+      <c r="CM57" s="21" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="58" spans="1:90" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="124">
         <v>53</v>
       </c>
@@ -15499,51 +15586,52 @@
       <c r="BQ58" s="22"/>
       <c r="BR58" s="22"/>
       <c r="BS58" s="22"/>
-      <c r="BT58" s="15"/>
+      <c r="BT58" s="22"/>
       <c r="BU58" s="15"/>
       <c r="BV58" s="15"/>
       <c r="BW58" s="15"/>
-      <c r="BX58" s="10" t="s">
+      <c r="BX58" s="15"/>
+      <c r="BY58" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY58" s="17" t="s">
+      <c r="BZ58" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BZ58" s="17"/>
-      <c r="CA58" s="17" t="s">
+      <c r="CA58" s="17"/>
+      <c r="CB58" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB58" s="49" t="s">
+      <c r="CC58" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC58" s="15" t="s">
+      <c r="CD58" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD58" s="22" t="s">
+      <c r="CE58" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="CE58" s="92" t="s">
+      <c r="CF58" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF58" s="22"/>
-      <c r="CG58" s="2"/>
-      <c r="CH58" s="14" t="s">
+      <c r="CG58" s="22"/>
+      <c r="CH58" s="2"/>
+      <c r="CI58" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI58" s="14" t="s">
+      <c r="CJ58" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ58" s="18" t="s">
+      <c r="CK58" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="CK58" s="18" t="s">
+      <c r="CL58" s="18" t="s">
         <v>725</v>
       </c>
-      <c r="CL58" s="21" t="s">
+      <c r="CM58" s="21" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="59" spans="1:90" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:91" s="9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="124">
         <v>54</v>
       </c>
@@ -15706,60 +15794,61 @@
       <c r="BN59" s="22"/>
       <c r="BO59" s="22"/>
       <c r="BP59" s="22"/>
-      <c r="BQ59" s="22" t="s">
+      <c r="BQ59" s="22"/>
+      <c r="BR59" s="22" t="s">
         <v>366</v>
       </c>
-      <c r="BR59" s="15" t="s">
+      <c r="BS59" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="BS59" s="22" t="s">
+      <c r="BT59" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="BT59" s="15"/>
       <c r="BU59" s="15"/>
       <c r="BV59" s="15"/>
       <c r="BW59" s="15"/>
-      <c r="BX59" s="10" t="s">
+      <c r="BX59" s="15"/>
+      <c r="BY59" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY59" s="17" t="s">
+      <c r="BZ59" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BZ59" s="17"/>
-      <c r="CA59" s="17" t="s">
+      <c r="CA59" s="17"/>
+      <c r="CB59" s="17" t="s">
         <v>845</v>
       </c>
-      <c r="CB59" s="49" t="s">
+      <c r="CC59" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC59" s="15" t="s">
+      <c r="CD59" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="CD59" s="22" t="s">
+      <c r="CE59" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="CE59" s="92" t="s">
+      <c r="CF59" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF59" s="22"/>
-      <c r="CG59" s="2"/>
-      <c r="CH59" s="14" t="s">
+      <c r="CG59" s="22"/>
+      <c r="CH59" s="2"/>
+      <c r="CI59" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="CI59" s="14" t="s">
+      <c r="CJ59" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="CJ59" s="18" t="s">
+      <c r="CK59" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="CK59" s="18" t="s">
+      <c r="CL59" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="CL59" s="21" t="s">
+      <c r="CM59" s="21" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="60" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="124">
         <v>55</v>
       </c>
@@ -15914,56 +16003,57 @@
       <c r="BL60" s="38"/>
       <c r="BM60" s="40"/>
       <c r="BN60" s="40"/>
-      <c r="BO60" s="38"/>
+      <c r="BO60" s="40"/>
       <c r="BP60" s="38"/>
       <c r="BQ60" s="38"/>
-      <c r="BR60" s="40"/>
-      <c r="BS60" s="38"/>
-      <c r="BT60" s="40"/>
+      <c r="BR60" s="38"/>
+      <c r="BS60" s="40"/>
+      <c r="BT60" s="38"/>
       <c r="BU60" s="40"/>
       <c r="BV60" s="40"/>
       <c r="BW60" s="40"/>
-      <c r="BX60" s="41" t="s">
+      <c r="BX60" s="40"/>
+      <c r="BY60" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="BY60" s="42" t="s">
+      <c r="BZ60" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="BZ60" s="42"/>
-      <c r="CA60" s="42" t="s">
+      <c r="CA60" s="42"/>
+      <c r="CB60" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB60" s="49" t="s">
+      <c r="CC60" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC60" s="40" t="s">
+      <c r="CD60" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="CD60" s="38" t="s">
+      <c r="CE60" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="CE60" s="131">
+      <c r="CF60" s="131">
         <v>200206</v>
       </c>
-      <c r="CF60" s="95"/>
-      <c r="CG60" s="3"/>
-      <c r="CH60" s="35" t="s">
+      <c r="CG60" s="95"/>
+      <c r="CH60" s="3"/>
+      <c r="CI60" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI60" s="35" t="s">
+      <c r="CJ60" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="CJ60" s="37" t="s">
+      <c r="CK60" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK60" s="37" t="s">
+      <c r="CL60" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="CL60" s="43" t="s">
+      <c r="CM60" s="43" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="61" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="124">
         <v>56</v>
       </c>
@@ -16118,56 +16208,57 @@
       <c r="BL61" s="38"/>
       <c r="BM61" s="40"/>
       <c r="BN61" s="40"/>
-      <c r="BO61" s="38"/>
+      <c r="BO61" s="40"/>
       <c r="BP61" s="38"/>
       <c r="BQ61" s="38"/>
       <c r="BR61" s="38"/>
       <c r="BS61" s="38"/>
-      <c r="BT61" s="40"/>
+      <c r="BT61" s="38"/>
       <c r="BU61" s="40"/>
       <c r="BV61" s="40"/>
       <c r="BW61" s="40"/>
-      <c r="BX61" s="41" t="s">
+      <c r="BX61" s="40"/>
+      <c r="BY61" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="BY61" s="42" t="s">
+      <c r="BZ61" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="BZ61" s="42"/>
-      <c r="CA61" s="42" t="s">
+      <c r="CA61" s="42"/>
+      <c r="CB61" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB61" s="49" t="s">
+      <c r="CC61" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC61" s="40" t="s">
+      <c r="CD61" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="CD61" s="38" t="s">
+      <c r="CE61" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="CE61" s="95" t="s">
+      <c r="CF61" s="95" t="s">
         <v>500</v>
       </c>
-      <c r="CF61" s="95"/>
       <c r="CG61" s="95"/>
-      <c r="CH61" s="35" t="s">
+      <c r="CH61" s="95"/>
+      <c r="CI61" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="CI61" s="3" t="s">
+      <c r="CJ61" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="CJ61" s="37" t="s">
+      <c r="CK61" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK61" s="37" t="s">
+      <c r="CL61" s="37" t="s">
         <v>692</v>
       </c>
-      <c r="CL61" s="43" t="s">
+      <c r="CM61" s="43" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="62" spans="1:90" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:91" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="124">
         <v>57</v>
       </c>
@@ -16330,58 +16421,59 @@
       <c r="BN62" s="38"/>
       <c r="BO62" s="38"/>
       <c r="BP62" s="38"/>
-      <c r="BQ62" s="38" t="s">
+      <c r="BQ62" s="38"/>
+      <c r="BR62" s="38" t="s">
         <v>366</v>
       </c>
-      <c r="BR62" s="40" t="s">
+      <c r="BS62" s="40" t="s">
         <v>367</v>
       </c>
-      <c r="BS62" s="38" t="s">
+      <c r="BT62" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="BT62" s="40"/>
       <c r="BU62" s="40"/>
       <c r="BV62" s="40"/>
       <c r="BW62" s="40"/>
-      <c r="BX62" s="41" t="s">
+      <c r="BX62" s="40"/>
+      <c r="BY62" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="BY62" s="42" t="s">
+      <c r="BZ62" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="BZ62" s="42"/>
-      <c r="CA62" s="42" t="s">
+      <c r="CA62" s="42"/>
+      <c r="CB62" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB62" s="49" t="s">
+      <c r="CC62" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC62" s="40" t="s">
+      <c r="CD62" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="CD62" s="3" t="s">
+      <c r="CE62" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="CE62" s="38"/>
       <c r="CF62" s="38"/>
-      <c r="CG62" s="3"/>
-      <c r="CH62" s="35" t="s">
+      <c r="CG62" s="38"/>
+      <c r="CH62" s="3"/>
+      <c r="CI62" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="CI62" s="35" t="s">
+      <c r="CJ62" s="35" t="s">
         <v>444</v>
       </c>
-      <c r="CJ62" s="37" t="s">
+      <c r="CK62" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="CK62" s="37" t="s">
+      <c r="CL62" s="37" t="s">
         <v>726</v>
       </c>
-      <c r="CL62" s="43" t="s">
+      <c r="CM62" s="43" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="63" spans="1:90" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="124">
         <v>58</v>
       </c>
@@ -16553,45 +16645,46 @@
       <c r="BU63" s="40"/>
       <c r="BV63" s="40"/>
       <c r="BW63" s="40"/>
-      <c r="BX63" s="41" t="s">
+      <c r="BX63" s="40"/>
+      <c r="BY63" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="BY63" s="42" t="s">
+      <c r="BZ63" s="42" t="s">
         <v>812</v>
       </c>
-      <c r="BZ63" s="42"/>
-      <c r="CA63" s="42" t="s">
+      <c r="CA63" s="42"/>
+      <c r="CB63" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB63" s="49" t="s">
+      <c r="CC63" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC63" s="96" t="s">
+      <c r="CD63" s="96" t="s">
         <v>245</v>
       </c>
-      <c r="CD63" s="3" t="s">
+      <c r="CE63" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="CE63" s="131">
+      <c r="CF63" s="131">
         <v>200206</v>
       </c>
-      <c r="CF63" s="95"/>
       <c r="CG63" s="95"/>
-      <c r="CH63" s="3" t="s">
+      <c r="CH63" s="95"/>
+      <c r="CI63" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="CI63" s="3" t="s">
+      <c r="CJ63" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="CJ63" s="37" t="s">
+      <c r="CK63" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK63" s="37"/>
-      <c r="CL63" s="43" t="s">
+      <c r="CL63" s="37"/>
+      <c r="CM63" s="43" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="64" spans="1:90" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:91" s="23" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="124">
         <v>59</v>
       </c>
@@ -16755,47 +16848,48 @@
       <c r="BU64" s="40"/>
       <c r="BV64" s="40"/>
       <c r="BW64" s="40"/>
-      <c r="BX64" s="41" t="s">
+      <c r="BX64" s="40"/>
+      <c r="BY64" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="BY64" s="42" t="s">
+      <c r="BZ64" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="BZ64" s="42"/>
-      <c r="CA64" s="42" t="s">
+      <c r="CA64" s="42"/>
+      <c r="CB64" s="42" t="s">
         <v>845</v>
       </c>
-      <c r="CB64" s="49" t="s">
+      <c r="CC64" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC64" s="96">
+      <c r="CD64" s="96">
         <v>162640</v>
       </c>
-      <c r="CD64" s="3" t="s">
+      <c r="CE64" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="CE64" s="132">
+      <c r="CF64" s="132">
         <v>201189</v>
       </c>
-      <c r="CF64" s="3"/>
-      <c r="CG64" s="95"/>
-      <c r="CH64" s="3" t="s">
+      <c r="CG64" s="3"/>
+      <c r="CH64" s="95"/>
+      <c r="CI64" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="CI64" s="3" t="s">
+      <c r="CJ64" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="CJ64" s="37" t="s">
+      <c r="CK64" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="CK64" s="37" t="s">
+      <c r="CL64" s="37" t="s">
         <v>727</v>
       </c>
-      <c r="CL64" s="43" t="s">
+      <c r="CM64" s="43" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="65" spans="1:121" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="124">
         <v>60</v>
       </c>
@@ -16968,47 +17062,48 @@
       <c r="BU65" s="22"/>
       <c r="BV65" s="22"/>
       <c r="BW65" s="22"/>
-      <c r="BX65" s="20" t="s">
+      <c r="BX65" s="22"/>
+      <c r="BY65" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY65" s="49" t="s">
+      <c r="BZ65" s="49" t="s">
         <v>812</v>
       </c>
-      <c r="BZ65" s="49"/>
-      <c r="CA65" s="49" t="s">
+      <c r="CA65" s="49"/>
+      <c r="CB65" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB65" s="49" t="s">
+      <c r="CC65" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC65" s="49">
+      <c r="CD65" s="49">
         <v>201383</v>
       </c>
-      <c r="CD65" s="2" t="s">
+      <c r="CE65" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="CE65" s="131">
+      <c r="CF65" s="131">
         <v>200206</v>
       </c>
-      <c r="CF65" s="97"/>
-      <c r="CG65" s="97" t="s">
+      <c r="CG65" s="97"/>
+      <c r="CH65" s="97" t="s">
         <v>496</v>
       </c>
-      <c r="CH65" s="2" t="s">
+      <c r="CI65" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="CI65" s="2" t="s">
+      <c r="CJ65" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="CJ65" s="18" t="s">
+      <c r="CK65" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK65" s="18"/>
-      <c r="CL65" s="21" t="s">
+      <c r="CL65" s="18"/>
+      <c r="CM65" s="21" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="66" spans="1:121" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="124">
         <v>61</v>
       </c>
@@ -17169,53 +17264,54 @@
       <c r="BQ66" s="22"/>
       <c r="BR66" s="22"/>
       <c r="BS66" s="22"/>
-      <c r="BT66" s="15"/>
+      <c r="BT66" s="22"/>
       <c r="BU66" s="15"/>
       <c r="BV66" s="15"/>
       <c r="BW66" s="15"/>
-      <c r="BX66" s="10" t="s">
+      <c r="BX66" s="15"/>
+      <c r="BY66" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY66" s="17" t="s">
+      <c r="BZ66" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BZ66" s="17"/>
-      <c r="CA66" s="49" t="s">
+      <c r="CA66" s="17"/>
+      <c r="CB66" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB66" s="49" t="s">
+      <c r="CC66" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC66" s="49">
+      <c r="CD66" s="49">
         <v>162640</v>
       </c>
-      <c r="CD66" s="2" t="s">
+      <c r="CE66" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="CE66" s="92" t="s">
+      <c r="CF66" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF66" s="22"/>
-      <c r="CG66" s="97" t="s">
+      <c r="CG66" s="22"/>
+      <c r="CH66" s="97" t="s">
         <v>471</v>
       </c>
-      <c r="CH66" s="2" t="s">
+      <c r="CI66" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="CI66" s="2" t="s">
+      <c r="CJ66" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ66" s="18" t="s">
+      <c r="CK66" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK66" s="18" t="s">
+      <c r="CL66" s="18" t="s">
         <v>728</v>
       </c>
-      <c r="CL66" s="21" t="s">
+      <c r="CM66" s="21" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="67" spans="1:121" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="124">
         <v>62</v>
       </c>
@@ -17378,51 +17474,52 @@
       <c r="BQ67" s="22"/>
       <c r="BR67" s="22"/>
       <c r="BS67" s="22"/>
-      <c r="BT67" s="15"/>
+      <c r="BT67" s="22"/>
       <c r="BU67" s="15"/>
       <c r="BV67" s="15"/>
       <c r="BW67" s="15"/>
-      <c r="BX67" s="10" t="s">
+      <c r="BX67" s="15"/>
+      <c r="BY67" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="BY67" s="17" t="s">
+      <c r="BZ67" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="BZ67" s="17"/>
-      <c r="CA67" s="49" t="s">
+      <c r="CA67" s="17"/>
+      <c r="CB67" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB67" s="49" t="s">
+      <c r="CC67" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC67" s="49" t="s">
+      <c r="CD67" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="CD67" s="2" t="s">
+      <c r="CE67" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="CE67" s="97" t="s">
+      <c r="CF67" s="97" t="s">
         <v>506</v>
       </c>
-      <c r="CF67" s="97"/>
       <c r="CG67" s="97"/>
-      <c r="CH67" s="2" t="s">
+      <c r="CH67" s="97"/>
+      <c r="CI67" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="CI67" s="2" t="s">
+      <c r="CJ67" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ67" s="18" t="s">
+      <c r="CK67" s="18" t="s">
         <v>501</v>
       </c>
-      <c r="CK67" s="18" t="s">
+      <c r="CL67" s="18" t="s">
         <v>729</v>
       </c>
-      <c r="CL67" s="21" t="s">
+      <c r="CM67" s="21" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="68" spans="1:121" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="124">
         <v>63</v>
       </c>
@@ -17588,58 +17685,59 @@
       <c r="BN68" s="22"/>
       <c r="BO68" s="22"/>
       <c r="BP68" s="22"/>
-      <c r="BQ68" s="22" t="s">
+      <c r="BQ68" s="22"/>
+      <c r="BR68" s="22" t="s">
         <v>366</v>
       </c>
-      <c r="BR68" s="22" t="s">
+      <c r="BS68" s="22" t="s">
         <v>367</v>
       </c>
-      <c r="BS68" s="22" t="s">
+      <c r="BT68" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="BT68" s="22"/>
       <c r="BU68" s="22"/>
       <c r="BV68" s="22"/>
       <c r="BW68" s="22"/>
-      <c r="BX68" s="20" t="s">
+      <c r="BX68" s="22"/>
+      <c r="BY68" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY68" s="49" t="s">
+      <c r="BZ68" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ68" s="49"/>
-      <c r="CA68" s="49" t="s">
+      <c r="CA68" s="49"/>
+      <c r="CB68" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB68" s="49" t="s">
+      <c r="CC68" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC68" s="49">
+      <c r="CD68" s="49">
         <v>162642</v>
       </c>
-      <c r="CD68" s="2" t="s">
+      <c r="CE68" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="CE68" s="97"/>
       <c r="CF68" s="97"/>
       <c r="CG68" s="97"/>
-      <c r="CH68" s="2" t="s">
+      <c r="CH68" s="97"/>
+      <c r="CI68" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="CI68" s="2" t="s">
+      <c r="CJ68" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ68" s="18" t="s">
+      <c r="CK68" s="18" t="s">
         <v>511</v>
       </c>
-      <c r="CK68" s="18" t="s">
+      <c r="CL68" s="18" t="s">
         <v>730</v>
       </c>
-      <c r="CL68" s="21" t="s">
+      <c r="CM68" s="21" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="69" spans="1:121" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:122" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="124">
         <v>64</v>
       </c>
@@ -17804,47 +17902,48 @@
       <c r="BU69" s="22"/>
       <c r="BV69" s="22"/>
       <c r="BW69" s="22"/>
-      <c r="BX69" s="20" t="s">
+      <c r="BX69" s="22"/>
+      <c r="BY69" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY69" s="49" t="s">
+      <c r="BZ69" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ69" s="49"/>
-      <c r="CA69" s="49" t="s">
+      <c r="CA69" s="49"/>
+      <c r="CB69" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB69" s="49" t="s">
+      <c r="CC69" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC69" s="15" t="s">
+      <c r="CD69" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="CD69" s="15" t="s">
+      <c r="CE69" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="CE69" s="92" t="s">
+      <c r="CF69" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF69" s="22"/>
-      <c r="CG69" s="97" t="s">
+      <c r="CG69" s="22"/>
+      <c r="CH69" s="97" t="s">
         <v>520</v>
       </c>
-      <c r="CH69" s="2" t="s">
+      <c r="CI69" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="CI69" s="2" t="s">
+      <c r="CJ69" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ69" s="18" t="s">
+      <c r="CK69" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK69" s="18"/>
-      <c r="CL69" s="21" t="s">
+      <c r="CL69" s="18"/>
+      <c r="CM69" s="21" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="70" spans="1:121" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:122" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="124">
         <v>65</v>
       </c>
@@ -18019,45 +18118,46 @@
       <c r="BU70" s="22"/>
       <c r="BV70" s="22"/>
       <c r="BW70" s="22"/>
-      <c r="BX70" s="20" t="s">
+      <c r="BX70" s="22"/>
+      <c r="BY70" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY70" s="49" t="s">
+      <c r="BZ70" s="49" t="s">
         <v>812</v>
       </c>
-      <c r="BZ70" s="49"/>
-      <c r="CA70" s="49" t="s">
+      <c r="CA70" s="49"/>
+      <c r="CB70" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB70" s="49" t="s">
+      <c r="CC70" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC70" s="22" t="s">
+      <c r="CD70" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="CD70" s="22" t="s">
+      <c r="CE70" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="CE70" s="92" t="s">
+      <c r="CF70" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF70" s="22"/>
-      <c r="CG70" s="2"/>
-      <c r="CH70" s="2" t="s">
+      <c r="CG70" s="22"/>
+      <c r="CH70" s="2"/>
+      <c r="CI70" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="CI70" s="2" t="s">
+      <c r="CJ70" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ70" s="18" t="s">
+      <c r="CK70" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK70" s="18"/>
-      <c r="CL70" s="21" t="s">
+      <c r="CL70" s="18"/>
+      <c r="CM70" s="21" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="71" spans="1:121" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:122" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="124">
         <v>66</v>
       </c>
@@ -18232,44 +18332,44 @@
       <c r="BU71" s="22"/>
       <c r="BV71" s="22"/>
       <c r="BW71" s="22"/>
-      <c r="BX71" s="20" t="s">
+      <c r="BX71" s="22"/>
+      <c r="BY71" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY71" s="49" t="s">
+      <c r="BZ71" s="49" t="s">
         <v>812</v>
       </c>
-      <c r="BZ71" s="49"/>
-      <c r="CA71" s="49" t="s">
+      <c r="CA71" s="49"/>
+      <c r="CB71" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB71" s="49" t="s">
+      <c r="CC71" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC71" s="22" t="s">
+      <c r="CD71" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="CD71" s="22" t="s">
+      <c r="CE71" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="CE71" s="92" t="s">
+      <c r="CF71" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF71" s="22"/>
-      <c r="CG71" s="2"/>
-      <c r="CH71" s="2" t="s">
+      <c r="CG71" s="22"/>
+      <c r="CH71" s="2"/>
+      <c r="CI71" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="CI71" s="2" t="s">
+      <c r="CJ71" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ71" s="18" t="s">
+      <c r="CK71" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK71" s="18"/>
-      <c r="CL71" s="21" t="s">
+      <c r="CL71" s="18"/>
+      <c r="CM71" s="21" t="s">
         <v>685</v>
       </c>
-      <c r="CM71" s="88"/>
       <c r="CN71" s="88"/>
       <c r="CO71" s="88"/>
       <c r="CP71" s="88"/>
@@ -18300,8 +18400,9 @@
       <c r="DO71" s="88"/>
       <c r="DP71" s="88"/>
       <c r="DQ71" s="88"/>
+      <c r="DR71" s="88"/>
     </row>
-    <row r="72" spans="1:121" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:122" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="124">
         <v>67</v>
       </c>
@@ -18467,46 +18568,46 @@
       <c r="BU72" s="22"/>
       <c r="BV72" s="22"/>
       <c r="BW72" s="22"/>
-      <c r="BX72" s="20" t="s">
+      <c r="BX72" s="22"/>
+      <c r="BY72" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY72" s="49" t="s">
+      <c r="BZ72" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ72" s="49"/>
-      <c r="CA72" s="49" t="s">
+      <c r="CA72" s="49"/>
+      <c r="CB72" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB72" s="49" t="s">
+      <c r="CC72" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC72" s="49" t="s">
+      <c r="CD72" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="CD72" s="2" t="s">
+      <c r="CE72" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="CE72" s="92" t="s">
+      <c r="CF72" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF72" s="22"/>
-      <c r="CG72" s="2"/>
-      <c r="CH72" s="2" t="s">
+      <c r="CG72" s="22"/>
+      <c r="CH72" s="2"/>
+      <c r="CI72" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="CI72" s="2" t="s">
+      <c r="CJ72" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ72" s="18" t="s">
+      <c r="CK72" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK72" s="18" t="s">
+      <c r="CL72" s="18" t="s">
         <v>731</v>
       </c>
-      <c r="CL72" s="21" t="s">
+      <c r="CM72" s="21" t="s">
         <v>670</v>
       </c>
-      <c r="CM72" s="88"/>
       <c r="CN72" s="88"/>
       <c r="CO72" s="88"/>
       <c r="CP72" s="88"/>
@@ -18537,8 +18638,9 @@
       <c r="DO72" s="88"/>
       <c r="DP72" s="88"/>
       <c r="DQ72" s="88"/>
+      <c r="DR72" s="88"/>
     </row>
-    <row r="73" spans="1:121" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="124">
         <v>68</v>
       </c>
@@ -18705,47 +18807,48 @@
       <c r="BU73" s="38"/>
       <c r="BV73" s="38"/>
       <c r="BW73" s="38"/>
-      <c r="BX73" s="34" t="s">
+      <c r="BX73" s="38"/>
+      <c r="BY73" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY73" s="96" t="s">
+      <c r="BZ73" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BZ73" s="96"/>
-      <c r="CA73" s="96" t="s">
+      <c r="CA73" s="96"/>
+      <c r="CB73" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB73" s="49" t="s">
+      <c r="CC73" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC73" s="38" t="s">
+      <c r="CD73" s="38" t="s">
         <v>513</v>
       </c>
-      <c r="CD73" s="38" t="s">
+      <c r="CE73" s="38" t="s">
         <v>514</v>
       </c>
-      <c r="CE73" s="92" t="s">
+      <c r="CF73" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF73" s="38"/>
-      <c r="CG73" s="3" t="s">
+      <c r="CG73" s="38"/>
+      <c r="CH73" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="CH73" s="3" t="s">
+      <c r="CI73" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI73" s="3" t="s">
+      <c r="CJ73" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ73" s="37" t="s">
+      <c r="CK73" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK73" s="37"/>
-      <c r="CL73" s="43" t="s">
+      <c r="CL73" s="37"/>
+      <c r="CM73" s="43" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="74" spans="1:121" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="124">
         <v>69</v>
       </c>
@@ -18912,45 +19015,46 @@
       <c r="BU74" s="38"/>
       <c r="BV74" s="38"/>
       <c r="BW74" s="38"/>
-      <c r="BX74" s="34" t="s">
+      <c r="BX74" s="38"/>
+      <c r="BY74" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY74" s="96" t="s">
+      <c r="BZ74" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BZ74" s="96"/>
-      <c r="CA74" s="96" t="s">
+      <c r="CA74" s="96"/>
+      <c r="CB74" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB74" s="49" t="s">
+      <c r="CC74" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC74" s="38" t="s">
+      <c r="CD74" s="38" t="s">
         <v>513</v>
       </c>
-      <c r="CD74" s="38" t="s">
+      <c r="CE74" s="38" t="s">
         <v>514</v>
       </c>
-      <c r="CE74" s="92" t="s">
+      <c r="CF74" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF74" s="38"/>
-      <c r="CG74" s="3"/>
-      <c r="CH74" s="3" t="s">
+      <c r="CG74" s="38"/>
+      <c r="CH74" s="3"/>
+      <c r="CI74" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI74" s="3" t="s">
+      <c r="CJ74" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ74" s="37" t="s">
+      <c r="CK74" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK74" s="37"/>
-      <c r="CL74" s="43" t="s">
+      <c r="CL74" s="37"/>
+      <c r="CM74" s="43" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="75" spans="1:121" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="124">
         <v>70</v>
       </c>
@@ -19112,56 +19216,57 @@
       <c r="BN75" s="38"/>
       <c r="BO75" s="38"/>
       <c r="BP75" s="38"/>
-      <c r="BQ75" s="38" t="s">
+      <c r="BQ75" s="38"/>
+      <c r="BR75" s="38" t="s">
         <v>366</v>
       </c>
-      <c r="BR75" s="38" t="s">
+      <c r="BS75" s="38" t="s">
         <v>367</v>
       </c>
-      <c r="BS75" s="38" t="s">
+      <c r="BT75" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="BT75" s="38"/>
       <c r="BU75" s="38"/>
       <c r="BV75" s="38"/>
       <c r="BW75" s="38"/>
-      <c r="BX75" s="34" t="s">
+      <c r="BX75" s="38"/>
+      <c r="BY75" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY75" s="96" t="s">
+      <c r="BZ75" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BZ75" s="96"/>
-      <c r="CA75" s="96" t="s">
+      <c r="CA75" s="96"/>
+      <c r="CB75" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB75" s="49" t="s">
+      <c r="CC75" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC75" s="38" t="s">
+      <c r="CD75" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="CD75" s="38" t="s">
+      <c r="CE75" s="38" t="s">
         <v>586</v>
       </c>
-      <c r="CE75" s="38"/>
       <c r="CF75" s="38"/>
-      <c r="CG75" s="3"/>
-      <c r="CH75" s="3" t="s">
+      <c r="CG75" s="38"/>
+      <c r="CH75" s="3"/>
+      <c r="CI75" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="CI75" s="3" t="s">
+      <c r="CJ75" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ75" s="37" t="s">
+      <c r="CK75" s="37" t="s">
         <v>681</v>
       </c>
-      <c r="CK75" s="37"/>
-      <c r="CL75" s="43" t="s">
+      <c r="CL75" s="37"/>
+      <c r="CM75" s="43" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="76" spans="1:121" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="124">
         <v>71</v>
       </c>
@@ -19328,43 +19433,44 @@
       <c r="BU76" s="38"/>
       <c r="BV76" s="38"/>
       <c r="BW76" s="38"/>
-      <c r="BX76" s="34" t="s">
+      <c r="BX76" s="38"/>
+      <c r="BY76" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY76" s="96" t="s">
+      <c r="BZ76" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BZ76" s="96"/>
-      <c r="CA76" s="96" t="s">
+      <c r="CA76" s="96"/>
+      <c r="CB76" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB76" s="49" t="s">
+      <c r="CC76" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC76" s="38" t="s">
+      <c r="CD76" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="CD76" s="38" t="s">
+      <c r="CE76" s="38" t="s">
         <v>587</v>
       </c>
-      <c r="CE76" s="92" t="s">
+      <c r="CF76" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF76" s="38"/>
-      <c r="CG76" s="3"/>
-      <c r="CH76" s="3" t="s">
+      <c r="CG76" s="38"/>
+      <c r="CH76" s="3"/>
+      <c r="CI76" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI76" s="3" t="s">
+      <c r="CJ76" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ76" s="37" t="s">
+      <c r="CK76" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK76" s="37"/>
-      <c r="CL76" s="43"/>
+      <c r="CL76" s="37"/>
+      <c r="CM76" s="43"/>
     </row>
-    <row r="77" spans="1:121" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="124">
         <v>72</v>
       </c>
@@ -19531,49 +19637,50 @@
       <c r="BU77" s="38"/>
       <c r="BV77" s="38"/>
       <c r="BW77" s="38"/>
-      <c r="BX77" s="34" t="s">
+      <c r="BX77" s="38"/>
+      <c r="BY77" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY77" s="96" t="s">
+      <c r="BZ77" s="96" t="s">
         <v>812</v>
       </c>
-      <c r="BZ77" s="96"/>
-      <c r="CA77" s="96" t="s">
+      <c r="CA77" s="96"/>
+      <c r="CB77" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB77" s="49" t="s">
+      <c r="CC77" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC77" s="38" t="s">
+      <c r="CD77" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="CD77" s="38" t="s">
+      <c r="CE77" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="CE77" s="92" t="s">
+      <c r="CF77" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF77" s="3">
+      <c r="CG77" s="3">
         <v>1540746</v>
       </c>
-      <c r="CG77" s="3"/>
-      <c r="CH77" s="3" t="s">
+      <c r="CH77" s="3"/>
+      <c r="CI77" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI77" s="3" t="s">
+      <c r="CJ77" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ77" s="37" t="s">
+      <c r="CK77" s="37" t="s">
         <v>697</v>
       </c>
-      <c r="CK77" s="37" t="s">
+      <c r="CL77" s="37" t="s">
         <v>732</v>
       </c>
-      <c r="CL77" s="43" t="s">
+      <c r="CM77" s="43" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="78" spans="1:121" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="124">
         <v>73</v>
       </c>
@@ -19740,49 +19847,50 @@
       <c r="BU78" s="38"/>
       <c r="BV78" s="38"/>
       <c r="BW78" s="38"/>
-      <c r="BX78" s="34" t="s">
+      <c r="BX78" s="38"/>
+      <c r="BY78" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY78" s="96" t="s">
+      <c r="BZ78" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BZ78" s="96"/>
-      <c r="CA78" s="96" t="s">
+      <c r="CA78" s="96"/>
+      <c r="CB78" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB78" s="49" t="s">
+      <c r="CC78" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC78" s="38" t="s">
+      <c r="CD78" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="CD78" s="38" t="s">
+      <c r="CE78" s="38" t="s">
         <v>587</v>
       </c>
-      <c r="CE78" s="92" t="s">
+      <c r="CF78" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF78" s="3">
+      <c r="CG78" s="3">
         <v>1272212</v>
       </c>
-      <c r="CG78" s="3" t="s">
+      <c r="CH78" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="CH78" s="3" t="s">
+      <c r="CI78" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI78" s="3" t="s">
+      <c r="CJ78" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ78" s="37" t="s">
+      <c r="CK78" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK78" s="37"/>
-      <c r="CL78" s="43" t="s">
+      <c r="CL78" s="37"/>
+      <c r="CM78" s="43" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="79" spans="1:121" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:122" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="124">
         <v>74</v>
       </c>
@@ -19949,49 +20057,50 @@
       <c r="BU79" s="38"/>
       <c r="BV79" s="38"/>
       <c r="BW79" s="38"/>
-      <c r="BX79" s="34" t="s">
+      <c r="BX79" s="38"/>
+      <c r="BY79" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY79" s="96" t="s">
+      <c r="BZ79" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BZ79" s="96"/>
-      <c r="CA79" s="96" t="s">
+      <c r="CA79" s="96"/>
+      <c r="CB79" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB79" s="49" t="s">
+      <c r="CC79" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC79" s="38" t="s">
+      <c r="CD79" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="CD79" s="38" t="s">
+      <c r="CE79" s="38" t="s">
         <v>586</v>
       </c>
-      <c r="CE79" s="92" t="s">
+      <c r="CF79" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF79" s="38" t="s">
+      <c r="CG79" s="38" t="s">
         <v>700</v>
       </c>
-      <c r="CG79" s="3" t="s">
+      <c r="CH79" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="CH79" s="3" t="s">
+      <c r="CI79" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI79" s="3" t="s">
+      <c r="CJ79" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ79" s="37" t="s">
+      <c r="CK79" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK79" s="37"/>
-      <c r="CL79" s="43" t="s">
+      <c r="CL79" s="37"/>
+      <c r="CM79" s="43" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="80" spans="1:121" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:122" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="124">
         <v>75</v>
       </c>
@@ -20158,51 +20267,52 @@
       <c r="BU80" s="38"/>
       <c r="BV80" s="38"/>
       <c r="BW80" s="38"/>
-      <c r="BX80" s="34" t="s">
+      <c r="BX80" s="38"/>
+      <c r="BY80" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY80" s="96" t="s">
+      <c r="BZ80" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BZ80" s="96"/>
-      <c r="CA80" s="96" t="s">
+      <c r="CA80" s="96"/>
+      <c r="CB80" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB80" s="49" t="s">
+      <c r="CC80" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC80" s="38" t="s">
+      <c r="CD80" s="38" t="s">
         <v>513</v>
       </c>
-      <c r="CD80" s="38" t="s">
+      <c r="CE80" s="38" t="s">
         <v>514</v>
       </c>
-      <c r="CE80" s="92" t="s">
+      <c r="CF80" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF80" s="38" t="s">
+      <c r="CG80" s="38" t="s">
         <v>700</v>
       </c>
-      <c r="CG80" s="3" t="s">
+      <c r="CH80" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="CH80" s="3" t="s">
+      <c r="CI80" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI80" s="3" t="s">
+      <c r="CJ80" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ80" s="37" t="s">
+      <c r="CK80" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="CK80" s="37" t="s">
+      <c r="CL80" s="37" t="s">
         <v>749</v>
       </c>
-      <c r="CL80" s="43" t="s">
+      <c r="CM80" s="43" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="81" spans="1:90" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:91" s="48" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="124">
         <v>76</v>
       </c>
@@ -20379,49 +20489,50 @@
       <c r="BU81" s="38"/>
       <c r="BV81" s="38"/>
       <c r="BW81" s="38"/>
-      <c r="BX81" s="34" t="s">
+      <c r="BX81" s="38"/>
+      <c r="BY81" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY81" s="96" t="s">
+      <c r="BZ81" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BZ81" s="96"/>
-      <c r="CA81" s="96" t="s">
+      <c r="CA81" s="96"/>
+      <c r="CB81" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB81" s="49" t="s">
+      <c r="CC81" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC81" s="38" t="s">
+      <c r="CD81" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="CD81" s="38" t="s">
+      <c r="CE81" s="38" t="s">
         <v>586</v>
       </c>
-      <c r="CE81" s="147" t="s">
+      <c r="CF81" s="147" t="s">
         <v>741</v>
       </c>
-      <c r="CF81" s="3">
+      <c r="CG81" s="3">
         <v>1540746</v>
       </c>
-      <c r="CG81" s="3"/>
-      <c r="CH81" s="3" t="s">
+      <c r="CH81" s="3"/>
+      <c r="CI81" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI81" s="3" t="s">
+      <c r="CJ81" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ81" s="37" t="s">
+      <c r="CK81" s="37" t="s">
         <v>756</v>
       </c>
-      <c r="CK81" s="37" t="s">
+      <c r="CL81" s="37" t="s">
         <v>866</v>
       </c>
-      <c r="CL81" s="43" t="s">
+      <c r="CM81" s="43" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="82" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="124">
         <v>77</v>
       </c>
@@ -20588,51 +20699,52 @@
       <c r="BU82" s="22"/>
       <c r="BV82" s="22"/>
       <c r="BW82" s="22"/>
-      <c r="BX82" s="20" t="s">
+      <c r="BX82" s="22"/>
+      <c r="BY82" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY82" s="49" t="s">
+      <c r="BZ82" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ82" s="49"/>
-      <c r="CA82" s="49" t="s">
+      <c r="CA82" s="49"/>
+      <c r="CB82" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB82" s="49" t="s">
+      <c r="CC82" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC82" s="22" t="s">
+      <c r="CD82" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="CD82" s="22" t="s">
+      <c r="CE82" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="CE82" s="92" t="s">
+      <c r="CF82" s="92" t="s">
         <v>765</v>
       </c>
-      <c r="CF82" s="2">
+      <c r="CG82" s="2">
         <v>1272212</v>
       </c>
-      <c r="CG82" s="157" t="s">
+      <c r="CH82" s="157" t="s">
         <v>755</v>
       </c>
-      <c r="CH82" s="2" t="s">
+      <c r="CI82" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI82" s="2" t="s">
+      <c r="CJ82" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ82" s="18" t="s">
+      <c r="CK82" s="18" t="s">
         <v>766</v>
       </c>
-      <c r="CK82" s="18" t="s">
+      <c r="CL82" s="18" t="s">
         <v>764</v>
       </c>
-      <c r="CL82" s="21" t="s">
+      <c r="CM82" s="21" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="83" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="124">
         <v>78</v>
       </c>
@@ -20799,47 +20911,48 @@
       <c r="BU83" s="22"/>
       <c r="BV83" s="22"/>
       <c r="BW83" s="22"/>
-      <c r="BX83" s="20" t="s">
+      <c r="BX83" s="22"/>
+      <c r="BY83" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY83" s="49" t="s">
+      <c r="BZ83" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ83" s="49"/>
-      <c r="CA83" s="49" t="s">
+      <c r="CA83" s="49"/>
+      <c r="CB83" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB83" s="49" t="s">
+      <c r="CC83" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC83" s="22" t="s">
+      <c r="CD83" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="CD83" s="22" t="s">
+      <c r="CE83" s="22" t="s">
         <v>586</v>
       </c>
-      <c r="CE83" s="92" t="s">
+      <c r="CF83" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF83" s="22" t="s">
+      <c r="CG83" s="22" t="s">
         <v>700</v>
       </c>
-      <c r="CG83" s="2"/>
-      <c r="CH83" s="2" t="s">
+      <c r="CH83" s="2"/>
+      <c r="CI83" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI83" s="2" t="s">
+      <c r="CJ83" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ83" s="18" t="s">
+      <c r="CK83" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK83" s="18"/>
-      <c r="CL83" s="21" t="s">
+      <c r="CL83" s="18"/>
+      <c r="CM83" s="21" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="84" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="124">
         <v>79</v>
       </c>
@@ -21006,49 +21119,50 @@
       <c r="BU84" s="22"/>
       <c r="BV84" s="22"/>
       <c r="BW84" s="22"/>
-      <c r="BX84" s="20" t="s">
+      <c r="BX84" s="22"/>
+      <c r="BY84" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY84" s="49" t="s">
+      <c r="BZ84" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ84" s="49"/>
-      <c r="CA84" s="49" t="s">
+      <c r="CA84" s="49"/>
+      <c r="CB84" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB84" s="49" t="s">
+      <c r="CC84" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC84" s="22" t="s">
+      <c r="CD84" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="CD84" s="22" t="s">
+      <c r="CE84" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="CE84" s="92" t="s">
+      <c r="CF84" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF84" s="2">
+      <c r="CG84" s="2">
         <v>1272212</v>
       </c>
-      <c r="CG84" s="2"/>
-      <c r="CH84" s="2" t="s">
+      <c r="CH84" s="2"/>
+      <c r="CI84" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI84" s="2" t="s">
+      <c r="CJ84" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ84" s="18" t="s">
+      <c r="CK84" s="18" t="s">
         <v>785</v>
       </c>
-      <c r="CK84" s="18" t="s">
+      <c r="CL84" s="18" t="s">
         <v>787</v>
       </c>
-      <c r="CL84" s="21" t="s">
+      <c r="CM84" s="21" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="85" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="124">
         <v>79</v>
       </c>
@@ -21215,49 +21329,50 @@
       <c r="BU85" s="22"/>
       <c r="BV85" s="22"/>
       <c r="BW85" s="22"/>
-      <c r="BX85" s="20" t="s">
+      <c r="BX85" s="22"/>
+      <c r="BY85" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY85" s="49" t="s">
+      <c r="BZ85" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ85" s="49"/>
-      <c r="CA85" s="49" t="s">
+      <c r="CA85" s="49"/>
+      <c r="CB85" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB85" s="49" t="s">
+      <c r="CC85" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC85" s="22" t="s">
+      <c r="CD85" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="CD85" s="22" t="s">
+      <c r="CE85" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="CE85" s="92" t="s">
+      <c r="CF85" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF85" s="2">
+      <c r="CG85" s="2">
         <v>1272212</v>
       </c>
-      <c r="CG85" s="2"/>
-      <c r="CH85" s="2" t="s">
+      <c r="CH85" s="2"/>
+      <c r="CI85" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI85" s="2" t="s">
+      <c r="CJ85" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ85" s="18" t="s">
+      <c r="CK85" s="18" t="s">
         <v>794</v>
       </c>
-      <c r="CK85" s="18" t="s">
+      <c r="CL85" s="18" t="s">
         <v>788</v>
       </c>
-      <c r="CL85" s="21" t="s">
+      <c r="CM85" s="21" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="86" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="124">
         <v>80</v>
       </c>
@@ -21424,49 +21539,50 @@
       <c r="BU86" s="22"/>
       <c r="BV86" s="22"/>
       <c r="BW86" s="22"/>
-      <c r="BX86" s="20" t="s">
+      <c r="BX86" s="22"/>
+      <c r="BY86" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY86" s="49" t="s">
+      <c r="BZ86" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ86" s="49"/>
-      <c r="CA86" s="49" t="s">
+      <c r="CA86" s="49"/>
+      <c r="CB86" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB86" s="49" t="s">
+      <c r="CC86" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC86" s="22" t="s">
+      <c r="CD86" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="CD86" s="22" t="s">
+      <c r="CE86" s="22" t="s">
         <v>586</v>
       </c>
-      <c r="CE86" s="92" t="s">
+      <c r="CF86" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF86" s="22" t="s">
+      <c r="CG86" s="22" t="s">
         <v>700</v>
       </c>
-      <c r="CG86" s="2"/>
-      <c r="CH86" s="2" t="s">
+      <c r="CH86" s="2"/>
+      <c r="CI86" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI86" s="2" t="s">
+      <c r="CJ86" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ86" s="18" t="s">
+      <c r="CK86" s="18" t="s">
         <v>785</v>
       </c>
-      <c r="CK86" s="18" t="s">
+      <c r="CL86" s="18" t="s">
         <v>867</v>
       </c>
-      <c r="CL86" s="21" t="s">
+      <c r="CM86" s="21" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="87" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="124">
         <v>81</v>
       </c>
@@ -21534,7 +21650,7 @@
         <v>934</v>
       </c>
       <c r="W87" s="2">
-        <f t="shared" ref="W87:W92" si="0">V87*2</f>
+        <f t="shared" ref="W87:W94" si="0">V87*2</f>
         <v>1868</v>
       </c>
       <c r="X87" s="18" t="s">
@@ -21633,47 +21749,48 @@
       <c r="BU87" s="22"/>
       <c r="BV87" s="22"/>
       <c r="BW87" s="22"/>
-      <c r="BX87" s="20" t="s">
+      <c r="BX87" s="22"/>
+      <c r="BY87" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY87" s="49" t="s">
+      <c r="BZ87" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ87" s="49"/>
-      <c r="CA87" s="49" t="s">
+      <c r="CA87" s="49"/>
+      <c r="CB87" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB87" s="49" t="s">
+      <c r="CC87" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC87" s="22" t="s">
+      <c r="CD87" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="CD87" s="22" t="s">
+      <c r="CE87" s="22" t="s">
         <v>747</v>
       </c>
-      <c r="CE87" s="92" t="s">
+      <c r="CF87" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF87" s="157">
+      <c r="CG87" s="157">
         <v>1272212</v>
       </c>
-      <c r="CG87" s="2"/>
-      <c r="CH87" s="2" t="s">
+      <c r="CH87" s="2"/>
+      <c r="CI87" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI87" s="2" t="s">
+      <c r="CJ87" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ87" s="18" t="s">
+      <c r="CK87" s="18" t="s">
         <v>794</v>
       </c>
-      <c r="CK87" s="18"/>
-      <c r="CL87" s="21" t="s">
+      <c r="CL87" s="18"/>
+      <c r="CM87" s="21" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="88" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" s="124">
         <v>82</v>
       </c>
@@ -21840,51 +21957,52 @@
       <c r="BU88" s="22"/>
       <c r="BV88" s="22"/>
       <c r="BW88" s="22"/>
-      <c r="BX88" s="20" t="s">
+      <c r="BX88" s="22"/>
+      <c r="BY88" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY88" s="49" t="s">
+      <c r="BZ88" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ88" s="49"/>
-      <c r="CA88" s="49" t="s">
+      <c r="CA88" s="49"/>
+      <c r="CB88" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB88" s="49" t="s">
+      <c r="CC88" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC88" s="22" t="s">
+      <c r="CD88" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="CD88" s="22" t="s">
+      <c r="CE88" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="CE88" s="92" t="s">
+      <c r="CF88" s="92" t="s">
         <v>136</v>
       </c>
-      <c r="CF88" s="22" t="s">
+      <c r="CG88" s="22" t="s">
         <v>803</v>
       </c>
-      <c r="CG88" s="2" t="s">
+      <c r="CH88" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="CH88" s="2" t="s">
+      <c r="CI88" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI88" s="2" t="s">
+      <c r="CJ88" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ88" s="18" t="s">
+      <c r="CK88" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK88" s="18" t="s">
+      <c r="CL88" s="18" t="s">
         <v>867</v>
       </c>
-      <c r="CL88" s="21" t="s">
+      <c r="CM88" s="21" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="89" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="124">
         <v>83</v>
       </c>
@@ -22051,47 +22169,48 @@
       <c r="BU89" s="22"/>
       <c r="BV89" s="22"/>
       <c r="BW89" s="22"/>
-      <c r="BX89" s="20" t="s">
+      <c r="BX89" s="22"/>
+      <c r="BY89" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY89" s="49" t="s">
+      <c r="BZ89" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ89" s="49"/>
-      <c r="CA89" s="49" t="s">
+      <c r="CA89" s="49"/>
+      <c r="CB89" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB89" s="49" t="s">
+      <c r="CC89" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC89" s="22" t="s">
+      <c r="CD89" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="CD89" s="22" t="s">
+      <c r="CE89" s="22" t="s">
         <v>586</v>
       </c>
-      <c r="CE89" s="92" t="s">
+      <c r="CF89" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF89" s="2">
+      <c r="CG89" s="2">
         <v>1272212</v>
       </c>
-      <c r="CG89" s="2"/>
-      <c r="CH89" s="2" t="s">
+      <c r="CH89" s="2"/>
+      <c r="CI89" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI89" s="2" t="s">
+      <c r="CJ89" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ89" s="18" t="s">
+      <c r="CK89" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK89" s="18"/>
-      <c r="CL89" s="21" t="s">
+      <c r="CL89" s="18"/>
+      <c r="CM89" s="21" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="90" spans="1:90" s="88" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:91" s="88" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A90" s="124">
         <v>84</v>
       </c>
@@ -22258,47 +22377,48 @@
       <c r="BU90" s="22"/>
       <c r="BV90" s="22"/>
       <c r="BW90" s="22"/>
-      <c r="BX90" s="20" t="s">
+      <c r="BX90" s="22"/>
+      <c r="BY90" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY90" s="49" t="s">
+      <c r="BZ90" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ90" s="49"/>
-      <c r="CA90" s="49" t="s">
+      <c r="CA90" s="49"/>
+      <c r="CB90" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB90" s="49" t="s">
+      <c r="CC90" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC90" s="22" t="s">
+      <c r="CD90" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="CD90" s="22" t="s">
+      <c r="CE90" s="22" t="s">
         <v>586</v>
       </c>
-      <c r="CE90" s="92" t="s">
+      <c r="CF90" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="CF90" s="2">
+      <c r="CG90" s="2">
         <v>1272212</v>
       </c>
-      <c r="CG90" s="2"/>
-      <c r="CH90" s="2" t="s">
+      <c r="CH90" s="2"/>
+      <c r="CI90" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI90" s="2" t="s">
+      <c r="CJ90" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ90" s="18" t="s">
+      <c r="CK90" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK90" s="18"/>
-      <c r="CL90" s="21" t="s">
+      <c r="CL90" s="18"/>
+      <c r="CM90" s="21" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="91" spans="1:90" s="88" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:91" s="88" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="124">
         <v>85</v>
       </c>
@@ -22465,49 +22585,50 @@
       <c r="BU91" s="22"/>
       <c r="BV91" s="22"/>
       <c r="BW91" s="22"/>
-      <c r="BX91" s="20" t="s">
+      <c r="BX91" s="22"/>
+      <c r="BY91" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY91" s="49" t="s">
+      <c r="BZ91" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="BZ91" s="49"/>
-      <c r="CA91" s="49" t="s">
+      <c r="CA91" s="49"/>
+      <c r="CB91" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB91" s="49" t="s">
+      <c r="CC91" s="49" t="s">
         <v>837</v>
       </c>
-      <c r="CC91" s="22" t="s">
+      <c r="CD91" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="CD91" s="22" t="s">
+      <c r="CE91" s="22" t="s">
         <v>514</v>
       </c>
-      <c r="CE91" s="22" t="s">
+      <c r="CF91" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="CF91" s="2">
+      <c r="CG91" s="2">
         <v>1272212</v>
       </c>
-      <c r="CG91" s="2"/>
-      <c r="CH91" s="2" t="s">
+      <c r="CH91" s="2"/>
+      <c r="CI91" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI91" s="2" t="s">
+      <c r="CJ91" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ91" s="18" t="s">
+      <c r="CK91" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK91" s="18" t="s">
+      <c r="CL91" s="18" t="s">
         <v>834</v>
       </c>
-      <c r="CL91" s="21" t="s">
+      <c r="CM91" s="21" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="92" spans="1:90" s="88" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:91" s="88" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="124">
         <v>86</v>
       </c>
@@ -22637,8 +22758,8 @@
       <c r="BB92" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="BC92" s="54" t="s">
-        <v>826</v>
+      <c r="BC92" s="39">
+        <v>45964</v>
       </c>
       <c r="BD92" s="22" t="s">
         <v>459</v>
@@ -22674,51 +22795,52 @@
       <c r="BU92" s="22"/>
       <c r="BV92" s="22"/>
       <c r="BW92" s="22"/>
-      <c r="BX92" s="20" t="s">
+      <c r="BX92" s="22"/>
+      <c r="BY92" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="BY92" s="49" t="s">
+      <c r="BZ92" s="49" t="s">
         <v>829</v>
       </c>
-      <c r="BZ92" s="49" t="s">
+      <c r="CA92" s="49" t="s">
         <v>858</v>
       </c>
-      <c r="CA92" s="49" t="s">
+      <c r="CB92" s="49" t="s">
         <v>845</v>
       </c>
-      <c r="CB92" s="49" t="s">
+      <c r="CC92" s="49" t="s">
         <v>836</v>
       </c>
-      <c r="CC92" s="22" t="s">
+      <c r="CD92" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="CD92" s="22" t="s">
+      <c r="CE92" s="22" t="s">
         <v>747</v>
       </c>
-      <c r="CE92" s="22" t="s">
+      <c r="CF92" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="CF92" s="22" t="s">
+      <c r="CG92" s="22" t="s">
         <v>700</v>
       </c>
-      <c r="CG92" s="2"/>
-      <c r="CH92" s="2" t="s">
+      <c r="CH92" s="2"/>
+      <c r="CI92" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="CI92" s="2" t="s">
+      <c r="CJ92" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="CJ92" s="18" t="s">
+      <c r="CK92" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="CK92" s="18" t="s">
+      <c r="CL92" s="18" t="s">
         <v>862</v>
       </c>
-      <c r="CL92" s="21" t="s">
+      <c r="CM92" s="21" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="93" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" s="136">
         <v>87</v>
       </c>
@@ -22746,22 +22868,49 @@
       <c r="I93" s="37" t="s">
         <v>860</v>
       </c>
-      <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="35"/>
-      <c r="M93" s="35"/>
-      <c r="N93" s="3"/>
-      <c r="O93" s="37"/>
-      <c r="P93" s="37"/>
-      <c r="Q93" s="37"/>
-      <c r="R93" s="37"/>
+      <c r="J93" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="K93" s="3">
+        <v>25.2</v>
+      </c>
+      <c r="L93" s="35">
+        <v>44.516300000000001</v>
+      </c>
+      <c r="M93" s="35">
+        <v>-63.411999999999999</v>
+      </c>
+      <c r="N93" s="137">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="O93" s="37">
+        <v>42.48</v>
+      </c>
+      <c r="P93" s="37">
+        <v>-63.42</v>
+      </c>
+      <c r="Q93" s="37">
+        <v>44.53</v>
+      </c>
+      <c r="R93" s="37">
+        <v>-61.42</v>
+      </c>
       <c r="S93" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="T93" s="3"/>
-      <c r="U93" s="3"/>
-      <c r="V93" s="3"/>
-      <c r="W93" s="3"/>
+      <c r="T93" s="3">
+        <v>23</v>
+      </c>
+      <c r="U93" s="3">
+        <v>623</v>
+      </c>
+      <c r="V93" s="3">
+        <v>1053</v>
+      </c>
+      <c r="W93" s="3">
+        <f t="shared" si="0"/>
+        <v>2106</v>
+      </c>
       <c r="X93" s="37" t="s">
         <v>36</v>
       </c>
@@ -22782,9 +22931,15 @@
       <c r="AG93" s="37"/>
       <c r="AH93" s="37"/>
       <c r="AI93" s="37"/>
-      <c r="AJ93" s="3"/>
-      <c r="AK93" s="3"/>
-      <c r="AL93" s="3"/>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
       <c r="AM93" s="3">
         <v>1024.9000000000001</v>
       </c>
@@ -22852,55 +23007,58 @@
       <c r="BU93" s="38"/>
       <c r="BV93" s="38"/>
       <c r="BW93" s="38"/>
-      <c r="BX93" s="34" t="s">
+      <c r="BX93" s="38"/>
+      <c r="BY93" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY93" s="96" t="s">
+      <c r="BZ93" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="BZ93" s="96"/>
-      <c r="CA93" s="96" t="s">
+      <c r="CA93" s="96"/>
+      <c r="CB93" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB93" s="96" t="s">
+      <c r="CC93" s="96" t="s">
         <v>837</v>
       </c>
-      <c r="CC93" s="38" t="s">
+      <c r="CD93" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="CD93" s="167" t="s">
+      <c r="CE93" s="167" t="s">
         <v>746</v>
       </c>
-      <c r="CE93" s="38" t="s">
+      <c r="CF93" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="CF93" s="3">
+      <c r="CG93" s="3">
         <v>1272212</v>
       </c>
-      <c r="CG93" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="CH93" s="3" t="s">
+      <c r="CH93" s="3"/>
+      <c r="CI93" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI93" s="3" t="s">
+      <c r="CJ93" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ93" s="37" t="s">
-        <v>899</v>
-      </c>
-      <c r="CK93" s="37"/>
-      <c r="CL93" s="43"/>
+      <c r="CK93" s="37" t="s">
+        <v>897</v>
+      </c>
+      <c r="CL93" s="37"/>
+      <c r="CM93" s="43"/>
     </row>
-    <row r="94" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A94" s="136">
         <v>88</v>
       </c>
       <c r="B94" s="136">
         <v>2</v>
       </c>
-      <c r="C94" s="35"/>
-      <c r="D94" s="35"/>
+      <c r="C94" s="35">
+        <v>20260423</v>
+      </c>
+      <c r="D94" s="35">
+        <v>20260508</v>
+      </c>
       <c r="E94" s="35" t="s">
         <v>35</v>
       </c>
@@ -22913,21 +23071,52 @@
       <c r="H94" s="35" t="s">
         <v>887</v>
       </c>
-      <c r="I94" s="37"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="35"/>
-      <c r="M94" s="35"/>
-      <c r="N94" s="3"/>
-      <c r="O94" s="37"/>
-      <c r="P94" s="37"/>
-      <c r="Q94" s="37"/>
-      <c r="R94" s="37"/>
-      <c r="S94" s="3"/>
-      <c r="T94" s="3"/>
-      <c r="U94" s="3"/>
-      <c r="V94" s="3"/>
-      <c r="W94" s="3"/>
+      <c r="I94" s="37" t="s">
+        <v>900</v>
+      </c>
+      <c r="J94" s="3">
+        <v>29.2</v>
+      </c>
+      <c r="K94" s="3">
+        <v>27</v>
+      </c>
+      <c r="L94" s="35">
+        <v>44.531700000000001</v>
+      </c>
+      <c r="M94" s="35">
+        <v>-63.394500000000001</v>
+      </c>
+      <c r="N94" s="137">
+        <v>0.60138888888888886</v>
+      </c>
+      <c r="O94" s="37">
+        <v>43.54</v>
+      </c>
+      <c r="P94" s="37">
+        <v>-63.41</v>
+      </c>
+      <c r="Q94" s="37">
+        <v>44.54</v>
+      </c>
+      <c r="R94" s="37">
+        <v>-62.5</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="T94" s="3">
+        <v>15</v>
+      </c>
+      <c r="U94" s="3">
+        <v>397</v>
+      </c>
+      <c r="V94" s="3">
+        <v>770</v>
+      </c>
+      <c r="W94" s="3">
+        <f t="shared" si="0"/>
+        <v>1540</v>
+      </c>
       <c r="X94" s="37" t="s">
         <v>36</v>
       </c>
@@ -22948,9 +23137,15 @@
       <c r="AG94" s="37"/>
       <c r="AH94" s="37"/>
       <c r="AI94" s="37"/>
-      <c r="AJ94" s="3"/>
-      <c r="AK94" s="3"/>
-      <c r="AL94" s="3"/>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
       <c r="AM94" s="3">
         <v>1024.7</v>
       </c>
@@ -23005,7 +23200,7 @@
         <v>769</v>
       </c>
       <c r="BL94" s="38" t="s">
-        <v>775</v>
+        <v>802</v>
       </c>
       <c r="BM94" s="38"/>
       <c r="BN94" s="38"/>
@@ -23018,59 +23213,66 @@
       <c r="BU94" s="38"/>
       <c r="BV94" s="38"/>
       <c r="BW94" s="38"/>
-      <c r="BX94" s="34" t="s">
+      <c r="BX94" s="38"/>
+      <c r="BY94" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY94" s="96" t="s">
+      <c r="BZ94" s="96" t="s">
         <v>829</v>
       </c>
-      <c r="BZ94" s="96" t="s">
+      <c r="CA94" s="96" t="s">
         <v>889</v>
       </c>
-      <c r="CA94" s="96" t="s">
+      <c r="CB94" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB94" s="96" t="s">
+      <c r="CC94" s="96" t="s">
         <v>836</v>
       </c>
-      <c r="CC94" s="38" t="s">
+      <c r="CD94" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="CD94" s="38" t="s">
+      <c r="CE94" s="38" t="s">
         <v>800</v>
       </c>
-      <c r="CE94" s="38" t="s">
+      <c r="CF94" s="38" t="s">
         <v>885</v>
       </c>
-      <c r="CF94" s="40" t="s">
+      <c r="CG94" s="40" t="s">
         <v>700</v>
       </c>
-      <c r="CG94" s="3" t="s">
-        <v>299</v>
-      </c>
       <c r="CH94" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="CI94" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI94" s="3" t="s">
+      <c r="CJ94" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ94" s="37" t="s">
-        <v>900</v>
-      </c>
-      <c r="CK94" s="37"/>
-      <c r="CL94" s="43" t="s">
-        <v>890</v>
+      <c r="CK94" s="37" t="s">
+        <v>903</v>
+      </c>
+      <c r="CL94" s="37" t="s">
+        <v>727</v>
+      </c>
+      <c r="CM94" s="43" t="s">
+        <v>905</v>
       </c>
     </row>
-    <row r="95" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A95" s="136">
         <v>89</v>
       </c>
       <c r="B95" s="136">
         <v>3</v>
       </c>
-      <c r="C95" s="35"/>
-      <c r="D95" s="35"/>
+      <c r="C95" s="35">
+        <v>20260423</v>
+      </c>
+      <c r="D95" s="35">
+        <v>20260508</v>
+      </c>
       <c r="E95" s="35" t="s">
         <v>24</v>
       </c>
@@ -23083,21 +23285,52 @@
       <c r="H95" s="35" t="s">
         <v>887</v>
       </c>
-      <c r="I95" s="37"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="35"/>
-      <c r="M95" s="35"/>
-      <c r="N95" s="3"/>
-      <c r="O95" s="37"/>
-      <c r="P95" s="37"/>
-      <c r="Q95" s="37"/>
-      <c r="R95" s="37"/>
-      <c r="S95" s="3"/>
-      <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
+      <c r="I95" s="37" t="s">
+        <v>901</v>
+      </c>
+      <c r="J95" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="K95" s="3">
+        <v>26.4</v>
+      </c>
+      <c r="L95" s="35">
+        <v>44.529400000000003</v>
+      </c>
+      <c r="M95" s="35">
+        <v>-63.398699999999998</v>
+      </c>
+      <c r="N95" s="137">
+        <v>0.57708333333333328</v>
+      </c>
+      <c r="O95" s="37">
+        <v>43.53</v>
+      </c>
+      <c r="P95" s="37">
+        <v>-63.41</v>
+      </c>
+      <c r="Q95" s="37">
+        <v>44.53</v>
+      </c>
+      <c r="R95" s="37">
+        <v>-62.48</v>
+      </c>
+      <c r="S95" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="T95" s="3">
+        <v>15</v>
+      </c>
+      <c r="U95" s="3">
+        <v>383</v>
+      </c>
+      <c r="V95" s="3">
+        <v>708</v>
+      </c>
+      <c r="W95" s="3">
+        <f>V95*2</f>
+        <v>1416</v>
+      </c>
       <c r="X95" s="37" t="s">
         <v>36</v>
       </c>
@@ -23118,9 +23351,15 @@
       <c r="AG95" s="37"/>
       <c r="AH95" s="37"/>
       <c r="AI95" s="37"/>
-      <c r="AJ95" s="3"/>
-      <c r="AK95" s="3"/>
-      <c r="AL95" s="3"/>
+      <c r="AJ95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK95" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL95" s="3">
+        <v>0</v>
+      </c>
       <c r="AM95" s="3">
         <v>1024.7</v>
       </c>
@@ -23151,8 +23390,8 @@
       <c r="BB95" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="BC95" s="38" t="s">
-        <v>751</v>
+      <c r="BC95" s="39">
+        <v>45631</v>
       </c>
       <c r="BD95" s="38" t="s">
         <v>459</v>
@@ -23175,7 +23414,7 @@
         <v>768</v>
       </c>
       <c r="BL95" s="38" t="s">
-        <v>781</v>
+        <v>815</v>
       </c>
       <c r="BM95" s="38"/>
       <c r="BN95" s="38"/>
@@ -23188,63 +23427,66 @@
       <c r="BU95" s="38"/>
       <c r="BV95" s="38"/>
       <c r="BW95" s="38"/>
-      <c r="BX95" s="34" t="s">
+      <c r="BX95" s="38"/>
+      <c r="BY95" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY95" s="96" t="s">
+      <c r="BZ95" s="96" t="s">
         <v>829</v>
       </c>
-      <c r="BZ95" s="96" t="s">
+      <c r="CA95" s="96" t="s">
         <v>889</v>
       </c>
-      <c r="CA95" s="96" t="s">
+      <c r="CB95" s="96" t="s">
         <v>165</v>
       </c>
-      <c r="CB95" s="96" t="s">
+      <c r="CC95" s="96" t="s">
         <v>836</v>
       </c>
-      <c r="CC95" s="40" t="s">
+      <c r="CD95" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="CD95" s="40" t="s">
+      <c r="CE95" s="40" t="s">
         <v>747</v>
       </c>
-      <c r="CE95" s="38" t="s">
+      <c r="CF95" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="CF95" s="38" t="s">
+      <c r="CG95" s="38" t="s">
         <v>803</v>
       </c>
-      <c r="CG95" s="3" t="s">
-        <v>299</v>
-      </c>
       <c r="CH95" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="CI95" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI95" s="3" t="s">
+      <c r="CJ95" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ95" s="37" t="s">
-        <v>900</v>
-      </c>
-      <c r="CK95" s="37"/>
-      <c r="CL95" s="43" t="s">
-        <v>891</v>
+      <c r="CK95" s="37" t="s">
+        <v>903</v>
+      </c>
+      <c r="CL95" s="37"/>
+      <c r="CM95" s="43" t="s">
+        <v>890</v>
       </c>
     </row>
-    <row r="96" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A96" s="136">
         <v>90</v>
       </c>
       <c r="B96" s="136">
         <v>4</v>
       </c>
-      <c r="C96" s="35"/>
+      <c r="C96" s="35">
+        <v>20260508</v>
+      </c>
       <c r="D96" s="35"/>
       <c r="E96" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F96" s="169">
+      <c r="F96" s="35">
         <v>151</v>
       </c>
       <c r="G96" s="35">
@@ -23253,7 +23495,9 @@
       <c r="H96" s="35" t="s">
         <v>887</v>
       </c>
-      <c r="I96" s="37"/>
+      <c r="I96" s="37" t="s">
+        <v>907</v>
+      </c>
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
       <c r="L96" s="35"/>
@@ -23263,13 +23507,15 @@
       <c r="P96" s="37"/>
       <c r="Q96" s="37"/>
       <c r="R96" s="37"/>
-      <c r="S96" s="3"/>
+      <c r="S96" s="3" t="s">
+        <v>908</v>
+      </c>
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
       <c r="X96" s="37" t="s">
-        <v>227</v>
+        <v>36</v>
       </c>
       <c r="Y96" s="37" t="s">
         <v>227</v>
@@ -23292,9 +23538,15 @@
       <c r="AI96" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="AJ96" s="3"/>
-      <c r="AK96" s="3"/>
-      <c r="AL96" s="3"/>
+      <c r="AJ96" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>1</v>
+      </c>
       <c r="AM96" s="3">
         <v>1024.4000000000001</v>
       </c>
@@ -23331,7 +23583,7 @@
         <v>869</v>
       </c>
       <c r="BH96" s="38" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="BI96" s="38" t="s">
         <v>418</v>
@@ -23343,81 +23595,94 @@
         <v>870</v>
       </c>
       <c r="BL96" s="38" t="s">
+        <v>892</v>
+      </c>
+      <c r="BM96" s="38"/>
+      <c r="BN96" s="38" t="s">
         <v>893</v>
       </c>
-      <c r="BM96" s="38" t="s">
+      <c r="BO96" s="38" t="s">
         <v>894</v>
       </c>
-      <c r="BN96" s="38" t="s">
-        <v>895</v>
-      </c>
-      <c r="BO96" s="38"/>
       <c r="BP96" s="38"/>
       <c r="BQ96" s="38"/>
       <c r="BR96" s="38"/>
       <c r="BS96" s="38"/>
-      <c r="BT96" s="38" t="s">
+      <c r="BT96" s="38"/>
+      <c r="BU96" s="38" t="s">
         <v>871</v>
       </c>
-      <c r="BU96" s="38" t="s">
+      <c r="BV96" s="38" t="s">
         <v>886</v>
       </c>
-      <c r="BV96" s="38" t="s">
+      <c r="BW96" s="38" t="s">
         <v>873</v>
       </c>
-      <c r="BW96" s="38" t="s">
-        <v>896</v>
-      </c>
-      <c r="BX96" s="34" t="s">
+      <c r="BX96" s="38" t="s">
+        <v>895</v>
+      </c>
+      <c r="BY96" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="BY96" s="96" t="s">
+      <c r="BZ96" s="96" t="s">
         <v>829</v>
       </c>
-      <c r="BZ96" s="49" t="s">
+      <c r="CA96" s="96" t="s">
         <v>858</v>
       </c>
-      <c r="CA96" s="96" t="s">
+      <c r="CB96" s="96" t="s">
         <v>845</v>
       </c>
-      <c r="CB96" s="96" t="s">
+      <c r="CC96" s="96" t="s">
         <v>836</v>
       </c>
-      <c r="CC96" s="38" t="s">
+      <c r="CD96" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="CD96" s="167" t="s">
+      <c r="CE96" s="167" t="s">
         <v>746</v>
-      </c>
-      <c r="CE96" s="38" t="s">
-        <v>188</v>
       </c>
       <c r="CF96" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="CG96" s="3"/>
-      <c r="CH96" s="3" t="s">
+      <c r="CG96" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="CH96" s="3"/>
+      <c r="CI96" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="CI96" s="3" t="s">
+      <c r="CJ96" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CJ96" s="37"/>
-      <c r="CK96" s="37"/>
-      <c r="CL96" s="43" t="s">
-        <v>898</v>
+      <c r="CK96" s="37" t="s">
+        <v>904</v>
+      </c>
+      <c r="CL96" s="37"/>
+      <c r="CM96" s="43" t="s">
+        <v>910</v>
       </c>
     </row>
-    <row r="97" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A97" s="136"/>
       <c r="B97" s="136"/>
       <c r="C97" s="35"/>
       <c r="D97" s="35"/>
-      <c r="E97" s="35"/>
-      <c r="F97" s="35"/>
-      <c r="G97" s="35"/>
-      <c r="H97" s="35"/>
-      <c r="I97" s="37"/>
+      <c r="E97" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="35">
+        <v>92</v>
+      </c>
+      <c r="G97" s="35">
+        <v>4800926</v>
+      </c>
+      <c r="H97" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="37" t="s">
+        <v>906</v>
+      </c>
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
       <c r="L97" s="35"/>
@@ -23432,13 +23697,21 @@
       <c r="U97" s="3"/>
       <c r="V97" s="3"/>
       <c r="W97" s="3"/>
-      <c r="X97" s="37"/>
-      <c r="Y97" s="37"/>
+      <c r="X97" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y97" s="37">
+        <v>1</v>
+      </c>
       <c r="Z97" s="37"/>
-      <c r="AA97" s="37"/>
+      <c r="AA97" s="37" t="s">
+        <v>182</v>
+      </c>
       <c r="AB97" s="37"/>
       <c r="AC97" s="37"/>
-      <c r="AD97" s="37"/>
+      <c r="AD97" s="37" t="s">
+        <v>776</v>
+      </c>
       <c r="AE97" s="37"/>
       <c r="AF97" s="37"/>
       <c r="AG97" s="37"/>
@@ -23447,12 +23720,24 @@
       <c r="AJ97" s="3"/>
       <c r="AK97" s="3"/>
       <c r="AL97" s="3"/>
-      <c r="AM97" s="3"/>
-      <c r="AN97" s="37"/>
-      <c r="AO97" s="37"/>
-      <c r="AP97" s="37"/>
-      <c r="AQ97" s="37"/>
-      <c r="AR97" s="35"/>
+      <c r="AM97" s="3">
+        <v>1024.2</v>
+      </c>
+      <c r="AN97" s="37">
+        <v>20260512</v>
+      </c>
+      <c r="AO97" s="37">
+        <v>1</v>
+      </c>
+      <c r="AP97" s="37" t="s">
+        <v>839</v>
+      </c>
+      <c r="AQ97" s="37" t="s">
+        <v>782</v>
+      </c>
+      <c r="AR97" s="35">
+        <v>29</v>
+      </c>
       <c r="AS97" s="34"/>
       <c r="AT97" s="38"/>
       <c r="AU97" s="38"/>
@@ -23462,17 +23747,35 @@
       <c r="AY97" s="38"/>
       <c r="AZ97" s="38"/>
       <c r="BA97" s="38"/>
-      <c r="BB97" s="34"/>
-      <c r="BC97" s="38"/>
-      <c r="BD97" s="38"/>
+      <c r="BB97" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC97" s="39">
+        <v>45631</v>
+      </c>
+      <c r="BD97" s="38" t="s">
+        <v>459</v>
+      </c>
       <c r="BE97" s="38"/>
       <c r="BF97" s="38"/>
-      <c r="BG97" s="38"/>
-      <c r="BH97" s="38"/>
-      <c r="BI97" s="38"/>
-      <c r="BJ97" s="38"/>
-      <c r="BK97" s="38"/>
-      <c r="BL97" s="38"/>
+      <c r="BG97" s="38" t="s">
+        <v>759</v>
+      </c>
+      <c r="BH97" s="38" t="s">
+        <v>780</v>
+      </c>
+      <c r="BI97" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="BJ97" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="BK97" s="38" t="s">
+        <v>768</v>
+      </c>
+      <c r="BL97" s="38" t="s">
+        <v>815</v>
+      </c>
       <c r="BM97" s="38"/>
       <c r="BN97" s="38"/>
       <c r="BO97" s="38"/>
@@ -23484,23 +23787,48 @@
       <c r="BU97" s="38"/>
       <c r="BV97" s="38"/>
       <c r="BW97" s="38"/>
-      <c r="BX97" s="34"/>
-      <c r="BY97" s="96"/>
-      <c r="BZ97" s="96"/>
-      <c r="CA97" s="96"/>
-      <c r="CB97" s="96"/>
-      <c r="CC97" s="38"/>
-      <c r="CD97" s="144"/>
-      <c r="CE97" s="38"/>
-      <c r="CF97" s="38"/>
-      <c r="CG97" s="3"/>
-      <c r="CH97" s="35"/>
-      <c r="CI97" s="35"/>
-      <c r="CJ97" s="37"/>
+      <c r="BX97" s="38"/>
+      <c r="BY97" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="BZ97" s="96" t="s">
+        <v>829</v>
+      </c>
+      <c r="CA97" s="96" t="s">
+        <v>889</v>
+      </c>
+      <c r="CB97" s="96" t="s">
+        <v>165</v>
+      </c>
+      <c r="CC97" s="96" t="s">
+        <v>836</v>
+      </c>
+      <c r="CD97" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="CE97" s="40" t="s">
+        <v>747</v>
+      </c>
+      <c r="CF97" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="CG97" s="38" t="s">
+        <v>803</v>
+      </c>
+      <c r="CH97" s="3"/>
+      <c r="CI97" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="CJ97" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="CK97" s="37"/>
-      <c r="CL97" s="43"/>
+      <c r="CL97" s="37"/>
+      <c r="CM97" s="43" t="s">
+        <v>909</v>
+      </c>
     </row>
-    <row r="98" spans="1:90" s="48" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:91" s="48" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A98" s="136"/>
       <c r="B98" s="136"/>
       <c r="C98" s="35"/>
@@ -23576,23 +23904,24 @@
       <c r="BU98" s="38"/>
       <c r="BV98" s="38"/>
       <c r="BW98" s="38"/>
-      <c r="BX98" s="34"/>
-      <c r="BY98" s="96"/>
+      <c r="BX98" s="38"/>
+      <c r="BY98" s="34"/>
       <c r="BZ98" s="96"/>
       <c r="CA98" s="96"/>
       <c r="CB98" s="96"/>
-      <c r="CC98" s="38"/>
-      <c r="CD98" s="144"/>
-      <c r="CE98" s="38"/>
+      <c r="CC98" s="96"/>
+      <c r="CD98" s="38"/>
+      <c r="CE98" s="144"/>
       <c r="CF98" s="38"/>
-      <c r="CG98" s="3"/>
-      <c r="CH98" s="35"/>
+      <c r="CG98" s="38"/>
+      <c r="CH98" s="3"/>
       <c r="CI98" s="35"/>
-      <c r="CJ98" s="37"/>
+      <c r="CJ98" s="35"/>
       <c r="CK98" s="37"/>
-      <c r="CL98" s="43"/>
+      <c r="CL98" s="37"/>
+      <c r="CM98" s="43"/>
     </row>
-    <row r="99" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C99" s="116"/>
       <c r="D99" s="116"/>
       <c r="E99" s="116"/>
@@ -23664,33 +23993,34 @@
       <c r="BU99" s="78"/>
       <c r="BV99" s="78"/>
       <c r="BW99" s="78"/>
-      <c r="BX99" s="117"/>
-      <c r="BY99" s="118" t="s">
+      <c r="BX99" s="78"/>
+      <c r="BY99" s="117"/>
+      <c r="BZ99" s="118" t="s">
         <v>831</v>
       </c>
-      <c r="BZ99" s="118"/>
       <c r="CA99" s="118"/>
       <c r="CB99" s="118"/>
-      <c r="CC99" s="40" t="s">
+      <c r="CC99" s="118"/>
+      <c r="CD99" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="CD99" s="160" t="s">
+      <c r="CE99" s="160" t="s">
         <v>747</v>
       </c>
-      <c r="CE99" s="40" t="s">
+      <c r="CF99" s="40" t="s">
         <v>885</v>
       </c>
-      <c r="CF99" s="40"/>
-      <c r="CG99" s="44"/>
-      <c r="CH99" s="121"/>
-      <c r="CI99" s="45"/>
-      <c r="CJ99" s="77"/>
-      <c r="CK99" s="77" t="s">
+      <c r="CG99" s="40"/>
+      <c r="CH99" s="44"/>
+      <c r="CI99" s="121"/>
+      <c r="CJ99" s="45"/>
+      <c r="CK99" s="77"/>
+      <c r="CL99" s="77" t="s">
         <v>820</v>
       </c>
-      <c r="CL99" s="119"/>
+      <c r="CM99" s="119"/>
     </row>
-    <row r="100" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C100" s="116"/>
       <c r="D100" s="116"/>
       <c r="E100" s="116"/>
@@ -23766,29 +24096,30 @@
       <c r="BU100" s="78"/>
       <c r="BV100" s="78"/>
       <c r="BW100" s="78"/>
-      <c r="BX100" s="117"/>
-      <c r="BY100" s="118" t="s">
+      <c r="BX100" s="78"/>
+      <c r="BY100" s="117"/>
+      <c r="BZ100" s="118" t="s">
         <v>832</v>
       </c>
-      <c r="BZ100" s="118"/>
       <c r="CA100" s="118"/>
       <c r="CB100" s="118"/>
-      <c r="CC100" s="38" t="s">
+      <c r="CC100" s="118"/>
+      <c r="CD100" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="CD100" s="143" t="s">
+      <c r="CE100" s="143" t="s">
         <v>586</v>
       </c>
-      <c r="CE100" s="38"/>
       <c r="CF100" s="38"/>
-      <c r="CG100" s="3"/>
-      <c r="CH100" s="120"/>
-      <c r="CI100" s="35"/>
-      <c r="CJ100" s="77"/>
+      <c r="CG100" s="38"/>
+      <c r="CH100" s="3"/>
+      <c r="CI100" s="120"/>
+      <c r="CJ100" s="35"/>
       <c r="CK100" s="77"/>
-      <c r="CL100" s="119"/>
+      <c r="CL100" s="77"/>
+      <c r="CM100" s="119"/>
     </row>
-    <row r="101" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C101" s="116"/>
       <c r="D101" s="116"/>
       <c r="E101" s="116"/>
@@ -23862,27 +24193,28 @@
       <c r="BU101" s="78"/>
       <c r="BV101" s="78"/>
       <c r="BW101" s="78"/>
-      <c r="BX101" s="117"/>
-      <c r="BY101" s="118"/>
+      <c r="BX101" s="78"/>
+      <c r="BY101" s="117"/>
       <c r="BZ101" s="118"/>
       <c r="CA101" s="118"/>
       <c r="CB101" s="118"/>
-      <c r="CC101" s="38" t="s">
+      <c r="CC101" s="118"/>
+      <c r="CD101" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="CD101" s="144" t="s">
+      <c r="CE101" s="144" t="s">
         <v>800</v>
       </c>
-      <c r="CE101" s="133"/>
       <c r="CF101" s="133"/>
-      <c r="CG101" s="134"/>
-      <c r="CH101" s="135"/>
-      <c r="CI101" s="29"/>
-      <c r="CJ101" s="77"/>
+      <c r="CG101" s="133"/>
+      <c r="CH101" s="134"/>
+      <c r="CI101" s="135"/>
+      <c r="CJ101" s="29"/>
       <c r="CK101" s="77"/>
-      <c r="CL101" s="119"/>
+      <c r="CL101" s="77"/>
+      <c r="CM101" s="119"/>
     </row>
-    <row r="102" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C102" s="116"/>
       <c r="D102" s="116"/>
       <c r="E102" s="116"/>
@@ -23960,27 +24292,28 @@
       <c r="BU102" s="78"/>
       <c r="BV102" s="78"/>
       <c r="BW102" s="78"/>
-      <c r="BX102" s="117"/>
-      <c r="BY102" s="118"/>
+      <c r="BX102" s="78"/>
+      <c r="BY102" s="117"/>
       <c r="BZ102" s="118"/>
       <c r="CA102" s="118"/>
       <c r="CB102" s="118"/>
-      <c r="CC102" s="38" t="s">
+      <c r="CC102" s="118"/>
+      <c r="CD102" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="CD102" s="144" t="s">
+      <c r="CE102" s="144" t="s">
         <v>746</v>
       </c>
-      <c r="CE102" s="38"/>
       <c r="CF102" s="38"/>
-      <c r="CG102" s="3"/>
-      <c r="CH102" s="29"/>
-      <c r="CI102" s="93"/>
-      <c r="CJ102" s="77"/>
+      <c r="CG102" s="38"/>
+      <c r="CH102" s="3"/>
+      <c r="CI102" s="29"/>
+      <c r="CJ102" s="93"/>
       <c r="CK102" s="77"/>
-      <c r="CL102" s="119"/>
+      <c r="CL102" s="77"/>
+      <c r="CM102" s="119"/>
     </row>
-    <row r="103" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C103" s="116"/>
       <c r="D103" s="116"/>
       <c r="E103" s="116"/>
@@ -24037,46 +24370,47 @@
         <v>870</v>
       </c>
       <c r="BL103" s="78"/>
-      <c r="BM103" s="78" t="s">
+      <c r="BM103" s="78"/>
+      <c r="BN103" s="78" t="s">
         <v>872</v>
       </c>
-      <c r="BN103" s="78"/>
       <c r="BO103" s="78"/>
       <c r="BP103" s="78"/>
       <c r="BQ103" s="78"/>
       <c r="BR103" s="78"/>
       <c r="BS103" s="78"/>
-      <c r="BT103" s="78" t="s">
+      <c r="BT103" s="78"/>
+      <c r="BU103" s="78" t="s">
         <v>871</v>
       </c>
-      <c r="BU103" s="78" t="s">
+      <c r="BV103" s="78" t="s">
         <v>886</v>
       </c>
-      <c r="BV103" s="78" t="s">
+      <c r="BW103" s="78" t="s">
         <v>873</v>
       </c>
-      <c r="BW103" s="78"/>
-      <c r="BX103" s="117"/>
-      <c r="BY103" s="118"/>
+      <c r="BX103" s="78"/>
+      <c r="BY103" s="117"/>
       <c r="BZ103" s="118"/>
       <c r="CA103" s="118"/>
       <c r="CB103" s="118"/>
-      <c r="CC103" s="38" t="s">
+      <c r="CC103" s="118"/>
+      <c r="CD103" s="38" t="s">
         <v>513</v>
       </c>
-      <c r="CD103" s="143" t="s">
+      <c r="CE103" s="143" t="s">
         <v>514</v>
       </c>
-      <c r="CE103" s="38"/>
       <c r="CF103" s="38"/>
-      <c r="CG103" s="3"/>
-      <c r="CH103" s="29"/>
+      <c r="CG103" s="38"/>
+      <c r="CH103" s="3"/>
       <c r="CI103" s="29"/>
-      <c r="CJ103" s="77"/>
+      <c r="CJ103" s="29"/>
       <c r="CK103" s="77"/>
-      <c r="CL103" s="119"/>
+      <c r="CL103" s="77"/>
+      <c r="CM103" s="119"/>
     </row>
-    <row r="104" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C104" s="116"/>
       <c r="D104" s="116"/>
       <c r="E104" s="116"/>
@@ -24133,14 +24467,14 @@
         <v>878</v>
       </c>
       <c r="BL104" s="78"/>
-      <c r="BM104" s="78" t="s">
+      <c r="BM104" s="78"/>
+      <c r="BN104" s="78" t="s">
         <v>879</v>
       </c>
-      <c r="BN104" s="78"/>
-      <c r="BO104" s="78" t="s">
+      <c r="BO104" s="78"/>
+      <c r="BP104" s="78" t="s">
         <v>880</v>
       </c>
-      <c r="BP104" s="78"/>
       <c r="BQ104" s="78"/>
       <c r="BR104" s="78"/>
       <c r="BS104" s="78"/>
@@ -24148,27 +24482,28 @@
       <c r="BU104" s="78"/>
       <c r="BV104" s="78"/>
       <c r="BW104" s="78"/>
-      <c r="BX104" s="117"/>
-      <c r="BY104" s="118"/>
+      <c r="BX104" s="78"/>
+      <c r="BY104" s="117"/>
       <c r="BZ104" s="118"/>
       <c r="CA104" s="118"/>
       <c r="CB104" s="118"/>
-      <c r="CC104" s="38" t="s">
+      <c r="CC104" s="118"/>
+      <c r="CD104" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="CD104" s="38" t="s">
+      <c r="CE104" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="CE104" s="46"/>
       <c r="CF104" s="46"/>
-      <c r="CG104" s="48"/>
-      <c r="CH104" s="29"/>
+      <c r="CG104" s="46"/>
+      <c r="CH104" s="48"/>
       <c r="CI104" s="29"/>
-      <c r="CJ104" s="77"/>
+      <c r="CJ104" s="29"/>
       <c r="CK104" s="77"/>
-      <c r="CL104" s="119"/>
+      <c r="CL104" s="77"/>
+      <c r="CM104" s="119"/>
     </row>
-    <row r="105" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C105" s="116"/>
       <c r="D105" s="116"/>
       <c r="E105" s="116"/>
@@ -24225,14 +24560,14 @@
         <v>882</v>
       </c>
       <c r="BL105" s="78"/>
-      <c r="BM105" s="78" t="s">
+      <c r="BM105" s="78"/>
+      <c r="BN105" s="78" t="s">
         <v>883</v>
       </c>
-      <c r="BN105" s="78"/>
-      <c r="BO105" s="78" t="s">
+      <c r="BO105" s="78"/>
+      <c r="BP105" s="78" t="s">
         <v>881</v>
       </c>
-      <c r="BP105" s="78"/>
       <c r="BQ105" s="78"/>
       <c r="BR105" s="78"/>
       <c r="BS105" s="78"/>
@@ -24240,26 +24575,27 @@
       <c r="BU105" s="78"/>
       <c r="BV105" s="78"/>
       <c r="BW105" s="78"/>
-      <c r="BX105" s="117"/>
-      <c r="BY105" s="118"/>
+      <c r="BX105" s="78"/>
+      <c r="BY105" s="117"/>
       <c r="BZ105" s="118"/>
       <c r="CA105" s="118"/>
       <c r="CB105" s="118"/>
-      <c r="CC105" s="46" t="s">
+      <c r="CC105" s="118"/>
+      <c r="CD105" s="46" t="s">
         <v>841</v>
       </c>
-      <c r="CD105" s="159" t="s">
+      <c r="CE105" s="159" t="s">
         <v>840</v>
       </c>
-      <c r="CE105" s="78"/>
       <c r="CF105" s="78"/>
-      <c r="CH105" s="116"/>
+      <c r="CG105" s="78"/>
       <c r="CI105" s="116"/>
-      <c r="CJ105" s="77"/>
+      <c r="CJ105" s="116"/>
       <c r="CK105" s="77"/>
-      <c r="CL105" s="119"/>
+      <c r="CL105" s="77"/>
+      <c r="CM105" s="119"/>
     </row>
-    <row r="106" spans="1:90" s="115" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:91" s="115" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C106" s="116"/>
       <c r="D106" s="116"/>
       <c r="E106" s="116"/>
@@ -24321,24 +24657,25 @@
       <c r="BU106" s="78"/>
       <c r="BV106" s="78"/>
       <c r="BW106" s="78"/>
-      <c r="BX106" s="117"/>
-      <c r="BY106" s="118"/>
+      <c r="BX106" s="78"/>
+      <c r="BY106" s="117"/>
       <c r="BZ106" s="118"/>
       <c r="CA106" s="118"/>
       <c r="CB106" s="118"/>
-      <c r="CC106" s="142">
+      <c r="CC106" s="118"/>
+      <c r="CD106" s="142">
         <v>286370</v>
       </c>
-      <c r="CD106" s="162" t="s">
+      <c r="CE106" s="162" t="s">
         <v>842</v>
       </c>
-      <c r="CE106" s="78"/>
       <c r="CF106" s="78"/>
-      <c r="CH106" s="116"/>
+      <c r="CG106" s="78"/>
       <c r="CI106" s="116"/>
-      <c r="CJ106" s="77"/>
+      <c r="CJ106" s="116"/>
       <c r="CK106" s="77"/>
-      <c r="CL106" s="119"/>
+      <c r="CL106" s="77"/>
+      <c r="CM106" s="119"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
